--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -28571,7 +28571,7 @@
         <v>37500</v>
       </c>
       <c r="F527" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G527" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -1761,7 +1761,7 @@
         <v>20900</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>5800</v>
       </c>
       <c r="F66" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -5451,7 +5451,7 @@
         <v>5500</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -10279,7 +10279,7 @@
         <v>4000</v>
       </c>
       <c r="F185" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -16249,7 +16249,7 @@
         <v>13700</v>
       </c>
       <c r="F296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G296" t="n">
         <v>0</v>
@@ -23365,7 +23365,7 @@
         <v>2000</v>
       </c>
       <c r="F430" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G430" t="n">
         <v>0</v>
@@ -23851,7 +23851,7 @@
         <v>3300</v>
       </c>
       <c r="F439" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G439" t="n">
         <v>0</v>
@@ -24171,7 +24171,7 @@
         <v>2500</v>
       </c>
       <c r="F445" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G445" t="n">
         <v>0</v>
@@ -24981,7 +24981,7 @@
         <v>9200</v>
       </c>
       <c r="F460" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G460" t="n">
         <v>0</v>
@@ -28571,7 +28571,7 @@
         <v>37500</v>
       </c>
       <c r="F527" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G527" t="n">
         <v>0</v>
@@ -30129,7 +30129,7 @@
         <v>1008.4</v>
       </c>
       <c r="F556" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G556" t="n">
         <v>0</v>
@@ -31355,7 +31355,7 @@
         <v>1200</v>
       </c>
       <c r="F579" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G579" t="n">
         <v>0</v>
@@ -31517,7 +31517,7 @@
         <v>2600</v>
       </c>
       <c r="F582" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G582" t="n">
         <v>0</v>
@@ -31737,7 +31737,7 @@
         <v>2500</v>
       </c>
       <c r="F586" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G586" t="n">
         <v>0</v>
@@ -32613,7 +32613,7 @@
         <v>2200</v>
       </c>
       <c r="F602" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G602" t="n">
         <v>0</v>
@@ -32883,7 +32883,7 @@
         <v>8800</v>
       </c>
       <c r="F607" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G607" t="n">
         <v>0</v>
@@ -39687,7 +39687,7 @@
         <v>1345</v>
       </c>
       <c r="F735" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G735" t="n">
         <v>0</v>
@@ -42593,7 +42593,7 @@
         <v>18200</v>
       </c>
       <c r="F790" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G790" t="n">
         <v>0</v>
@@ -46975,7 +46975,7 @@
         <v>2700</v>
       </c>
       <c r="F871" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G871" t="n">
         <v>0</v>
@@ -48583,7 +48583,7 @@
         <v>3500</v>
       </c>
       <c r="F901" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G901" t="n">
         <v>0</v>
@@ -51369,7 +51369,7 @@
         <v>9200</v>
       </c>
       <c r="F954" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G954" t="n">
         <v>0</v>
@@ -52894,7 +52894,7 @@
         <v>1500</v>
       </c>
       <c r="F982" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G982" t="n">
         <v>0</v>
@@ -53758,7 +53758,7 @@
         <v>924</v>
       </c>
       <c r="F998" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G998" t="n">
         <v>0</v>
@@ -55670,7 +55670,7 @@
         <v>3500</v>
       </c>
       <c r="F1034" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1034" t="n">
         <v>0</v>
@@ -64564,7 +64564,7 @@
         <v>32700</v>
       </c>
       <c r="F1199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1199" t="n">
         <v>0</v>
@@ -72172,7 +72172,7 @@
         <v>3800</v>
       </c>
       <c r="F1345" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G1345" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -5073,7 +5073,7 @@
         <v>12200</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -11747,7 +11747,7 @@
         <v>4800</v>
       </c>
       <c r="F213" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -12569,7 +12569,7 @@
         <v>4500</v>
       </c>
       <c r="F228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -13969,7 +13969,7 @@
         <v>672</v>
       </c>
       <c r="F254" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -17017,7 +17017,7 @@
         <v>3800</v>
       </c>
       <c r="F310" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G310" t="n">
         <v>0</v>
@@ -22193,7 +22193,7 @@
         <v>1500</v>
       </c>
       <c r="F408" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G408" t="n">
         <v>0</v>
@@ -22251,7 +22251,7 @@
         <v>7900</v>
       </c>
       <c r="F409" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G409" t="n">
         <v>0</v>
@@ -23631,7 +23631,7 @@
         <v>2900</v>
       </c>
       <c r="F435" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G435" t="n">
         <v>0</v>
@@ -24981,7 +24981,7 @@
         <v>9200</v>
       </c>
       <c r="F460" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G460" t="n">
         <v>0</v>
@@ -25093,7 +25093,7 @@
         <v>10900</v>
       </c>
       <c r="F462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G462" t="n">
         <v>0</v>
@@ -26967,7 +26967,7 @@
         <v>504.2</v>
       </c>
       <c r="F497" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G497" t="n">
         <v>0</v>
@@ -32115,7 +32115,7 @@
         <v>2200</v>
       </c>
       <c r="F593" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G593" t="n">
         <v>0</v>
@@ -32725,7 +32725,7 @@
         <v>2900</v>
       </c>
       <c r="F604" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G604" t="n">
         <v>0</v>
@@ -44299,7 +44299,7 @@
         <v>7000</v>
       </c>
       <c r="F821" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G821" t="n">
         <v>0</v>
@@ -46975,7 +46975,7 @@
         <v>2700</v>
       </c>
       <c r="F871" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G871" t="n">
         <v>0</v>
@@ -51311,7 +51311,7 @@
         <v>2200</v>
       </c>
       <c r="F953" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G953" t="n">
         <v>0</v>
@@ -55072,7 +55072,7 @@
         <v>3200</v>
       </c>
       <c r="F1023" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1023" t="n">
         <v>0</v>
@@ -55670,7 +55670,7 @@
         <v>3500</v>
       </c>
       <c r="F1034" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G1034" t="n">
         <v>0</v>
@@ -56920,7 +56920,7 @@
         <v>9500</v>
       </c>
       <c r="F1057" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1057" t="n">
         <v>0</v>
@@ -60348,7 +60348,7 @@
         <v>6300</v>
       </c>
       <c r="F1121" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G1121" t="n">
         <v>0</v>
@@ -64066,7 +64066,7 @@
         <v>3000</v>
       </c>
       <c r="F1190" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1190" t="n">
         <v>0</v>
@@ -64182,7 +64182,7 @@
         <v>4800</v>
       </c>
       <c r="F1192" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1192" t="n">
         <v>0</v>
@@ -66858,7 +66858,7 @@
         <v>2200</v>
       </c>
       <c r="F1242" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1242" t="n">
         <v>0</v>
@@ -75522,7 +75522,7 @@
         <v>2500</v>
       </c>
       <c r="F1410" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G1410" t="n">
         <v>0</v>
@@ -77036,7 +77036,7 @@
         <v>10900</v>
       </c>
       <c r="F1439" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1439" t="n">
         <v>0</v>
@@ -80166,7 +80166,7 @@
         <v>6200</v>
       </c>
       <c r="F1500" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1500" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -3843,7 +3843,7 @@
         <v>1800</v>
       </c>
       <c r="F65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -10167,7 +10167,7 @@
         <v>2500</v>
       </c>
       <c r="F183" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -19655,7 +19655,7 @@
         <v>25000</v>
       </c>
       <c r="F361" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G361" t="n">
         <v>0</v>
@@ -31243,7 +31243,7 @@
         <v>2700</v>
       </c>
       <c r="F577" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G577" t="n">
         <v>0</v>
@@ -44025,7 +44025,7 @@
         <v>20500</v>
       </c>
       <c r="F816" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G816" t="n">
         <v>0</v>
@@ -50275,7 +50275,7 @@
         <v>2300</v>
       </c>
       <c r="F933" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G933" t="n">
         <v>0</v>
@@ -66858,7 +66858,7 @@
         <v>2200</v>
       </c>
       <c r="F1242" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1242" t="n">
         <v>0</v>
@@ -75776,7 +75776,7 @@
         <v>6300</v>
       </c>
       <c r="F1415" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1415" t="n">
         <v>0</v>
@@ -80466,7 +80466,7 @@
         <v>5400</v>
       </c>
       <c r="F1506" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1506" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -14185,7 +14185,7 @@
         <v>840</v>
       </c>
       <c r="F258" t="n">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -19093,7 +19093,7 @@
         <v>43200</v>
       </c>
       <c r="F350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G350" t="n">
         <v>0</v>
@@ -43245,7 +43245,7 @@
         <v>6500</v>
       </c>
       <c r="F802" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G802" t="n">
         <v>0</v>
@@ -80516,7 +80516,7 @@
         <v>5500</v>
       </c>
       <c r="F1507" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G1507" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1509"/>
+  <dimension ref="A1:N1512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5451,7 +5451,7 @@
         <v>5500</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -23631,7 +23631,7 @@
         <v>2900</v>
       </c>
       <c r="F435" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G435" t="n">
         <v>0</v>
@@ -28571,7 +28571,7 @@
         <v>37500</v>
       </c>
       <c r="F527" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G527" t="n">
         <v>0</v>
@@ -31625,7 +31625,7 @@
         <v>2800</v>
       </c>
       <c r="F584" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G584" t="n">
         <v>0</v>
@@ -37721,7 +37721,7 @@
         <v>2200</v>
       </c>
       <c r="F698" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="G698" t="n">
         <v>0</v>
@@ -60348,7 +60348,7 @@
         <v>6300</v>
       </c>
       <c r="F1121" t="n">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="G1121" t="n">
         <v>0</v>
@@ -64564,7 +64564,7 @@
         <v>32700</v>
       </c>
       <c r="F1199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1199" t="n">
         <v>0</v>
@@ -72716,25 +72716,21 @@
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>Hidraplus 75 zinc uva 400ml</t>
-        </is>
-      </c>
-      <c r="C1356" t="inlineStr">
-        <is>
-          <t>7702057010928</t>
-        </is>
-      </c>
+          <t>HEPATODREN JARABE FCO X 240ML</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr"/>
       <c r="D1356" t="inlineStr"/>
       <c r="E1356" t="n">
-        <v>10600</v>
+        <v>34500</v>
       </c>
       <c r="F1356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1356" t="n">
         <v>0</v>
@@ -72770,21 +72766,21 @@
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
+          <t>HEPATODREN X 60 CAPSULAS</t>
         </is>
       </c>
       <c r="C1357" t="inlineStr"/>
       <c r="D1357" t="inlineStr"/>
       <c r="E1357" t="n">
-        <v>15900</v>
+        <v>58300</v>
       </c>
       <c r="F1357" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1357" t="n">
         <v>0</v>
@@ -72820,22 +72816,22 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
+          <t>Hidraplus 75 zinc uva 400ml</t>
         </is>
       </c>
       <c r="C1358" t="inlineStr">
         <is>
-          <t>77099475597789</t>
+          <t>7702057010928</t>
         </is>
       </c>
       <c r="D1358" t="inlineStr"/>
       <c r="E1358" t="n">
-        <v>28000</v>
+        <v>10600</v>
       </c>
       <c r="F1358" t="n">
         <v>0</v>
@@ -72874,22 +72870,18 @@
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>Hidroxicina 0.25 JBE x 120 ML</t>
-        </is>
-      </c>
-      <c r="C1359" t="inlineStr">
-        <is>
-          <t>7707035540596</t>
-        </is>
-      </c>
+          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr"/>
       <c r="D1359" t="inlineStr"/>
       <c r="E1359" t="n">
-        <v>11000</v>
+        <v>15900</v>
       </c>
       <c r="F1359" t="n">
         <v>2</v>
@@ -72928,21 +72920,25 @@
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
-        </is>
-      </c>
-      <c r="C1360" t="inlineStr"/>
+          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>77099475597789</t>
+        </is>
+      </c>
       <c r="D1360" t="inlineStr"/>
       <c r="E1360" t="n">
-        <v>4500</v>
+        <v>28000</v>
       </c>
       <c r="F1360" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1360" t="n">
         <v>0</v>
@@ -72978,21 +72974,25 @@
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1361" t="inlineStr"/>
+          <t>Hidroxicina 0.25 JBE x 120 ML</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>7707035540596</t>
+        </is>
+      </c>
       <c r="D1361" t="inlineStr"/>
       <c r="E1361" t="n">
-        <v>6900</v>
+        <v>11000</v>
       </c>
       <c r="F1361" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1361" t="n">
         <v>0</v>
@@ -73028,21 +73028,21 @@
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
+          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
         </is>
       </c>
       <c r="C1362" t="inlineStr"/>
       <c r="D1362" t="inlineStr"/>
       <c r="E1362" t="n">
-        <v>12000</v>
+        <v>4500</v>
       </c>
       <c r="F1362" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1362" t="n">
         <v>0</v>
@@ -73078,21 +73078,21 @@
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>Hylo Gel</t>
+          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
         </is>
       </c>
       <c r="C1363" t="inlineStr"/>
       <c r="D1363" t="inlineStr"/>
       <c r="E1363" t="n">
-        <v>131600</v>
+        <v>6900</v>
       </c>
       <c r="F1363" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1363" t="n">
         <v>0</v>
@@ -73128,25 +73128,21 @@
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>IBUPROFENO 400MG/ GENFAR</t>
-        </is>
-      </c>
-      <c r="C1364" t="inlineStr">
-        <is>
-          <t>7702605101498</t>
-        </is>
-      </c>
+          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr"/>
       <c r="D1364" t="inlineStr"/>
       <c r="E1364" t="n">
-        <v>4400</v>
+        <v>12000</v>
       </c>
       <c r="F1364" t="n">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="G1364" t="n">
         <v>0</v>
@@ -73182,22 +73178,18 @@
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>Ibuprofeno 800mg AG</t>
-        </is>
-      </c>
-      <c r="C1365" t="inlineStr">
-        <is>
-          <t>7706569000385</t>
-        </is>
-      </c>
+          <t>Hylo Gel</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr"/>
       <c r="D1365" t="inlineStr"/>
       <c r="E1365" t="n">
-        <v>800</v>
+        <v>131600</v>
       </c>
       <c r="F1365" t="n">
         <v>0</v>
@@ -73236,25 +73228,25 @@
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
+          <t>IBUPROFENO 400MG/ GENFAR</t>
         </is>
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>7705959885229</t>
+          <t>7702605101498</t>
         </is>
       </c>
       <c r="D1366" t="inlineStr"/>
       <c r="E1366" t="n">
-        <v>17900</v>
+        <v>4400</v>
       </c>
       <c r="F1366" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="G1366" t="n">
         <v>0</v>
@@ -73290,25 +73282,25 @@
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>ICE POWER 30 GR GEL COSMETICA</t>
+          <t>Ibuprofeno 800mg AG</t>
         </is>
       </c>
       <c r="C1367" t="inlineStr">
         <is>
-          <t>737186238889</t>
+          <t>7706569000385</t>
         </is>
       </c>
       <c r="D1367" t="inlineStr"/>
       <c r="E1367" t="n">
-        <v>12521.008403</v>
+        <v>800</v>
       </c>
       <c r="F1367" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1367" t="n">
         <v>0</v>
@@ -73336,7 +73328,7 @@
       </c>
       <c r="M1367" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1367" t="inlineStr"/>
@@ -73344,21 +73336,25 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
-        </is>
-      </c>
-      <c r="C1368" t="inlineStr"/>
+          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>7705959885229</t>
+        </is>
+      </c>
       <c r="D1368" t="inlineStr"/>
       <c r="E1368" t="n">
-        <v>38900</v>
+        <v>17900</v>
       </c>
       <c r="F1368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1368" t="n">
         <v>0</v>
@@ -73394,21 +73390,25 @@
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
-        </is>
-      </c>
-      <c r="C1369" t="inlineStr"/>
+          <t>ICE POWER 30 GR GEL COSMETICA</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>737186238889</t>
+        </is>
+      </c>
       <c r="D1369" t="inlineStr"/>
       <c r="E1369" t="n">
-        <v>38900</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1369" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1369" t="n">
         <v>0</v>
@@ -73436,7 +73436,7 @@
       </c>
       <c r="M1369" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1369" t="inlineStr"/>
@@ -73444,21 +73444,21 @@
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
+          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
         </is>
       </c>
       <c r="C1370" t="inlineStr"/>
       <c r="D1370" t="inlineStr"/>
       <c r="E1370" t="n">
-        <v>8235.294118</v>
+        <v>38900</v>
       </c>
       <c r="F1370" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1370" t="n">
         <v>0</v>
@@ -73486,7 +73486,7 @@
       </c>
       <c r="M1370" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1370" t="inlineStr"/>
@@ -73494,18 +73494,18 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
+          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
         </is>
       </c>
       <c r="C1371" t="inlineStr"/>
       <c r="D1371" t="inlineStr"/>
       <c r="E1371" t="n">
-        <v>9831.932773</v>
+        <v>38900</v>
       </c>
       <c r="F1371" t="n">
         <v>1</v>
@@ -73536,7 +73536,7 @@
       </c>
       <c r="M1371" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1371" t="inlineStr"/>
@@ -73544,21 +73544,21 @@
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
+          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
         </is>
       </c>
       <c r="C1372" t="inlineStr"/>
       <c r="D1372" t="inlineStr"/>
       <c r="E1372" t="n">
-        <v>4201.680672</v>
+        <v>8235.294118</v>
       </c>
       <c r="F1372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1372" t="n">
         <v>0</v>
@@ -73594,21 +73594,21 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
+          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
         </is>
       </c>
       <c r="C1373" t="inlineStr"/>
       <c r="D1373" t="inlineStr"/>
       <c r="E1373" t="n">
-        <v>4201.680672</v>
+        <v>9831.932773</v>
       </c>
       <c r="F1373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1373" t="n">
         <v>0</v>
@@ -73644,18 +73644,18 @@
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>JABON PROTEX HERBAL 110GR</t>
+          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
         </is>
       </c>
       <c r="C1374" t="inlineStr"/>
       <c r="D1374" t="inlineStr"/>
       <c r="E1374" t="n">
-        <v>4537.815126</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1374" t="n">
         <v>2</v>
@@ -73694,22 +73694,18 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>JARABE ZETYGRIP FCO 60ML</t>
-        </is>
-      </c>
-      <c r="C1375" t="inlineStr">
-        <is>
-          <t>7709805542830</t>
-        </is>
-      </c>
+          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr"/>
       <c r="D1375" t="inlineStr"/>
       <c r="E1375" t="n">
-        <v>14000</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1375" t="n">
         <v>2</v>
@@ -73740,7 +73736,7 @@
       </c>
       <c r="M1375" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1375" t="inlineStr"/>
@@ -73748,21 +73744,21 @@
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>JERINGA DE 50ML</t>
+          <t>JABON PROTEX HERBAL 110GR</t>
         </is>
       </c>
       <c r="C1376" t="inlineStr"/>
       <c r="D1376" t="inlineStr"/>
       <c r="E1376" t="n">
-        <v>2500</v>
+        <v>4537.815126</v>
       </c>
       <c r="F1376" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1376" t="n">
         <v>0</v>
@@ -73790,7 +73786,7 @@
       </c>
       <c r="M1376" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1376" t="inlineStr"/>
@@ -73798,21 +73794,25 @@
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>Jeringa desechable estéril 20ml impormedicas</t>
-        </is>
-      </c>
-      <c r="C1377" t="inlineStr"/>
+          <t>JARABE ZETYGRIP FCO 60ML</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>7709805542830</t>
+        </is>
+      </c>
       <c r="D1377" t="inlineStr"/>
       <c r="E1377" t="n">
-        <v>920</v>
+        <v>14000</v>
       </c>
       <c r="F1377" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G1377" t="n">
         <v>0</v>
@@ -73840,7 +73840,7 @@
       </c>
       <c r="M1377" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1377" t="inlineStr"/>
@@ -73848,21 +73848,21 @@
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
+          <t>JERINGA DE 50ML</t>
         </is>
       </c>
       <c r="C1378" t="inlineStr"/>
       <c r="D1378" t="inlineStr"/>
       <c r="E1378" t="n">
-        <v>1100</v>
+        <v>2500</v>
       </c>
       <c r="F1378" t="n">
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="G1378" t="n">
         <v>0</v>
@@ -73898,21 +73898,21 @@
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>Kelocate</t>
+          <t>Jeringa desechable estéril 20ml impormedicas</t>
         </is>
       </c>
       <c r="C1379" t="inlineStr"/>
       <c r="D1379" t="inlineStr"/>
       <c r="E1379" t="n">
-        <v>180000</v>
+        <v>920</v>
       </c>
       <c r="F1379" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G1379" t="n">
         <v>0</v>
@@ -73940,7 +73940,7 @@
       </c>
       <c r="M1379" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1379" t="inlineStr"/>
@@ -73948,25 +73948,21 @@
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
-        </is>
-      </c>
-      <c r="C1380" t="inlineStr">
-        <is>
-          <t>7702057073695</t>
-        </is>
-      </c>
+          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr"/>
       <c r="D1380" t="inlineStr"/>
       <c r="E1380" t="n">
-        <v>19500</v>
+        <v>1100</v>
       </c>
       <c r="F1380" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G1380" t="n">
         <v>0</v>
@@ -74002,22 +73998,18 @@
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
-        </is>
-      </c>
-      <c r="C1381" t="inlineStr">
-        <is>
-          <t>7709947559772</t>
-        </is>
-      </c>
+          <t>Kelocate</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr"/>
       <c r="D1381" t="inlineStr"/>
       <c r="E1381" t="n">
-        <v>15000</v>
+        <v>180000</v>
       </c>
       <c r="F1381" t="n">
         <v>0</v>
@@ -74056,18 +74048,22 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
-        </is>
-      </c>
-      <c r="C1382" t="inlineStr"/>
+          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>7702057073695</t>
+        </is>
+      </c>
       <c r="D1382" t="inlineStr"/>
       <c r="E1382" t="n">
-        <v>71000</v>
+        <v>19500</v>
       </c>
       <c r="F1382" t="n">
         <v>0</v>
@@ -74106,25 +74102,25 @@
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>Levotiroxina 100mcg MK</t>
+          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
         </is>
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>7702057715908</t>
+          <t>7709947559772</t>
         </is>
       </c>
       <c r="D1383" t="inlineStr"/>
       <c r="E1383" t="n">
-        <v>27900</v>
+        <v>15000</v>
       </c>
       <c r="F1383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1383" t="n">
         <v>0</v>
@@ -74160,21 +74156,21 @@
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>LIMA MAYOMI 10/180</t>
+          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
         </is>
       </c>
       <c r="C1384" t="inlineStr"/>
       <c r="D1384" t="inlineStr"/>
       <c r="E1384" t="n">
-        <v>3900</v>
+        <v>71000</v>
       </c>
       <c r="F1384" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1384" t="n">
         <v>0</v>
@@ -74210,21 +74206,25 @@
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
-        </is>
-      </c>
-      <c r="C1385" t="inlineStr"/>
+          <t>Levotiroxina 100mcg MK</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>7702057715908</t>
+        </is>
+      </c>
       <c r="D1385" t="inlineStr"/>
       <c r="E1385" t="n">
-        <v>16807</v>
+        <v>27900</v>
       </c>
       <c r="F1385" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1385" t="n">
         <v>0</v>
@@ -74252,7 +74252,7 @@
       </c>
       <c r="M1385" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1385" t="inlineStr"/>
@@ -74260,18 +74260,18 @@
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
+          <t>LIMA MAYOMI 10/180</t>
         </is>
       </c>
       <c r="C1386" t="inlineStr"/>
       <c r="D1386" t="inlineStr"/>
       <c r="E1386" t="n">
-        <v>15042.016807</v>
+        <v>3900</v>
       </c>
       <c r="F1386" t="n">
         <v>1</v>
@@ -74302,7 +74302,7 @@
       </c>
       <c r="M1386" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1386" t="inlineStr"/>
@@ -74310,21 +74310,21 @@
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>LISTERINE CUIDADO TOTAL 180ML</t>
+          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr"/>
       <c r="D1387" t="inlineStr"/>
       <c r="E1387" t="n">
-        <v>16386.554622</v>
+        <v>16807</v>
       </c>
       <c r="F1387" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1387" t="n">
         <v>0</v>
@@ -74360,21 +74360,21 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
+          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
         </is>
       </c>
       <c r="C1388" t="inlineStr"/>
       <c r="D1388" t="inlineStr"/>
       <c r="E1388" t="n">
-        <v>3500</v>
+        <v>15042.016807</v>
       </c>
       <c r="F1388" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G1388" t="n">
         <v>0</v>
@@ -74402,7 +74402,7 @@
       </c>
       <c r="M1388" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1388" t="inlineStr"/>
@@ -74410,21 +74410,21 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+          <t>LISTERINE CUIDADO TOTAL 180ML</t>
         </is>
       </c>
       <c r="C1389" t="inlineStr"/>
       <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="n">
-        <v>3500</v>
+        <v>16386.554622</v>
       </c>
       <c r="F1389" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1389" t="n">
         <v>0</v>
@@ -74452,7 +74452,7 @@
       </c>
       <c r="M1389" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1389" t="inlineStr"/>
@@ -74460,21 +74460,21 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
         </is>
       </c>
       <c r="C1390" t="inlineStr"/>
       <c r="D1390" t="inlineStr"/>
       <c r="E1390" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="F1390" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G1390" t="n">
         <v>0</v>
@@ -74510,22 +74510,18 @@
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>Losartan Tensofar 100 Mg</t>
-        </is>
-      </c>
-      <c r="C1391" t="inlineStr">
-        <is>
-          <t>7703546012119</t>
-        </is>
-      </c>
+          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr"/>
       <c r="D1391" t="inlineStr"/>
       <c r="E1391" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="F1391" t="n">
         <v>1</v>
@@ -74564,25 +74560,21 @@
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
-        </is>
-      </c>
-      <c r="C1392" t="inlineStr">
-        <is>
-          <t>7501007528939</t>
-        </is>
-      </c>
+          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr"/>
       <c r="D1392" t="inlineStr"/>
       <c r="E1392" t="n">
-        <v>18907.563025</v>
+        <v>4500</v>
       </c>
       <c r="F1392" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1392" t="n">
         <v>0</v>
@@ -74610,7 +74602,7 @@
       </c>
       <c r="M1392" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1392" t="inlineStr"/>
@@ -74618,21 +74610,25 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>MANTECA DE CACAO LABIAL LIMON</t>
-        </is>
-      </c>
-      <c r="C1393" t="inlineStr"/>
+          <t>Losartan Tensofar 100 Mg</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>7703546012119</t>
+        </is>
+      </c>
       <c r="D1393" t="inlineStr"/>
       <c r="E1393" t="n">
-        <v>3361.344538</v>
+        <v>5000</v>
       </c>
       <c r="F1393" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1393" t="n">
         <v>0</v>
@@ -74660,7 +74656,7 @@
       </c>
       <c r="M1393" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1393" t="inlineStr"/>
@@ -74668,18 +74664,22 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
-        </is>
-      </c>
-      <c r="C1394" t="inlineStr"/>
+          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>7501007528939</t>
+        </is>
+      </c>
       <c r="D1394" t="inlineStr"/>
       <c r="E1394" t="n">
-        <v>3361.344538</v>
+        <v>18907.563025</v>
       </c>
       <c r="F1394" t="n">
         <v>0</v>
@@ -74718,21 +74718,21 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>Mega sex</t>
+          <t>MANTECA DE CACAO LABIAL LIMON</t>
         </is>
       </c>
       <c r="C1395" t="inlineStr"/>
       <c r="D1395" t="inlineStr"/>
       <c r="E1395" t="n">
-        <v>3200</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1395" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G1395" t="n">
         <v>0</v>
@@ -74760,7 +74760,7 @@
       </c>
       <c r="M1395" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1395" t="inlineStr"/>
@@ -74768,26 +74768,18 @@
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>Melatonina 3mg</t>
-        </is>
-      </c>
-      <c r="C1396" t="inlineStr">
-        <is>
-          <t>7706849112906</t>
-        </is>
-      </c>
-      <c r="D1396" t="inlineStr">
-        <is>
-          <t>producto nuevo</t>
-        </is>
-      </c>
+          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr"/>
+      <c r="D1396" t="inlineStr"/>
       <c r="E1396" t="n">
-        <v>52000</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1396" t="n">
         <v>0</v>
@@ -74818,7 +74810,7 @@
       </c>
       <c r="M1396" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1396" t="inlineStr"/>
@@ -74826,25 +74818,21 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
-        </is>
-      </c>
-      <c r="C1397" t="inlineStr">
-        <is>
-          <t>7707529435209</t>
-        </is>
-      </c>
+          <t>Mega sex</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr"/>
       <c r="D1397" t="inlineStr"/>
       <c r="E1397" t="n">
-        <v>36000</v>
+        <v>3200</v>
       </c>
       <c r="F1397" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G1397" t="n">
         <v>0</v>
@@ -74880,22 +74868,26 @@
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>Meloxicam 15mg AG</t>
+          <t>Melatonina 3mg</t>
         </is>
       </c>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>7706569020437</t>
-        </is>
-      </c>
-      <c r="D1398" t="inlineStr"/>
+          <t>7706849112906</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>producto nuevo</t>
+        </is>
+      </c>
       <c r="E1398" t="n">
-        <v>1500</v>
+        <v>52000</v>
       </c>
       <c r="F1398" t="n">
         <v>0</v>
@@ -74934,21 +74926,25 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
-        </is>
-      </c>
-      <c r="C1399" t="inlineStr"/>
+          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>7707529435209</t>
+        </is>
+      </c>
       <c r="D1399" t="inlineStr"/>
       <c r="E1399" t="n">
-        <v>9700</v>
+        <v>36000</v>
       </c>
       <c r="F1399" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1399" t="n">
         <v>0</v>
@@ -74984,22 +74980,22 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>MELOXICAM COASPHARMA</t>
+          <t>Meloxicam 15mg AG</t>
         </is>
       </c>
       <c r="C1400" t="inlineStr">
         <is>
-          <t>7703712036253</t>
+          <t>7706569020437</t>
         </is>
       </c>
       <c r="D1400" t="inlineStr"/>
       <c r="E1400" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F1400" t="n">
         <v>0</v>
@@ -75028,31 +75024,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1400" t="inlineStr"/>
+      <c r="M1400" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1400" t="inlineStr"/>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>metformina 850 mg pisa</t>
-        </is>
-      </c>
-      <c r="C1401" t="inlineStr">
-        <is>
-          <t>7501125188039</t>
-        </is>
-      </c>
+          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr"/>
       <c r="D1401" t="inlineStr"/>
       <c r="E1401" t="n">
-        <v>5500</v>
+        <v>9700</v>
       </c>
       <c r="F1401" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G1401" t="n">
         <v>0</v>
@@ -75088,25 +75084,25 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10MG RECIPE</t>
+          <t>MELOXICAM COASPHARMA</t>
         </is>
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>7702195084355</t>
+          <t>7703712036253</t>
         </is>
       </c>
       <c r="D1402" t="inlineStr"/>
       <c r="E1402" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="F1402" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1402" t="n">
         <v>0</v>
@@ -75132,35 +75128,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1402" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1402" t="inlineStr"/>
       <c r="N1402" t="inlineStr"/>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>MICROPOR 1X3 Y</t>
+          <t>metformina 850 mg pisa</t>
         </is>
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>7707282990205</t>
+          <t>7501125188039</t>
         </is>
       </c>
       <c r="D1403" t="inlineStr"/>
       <c r="E1403" t="n">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="F1403" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G1403" t="n">
         <v>0</v>
@@ -75196,25 +75188,25 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>MICROPOR CINTA 1/2X5Y</t>
+          <t>METOCLOPRAMIDA 10MG RECIPE</t>
         </is>
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>7707282990182</t>
+          <t>7702195084355</t>
         </is>
       </c>
       <c r="D1404" t="inlineStr"/>
       <c r="E1404" t="n">
-        <v>3900</v>
+        <v>1000</v>
       </c>
       <c r="F1404" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G1404" t="n">
         <v>0</v>
@@ -75250,21 +75242,25 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>MICROPORE COLOR PIEL 2YARDAS</t>
-        </is>
-      </c>
-      <c r="C1405" t="inlineStr"/>
+          <t>MICROPOR 1X3 Y</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>7707282990205</t>
+        </is>
+      </c>
       <c r="D1405" t="inlineStr"/>
       <c r="E1405" t="n">
-        <v>3700</v>
+        <v>5300</v>
       </c>
       <c r="F1405" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1405" t="n">
         <v>0</v>
@@ -75300,21 +75296,25 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
-        </is>
-      </c>
-      <c r="C1406" t="inlineStr"/>
+          <t>MICROPOR CINTA 1/2X5Y</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>7707282990182</t>
+        </is>
+      </c>
       <c r="D1406" t="inlineStr"/>
       <c r="E1406" t="n">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="F1406" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G1406" t="n">
         <v>0</v>
@@ -75350,22 +75350,18 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>MIELTERTOS JARABE X 240ML</t>
-        </is>
-      </c>
-      <c r="C1407" t="inlineStr">
-        <is>
-          <t>7707232095608</t>
-        </is>
-      </c>
+          <t>MICROPORE COLOR PIEL 2YARDAS</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr"/>
       <c r="D1407" t="inlineStr"/>
       <c r="E1407" t="n">
-        <v>34500</v>
+        <v>3700</v>
       </c>
       <c r="F1407" t="n">
         <v>0</v>
@@ -75404,25 +75400,21 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
+          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
         </is>
       </c>
       <c r="C1408" t="inlineStr"/>
-      <c r="D1408" t="inlineStr">
-        <is>
-          <t>subio precio hector</t>
-        </is>
-      </c>
+      <c r="D1408" t="inlineStr"/>
       <c r="E1408" t="n">
-        <v>22700</v>
+        <v>4000</v>
       </c>
       <c r="F1408" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1408" t="n">
         <v>0</v>
@@ -75458,21 +75450,25 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
-        </is>
-      </c>
-      <c r="C1409" t="inlineStr"/>
+          <t>MIELTERTOS JARABE X 240ML</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>7707232095608</t>
+        </is>
+      </c>
       <c r="D1409" t="inlineStr"/>
       <c r="E1409" t="n">
-        <v>5500</v>
+        <v>34500</v>
       </c>
       <c r="F1409" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G1409" t="n">
         <v>0</v>
@@ -75508,21 +75504,25 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>NEOSALDINA TABLETA X UND</t>
+          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
         </is>
       </c>
       <c r="C1410" t="inlineStr"/>
-      <c r="D1410" t="inlineStr"/>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>subio precio hector</t>
+        </is>
+      </c>
       <c r="E1410" t="n">
-        <v>2500</v>
+        <v>22700</v>
       </c>
       <c r="F1410" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G1410" t="n">
         <v>0</v>
@@ -75558,21 +75558,21 @@
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>NIFEDIPINO 30MG NOVAMED</t>
+          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
         </is>
       </c>
       <c r="C1411" t="inlineStr"/>
       <c r="D1411" t="inlineStr"/>
       <c r="E1411" t="n">
-        <v>19000</v>
+        <v>5500</v>
       </c>
       <c r="F1411" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1411" t="n">
         <v>0</v>
@@ -75608,21 +75608,21 @@
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
+          <t>NEOSALDINA TABLETA X UND</t>
         </is>
       </c>
       <c r="C1412" t="inlineStr"/>
       <c r="D1412" t="inlineStr"/>
       <c r="E1412" t="n">
-        <v>23000</v>
+        <v>2500</v>
       </c>
       <c r="F1412" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G1412" t="n">
         <v>0</v>
@@ -75658,21 +75658,21 @@
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>NITOXIPAR X 6 TABLETAS</t>
+          <t>NIFEDIPINO 30MG NOVAMED</t>
         </is>
       </c>
       <c r="C1413" t="inlineStr"/>
       <c r="D1413" t="inlineStr"/>
       <c r="E1413" t="n">
-        <v>24500</v>
+        <v>19000</v>
       </c>
       <c r="F1413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1413" t="n">
         <v>0</v>
@@ -75708,18 +75708,18 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>NORAVER SPRAY CEREZA 120ML</t>
+          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
         </is>
       </c>
       <c r="C1414" t="inlineStr"/>
       <c r="D1414" t="inlineStr"/>
       <c r="E1414" t="n">
-        <v>52900</v>
+        <v>23000</v>
       </c>
       <c r="F1414" t="n">
         <v>1</v>
@@ -75758,25 +75758,21 @@
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
-        </is>
-      </c>
-      <c r="C1415" t="inlineStr">
-        <is>
-          <t>7702027041662</t>
-        </is>
-      </c>
+          <t>NITOXIPAR X 6 TABLETAS</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr"/>
       <c r="D1415" t="inlineStr"/>
       <c r="E1415" t="n">
-        <v>6300</v>
+        <v>24500</v>
       </c>
       <c r="F1415" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1415" t="n">
         <v>0</v>
@@ -75812,21 +75808,21 @@
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+          <t>NORAVER SPRAY CEREZA 120ML</t>
         </is>
       </c>
       <c r="C1416" t="inlineStr"/>
       <c r="D1416" t="inlineStr"/>
       <c r="E1416" t="n">
-        <v>8823.529412</v>
+        <v>52900</v>
       </c>
       <c r="F1416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1416" t="n">
         <v>0</v>
@@ -75854,7 +75850,7 @@
       </c>
       <c r="M1416" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1416" t="inlineStr"/>
@@ -75862,22 +75858,22 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
         </is>
       </c>
       <c r="C1417" t="inlineStr">
         <is>
-          <t>7702026158644</t>
+          <t>7702027041662</t>
         </is>
       </c>
       <c r="D1417" t="inlineStr"/>
       <c r="E1417" t="n">
-        <v>8823.529412</v>
+        <v>6300</v>
       </c>
       <c r="F1417" t="n">
         <v>0</v>
@@ -75908,7 +75904,7 @@
       </c>
       <c r="M1417" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1417" t="inlineStr"/>
@@ -75916,25 +75912,21 @@
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JBE 120ML</t>
-        </is>
-      </c>
-      <c r="C1418" t="inlineStr">
-        <is>
-          <t>7707355053363</t>
-        </is>
-      </c>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr"/>
       <c r="D1418" t="inlineStr"/>
       <c r="E1418" t="n">
-        <v>22700</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1418" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1418" t="n">
         <v>0</v>
@@ -75962,7 +75954,7 @@
       </c>
       <c r="M1418" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1418" t="inlineStr"/>
@@ -75970,22 +75962,22 @@
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
         </is>
       </c>
       <c r="C1419" t="inlineStr">
         <is>
-          <t>7707355053356</t>
+          <t>7702026158644</t>
         </is>
       </c>
       <c r="D1419" t="inlineStr"/>
       <c r="E1419" t="n">
-        <v>17200</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1419" t="n">
         <v>0</v>
@@ -76016,7 +76008,7 @@
       </c>
       <c r="M1419" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1419" t="inlineStr"/>
@@ -76024,18 +76016,22 @@
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>NUTRIBELL ACEITE DE COCO</t>
-        </is>
-      </c>
-      <c r="C1420" t="inlineStr"/>
+          <t>NOXPIRIN JUNIOR JBE 120ML</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>7707355053363</t>
+        </is>
+      </c>
       <c r="D1420" t="inlineStr"/>
       <c r="E1420" t="n">
-        <v>2700</v>
+        <v>22700</v>
       </c>
       <c r="F1420" t="n">
         <v>1</v>
@@ -76074,29 +76070,25 @@
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>Omega 3 6 9 suplemento totalmax</t>
+          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
         </is>
       </c>
       <c r="C1421" t="inlineStr">
         <is>
-          <t>7707529434974</t>
-        </is>
-      </c>
-      <c r="D1421" t="inlineStr">
-        <is>
-          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
-        </is>
-      </c>
+          <t>7707355053356</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr"/>
       <c r="E1421" t="n">
-        <v>35000</v>
+        <v>17200</v>
       </c>
       <c r="F1421" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1421" t="n">
         <v>0</v>
@@ -76132,21 +76124,21 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
+          <t>NUTRIBELL ACEITE DE COCO</t>
         </is>
       </c>
       <c r="C1422" t="inlineStr"/>
       <c r="D1422" t="inlineStr"/>
       <c r="E1422" t="n">
-        <v>5500</v>
+        <v>2700</v>
       </c>
       <c r="F1422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1422" t="n">
         <v>0</v>
@@ -76182,25 +76174,29 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
+          <t>Omega 3 6 9 suplemento totalmax</t>
         </is>
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>7707529435940</t>
-        </is>
-      </c>
-      <c r="D1423" t="inlineStr"/>
+          <t>7707529434974</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
+        </is>
+      </c>
       <c r="E1423" t="n">
         <v>35000</v>
       </c>
       <c r="F1423" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1423" t="n">
         <v>0</v>
@@ -76236,21 +76232,21 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
+          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
         </is>
       </c>
       <c r="C1424" t="inlineStr"/>
       <c r="D1424" t="inlineStr"/>
       <c r="E1424" t="n">
-        <v>48000</v>
+        <v>5500</v>
       </c>
       <c r="F1424" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1424" t="n">
         <v>0</v>
@@ -76286,25 +76282,25 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>OROCAL CALCIO 600MG</t>
-        </is>
-      </c>
-      <c r="C1425" t="inlineStr"/>
-      <c r="D1425" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>7707529435940</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="n">
-        <v>30500</v>
+        <v>35000</v>
       </c>
       <c r="F1425" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1425" t="n">
         <v>0</v>
@@ -76340,21 +76336,21 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>PALA DE MADERA RASPACALLO</t>
+          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
         </is>
       </c>
       <c r="C1426" t="inlineStr"/>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="n">
-        <v>4000</v>
+        <v>48000</v>
       </c>
       <c r="F1426" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1426" t="n">
         <v>0</v>
@@ -76390,21 +76386,25 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>PALO DE NARANJO X UNIDAD</t>
+          <t>OROCAL CALCIO 600MG</t>
         </is>
       </c>
       <c r="C1427" t="inlineStr"/>
-      <c r="D1427" t="inlineStr"/>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E1427" t="n">
-        <v>400</v>
+        <v>30500</v>
       </c>
       <c r="F1427" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G1427" t="n">
         <v>0</v>
@@ -76440,22 +76440,18 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
-        </is>
-      </c>
-      <c r="C1428" t="inlineStr">
-        <is>
-          <t>7704412170896</t>
-        </is>
-      </c>
+          <t>PALA DE MADERA RASPACALLO</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr"/>
       <c r="D1428" t="inlineStr"/>
       <c r="E1428" t="n">
-        <v>6200</v>
+        <v>4000</v>
       </c>
       <c r="F1428" t="n">
         <v>1</v>
@@ -76494,21 +76490,21 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+          <t>PALO DE NARANJO X UNIDAD</t>
         </is>
       </c>
       <c r="C1429" t="inlineStr"/>
       <c r="D1429" t="inlineStr"/>
       <c r="E1429" t="n">
-        <v>41176.470588</v>
+        <v>400</v>
       </c>
       <c r="F1429" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G1429" t="n">
         <v>0</v>
@@ -76536,7 +76532,7 @@
       </c>
       <c r="M1429" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1429" t="inlineStr"/>
@@ -76544,22 +76540,22 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Pañales Winny Etapa 5 X PAQUETE</t>
+          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
         </is>
       </c>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>7701021114174</t>
+          <t>7704412170896</t>
         </is>
       </c>
       <c r="D1430" t="inlineStr"/>
       <c r="E1430" t="n">
-        <v>41849</v>
+        <v>6200</v>
       </c>
       <c r="F1430" t="n">
         <v>1</v>
@@ -76590,7 +76586,7 @@
       </c>
       <c r="M1430" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1430" t="inlineStr"/>
@@ -76598,21 +76594,21 @@
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>PAÑALWINNY ETA 5 X 16 UND</t>
+          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
         </is>
       </c>
       <c r="C1431" t="inlineStr"/>
       <c r="D1431" t="inlineStr"/>
       <c r="E1431" t="n">
-        <v>24369.747899</v>
+        <v>41176.470588</v>
       </c>
       <c r="F1431" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1431" t="n">
         <v>0</v>
@@ -76648,21 +76644,25 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>pañitos humedos pequeñin 100unidades</t>
-        </is>
-      </c>
-      <c r="C1432" t="inlineStr"/>
+          <t>Pañales Winny Etapa 5 X PAQUETE</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>7701021114174</t>
+        </is>
+      </c>
       <c r="D1432" t="inlineStr"/>
       <c r="E1432" t="n">
-        <v>10925</v>
+        <v>41849</v>
       </c>
       <c r="F1432" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1432" t="n">
         <v>0</v>
@@ -76698,18 +76698,18 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
+          <t>PAÑALWINNY ETA 5 X 16 UND</t>
         </is>
       </c>
       <c r="C1433" t="inlineStr"/>
       <c r="D1433" t="inlineStr"/>
       <c r="E1433" t="n">
-        <v>14900</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1433" t="n">
         <v>2</v>
@@ -76740,7 +76740,7 @@
       </c>
       <c r="M1433" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1433" t="inlineStr"/>
@@ -76748,21 +76748,21 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>Panotil B x 8ML</t>
+          <t>pañitos humedos pequeñin 100unidades</t>
         </is>
       </c>
       <c r="C1434" t="inlineStr"/>
       <c r="D1434" t="inlineStr"/>
       <c r="E1434" t="n">
-        <v>26400</v>
+        <v>10925</v>
       </c>
       <c r="F1434" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1434" t="n">
         <v>0</v>
@@ -76790,7 +76790,7 @@
       </c>
       <c r="M1434" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1434" t="inlineStr"/>
@@ -76798,25 +76798,21 @@
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>PANTENE ACONDICIONADOR</t>
-        </is>
-      </c>
-      <c r="C1435" t="inlineStr">
-        <is>
-          <t>7500435153683</t>
-        </is>
-      </c>
+          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr"/>
       <c r="D1435" t="inlineStr"/>
       <c r="E1435" t="n">
-        <v>1500</v>
+        <v>14900</v>
       </c>
       <c r="F1435" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>
@@ -76852,21 +76848,21 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>Parche Ocular Colostol</t>
+          <t>Panotil B x 8ML</t>
         </is>
       </c>
       <c r="C1436" t="inlineStr"/>
       <c r="D1436" t="inlineStr"/>
       <c r="E1436" t="n">
-        <v>1300</v>
+        <v>26400</v>
       </c>
       <c r="F1436" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G1436" t="n">
         <v>0</v>
@@ -76902,25 +76898,25 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
+          <t>PANTENE ACONDICIONADOR</t>
         </is>
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>7501033957413</t>
+          <t>7500435153683</t>
         </is>
       </c>
       <c r="D1437" t="inlineStr"/>
       <c r="E1437" t="n">
-        <v>10600</v>
+        <v>1500</v>
       </c>
       <c r="F1437" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1437" t="n">
         <v>0</v>
@@ -76956,29 +76952,21 @@
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
-        </is>
-      </c>
-      <c r="C1438" t="inlineStr">
-        <is>
-          <t>7501033961557</t>
-        </is>
-      </c>
-      <c r="D1438" t="inlineStr">
-        <is>
-          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
-        </is>
-      </c>
+          <t>Parche Ocular Colostol</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr"/>
+      <c r="D1438" t="inlineStr"/>
       <c r="E1438" t="n">
-        <v>10900</v>
+        <v>1300</v>
       </c>
       <c r="F1438" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G1438" t="n">
         <v>0</v>
@@ -77014,29 +77002,25 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
         </is>
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>7501033957376</t>
-        </is>
-      </c>
-      <c r="D1439" t="inlineStr">
-        <is>
-          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
-        </is>
-      </c>
+          <t>7501033957413</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr"/>
       <c r="E1439" t="n">
-        <v>10900</v>
+        <v>10600</v>
       </c>
       <c r="F1439" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1439" t="n">
         <v>0</v>
@@ -77072,21 +77056,29 @@
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>PEGANTE GLUE X 10GR X UND</t>
-        </is>
-      </c>
-      <c r="C1440" t="inlineStr"/>
-      <c r="D1440" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>7501033961557</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
+        </is>
+      </c>
       <c r="E1440" t="n">
-        <v>2000</v>
+        <v>10900</v>
       </c>
       <c r="F1440" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1440" t="n">
         <v>0</v>
@@ -77122,21 +77114,29 @@
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>PEINETA COLA DE RATON METALICA</t>
-        </is>
-      </c>
-      <c r="C1441" t="inlineStr"/>
-      <c r="D1441" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>7501033957376</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+        </is>
+      </c>
       <c r="E1441" t="n">
-        <v>4700</v>
+        <v>10900</v>
       </c>
       <c r="F1441" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1441" t="n">
         <v>0</v>
@@ -77172,21 +77172,21 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>PERFILADORES DE CEJAS</t>
+          <t>PEGANTE GLUE X 10GR X UND</t>
         </is>
       </c>
       <c r="C1442" t="inlineStr"/>
       <c r="D1442" t="inlineStr"/>
       <c r="E1442" t="n">
-        <v>3900</v>
+        <v>2000</v>
       </c>
       <c r="F1442" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1442" t="n">
         <v>0</v>
@@ -77222,18 +77222,18 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
+          <t>PEINETA COLA DE RATON METALICA</t>
         </is>
       </c>
       <c r="C1443" t="inlineStr"/>
       <c r="D1443" t="inlineStr"/>
       <c r="E1443" t="n">
-        <v>27983.193277</v>
+        <v>4700</v>
       </c>
       <c r="F1443" t="n">
         <v>1</v>
@@ -77264,7 +77264,7 @@
       </c>
       <c r="M1443" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1443" t="inlineStr"/>
@@ -77272,21 +77272,21 @@
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+          <t>PERFILADORES DE CEJAS</t>
         </is>
       </c>
       <c r="C1444" t="inlineStr"/>
       <c r="D1444" t="inlineStr"/>
       <c r="E1444" t="n">
-        <v>20500</v>
+        <v>3900</v>
       </c>
       <c r="F1444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1444" t="n">
         <v>0</v>
@@ -77322,26 +77322,18 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>privatos miel limon la francol 120ml</t>
-        </is>
-      </c>
-      <c r="C1445" t="inlineStr">
-        <is>
-          <t>7702207163948</t>
-        </is>
-      </c>
-      <c r="D1445" t="inlineStr">
-        <is>
-          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
-        </is>
-      </c>
+          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr"/>
+      <c r="D1445" t="inlineStr"/>
       <c r="E1445" t="n">
-        <v>35900</v>
+        <v>27983.193277</v>
       </c>
       <c r="F1445" t="n">
         <v>1</v>
@@ -77372,7 +77364,7 @@
       </c>
       <c r="M1445" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1445" t="inlineStr"/>
@@ -77380,18 +77372,18 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
+          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
         </is>
       </c>
       <c r="C1446" t="inlineStr"/>
       <c r="D1446" t="inlineStr"/>
       <c r="E1446" t="n">
-        <v>0</v>
+        <v>20500</v>
       </c>
       <c r="F1446" t="n">
         <v>0</v>
@@ -77422,7 +77414,7 @@
       </c>
       <c r="M1446" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1446" t="inlineStr"/>
@@ -77430,18 +77422,26 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>PROTECTOR NOSOTRAS LARGOS</t>
-        </is>
-      </c>
-      <c r="C1447" t="inlineStr"/>
-      <c r="D1447" t="inlineStr"/>
+          <t>privatos miel limon la francol 120ml</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>7702207163948</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
+        </is>
+      </c>
       <c r="E1447" t="n">
-        <v>3700</v>
+        <v>35900</v>
       </c>
       <c r="F1447" t="n">
         <v>1</v>
@@ -77480,21 +77480,21 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>778</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
+          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
         </is>
       </c>
       <c r="C1448" t="inlineStr"/>
       <c r="D1448" t="inlineStr"/>
       <c r="E1448" t="n">
-        <v>8900</v>
+        <v>0</v>
       </c>
       <c r="F1448" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1448" t="n">
         <v>0</v>
@@ -77522,7 +77522,7 @@
       </c>
       <c r="M1448" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1448" t="inlineStr"/>
@@ -77530,21 +77530,21 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>Protector Solar Sunaid</t>
+          <t>PROTECTOR NOSOTRAS LARGOS</t>
         </is>
       </c>
       <c r="C1449" t="inlineStr"/>
       <c r="D1449" t="inlineStr"/>
       <c r="E1449" t="n">
-        <v>158000</v>
+        <v>3700</v>
       </c>
       <c r="F1449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1449" t="n">
         <v>0</v>
@@ -77580,25 +77580,21 @@
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Prueba de embarazo esfero</t>
-        </is>
-      </c>
-      <c r="C1450" t="inlineStr">
-        <is>
-          <t>7709299854228</t>
-        </is>
-      </c>
+          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr"/>
       <c r="D1450" t="inlineStr"/>
       <c r="E1450" t="n">
-        <v>16500</v>
+        <v>8900</v>
       </c>
       <c r="F1450" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1450" t="n">
         <v>0</v>
@@ -77634,25 +77630,21 @@
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Prueba de embarazo HCG cassette begut</t>
-        </is>
-      </c>
-      <c r="C1451" t="inlineStr">
-        <is>
-          <t>7707282990953</t>
-        </is>
-      </c>
+          <t>Protector Solar Sunaid</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr"/>
       <c r="D1451" t="inlineStr"/>
       <c r="E1451" t="n">
-        <v>8900</v>
+        <v>158000</v>
       </c>
       <c r="F1451" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G1451" t="n">
         <v>0</v>
@@ -77688,21 +77680,25 @@
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>PUSHER METALICO</t>
-        </is>
-      </c>
-      <c r="C1452" t="inlineStr"/>
+          <t>Prueba de embarazo esfero</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>7709299854228</t>
+        </is>
+      </c>
       <c r="D1452" t="inlineStr"/>
       <c r="E1452" t="n">
-        <v>4300</v>
+        <v>16500</v>
       </c>
       <c r="F1452" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1452" t="n">
         <v>0</v>
@@ -77738,25 +77734,25 @@
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Recolector de orina granandina</t>
+          <t>Prueba de embarazo HCG cassette begut</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>7707233050590</t>
+          <t>7707282990953</t>
         </is>
       </c>
       <c r="D1453" t="inlineStr"/>
       <c r="E1453" t="n">
-        <v>673</v>
+        <v>8900</v>
       </c>
       <c r="F1453" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="G1453" t="n">
         <v>0</v>
@@ -77784,7 +77780,7 @@
       </c>
       <c r="M1453" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1453" t="inlineStr"/>
@@ -77792,21 +77788,21 @@
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
+          <t>PUSHER METALICO</t>
         </is>
       </c>
       <c r="C1454" t="inlineStr"/>
       <c r="D1454" t="inlineStr"/>
       <c r="E1454" t="n">
-        <v>3820</v>
+        <v>4300</v>
       </c>
       <c r="F1454" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1454" t="n">
         <v>0</v>
@@ -77842,21 +77838,25 @@
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>RegistroManual - Registro manual</t>
-        </is>
-      </c>
-      <c r="C1455" t="inlineStr"/>
+          <t>Recolector de orina granandina</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>7707233050590</t>
+        </is>
+      </c>
       <c r="D1455" t="inlineStr"/>
       <c r="E1455" t="n">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="F1455" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G1455" t="n">
         <v>0</v>
@@ -77892,21 +77892,21 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>REMOVEDOR DE ESMALTE 60CC</t>
+          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
         </is>
       </c>
       <c r="C1456" t="inlineStr"/>
       <c r="D1456" t="inlineStr"/>
       <c r="E1456" t="n">
-        <v>3500</v>
+        <v>3820</v>
       </c>
       <c r="F1456" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1456" t="n">
         <v>0</v>
@@ -77942,25 +77942,21 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
-        </is>
-      </c>
-      <c r="C1457" t="inlineStr">
-        <is>
-          <t>7591005981270</t>
-        </is>
-      </c>
+          <t>RegistroManual - Registro manual</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr"/>
       <c r="D1457" t="inlineStr"/>
       <c r="E1457" t="n">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="F1457" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1457" t="n">
         <v>0</v>
@@ -77988,7 +77984,7 @@
       </c>
       <c r="M1457" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1457" t="inlineStr"/>
@@ -77996,25 +77992,21 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
-        </is>
-      </c>
-      <c r="C1458" t="inlineStr">
-        <is>
-          <t>7503051868245</t>
-        </is>
-      </c>
+          <t>REMOVEDOR DE ESMALTE 60CC</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr"/>
       <c r="D1458" t="inlineStr"/>
       <c r="E1458" t="n">
-        <v>20900</v>
+        <v>3500</v>
       </c>
       <c r="F1458" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1458" t="n">
         <v>0</v>
@@ -78050,25 +78042,25 @@
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
         </is>
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>7702057079642</t>
+          <t>7591005981270</t>
         </is>
       </c>
       <c r="D1459" t="inlineStr"/>
       <c r="E1459" t="n">
-        <v>13000</v>
+        <v>9500</v>
       </c>
       <c r="F1459" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1459" t="n">
         <v>0</v>
@@ -78104,21 +78096,25 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>Ryaltris Spray Nasal 240 dosis</t>
-        </is>
-      </c>
-      <c r="C1460" t="inlineStr"/>
+          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>7503051868245</t>
+        </is>
+      </c>
       <c r="D1460" t="inlineStr"/>
       <c r="E1460" t="n">
-        <v>216400</v>
+        <v>20900</v>
       </c>
       <c r="F1460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1460" t="n">
         <v>0</v>
@@ -78154,25 +78150,25 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+          <t>RISPERIDONA 1MG X 20 TABL MK</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>7706849116676</t>
+          <t>7702057079642</t>
         </is>
       </c>
       <c r="D1461" t="inlineStr"/>
       <c r="E1461" t="n">
-        <v>31500</v>
+        <v>13000</v>
       </c>
       <c r="F1461" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1461" t="n">
         <v>0</v>
@@ -78208,21 +78204,21 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>SCOBIT PURGANTE 60GR</t>
+          <t>Ryaltris Spray Nasal 240 dosis</t>
         </is>
       </c>
       <c r="C1462" t="inlineStr"/>
       <c r="D1462" t="inlineStr"/>
       <c r="E1462" t="n">
-        <v>15238.095238</v>
+        <v>216400</v>
       </c>
       <c r="F1462" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1462" t="n">
         <v>0</v>
@@ -78250,7 +78246,7 @@
       </c>
       <c r="M1462" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1462" t="inlineStr"/>
@@ -78258,21 +78254,25 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
-        </is>
-      </c>
-      <c r="C1463" t="inlineStr"/>
+          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>7706849116676</t>
+        </is>
+      </c>
       <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="n">
-        <v>6554.621849</v>
+        <v>31500</v>
       </c>
       <c r="F1463" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1463" t="n">
         <v>0</v>
@@ -78300,7 +78300,7 @@
       </c>
       <c r="M1463" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1463" t="inlineStr"/>
@@ -78308,25 +78308,21 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>SHAMPOO PANTENE COLAGENO</t>
-        </is>
-      </c>
-      <c r="C1464" t="inlineStr">
-        <is>
-          <t>7500435191500</t>
-        </is>
-      </c>
+          <t>SCOBIT PURGANTE 60GR</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr"/>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="n">
-        <v>1429</v>
+        <v>15238.095238</v>
       </c>
       <c r="F1464" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1464" t="n">
         <v>0</v>
@@ -78354,7 +78350,7 @@
       </c>
       <c r="M1464" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1464" t="inlineStr"/>
@@ -78362,21 +78358,21 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>SILDENAFIL 50MG TQ</t>
+          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
         </is>
       </c>
       <c r="C1465" t="inlineStr"/>
       <c r="D1465" t="inlineStr"/>
       <c r="E1465" t="n">
-        <v>5000</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1465" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1465" t="n">
         <v>0</v>
@@ -78404,7 +78400,7 @@
       </c>
       <c r="M1465" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1465" t="inlineStr"/>
@@ -78412,25 +78408,25 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>SILIMARINA 167MG EPANAT</t>
+          <t>SHAMPOO PANTENE COLAGENO</t>
         </is>
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>7706849115921</t>
+          <t>7500435191500</t>
         </is>
       </c>
       <c r="D1466" t="inlineStr"/>
       <c r="E1466" t="n">
-        <v>2000</v>
+        <v>1429</v>
       </c>
       <c r="F1466" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="G1466" t="n">
         <v>0</v>
@@ -78458,7 +78454,7 @@
       </c>
       <c r="M1466" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1466" t="inlineStr"/>
@@ -78466,18 +78462,18 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>SMECTA 3GR NARANJA S/B</t>
+          <t>SILDENAFIL 50MG TQ</t>
         </is>
       </c>
       <c r="C1467" t="inlineStr"/>
       <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="n">
-        <v>8900</v>
+        <v>5000</v>
       </c>
       <c r="F1467" t="n">
         <v>0</v>
@@ -78516,21 +78512,25 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>SONDA FOLEY 2 VIAS BAL #18</t>
-        </is>
-      </c>
-      <c r="C1468" t="inlineStr"/>
+          <t>SILIMARINA 167MG EPANAT</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>7706849115921</t>
+        </is>
+      </c>
       <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="n">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="F1468" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="G1468" t="n">
         <v>0</v>
@@ -78566,21 +78566,21 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>SONDA NELATON #6</t>
+          <t>SMECTA 3GR NARANJA S/B</t>
         </is>
       </c>
       <c r="C1469" t="inlineStr"/>
       <c r="D1469" t="inlineStr"/>
       <c r="E1469" t="n">
-        <v>2500</v>
+        <v>8900</v>
       </c>
       <c r="F1469" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1469" t="n">
         <v>0</v>
@@ -78616,21 +78616,21 @@
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>SPRAY NASAL MOMETASONA 18ML</t>
+          <t>SONDA FOLEY 2 VIAS BAL #18</t>
         </is>
       </c>
       <c r="C1470" t="inlineStr"/>
       <c r="D1470" t="inlineStr"/>
       <c r="E1470" t="n">
-        <v>36900</v>
+        <v>7500</v>
       </c>
       <c r="F1470" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1470" t="n">
         <v>0</v>
@@ -78666,25 +78666,21 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1471" t="inlineStr">
-        <is>
-          <t>7703712035034</t>
-        </is>
-      </c>
+          <t>SONDA NELATON #6</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr"/>
       <c r="D1471" t="inlineStr"/>
       <c r="E1471" t="n">
-        <v>14800</v>
+        <v>2500</v>
       </c>
       <c r="F1471" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1471" t="n">
         <v>0</v>
@@ -78720,18 +78716,18 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
+          <t>SPRAY NASAL MOMETASONA 18ML</t>
         </is>
       </c>
       <c r="C1472" t="inlineStr"/>
       <c r="D1472" t="inlineStr"/>
       <c r="E1472" t="n">
-        <v>3781.512605</v>
+        <v>36900</v>
       </c>
       <c r="F1472" t="n">
         <v>1</v>
@@ -78762,7 +78758,7 @@
       </c>
       <c r="M1472" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1472" t="inlineStr"/>
@@ -78770,18 +78766,22 @@
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
-        </is>
-      </c>
-      <c r="C1473" t="inlineStr"/>
+          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>7703712035034</t>
+        </is>
+      </c>
       <c r="D1473" t="inlineStr"/>
       <c r="E1473" t="n">
-        <v>5210.084034</v>
+        <v>14800</v>
       </c>
       <c r="F1473" t="n">
         <v>0</v>
@@ -78812,7 +78812,7 @@
       </c>
       <c r="M1473" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1473" t="inlineStr"/>
@@ -78820,18 +78820,18 @@
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
+          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
         </is>
       </c>
       <c r="C1474" t="inlineStr"/>
       <c r="D1474" t="inlineStr"/>
       <c r="E1474" t="n">
-        <v>8319.327730999999</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1474" t="n">
         <v>1</v>
@@ -78870,21 +78870,21 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>SULZINC SUSP X 80ML HUMAX</t>
+          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
         </is>
       </c>
       <c r="C1475" t="inlineStr"/>
       <c r="D1475" t="inlineStr"/>
       <c r="E1475" t="n">
-        <v>22400</v>
+        <v>5210.084034</v>
       </c>
       <c r="F1475" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1475" t="n">
         <v>0</v>
@@ -78912,7 +78912,7 @@
       </c>
       <c r="M1475" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1475" t="inlineStr"/>
@@ -78920,21 +78920,21 @@
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>SUNDARK FPS 60 CON TAPA</t>
+          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
         </is>
       </c>
       <c r="C1476" t="inlineStr"/>
       <c r="D1476" t="inlineStr"/>
       <c r="E1476" t="n">
-        <v>3781.512605</v>
+        <v>8319.327730999999</v>
       </c>
       <c r="F1476" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1476" t="n">
         <v>0</v>
@@ -78970,21 +78970,21 @@
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>Synthroid 125 mcg</t>
+          <t>SULZINC SUSP X 80ML HUMAX</t>
         </is>
       </c>
       <c r="C1477" t="inlineStr"/>
       <c r="D1477" t="inlineStr"/>
       <c r="E1477" t="n">
-        <v>178000</v>
+        <v>22400</v>
       </c>
       <c r="F1477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1477" t="n">
         <v>0</v>
@@ -79020,25 +79020,21 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>Talco medicado Neofungina 40gm</t>
-        </is>
-      </c>
-      <c r="C1478" t="inlineStr">
-        <is>
-          <t>7706142707106</t>
-        </is>
-      </c>
+          <t>SUNDARK FPS 60 CON TAPA</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr"/>
       <c r="D1478" t="inlineStr"/>
       <c r="E1478" t="n">
-        <v>14900</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1478" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1478" t="n">
         <v>0</v>
@@ -79066,7 +79062,7 @@
       </c>
       <c r="M1478" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1478" t="inlineStr"/>
@@ -79074,18 +79070,18 @@
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
+          <t>Synthroid 125 mcg</t>
         </is>
       </c>
       <c r="C1479" t="inlineStr"/>
       <c r="D1479" t="inlineStr"/>
       <c r="E1479" t="n">
-        <v>13300</v>
+        <v>178000</v>
       </c>
       <c r="F1479" t="n">
         <v>0</v>
@@ -79124,21 +79120,25 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
-        </is>
-      </c>
-      <c r="C1480" t="inlineStr"/>
+          <t>Talco medicado Neofungina 40gm</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>7706142707106</t>
+        </is>
+      </c>
       <c r="D1480" t="inlineStr"/>
       <c r="E1480" t="n">
-        <v>4874</v>
+        <v>14900</v>
       </c>
       <c r="F1480" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G1480" t="n">
         <v>0</v>
@@ -79166,7 +79166,7 @@
       </c>
       <c r="M1480" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1480" t="inlineStr"/>
@@ -79174,21 +79174,21 @@
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
+          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
         </is>
       </c>
       <c r="C1481" t="inlineStr"/>
       <c r="D1481" t="inlineStr"/>
       <c r="E1481" t="n">
-        <v>28800</v>
+        <v>13300</v>
       </c>
       <c r="F1481" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1481" t="n">
         <v>0</v>
@@ -79224,21 +79224,21 @@
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
+          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
         </is>
       </c>
       <c r="C1482" t="inlineStr"/>
       <c r="D1482" t="inlineStr"/>
       <c r="E1482" t="n">
-        <v>11596.638655</v>
+        <v>4874</v>
       </c>
       <c r="F1482" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G1482" t="n">
         <v>0</v>
@@ -79274,21 +79274,21 @@
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>TIJERA DE DOBLAR METALICA</t>
+          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
         </is>
       </c>
       <c r="C1483" t="inlineStr"/>
       <c r="D1483" t="inlineStr"/>
       <c r="E1483" t="n">
-        <v>3500</v>
+        <v>28800</v>
       </c>
       <c r="F1483" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1483" t="n">
         <v>0</v>
@@ -79324,21 +79324,21 @@
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
         </is>
       </c>
       <c r="C1484" t="inlineStr"/>
       <c r="D1484" t="inlineStr"/>
       <c r="E1484" t="n">
-        <v>3781.512605</v>
+        <v>11596.638655</v>
       </c>
       <c r="F1484" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1484" t="n">
         <v>0</v>
@@ -79374,21 +79374,21 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+          <t>TIJERA DE DOBLAR METALICA</t>
         </is>
       </c>
       <c r="C1485" t="inlineStr"/>
       <c r="D1485" t="inlineStr"/>
       <c r="E1485" t="n">
-        <v>29800</v>
+        <v>3500</v>
       </c>
       <c r="F1485" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1485" t="n">
         <v>0</v>
@@ -79424,22 +79424,18 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
-        </is>
-      </c>
-      <c r="C1486" t="inlineStr">
-        <is>
-          <t>7702026149567</t>
-        </is>
-      </c>
+          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr"/>
       <c r="D1486" t="inlineStr"/>
       <c r="E1486" t="n">
-        <v>13500</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1486" t="n">
         <v>2</v>
@@ -79470,7 +79466,7 @@
       </c>
       <c r="M1486" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1486" t="inlineStr"/>
@@ -79478,25 +79474,21 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>Toallas húmedas winny 24unidades</t>
-        </is>
-      </c>
-      <c r="C1487" t="inlineStr">
-        <is>
-          <t>7701021143655</t>
-        </is>
-      </c>
+          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr"/>
       <c r="D1487" t="inlineStr"/>
       <c r="E1487" t="n">
-        <v>4033.613445</v>
+        <v>29800</v>
       </c>
       <c r="F1487" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G1487" t="n">
         <v>0</v>
@@ -79524,7 +79516,7 @@
       </c>
       <c r="M1487" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1487" t="inlineStr"/>
@@ -79532,25 +79524,25 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>Toallas maternas maternity</t>
+          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
         </is>
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>7703252489526</t>
+          <t>7702026149567</t>
         </is>
       </c>
       <c r="D1488" t="inlineStr"/>
       <c r="E1488" t="n">
-        <v>16900</v>
+        <v>13500</v>
       </c>
       <c r="F1488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1488" t="n">
         <v>0</v>
@@ -79586,25 +79578,25 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>Toallas Nosotras Rapigel x Und</t>
+          <t>Toallas húmedas winny 24unidades</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>7702027416859</t>
+          <t>7701021143655</t>
         </is>
       </c>
       <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="n">
-        <v>756.302521</v>
+        <v>4033.613445</v>
       </c>
       <c r="F1489" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G1489" t="n">
         <v>0</v>
@@ -79640,21 +79632,25 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>TRAMADOL 50MG CAPSULA MP</t>
-        </is>
-      </c>
-      <c r="C1490" t="inlineStr"/>
+          <t>Toallas maternas maternity</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>7703252489526</t>
+        </is>
+      </c>
       <c r="D1490" t="inlineStr"/>
       <c r="E1490" t="n">
-        <v>1500</v>
+        <v>16900</v>
       </c>
       <c r="F1490" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G1490" t="n">
         <v>0</v>
@@ -79690,25 +79686,25 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Tramadol clorhidrato 100mg laquifar</t>
+          <t>Toallas Nosotras Rapigel x Und</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>7707019426977</t>
+          <t>7702027416859</t>
         </is>
       </c>
       <c r="D1491" t="inlineStr"/>
       <c r="E1491" t="n">
-        <v>1600</v>
+        <v>756.302521</v>
       </c>
       <c r="F1491" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G1491" t="n">
         <v>0</v>
@@ -79736,7 +79732,7 @@
       </c>
       <c r="M1491" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1491" t="inlineStr"/>
@@ -79744,21 +79740,21 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>TRIGENTAX CREMA TBO X 20GR</t>
+          <t>TRAMADOL 50MG CAPSULA MP</t>
         </is>
       </c>
       <c r="C1492" t="inlineStr"/>
       <c r="D1492" t="inlineStr"/>
       <c r="E1492" t="n">
-        <v>33500</v>
+        <v>1500</v>
       </c>
       <c r="F1492" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G1492" t="n">
         <v>0</v>
@@ -79794,21 +79790,25 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
-        </is>
-      </c>
-      <c r="C1493" t="inlineStr"/>
+          <t>Tramadol clorhidrato 100mg laquifar</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>7707019426977</t>
+        </is>
+      </c>
       <c r="D1493" t="inlineStr"/>
       <c r="E1493" t="n">
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="F1493" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1493" t="n">
         <v>0</v>
@@ -79844,21 +79844,21 @@
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
+          <t>TRIGENTAX CREMA TBO X 20GR</t>
         </is>
       </c>
       <c r="C1494" t="inlineStr"/>
       <c r="D1494" t="inlineStr"/>
       <c r="E1494" t="n">
-        <v>10500</v>
+        <v>33500</v>
       </c>
       <c r="F1494" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1494" t="n">
         <v>0</v>
@@ -79894,21 +79894,21 @@
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
+          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
         </is>
       </c>
       <c r="C1495" t="inlineStr"/>
       <c r="D1495" t="inlineStr"/>
       <c r="E1495" t="n">
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="F1495" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G1495" t="n">
         <v>0</v>
@@ -79944,21 +79944,21 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
+          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
         </is>
       </c>
       <c r="C1496" t="inlineStr"/>
       <c r="D1496" t="inlineStr"/>
       <c r="E1496" t="n">
-        <v>18800</v>
+        <v>10500</v>
       </c>
       <c r="F1496" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1496" t="n">
         <v>0</v>
@@ -79994,21 +79994,21 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
+          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr"/>
       <c r="D1497" t="inlineStr"/>
       <c r="E1497" t="n">
-        <v>7900</v>
+        <v>10500</v>
       </c>
       <c r="F1497" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G1497" t="n">
         <v>0</v>
@@ -80044,21 +80044,21 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>VASELINA FC X 200GR YOMA</t>
+          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
         </is>
       </c>
       <c r="C1498" t="inlineStr"/>
       <c r="D1498" t="inlineStr"/>
       <c r="E1498" t="n">
-        <v>12521.008403</v>
+        <v>18800</v>
       </c>
       <c r="F1498" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1498" t="n">
         <v>0</v>
@@ -80086,7 +80086,7 @@
       </c>
       <c r="M1498" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1498" t="inlineStr"/>
@@ -80094,25 +80094,21 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
-        </is>
-      </c>
-      <c r="C1499" t="inlineStr">
-        <is>
-          <t>7708480649803</t>
-        </is>
-      </c>
+          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr"/>
       <c r="D1499" t="inlineStr"/>
       <c r="E1499" t="n">
-        <v>28000</v>
+        <v>13800</v>
       </c>
       <c r="F1499" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1499" t="n">
         <v>0</v>
@@ -80148,25 +80144,21 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>Venda Elastica 6x5 y piel</t>
+          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
         </is>
       </c>
       <c r="C1500" t="inlineStr"/>
-      <c r="D1500" t="inlineStr">
-        <is>
-          <t>SUBIO A 6200 ANTES 5700</t>
-        </is>
-      </c>
+      <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="n">
-        <v>6200</v>
+        <v>7900</v>
       </c>
       <c r="F1500" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1500" t="n">
         <v>0</v>
@@ -80202,21 +80194,21 @@
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
+          <t>VASELINA FC X 200GR YOMA</t>
         </is>
       </c>
       <c r="C1501" t="inlineStr"/>
       <c r="D1501" t="inlineStr"/>
       <c r="E1501" t="n">
-        <v>5500</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1501" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1501" t="n">
         <v>0</v>
@@ -80244,7 +80236,7 @@
       </c>
       <c r="M1501" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1501" t="inlineStr"/>
@@ -80252,18 +80244,22 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>Venta simple</t>
-        </is>
-      </c>
-      <c r="C1502" t="inlineStr"/>
+          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>7708480649803</t>
+        </is>
+      </c>
       <c r="D1502" t="inlineStr"/>
       <c r="E1502" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="F1502" t="n">
         <v>0</v>
@@ -80284,7 +80280,7 @@
       </c>
       <c r="K1502" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="L1502" t="inlineStr">
@@ -80292,27 +80288,35 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1502" t="inlineStr"/>
+      <c r="M1502" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1502" t="inlineStr"/>
     </row>
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
+          <t>Venda Elastica 6x5 y piel</t>
         </is>
       </c>
       <c r="C1503" t="inlineStr"/>
-      <c r="D1503" t="inlineStr"/>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>SUBIO A 6200 ANTES 5700</t>
+        </is>
+      </c>
       <c r="E1503" t="n">
-        <v>1000</v>
+        <v>6200</v>
       </c>
       <c r="F1503" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1503" t="n">
         <v>0</v>
@@ -80348,25 +80352,21 @@
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
-        </is>
-      </c>
-      <c r="C1504" t="inlineStr">
-        <is>
-          <t>793969226467</t>
-        </is>
-      </c>
+          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr"/>
       <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="n">
-        <v>17000</v>
+        <v>5500</v>
       </c>
       <c r="F1504" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1504" t="n">
         <v>0</v>
@@ -80389,7 +80389,7 @@
       </c>
       <c r="L1504" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="M1504" t="inlineStr">
@@ -80402,21 +80402,21 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>VINO CEREBRAL JARABE X 1100ML</t>
+          <t>Venta simple</t>
         </is>
       </c>
       <c r="C1505" t="inlineStr"/>
       <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="n">
-        <v>48900</v>
+        <v>0</v>
       </c>
       <c r="F1505" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1505" t="n">
         <v>0</v>
@@ -80434,7 +80434,7 @@
       </c>
       <c r="K1505" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="L1505" t="inlineStr">
@@ -80442,31 +80442,27 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1505" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1505" t="inlineStr"/>
       <c r="N1505" t="inlineStr"/>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
+          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
         </is>
       </c>
       <c r="C1506" t="inlineStr"/>
       <c r="D1506" t="inlineStr"/>
       <c r="E1506" t="n">
-        <v>5400</v>
+        <v>1000</v>
       </c>
       <c r="F1506" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G1506" t="n">
         <v>0</v>
@@ -80502,21 +80498,25 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
-        </is>
-      </c>
-      <c r="C1507" t="inlineStr"/>
+          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>793969226467</t>
+        </is>
+      </c>
       <c r="D1507" t="inlineStr"/>
       <c r="E1507" t="n">
-        <v>5500</v>
+        <v>17000</v>
       </c>
       <c r="F1507" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G1507" t="n">
         <v>0</v>
@@ -80539,7 +80539,7 @@
       </c>
       <c r="L1507" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="M1507" t="inlineStr">
@@ -80552,21 +80552,21 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>WINNY PAÑAL ETP 6 X 30</t>
+          <t>VINO CEREBRAL JARABE X 1100ML</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr"/>
       <c r="D1508" t="inlineStr"/>
       <c r="E1508" t="n">
-        <v>57000</v>
+        <v>48900</v>
       </c>
       <c r="F1508" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1508" t="n">
         <v>0</v>
@@ -80602,52 +80602,202 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>YODO BLANCO FC X30ML</t>
+          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
         </is>
       </c>
       <c r="C1509" t="inlineStr"/>
       <c r="D1509" t="inlineStr"/>
       <c r="E1509" t="n">
+        <v>5400</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1509" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1509" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1509" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1509" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1509" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1509" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1509" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1509" t="inlineStr"/>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr"/>
+      <c r="D1510" t="inlineStr"/>
+      <c r="E1510" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>14</v>
+      </c>
+      <c r="G1510" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1510" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1510" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1510" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1510" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1510" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1510" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1510" t="inlineStr"/>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>WINNY PAÑAL ETP 6 X 30</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr"/>
+      <c r="D1511" t="inlineStr"/>
+      <c r="E1511" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F1511" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1511" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1511" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1511" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1511" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1511" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1511" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1511" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1511" t="inlineStr"/>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>YODO BLANCO FC X30ML</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr"/>
+      <c r="D1512" t="inlineStr"/>
+      <c r="E1512" t="n">
         <v>6000</v>
       </c>
-      <c r="F1509" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1509" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1509" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1509" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1509" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="K1509" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="L1509" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="M1509" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="N1509" t="inlineStr"/>
+      <c r="F1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1512" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1512" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1512" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1512" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1512" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -8733,7 +8733,7 @@
         <v>2900</v>
       </c>
       <c r="F156" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -10279,7 +10279,7 @@
         <v>4000</v>
       </c>
       <c r="F185" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -11115,7 +11115,7 @@
         <v>14900</v>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -13097,7 +13097,7 @@
         <v>3800</v>
       </c>
       <c r="F238" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -15381,7 +15381,7 @@
         <v>7800</v>
       </c>
       <c r="F280" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
@@ -16627,7 +16627,7 @@
         <v>3800</v>
       </c>
       <c r="F303" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G303" t="n">
         <v>0</v>
@@ -17835,7 +17835,7 @@
         <v>1500</v>
       </c>
       <c r="F325" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G325" t="n">
         <v>0</v>
@@ -19875,7 +19875,7 @@
         <v>31500</v>
       </c>
       <c r="F365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G365" t="n">
         <v>0</v>
@@ -20731,7 +20731,7 @@
         <v>9000</v>
       </c>
       <c r="F381" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G381" t="n">
         <v>0</v>
@@ -21715,7 +21715,7 @@
         <v>3500</v>
       </c>
       <c r="F399" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G399" t="n">
         <v>0</v>
@@ -23365,7 +23365,7 @@
         <v>2000</v>
       </c>
       <c r="F430" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="G430" t="n">
         <v>0</v>
@@ -23577,7 +23577,7 @@
         <v>3300</v>
       </c>
       <c r="F434" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G434" t="n">
         <v>0</v>
@@ -23631,7 +23631,7 @@
         <v>2900</v>
       </c>
       <c r="F435" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G435" t="n">
         <v>0</v>
@@ -25093,7 +25093,7 @@
         <v>10900</v>
       </c>
       <c r="F462" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G462" t="n">
         <v>0</v>
@@ -28459,7 +28459,7 @@
         <v>7200</v>
       </c>
       <c r="F525" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G525" t="n">
         <v>0</v>
@@ -29585,7 +29585,7 @@
         <v>3500</v>
       </c>
       <c r="F546" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G546" t="n">
         <v>0</v>
@@ -31301,7 +31301,7 @@
         <v>3400</v>
       </c>
       <c r="F578" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G578" t="n">
         <v>0</v>
@@ -31571,7 +31571,7 @@
         <v>2800</v>
       </c>
       <c r="F583" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G583" t="n">
         <v>0</v>
@@ -31625,7 +31625,7 @@
         <v>2800</v>
       </c>
       <c r="F584" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G584" t="n">
         <v>0</v>
@@ -31845,7 +31845,7 @@
         <v>3000</v>
       </c>
       <c r="F588" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G588" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>800</v>
       </c>
       <c r="F597" t="n">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G597" t="n">
         <v>0</v>
@@ -32725,7 +32725,7 @@
         <v>2900</v>
       </c>
       <c r="F604" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G604" t="n">
         <v>0</v>
@@ -32883,7 +32883,7 @@
         <v>8800</v>
       </c>
       <c r="F607" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G607" t="n">
         <v>0</v>
@@ -34371,7 +34371,7 @@
         <v>2800</v>
       </c>
       <c r="F635" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="G635" t="n">
         <v>0</v>
@@ -39687,7 +39687,7 @@
         <v>1345</v>
       </c>
       <c r="F735" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G735" t="n">
         <v>0</v>
@@ -43191,7 +43191,7 @@
         <v>17000</v>
       </c>
       <c r="F801" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G801" t="n">
         <v>0</v>
@@ -55994,7 +55994,7 @@
         <v>3500</v>
       </c>
       <c r="F1040" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1040" t="n">
         <v>0</v>
@@ -56862,7 +56862,7 @@
         <v>30252</v>
       </c>
       <c r="F1056" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1056" t="n">
         <v>0</v>
@@ -58524,7 +58524,7 @@
         <v>27900</v>
       </c>
       <c r="F1087" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1087" t="n">
         <v>0</v>
@@ -60950,7 +60950,7 @@
         <v>6134.453782</v>
       </c>
       <c r="F1132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1132" t="n">
         <v>0</v>
@@ -62504,7 +62504,7 @@
         <v>14700</v>
       </c>
       <c r="F1161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1161" t="n">
         <v>0</v>
@@ -63260,7 +63260,7 @@
         <v>4200</v>
       </c>
       <c r="F1175" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G1175" t="n">
         <v>0</v>
@@ -63962,7 +63962,7 @@
         <v>3800</v>
       </c>
       <c r="F1188" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1188" t="n">
         <v>0</v>
@@ -64124,7 +64124,7 @@
         <v>29900</v>
       </c>
       <c r="F1191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1191" t="n">
         <v>0</v>
@@ -66858,7 +66858,7 @@
         <v>2200</v>
       </c>
       <c r="F1242" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1242" t="n">
         <v>0</v>
@@ -68010,7 +68010,7 @@
         <v>6900</v>
       </c>
       <c r="F1264" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1264" t="n">
         <v>0</v>
@@ -70474,7 +70474,7 @@
         <v>300</v>
       </c>
       <c r="F1312" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G1312" t="n">
         <v>0</v>
@@ -73962,7 +73962,7 @@
         <v>1100</v>
       </c>
       <c r="F1380" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G1380" t="n">
         <v>0</v>
@@ -75722,7 +75722,7 @@
         <v>23000</v>
       </c>
       <c r="F1414" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1414" t="n">
         <v>0</v>
@@ -77444,7 +77444,7 @@
         <v>35900</v>
       </c>
       <c r="F1447" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1447" t="n">
         <v>0</v>
@@ -77856,7 +77856,7 @@
         <v>673</v>
       </c>
       <c r="F1455" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G1455" t="n">
         <v>0</v>
@@ -78060,7 +78060,7 @@
         <v>9500</v>
       </c>
       <c r="F1459" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1459" t="n">
         <v>0</v>
@@ -80666,7 +80666,7 @@
         <v>5500</v>
       </c>
       <c r="F1510" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1510" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -64564,7 +64564,7 @@
         <v>32700</v>
       </c>
       <c r="F1199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1199" t="n">
         <v>0</v>
@@ -75772,7 +75772,7 @@
         <v>24500</v>
       </c>
       <c r="F1415" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1415" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -4853,7 +4853,7 @@
         <v>4500</v>
       </c>
       <c r="F84" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -14077,7 +14077,7 @@
         <v>840.336134</v>
       </c>
       <c r="F256" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -14185,7 +14185,7 @@
         <v>840</v>
       </c>
       <c r="F258" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -14771,7 +14771,7 @@
         <v>6000</v>
       </c>
       <c r="F269" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -15273,7 +15273,7 @@
         <v>9600</v>
       </c>
       <c r="F278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G278" t="n">
         <v>0</v>
@@ -15381,7 +15381,7 @@
         <v>7800</v>
       </c>
       <c r="F280" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
@@ -17835,7 +17835,7 @@
         <v>1500</v>
       </c>
       <c r="F325" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G325" t="n">
         <v>0</v>
@@ -51311,7 +51311,7 @@
         <v>2200</v>
       </c>
       <c r="F953" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G953" t="n">
         <v>0</v>
@@ -54756,7 +54756,7 @@
         <v>4800</v>
       </c>
       <c r="F1017" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1017" t="n">
         <v>0</v>
@@ -65702,7 +65702,7 @@
         <v>7000</v>
       </c>
       <c r="F1220" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1220" t="n">
         <v>0</v>
@@ -68684,7 +68684,7 @@
         <v>10800</v>
       </c>
       <c r="F1277" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1277" t="n">
         <v>0</v>
@@ -74474,7 +74474,7 @@
         <v>3500</v>
       </c>
       <c r="F1390" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G1390" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -4479,7 +4479,7 @@
         <v>6000</v>
       </c>
       <c r="F77" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         <v>29000</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -23107,7 +23107,7 @@
         <v>1300</v>
       </c>
       <c r="F425" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G425" t="n">
         <v>0</v>
@@ -23161,7 +23161,7 @@
         <v>2200</v>
       </c>
       <c r="F426" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G426" t="n">
         <v>0</v>
@@ -23797,7 +23797,7 @@
         <v>3300</v>
       </c>
       <c r="F438" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G438" t="n">
         <v>0</v>
@@ -32231,7 +32231,7 @@
         <v>20200</v>
       </c>
       <c r="F595" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G595" t="n">
         <v>0</v>
@@ -50524,7 +50524,7 @@
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>73 - Metoclopramida 10MG C</t>
+          <t>73 - Metoclopramida 10MG SOBRE X 15</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
@@ -50538,10 +50538,10 @@
         </is>
       </c>
       <c r="E938" t="n">
-        <v>1000</v>
+        <v>8500</v>
       </c>
       <c r="F938" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G938" t="n">
         <v>0</v>
@@ -58632,7 +58632,7 @@
         <v>1600</v>
       </c>
       <c r="F1089" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="G1089" t="n">
         <v>0</v>
@@ -65490,7 +65490,7 @@
         <v>12000</v>
       </c>
       <c r="F1216" t="n">
-        <v>-26</v>
+        <v>-23</v>
       </c>
       <c r="G1216" t="n">
         <v>0</v>
@@ -78580,7 +78580,7 @@
         <v>8900</v>
       </c>
       <c r="F1469" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G1469" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1512"/>
+  <dimension ref="A1:N1523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66894,25 +66894,21 @@
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>ALBENDAZOL 200MG X 2 TABL DE A.G</t>
-        </is>
-      </c>
-      <c r="C1243" t="inlineStr">
-        <is>
-          <t>7706569000019</t>
-        </is>
-      </c>
+          <t>AGUA MIA CON GAS 600ML</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr"/>
       <c r="D1243" t="inlineStr"/>
       <c r="E1243" t="n">
-        <v>4900</v>
+        <v>2500</v>
       </c>
       <c r="F1243" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1243" t="n">
         <v>0</v>
@@ -66948,21 +66944,25 @@
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>ALBENDAZOL 200MG X SOBRE DE LAPROFF</t>
-        </is>
-      </c>
-      <c r="C1244" t="inlineStr"/>
+          <t>ALBENDAZOL 200MG X 2 TABL DE A.G</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>7706569000019</t>
+        </is>
+      </c>
       <c r="D1244" t="inlineStr"/>
       <c r="E1244" t="n">
-        <v>3800</v>
+        <v>4900</v>
       </c>
       <c r="F1244" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="G1244" t="n">
         <v>0</v>
@@ -66998,21 +66998,21 @@
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>ALCOHOL ANTISEP70% DE JGB X 350ML</t>
+          <t>ALBENDAZOL 200MG X SOBRE DE LAPROFF</t>
         </is>
       </c>
       <c r="C1245" t="inlineStr"/>
       <c r="D1245" t="inlineStr"/>
       <c r="E1245" t="n">
-        <v>8700</v>
+        <v>3800</v>
       </c>
       <c r="F1245" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G1245" t="n">
         <v>0</v>
@@ -67048,25 +67048,21 @@
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Algodón zig zag Jgb 50gr</t>
-        </is>
-      </c>
-      <c r="C1246" t="inlineStr">
-        <is>
-          <t>7702560000379</t>
-        </is>
-      </c>
+          <t>ALCOHOL ANTISEP70% DE JGB X 350ML</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr"/>
       <c r="D1246" t="inlineStr"/>
       <c r="E1246" t="n">
-        <v>5900</v>
+        <v>8700</v>
       </c>
       <c r="F1246" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1246" t="n">
         <v>0</v>
@@ -67102,18 +67098,22 @@
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Algodón zinc zac 50gm jgb</t>
-        </is>
-      </c>
-      <c r="C1247" t="inlineStr"/>
+          <t>Algodón zig zag Jgb 50gr</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>7702560000379</t>
+        </is>
+      </c>
       <c r="D1247" t="inlineStr"/>
       <c r="E1247" t="n">
-        <v>2750</v>
+        <v>5900</v>
       </c>
       <c r="F1247" t="n">
         <v>0</v>
@@ -67152,18 +67152,18 @@
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>ALIMENTO EN POLVO X 450GR</t>
+          <t>Algodón zinc zac 50gm jgb</t>
         </is>
       </c>
       <c r="C1248" t="inlineStr"/>
       <c r="D1248" t="inlineStr"/>
       <c r="E1248" t="n">
-        <v>42800</v>
+        <v>2750</v>
       </c>
       <c r="F1248" t="n">
         <v>0</v>
@@ -67202,25 +67202,21 @@
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>Amoxicilina 500 Mg La Sante</t>
-        </is>
-      </c>
-      <c r="C1249" t="inlineStr">
-        <is>
-          <t>7703763070237</t>
-        </is>
-      </c>
+          <t>ALIMENTO EN POLVO X 450GR</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr"/>
       <c r="D1249" t="inlineStr"/>
       <c r="E1249" t="n">
-        <v>700</v>
+        <v>42800</v>
       </c>
       <c r="F1249" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G1249" t="n">
         <v>0</v>
@@ -67256,21 +67252,25 @@
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>AMOXICILINA 500MG SB X 10 DE COLMD</t>
-        </is>
-      </c>
-      <c r="C1250" t="inlineStr"/>
+          <t>Amoxicilina 500 Mg La Sante</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>7703763070237</t>
+        </is>
+      </c>
       <c r="D1250" t="inlineStr"/>
       <c r="E1250" t="n">
-        <v>6300</v>
+        <v>700</v>
       </c>
       <c r="F1250" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G1250" t="n">
         <v>0</v>
@@ -67306,21 +67306,21 @@
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Anemidox</t>
+          <t>AMOXICILINA 500MG SB X 10 DE COLMD</t>
         </is>
       </c>
       <c r="C1251" t="inlineStr"/>
       <c r="D1251" t="inlineStr"/>
       <c r="E1251" t="n">
-        <v>119000</v>
+        <v>6300</v>
       </c>
       <c r="F1251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1251" t="n">
         <v>0</v>
@@ -67356,29 +67356,21 @@
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>Antax Antiinflaatorio fco x 170 Ml Funat</t>
-        </is>
-      </c>
-      <c r="C1252" t="inlineStr">
-        <is>
-          <t>7706849110865</t>
-        </is>
-      </c>
-      <c r="D1252" t="inlineStr">
-        <is>
-          <t>SE AUNMENTA PRECIO A 28.200 ANTES ESTAB EN 24900/LEYDI</t>
-        </is>
-      </c>
+          <t>Anemidox</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr"/>
+      <c r="D1252" t="inlineStr"/>
       <c r="E1252" t="n">
-        <v>28200</v>
+        <v>119000</v>
       </c>
       <c r="F1252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1252" t="n">
         <v>0</v>
@@ -67414,21 +67406,29 @@
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Antiácido hidróxido de aluminio 360ml coaspharma</t>
-        </is>
-      </c>
-      <c r="C1253" t="inlineStr"/>
-      <c r="D1253" t="inlineStr"/>
+          <t>Antax Antiinflaatorio fco x 170 Ml Funat</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>7706849110865</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>SE AUNMENTA PRECIO A 28.200 ANTES ESTAB EN 24900/LEYDI</t>
+        </is>
+      </c>
       <c r="E1253" t="n">
-        <v>20000</v>
+        <v>28200</v>
       </c>
       <c r="F1253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1253" t="n">
         <v>0</v>
@@ -67464,25 +67464,21 @@
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>ATORVASTATINA 40MG X 10TAB. ECAR</t>
-        </is>
-      </c>
-      <c r="C1254" t="inlineStr">
-        <is>
-          <t>7702184011560</t>
-        </is>
-      </c>
+          <t>Antiácido hidróxido de aluminio 360ml coaspharma</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr"/>
       <c r="D1254" t="inlineStr"/>
       <c r="E1254" t="n">
-        <v>15800</v>
+        <v>20000</v>
       </c>
       <c r="F1254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1254" t="n">
         <v>0</v>
@@ -67518,21 +67514,25 @@
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>AZITROMICINA 500MG X 3 CAPS DE COLMED</t>
-        </is>
-      </c>
-      <c r="C1255" t="inlineStr"/>
+          <t>ATORVASTATINA 40MG X 10TAB. ECAR</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>7702184011560</t>
+        </is>
+      </c>
       <c r="D1255" t="inlineStr"/>
       <c r="E1255" t="n">
-        <v>12400</v>
+        <v>15800</v>
       </c>
       <c r="F1255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1255" t="n">
         <v>0</v>
@@ -67568,21 +67568,21 @@
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>AZUFRE BOLSA X 125GR</t>
+          <t>AZITROMICINA 500MG X 3 CAPS DE COLMED</t>
         </is>
       </c>
       <c r="C1256" t="inlineStr"/>
       <c r="D1256" t="inlineStr"/>
       <c r="E1256" t="n">
-        <v>3193.277311</v>
+        <v>12400</v>
       </c>
       <c r="F1256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1256" t="n">
         <v>0</v>
@@ -67610,7 +67610,7 @@
       </c>
       <c r="M1256" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1256" t="inlineStr"/>
@@ -67618,25 +67618,21 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>Benzirin verde enjuague bucal</t>
-        </is>
-      </c>
-      <c r="C1257" t="inlineStr">
-        <is>
-          <t>7702057018054</t>
-        </is>
-      </c>
+          <t>AZUFRE BOLSA X 125GR</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr"/>
       <c r="D1257" t="inlineStr"/>
       <c r="E1257" t="n">
-        <v>53700</v>
+        <v>3193.277311</v>
       </c>
       <c r="F1257" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1257" t="n">
         <v>0</v>
@@ -67664,7 +67660,7 @@
       </c>
       <c r="M1257" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1257" t="inlineStr"/>
@@ -67672,21 +67668,25 @@
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>BETAMETASONA 0.05% CREMA X 20GR OPHALAC</t>
-        </is>
-      </c>
-      <c r="C1258" t="inlineStr"/>
+          <t>Benzirin verde enjuague bucal</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>7702057018054</t>
+        </is>
+      </c>
       <c r="D1258" t="inlineStr"/>
       <c r="E1258" t="n">
-        <v>12000</v>
+        <v>53700</v>
       </c>
       <c r="F1258" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1258" t="n">
         <v>0</v>
@@ -67722,25 +67722,21 @@
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>BETAMETASONA 0.05% CREMA X 40GR LAPROFF</t>
-        </is>
-      </c>
-      <c r="C1259" t="inlineStr">
-        <is>
-          <t>7703038808770</t>
-        </is>
-      </c>
+          <t>BETAMETASONA 0.05% CREMA X 20GR OPHALAC</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr"/>
       <c r="D1259" t="inlineStr"/>
       <c r="E1259" t="n">
-        <v>10800</v>
+        <v>12000</v>
       </c>
       <c r="F1259" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1259" t="n">
         <v>0</v>
@@ -67776,22 +67772,22 @@
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>BETAMETASONA 0.1% CREMA X 20GR A.G</t>
+          <t>BETAMETASONA 0.05% CREMA X 40GR LAPROFF</t>
         </is>
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>7706569001672</t>
+          <t>7703038808770</t>
         </is>
       </c>
       <c r="D1260" t="inlineStr"/>
       <c r="E1260" t="n">
-        <v>17600</v>
+        <v>10800</v>
       </c>
       <c r="F1260" t="n">
         <v>3</v>
@@ -67830,29 +67826,25 @@
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>Betametasona/Betametasona acetato 3/3mg AMP</t>
+          <t>BETAMETASONA 0.1% CREMA X 20GR A.G</t>
         </is>
       </c>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>´7706569020321</t>
-        </is>
-      </c>
-      <c r="D1261" t="inlineStr">
-        <is>
-          <t>SE QUITO CODIGO DE BARRAS HECTOR</t>
-        </is>
-      </c>
+          <t>7706569001672</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr"/>
       <c r="E1261" t="n">
-        <v>55000</v>
+        <v>17600</v>
       </c>
       <c r="F1261" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1261" t="n">
         <v>0</v>
@@ -67888,25 +67880,29 @@
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>Biocicar Crema Topica x 60 gr</t>
+          <t>Betametasona/Betametasona acetato 3/3mg AMP</t>
         </is>
       </c>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>7703234100968</t>
-        </is>
-      </c>
-      <c r="D1262" t="inlineStr"/>
+          <t>´7706569020321</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>SE QUITO CODIGO DE BARRAS HECTOR</t>
+        </is>
+      </c>
       <c r="E1262" t="n">
-        <v>42000</v>
+        <v>55000</v>
       </c>
       <c r="F1262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1262" t="n">
         <v>0</v>
@@ -67942,22 +67938,22 @@
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>BISACUDILO 5MG X 10 TABL. HUMAX</t>
+          <t>Biocicar Crema Topica x 60 gr</t>
         </is>
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>77072888220247</t>
+          <t>7703234100968</t>
         </is>
       </c>
       <c r="D1263" t="inlineStr"/>
       <c r="E1263" t="n">
-        <v>4000</v>
+        <v>42000</v>
       </c>
       <c r="F1263" t="n">
         <v>0</v>
@@ -67996,21 +67992,25 @@
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>BISACUDILO 5MG X SOBRE DE RECIPE</t>
-        </is>
-      </c>
-      <c r="C1264" t="inlineStr"/>
+          <t>BISACUDILO 5MG X 10 TABL. HUMAX</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>77072888220247</t>
+        </is>
+      </c>
       <c r="D1264" t="inlineStr"/>
       <c r="E1264" t="n">
-        <v>6900</v>
+        <v>4000</v>
       </c>
       <c r="F1264" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1264" t="n">
         <v>0</v>
@@ -68046,25 +68046,21 @@
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>BISGLICINATO DE MAGNESIO X 60 CAPS</t>
-        </is>
-      </c>
-      <c r="C1265" t="inlineStr">
-        <is>
-          <t>610985519338</t>
-        </is>
-      </c>
+          <t>BISACUDILO 5MG X SOBRE DE RECIPE</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr"/>
       <c r="D1265" t="inlineStr"/>
       <c r="E1265" t="n">
-        <v>48000</v>
+        <v>6900</v>
       </c>
       <c r="F1265" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1265" t="n">
         <v>0</v>
@@ -68100,21 +68096,25 @@
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>BOLSAS INYECTOLOGIA</t>
-        </is>
-      </c>
-      <c r="C1266" t="inlineStr"/>
+          <t>BISGLICINATO DE MAGNESIO X 60 CAPS</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>610985519338</t>
+        </is>
+      </c>
       <c r="D1266" t="inlineStr"/>
       <c r="E1266" t="n">
-        <v>840.336134</v>
+        <v>48000</v>
       </c>
       <c r="F1266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1266" t="n">
         <v>0</v>
@@ -68142,7 +68142,7 @@
       </c>
       <c r="M1266" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1266" t="inlineStr"/>
@@ -68150,29 +68150,21 @@
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>BROMHEXINA MG/ML MUCOTROP NIÑO</t>
-        </is>
-      </c>
-      <c r="C1267" t="inlineStr">
-        <is>
-          <t>7703038067450</t>
-        </is>
-      </c>
-      <c r="D1267" t="inlineStr">
-        <is>
-          <t>SE SUBE PRECIO A 17000 ANTES ESTABA EN 15000/MODIF LEYDI</t>
-        </is>
-      </c>
+          <t>BOLSAS INYECTOLOGIA</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr"/>
+      <c r="D1267" t="inlineStr"/>
       <c r="E1267" t="n">
-        <v>17000</v>
+        <v>840.336134</v>
       </c>
       <c r="F1267" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1267" t="n">
         <v>0</v>
@@ -68200,7 +68192,7 @@
       </c>
       <c r="M1267" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1267" t="inlineStr"/>
@@ -68208,21 +68200,29 @@
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>BRONQUISAN JALEA ADULTO JARABE 240ML</t>
-        </is>
-      </c>
-      <c r="C1268" t="inlineStr"/>
-      <c r="D1268" t="inlineStr"/>
+          <t>BROMHEXINA MG/ML MUCOTROP NIÑO</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>7703038067450</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>SE SUBE PRECIO A 17000 ANTES ESTABA EN 15000/MODIF LEYDI</t>
+        </is>
+      </c>
       <c r="E1268" t="n">
-        <v>19900</v>
+        <v>17000</v>
       </c>
       <c r="F1268" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1268" t="n">
         <v>0</v>
@@ -68258,18 +68258,18 @@
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>Bronsinex JBE x 120ML</t>
+          <t>BRONQUISAN JALEA ADULTO JARABE 240ML</t>
         </is>
       </c>
       <c r="C1269" t="inlineStr"/>
       <c r="D1269" t="inlineStr"/>
       <c r="E1269" t="n">
-        <v>17000</v>
+        <v>19900</v>
       </c>
       <c r="F1269" t="n">
         <v>1</v>
@@ -68308,25 +68308,21 @@
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>CAJA DE BEDOYECTA X 3 AMPOLLA</t>
-        </is>
-      </c>
-      <c r="C1270" t="inlineStr">
-        <is>
-          <t>7707288826935</t>
-        </is>
-      </c>
+          <t>Bronsinex JBE x 120ML</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr"/>
       <c r="D1270" t="inlineStr"/>
       <c r="E1270" t="n">
-        <v>58000</v>
+        <v>17000</v>
       </c>
       <c r="F1270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1270" t="n">
         <v>0</v>
@@ -68362,21 +68358,25 @@
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>CALADERM CLEAR PLUS 120GR</t>
-        </is>
-      </c>
-      <c r="C1271" t="inlineStr"/>
+          <t>CAJA DE BEDOYECTA X 3 AMPOLLA</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>7707288826935</t>
+        </is>
+      </c>
       <c r="D1271" t="inlineStr"/>
       <c r="E1271" t="n">
-        <v>22268.907563</v>
+        <v>58000</v>
       </c>
       <c r="F1271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1271" t="n">
         <v>0</v>
@@ -68404,7 +68404,7 @@
       </c>
       <c r="M1271" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1271" t="inlineStr"/>
@@ -68412,25 +68412,21 @@
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>CAPILAR POLIMERO ROSADO 20ML</t>
-        </is>
-      </c>
-      <c r="C1272" t="inlineStr">
-        <is>
-          <t>7701168181244</t>
-        </is>
-      </c>
+          <t>CALADERM CLEAR PLUS 120GR</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr"/>
       <c r="D1272" t="inlineStr"/>
       <c r="E1272" t="n">
-        <v>4300</v>
+        <v>22268.907563</v>
       </c>
       <c r="F1272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1272" t="n">
         <v>0</v>
@@ -68458,7 +68454,7 @@
       </c>
       <c r="M1272" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1272" t="inlineStr"/>
@@ -68466,25 +68462,25 @@
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>CARVEDIDOL 6,25MG MEPHIS</t>
+          <t>CAPILAR POLIMERO ROSADO 20ML</t>
         </is>
       </c>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>7704412376328</t>
+          <t>7701168181244</t>
         </is>
       </c>
       <c r="D1273" t="inlineStr"/>
       <c r="E1273" t="n">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="F1273" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1273" t="n">
         <v>0</v>
@@ -68520,21 +68516,25 @@
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>CARVEDILOL 6.25MG SOBRE X 10 TABLE DE L.S</t>
-        </is>
-      </c>
-      <c r="C1274" t="inlineStr"/>
+          <t>CARVEDIDOL 6,25MG MEPHIS</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>7704412376328</t>
+        </is>
+      </c>
       <c r="D1274" t="inlineStr"/>
       <c r="E1274" t="n">
-        <v>5900</v>
+        <v>4400</v>
       </c>
       <c r="F1274" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1274" t="n">
         <v>0</v>
@@ -68570,21 +68570,21 @@
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>CAUCHO PARA EL CABELLO AKARELLA YUMBO</t>
+          <t>CARVEDILOL 6.25MG SOBRE X 10 TABLE DE L.S</t>
         </is>
       </c>
       <c r="C1275" t="inlineStr"/>
       <c r="D1275" t="inlineStr"/>
       <c r="E1275" t="n">
-        <v>2800</v>
+        <v>5900</v>
       </c>
       <c r="F1275" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1275" t="n">
         <v>0</v>
@@ -68620,21 +68620,21 @@
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>CAUCHOS AKARELA PASTEL ROSADO</t>
+          <t>CAUCHO PARA EL CABELLO AKARELLA YUMBO</t>
         </is>
       </c>
       <c r="C1276" t="inlineStr"/>
       <c r="D1276" t="inlineStr"/>
       <c r="E1276" t="n">
-        <v>1512.605042</v>
+        <v>2800</v>
       </c>
       <c r="F1276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1276" t="n">
         <v>0</v>
@@ -68662,7 +68662,7 @@
       </c>
       <c r="M1276" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1276" t="inlineStr"/>
@@ -68670,21 +68670,21 @@
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>CEFALEXINA 500MG CAPSULAS DE LA SANTE</t>
+          <t>CAUCHOS AKARELA PASTEL ROSADO</t>
         </is>
       </c>
       <c r="C1277" t="inlineStr"/>
       <c r="D1277" t="inlineStr"/>
       <c r="E1277" t="n">
-        <v>10800</v>
+        <v>1512.605042</v>
       </c>
       <c r="F1277" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G1277" t="n">
         <v>0</v>
@@ -68712,7 +68712,7 @@
       </c>
       <c r="M1277" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1277" t="inlineStr"/>
@@ -68720,25 +68720,21 @@
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>Cefalexina 500mg laproff</t>
-        </is>
-      </c>
-      <c r="C1278" t="inlineStr">
-        <is>
-          <t>7703038612636</t>
-        </is>
-      </c>
+          <t>CEFALEXINA 500MG CAPSULAS DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr"/>
       <c r="D1278" t="inlineStr"/>
       <c r="E1278" t="n">
-        <v>10000</v>
+        <v>10800</v>
       </c>
       <c r="F1278" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G1278" t="n">
         <v>0</v>
@@ -68774,21 +68770,25 @@
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>CERA EGO POTE X 60ML</t>
-        </is>
-      </c>
-      <c r="C1279" t="inlineStr"/>
+          <t>Cefalexina 500mg laproff</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>7703038612636</t>
+        </is>
+      </c>
       <c r="D1279" t="inlineStr"/>
       <c r="E1279" t="n">
-        <v>6800</v>
+        <v>10000</v>
       </c>
       <c r="F1279" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1279" t="n">
         <v>0</v>
@@ -68824,21 +68824,21 @@
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>CERA PROQUIDENT ORTD</t>
+          <t>CERA EGO POTE X 60ML</t>
         </is>
       </c>
       <c r="C1280" t="inlineStr"/>
       <c r="D1280" t="inlineStr"/>
       <c r="E1280" t="n">
-        <v>6554.621849</v>
+        <v>6800</v>
       </c>
       <c r="F1280" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1280" t="n">
         <v>0</v>
@@ -68866,7 +68866,7 @@
       </c>
       <c r="M1280" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1280" t="inlineStr"/>
@@ -68874,21 +68874,21 @@
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>CHA-P JARABE ARMONIZA 500ML</t>
+          <t>CERA PROQUIDENT ORTD</t>
         </is>
       </c>
       <c r="C1281" t="inlineStr"/>
       <c r="D1281" t="inlineStr"/>
       <c r="E1281" t="n">
-        <v>38000</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1281" t="n">
         <v>0</v>
@@ -68916,7 +68916,7 @@
       </c>
       <c r="M1281" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1281" t="inlineStr"/>
@@ -68924,21 +68924,21 @@
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>CHAPSTICK LABIAL CEREZA</t>
+          <t>CHA-P JARABE ARMONIZA 500ML</t>
         </is>
       </c>
       <c r="C1282" t="inlineStr"/>
       <c r="D1282" t="inlineStr"/>
       <c r="E1282" t="n">
-        <v>17563.02521</v>
+        <v>38000</v>
       </c>
       <c r="F1282" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1282" t="n">
         <v>0</v>
@@ -68966,7 +68966,7 @@
       </c>
       <c r="M1282" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1282" t="inlineStr"/>
@@ -68974,21 +68974,21 @@
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>CHUPO SILICONA GRANDE</t>
+          <t>CHAPSTICK LABIAL CEREZA</t>
         </is>
       </c>
       <c r="C1283" t="inlineStr"/>
       <c r="D1283" t="inlineStr"/>
       <c r="E1283" t="n">
-        <v>4500</v>
+        <v>17563.02521</v>
       </c>
       <c r="F1283" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1283" t="n">
         <v>0</v>
@@ -69016,7 +69016,7 @@
       </c>
       <c r="M1283" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1283" t="inlineStr"/>
@@ -69024,18 +69024,18 @@
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>Cianocobalamina</t>
+          <t>CHICLE TRIDENT SURTIDOS SABORES X PAQUE</t>
         </is>
       </c>
       <c r="C1284" t="inlineStr"/>
       <c r="D1284" t="inlineStr"/>
       <c r="E1284" t="n">
-        <v>6500</v>
+        <v>2016.806723</v>
       </c>
       <c r="F1284" t="n">
         <v>0</v>
@@ -69066,7 +69066,7 @@
       </c>
       <c r="M1284" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1284" t="inlineStr"/>
@@ -69074,25 +69074,21 @@
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>Cicaderm crema protector cutáneo 60gm NF</t>
-        </is>
-      </c>
-      <c r="C1285" t="inlineStr">
-        <is>
-          <t>7707173600091</t>
-        </is>
-      </c>
+          <t>CHOCOLATINA JUMBO MANI 17GR X 1 UND</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr"/>
       <c r="D1285" t="inlineStr"/>
       <c r="E1285" t="n">
-        <v>57000</v>
+        <v>1680.672269</v>
       </c>
       <c r="F1285" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1285" t="n">
         <v>0</v>
@@ -69120,7 +69116,7 @@
       </c>
       <c r="M1285" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1285" t="inlineStr"/>
@@ -69128,21 +69124,21 @@
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>Citrato de calcio / Vitamina D3 600 MG/400UI (1500MG) Granulos Caja x 15 Sobres</t>
+          <t>CHUPO SILICONA GRANDE</t>
         </is>
       </c>
       <c r="C1286" t="inlineStr"/>
       <c r="D1286" t="inlineStr"/>
       <c r="E1286" t="n">
-        <v>53000</v>
+        <v>4500</v>
       </c>
       <c r="F1286" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1286" t="n">
         <v>0</v>
@@ -69178,21 +69174,21 @@
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>CLENOX 40MG 1J/PRELLE.</t>
+          <t>Cianocobalamina</t>
         </is>
       </c>
       <c r="C1287" t="inlineStr"/>
       <c r="D1287" t="inlineStr"/>
       <c r="E1287" t="n">
-        <v>17800</v>
+        <v>6500</v>
       </c>
       <c r="F1287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1287" t="n">
         <v>0</v>
@@ -69228,25 +69224,25 @@
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>CLINBAC CLINDAMICINA 300MG CAPS</t>
+          <t>Cicaderm crema protector cutáneo 60gm NF</t>
         </is>
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>7707019413816</t>
+          <t>7707173600091</t>
         </is>
       </c>
       <c r="D1288" t="inlineStr"/>
       <c r="E1288" t="n">
-        <v>19200</v>
+        <v>57000</v>
       </c>
       <c r="F1288" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1288" t="n">
         <v>0</v>
@@ -69282,21 +69278,21 @@
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>769</t>
         </is>
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>CLINDABACT CLOTRI+CLIND CJA X 3 OVULOS</t>
+          <t>Citrato de calcio / Vitamina D3 600 MG/400UI (1500MG) Granulos Caja x 15 Sobres</t>
         </is>
       </c>
       <c r="C1289" t="inlineStr"/>
       <c r="D1289" t="inlineStr"/>
       <c r="E1289" t="n">
-        <v>35700</v>
+        <v>53000</v>
       </c>
       <c r="F1289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1289" t="n">
         <v>0</v>
@@ -69332,22 +69328,18 @@
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>CLOBETASOL 0,05% TRIDIRTEX CREMA X 40GR</t>
-        </is>
-      </c>
-      <c r="C1290" t="inlineStr">
-        <is>
-          <t>7709740450351</t>
-        </is>
-      </c>
+          <t>CLENOX 40MG 1J/PRELLE.</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr"/>
       <c r="D1290" t="inlineStr"/>
       <c r="E1290" t="n">
-        <v>27900</v>
+        <v>17800</v>
       </c>
       <c r="F1290" t="n">
         <v>1</v>
@@ -69386,25 +69378,25 @@
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Clotrimazol 1% 40gr AG</t>
+          <t>CLINBAC CLINDAMICINA 300MG CAPS</t>
         </is>
       </c>
       <c r="C1291" t="inlineStr">
         <is>
-          <t>7706569001191</t>
+          <t>7707019413816</t>
         </is>
       </c>
       <c r="D1291" t="inlineStr"/>
       <c r="E1291" t="n">
-        <v>19000</v>
+        <v>19200</v>
       </c>
       <c r="F1291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1291" t="n">
         <v>0</v>
@@ -69440,25 +69432,21 @@
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>CLOTRIMAZOL 1% CREMA TOPICA DE VITALIS</t>
-        </is>
-      </c>
-      <c r="C1292" t="inlineStr">
-        <is>
-          <t>7709990212204</t>
-        </is>
-      </c>
+          <t>CLINDABACT CLOTRI+CLIND CJA X 3 OVULOS</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr"/>
       <c r="D1292" t="inlineStr"/>
       <c r="E1292" t="n">
-        <v>14500</v>
+        <v>35700</v>
       </c>
       <c r="F1292" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1292" t="n">
         <v>0</v>
@@ -69494,21 +69482,25 @@
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>COLAGENO HIDROLIZADO EN POLVO 700GR ARMONIZA</t>
-        </is>
-      </c>
-      <c r="C1293" t="inlineStr"/>
+          <t>CLOBETASOL 0,05% TRIDIRTEX CREMA X 40GR</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>7709740450351</t>
+        </is>
+      </c>
       <c r="D1293" t="inlineStr"/>
       <c r="E1293" t="n">
-        <v>56000</v>
+        <v>27900</v>
       </c>
       <c r="F1293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1293" t="n">
         <v>0</v>
@@ -69544,18 +69536,22 @@
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>Colchicina Coas</t>
-        </is>
-      </c>
-      <c r="C1294" t="inlineStr"/>
+          <t>Clotrimazol 1% 40gr AG</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>7706569001191</t>
+        </is>
+      </c>
       <c r="D1294" t="inlineStr"/>
       <c r="E1294" t="n">
-        <v>3900</v>
+        <v>19000</v>
       </c>
       <c r="F1294" t="n">
         <v>1</v>
@@ -69594,21 +69590,25 @@
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>CONDON DUO LUBRICADO X 3 UND</t>
-        </is>
-      </c>
-      <c r="C1295" t="inlineStr"/>
+          <t>CLOTRIMAZOL 1% CREMA TOPICA DE VITALIS</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>7709990212204</t>
+        </is>
+      </c>
       <c r="D1295" t="inlineStr"/>
       <c r="E1295" t="n">
-        <v>16500</v>
+        <v>14500</v>
       </c>
       <c r="F1295" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1295" t="n">
         <v>0</v>
@@ -69644,21 +69644,21 @@
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
+          <t>COLAGENO HIDROLIZADO EN POLVO 700GR ARMONIZA</t>
         </is>
       </c>
       <c r="C1296" t="inlineStr"/>
       <c r="D1296" t="inlineStr"/>
       <c r="E1296" t="n">
-        <v>8900</v>
+        <v>56000</v>
       </c>
       <c r="F1296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1296" t="n">
         <v>0</v>
@@ -69694,21 +69694,21 @@
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
+          <t>Colchicina Coas</t>
         </is>
       </c>
       <c r="C1297" t="inlineStr"/>
       <c r="D1297" t="inlineStr"/>
       <c r="E1297" t="n">
-        <v>8900</v>
+        <v>3900</v>
       </c>
       <c r="F1297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1297" t="n">
         <v>0</v>
@@ -69744,21 +69744,21 @@
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>CONDON PIEL SABORES CJA X 3 UNDS</t>
+          <t>CONDON DUO LUBRICADO X 3 UND</t>
         </is>
       </c>
       <c r="C1298" t="inlineStr"/>
       <c r="D1298" t="inlineStr"/>
       <c r="E1298" t="n">
-        <v>8900</v>
+        <v>16500</v>
       </c>
       <c r="F1298" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1298" t="n">
         <v>0</v>
@@ -69794,25 +69794,21 @@
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>CONDON PRUDENCE EFEC.RETARDX3UNDS</t>
-        </is>
-      </c>
-      <c r="C1299" t="inlineStr">
-        <is>
-          <t>77309632510504387</t>
-        </is>
-      </c>
+          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr"/>
       <c r="D1299" t="inlineStr"/>
       <c r="E1299" t="n">
-        <v>12200</v>
+        <v>8900</v>
       </c>
       <c r="F1299" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1299" t="n">
         <v>0</v>
@@ -69848,25 +69844,21 @@
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>CONDON PRUDENCE EXTRA GRANDE ULT SENSIBX3UND</t>
-        </is>
-      </c>
-      <c r="C1300" t="inlineStr">
-        <is>
-          <t>7730963250343</t>
-        </is>
-      </c>
+          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr"/>
       <c r="D1300" t="inlineStr"/>
       <c r="E1300" t="n">
-        <v>13800</v>
+        <v>8900</v>
       </c>
       <c r="F1300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1300" t="n">
         <v>0</v>
@@ -69902,25 +69894,21 @@
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>CONTENT MEDICAL PAÑAL TALLA L X UND</t>
+          <t>CONDON PIEL SABORES CJA X 3 UNDS</t>
         </is>
       </c>
       <c r="C1301" t="inlineStr"/>
-      <c r="D1301" t="inlineStr">
-        <is>
-          <t>pañal adulto no paga iva articulo 424</t>
-        </is>
-      </c>
+      <c r="D1301" t="inlineStr"/>
       <c r="E1301" t="n">
-        <v>4800</v>
+        <v>8900</v>
       </c>
       <c r="F1301" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G1301" t="n">
         <v>0</v>
@@ -69956,21 +69944,25 @@
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>CONTENT MEDICAL PAÑAL TALLA M X UND</t>
-        </is>
-      </c>
-      <c r="C1302" t="inlineStr"/>
+          <t>CONDON PRUDENCE EFEC.RETARDX3UNDS</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>77309632510504387</t>
+        </is>
+      </c>
       <c r="D1302" t="inlineStr"/>
       <c r="E1302" t="n">
-        <v>3697.478992</v>
+        <v>12200</v>
       </c>
       <c r="F1302" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G1302" t="n">
         <v>0</v>
@@ -69998,7 +69990,7 @@
       </c>
       <c r="M1302" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1302" t="inlineStr"/>
@@ -70006,21 +69998,25 @@
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 100 UNDS</t>
-        </is>
-      </c>
-      <c r="C1303" t="inlineStr"/>
+          <t>CONDON PRUDENCE EXTRA GRANDE ULT SENSIBX3UND</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>7730963250343</t>
+        </is>
+      </c>
       <c r="D1303" t="inlineStr"/>
       <c r="E1303" t="n">
-        <v>8500</v>
+        <v>13800</v>
       </c>
       <c r="F1303" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1303" t="n">
         <v>0</v>
@@ -70056,21 +70052,25 @@
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 50 UNDS</t>
+          <t>CONTENT MEDICAL PAÑAL TALLA L X UND</t>
         </is>
       </c>
       <c r="C1304" t="inlineStr"/>
-      <c r="D1304" t="inlineStr"/>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>pañal adulto no paga iva articulo 424</t>
+        </is>
+      </c>
       <c r="E1304" t="n">
-        <v>6400</v>
+        <v>4800</v>
       </c>
       <c r="F1304" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1304" t="n">
         <v>0</v>
@@ -70106,21 +70106,21 @@
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 60 UNDS</t>
+          <t>CONTENT MEDICAL PAÑAL TALLA M X UND</t>
         </is>
       </c>
       <c r="C1305" t="inlineStr"/>
       <c r="D1305" t="inlineStr"/>
       <c r="E1305" t="n">
-        <v>7142.857143</v>
+        <v>3697.478992</v>
       </c>
       <c r="F1305" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G1305" t="n">
         <v>0</v>
@@ -70156,21 +70156,21 @@
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>CORTA CUTICULA TRIM METALICO</t>
+          <t>COPITOS YOKY X 100 UNDS</t>
         </is>
       </c>
       <c r="C1306" t="inlineStr"/>
       <c r="D1306" t="inlineStr"/>
       <c r="E1306" t="n">
-        <v>16000</v>
+        <v>8500</v>
       </c>
       <c r="F1306" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1306" t="n">
         <v>0</v>
@@ -70206,18 +70206,18 @@
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>CREMA ARNICA PROTECTORA 12GR ICE POWER</t>
+          <t>COPITOS YOKY X 50 UNDS</t>
         </is>
       </c>
       <c r="C1307" t="inlineStr"/>
       <c r="D1307" t="inlineStr"/>
       <c r="E1307" t="n">
-        <v>10084.033613</v>
+        <v>6400</v>
       </c>
       <c r="F1307" t="n">
         <v>3</v>
@@ -70248,7 +70248,7 @@
       </c>
       <c r="M1307" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1307" t="inlineStr"/>
@@ -70256,21 +70256,21 @@
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>CREMA BENLIC DE 40GR</t>
+          <t>COPITOS YOKY X 60 UNDS</t>
         </is>
       </c>
       <c r="C1308" t="inlineStr"/>
       <c r="D1308" t="inlineStr"/>
       <c r="E1308" t="n">
-        <v>28900</v>
+        <v>7142.857143</v>
       </c>
       <c r="F1308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1308" t="n">
         <v>0</v>
@@ -70298,7 +70298,7 @@
       </c>
       <c r="M1308" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1308" t="inlineStr"/>
@@ -70306,18 +70306,18 @@
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>CREMA CASTAÑO DE INDIAS X 12GR ARMONIZA</t>
+          <t>CORTA CUTICULA TRIM METALICO</t>
         </is>
       </c>
       <c r="C1309" t="inlineStr"/>
       <c r="D1309" t="inlineStr"/>
       <c r="E1309" t="n">
-        <v>9000</v>
+        <v>16000</v>
       </c>
       <c r="F1309" t="n">
         <v>1</v>
@@ -70356,25 +70356,21 @@
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>Crema Colgate triple acción xtra blancura 60ml</t>
-        </is>
-      </c>
-      <c r="C1310" t="inlineStr">
-        <is>
-          <t>7702010111587</t>
-        </is>
-      </c>
+          <t>CREMA ARNICA PROTECTORA 12GR ICE POWER</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr"/>
       <c r="D1310" t="inlineStr"/>
       <c r="E1310" t="n">
-        <v>5630.252101</v>
+        <v>10084.033613</v>
       </c>
       <c r="F1310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1310" t="n">
         <v>0</v>
@@ -70410,18 +70406,18 @@
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>CREMA PONDS CLARANT B3 X SACHETS</t>
+          <t>CREMA BENLIC DE 40GR</t>
         </is>
       </c>
       <c r="C1311" t="inlineStr"/>
       <c r="D1311" t="inlineStr"/>
       <c r="E1311" t="n">
-        <v>2521.008403</v>
+        <v>28900</v>
       </c>
       <c r="F1311" t="n">
         <v>1</v>
@@ -70452,7 +70448,7 @@
       </c>
       <c r="M1311" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1311" t="inlineStr"/>
@@ -70460,21 +70456,21 @@
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>CURAS LARGAS RESIST AL AGUA</t>
+          <t>CREMA CASTAÑO DE INDIAS X 12GR ARMONIZA</t>
         </is>
       </c>
       <c r="C1312" t="inlineStr"/>
       <c r="D1312" t="inlineStr"/>
       <c r="E1312" t="n">
-        <v>300</v>
+        <v>9000</v>
       </c>
       <c r="F1312" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="G1312" t="n">
         <v>0</v>
@@ -70510,25 +70506,25 @@
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>CYCLOFEM AMPOLLA INYECTABLE .PROFAMILIA</t>
+          <t>Crema Colgate triple acción xtra blancura 60ml</t>
         </is>
       </c>
       <c r="C1313" t="inlineStr">
         <is>
-          <t>7703689000448</t>
+          <t>7702010111587</t>
         </is>
       </c>
       <c r="D1313" t="inlineStr"/>
       <c r="E1313" t="n">
-        <v>28900</v>
+        <v>5630.252101</v>
       </c>
       <c r="F1313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1313" t="n">
         <v>0</v>
@@ -70556,7 +70552,7 @@
       </c>
       <c r="M1313" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1313" t="inlineStr"/>
@@ -70564,25 +70560,21 @@
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>CYCLOFEMINA AMPOLLA 0.5ML</t>
-        </is>
-      </c>
-      <c r="C1314" t="inlineStr">
-        <is>
-          <t>7707271451410</t>
-        </is>
-      </c>
+          <t>CREMA PONDS CLARANT B3 X SACHETS</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr"/>
       <c r="D1314" t="inlineStr"/>
       <c r="E1314" t="n">
-        <v>33900</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1314" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1314" t="n">
         <v>0</v>
@@ -70610,7 +70602,7 @@
       </c>
       <c r="M1314" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1314" t="inlineStr"/>
@@ -70618,25 +70610,21 @@
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>Desonida bussie 0.1% crema 15gr</t>
-        </is>
-      </c>
-      <c r="C1315" t="inlineStr">
-        <is>
-          <t>7702195210587</t>
-        </is>
-      </c>
+          <t>CURAS LARGAS RESIST AL AGUA</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr"/>
       <c r="D1315" t="inlineStr"/>
       <c r="E1315" t="n">
-        <v>19000</v>
+        <v>300</v>
       </c>
       <c r="F1315" t="n">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="G1315" t="n">
         <v>0</v>
@@ -70672,22 +70660,22 @@
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>Diclofenaco gel vitalis 50gr</t>
+          <t>CYCLOFEM AMPOLLA INYECTABLE .PROFAMILIA</t>
         </is>
       </c>
       <c r="C1316" t="inlineStr">
         <is>
-          <t>7709141546059</t>
+          <t>7703689000448</t>
         </is>
       </c>
       <c r="D1316" t="inlineStr"/>
       <c r="E1316" t="n">
-        <v>16000</v>
+        <v>28900</v>
       </c>
       <c r="F1316" t="n">
         <v>3</v>
@@ -70716,31 +70704,35 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1316" t="inlineStr"/>
+      <c r="M1316" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1316" t="inlineStr"/>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>Diclofenaco sódico 100mg +hidróxido de aluminio200mg colmed</t>
+          <t>CYCLOFEMINA AMPOLLA 0.5ML</t>
         </is>
       </c>
       <c r="C1317" t="inlineStr">
         <is>
-          <t>7703153020286</t>
+          <t>7707271451410</t>
         </is>
       </c>
       <c r="D1317" t="inlineStr"/>
       <c r="E1317" t="n">
-        <v>19200</v>
+        <v>33900</v>
       </c>
       <c r="F1317" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1317" t="n">
         <v>0</v>
@@ -70776,18 +70768,22 @@
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>DICLOFENACOXUND75MG/3MLAMPCOMERCIAL VITALIS</t>
-        </is>
-      </c>
-      <c r="C1318" t="inlineStr"/>
+          <t>Desonida bussie 0.1% crema 15gr</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>7702195210587</t>
+        </is>
+      </c>
       <c r="D1318" t="inlineStr"/>
       <c r="E1318" t="n">
-        <v>5500</v>
+        <v>19000</v>
       </c>
       <c r="F1318" t="n">
         <v>1</v>
@@ -70826,21 +70822,25 @@
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>DIFENZ DESPIGMENTADOR CREMA TUBO X 1 UND</t>
-        </is>
-      </c>
-      <c r="C1319" t="inlineStr"/>
+          <t>Diclofenaco gel vitalis 50gr</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>7709141546059</t>
+        </is>
+      </c>
       <c r="D1319" t="inlineStr"/>
       <c r="E1319" t="n">
-        <v>163300</v>
+        <v>16000</v>
       </c>
       <c r="F1319" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1319" t="n">
         <v>0</v>
@@ -70866,31 +70866,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1319" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1319" t="inlineStr"/>
       <c r="N1319" t="inlineStr"/>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>DIPIORNA 500MG TABLETA X 10 DE ECAR</t>
-        </is>
-      </c>
-      <c r="C1320" t="inlineStr"/>
+          <t>Diclofenaco sódico 100mg +hidróxido de aluminio200mg colmed</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>7703153020286</t>
+        </is>
+      </c>
       <c r="D1320" t="inlineStr"/>
       <c r="E1320" t="n">
-        <v>7900</v>
+        <v>19200</v>
       </c>
       <c r="F1320" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G1320" t="n">
         <v>0</v>
@@ -70926,21 +70926,21 @@
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>DIPIRONA 500MG TABLETA X 10 DE ECAR</t>
+          <t>DICLOFENACOXUND75MG/3MLAMPCOMERCIAL VITALIS</t>
         </is>
       </c>
       <c r="C1321" t="inlineStr"/>
       <c r="D1321" t="inlineStr"/>
       <c r="E1321" t="n">
-        <v>7900</v>
+        <v>5500</v>
       </c>
       <c r="F1321" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1321" t="n">
         <v>0</v>
@@ -70976,21 +70976,21 @@
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>DOMICILIO</t>
+          <t>DIFENZ DESPIGMENTADOR CREMA TUBO X 1 UND</t>
         </is>
       </c>
       <c r="C1322" t="inlineStr"/>
       <c r="D1322" t="inlineStr"/>
       <c r="E1322" t="n">
-        <v>3000</v>
+        <v>163300</v>
       </c>
       <c r="F1322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1322" t="n">
         <v>0</v>
@@ -71016,27 +71016,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1322" t="inlineStr"/>
+      <c r="M1322" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1322" t="inlineStr"/>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>DOXICICLINA 100MG X 10 TABL GENFAR</t>
+          <t>DIPIORNA 500MG TABLETA X 10 DE ECAR</t>
         </is>
       </c>
       <c r="C1323" t="inlineStr"/>
       <c r="D1323" t="inlineStr"/>
       <c r="E1323" t="n">
-        <v>12000</v>
+        <v>7900</v>
       </c>
       <c r="F1323" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1323" t="n">
         <v>0</v>
@@ -71072,21 +71076,21 @@
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>DUCHA INTIMA DESECHABLE VINAGRE</t>
+          <t>DIPIRONA 500MG TABLETA X 10 DE ECAR</t>
         </is>
       </c>
       <c r="C1324" t="inlineStr"/>
       <c r="D1324" t="inlineStr"/>
       <c r="E1324" t="n">
-        <v>24800</v>
+        <v>7900</v>
       </c>
       <c r="F1324" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1324" t="n">
         <v>0</v>
@@ -71122,22 +71126,18 @@
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>E ala proel maléate 20mg medicbrand</t>
-        </is>
-      </c>
-      <c r="C1325" t="inlineStr">
-        <is>
-          <t>7703712035997</t>
-        </is>
-      </c>
+          <t>DOMICILIO</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr"/>
       <c r="D1325" t="inlineStr"/>
       <c r="E1325" t="n">
-        <v>1250</v>
+        <v>3000</v>
       </c>
       <c r="F1325" t="n">
         <v>0</v>
@@ -71166,35 +71166,27 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1325" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1325" t="inlineStr"/>
       <c r="N1325" t="inlineStr"/>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>Enalapril 20 mg MK</t>
-        </is>
-      </c>
-      <c r="C1326" t="inlineStr">
-        <is>
-          <t>7702057716578</t>
-        </is>
-      </c>
+          <t>DOXICICLINA 100MG X 10 TABL GENFAR</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr"/>
       <c r="D1326" t="inlineStr"/>
       <c r="E1326" t="n">
-        <v>4700</v>
+        <v>12000</v>
       </c>
       <c r="F1326" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1326" t="n">
         <v>0</v>
@@ -71230,21 +71222,21 @@
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>ENALAPRIL 20MG TABLETA COAS</t>
+          <t>DUCHA INTIMA DESECHABLE VINAGRE</t>
         </is>
       </c>
       <c r="C1327" t="inlineStr"/>
       <c r="D1327" t="inlineStr"/>
       <c r="E1327" t="n">
-        <v>3000</v>
+        <v>24800</v>
       </c>
       <c r="F1327" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1327" t="n">
         <v>0</v>
@@ -71280,21 +71272,25 @@
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>ENSURE ADVANCE VAINILLA 400GR</t>
-        </is>
-      </c>
-      <c r="C1328" t="inlineStr"/>
+          <t>E ala proel maléate 20mg medicbrand</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>7703712035997</t>
+        </is>
+      </c>
       <c r="D1328" t="inlineStr"/>
       <c r="E1328" t="n">
-        <v>85900</v>
+        <v>1250</v>
       </c>
       <c r="F1328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1328" t="n">
         <v>0</v>
@@ -71330,18 +71326,22 @@
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>ENTRETENEDOR BEBE</t>
-        </is>
-      </c>
-      <c r="C1329" t="inlineStr"/>
+          <t>Enalapril 20 mg MK</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>7702057716578</t>
+        </is>
+      </c>
       <c r="D1329" t="inlineStr"/>
       <c r="E1329" t="n">
-        <v>9000</v>
+        <v>4700</v>
       </c>
       <c r="F1329" t="n">
         <v>1</v>
@@ -71380,21 +71380,21 @@
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>ESMALTE BRILLO ACRILICO BRESCIA</t>
+          <t>ENALAPRIL 20MG TABLETA COAS</t>
         </is>
       </c>
       <c r="C1330" t="inlineStr"/>
       <c r="D1330" t="inlineStr"/>
       <c r="E1330" t="n">
-        <v>11500</v>
+        <v>3000</v>
       </c>
       <c r="F1330" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1330" t="n">
         <v>0</v>
@@ -71430,21 +71430,21 @@
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>ESOMEPRAZOL 20MG NOVAMED</t>
+          <t>ENSURE ADVANCE VAINILLA 400GR</t>
         </is>
       </c>
       <c r="C1331" t="inlineStr"/>
       <c r="D1331" t="inlineStr"/>
       <c r="E1331" t="n">
-        <v>2000</v>
+        <v>85900</v>
       </c>
       <c r="F1331" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G1331" t="n">
         <v>0</v>
@@ -71480,18 +71480,18 @@
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>ESPASMOK HIOS +DIPIRO 5ML AMP BLASKOV</t>
+          <t>ENTRETENEDOR BEBE</t>
         </is>
       </c>
       <c r="C1332" t="inlineStr"/>
       <c r="D1332" t="inlineStr"/>
       <c r="E1332" t="n">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="F1332" t="n">
         <v>1</v>
@@ -71530,22 +71530,18 @@
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>EXTRACTOR DE LECHE MOBY</t>
-        </is>
-      </c>
-      <c r="C1333" t="inlineStr">
-        <is>
-          <t>7707233051436</t>
-        </is>
-      </c>
+          <t>ESMALTE BRILLO ACRILICO BRESCIA</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr"/>
       <c r="D1333" t="inlineStr"/>
       <c r="E1333" t="n">
-        <v>14285.714286</v>
+        <v>11500</v>
       </c>
       <c r="F1333" t="n">
         <v>1</v>
@@ -71576,7 +71572,7 @@
       </c>
       <c r="M1333" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1333" t="inlineStr"/>
@@ -71584,25 +71580,21 @@
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>FAMIIA MEGARROLLO PAPEL HIGUIEN</t>
-        </is>
-      </c>
-      <c r="C1334" t="inlineStr">
-        <is>
-          <t>7702026147471</t>
-        </is>
-      </c>
+          <t>ESOMEPRAZOL 20MG NOVAMED</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr"/>
       <c r="D1334" t="inlineStr"/>
       <c r="E1334" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="F1334" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G1334" t="n">
         <v>0</v>
@@ -71638,21 +71630,21 @@
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Farma D 500 UI</t>
+          <t>ESPASMOK HIOS +DIPIRO 5ML AMP BLASKOV</t>
         </is>
       </c>
       <c r="C1335" t="inlineStr"/>
       <c r="D1335" t="inlineStr"/>
       <c r="E1335" t="n">
-        <v>74000</v>
+        <v>12000</v>
       </c>
       <c r="F1335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1335" t="n">
         <v>0</v>
@@ -71688,18 +71680,22 @@
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>FIBRA AMARILLA ARMONIZA X 450GR</t>
-        </is>
-      </c>
-      <c r="C1336" t="inlineStr"/>
+          <t>EXTRACTOR DE LECHE MOBY</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>7707233051436</t>
+        </is>
+      </c>
       <c r="D1336" t="inlineStr"/>
       <c r="E1336" t="n">
-        <v>28571.428571</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1336" t="n">
         <v>1</v>
@@ -71730,7 +71726,7 @@
       </c>
       <c r="M1336" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1336" t="inlineStr"/>
@@ -71738,21 +71734,25 @@
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>FIBRA DE AVENA Y SALVADO DE TRIGO 450GR</t>
-        </is>
-      </c>
-      <c r="C1337" t="inlineStr"/>
+          <t>FAMIIA MEGARROLLO PAPEL HIGUIEN</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>7702026147471</t>
+        </is>
+      </c>
       <c r="D1337" t="inlineStr"/>
       <c r="E1337" t="n">
-        <v>30000</v>
+        <v>3500</v>
       </c>
       <c r="F1337" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1337" t="n">
         <v>0</v>
@@ -71788,21 +71788,21 @@
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>FITOSTIMONE 15% GEL</t>
+          <t>Farma D 500 UI</t>
         </is>
       </c>
       <c r="C1338" t="inlineStr"/>
       <c r="D1338" t="inlineStr"/>
       <c r="E1338" t="n">
-        <v>48900</v>
+        <v>74000</v>
       </c>
       <c r="F1338" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1338" t="n">
         <v>0</v>
@@ -71838,25 +71838,21 @@
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG CJA X 10 UND EXPORF</t>
-        </is>
-      </c>
-      <c r="C1339" t="inlineStr">
-        <is>
-          <t>7703432421681</t>
-        </is>
-      </c>
+          <t>FIBRA AMARILLA ARMONIZA X 450GR</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr"/>
       <c r="D1339" t="inlineStr"/>
       <c r="E1339" t="n">
-        <v>18300</v>
+        <v>28571.428571</v>
       </c>
       <c r="F1339" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G1339" t="n">
         <v>0</v>
@@ -71884,7 +71880,7 @@
       </c>
       <c r="M1339" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1339" t="inlineStr"/>
@@ -71892,21 +71888,21 @@
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS DE GENFAR</t>
+          <t>FIBRA DE AVENA Y SALVADO DE TRIGO 450GR</t>
         </is>
       </c>
       <c r="C1340" t="inlineStr"/>
       <c r="D1340" t="inlineStr"/>
       <c r="E1340" t="n">
-        <v>16900</v>
+        <v>30000</v>
       </c>
       <c r="F1340" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1340" t="n">
         <v>0</v>
@@ -71942,25 +71938,21 @@
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS. LA SANTE</t>
-        </is>
-      </c>
-      <c r="C1341" t="inlineStr">
-        <is>
-          <t>7703763480166</t>
-        </is>
-      </c>
+          <t>FITOSTIMONE 15% GEL</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr"/>
       <c r="D1341" t="inlineStr"/>
       <c r="E1341" t="n">
-        <v>14700</v>
+        <v>48900</v>
       </c>
       <c r="F1341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1341" t="n">
         <v>0</v>
@@ -71996,25 +71988,25 @@
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS.NOVAMED</t>
+          <t>FLUCONAZOL 200MG CJA X 10 UND EXPORF</t>
         </is>
       </c>
       <c r="C1342" t="inlineStr">
         <is>
-          <t>7703546927468</t>
+          <t>7703432421681</t>
         </is>
       </c>
       <c r="D1342" t="inlineStr"/>
       <c r="E1342" t="n">
-        <v>10900</v>
+        <v>18300</v>
       </c>
       <c r="F1342" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G1342" t="n">
         <v>0</v>
@@ -72050,18 +72042,18 @@
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>Fluconazol Suspension</t>
+          <t>FLUCONAZOL 200MG X 4 CAPS DE GENFAR</t>
         </is>
       </c>
       <c r="C1343" t="inlineStr"/>
       <c r="D1343" t="inlineStr"/>
       <c r="E1343" t="n">
-        <v>148000</v>
+        <v>16900</v>
       </c>
       <c r="F1343" t="n">
         <v>2</v>
@@ -72100,21 +72092,25 @@
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>FUNGI-FIN LOCION GOTAS TOPICA 20ML</t>
-        </is>
-      </c>
-      <c r="C1344" t="inlineStr"/>
+          <t>FLUCONAZOL 200MG X 4 CAPS. LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>7703763480166</t>
+        </is>
+      </c>
       <c r="D1344" t="inlineStr"/>
       <c r="E1344" t="n">
-        <v>15966.386555</v>
+        <v>14700</v>
       </c>
       <c r="F1344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1344" t="n">
         <v>0</v>
@@ -72142,7 +72138,7 @@
       </c>
       <c r="M1344" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1344" t="inlineStr"/>
@@ -72150,29 +72146,25 @@
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>GASTROFAST ADVANCE</t>
+          <t>FLUCONAZOL 200MG X 4 CAPS.NOVAMED</t>
         </is>
       </c>
       <c r="C1345" t="inlineStr">
         <is>
-          <t>7702057803254</t>
-        </is>
-      </c>
-      <c r="D1345" t="inlineStr">
-        <is>
-          <t>se subio A 3800 ANTES 3.600, LEYDI</t>
-        </is>
-      </c>
+          <t>7703546927468</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr"/>
       <c r="E1345" t="n">
-        <v>3800</v>
+        <v>10900</v>
       </c>
       <c r="F1345" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G1345" t="n">
         <v>0</v>
@@ -72208,21 +72200,21 @@
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>GASTROFAST ADVANCE X 240 ML</t>
+          <t>Fluconazol Suspension</t>
         </is>
       </c>
       <c r="C1346" t="inlineStr"/>
       <c r="D1346" t="inlineStr"/>
       <c r="E1346" t="n">
-        <v>69500</v>
+        <v>148000</v>
       </c>
       <c r="F1346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1346" t="n">
         <v>0</v>
@@ -72258,22 +72250,18 @@
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>gatorade</t>
-        </is>
-      </c>
-      <c r="C1347" t="inlineStr">
-        <is>
-          <t>248656546</t>
-        </is>
-      </c>
+          <t>FUNGI-FIN LOCION GOTAS TOPICA 20ML</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr"/>
       <c r="D1347" t="inlineStr"/>
       <c r="E1347" t="n">
-        <v>3782</v>
+        <v>15966.386555</v>
       </c>
       <c r="F1347" t="n">
         <v>0</v>
@@ -72312,21 +72300,21 @@
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>GEL BACHUE 150GR</t>
+          <t>GALLETA OREO PAQUETE X 6 UNDS</t>
         </is>
       </c>
       <c r="C1348" t="inlineStr"/>
       <c r="D1348" t="inlineStr"/>
       <c r="E1348" t="n">
-        <v>8800</v>
+        <v>1932.773109</v>
       </c>
       <c r="F1348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1348" t="n">
         <v>0</v>
@@ -72354,7 +72342,7 @@
       </c>
       <c r="M1348" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1348" t="inlineStr"/>
@@ -72362,21 +72350,21 @@
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>GEMFIBROZILO 600 MG</t>
+          <t>GASEOSA PREMIO 400ML ROJO</t>
         </is>
       </c>
       <c r="C1349" t="inlineStr"/>
       <c r="D1349" t="inlineStr"/>
       <c r="E1349" t="n">
-        <v>8300</v>
+        <v>2941.176471</v>
       </c>
       <c r="F1349" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1349" t="n">
         <v>0</v>
@@ -72404,7 +72392,7 @@
       </c>
       <c r="M1349" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1349" t="inlineStr"/>
@@ -72412,21 +72400,29 @@
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>GLICERINA CARBONATADA X 20ML FCO YOMA</t>
-        </is>
-      </c>
-      <c r="C1350" t="inlineStr"/>
-      <c r="D1350" t="inlineStr"/>
+          <t>GASTROFAST ADVANCE</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>7702057803254</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>se subio A 3800 ANTES 3.600, LEYDI</t>
+        </is>
+      </c>
       <c r="E1350" t="n">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="F1350" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G1350" t="n">
         <v>0</v>
@@ -72462,18 +72458,18 @@
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
+          <t>GASTROFAST ADVANCE X 240 ML</t>
         </is>
       </c>
       <c r="C1351" t="inlineStr"/>
       <c r="D1351" t="inlineStr"/>
       <c r="E1351" t="n">
-        <v>3361.344538</v>
+        <v>69500</v>
       </c>
       <c r="F1351" t="n">
         <v>1</v>
@@ -72504,7 +72500,7 @@
       </c>
       <c r="M1351" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1351" t="inlineStr"/>
@@ -72512,21 +72508,25 @@
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1352" t="inlineStr"/>
+          <t>gatorade</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>248656546</t>
+        </is>
+      </c>
       <c r="D1352" t="inlineStr"/>
       <c r="E1352" t="n">
-        <v>23109.243697</v>
+        <v>3782</v>
       </c>
       <c r="F1352" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G1352" t="n">
         <v>0</v>
@@ -72562,25 +72562,21 @@
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1353" t="inlineStr">
-        <is>
-          <t>7709195419279</t>
-        </is>
-      </c>
+          <t>GEL BACHUE 150GR</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr"/>
       <c r="D1353" t="inlineStr"/>
       <c r="E1353" t="n">
-        <v>24370</v>
+        <v>8800</v>
       </c>
       <c r="F1353" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G1353" t="n">
         <v>0</v>
@@ -72608,7 +72604,7 @@
       </c>
       <c r="M1353" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1353" t="inlineStr"/>
@@ -72616,21 +72612,21 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
+          <t>GEMFIBROZILO 600 MG</t>
         </is>
       </c>
       <c r="C1354" t="inlineStr"/>
       <c r="D1354" t="inlineStr"/>
       <c r="E1354" t="n">
-        <v>24369.747899</v>
+        <v>8300</v>
       </c>
       <c r="F1354" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="G1354" t="n">
         <v>0</v>
@@ -72658,7 +72654,7 @@
       </c>
       <c r="M1354" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1354" t="inlineStr"/>
@@ -72666,21 +72662,21 @@
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
+          <t>GLICERINA CARBONATADA X 20ML FCO YOMA</t>
         </is>
       </c>
       <c r="C1355" t="inlineStr"/>
       <c r="D1355" t="inlineStr"/>
       <c r="E1355" t="n">
-        <v>23109.243697</v>
+        <v>3900</v>
       </c>
       <c r="F1355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1355" t="n">
         <v>0</v>
@@ -72708,7 +72704,7 @@
       </c>
       <c r="M1355" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1355" t="inlineStr"/>
@@ -72716,18 +72712,18 @@
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>HEPATODREN JARABE FCO X 240ML</t>
+          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
         </is>
       </c>
       <c r="C1356" t="inlineStr"/>
       <c r="D1356" t="inlineStr"/>
       <c r="E1356" t="n">
-        <v>34500</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1356" t="n">
         <v>1</v>
@@ -72758,7 +72754,7 @@
       </c>
       <c r="M1356" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1356" t="inlineStr"/>
@@ -72766,21 +72762,21 @@
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>HEPATODREN X 60 CAPSULAS</t>
+          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
         </is>
       </c>
       <c r="C1357" t="inlineStr"/>
       <c r="D1357" t="inlineStr"/>
       <c r="E1357" t="n">
-        <v>58300</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1357" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="G1357" t="n">
         <v>0</v>
@@ -72808,7 +72804,7 @@
       </c>
       <c r="M1357" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1357" t="inlineStr"/>
@@ -72816,25 +72812,25 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>Hidraplus 75 zinc uva 400ml</t>
+          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
         </is>
       </c>
       <c r="C1358" t="inlineStr">
         <is>
-          <t>7702057010928</t>
+          <t>7709195419279</t>
         </is>
       </c>
       <c r="D1358" t="inlineStr"/>
       <c r="E1358" t="n">
-        <v>10600</v>
+        <v>24370</v>
       </c>
       <c r="F1358" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G1358" t="n">
         <v>0</v>
@@ -72862,7 +72858,7 @@
       </c>
       <c r="M1358" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1358" t="inlineStr"/>
@@ -72870,21 +72866,21 @@
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
+          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
         </is>
       </c>
       <c r="C1359" t="inlineStr"/>
       <c r="D1359" t="inlineStr"/>
       <c r="E1359" t="n">
-        <v>15900</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1359" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G1359" t="n">
         <v>0</v>
@@ -72912,7 +72908,7 @@
       </c>
       <c r="M1359" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1359" t="inlineStr"/>
@@ -72920,22 +72916,18 @@
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
-        </is>
-      </c>
-      <c r="C1360" t="inlineStr">
-        <is>
-          <t>77099475597789</t>
-        </is>
-      </c>
+          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr"/>
       <c r="D1360" t="inlineStr"/>
       <c r="E1360" t="n">
-        <v>28000</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1360" t="n">
         <v>0</v>
@@ -72966,7 +72958,7 @@
       </c>
       <c r="M1360" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1360" t="inlineStr"/>
@@ -72974,25 +72966,21 @@
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>Hidroxicina 0.25 JBE x 120 ML</t>
-        </is>
-      </c>
-      <c r="C1361" t="inlineStr">
-        <is>
-          <t>7707035540596</t>
-        </is>
-      </c>
+          <t>HALLS BARRA SURTIDOS SABORES</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr"/>
       <c r="D1361" t="inlineStr"/>
       <c r="E1361" t="n">
-        <v>11000</v>
+        <v>2100.840336</v>
       </c>
       <c r="F1361" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1361" t="n">
         <v>0</v>
@@ -73020,7 +73008,7 @@
       </c>
       <c r="M1361" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1361" t="inlineStr"/>
@@ -73028,21 +73016,21 @@
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
+          <t>HALLS PEPA ROJO CEREZA X UND</t>
         </is>
       </c>
       <c r="C1362" t="inlineStr"/>
       <c r="D1362" t="inlineStr"/>
       <c r="E1362" t="n">
-        <v>4500</v>
+        <v>336.134454</v>
       </c>
       <c r="F1362" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1362" t="n">
         <v>0</v>
@@ -73070,7 +73058,7 @@
       </c>
       <c r="M1362" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1362" t="inlineStr"/>
@@ -73078,21 +73066,21 @@
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
+          <t>HEPATODREN JARABE FCO X 240ML</t>
         </is>
       </c>
       <c r="C1363" t="inlineStr"/>
       <c r="D1363" t="inlineStr"/>
       <c r="E1363" t="n">
-        <v>6900</v>
+        <v>34500</v>
       </c>
       <c r="F1363" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1363" t="n">
         <v>0</v>
@@ -73128,21 +73116,21 @@
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
+          <t>HEPATODREN X 60 CAPSULAS</t>
         </is>
       </c>
       <c r="C1364" t="inlineStr"/>
       <c r="D1364" t="inlineStr"/>
       <c r="E1364" t="n">
-        <v>12000</v>
+        <v>58300</v>
       </c>
       <c r="F1364" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1364" t="n">
         <v>0</v>
@@ -73178,18 +73166,22 @@
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>Hylo Gel</t>
-        </is>
-      </c>
-      <c r="C1365" t="inlineStr"/>
+          <t>Hidraplus 75 zinc uva 400ml</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>7702057010928</t>
+        </is>
+      </c>
       <c r="D1365" t="inlineStr"/>
       <c r="E1365" t="n">
-        <v>131600</v>
+        <v>10600</v>
       </c>
       <c r="F1365" t="n">
         <v>0</v>
@@ -73228,25 +73220,21 @@
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>IBUPROFENO 400MG/ GENFAR</t>
-        </is>
-      </c>
-      <c r="C1366" t="inlineStr">
-        <is>
-          <t>7702605101498</t>
-        </is>
-      </c>
+          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr"/>
       <c r="D1366" t="inlineStr"/>
       <c r="E1366" t="n">
-        <v>4400</v>
+        <v>15900</v>
       </c>
       <c r="F1366" t="n">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="G1366" t="n">
         <v>0</v>
@@ -73282,22 +73270,22 @@
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>Ibuprofeno 800mg AG</t>
+          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
         </is>
       </c>
       <c r="C1367" t="inlineStr">
         <is>
-          <t>7706569000385</t>
+          <t>77099475597789</t>
         </is>
       </c>
       <c r="D1367" t="inlineStr"/>
       <c r="E1367" t="n">
-        <v>800</v>
+        <v>28000</v>
       </c>
       <c r="F1367" t="n">
         <v>0</v>
@@ -73336,22 +73324,22 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
+          <t>Hidroxicina 0.25 JBE x 120 ML</t>
         </is>
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>7705959885229</t>
+          <t>7707035540596</t>
         </is>
       </c>
       <c r="D1368" t="inlineStr"/>
       <c r="E1368" t="n">
-        <v>17900</v>
+        <v>11000</v>
       </c>
       <c r="F1368" t="n">
         <v>2</v>
@@ -73390,22 +73378,18 @@
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>ICE POWER 30 GR GEL COSMETICA</t>
-        </is>
-      </c>
-      <c r="C1369" t="inlineStr">
-        <is>
-          <t>737186238889</t>
-        </is>
-      </c>
+          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr"/>
       <c r="D1369" t="inlineStr"/>
       <c r="E1369" t="n">
-        <v>12521.008403</v>
+        <v>4500</v>
       </c>
       <c r="F1369" t="n">
         <v>2</v>
@@ -73436,7 +73420,7 @@
       </c>
       <c r="M1369" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1369" t="inlineStr"/>
@@ -73444,21 +73428,21 @@
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
+          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
         </is>
       </c>
       <c r="C1370" t="inlineStr"/>
       <c r="D1370" t="inlineStr"/>
       <c r="E1370" t="n">
-        <v>38900</v>
+        <v>6900</v>
       </c>
       <c r="F1370" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1370" t="n">
         <v>0</v>
@@ -73494,21 +73478,21 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
+          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
         </is>
       </c>
       <c r="C1371" t="inlineStr"/>
       <c r="D1371" t="inlineStr"/>
       <c r="E1371" t="n">
-        <v>38900</v>
+        <v>12000</v>
       </c>
       <c r="F1371" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1371" t="n">
         <v>0</v>
@@ -73544,21 +73528,21 @@
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
+          <t>Hylo Gel</t>
         </is>
       </c>
       <c r="C1372" t="inlineStr"/>
       <c r="D1372" t="inlineStr"/>
       <c r="E1372" t="n">
-        <v>8235.294118</v>
+        <v>131600</v>
       </c>
       <c r="F1372" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1372" t="n">
         <v>0</v>
@@ -73586,7 +73570,7 @@
       </c>
       <c r="M1372" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1372" t="inlineStr"/>
@@ -73594,21 +73578,25 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
-        </is>
-      </c>
-      <c r="C1373" t="inlineStr"/>
+          <t>IBUPROFENO 400MG/ GENFAR</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>7702605101498</t>
+        </is>
+      </c>
       <c r="D1373" t="inlineStr"/>
       <c r="E1373" t="n">
-        <v>9831.932773</v>
+        <v>4400</v>
       </c>
       <c r="F1373" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="G1373" t="n">
         <v>0</v>
@@ -73636,7 +73624,7 @@
       </c>
       <c r="M1373" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1373" t="inlineStr"/>
@@ -73644,21 +73632,25 @@
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
-        </is>
-      </c>
-      <c r="C1374" t="inlineStr"/>
+          <t>Ibuprofeno 800mg AG</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>7706569000385</t>
+        </is>
+      </c>
       <c r="D1374" t="inlineStr"/>
       <c r="E1374" t="n">
-        <v>4201.680672</v>
+        <v>800</v>
       </c>
       <c r="F1374" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1374" t="n">
         <v>0</v>
@@ -73686,7 +73678,7 @@
       </c>
       <c r="M1374" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1374" t="inlineStr"/>
@@ -73694,18 +73686,22 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
-        </is>
-      </c>
-      <c r="C1375" t="inlineStr"/>
+          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>7705959885229</t>
+        </is>
+      </c>
       <c r="D1375" t="inlineStr"/>
       <c r="E1375" t="n">
-        <v>4201.680672</v>
+        <v>17900</v>
       </c>
       <c r="F1375" t="n">
         <v>2</v>
@@ -73736,7 +73732,7 @@
       </c>
       <c r="M1375" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1375" t="inlineStr"/>
@@ -73744,18 +73740,22 @@
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>JABON PROTEX HERBAL 110GR</t>
-        </is>
-      </c>
-      <c r="C1376" t="inlineStr"/>
+          <t>ICE POWER 30 GR GEL COSMETICA</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>737186238889</t>
+        </is>
+      </c>
       <c r="D1376" t="inlineStr"/>
       <c r="E1376" t="n">
-        <v>4537.815126</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1376" t="n">
         <v>2</v>
@@ -73794,25 +73794,21 @@
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>JARABE ZETYGRIP FCO 60ML</t>
-        </is>
-      </c>
-      <c r="C1377" t="inlineStr">
-        <is>
-          <t>7709805542830</t>
-        </is>
-      </c>
+          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr"/>
       <c r="D1377" t="inlineStr"/>
       <c r="E1377" t="n">
-        <v>14000</v>
+        <v>38900</v>
       </c>
       <c r="F1377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1377" t="n">
         <v>0</v>
@@ -73848,21 +73844,21 @@
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>JERINGA DE 50ML</t>
+          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
         </is>
       </c>
       <c r="C1378" t="inlineStr"/>
       <c r="D1378" t="inlineStr"/>
       <c r="E1378" t="n">
-        <v>2500</v>
+        <v>38900</v>
       </c>
       <c r="F1378" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1378" t="n">
         <v>0</v>
@@ -73898,21 +73894,21 @@
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>Jeringa desechable estéril 20ml impormedicas</t>
+          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
         </is>
       </c>
       <c r="C1379" t="inlineStr"/>
       <c r="D1379" t="inlineStr"/>
       <c r="E1379" t="n">
-        <v>920</v>
+        <v>8235.294118</v>
       </c>
       <c r="F1379" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G1379" t="n">
         <v>0</v>
@@ -73948,21 +73944,21 @@
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
+          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
         </is>
       </c>
       <c r="C1380" t="inlineStr"/>
       <c r="D1380" t="inlineStr"/>
       <c r="E1380" t="n">
-        <v>1100</v>
+        <v>9831.932773</v>
       </c>
       <c r="F1380" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="G1380" t="n">
         <v>0</v>
@@ -73990,7 +73986,7 @@
       </c>
       <c r="M1380" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1380" t="inlineStr"/>
@@ -73998,21 +73994,21 @@
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>Kelocate</t>
+          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
         </is>
       </c>
       <c r="C1381" t="inlineStr"/>
       <c r="D1381" t="inlineStr"/>
       <c r="E1381" t="n">
-        <v>180000</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1381" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1381" t="n">
         <v>0</v>
@@ -74040,7 +74036,7 @@
       </c>
       <c r="M1381" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1381" t="inlineStr"/>
@@ -74048,25 +74044,21 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
-        </is>
-      </c>
-      <c r="C1382" t="inlineStr">
-        <is>
-          <t>7702057073695</t>
-        </is>
-      </c>
+          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr"/>
       <c r="D1382" t="inlineStr"/>
       <c r="E1382" t="n">
-        <v>19500</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1382" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1382" t="n">
         <v>0</v>
@@ -74094,7 +74086,7 @@
       </c>
       <c r="M1382" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1382" t="inlineStr"/>
@@ -74102,25 +74094,21 @@
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
-        </is>
-      </c>
-      <c r="C1383" t="inlineStr">
-        <is>
-          <t>7709947559772</t>
-        </is>
-      </c>
+          <t>JABON PROTEX HERBAL 110GR</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr"/>
       <c r="D1383" t="inlineStr"/>
       <c r="E1383" t="n">
-        <v>15000</v>
+        <v>4537.815126</v>
       </c>
       <c r="F1383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1383" t="n">
         <v>0</v>
@@ -74148,7 +74136,7 @@
       </c>
       <c r="M1383" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1383" t="inlineStr"/>
@@ -74156,21 +74144,25 @@
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
-        </is>
-      </c>
-      <c r="C1384" t="inlineStr"/>
+          <t>JARABE ZETYGRIP FCO 60ML</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>7709805542830</t>
+        </is>
+      </c>
       <c r="D1384" t="inlineStr"/>
       <c r="E1384" t="n">
-        <v>71000</v>
+        <v>14000</v>
       </c>
       <c r="F1384" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1384" t="n">
         <v>0</v>
@@ -74206,25 +74198,21 @@
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>Levotiroxina 100mcg MK</t>
-        </is>
-      </c>
-      <c r="C1385" t="inlineStr">
-        <is>
-          <t>7702057715908</t>
-        </is>
-      </c>
+          <t>JERINGA DE 50ML</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr"/>
       <c r="D1385" t="inlineStr"/>
       <c r="E1385" t="n">
-        <v>27900</v>
+        <v>2500</v>
       </c>
       <c r="F1385" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1385" t="n">
         <v>0</v>
@@ -74260,21 +74248,21 @@
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>LIMA MAYOMI 10/180</t>
+          <t>Jeringa desechable estéril 20ml impormedicas</t>
         </is>
       </c>
       <c r="C1386" t="inlineStr"/>
       <c r="D1386" t="inlineStr"/>
       <c r="E1386" t="n">
-        <v>3900</v>
+        <v>920</v>
       </c>
       <c r="F1386" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="G1386" t="n">
         <v>0</v>
@@ -74302,7 +74290,7 @@
       </c>
       <c r="M1386" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1386" t="inlineStr"/>
@@ -74310,21 +74298,21 @@
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
+          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr"/>
       <c r="D1387" t="inlineStr"/>
       <c r="E1387" t="n">
-        <v>16807</v>
+        <v>1100</v>
       </c>
       <c r="F1387" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G1387" t="n">
         <v>0</v>
@@ -74352,7 +74340,7 @@
       </c>
       <c r="M1387" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1387" t="inlineStr"/>
@@ -74360,21 +74348,21 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
+          <t>Kelocate</t>
         </is>
       </c>
       <c r="C1388" t="inlineStr"/>
       <c r="D1388" t="inlineStr"/>
       <c r="E1388" t="n">
-        <v>15042.016807</v>
+        <v>180000</v>
       </c>
       <c r="F1388" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1388" t="n">
         <v>0</v>
@@ -74402,7 +74390,7 @@
       </c>
       <c r="M1388" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1388" t="inlineStr"/>
@@ -74410,21 +74398,25 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>LISTERINE CUIDADO TOTAL 180ML</t>
-        </is>
-      </c>
-      <c r="C1389" t="inlineStr"/>
+          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>7702057073695</t>
+        </is>
+      </c>
       <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="n">
-        <v>16386.554622</v>
+        <v>19500</v>
       </c>
       <c r="F1389" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1389" t="n">
         <v>0</v>
@@ -74452,7 +74444,7 @@
       </c>
       <c r="M1389" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1389" t="inlineStr"/>
@@ -74460,21 +74452,25 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
-        </is>
-      </c>
-      <c r="C1390" t="inlineStr"/>
+          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>7709947559772</t>
+        </is>
+      </c>
       <c r="D1390" t="inlineStr"/>
       <c r="E1390" t="n">
-        <v>3500</v>
+        <v>15000</v>
       </c>
       <c r="F1390" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G1390" t="n">
         <v>0</v>
@@ -74510,21 +74506,21 @@
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
         </is>
       </c>
       <c r="C1391" t="inlineStr"/>
       <c r="D1391" t="inlineStr"/>
       <c r="E1391" t="n">
-        <v>3500</v>
+        <v>71000</v>
       </c>
       <c r="F1391" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1391" t="n">
         <v>0</v>
@@ -74560,21 +74556,25 @@
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
-        </is>
-      </c>
-      <c r="C1392" t="inlineStr"/>
+          <t>Levotiroxina 100mcg MK</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>7702057715908</t>
+        </is>
+      </c>
       <c r="D1392" t="inlineStr"/>
       <c r="E1392" t="n">
-        <v>4500</v>
+        <v>27900</v>
       </c>
       <c r="F1392" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1392" t="n">
         <v>0</v>
@@ -74610,22 +74610,18 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>Losartan Tensofar 100 Mg</t>
-        </is>
-      </c>
-      <c r="C1393" t="inlineStr">
-        <is>
-          <t>7703546012119</t>
-        </is>
-      </c>
+          <t>LIMA MAYOMI 10/180</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr"/>
       <c r="D1393" t="inlineStr"/>
       <c r="E1393" t="n">
-        <v>5000</v>
+        <v>3900</v>
       </c>
       <c r="F1393" t="n">
         <v>1</v>
@@ -74664,22 +74660,18 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
-        </is>
-      </c>
-      <c r="C1394" t="inlineStr">
-        <is>
-          <t>7501007528939</t>
-        </is>
-      </c>
+          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr"/>
       <c r="D1394" t="inlineStr"/>
       <c r="E1394" t="n">
-        <v>18907.563025</v>
+        <v>16807</v>
       </c>
       <c r="F1394" t="n">
         <v>0</v>
@@ -74718,21 +74710,21 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>MANTECA DE CACAO LABIAL LIMON</t>
+          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
         </is>
       </c>
       <c r="C1395" t="inlineStr"/>
       <c r="D1395" t="inlineStr"/>
       <c r="E1395" t="n">
-        <v>3361.344538</v>
+        <v>15042.016807</v>
       </c>
       <c r="F1395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1395" t="n">
         <v>0</v>
@@ -74768,21 +74760,21 @@
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
+          <t>LISTERINE CUIDADO TOTAL 180ML</t>
         </is>
       </c>
       <c r="C1396" t="inlineStr"/>
       <c r="D1396" t="inlineStr"/>
       <c r="E1396" t="n">
-        <v>3361.344538</v>
+        <v>16386.554622</v>
       </c>
       <c r="F1396" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1396" t="n">
         <v>0</v>
@@ -74818,21 +74810,21 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>Mega sex</t>
+          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
         </is>
       </c>
       <c r="C1397" t="inlineStr"/>
       <c r="D1397" t="inlineStr"/>
       <c r="E1397" t="n">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="F1397" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G1397" t="n">
         <v>0</v>
@@ -74868,29 +74860,21 @@
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>Melatonina 3mg</t>
-        </is>
-      </c>
-      <c r="C1398" t="inlineStr">
-        <is>
-          <t>7706849112906</t>
-        </is>
-      </c>
-      <c r="D1398" t="inlineStr">
-        <is>
-          <t>producto nuevo</t>
-        </is>
-      </c>
+          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr"/>
+      <c r="D1398" t="inlineStr"/>
       <c r="E1398" t="n">
-        <v>52000</v>
+        <v>3500</v>
       </c>
       <c r="F1398" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1398" t="n">
         <v>0</v>
@@ -74926,25 +74910,21 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
-        </is>
-      </c>
-      <c r="C1399" t="inlineStr">
-        <is>
-          <t>7707529435209</t>
-        </is>
-      </c>
+          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr"/>
       <c r="D1399" t="inlineStr"/>
       <c r="E1399" t="n">
-        <v>36000</v>
+        <v>4500</v>
       </c>
       <c r="F1399" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1399" t="n">
         <v>0</v>
@@ -74980,25 +74960,25 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>Meloxicam 15mg AG</t>
+          <t>Losartan Tensofar 100 Mg</t>
         </is>
       </c>
       <c r="C1400" t="inlineStr">
         <is>
-          <t>7706569020437</t>
+          <t>7703546012119</t>
         </is>
       </c>
       <c r="D1400" t="inlineStr"/>
       <c r="E1400" t="n">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="F1400" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1400" t="n">
         <v>0</v>
@@ -75034,21 +75014,25 @@
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
-        </is>
-      </c>
-      <c r="C1401" t="inlineStr"/>
+          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>7501007528939</t>
+        </is>
+      </c>
       <c r="D1401" t="inlineStr"/>
       <c r="E1401" t="n">
-        <v>9700</v>
+        <v>18907.563025</v>
       </c>
       <c r="F1401" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1401" t="n">
         <v>0</v>
@@ -75076,7 +75060,7 @@
       </c>
       <c r="M1401" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1401" t="inlineStr"/>
@@ -75084,22 +75068,18 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>MELOXICAM COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1402" t="inlineStr">
-        <is>
-          <t>7703712036253</t>
-        </is>
-      </c>
+          <t>MANTECA DE CACAO LABIAL LIMON</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr"/>
       <c r="D1402" t="inlineStr"/>
       <c r="E1402" t="n">
-        <v>1300</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1402" t="n">
         <v>0</v>
@@ -75128,31 +75108,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1402" t="inlineStr"/>
+      <c r="M1402" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
       <c r="N1402" t="inlineStr"/>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>metformina 850 mg pisa</t>
-        </is>
-      </c>
-      <c r="C1403" t="inlineStr">
-        <is>
-          <t>7501125188039</t>
-        </is>
-      </c>
+          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr"/>
       <c r="D1403" t="inlineStr"/>
       <c r="E1403" t="n">
-        <v>5500</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1403" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G1403" t="n">
         <v>0</v>
@@ -75180,7 +75160,7 @@
       </c>
       <c r="M1403" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1403" t="inlineStr"/>
@@ -75188,25 +75168,21 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10MG RECIPE</t>
-        </is>
-      </c>
-      <c r="C1404" t="inlineStr">
-        <is>
-          <t>7702195084355</t>
-        </is>
-      </c>
+          <t>Mega sex</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr"/>
       <c r="D1404" t="inlineStr"/>
       <c r="E1404" t="n">
-        <v>1000</v>
+        <v>3200</v>
       </c>
       <c r="F1404" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G1404" t="n">
         <v>0</v>
@@ -75242,25 +75218,29 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>MICROPOR 1X3 Y</t>
+          <t>Melatonina 3mg</t>
         </is>
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>7707282990205</t>
-        </is>
-      </c>
-      <c r="D1405" t="inlineStr"/>
+          <t>7706849112906</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>producto nuevo</t>
+        </is>
+      </c>
       <c r="E1405" t="n">
-        <v>5300</v>
+        <v>52000</v>
       </c>
       <c r="F1405" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1405" t="n">
         <v>0</v>
@@ -75296,25 +75276,25 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>MICROPOR CINTA 1/2X5Y</t>
+          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
         </is>
       </c>
       <c r="C1406" t="inlineStr">
         <is>
-          <t>7707282990182</t>
+          <t>7707529435209</t>
         </is>
       </c>
       <c r="D1406" t="inlineStr"/>
       <c r="E1406" t="n">
-        <v>3900</v>
+        <v>36000</v>
       </c>
       <c r="F1406" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G1406" t="n">
         <v>0</v>
@@ -75350,18 +75330,22 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>MICROPORE COLOR PIEL 2YARDAS</t>
-        </is>
-      </c>
-      <c r="C1407" t="inlineStr"/>
+          <t>Meloxicam 15mg AG</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>7706569020437</t>
+        </is>
+      </c>
       <c r="D1407" t="inlineStr"/>
       <c r="E1407" t="n">
-        <v>3700</v>
+        <v>1500</v>
       </c>
       <c r="F1407" t="n">
         <v>0</v>
@@ -75400,21 +75384,21 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
+          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
         </is>
       </c>
       <c r="C1408" t="inlineStr"/>
       <c r="D1408" t="inlineStr"/>
       <c r="E1408" t="n">
-        <v>4000</v>
+        <v>9700</v>
       </c>
       <c r="F1408" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1408" t="n">
         <v>0</v>
@@ -75450,22 +75434,22 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>MIELTERTOS JARABE X 240ML</t>
+          <t>MELOXICAM COASPHARMA</t>
         </is>
       </c>
       <c r="C1409" t="inlineStr">
         <is>
-          <t>7707232095608</t>
+          <t>7703712036253</t>
         </is>
       </c>
       <c r="D1409" t="inlineStr"/>
       <c r="E1409" t="n">
-        <v>34500</v>
+        <v>1300</v>
       </c>
       <c r="F1409" t="n">
         <v>0</v>
@@ -75494,35 +75478,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1409" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1409" t="inlineStr"/>
       <c r="N1409" t="inlineStr"/>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
-        </is>
-      </c>
-      <c r="C1410" t="inlineStr"/>
-      <c r="D1410" t="inlineStr">
-        <is>
-          <t>subio precio hector</t>
-        </is>
-      </c>
+          <t>metformina 850 mg pisa</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>7501125188039</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr"/>
       <c r="E1410" t="n">
-        <v>22700</v>
+        <v>5500</v>
       </c>
       <c r="F1410" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G1410" t="n">
         <v>0</v>
@@ -75558,21 +75538,25 @@
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
-        </is>
-      </c>
-      <c r="C1411" t="inlineStr"/>
+          <t>METOCLOPRAMIDA 10MG RECIPE</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>7702195084355</t>
+        </is>
+      </c>
       <c r="D1411" t="inlineStr"/>
       <c r="E1411" t="n">
-        <v>5500</v>
+        <v>1000</v>
       </c>
       <c r="F1411" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G1411" t="n">
         <v>0</v>
@@ -75608,21 +75592,25 @@
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>NEOSALDINA TABLETA X UND</t>
-        </is>
-      </c>
-      <c r="C1412" t="inlineStr"/>
+          <t>MICROPOR 1X3 Y</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>7707282990205</t>
+        </is>
+      </c>
       <c r="D1412" t="inlineStr"/>
       <c r="E1412" t="n">
-        <v>2500</v>
+        <v>5300</v>
       </c>
       <c r="F1412" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G1412" t="n">
         <v>0</v>
@@ -75658,21 +75646,25 @@
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>NIFEDIPINO 30MG NOVAMED</t>
-        </is>
-      </c>
-      <c r="C1413" t="inlineStr"/>
+          <t>MICROPOR CINTA 1/2X5Y</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>7707282990182</t>
+        </is>
+      </c>
       <c r="D1413" t="inlineStr"/>
       <c r="E1413" t="n">
-        <v>19000</v>
+        <v>3900</v>
       </c>
       <c r="F1413" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G1413" t="n">
         <v>0</v>
@@ -75708,18 +75700,18 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
+          <t>MICROPORE COLOR PIEL 2YARDAS</t>
         </is>
       </c>
       <c r="C1414" t="inlineStr"/>
       <c r="D1414" t="inlineStr"/>
       <c r="E1414" t="n">
-        <v>23000</v>
+        <v>3700</v>
       </c>
       <c r="F1414" t="n">
         <v>0</v>
@@ -75758,18 +75750,18 @@
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>NITOXIPAR X 6 TABLETAS</t>
+          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
         </is>
       </c>
       <c r="C1415" t="inlineStr"/>
       <c r="D1415" t="inlineStr"/>
       <c r="E1415" t="n">
-        <v>24500</v>
+        <v>4000</v>
       </c>
       <c r="F1415" t="n">
         <v>0</v>
@@ -75808,21 +75800,25 @@
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>NORAVER SPRAY CEREZA 120ML</t>
-        </is>
-      </c>
-      <c r="C1416" t="inlineStr"/>
+          <t>MIELTERTOS JARABE X 240ML</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>7707232095608</t>
+        </is>
+      </c>
       <c r="D1416" t="inlineStr"/>
       <c r="E1416" t="n">
-        <v>52900</v>
+        <v>34500</v>
       </c>
       <c r="F1416" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1416" t="n">
         <v>0</v>
@@ -75858,25 +75854,25 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
-        </is>
-      </c>
-      <c r="C1417" t="inlineStr">
-        <is>
-          <t>7702027041662</t>
-        </is>
-      </c>
-      <c r="D1417" t="inlineStr"/>
+          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr"/>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>subio precio hector</t>
+        </is>
+      </c>
       <c r="E1417" t="n">
-        <v>6300</v>
+        <v>22700</v>
       </c>
       <c r="F1417" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1417" t="n">
         <v>0</v>
@@ -75912,21 +75908,21 @@
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
         </is>
       </c>
       <c r="C1418" t="inlineStr"/>
       <c r="D1418" t="inlineStr"/>
       <c r="E1418" t="n">
-        <v>8823.529412</v>
+        <v>5500</v>
       </c>
       <c r="F1418" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G1418" t="n">
         <v>0</v>
@@ -75954,7 +75950,7 @@
       </c>
       <c r="M1418" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1418" t="inlineStr"/>
@@ -75962,25 +75958,21 @@
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
-        </is>
-      </c>
-      <c r="C1419" t="inlineStr">
-        <is>
-          <t>7702026158644</t>
-        </is>
-      </c>
+          <t>NEOSALDINA TABLETA X UND</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr"/>
       <c r="D1419" t="inlineStr"/>
       <c r="E1419" t="n">
-        <v>8823.529412</v>
+        <v>2500</v>
       </c>
       <c r="F1419" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G1419" t="n">
         <v>0</v>
@@ -76008,7 +76000,7 @@
       </c>
       <c r="M1419" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1419" t="inlineStr"/>
@@ -76016,25 +76008,21 @@
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JBE 120ML</t>
-        </is>
-      </c>
-      <c r="C1420" t="inlineStr">
-        <is>
-          <t>7707355053363</t>
-        </is>
-      </c>
+          <t>NIFEDIPINO 30MG NOVAMED</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr"/>
       <c r="D1420" t="inlineStr"/>
       <c r="E1420" t="n">
-        <v>22700</v>
+        <v>19000</v>
       </c>
       <c r="F1420" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1420" t="n">
         <v>0</v>
@@ -76070,22 +76058,18 @@
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
-        </is>
-      </c>
-      <c r="C1421" t="inlineStr">
-        <is>
-          <t>7707355053356</t>
-        </is>
-      </c>
+          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr"/>
       <c r="D1421" t="inlineStr"/>
       <c r="E1421" t="n">
-        <v>17200</v>
+        <v>23000</v>
       </c>
       <c r="F1421" t="n">
         <v>0</v>
@@ -76124,21 +76108,21 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>NUTRIBELL ACEITE DE COCO</t>
+          <t>NITOXIPAR X 6 TABLETAS</t>
         </is>
       </c>
       <c r="C1422" t="inlineStr"/>
       <c r="D1422" t="inlineStr"/>
       <c r="E1422" t="n">
-        <v>2700</v>
+        <v>24500</v>
       </c>
       <c r="F1422" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1422" t="n">
         <v>0</v>
@@ -76174,29 +76158,21 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>Omega 3 6 9 suplemento totalmax</t>
-        </is>
-      </c>
-      <c r="C1423" t="inlineStr">
-        <is>
-          <t>7707529434974</t>
-        </is>
-      </c>
-      <c r="D1423" t="inlineStr">
-        <is>
-          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
-        </is>
-      </c>
+          <t>NORAVER SPRAY CEREZA 120ML</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr"/>
+      <c r="D1423" t="inlineStr"/>
       <c r="E1423" t="n">
-        <v>35000</v>
+        <v>52900</v>
       </c>
       <c r="F1423" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1423" t="n">
         <v>0</v>
@@ -76232,18 +76208,22 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1424" t="inlineStr"/>
+          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>7702027041662</t>
+        </is>
+      </c>
       <c r="D1424" t="inlineStr"/>
       <c r="E1424" t="n">
-        <v>5500</v>
+        <v>6300</v>
       </c>
       <c r="F1424" t="n">
         <v>0</v>
@@ -76282,22 +76262,18 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
-        </is>
-      </c>
-      <c r="C1425" t="inlineStr">
-        <is>
-          <t>7707529435940</t>
-        </is>
-      </c>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr"/>
       <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="n">
-        <v>35000</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1425" t="n">
         <v>0</v>
@@ -76328,7 +76304,7 @@
       </c>
       <c r="M1425" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1425" t="inlineStr"/>
@@ -76336,21 +76312,25 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
-        </is>
-      </c>
-      <c r="C1426" t="inlineStr"/>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>7702026158644</t>
+        </is>
+      </c>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="n">
-        <v>48000</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1426" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1426" t="n">
         <v>0</v>
@@ -76378,7 +76358,7 @@
       </c>
       <c r="M1426" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1426" t="inlineStr"/>
@@ -76386,22 +76366,22 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>OROCAL CALCIO 600MG</t>
-        </is>
-      </c>
-      <c r="C1427" t="inlineStr"/>
-      <c r="D1427" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>NOXPIRIN JUNIOR JBE 120ML</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>7707355053363</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr"/>
       <c r="E1427" t="n">
-        <v>30500</v>
+        <v>22700</v>
       </c>
       <c r="F1427" t="n">
         <v>1</v>
@@ -76440,21 +76420,25 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>PALA DE MADERA RASPACALLO</t>
-        </is>
-      </c>
-      <c r="C1428" t="inlineStr"/>
+          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>7707355053356</t>
+        </is>
+      </c>
       <c r="D1428" t="inlineStr"/>
       <c r="E1428" t="n">
-        <v>4000</v>
+        <v>17200</v>
       </c>
       <c r="F1428" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1428" t="n">
         <v>0</v>
@@ -76490,21 +76474,21 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>PALO DE NARANJO X UNIDAD</t>
+          <t>NUTRIBELL ACEITE DE COCO</t>
         </is>
       </c>
       <c r="C1429" t="inlineStr"/>
       <c r="D1429" t="inlineStr"/>
       <c r="E1429" t="n">
-        <v>400</v>
+        <v>2700</v>
       </c>
       <c r="F1429" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G1429" t="n">
         <v>0</v>
@@ -76540,25 +76524,29 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
+          <t>Omega 3 6 9 suplemento totalmax</t>
         </is>
       </c>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>7704412170896</t>
-        </is>
-      </c>
-      <c r="D1430" t="inlineStr"/>
+          <t>7707529434974</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
+        </is>
+      </c>
       <c r="E1430" t="n">
-        <v>6200</v>
+        <v>35000</v>
       </c>
       <c r="F1430" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1430" t="n">
         <v>0</v>
@@ -76594,21 +76582,21 @@
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
         </is>
       </c>
       <c r="C1431" t="inlineStr"/>
       <c r="D1431" t="inlineStr"/>
       <c r="E1431" t="n">
-        <v>41176.470588</v>
+        <v>5500</v>
       </c>
       <c r="F1431" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1431" t="n">
         <v>0</v>
@@ -76636,7 +76624,7 @@
       </c>
       <c r="M1431" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1431" t="inlineStr"/>
@@ -76644,25 +76632,25 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Pañales Winny Etapa 5 X PAQUETE</t>
+          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
         </is>
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>7701021114174</t>
+          <t>7707529435940</t>
         </is>
       </c>
       <c r="D1432" t="inlineStr"/>
       <c r="E1432" t="n">
-        <v>41849</v>
+        <v>35000</v>
       </c>
       <c r="F1432" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1432" t="n">
         <v>0</v>
@@ -76690,7 +76678,7 @@
       </c>
       <c r="M1432" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1432" t="inlineStr"/>
@@ -76698,18 +76686,18 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>PAÑALWINNY ETA 5 X 16 UND</t>
+          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
         </is>
       </c>
       <c r="C1433" t="inlineStr"/>
       <c r="D1433" t="inlineStr"/>
       <c r="E1433" t="n">
-        <v>24369.747899</v>
+        <v>48000</v>
       </c>
       <c r="F1433" t="n">
         <v>2</v>
@@ -76740,7 +76728,7 @@
       </c>
       <c r="M1433" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1433" t="inlineStr"/>
@@ -76748,21 +76736,25 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>pañitos humedos pequeñin 100unidades</t>
+          <t>OROCAL CALCIO 600MG</t>
         </is>
       </c>
       <c r="C1434" t="inlineStr"/>
-      <c r="D1434" t="inlineStr"/>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E1434" t="n">
-        <v>10925</v>
+        <v>30500</v>
       </c>
       <c r="F1434" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1434" t="n">
         <v>0</v>
@@ -76790,7 +76782,7 @@
       </c>
       <c r="M1434" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1434" t="inlineStr"/>
@@ -76798,21 +76790,21 @@
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
+          <t>PALA DE MADERA RASPACALLO</t>
         </is>
       </c>
       <c r="C1435" t="inlineStr"/>
       <c r="D1435" t="inlineStr"/>
       <c r="E1435" t="n">
-        <v>14900</v>
+        <v>4000</v>
       </c>
       <c r="F1435" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>
@@ -76848,21 +76840,21 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>Panotil B x 8ML</t>
+          <t>PALO DE NARANJO X UNIDAD</t>
         </is>
       </c>
       <c r="C1436" t="inlineStr"/>
       <c r="D1436" t="inlineStr"/>
       <c r="E1436" t="n">
-        <v>26400</v>
+        <v>400</v>
       </c>
       <c r="F1436" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G1436" t="n">
         <v>0</v>
@@ -76898,25 +76890,25 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>PANTENE ACONDICIONADOR</t>
+          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
         </is>
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>7500435153683</t>
+          <t>7704412170896</t>
         </is>
       </c>
       <c r="D1437" t="inlineStr"/>
       <c r="E1437" t="n">
-        <v>1500</v>
+        <v>6200</v>
       </c>
       <c r="F1437" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1437" t="n">
         <v>0</v>
@@ -76952,21 +76944,21 @@
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Parche Ocular Colostol</t>
+          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
         </is>
       </c>
       <c r="C1438" t="inlineStr"/>
       <c r="D1438" t="inlineStr"/>
       <c r="E1438" t="n">
-        <v>1300</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1438" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G1438" t="n">
         <v>0</v>
@@ -76994,7 +76986,7 @@
       </c>
       <c r="M1438" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1438" t="inlineStr"/>
@@ -77002,22 +76994,18 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
-        </is>
-      </c>
-      <c r="C1439" t="inlineStr">
-        <is>
-          <t>7501033957413</t>
-        </is>
-      </c>
+          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr"/>
       <c r="D1439" t="inlineStr"/>
       <c r="E1439" t="n">
-        <v>10600</v>
+        <v>28991.596639</v>
       </c>
       <c r="F1439" t="n">
         <v>0</v>
@@ -77048,7 +77036,7 @@
       </c>
       <c r="M1439" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1439" t="inlineStr"/>
@@ -77056,29 +77044,21 @@
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
-        </is>
-      </c>
-      <c r="C1440" t="inlineStr">
-        <is>
-          <t>7501033961557</t>
-        </is>
-      </c>
-      <c r="D1440" t="inlineStr">
-        <is>
-          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
-        </is>
-      </c>
+          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr"/>
+      <c r="D1440" t="inlineStr"/>
       <c r="E1440" t="n">
-        <v>10900</v>
+        <v>41176.470588</v>
       </c>
       <c r="F1440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1440" t="n">
         <v>0</v>
@@ -77106,7 +77086,7 @@
       </c>
       <c r="M1440" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1440" t="inlineStr"/>
@@ -77114,29 +77094,25 @@
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+          <t>Pañales Winny Etapa 5 X PAQUETE</t>
         </is>
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>7501033957376</t>
-        </is>
-      </c>
-      <c r="D1441" t="inlineStr">
-        <is>
-          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
-        </is>
-      </c>
+          <t>7701021114174</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr"/>
       <c r="E1441" t="n">
-        <v>10900</v>
+        <v>41849</v>
       </c>
       <c r="F1441" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1441" t="n">
         <v>0</v>
@@ -77164,7 +77140,7 @@
       </c>
       <c r="M1441" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1441" t="inlineStr"/>
@@ -77172,21 +77148,21 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>PEGANTE GLUE X 10GR X UND</t>
+          <t>PAÑALWINNY ETA 5 X 16 UND</t>
         </is>
       </c>
       <c r="C1442" t="inlineStr"/>
       <c r="D1442" t="inlineStr"/>
       <c r="E1442" t="n">
-        <v>2000</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1442" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1442" t="n">
         <v>0</v>
@@ -77214,7 +77190,7 @@
       </c>
       <c r="M1442" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1442" t="inlineStr"/>
@@ -77222,21 +77198,21 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>PEINETA COLA DE RATON METALICA</t>
+          <t>pañitos humedos pequeñin 100unidades</t>
         </is>
       </c>
       <c r="C1443" t="inlineStr"/>
       <c r="D1443" t="inlineStr"/>
       <c r="E1443" t="n">
-        <v>4700</v>
+        <v>10925</v>
       </c>
       <c r="F1443" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1443" t="n">
         <v>0</v>
@@ -77264,7 +77240,7 @@
       </c>
       <c r="M1443" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1443" t="inlineStr"/>
@@ -77272,21 +77248,21 @@
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>PERFILADORES DE CEJAS</t>
+          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
         </is>
       </c>
       <c r="C1444" t="inlineStr"/>
       <c r="D1444" t="inlineStr"/>
       <c r="E1444" t="n">
-        <v>3900</v>
+        <v>14900</v>
       </c>
       <c r="F1444" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1444" t="n">
         <v>0</v>
@@ -77322,18 +77298,18 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
+          <t>Panotil B x 8ML</t>
         </is>
       </c>
       <c r="C1445" t="inlineStr"/>
       <c r="D1445" t="inlineStr"/>
       <c r="E1445" t="n">
-        <v>27983.193277</v>
+        <v>26400</v>
       </c>
       <c r="F1445" t="n">
         <v>1</v>
@@ -77364,7 +77340,7 @@
       </c>
       <c r="M1445" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1445" t="inlineStr"/>
@@ -77372,21 +77348,25 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
-        </is>
-      </c>
-      <c r="C1446" t="inlineStr"/>
+          <t>PANTENE ACONDICIONADOR</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>7500435153683</t>
+        </is>
+      </c>
       <c r="D1446" t="inlineStr"/>
       <c r="E1446" t="n">
-        <v>20500</v>
+        <v>1500</v>
       </c>
       <c r="F1446" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1446" t="n">
         <v>0</v>
@@ -77422,29 +77402,21 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>privatos miel limon la francol 120ml</t>
-        </is>
-      </c>
-      <c r="C1447" t="inlineStr">
-        <is>
-          <t>7702207163948</t>
-        </is>
-      </c>
-      <c r="D1447" t="inlineStr">
-        <is>
-          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
-        </is>
-      </c>
+          <t>Parche Ocular Colostol</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr"/>
+      <c r="D1447" t="inlineStr"/>
       <c r="E1447" t="n">
-        <v>35900</v>
+        <v>1300</v>
       </c>
       <c r="F1447" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G1447" t="n">
         <v>0</v>
@@ -77480,18 +77452,22 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
-        </is>
-      </c>
-      <c r="C1448" t="inlineStr"/>
+          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>7501033957413</t>
+        </is>
+      </c>
       <c r="D1448" t="inlineStr"/>
       <c r="E1448" t="n">
-        <v>0</v>
+        <v>10600</v>
       </c>
       <c r="F1448" t="n">
         <v>0</v>
@@ -77522,7 +77498,7 @@
       </c>
       <c r="M1448" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1448" t="inlineStr"/>
@@ -77530,21 +77506,29 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>PROTECTOR NOSOTRAS LARGOS</t>
-        </is>
-      </c>
-      <c r="C1449" t="inlineStr"/>
-      <c r="D1449" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>7501033961557</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
+        </is>
+      </c>
       <c r="E1449" t="n">
-        <v>3700</v>
+        <v>10900</v>
       </c>
       <c r="F1449" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1449" t="n">
         <v>0</v>
@@ -77580,21 +77564,29 @@
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
-        </is>
-      </c>
-      <c r="C1450" t="inlineStr"/>
-      <c r="D1450" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>7501033957376</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+        </is>
+      </c>
       <c r="E1450" t="n">
-        <v>8900</v>
+        <v>10900</v>
       </c>
       <c r="F1450" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1450" t="n">
         <v>0</v>
@@ -77630,21 +77622,21 @@
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Protector Solar Sunaid</t>
+          <t>PEGANTE GLUE X 10GR X UND</t>
         </is>
       </c>
       <c r="C1451" t="inlineStr"/>
       <c r="D1451" t="inlineStr"/>
       <c r="E1451" t="n">
-        <v>158000</v>
+        <v>2000</v>
       </c>
       <c r="F1451" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1451" t="n">
         <v>0</v>
@@ -77680,25 +77672,21 @@
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Prueba de embarazo esfero</t>
-        </is>
-      </c>
-      <c r="C1452" t="inlineStr">
-        <is>
-          <t>7709299854228</t>
-        </is>
-      </c>
+          <t>PEINETA COLA DE RATON METALICA</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr"/>
       <c r="D1452" t="inlineStr"/>
       <c r="E1452" t="n">
-        <v>16500</v>
+        <v>4700</v>
       </c>
       <c r="F1452" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1452" t="n">
         <v>0</v>
@@ -77734,25 +77722,21 @@
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Prueba de embarazo HCG cassette begut</t>
-        </is>
-      </c>
-      <c r="C1453" t="inlineStr">
-        <is>
-          <t>7707282990953</t>
-        </is>
-      </c>
+          <t>PERFILADORES DE CEJAS</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr"/>
       <c r="D1453" t="inlineStr"/>
       <c r="E1453" t="n">
-        <v>8900</v>
+        <v>3900</v>
       </c>
       <c r="F1453" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G1453" t="n">
         <v>0</v>
@@ -77788,18 +77772,18 @@
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>PUSHER METALICO</t>
+          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
         </is>
       </c>
       <c r="C1454" t="inlineStr"/>
       <c r="D1454" t="inlineStr"/>
       <c r="E1454" t="n">
-        <v>4300</v>
+        <v>27983.193277</v>
       </c>
       <c r="F1454" t="n">
         <v>1</v>
@@ -77830,7 +77814,7 @@
       </c>
       <c r="M1454" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1454" t="inlineStr"/>
@@ -77838,25 +77822,21 @@
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>Recolector de orina granandina</t>
-        </is>
-      </c>
-      <c r="C1455" t="inlineStr">
-        <is>
-          <t>7707233050590</t>
-        </is>
-      </c>
+          <t>POPETAS SURTIDAS X UND</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr"/>
       <c r="D1455" t="inlineStr"/>
       <c r="E1455" t="n">
-        <v>673</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1455" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G1455" t="n">
         <v>0</v>
@@ -77892,21 +77872,21 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
+          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
         </is>
       </c>
       <c r="C1456" t="inlineStr"/>
       <c r="D1456" t="inlineStr"/>
       <c r="E1456" t="n">
-        <v>3820</v>
+        <v>20500</v>
       </c>
       <c r="F1456" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1456" t="n">
         <v>0</v>
@@ -77942,18 +77922,26 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>RegistroManual - Registro manual</t>
-        </is>
-      </c>
-      <c r="C1457" t="inlineStr"/>
-      <c r="D1457" t="inlineStr"/>
+          <t>privatos miel limon la francol 120ml</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>7702207163948</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
+        </is>
+      </c>
       <c r="E1457" t="n">
-        <v>0</v>
+        <v>35900</v>
       </c>
       <c r="F1457" t="n">
         <v>0</v>
@@ -77984,7 +77972,7 @@
       </c>
       <c r="M1457" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1457" t="inlineStr"/>
@@ -77992,21 +77980,21 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>778</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>REMOVEDOR DE ESMALTE 60CC</t>
+          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
         </is>
       </c>
       <c r="C1458" t="inlineStr"/>
       <c r="D1458" t="inlineStr"/>
       <c r="E1458" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="F1458" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1458" t="n">
         <v>0</v>
@@ -78034,7 +78022,7 @@
       </c>
       <c r="M1458" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1458" t="inlineStr"/>
@@ -78042,22 +78030,18 @@
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
-        </is>
-      </c>
-      <c r="C1459" t="inlineStr">
-        <is>
-          <t>7591005981270</t>
-        </is>
-      </c>
+          <t>PROTECTOR NOSOTRAS LARGOS</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr"/>
       <c r="D1459" t="inlineStr"/>
       <c r="E1459" t="n">
-        <v>9500</v>
+        <v>3700</v>
       </c>
       <c r="F1459" t="n">
         <v>1</v>
@@ -78096,22 +78080,18 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
-        </is>
-      </c>
-      <c r="C1460" t="inlineStr">
-        <is>
-          <t>7503051868245</t>
-        </is>
-      </c>
+          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr"/>
       <c r="D1460" t="inlineStr"/>
       <c r="E1460" t="n">
-        <v>20900</v>
+        <v>8900</v>
       </c>
       <c r="F1460" t="n">
         <v>1</v>
@@ -78150,22 +78130,18 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1MG X 20 TABL MK</t>
-        </is>
-      </c>
-      <c r="C1461" t="inlineStr">
-        <is>
-          <t>7702057079642</t>
-        </is>
-      </c>
+          <t>Protector Solar Sunaid</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr"/>
       <c r="D1461" t="inlineStr"/>
       <c r="E1461" t="n">
-        <v>13000</v>
+        <v>158000</v>
       </c>
       <c r="F1461" t="n">
         <v>0</v>
@@ -78204,21 +78180,25 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Ryaltris Spray Nasal 240 dosis</t>
-        </is>
-      </c>
-      <c r="C1462" t="inlineStr"/>
+          <t>Prueba de embarazo esfero</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>7709299854228</t>
+        </is>
+      </c>
       <c r="D1462" t="inlineStr"/>
       <c r="E1462" t="n">
-        <v>216400</v>
+        <v>16500</v>
       </c>
       <c r="F1462" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1462" t="n">
         <v>0</v>
@@ -78254,25 +78234,25 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+          <t>Prueba de embarazo HCG cassette begut</t>
         </is>
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>7706849116676</t>
+          <t>7707282990953</t>
         </is>
       </c>
       <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="n">
-        <v>31500</v>
+        <v>8900</v>
       </c>
       <c r="F1463" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1463" t="n">
         <v>0</v>
@@ -78308,21 +78288,21 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>SCOBIT PURGANTE 60GR</t>
+          <t>PUSHER METALICO</t>
         </is>
       </c>
       <c r="C1464" t="inlineStr"/>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="n">
-        <v>15238.095238</v>
+        <v>4300</v>
       </c>
       <c r="F1464" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1464" t="n">
         <v>0</v>
@@ -78350,7 +78330,7 @@
       </c>
       <c r="M1464" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1464" t="inlineStr"/>
@@ -78358,21 +78338,25 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
-        </is>
-      </c>
-      <c r="C1465" t="inlineStr"/>
+          <t>Recolector de orina granandina</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>7707233050590</t>
+        </is>
+      </c>
       <c r="D1465" t="inlineStr"/>
       <c r="E1465" t="n">
-        <v>6554.621849</v>
+        <v>673</v>
       </c>
       <c r="F1465" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="G1465" t="n">
         <v>0</v>
@@ -78408,25 +78392,21 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>SHAMPOO PANTENE COLAGENO</t>
-        </is>
-      </c>
-      <c r="C1466" t="inlineStr">
-        <is>
-          <t>7500435191500</t>
-        </is>
-      </c>
+          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr"/>
       <c r="D1466" t="inlineStr"/>
       <c r="E1466" t="n">
-        <v>1429</v>
+        <v>3820</v>
       </c>
       <c r="F1466" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1466" t="n">
         <v>0</v>
@@ -78454,7 +78434,7 @@
       </c>
       <c r="M1466" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1466" t="inlineStr"/>
@@ -78462,18 +78442,18 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>SILDENAFIL 50MG TQ</t>
+          <t>RegistroManual - Registro manual</t>
         </is>
       </c>
       <c r="C1467" t="inlineStr"/>
       <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="F1467" t="n">
         <v>0</v>
@@ -78504,7 +78484,7 @@
       </c>
       <c r="M1467" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1467" t="inlineStr"/>
@@ -78512,25 +78492,21 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>SILIMARINA 167MG EPANAT</t>
-        </is>
-      </c>
-      <c r="C1468" t="inlineStr">
-        <is>
-          <t>7706849115921</t>
-        </is>
-      </c>
+          <t>REMOVEDOR DE ESMALTE 60CC</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr"/>
       <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="n">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="F1468" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G1468" t="n">
         <v>0</v>
@@ -78566,21 +78542,25 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>SMECTA 3GR NARANJA S/B</t>
-        </is>
-      </c>
-      <c r="C1469" t="inlineStr"/>
+          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>7591005981270</t>
+        </is>
+      </c>
       <c r="D1469" t="inlineStr"/>
       <c r="E1469" t="n">
-        <v>8900</v>
+        <v>9500</v>
       </c>
       <c r="F1469" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G1469" t="n">
         <v>0</v>
@@ -78616,21 +78596,25 @@
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>SONDA FOLEY 2 VIAS BAL #18</t>
-        </is>
-      </c>
-      <c r="C1470" t="inlineStr"/>
+          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>7503051868245</t>
+        </is>
+      </c>
       <c r="D1470" t="inlineStr"/>
       <c r="E1470" t="n">
-        <v>7500</v>
+        <v>20900</v>
       </c>
       <c r="F1470" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1470" t="n">
         <v>0</v>
@@ -78666,21 +78650,25 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>SONDA NELATON #6</t>
-        </is>
-      </c>
-      <c r="C1471" t="inlineStr"/>
+          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>7702057079642</t>
+        </is>
+      </c>
       <c r="D1471" t="inlineStr"/>
       <c r="E1471" t="n">
-        <v>2500</v>
+        <v>13000</v>
       </c>
       <c r="F1471" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1471" t="n">
         <v>0</v>
@@ -78716,21 +78704,21 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>SPRAY NASAL MOMETASONA 18ML</t>
+          <t>Ryaltris Spray Nasal 240 dosis</t>
         </is>
       </c>
       <c r="C1472" t="inlineStr"/>
       <c r="D1472" t="inlineStr"/>
       <c r="E1472" t="n">
-        <v>36900</v>
+        <v>216400</v>
       </c>
       <c r="F1472" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1472" t="n">
         <v>0</v>
@@ -78766,25 +78754,25 @@
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
+          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
         </is>
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>7703712035034</t>
+          <t>7706849116676</t>
         </is>
       </c>
       <c r="D1473" t="inlineStr"/>
       <c r="E1473" t="n">
-        <v>14800</v>
+        <v>31500</v>
       </c>
       <c r="F1473" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1473" t="n">
         <v>0</v>
@@ -78820,21 +78808,21 @@
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
+          <t>SCOBIT PURGANTE 60GR</t>
         </is>
       </c>
       <c r="C1474" t="inlineStr"/>
       <c r="D1474" t="inlineStr"/>
       <c r="E1474" t="n">
-        <v>3781.512605</v>
+        <v>15238.095238</v>
       </c>
       <c r="F1474" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1474" t="n">
         <v>0</v>
@@ -78862,7 +78850,7 @@
       </c>
       <c r="M1474" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1474" t="inlineStr"/>
@@ -78870,21 +78858,21 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
+          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
         </is>
       </c>
       <c r="C1475" t="inlineStr"/>
       <c r="D1475" t="inlineStr"/>
       <c r="E1475" t="n">
-        <v>5210.084034</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1475" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1475" t="n">
         <v>0</v>
@@ -78920,21 +78908,25 @@
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
-        </is>
-      </c>
-      <c r="C1476" t="inlineStr"/>
+          <t>SHAMPOO PANTENE COLAGENO</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>7500435191500</t>
+        </is>
+      </c>
       <c r="D1476" t="inlineStr"/>
       <c r="E1476" t="n">
-        <v>8319.327730999999</v>
+        <v>1429</v>
       </c>
       <c r="F1476" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1476" t="n">
         <v>0</v>
@@ -78970,21 +78962,21 @@
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>SULZINC SUSP X 80ML HUMAX</t>
+          <t>SILDENAFIL 50MG TQ</t>
         </is>
       </c>
       <c r="C1477" t="inlineStr"/>
       <c r="D1477" t="inlineStr"/>
       <c r="E1477" t="n">
-        <v>22400</v>
+        <v>5000</v>
       </c>
       <c r="F1477" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1477" t="n">
         <v>0</v>
@@ -79020,21 +79012,25 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>SUNDARK FPS 60 CON TAPA</t>
-        </is>
-      </c>
-      <c r="C1478" t="inlineStr"/>
+          <t>SILIMARINA 167MG EPANAT</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>7706849115921</t>
+        </is>
+      </c>
       <c r="D1478" t="inlineStr"/>
       <c r="E1478" t="n">
-        <v>3781.512605</v>
+        <v>2000</v>
       </c>
       <c r="F1478" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="G1478" t="n">
         <v>0</v>
@@ -79062,7 +79058,7 @@
       </c>
       <c r="M1478" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1478" t="inlineStr"/>
@@ -79070,21 +79066,21 @@
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>Synthroid 125 mcg</t>
+          <t>SMECTA 3GR NARANJA S/B</t>
         </is>
       </c>
       <c r="C1479" t="inlineStr"/>
       <c r="D1479" t="inlineStr"/>
       <c r="E1479" t="n">
-        <v>178000</v>
+        <v>8900</v>
       </c>
       <c r="F1479" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G1479" t="n">
         <v>0</v>
@@ -79120,25 +79116,21 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>Talco medicado Neofungina 40gm</t>
-        </is>
-      </c>
-      <c r="C1480" t="inlineStr">
-        <is>
-          <t>7706142707106</t>
-        </is>
-      </c>
+          <t>SONDA FOLEY 2 VIAS BAL #18</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr"/>
       <c r="D1480" t="inlineStr"/>
       <c r="E1480" t="n">
-        <v>14900</v>
+        <v>7500</v>
       </c>
       <c r="F1480" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1480" t="n">
         <v>0</v>
@@ -79174,21 +79166,21 @@
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
+          <t>SONDA NELATON #6</t>
         </is>
       </c>
       <c r="C1481" t="inlineStr"/>
       <c r="D1481" t="inlineStr"/>
       <c r="E1481" t="n">
-        <v>13300</v>
+        <v>2500</v>
       </c>
       <c r="F1481" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1481" t="n">
         <v>0</v>
@@ -79224,21 +79216,21 @@
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
+          <t>SPRAY NASAL MOMETASONA 18ML</t>
         </is>
       </c>
       <c r="C1482" t="inlineStr"/>
       <c r="D1482" t="inlineStr"/>
       <c r="E1482" t="n">
-        <v>4874</v>
+        <v>36900</v>
       </c>
       <c r="F1482" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G1482" t="n">
         <v>0</v>
@@ -79266,7 +79258,7 @@
       </c>
       <c r="M1482" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1482" t="inlineStr"/>
@@ -79274,21 +79266,25 @@
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
-        </is>
-      </c>
-      <c r="C1483" t="inlineStr"/>
+          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>7703712035034</t>
+        </is>
+      </c>
       <c r="D1483" t="inlineStr"/>
       <c r="E1483" t="n">
-        <v>28800</v>
+        <v>14800</v>
       </c>
       <c r="F1483" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1483" t="n">
         <v>0</v>
@@ -79324,21 +79320,21 @@
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
+          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
         </is>
       </c>
       <c r="C1484" t="inlineStr"/>
       <c r="D1484" t="inlineStr"/>
       <c r="E1484" t="n">
-        <v>11596.638655</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1484" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1484" t="n">
         <v>0</v>
@@ -79374,21 +79370,21 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>TIJERA DE DOBLAR METALICA</t>
+          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
         </is>
       </c>
       <c r="C1485" t="inlineStr"/>
       <c r="D1485" t="inlineStr"/>
       <c r="E1485" t="n">
-        <v>3500</v>
+        <v>5210.084034</v>
       </c>
       <c r="F1485" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1485" t="n">
         <v>0</v>
@@ -79416,7 +79412,7 @@
       </c>
       <c r="M1485" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1485" t="inlineStr"/>
@@ -79424,21 +79420,21 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
         </is>
       </c>
       <c r="C1486" t="inlineStr"/>
       <c r="D1486" t="inlineStr"/>
       <c r="E1486" t="n">
-        <v>3781.512605</v>
+        <v>8319.327730999999</v>
       </c>
       <c r="F1486" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1486" t="n">
         <v>0</v>
@@ -79474,18 +79470,18 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+          <t>SULZINC SUSP X 80ML HUMAX</t>
         </is>
       </c>
       <c r="C1487" t="inlineStr"/>
       <c r="D1487" t="inlineStr"/>
       <c r="E1487" t="n">
-        <v>29800</v>
+        <v>22400</v>
       </c>
       <c r="F1487" t="n">
         <v>1</v>
@@ -79524,25 +79520,21 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
-        </is>
-      </c>
-      <c r="C1488" t="inlineStr">
-        <is>
-          <t>7702026149567</t>
-        </is>
-      </c>
+          <t>SUNDARK FPS 60 CON TAPA</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr"/>
       <c r="D1488" t="inlineStr"/>
       <c r="E1488" t="n">
-        <v>13500</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1488" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G1488" t="n">
         <v>0</v>
@@ -79570,7 +79562,7 @@
       </c>
       <c r="M1488" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1488" t="inlineStr"/>
@@ -79578,25 +79570,21 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>Toallas húmedas winny 24unidades</t>
-        </is>
-      </c>
-      <c r="C1489" t="inlineStr">
-        <is>
-          <t>7701021143655</t>
-        </is>
-      </c>
+          <t>Synthroid 125 mcg</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr"/>
       <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="n">
-        <v>4033.613445</v>
+        <v>178000</v>
       </c>
       <c r="F1489" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G1489" t="n">
         <v>0</v>
@@ -79624,7 +79612,7 @@
       </c>
       <c r="M1489" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1489" t="inlineStr"/>
@@ -79632,25 +79620,25 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>Toallas maternas maternity</t>
+          <t>Talco medicado Neofungina 40gm</t>
         </is>
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>7703252489526</t>
+          <t>7706142707106</t>
         </is>
       </c>
       <c r="D1490" t="inlineStr"/>
       <c r="E1490" t="n">
-        <v>16900</v>
+        <v>14900</v>
       </c>
       <c r="F1490" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1490" t="n">
         <v>0</v>
@@ -79686,25 +79674,21 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Toallas Nosotras Rapigel x Und</t>
-        </is>
-      </c>
-      <c r="C1491" t="inlineStr">
-        <is>
-          <t>7702027416859</t>
-        </is>
-      </c>
+          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr"/>
       <c r="D1491" t="inlineStr"/>
       <c r="E1491" t="n">
-        <v>756.302521</v>
+        <v>13300</v>
       </c>
       <c r="F1491" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G1491" t="n">
         <v>0</v>
@@ -79732,7 +79716,7 @@
       </c>
       <c r="M1491" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1491" t="inlineStr"/>
@@ -79740,21 +79724,21 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>TRAMADOL 50MG CAPSULA MP</t>
+          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
         </is>
       </c>
       <c r="C1492" t="inlineStr"/>
       <c r="D1492" t="inlineStr"/>
       <c r="E1492" t="n">
-        <v>1500</v>
+        <v>4874</v>
       </c>
       <c r="F1492" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G1492" t="n">
         <v>0</v>
@@ -79782,7 +79766,7 @@
       </c>
       <c r="M1492" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1492" t="inlineStr"/>
@@ -79790,25 +79774,21 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>Tramadol clorhidrato 100mg laquifar</t>
-        </is>
-      </c>
-      <c r="C1493" t="inlineStr">
-        <is>
-          <t>7707019426977</t>
-        </is>
-      </c>
+          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr"/>
       <c r="D1493" t="inlineStr"/>
       <c r="E1493" t="n">
-        <v>1600</v>
+        <v>28800</v>
       </c>
       <c r="F1493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1493" t="n">
         <v>0</v>
@@ -79844,21 +79824,21 @@
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>TRIGENTAX CREMA TBO X 20GR</t>
+          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
         </is>
       </c>
       <c r="C1494" t="inlineStr"/>
       <c r="D1494" t="inlineStr"/>
       <c r="E1494" t="n">
-        <v>33500</v>
+        <v>11596.638655</v>
       </c>
       <c r="F1494" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1494" t="n">
         <v>0</v>
@@ -79886,7 +79866,7 @@
       </c>
       <c r="M1494" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1494" t="inlineStr"/>
@@ -79894,21 +79874,21 @@
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
+          <t>TIJERA DE DOBLAR METALICA</t>
         </is>
       </c>
       <c r="C1495" t="inlineStr"/>
       <c r="D1495" t="inlineStr"/>
       <c r="E1495" t="n">
-        <v>9000</v>
+        <v>3500</v>
       </c>
       <c r="F1495" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1495" t="n">
         <v>0</v>
@@ -79944,21 +79924,21 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
+          <t>TINTURA DE RUIBARDO FCO 30ML</t>
         </is>
       </c>
       <c r="C1496" t="inlineStr"/>
       <c r="D1496" t="inlineStr"/>
       <c r="E1496" t="n">
-        <v>10500</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1496" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1496" t="n">
         <v>0</v>
@@ -79986,7 +79966,7 @@
       </c>
       <c r="M1496" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1496" t="inlineStr"/>
@@ -79994,21 +79974,21 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
+          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr"/>
       <c r="D1497" t="inlineStr"/>
       <c r="E1497" t="n">
-        <v>10500</v>
+        <v>29800</v>
       </c>
       <c r="F1497" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G1497" t="n">
         <v>0</v>
@@ -80044,21 +80024,25 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
-        </is>
-      </c>
-      <c r="C1498" t="inlineStr"/>
+          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>7702026149567</t>
+        </is>
+      </c>
       <c r="D1498" t="inlineStr"/>
       <c r="E1498" t="n">
-        <v>18800</v>
+        <v>13500</v>
       </c>
       <c r="F1498" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1498" t="n">
         <v>0</v>
@@ -80094,21 +80078,25 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
-        </is>
-      </c>
-      <c r="C1499" t="inlineStr"/>
+          <t>Toallas húmedas winny 24unidades</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>7701021143655</t>
+        </is>
+      </c>
       <c r="D1499" t="inlineStr"/>
       <c r="E1499" t="n">
-        <v>13800</v>
+        <v>4033.613445</v>
       </c>
       <c r="F1499" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G1499" t="n">
         <v>0</v>
@@ -80136,7 +80124,7 @@
       </c>
       <c r="M1499" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1499" t="inlineStr"/>
@@ -80144,21 +80132,25 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
-        </is>
-      </c>
-      <c r="C1500" t="inlineStr"/>
+          <t>Toallas maternas maternity</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>7703252489526</t>
+        </is>
+      </c>
       <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="n">
-        <v>7900</v>
+        <v>16900</v>
       </c>
       <c r="F1500" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1500" t="n">
         <v>0</v>
@@ -80194,21 +80186,25 @@
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>VASELINA FC X 200GR YOMA</t>
-        </is>
-      </c>
-      <c r="C1501" t="inlineStr"/>
+          <t>Toallas Nosotras Rapigel x Und</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>7702027416859</t>
+        </is>
+      </c>
       <c r="D1501" t="inlineStr"/>
       <c r="E1501" t="n">
-        <v>12521.008403</v>
+        <v>756.302521</v>
       </c>
       <c r="F1501" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G1501" t="n">
         <v>0</v>
@@ -80244,25 +80240,21 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
-        </is>
-      </c>
-      <c r="C1502" t="inlineStr">
-        <is>
-          <t>7708480649803</t>
-        </is>
-      </c>
+          <t>TRAMADOL 50MG CAPSULA MP</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr"/>
       <c r="D1502" t="inlineStr"/>
       <c r="E1502" t="n">
-        <v>28000</v>
+        <v>1500</v>
       </c>
       <c r="F1502" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G1502" t="n">
         <v>0</v>
@@ -80298,25 +80290,25 @@
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>Venda Elastica 6x5 y piel</t>
-        </is>
-      </c>
-      <c r="C1503" t="inlineStr"/>
-      <c r="D1503" t="inlineStr">
-        <is>
-          <t>SUBIO A 6200 ANTES 5700</t>
-        </is>
-      </c>
+          <t>Tramadol clorhidrato 100mg laquifar</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>7707019426977</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr"/>
       <c r="E1503" t="n">
-        <v>6200</v>
+        <v>1600</v>
       </c>
       <c r="F1503" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1503" t="n">
         <v>0</v>
@@ -80352,21 +80344,21 @@
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
+          <t>TRIGENTAX CREMA TBO X 20GR</t>
         </is>
       </c>
       <c r="C1504" t="inlineStr"/>
       <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="n">
-        <v>5500</v>
+        <v>33500</v>
       </c>
       <c r="F1504" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1504" t="n">
         <v>0</v>
@@ -80402,21 +80394,21 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>Venta simple</t>
+          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
         </is>
       </c>
       <c r="C1505" t="inlineStr"/>
       <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="F1505" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1505" t="n">
         <v>0</v>
@@ -80434,7 +80426,7 @@
       </c>
       <c r="K1505" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="L1505" t="inlineStr">
@@ -80442,27 +80434,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1505" t="inlineStr"/>
+      <c r="M1505" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1505" t="inlineStr"/>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
+          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
         </is>
       </c>
       <c r="C1506" t="inlineStr"/>
       <c r="D1506" t="inlineStr"/>
       <c r="E1506" t="n">
-        <v>1000</v>
+        <v>10500</v>
       </c>
       <c r="F1506" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1506" t="n">
         <v>0</v>
@@ -80498,25 +80494,21 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
-        </is>
-      </c>
-      <c r="C1507" t="inlineStr">
-        <is>
-          <t>793969226467</t>
-        </is>
-      </c>
+          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr"/>
       <c r="D1507" t="inlineStr"/>
       <c r="E1507" t="n">
-        <v>17000</v>
+        <v>10500</v>
       </c>
       <c r="F1507" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G1507" t="n">
         <v>0</v>
@@ -80539,7 +80531,7 @@
       </c>
       <c r="L1507" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="M1507" t="inlineStr">
@@ -80552,21 +80544,21 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>VINO CEREBRAL JARABE X 1100ML</t>
+          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr"/>
       <c r="D1508" t="inlineStr"/>
       <c r="E1508" t="n">
-        <v>48900</v>
+        <v>18800</v>
       </c>
       <c r="F1508" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1508" t="n">
         <v>0</v>
@@ -80602,21 +80594,21 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
+          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
         </is>
       </c>
       <c r="C1509" t="inlineStr"/>
       <c r="D1509" t="inlineStr"/>
       <c r="E1509" t="n">
-        <v>5400</v>
+        <v>13800</v>
       </c>
       <c r="F1509" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G1509" t="n">
         <v>0</v>
@@ -80652,21 +80644,21 @@
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
+          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr"/>
       <c r="D1510" t="inlineStr"/>
       <c r="E1510" t="n">
-        <v>5500</v>
+        <v>7900</v>
       </c>
       <c r="F1510" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G1510" t="n">
         <v>0</v>
@@ -80702,18 +80694,18 @@
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>WINNY PAÑAL ETP 6 X 30</t>
+          <t>VASELINA FC X 200GR YOMA</t>
         </is>
       </c>
       <c r="C1511" t="inlineStr"/>
       <c r="D1511" t="inlineStr"/>
       <c r="E1511" t="n">
-        <v>57000</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1511" t="n">
         <v>0</v>
@@ -80744,7 +80736,7 @@
       </c>
       <c r="M1511" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1511" t="inlineStr"/>
@@ -80752,52 +80744,610 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>YODO BLANCO FC X30ML</t>
+          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
         </is>
       </c>
       <c r="C1512" t="inlineStr"/>
       <c r="D1512" t="inlineStr"/>
       <c r="E1512" t="n">
+        <v>420.168067</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1512" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1512" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1512" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1512" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="N1512" t="inlineStr"/>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>1253</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>7708480649803</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr"/>
+      <c r="E1513" t="n">
+        <v>28000</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1513" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1513" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1513" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1513" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1513" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1513" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1513" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1513" t="inlineStr"/>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>1136</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>Venda Elastica 6x5 y piel</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr"/>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>SUBIO A 6200 ANTES 5700</t>
+        </is>
+      </c>
+      <c r="E1514" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F1514" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1514" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1514" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1514" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1514" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1514" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1514" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1514" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1514" t="inlineStr"/>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>1247</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr"/>
+      <c r="D1515" t="inlineStr"/>
+      <c r="E1515" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F1515" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1515" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1515" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1515" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1515" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1515" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1515" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1515" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1515" t="inlineStr"/>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>1277</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>Venta simple</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr"/>
+      <c r="D1516" t="inlineStr"/>
+      <c r="E1516" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1516" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1516" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1516" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1516" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1516" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1516" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="L1516" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1516" t="inlineStr"/>
+      <c r="N1516" t="inlineStr"/>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr"/>
+      <c r="D1517" t="inlineStr"/>
+      <c r="E1517" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1517" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1517" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1517" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1517" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1517" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1517" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1517" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1517" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1517" t="inlineStr"/>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>793969226467</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr"/>
+      <c r="E1518" t="n">
+        <v>17000</v>
+      </c>
+      <c r="F1518" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1518" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1518" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1518" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1518" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1518" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1518" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
+      </c>
+      <c r="M1518" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1518" t="inlineStr"/>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>1478</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>VINO CEREBRAL JARABE X 1100ML</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr"/>
+      <c r="D1519" t="inlineStr"/>
+      <c r="E1519" t="n">
+        <v>48900</v>
+      </c>
+      <c r="F1519" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1519" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1519" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1519" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1519" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1519" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1519" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1519" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1519" t="inlineStr"/>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr"/>
+      <c r="D1520" t="inlineStr"/>
+      <c r="E1520" t="n">
+        <v>5400</v>
+      </c>
+      <c r="F1520" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1520" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1520" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1520" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1520" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1520" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1520" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1520" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1520" t="inlineStr"/>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr"/>
+      <c r="D1521" t="inlineStr"/>
+      <c r="E1521" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F1521" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1521" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1521" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1521" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1521" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1521" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1521" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1521" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1521" t="inlineStr"/>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>WINNY PAÑAL ETP 6 X 30</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr"/>
+      <c r="D1522" t="inlineStr"/>
+      <c r="E1522" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F1522" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1522" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1522" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1522" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1522" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1522" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1522" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1522" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1522" t="inlineStr"/>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>YODO BLANCO FC X30ML</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr"/>
+      <c r="D1523" t="inlineStr"/>
+      <c r="E1523" t="n">
         <v>6000</v>
       </c>
-      <c r="F1512" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1512" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1512" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1512" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1512" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="K1512" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="L1512" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="M1512" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="N1512" t="inlineStr"/>
+      <c r="F1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1523" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1523" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1523" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1523" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1523" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -1545,7 +1545,7 @@
         <v>2941.176471</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>5800</v>
       </c>
       <c r="F66" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -11061,7 +11061,7 @@
         <v>7815</v>
       </c>
       <c r="F200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -11165,7 +11165,7 @@
         <v>23000</v>
       </c>
       <c r="F202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -14239,7 +14239,7 @@
         <v>840.336134</v>
       </c>
       <c r="F259" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G259" t="n">
         <v>0</v>
@@ -14771,7 +14771,7 @@
         <v>6000</v>
       </c>
       <c r="F269" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -17187,7 +17187,7 @@
         <v>6300</v>
       </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G313" t="n">
         <v>0</v>
@@ -18093,7 +18093,7 @@
         <v>6723</v>
       </c>
       <c r="F330" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G330" t="n">
         <v>0</v>
@@ -18243,7 +18243,7 @@
         <v>3361.344538</v>
       </c>
       <c r="F333" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G333" t="n">
         <v>0</v>
@@ -20731,7 +20731,7 @@
         <v>9000</v>
       </c>
       <c r="F381" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G381" t="n">
         <v>0</v>
@@ -22741,7 +22741,7 @@
         <v>5000</v>
       </c>
       <c r="F418" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G418" t="n">
         <v>0</v>
@@ -23365,7 +23365,7 @@
         <v>2000</v>
       </c>
       <c r="F430" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G430" t="n">
         <v>0</v>
@@ -24815,7 +24815,7 @@
         <v>9200</v>
       </c>
       <c r="F457" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G457" t="n">
         <v>0</v>
@@ -24873,7 +24873,7 @@
         <v>9200</v>
       </c>
       <c r="F458" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G458" t="n">
         <v>0</v>
@@ -24981,7 +24981,7 @@
         <v>9200</v>
       </c>
       <c r="F460" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G460" t="n">
         <v>0</v>
@@ -28027,7 +28027,7 @@
         <v>34500</v>
       </c>
       <c r="F517" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G517" t="n">
         <v>0</v>
@@ -32339,7 +32339,7 @@
         <v>800</v>
       </c>
       <c r="F597" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G597" t="n">
         <v>0</v>
@@ -32613,7 +32613,7 @@
         <v>2200</v>
       </c>
       <c r="F602" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G602" t="n">
         <v>0</v>
@@ -32941,7 +32941,7 @@
         <v>3700</v>
       </c>
       <c r="F608" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G608" t="n">
         <v>0</v>
@@ -34533,7 +34533,7 @@
         <v>3700</v>
       </c>
       <c r="F638" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G638" t="n">
         <v>0</v>
@@ -37721,7 +37721,7 @@
         <v>2200</v>
       </c>
       <c r="F698" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G698" t="n">
         <v>0</v>
@@ -40905,7 +40905,7 @@
         <v>4369.75</v>
       </c>
       <c r="F758" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G758" t="n">
         <v>0</v>
@@ -43628,14 +43628,14 @@
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>SE SUBIO PRECIO</t>
+          <t>SE SUBIO PRECIO A 9700 ANTES 8700</t>
         </is>
       </c>
       <c r="E809" t="n">
-        <v>8900</v>
+        <v>9700</v>
       </c>
       <c r="F809" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G809" t="n">
         <v>0</v>
@@ -43689,7 +43689,7 @@
         <v>8800</v>
       </c>
       <c r="F810" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G810" t="n">
         <v>0</v>
@@ -45741,7 +45741,7 @@
         <v>4957.983193</v>
       </c>
       <c r="F848" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G848" t="n">
         <v>0</v>
@@ -51369,7 +51369,7 @@
         <v>9200</v>
       </c>
       <c r="F954" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G954" t="n">
         <v>0</v>
@@ -51926,7 +51926,7 @@
         <v>9200</v>
       </c>
       <c r="F964" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G964" t="n">
         <v>0</v>
@@ -57248,7 +57248,7 @@
         <v>12016.806723</v>
       </c>
       <c r="F1063" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1063" t="n">
         <v>0</v>
@@ -58736,7 +58736,7 @@
         <v>2900</v>
       </c>
       <c r="F1091" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1091" t="n">
         <v>0</v>
@@ -60348,7 +60348,7 @@
         <v>6300</v>
       </c>
       <c r="F1121" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G1121" t="n">
         <v>0</v>
@@ -62874,7 +62874,7 @@
         <v>4800</v>
       </c>
       <c r="F1168" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1168" t="n">
         <v>0</v>
@@ -65814,7 +65814,7 @@
         <v>3400</v>
       </c>
       <c r="F1222" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1222" t="n">
         <v>0</v>
@@ -66858,7 +66858,7 @@
         <v>2200</v>
       </c>
       <c r="F1242" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G1242" t="n">
         <v>0</v>
@@ -66908,7 +66908,7 @@
         <v>2500</v>
       </c>
       <c r="F1243" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G1243" t="n">
         <v>0</v>
@@ -69038,7 +69038,7 @@
         <v>2016.806723</v>
       </c>
       <c r="F1284" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G1284" t="n">
         <v>0</v>
@@ -69088,7 +69088,7 @@
         <v>1680.672269</v>
       </c>
       <c r="F1285" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G1285" t="n">
         <v>0</v>
@@ -71752,7 +71752,7 @@
         <v>3500</v>
       </c>
       <c r="F1337" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1337" t="n">
         <v>0</v>
@@ -72314,7 +72314,7 @@
         <v>1932.773109</v>
       </c>
       <c r="F1348" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1348" t="n">
         <v>0</v>
@@ -72364,7 +72364,7 @@
         <v>2941.176471</v>
       </c>
       <c r="F1349" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G1349" t="n">
         <v>0</v>
@@ -72980,7 +72980,7 @@
         <v>2100.840336</v>
       </c>
       <c r="F1361" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G1361" t="n">
         <v>0</v>
@@ -73030,7 +73030,7 @@
         <v>336.134454</v>
       </c>
       <c r="F1362" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G1362" t="n">
         <v>0</v>
@@ -74008,7 +74008,7 @@
         <v>4201.680672</v>
       </c>
       <c r="F1381" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1381" t="n">
         <v>0</v>
@@ -75556,7 +75556,7 @@
         <v>1000</v>
       </c>
       <c r="F1411" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1411" t="n">
         <v>0</v>
@@ -75922,7 +75922,7 @@
         <v>5500</v>
       </c>
       <c r="F1418" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G1418" t="n">
         <v>0</v>
@@ -76958,7 +76958,7 @@
         <v>14285.714286</v>
       </c>
       <c r="F1438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1438" t="n">
         <v>0</v>
@@ -77008,7 +77008,7 @@
         <v>28991.596639</v>
       </c>
       <c r="F1439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1439" t="n">
         <v>0</v>
@@ -77836,7 +77836,7 @@
         <v>2521.008403</v>
       </c>
       <c r="F1455" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1455" t="n">
         <v>0</v>
@@ -78356,7 +78356,7 @@
         <v>673</v>
       </c>
       <c r="F1465" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G1465" t="n">
         <v>0</v>
@@ -80204,7 +80204,7 @@
         <v>756.302521</v>
       </c>
       <c r="F1501" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="G1501" t="n">
         <v>0</v>
@@ -80458,7 +80458,7 @@
         <v>10500</v>
       </c>
       <c r="F1506" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1506" t="n">
         <v>0</v>
@@ -80758,7 +80758,7 @@
         <v>420.168067</v>
       </c>
       <c r="F1512" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1512" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -26802,7 +26802,7 @@
       </c>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="n">
-        <v>400</v>
+        <v>336.134454</v>
       </c>
       <c r="F494" t="n">
         <v>89</v>
@@ -26833,7 +26833,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N494" t="inlineStr"/>
@@ -29968,7 +29968,7 @@
         </is>
       </c>
       <c r="E553" t="n">
-        <v>4873.94958</v>
+        <v>4500</v>
       </c>
       <c r="F553" t="n">
         <v>3</v>
@@ -29999,7 +29999,7 @@
       </c>
       <c r="M553" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N553" t="inlineStr"/>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -14509,7 +14509,7 @@
         <v>200</v>
       </c>
       <c r="F264" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -23577,7 +23577,7 @@
         <v>3300</v>
       </c>
       <c r="F434" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G434" t="n">
         <v>0</v>
@@ -26805,7 +26805,7 @@
         <v>336.134454</v>
       </c>
       <c r="F494" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G494" t="n">
         <v>0</v>
@@ -29971,7 +29971,7 @@
         <v>4500</v>
       </c>
       <c r="F553" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G553" t="n">
         <v>0</v>
@@ -31845,7 +31845,7 @@
         <v>3000</v>
       </c>
       <c r="F588" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G588" t="n">
         <v>0</v>
@@ -38727,7 +38727,7 @@
         <v>3781.512605</v>
       </c>
       <c r="F717" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G717" t="n">
         <v>0</v>
@@ -42377,7 +42377,7 @@
         <v>2300</v>
       </c>
       <c r="F786" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G786" t="n">
         <v>0</v>
@@ -59268,7 +59268,7 @@
         <v>19500</v>
       </c>
       <c r="F1101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1101" t="n">
         <v>0</v>
@@ -64182,7 +64182,7 @@
         <v>4800</v>
       </c>
       <c r="F1192" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1192" t="n">
         <v>0</v>
@@ -64950,7 +64950,7 @@
         <v>3100</v>
       </c>
       <c r="F1206" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1206" t="n">
         <v>0</v>
@@ -66908,7 +66908,7 @@
         <v>2500</v>
       </c>
       <c r="F1243" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1243" t="n">
         <v>0</v>
@@ -75872,7 +75872,7 @@
         <v>22700</v>
       </c>
       <c r="F1417" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1417" t="n">
         <v>0</v>
@@ -79988,7 +79988,7 @@
         <v>29800</v>
       </c>
       <c r="F1497" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1497" t="n">
         <v>0</v>
@@ -81166,7 +81166,7 @@
         <v>5400</v>
       </c>
       <c r="F1520" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1520" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1523"/>
+  <dimension ref="A1:N1524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8733,7 +8733,7 @@
         <v>2900</v>
       </c>
       <c r="F156" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -11115,7 +11115,7 @@
         <v>14900</v>
       </c>
       <c r="F201" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -16249,7 +16249,7 @@
         <v>13700</v>
       </c>
       <c r="F296" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G296" t="n">
         <v>0</v>
@@ -17187,7 +17187,7 @@
         <v>6300</v>
       </c>
       <c r="F313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G313" t="n">
         <v>0</v>
@@ -19875,7 +19875,7 @@
         <v>31500</v>
       </c>
       <c r="F365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G365" t="n">
         <v>0</v>
@@ -28027,7 +28027,7 @@
         <v>34500</v>
       </c>
       <c r="F517" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G517" t="n">
         <v>0</v>
@@ -31571,7 +31571,7 @@
         <v>2800</v>
       </c>
       <c r="F583" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G583" t="n">
         <v>0</v>
@@ -31737,7 +31737,7 @@
         <v>2500</v>
       </c>
       <c r="F586" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G586" t="n">
         <v>0</v>
@@ -32115,7 +32115,7 @@
         <v>2200</v>
       </c>
       <c r="F593" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G593" t="n">
         <v>0</v>
@@ -43191,7 +43191,7 @@
         <v>17000</v>
       </c>
       <c r="F801" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G801" t="n">
         <v>0</v>
@@ -43635,7 +43635,7 @@
         <v>9700</v>
       </c>
       <c r="F809" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G809" t="n">
         <v>0</v>
@@ -43689,7 +43689,7 @@
         <v>8800</v>
       </c>
       <c r="F810" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G810" t="n">
         <v>0</v>
@@ -50275,7 +50275,7 @@
         <v>2300</v>
       </c>
       <c r="F933" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G933" t="n">
         <v>0</v>
@@ -55882,7 +55882,7 @@
         <v>20588.235294</v>
       </c>
       <c r="F1038" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G1038" t="n">
         <v>0</v>
@@ -60950,7 +60950,7 @@
         <v>6134.453782</v>
       </c>
       <c r="F1132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1132" t="n">
         <v>0</v>
@@ -64838,7 +64838,7 @@
         <v>9300</v>
       </c>
       <c r="F1204" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1204" t="n">
         <v>0</v>
@@ -67826,25 +67826,21 @@
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>BETAMETASONA 0.1% CREMA X 20GR A.G</t>
-        </is>
-      </c>
-      <c r="C1261" t="inlineStr">
-        <is>
-          <t>7706569001672</t>
-        </is>
-      </c>
+          <t>BETAMETASONA 0.05% LG PHARMA X 40 GR</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr"/>
       <c r="D1261" t="inlineStr"/>
       <c r="E1261" t="n">
-        <v>17600</v>
+        <v>14900</v>
       </c>
       <c r="F1261" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1261" t="n">
         <v>0</v>
@@ -67880,29 +67876,25 @@
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>Betametasona/Betametasona acetato 3/3mg AMP</t>
+          <t>BETAMETASONA 0.1% CREMA X 20GR A.G</t>
         </is>
       </c>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>´7706569020321</t>
-        </is>
-      </c>
-      <c r="D1262" t="inlineStr">
-        <is>
-          <t>SE QUITO CODIGO DE BARRAS HECTOR</t>
-        </is>
-      </c>
+          <t>7706569001672</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr"/>
       <c r="E1262" t="n">
-        <v>55000</v>
+        <v>17600</v>
       </c>
       <c r="F1262" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1262" t="n">
         <v>0</v>
@@ -67938,25 +67930,29 @@
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>Biocicar Crema Topica x 60 gr</t>
+          <t>Betametasona/Betametasona acetato 3/3mg AMP</t>
         </is>
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>7703234100968</t>
-        </is>
-      </c>
-      <c r="D1263" t="inlineStr"/>
+          <t>´7706569020321</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>SE QUITO CODIGO DE BARRAS HECTOR</t>
+        </is>
+      </c>
       <c r="E1263" t="n">
-        <v>42000</v>
+        <v>55000</v>
       </c>
       <c r="F1263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1263" t="n">
         <v>0</v>
@@ -67992,22 +67988,22 @@
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>BISACUDILO 5MG X 10 TABL. HUMAX</t>
+          <t>Biocicar Crema Topica x 60 gr</t>
         </is>
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>77072888220247</t>
+          <t>7703234100968</t>
         </is>
       </c>
       <c r="D1264" t="inlineStr"/>
       <c r="E1264" t="n">
-        <v>4000</v>
+        <v>42000</v>
       </c>
       <c r="F1264" t="n">
         <v>0</v>
@@ -68046,21 +68042,25 @@
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>BISACUDILO 5MG X SOBRE DE RECIPE</t>
-        </is>
-      </c>
-      <c r="C1265" t="inlineStr"/>
+          <t>BISACUDILO 5MG X 10 TABL. HUMAX</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>77072888220247</t>
+        </is>
+      </c>
       <c r="D1265" t="inlineStr"/>
       <c r="E1265" t="n">
-        <v>6900</v>
+        <v>4000</v>
       </c>
       <c r="F1265" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1265" t="n">
         <v>0</v>
@@ -68096,25 +68096,21 @@
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>BISGLICINATO DE MAGNESIO X 60 CAPS</t>
-        </is>
-      </c>
-      <c r="C1266" t="inlineStr">
-        <is>
-          <t>610985519338</t>
-        </is>
-      </c>
+          <t>BISACUDILO 5MG X SOBRE DE RECIPE</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr"/>
       <c r="D1266" t="inlineStr"/>
       <c r="E1266" t="n">
-        <v>48000</v>
+        <v>6900</v>
       </c>
       <c r="F1266" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1266" t="n">
         <v>0</v>
@@ -68150,21 +68146,25 @@
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>BOLSAS INYECTOLOGIA</t>
-        </is>
-      </c>
-      <c r="C1267" t="inlineStr"/>
+          <t>BISGLICINATO DE MAGNESIO X 60 CAPS</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>610985519338</t>
+        </is>
+      </c>
       <c r="D1267" t="inlineStr"/>
       <c r="E1267" t="n">
-        <v>840.336134</v>
+        <v>48000</v>
       </c>
       <c r="F1267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1267" t="n">
         <v>0</v>
@@ -68192,7 +68192,7 @@
       </c>
       <c r="M1267" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1267" t="inlineStr"/>
@@ -68200,29 +68200,21 @@
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>BROMHEXINA MG/ML MUCOTROP NIÑO</t>
-        </is>
-      </c>
-      <c r="C1268" t="inlineStr">
-        <is>
-          <t>7703038067450</t>
-        </is>
-      </c>
-      <c r="D1268" t="inlineStr">
-        <is>
-          <t>SE SUBE PRECIO A 17000 ANTES ESTABA EN 15000/MODIF LEYDI</t>
-        </is>
-      </c>
+          <t>BOLSAS INYECTOLOGIA</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr"/>
+      <c r="D1268" t="inlineStr"/>
       <c r="E1268" t="n">
-        <v>17000</v>
+        <v>840.336134</v>
       </c>
       <c r="F1268" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1268" t="n">
         <v>0</v>
@@ -68250,7 +68242,7 @@
       </c>
       <c r="M1268" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1268" t="inlineStr"/>
@@ -68258,21 +68250,29 @@
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>BRONQUISAN JALEA ADULTO JARABE 240ML</t>
-        </is>
-      </c>
-      <c r="C1269" t="inlineStr"/>
-      <c r="D1269" t="inlineStr"/>
+          <t>BROMHEXINA MG/ML MUCOTROP NIÑO</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>7703038067450</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>SE SUBE PRECIO A 17000 ANTES ESTABA EN 15000/MODIF LEYDI</t>
+        </is>
+      </c>
       <c r="E1269" t="n">
-        <v>19900</v>
+        <v>17000</v>
       </c>
       <c r="F1269" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1269" t="n">
         <v>0</v>
@@ -68308,18 +68308,18 @@
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>Bronsinex JBE x 120ML</t>
+          <t>BRONQUISAN JALEA ADULTO JARABE 240ML</t>
         </is>
       </c>
       <c r="C1270" t="inlineStr"/>
       <c r="D1270" t="inlineStr"/>
       <c r="E1270" t="n">
-        <v>17000</v>
+        <v>19900</v>
       </c>
       <c r="F1270" t="n">
         <v>1</v>
@@ -68358,25 +68358,21 @@
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>CAJA DE BEDOYECTA X 3 AMPOLLA</t>
-        </is>
-      </c>
-      <c r="C1271" t="inlineStr">
-        <is>
-          <t>7707288826935</t>
-        </is>
-      </c>
+          <t>Bronsinex JBE x 120ML</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr"/>
       <c r="D1271" t="inlineStr"/>
       <c r="E1271" t="n">
-        <v>58000</v>
+        <v>17000</v>
       </c>
       <c r="F1271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1271" t="n">
         <v>0</v>
@@ -68412,21 +68408,25 @@
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>CALADERM CLEAR PLUS 120GR</t>
-        </is>
-      </c>
-      <c r="C1272" t="inlineStr"/>
+          <t>CAJA DE BEDOYECTA X 3 AMPOLLA</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>7707288826935</t>
+        </is>
+      </c>
       <c r="D1272" t="inlineStr"/>
       <c r="E1272" t="n">
-        <v>22268.907563</v>
+        <v>58000</v>
       </c>
       <c r="F1272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1272" t="n">
         <v>0</v>
@@ -68454,7 +68454,7 @@
       </c>
       <c r="M1272" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1272" t="inlineStr"/>
@@ -68462,25 +68462,21 @@
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>CAPILAR POLIMERO ROSADO 20ML</t>
-        </is>
-      </c>
-      <c r="C1273" t="inlineStr">
-        <is>
-          <t>7701168181244</t>
-        </is>
-      </c>
+          <t>CALADERM CLEAR PLUS 120GR</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr"/>
       <c r="D1273" t="inlineStr"/>
       <c r="E1273" t="n">
-        <v>4300</v>
+        <v>22268.907563</v>
       </c>
       <c r="F1273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1273" t="n">
         <v>0</v>
@@ -68508,7 +68504,7 @@
       </c>
       <c r="M1273" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1273" t="inlineStr"/>
@@ -68516,25 +68512,25 @@
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>CARVEDIDOL 6,25MG MEPHIS</t>
+          <t>CAPILAR POLIMERO ROSADO 20ML</t>
         </is>
       </c>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>7704412376328</t>
+          <t>7701168181244</t>
         </is>
       </c>
       <c r="D1274" t="inlineStr"/>
       <c r="E1274" t="n">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="F1274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1274" t="n">
         <v>0</v>
@@ -68570,21 +68566,25 @@
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>CARVEDILOL 6.25MG SOBRE X 10 TABLE DE L.S</t>
-        </is>
-      </c>
-      <c r="C1275" t="inlineStr"/>
+          <t>CARVEDIDOL 6,25MG MEPHIS</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>7704412376328</t>
+        </is>
+      </c>
       <c r="D1275" t="inlineStr"/>
       <c r="E1275" t="n">
-        <v>5900</v>
+        <v>4400</v>
       </c>
       <c r="F1275" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1275" t="n">
         <v>0</v>
@@ -68620,21 +68620,21 @@
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>CAUCHO PARA EL CABELLO AKARELLA YUMBO</t>
+          <t>CARVEDILOL 6.25MG SOBRE X 10 TABLE DE L.S</t>
         </is>
       </c>
       <c r="C1276" t="inlineStr"/>
       <c r="D1276" t="inlineStr"/>
       <c r="E1276" t="n">
-        <v>2800</v>
+        <v>5900</v>
       </c>
       <c r="F1276" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1276" t="n">
         <v>0</v>
@@ -68670,21 +68670,21 @@
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>CAUCHOS AKARELA PASTEL ROSADO</t>
+          <t>CAUCHO PARA EL CABELLO AKARELLA YUMBO</t>
         </is>
       </c>
       <c r="C1277" t="inlineStr"/>
       <c r="D1277" t="inlineStr"/>
       <c r="E1277" t="n">
-        <v>1512.605042</v>
+        <v>2800</v>
       </c>
       <c r="F1277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1277" t="n">
         <v>0</v>
@@ -68712,7 +68712,7 @@
       </c>
       <c r="M1277" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1277" t="inlineStr"/>
@@ -68720,21 +68720,21 @@
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>CEFALEXINA 500MG CAPSULAS DE LA SANTE</t>
+          <t>CAUCHOS AKARELA PASTEL ROSADO</t>
         </is>
       </c>
       <c r="C1278" t="inlineStr"/>
       <c r="D1278" t="inlineStr"/>
       <c r="E1278" t="n">
-        <v>10800</v>
+        <v>1512.605042</v>
       </c>
       <c r="F1278" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G1278" t="n">
         <v>0</v>
@@ -68762,7 +68762,7 @@
       </c>
       <c r="M1278" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1278" t="inlineStr"/>
@@ -68770,25 +68770,21 @@
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>Cefalexina 500mg laproff</t>
-        </is>
-      </c>
-      <c r="C1279" t="inlineStr">
-        <is>
-          <t>7703038612636</t>
-        </is>
-      </c>
+          <t>CEFALEXINA 500MG CAPSULAS DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr"/>
       <c r="D1279" t="inlineStr"/>
       <c r="E1279" t="n">
-        <v>10000</v>
+        <v>10800</v>
       </c>
       <c r="F1279" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G1279" t="n">
         <v>0</v>
@@ -68824,21 +68820,25 @@
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>CERA EGO POTE X 60ML</t>
-        </is>
-      </c>
-      <c r="C1280" t="inlineStr"/>
+          <t>Cefalexina 500mg laproff</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>7703038612636</t>
+        </is>
+      </c>
       <c r="D1280" t="inlineStr"/>
       <c r="E1280" t="n">
-        <v>6800</v>
+        <v>10000</v>
       </c>
       <c r="F1280" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1280" t="n">
         <v>0</v>
@@ -68874,21 +68874,21 @@
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>CERA PROQUIDENT ORTD</t>
+          <t>CERA EGO POTE X 60ML</t>
         </is>
       </c>
       <c r="C1281" t="inlineStr"/>
       <c r="D1281" t="inlineStr"/>
       <c r="E1281" t="n">
-        <v>6554.621849</v>
+        <v>6800</v>
       </c>
       <c r="F1281" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1281" t="n">
         <v>0</v>
@@ -68916,7 +68916,7 @@
       </c>
       <c r="M1281" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1281" t="inlineStr"/>
@@ -68924,21 +68924,21 @@
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>CHA-P JARABE ARMONIZA 500ML</t>
+          <t>CERA PROQUIDENT ORTD</t>
         </is>
       </c>
       <c r="C1282" t="inlineStr"/>
       <c r="D1282" t="inlineStr"/>
       <c r="E1282" t="n">
-        <v>38000</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1282" t="n">
         <v>0</v>
@@ -68966,7 +68966,7 @@
       </c>
       <c r="M1282" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1282" t="inlineStr"/>
@@ -68974,21 +68974,21 @@
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>CHAPSTICK LABIAL CEREZA</t>
+          <t>CHA-P JARABE ARMONIZA 500ML</t>
         </is>
       </c>
       <c r="C1283" t="inlineStr"/>
       <c r="D1283" t="inlineStr"/>
       <c r="E1283" t="n">
-        <v>17563.02521</v>
+        <v>38000</v>
       </c>
       <c r="F1283" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1283" t="n">
         <v>0</v>
@@ -69016,7 +69016,7 @@
       </c>
       <c r="M1283" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1283" t="inlineStr"/>
@@ -69024,21 +69024,21 @@
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>CHICLE TRIDENT SURTIDOS SABORES X PAQUE</t>
+          <t>CHAPSTICK LABIAL CEREZA</t>
         </is>
       </c>
       <c r="C1284" t="inlineStr"/>
       <c r="D1284" t="inlineStr"/>
       <c r="E1284" t="n">
-        <v>2016.806723</v>
+        <v>17563.02521</v>
       </c>
       <c r="F1284" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G1284" t="n">
         <v>0</v>
@@ -69074,21 +69074,21 @@
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>CHOCOLATINA JUMBO MANI 17GR X 1 UND</t>
+          <t>CHICLE TRIDENT SURTIDOS SABORES X PAQUE</t>
         </is>
       </c>
       <c r="C1285" t="inlineStr"/>
       <c r="D1285" t="inlineStr"/>
       <c r="E1285" t="n">
-        <v>1680.672269</v>
+        <v>2016.806723</v>
       </c>
       <c r="F1285" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G1285" t="n">
         <v>0</v>
@@ -69124,21 +69124,21 @@
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>CHUPO SILICONA GRANDE</t>
+          <t>CHOCOLATINA JUMBO MANI 17GR X 1 UND</t>
         </is>
       </c>
       <c r="C1286" t="inlineStr"/>
       <c r="D1286" t="inlineStr"/>
       <c r="E1286" t="n">
-        <v>4500</v>
+        <v>1680.672269</v>
       </c>
       <c r="F1286" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G1286" t="n">
         <v>0</v>
@@ -69166,7 +69166,7 @@
       </c>
       <c r="M1286" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1286" t="inlineStr"/>
@@ -69174,21 +69174,21 @@
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>Cianocobalamina</t>
+          <t>CHUPO SILICONA GRANDE</t>
         </is>
       </c>
       <c r="C1287" t="inlineStr"/>
       <c r="D1287" t="inlineStr"/>
       <c r="E1287" t="n">
-        <v>6500</v>
+        <v>4500</v>
       </c>
       <c r="F1287" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1287" t="n">
         <v>0</v>
@@ -69224,25 +69224,21 @@
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>Cicaderm crema protector cutáneo 60gm NF</t>
-        </is>
-      </c>
-      <c r="C1288" t="inlineStr">
-        <is>
-          <t>7707173600091</t>
-        </is>
-      </c>
+          <t>Cianocobalamina</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr"/>
       <c r="D1288" t="inlineStr"/>
       <c r="E1288" t="n">
-        <v>57000</v>
+        <v>6500</v>
       </c>
       <c r="F1288" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1288" t="n">
         <v>0</v>
@@ -69278,21 +69274,25 @@
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>Citrato de calcio / Vitamina D3 600 MG/400UI (1500MG) Granulos Caja x 15 Sobres</t>
-        </is>
-      </c>
-      <c r="C1289" t="inlineStr"/>
+          <t>Cicaderm crema protector cutáneo 60gm NF</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>7707173600091</t>
+        </is>
+      </c>
       <c r="D1289" t="inlineStr"/>
       <c r="E1289" t="n">
-        <v>53000</v>
+        <v>57000</v>
       </c>
       <c r="F1289" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1289" t="n">
         <v>0</v>
@@ -69328,21 +69328,21 @@
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>769</t>
         </is>
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>CLENOX 40MG 1J/PRELLE.</t>
+          <t>Citrato de calcio / Vitamina D3 600 MG/400UI (1500MG) Granulos Caja x 15 Sobres</t>
         </is>
       </c>
       <c r="C1290" t="inlineStr"/>
       <c r="D1290" t="inlineStr"/>
       <c r="E1290" t="n">
-        <v>17800</v>
+        <v>53000</v>
       </c>
       <c r="F1290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1290" t="n">
         <v>0</v>
@@ -69378,25 +69378,21 @@
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>CLINBAC CLINDAMICINA 300MG CAPS</t>
-        </is>
-      </c>
-      <c r="C1291" t="inlineStr">
-        <is>
-          <t>7707019413816</t>
-        </is>
-      </c>
+          <t>CLENOX 40MG 1J/PRELLE.</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr"/>
       <c r="D1291" t="inlineStr"/>
       <c r="E1291" t="n">
-        <v>19200</v>
+        <v>17800</v>
       </c>
       <c r="F1291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1291" t="n">
         <v>0</v>
@@ -69432,18 +69428,22 @@
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>CLINDABACT CLOTRI+CLIND CJA X 3 OVULOS</t>
-        </is>
-      </c>
-      <c r="C1292" t="inlineStr"/>
+          <t>CLINBAC CLINDAMICINA 300MG CAPS</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>7707019413816</t>
+        </is>
+      </c>
       <c r="D1292" t="inlineStr"/>
       <c r="E1292" t="n">
-        <v>35700</v>
+        <v>19200</v>
       </c>
       <c r="F1292" t="n">
         <v>2</v>
@@ -69482,25 +69482,21 @@
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>CLOBETASOL 0,05% TRIDIRTEX CREMA X 40GR</t>
-        </is>
-      </c>
-      <c r="C1293" t="inlineStr">
-        <is>
-          <t>7709740450351</t>
-        </is>
-      </c>
+          <t>CLINDABACT CLOTRI+CLIND CJA X 3 OVULOS</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr"/>
       <c r="D1293" t="inlineStr"/>
       <c r="E1293" t="n">
-        <v>27900</v>
+        <v>35700</v>
       </c>
       <c r="F1293" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1293" t="n">
         <v>0</v>
@@ -69536,22 +69532,22 @@
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>Clotrimazol 1% 40gr AG</t>
+          <t>CLOBETASOL 0,05% TRIDIRTEX CREMA X 40GR</t>
         </is>
       </c>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>7706569001191</t>
+          <t>7709740450351</t>
         </is>
       </c>
       <c r="D1294" t="inlineStr"/>
       <c r="E1294" t="n">
-        <v>19000</v>
+        <v>27900</v>
       </c>
       <c r="F1294" t="n">
         <v>1</v>
@@ -69590,25 +69586,25 @@
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>CLOTRIMAZOL 1% CREMA TOPICA DE VITALIS</t>
+          <t>Clotrimazol 1% 40gr AG</t>
         </is>
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>7709990212204</t>
+          <t>7706569001191</t>
         </is>
       </c>
       <c r="D1295" t="inlineStr"/>
       <c r="E1295" t="n">
-        <v>14500</v>
+        <v>19000</v>
       </c>
       <c r="F1295" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1295" t="n">
         <v>0</v>
@@ -69644,21 +69640,25 @@
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>COLAGENO HIDROLIZADO EN POLVO 700GR ARMONIZA</t>
-        </is>
-      </c>
-      <c r="C1296" t="inlineStr"/>
+          <t>CLOTRIMAZOL 1% CREMA TOPICA DE VITALIS</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>7709990212204</t>
+        </is>
+      </c>
       <c r="D1296" t="inlineStr"/>
       <c r="E1296" t="n">
-        <v>56000</v>
+        <v>14500</v>
       </c>
       <c r="F1296" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1296" t="n">
         <v>0</v>
@@ -69694,21 +69694,21 @@
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>Colchicina Coas</t>
+          <t>COLAGENO HIDROLIZADO EN POLVO 700GR ARMONIZA</t>
         </is>
       </c>
       <c r="C1297" t="inlineStr"/>
       <c r="D1297" t="inlineStr"/>
       <c r="E1297" t="n">
-        <v>3900</v>
+        <v>56000</v>
       </c>
       <c r="F1297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1297" t="n">
         <v>0</v>
@@ -69744,18 +69744,18 @@
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>CONDON DUO LUBRICADO X 3 UND</t>
+          <t>Colchicina Coas</t>
         </is>
       </c>
       <c r="C1298" t="inlineStr"/>
       <c r="D1298" t="inlineStr"/>
       <c r="E1298" t="n">
-        <v>16500</v>
+        <v>3900</v>
       </c>
       <c r="F1298" t="n">
         <v>1</v>
@@ -69794,18 +69794,18 @@
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
+          <t>CONDON DUO LUBRICADO X 3 UND</t>
         </is>
       </c>
       <c r="C1299" t="inlineStr"/>
       <c r="D1299" t="inlineStr"/>
       <c r="E1299" t="n">
-        <v>8900</v>
+        <v>16500</v>
       </c>
       <c r="F1299" t="n">
         <v>1</v>
@@ -69844,7 +69844,7 @@
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="B1300" t="inlineStr">
@@ -69858,7 +69858,7 @@
         <v>8900</v>
       </c>
       <c r="F1300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1300" t="n">
         <v>0</v>
@@ -69894,12 +69894,12 @@
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>CONDON PIEL SABORES CJA X 3 UNDS</t>
+          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
         </is>
       </c>
       <c r="C1301" t="inlineStr"/>
@@ -69908,7 +69908,7 @@
         <v>8900</v>
       </c>
       <c r="F1301" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1301" t="n">
         <v>0</v>
@@ -69944,25 +69944,21 @@
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>CONDON PRUDENCE EFEC.RETARDX3UNDS</t>
-        </is>
-      </c>
-      <c r="C1302" t="inlineStr">
-        <is>
-          <t>77309632510504387</t>
-        </is>
-      </c>
+          <t>CONDON PIEL SABORES CJA X 3 UNDS</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr"/>
       <c r="D1302" t="inlineStr"/>
       <c r="E1302" t="n">
-        <v>12200</v>
+        <v>8900</v>
       </c>
       <c r="F1302" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1302" t="n">
         <v>0</v>
@@ -69998,25 +69994,25 @@
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>CONDON PRUDENCE EXTRA GRANDE ULT SENSIBX3UND</t>
+          <t>CONDON PRUDENCE EFEC.RETARDX3UNDS</t>
         </is>
       </c>
       <c r="C1303" t="inlineStr">
         <is>
-          <t>7730963250343</t>
+          <t>77309632510504387</t>
         </is>
       </c>
       <c r="D1303" t="inlineStr"/>
       <c r="E1303" t="n">
-        <v>13800</v>
+        <v>12200</v>
       </c>
       <c r="F1303" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1303" t="n">
         <v>0</v>
@@ -70052,25 +70048,25 @@
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>CONTENT MEDICAL PAÑAL TALLA L X UND</t>
-        </is>
-      </c>
-      <c r="C1304" t="inlineStr"/>
-      <c r="D1304" t="inlineStr">
-        <is>
-          <t>pañal adulto no paga iva articulo 424</t>
-        </is>
-      </c>
+          <t>CONDON PRUDENCE EXTRA GRANDE ULT SENSIBX3UND</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>7730963250343</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr"/>
       <c r="E1304" t="n">
-        <v>4800</v>
+        <v>13800</v>
       </c>
       <c r="F1304" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G1304" t="n">
         <v>0</v>
@@ -70106,21 +70102,25 @@
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>CONTENT MEDICAL PAÑAL TALLA M X UND</t>
+          <t>CONTENT MEDICAL PAÑAL TALLA L X UND</t>
         </is>
       </c>
       <c r="C1305" t="inlineStr"/>
-      <c r="D1305" t="inlineStr"/>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>pañal adulto no paga iva articulo 424</t>
+        </is>
+      </c>
       <c r="E1305" t="n">
-        <v>3697.478992</v>
+        <v>4800</v>
       </c>
       <c r="F1305" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G1305" t="n">
         <v>0</v>
@@ -70148,7 +70148,7 @@
       </c>
       <c r="M1305" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1305" t="inlineStr"/>
@@ -70156,21 +70156,21 @@
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 100 UNDS</t>
+          <t>CONTENT MEDICAL PAÑAL TALLA M X UND</t>
         </is>
       </c>
       <c r="C1306" t="inlineStr"/>
       <c r="D1306" t="inlineStr"/>
       <c r="E1306" t="n">
-        <v>8500</v>
+        <v>3697.478992</v>
       </c>
       <c r="F1306" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G1306" t="n">
         <v>0</v>
@@ -70198,7 +70198,7 @@
       </c>
       <c r="M1306" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1306" t="inlineStr"/>
@@ -70206,18 +70206,18 @@
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 50 UNDS</t>
+          <t>COPITOS YOKY X 100 UNDS</t>
         </is>
       </c>
       <c r="C1307" t="inlineStr"/>
       <c r="D1307" t="inlineStr"/>
       <c r="E1307" t="n">
-        <v>6400</v>
+        <v>8500</v>
       </c>
       <c r="F1307" t="n">
         <v>3</v>
@@ -70256,21 +70256,21 @@
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 60 UNDS</t>
+          <t>COPITOS YOKY X 50 UNDS</t>
         </is>
       </c>
       <c r="C1308" t="inlineStr"/>
       <c r="D1308" t="inlineStr"/>
       <c r="E1308" t="n">
-        <v>7142.857143</v>
+        <v>6400</v>
       </c>
       <c r="F1308" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1308" t="n">
         <v>0</v>
@@ -70298,7 +70298,7 @@
       </c>
       <c r="M1308" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1308" t="inlineStr"/>
@@ -70306,21 +70306,21 @@
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>CORTA CUTICULA TRIM METALICO</t>
+          <t>COPITOS YOKY X 60 UNDS</t>
         </is>
       </c>
       <c r="C1309" t="inlineStr"/>
       <c r="D1309" t="inlineStr"/>
       <c r="E1309" t="n">
-        <v>16000</v>
+        <v>7142.857143</v>
       </c>
       <c r="F1309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1309" t="n">
         <v>0</v>
@@ -70348,7 +70348,7 @@
       </c>
       <c r="M1309" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1309" t="inlineStr"/>
@@ -70356,21 +70356,21 @@
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>CREMA ARNICA PROTECTORA 12GR ICE POWER</t>
+          <t>CORTA CUTICULA TRIM METALICO</t>
         </is>
       </c>
       <c r="C1310" t="inlineStr"/>
       <c r="D1310" t="inlineStr"/>
       <c r="E1310" t="n">
-        <v>10084.033613</v>
+        <v>16000</v>
       </c>
       <c r="F1310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1310" t="n">
         <v>0</v>
@@ -70398,7 +70398,7 @@
       </c>
       <c r="M1310" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1310" t="inlineStr"/>
@@ -70406,21 +70406,21 @@
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>CREMA BENLIC DE 40GR</t>
+          <t>CREMA ARNICA PROTECTORA 12GR ICE POWER</t>
         </is>
       </c>
       <c r="C1311" t="inlineStr"/>
       <c r="D1311" t="inlineStr"/>
       <c r="E1311" t="n">
-        <v>28900</v>
+        <v>10084.033613</v>
       </c>
       <c r="F1311" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1311" t="n">
         <v>0</v>
@@ -70448,7 +70448,7 @@
       </c>
       <c r="M1311" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1311" t="inlineStr"/>
@@ -70456,18 +70456,18 @@
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>CREMA CASTAÑO DE INDIAS X 12GR ARMONIZA</t>
+          <t>CREMA BENLIC DE 40GR</t>
         </is>
       </c>
       <c r="C1312" t="inlineStr"/>
       <c r="D1312" t="inlineStr"/>
       <c r="E1312" t="n">
-        <v>9000</v>
+        <v>28900</v>
       </c>
       <c r="F1312" t="n">
         <v>1</v>
@@ -70506,25 +70506,21 @@
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>Crema Colgate triple acción xtra blancura 60ml</t>
-        </is>
-      </c>
-      <c r="C1313" t="inlineStr">
-        <is>
-          <t>7702010111587</t>
-        </is>
-      </c>
+          <t>CREMA CASTAÑO DE INDIAS X 12GR ARMONIZA</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr"/>
       <c r="D1313" t="inlineStr"/>
       <c r="E1313" t="n">
-        <v>5630.252101</v>
+        <v>9000</v>
       </c>
       <c r="F1313" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1313" t="n">
         <v>0</v>
@@ -70552,7 +70548,7 @@
       </c>
       <c r="M1313" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1313" t="inlineStr"/>
@@ -70560,21 +70556,25 @@
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>CREMA PONDS CLARANT B3 X SACHETS</t>
-        </is>
-      </c>
-      <c r="C1314" t="inlineStr"/>
+          <t>Crema Colgate triple acción xtra blancura 60ml</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>7702010111587</t>
+        </is>
+      </c>
       <c r="D1314" t="inlineStr"/>
       <c r="E1314" t="n">
-        <v>2521.008403</v>
+        <v>5630.252101</v>
       </c>
       <c r="F1314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1314" t="n">
         <v>0</v>
@@ -70610,21 +70610,21 @@
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>CURAS LARGAS RESIST AL AGUA</t>
+          <t>CREMA PONDS CLARANT B3 X SACHETS</t>
         </is>
       </c>
       <c r="C1315" t="inlineStr"/>
       <c r="D1315" t="inlineStr"/>
       <c r="E1315" t="n">
-        <v>300</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1315" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="G1315" t="n">
         <v>0</v>
@@ -70652,7 +70652,7 @@
       </c>
       <c r="M1315" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1315" t="inlineStr"/>
@@ -70660,25 +70660,21 @@
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>CYCLOFEM AMPOLLA INYECTABLE .PROFAMILIA</t>
-        </is>
-      </c>
-      <c r="C1316" t="inlineStr">
-        <is>
-          <t>7703689000448</t>
-        </is>
-      </c>
+          <t>CURAS LARGAS RESIST AL AGUA</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr"/>
       <c r="D1316" t="inlineStr"/>
       <c r="E1316" t="n">
-        <v>28900</v>
+        <v>300</v>
       </c>
       <c r="F1316" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="G1316" t="n">
         <v>0</v>
@@ -70714,25 +70710,25 @@
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>CYCLOFEMINA AMPOLLA 0.5ML</t>
+          <t>CYCLOFEM AMPOLLA INYECTABLE .PROFAMILIA</t>
         </is>
       </c>
       <c r="C1317" t="inlineStr">
         <is>
-          <t>7707271451410</t>
+          <t>7703689000448</t>
         </is>
       </c>
       <c r="D1317" t="inlineStr"/>
       <c r="E1317" t="n">
-        <v>33900</v>
+        <v>28900</v>
       </c>
       <c r="F1317" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1317" t="n">
         <v>0</v>
@@ -70768,25 +70764,25 @@
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>Desonida bussie 0.1% crema 15gr</t>
+          <t>CYCLOFEMINA AMPOLLA 0.5ML</t>
         </is>
       </c>
       <c r="C1318" t="inlineStr">
         <is>
-          <t>7702195210587</t>
+          <t>7707271451410</t>
         </is>
       </c>
       <c r="D1318" t="inlineStr"/>
       <c r="E1318" t="n">
-        <v>19000</v>
+        <v>33900</v>
       </c>
       <c r="F1318" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1318" t="n">
         <v>0</v>
@@ -70822,25 +70818,25 @@
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>Diclofenaco gel vitalis 50gr</t>
+          <t>Desonida bussie 0.1% crema 15gr</t>
         </is>
       </c>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>7709141546059</t>
+          <t>7702195210587</t>
         </is>
       </c>
       <c r="D1319" t="inlineStr"/>
       <c r="E1319" t="n">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="F1319" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1319" t="n">
         <v>0</v>
@@ -70866,31 +70862,35 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1319" t="inlineStr"/>
+      <c r="M1319" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1319" t="inlineStr"/>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>Diclofenaco sódico 100mg +hidróxido de aluminio200mg colmed</t>
+          <t>Diclofenaco gel vitalis 50gr</t>
         </is>
       </c>
       <c r="C1320" t="inlineStr">
         <is>
-          <t>7703153020286</t>
+          <t>7709141546059</t>
         </is>
       </c>
       <c r="D1320" t="inlineStr"/>
       <c r="E1320" t="n">
-        <v>19200</v>
+        <v>16000</v>
       </c>
       <c r="F1320" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1320" t="n">
         <v>0</v>
@@ -70916,31 +70916,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1320" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1320" t="inlineStr"/>
       <c r="N1320" t="inlineStr"/>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>DICLOFENACOXUND75MG/3MLAMPCOMERCIAL VITALIS</t>
-        </is>
-      </c>
-      <c r="C1321" t="inlineStr"/>
+          <t>Diclofenaco sódico 100mg +hidróxido de aluminio200mg colmed</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>7703153020286</t>
+        </is>
+      </c>
       <c r="D1321" t="inlineStr"/>
       <c r="E1321" t="n">
-        <v>5500</v>
+        <v>19200</v>
       </c>
       <c r="F1321" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1321" t="n">
         <v>0</v>
@@ -70976,18 +70976,18 @@
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>DIFENZ DESPIGMENTADOR CREMA TUBO X 1 UND</t>
+          <t>DICLOFENACOXUND75MG/3MLAMPCOMERCIAL VITALIS</t>
         </is>
       </c>
       <c r="C1322" t="inlineStr"/>
       <c r="D1322" t="inlineStr"/>
       <c r="E1322" t="n">
-        <v>163300</v>
+        <v>5500</v>
       </c>
       <c r="F1322" t="n">
         <v>1</v>
@@ -71026,21 +71026,21 @@
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>DIPIORNA 500MG TABLETA X 10 DE ECAR</t>
+          <t>DIFENZ DESPIGMENTADOR CREMA TUBO X 1 UND</t>
         </is>
       </c>
       <c r="C1323" t="inlineStr"/>
       <c r="D1323" t="inlineStr"/>
       <c r="E1323" t="n">
-        <v>7900</v>
+        <v>163300</v>
       </c>
       <c r="F1323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1323" t="n">
         <v>0</v>
@@ -71076,12 +71076,12 @@
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>DIPIRONA 500MG TABLETA X 10 DE ECAR</t>
+          <t>DIPIORNA 500MG TABLETA X 10 DE ECAR</t>
         </is>
       </c>
       <c r="C1324" t="inlineStr"/>
@@ -71090,7 +71090,7 @@
         <v>7900</v>
       </c>
       <c r="F1324" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1324" t="n">
         <v>0</v>
@@ -71126,21 +71126,21 @@
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>DOMICILIO</t>
+          <t>DIPIRONA 500MG TABLETA X 10 DE ECAR</t>
         </is>
       </c>
       <c r="C1325" t="inlineStr"/>
       <c r="D1325" t="inlineStr"/>
       <c r="E1325" t="n">
-        <v>3000</v>
+        <v>7900</v>
       </c>
       <c r="F1325" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1325" t="n">
         <v>0</v>
@@ -71166,27 +71166,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1325" t="inlineStr"/>
+      <c r="M1325" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1325" t="inlineStr"/>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>DOXICICLINA 100MG X 10 TABL GENFAR</t>
+          <t>DOMICILIO</t>
         </is>
       </c>
       <c r="C1326" t="inlineStr"/>
       <c r="D1326" t="inlineStr"/>
       <c r="E1326" t="n">
-        <v>12000</v>
+        <v>3000</v>
       </c>
       <c r="F1326" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1326" t="n">
         <v>0</v>
@@ -71212,31 +71216,27 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1326" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1326" t="inlineStr"/>
       <c r="N1326" t="inlineStr"/>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>DUCHA INTIMA DESECHABLE VINAGRE</t>
+          <t>DOXICICLINA 100MG X 10 TABL GENFAR</t>
         </is>
       </c>
       <c r="C1327" t="inlineStr"/>
       <c r="D1327" t="inlineStr"/>
       <c r="E1327" t="n">
-        <v>24800</v>
+        <v>12000</v>
       </c>
       <c r="F1327" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1327" t="n">
         <v>0</v>
@@ -71272,25 +71272,21 @@
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>E ala proel maléate 20mg medicbrand</t>
-        </is>
-      </c>
-      <c r="C1328" t="inlineStr">
-        <is>
-          <t>7703712035997</t>
-        </is>
-      </c>
+          <t>DUCHA INTIMA DESECHABLE VINAGRE</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr"/>
       <c r="D1328" t="inlineStr"/>
       <c r="E1328" t="n">
-        <v>1250</v>
+        <v>24800</v>
       </c>
       <c r="F1328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1328" t="n">
         <v>0</v>
@@ -71326,25 +71322,25 @@
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>Enalapril 20 mg MK</t>
+          <t>E ala proel maléate 20mg medicbrand</t>
         </is>
       </c>
       <c r="C1329" t="inlineStr">
         <is>
-          <t>7702057716578</t>
+          <t>7703712035997</t>
         </is>
       </c>
       <c r="D1329" t="inlineStr"/>
       <c r="E1329" t="n">
-        <v>4700</v>
+        <v>1250</v>
       </c>
       <c r="F1329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1329" t="n">
         <v>0</v>
@@ -71380,21 +71376,25 @@
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>ENALAPRIL 20MG TABLETA COAS</t>
-        </is>
-      </c>
-      <c r="C1330" t="inlineStr"/>
+          <t>Enalapril 20 mg MK</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>7702057716578</t>
+        </is>
+      </c>
       <c r="D1330" t="inlineStr"/>
       <c r="E1330" t="n">
-        <v>3000</v>
+        <v>4700</v>
       </c>
       <c r="F1330" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1330" t="n">
         <v>0</v>
@@ -71430,21 +71430,21 @@
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>ENSURE ADVANCE VAINILLA 400GR</t>
+          <t>ENALAPRIL 20MG TABLETA COAS</t>
         </is>
       </c>
       <c r="C1331" t="inlineStr"/>
       <c r="D1331" t="inlineStr"/>
       <c r="E1331" t="n">
-        <v>85900</v>
+        <v>3000</v>
       </c>
       <c r="F1331" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1331" t="n">
         <v>0</v>
@@ -71480,18 +71480,18 @@
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>ENTRETENEDOR BEBE</t>
+          <t>ENSURE ADVANCE VAINILLA 400GR</t>
         </is>
       </c>
       <c r="C1332" t="inlineStr"/>
       <c r="D1332" t="inlineStr"/>
       <c r="E1332" t="n">
-        <v>9000</v>
+        <v>85900</v>
       </c>
       <c r="F1332" t="n">
         <v>1</v>
@@ -71530,18 +71530,18 @@
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>ESMALTE BRILLO ACRILICO BRESCIA</t>
+          <t>ENTRETENEDOR BEBE</t>
         </is>
       </c>
       <c r="C1333" t="inlineStr"/>
       <c r="D1333" t="inlineStr"/>
       <c r="E1333" t="n">
-        <v>11500</v>
+        <v>9000</v>
       </c>
       <c r="F1333" t="n">
         <v>1</v>
@@ -71580,21 +71580,21 @@
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>ESOMEPRAZOL 20MG NOVAMED</t>
+          <t>ESMALTE BRILLO ACRILICO BRESCIA</t>
         </is>
       </c>
       <c r="C1334" t="inlineStr"/>
       <c r="D1334" t="inlineStr"/>
       <c r="E1334" t="n">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="F1334" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G1334" t="n">
         <v>0</v>
@@ -71630,21 +71630,21 @@
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>ESPASMOK HIOS +DIPIRO 5ML AMP BLASKOV</t>
+          <t>ESOMEPRAZOL 20MG NOVAMED</t>
         </is>
       </c>
       <c r="C1335" t="inlineStr"/>
       <c r="D1335" t="inlineStr"/>
       <c r="E1335" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="F1335" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G1335" t="n">
         <v>0</v>
@@ -71680,22 +71680,18 @@
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>EXTRACTOR DE LECHE MOBY</t>
-        </is>
-      </c>
-      <c r="C1336" t="inlineStr">
-        <is>
-          <t>7707233051436</t>
-        </is>
-      </c>
+          <t>ESPASMOK HIOS +DIPIRO 5ML AMP BLASKOV</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr"/>
       <c r="D1336" t="inlineStr"/>
       <c r="E1336" t="n">
-        <v>14285.714286</v>
+        <v>12000</v>
       </c>
       <c r="F1336" t="n">
         <v>1</v>
@@ -71726,7 +71722,7 @@
       </c>
       <c r="M1336" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1336" t="inlineStr"/>
@@ -71734,25 +71730,25 @@
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>FAMIIA MEGARROLLO PAPEL HIGUIEN</t>
+          <t>EXTRACTOR DE LECHE MOBY</t>
         </is>
       </c>
       <c r="C1337" t="inlineStr">
         <is>
-          <t>7702026147471</t>
+          <t>7707233051436</t>
         </is>
       </c>
       <c r="D1337" t="inlineStr"/>
       <c r="E1337" t="n">
-        <v>3500</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1337" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1337" t="n">
         <v>0</v>
@@ -71780,7 +71776,7 @@
       </c>
       <c r="M1337" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1337" t="inlineStr"/>
@@ -71788,21 +71784,25 @@
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>Farma D 500 UI</t>
-        </is>
-      </c>
-      <c r="C1338" t="inlineStr"/>
+          <t>FAMIIA MEGARROLLO PAPEL HIGUIEN</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>7702026147471</t>
+        </is>
+      </c>
       <c r="D1338" t="inlineStr"/>
       <c r="E1338" t="n">
-        <v>74000</v>
+        <v>3500</v>
       </c>
       <c r="F1338" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G1338" t="n">
         <v>0</v>
@@ -71838,21 +71838,21 @@
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>FIBRA AMARILLA ARMONIZA X 450GR</t>
+          <t>Farma D 500 UI</t>
         </is>
       </c>
       <c r="C1339" t="inlineStr"/>
       <c r="D1339" t="inlineStr"/>
       <c r="E1339" t="n">
-        <v>28571.428571</v>
+        <v>74000</v>
       </c>
       <c r="F1339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1339" t="n">
         <v>0</v>
@@ -71880,7 +71880,7 @@
       </c>
       <c r="M1339" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1339" t="inlineStr"/>
@@ -71888,21 +71888,21 @@
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>FIBRA DE AVENA Y SALVADO DE TRIGO 450GR</t>
+          <t>FIBRA AMARILLA ARMONIZA X 450GR</t>
         </is>
       </c>
       <c r="C1340" t="inlineStr"/>
       <c r="D1340" t="inlineStr"/>
       <c r="E1340" t="n">
-        <v>30000</v>
+        <v>28571.428571</v>
       </c>
       <c r="F1340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1340" t="n">
         <v>0</v>
@@ -71930,7 +71930,7 @@
       </c>
       <c r="M1340" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1340" t="inlineStr"/>
@@ -71938,21 +71938,21 @@
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>FITOSTIMONE 15% GEL</t>
+          <t>FIBRA DE AVENA Y SALVADO DE TRIGO 450GR</t>
         </is>
       </c>
       <c r="C1341" t="inlineStr"/>
       <c r="D1341" t="inlineStr"/>
       <c r="E1341" t="n">
-        <v>48900</v>
+        <v>30000</v>
       </c>
       <c r="F1341" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1341" t="n">
         <v>0</v>
@@ -71988,25 +71988,21 @@
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG CJA X 10 UND EXPORF</t>
-        </is>
-      </c>
-      <c r="C1342" t="inlineStr">
-        <is>
-          <t>7703432421681</t>
-        </is>
-      </c>
+          <t>FITOSTIMONE 15% GEL</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr"/>
       <c r="D1342" t="inlineStr"/>
       <c r="E1342" t="n">
-        <v>18300</v>
+        <v>48900</v>
       </c>
       <c r="F1342" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G1342" t="n">
         <v>0</v>
@@ -72042,21 +72038,25 @@
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1343" t="inlineStr"/>
+          <t>FLUCONAZOL 200MG CJA X 10 UND EXPORF</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>7703432421681</t>
+        </is>
+      </c>
       <c r="D1343" t="inlineStr"/>
       <c r="E1343" t="n">
-        <v>16900</v>
+        <v>18300</v>
       </c>
       <c r="F1343" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G1343" t="n">
         <v>0</v>
@@ -72092,25 +72092,21 @@
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS. LA SANTE</t>
-        </is>
-      </c>
-      <c r="C1344" t="inlineStr">
-        <is>
-          <t>7703763480166</t>
-        </is>
-      </c>
+          <t>FLUCONAZOL 200MG X 4 CAPS DE GENFAR</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr"/>
       <c r="D1344" t="inlineStr"/>
       <c r="E1344" t="n">
-        <v>14700</v>
+        <v>16900</v>
       </c>
       <c r="F1344" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1344" t="n">
         <v>0</v>
@@ -72146,25 +72142,25 @@
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS.NOVAMED</t>
+          <t>FLUCONAZOL 200MG X 4 CAPS. LA SANTE</t>
         </is>
       </c>
       <c r="C1345" t="inlineStr">
         <is>
-          <t>7703546927468</t>
+          <t>7703763480166</t>
         </is>
       </c>
       <c r="D1345" t="inlineStr"/>
       <c r="E1345" t="n">
-        <v>10900</v>
+        <v>14700</v>
       </c>
       <c r="F1345" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1345" t="n">
         <v>0</v>
@@ -72200,18 +72196,22 @@
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>Fluconazol Suspension</t>
-        </is>
-      </c>
-      <c r="C1346" t="inlineStr"/>
+          <t>FLUCONAZOL 200MG X 4 CAPS.NOVAMED</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>7703546927468</t>
+        </is>
+      </c>
       <c r="D1346" t="inlineStr"/>
       <c r="E1346" t="n">
-        <v>148000</v>
+        <v>10900</v>
       </c>
       <c r="F1346" t="n">
         <v>2</v>
@@ -72250,21 +72250,21 @@
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>FUNGI-FIN LOCION GOTAS TOPICA 20ML</t>
+          <t>Fluconazol Suspension</t>
         </is>
       </c>
       <c r="C1347" t="inlineStr"/>
       <c r="D1347" t="inlineStr"/>
       <c r="E1347" t="n">
-        <v>15966.386555</v>
+        <v>148000</v>
       </c>
       <c r="F1347" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1347" t="n">
         <v>0</v>
@@ -72292,7 +72292,7 @@
       </c>
       <c r="M1347" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1347" t="inlineStr"/>
@@ -72300,21 +72300,21 @@
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>GALLETA OREO PAQUETE X 6 UNDS</t>
+          <t>FUNGI-FIN LOCION GOTAS TOPICA 20ML</t>
         </is>
       </c>
       <c r="C1348" t="inlineStr"/>
       <c r="D1348" t="inlineStr"/>
       <c r="E1348" t="n">
-        <v>1932.773109</v>
+        <v>15966.386555</v>
       </c>
       <c r="F1348" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1348" t="n">
         <v>0</v>
@@ -72350,21 +72350,21 @@
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>GASEOSA PREMIO 400ML ROJO</t>
+          <t>GALLETA OREO PAQUETE X 6 UNDS</t>
         </is>
       </c>
       <c r="C1349" t="inlineStr"/>
       <c r="D1349" t="inlineStr"/>
       <c r="E1349" t="n">
-        <v>2941.176471</v>
+        <v>1932.773109</v>
       </c>
       <c r="F1349" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G1349" t="n">
         <v>0</v>
@@ -72400,29 +72400,21 @@
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>GASTROFAST ADVANCE</t>
-        </is>
-      </c>
-      <c r="C1350" t="inlineStr">
-        <is>
-          <t>7702057803254</t>
-        </is>
-      </c>
-      <c r="D1350" t="inlineStr">
-        <is>
-          <t>se subio A 3800 ANTES 3.600, LEYDI</t>
-        </is>
-      </c>
+          <t>GASEOSA PREMIO 400ML ROJO</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr"/>
+      <c r="D1350" t="inlineStr"/>
       <c r="E1350" t="n">
-        <v>3800</v>
+        <v>2941.176471</v>
       </c>
       <c r="F1350" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G1350" t="n">
         <v>0</v>
@@ -72450,7 +72442,7 @@
       </c>
       <c r="M1350" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1350" t="inlineStr"/>
@@ -72458,21 +72450,29 @@
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>GASTROFAST ADVANCE X 240 ML</t>
-        </is>
-      </c>
-      <c r="C1351" t="inlineStr"/>
-      <c r="D1351" t="inlineStr"/>
+          <t>GASTROFAST ADVANCE</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>7702057803254</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>se subio A 3800 ANTES 3.600, LEYDI</t>
+        </is>
+      </c>
       <c r="E1351" t="n">
-        <v>69500</v>
+        <v>3800</v>
       </c>
       <c r="F1351" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G1351" t="n">
         <v>0</v>
@@ -72508,25 +72508,21 @@
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>gatorade</t>
-        </is>
-      </c>
-      <c r="C1352" t="inlineStr">
-        <is>
-          <t>248656546</t>
-        </is>
-      </c>
+          <t>GASTROFAST ADVANCE X 240 ML</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr"/>
       <c r="D1352" t="inlineStr"/>
       <c r="E1352" t="n">
-        <v>3782</v>
+        <v>69500</v>
       </c>
       <c r="F1352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1352" t="n">
         <v>0</v>
@@ -72554,7 +72550,7 @@
       </c>
       <c r="M1352" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1352" t="inlineStr"/>
@@ -72562,21 +72558,25 @@
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>GEL BACHUE 150GR</t>
-        </is>
-      </c>
-      <c r="C1353" t="inlineStr"/>
+          <t>gatorade</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>248656546</t>
+        </is>
+      </c>
       <c r="D1353" t="inlineStr"/>
       <c r="E1353" t="n">
-        <v>8800</v>
+        <v>3782</v>
       </c>
       <c r="F1353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1353" t="n">
         <v>0</v>
@@ -72604,7 +72604,7 @@
       </c>
       <c r="M1353" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1353" t="inlineStr"/>
@@ -72612,21 +72612,21 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>GEMFIBROZILO 600 MG</t>
+          <t>GEL BACHUE 150GR</t>
         </is>
       </c>
       <c r="C1354" t="inlineStr"/>
       <c r="D1354" t="inlineStr"/>
       <c r="E1354" t="n">
-        <v>8300</v>
+        <v>8800</v>
       </c>
       <c r="F1354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1354" t="n">
         <v>0</v>
@@ -72662,21 +72662,21 @@
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>GLICERINA CARBONATADA X 20ML FCO YOMA</t>
+          <t>GEMFIBROZILO 600 MG</t>
         </is>
       </c>
       <c r="C1355" t="inlineStr"/>
       <c r="D1355" t="inlineStr"/>
       <c r="E1355" t="n">
-        <v>3900</v>
+        <v>8300</v>
       </c>
       <c r="F1355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1355" t="n">
         <v>0</v>
@@ -72712,18 +72712,18 @@
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
+          <t>GLICERINA CARBONATADA X 20ML FCO YOMA</t>
         </is>
       </c>
       <c r="C1356" t="inlineStr"/>
       <c r="D1356" t="inlineStr"/>
       <c r="E1356" t="n">
-        <v>3361.344538</v>
+        <v>3900</v>
       </c>
       <c r="F1356" t="n">
         <v>1</v>
@@ -72754,7 +72754,7 @@
       </c>
       <c r="M1356" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1356" t="inlineStr"/>
@@ -72762,21 +72762,21 @@
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
+          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
         </is>
       </c>
       <c r="C1357" t="inlineStr"/>
       <c r="D1357" t="inlineStr"/>
       <c r="E1357" t="n">
-        <v>23109.243697</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1357" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="G1357" t="n">
         <v>0</v>
@@ -72812,25 +72812,21 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1358" t="inlineStr">
-        <is>
-          <t>7709195419279</t>
-        </is>
-      </c>
+          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr"/>
       <c r="D1358" t="inlineStr"/>
       <c r="E1358" t="n">
-        <v>24370</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1358" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1358" t="n">
         <v>0</v>
@@ -72866,18 +72862,22 @@
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1359" t="inlineStr"/>
+          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>7709195419279</t>
+        </is>
+      </c>
       <c r="D1359" t="inlineStr"/>
       <c r="E1359" t="n">
-        <v>24369.747899</v>
+        <v>24370</v>
       </c>
       <c r="F1359" t="n">
         <v>50</v>
@@ -72916,21 +72916,21 @@
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
+          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
         </is>
       </c>
       <c r="C1360" t="inlineStr"/>
       <c r="D1360" t="inlineStr"/>
       <c r="E1360" t="n">
-        <v>23109.243697</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1360" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G1360" t="n">
         <v>0</v>
@@ -72966,21 +72966,21 @@
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>HALLS BARRA SURTIDOS SABORES</t>
+          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
         </is>
       </c>
       <c r="C1361" t="inlineStr"/>
       <c r="D1361" t="inlineStr"/>
       <c r="E1361" t="n">
-        <v>2100.840336</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1361" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G1361" t="n">
         <v>0</v>
@@ -73016,21 +73016,21 @@
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>HALLS PEPA ROJO CEREZA X UND</t>
+          <t>HALLS BARRA SURTIDOS SABORES</t>
         </is>
       </c>
       <c r="C1362" t="inlineStr"/>
       <c r="D1362" t="inlineStr"/>
       <c r="E1362" t="n">
-        <v>336.134454</v>
+        <v>2100.840336</v>
       </c>
       <c r="F1362" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="G1362" t="n">
         <v>0</v>
@@ -73066,21 +73066,21 @@
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>HEPATODREN JARABE FCO X 240ML</t>
+          <t>HALLS PEPA ROJO CEREZA X UND</t>
         </is>
       </c>
       <c r="C1363" t="inlineStr"/>
       <c r="D1363" t="inlineStr"/>
       <c r="E1363" t="n">
-        <v>34500</v>
+        <v>336.134454</v>
       </c>
       <c r="F1363" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G1363" t="n">
         <v>0</v>
@@ -73108,7 +73108,7 @@
       </c>
       <c r="M1363" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1363" t="inlineStr"/>
@@ -73116,18 +73116,18 @@
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>HEPATODREN X 60 CAPSULAS</t>
+          <t>HEPATODREN JARABE FCO X 240ML</t>
         </is>
       </c>
       <c r="C1364" t="inlineStr"/>
       <c r="D1364" t="inlineStr"/>
       <c r="E1364" t="n">
-        <v>58300</v>
+        <v>34500</v>
       </c>
       <c r="F1364" t="n">
         <v>1</v>
@@ -73166,25 +73166,21 @@
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>Hidraplus 75 zinc uva 400ml</t>
-        </is>
-      </c>
-      <c r="C1365" t="inlineStr">
-        <is>
-          <t>7702057010928</t>
-        </is>
-      </c>
+          <t>HEPATODREN X 60 CAPSULAS</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr"/>
       <c r="D1365" t="inlineStr"/>
       <c r="E1365" t="n">
-        <v>10600</v>
+        <v>58300</v>
       </c>
       <c r="F1365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1365" t="n">
         <v>0</v>
@@ -73220,21 +73216,25 @@
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
-        </is>
-      </c>
-      <c r="C1366" t="inlineStr"/>
+          <t>Hidraplus 75 zinc uva 400ml</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>7702057010928</t>
+        </is>
+      </c>
       <c r="D1366" t="inlineStr"/>
       <c r="E1366" t="n">
-        <v>15900</v>
+        <v>10600</v>
       </c>
       <c r="F1366" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1366" t="n">
         <v>0</v>
@@ -73270,25 +73270,21 @@
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
-        </is>
-      </c>
-      <c r="C1367" t="inlineStr">
-        <is>
-          <t>77099475597789</t>
-        </is>
-      </c>
+          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr"/>
       <c r="D1367" t="inlineStr"/>
       <c r="E1367" t="n">
-        <v>28000</v>
+        <v>15900</v>
       </c>
       <c r="F1367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1367" t="n">
         <v>0</v>
@@ -73324,25 +73320,25 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>Hidroxicina 0.25 JBE x 120 ML</t>
+          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
         </is>
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>7707035540596</t>
+          <t>77099475597789</t>
         </is>
       </c>
       <c r="D1368" t="inlineStr"/>
       <c r="E1368" t="n">
-        <v>11000</v>
+        <v>28000</v>
       </c>
       <c r="F1368" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1368" t="n">
         <v>0</v>
@@ -73378,18 +73374,22 @@
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
-        </is>
-      </c>
-      <c r="C1369" t="inlineStr"/>
+          <t>Hidroxicina 0.25 JBE x 120 ML</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>7707035540596</t>
+        </is>
+      </c>
       <c r="D1369" t="inlineStr"/>
       <c r="E1369" t="n">
-        <v>4500</v>
+        <v>11000</v>
       </c>
       <c r="F1369" t="n">
         <v>2</v>
@@ -73428,21 +73428,21 @@
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
+          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
         </is>
       </c>
       <c r="C1370" t="inlineStr"/>
       <c r="D1370" t="inlineStr"/>
       <c r="E1370" t="n">
-        <v>6900</v>
+        <v>4500</v>
       </c>
       <c r="F1370" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1370" t="n">
         <v>0</v>
@@ -73478,18 +73478,18 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
+          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
         </is>
       </c>
       <c r="C1371" t="inlineStr"/>
       <c r="D1371" t="inlineStr"/>
       <c r="E1371" t="n">
-        <v>12000</v>
+        <v>6900</v>
       </c>
       <c r="F1371" t="n">
         <v>4</v>
@@ -73528,21 +73528,21 @@
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>Hylo Gel</t>
+          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
         </is>
       </c>
       <c r="C1372" t="inlineStr"/>
       <c r="D1372" t="inlineStr"/>
       <c r="E1372" t="n">
-        <v>131600</v>
+        <v>12000</v>
       </c>
       <c r="F1372" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1372" t="n">
         <v>0</v>
@@ -73578,25 +73578,21 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>IBUPROFENO 400MG/ GENFAR</t>
-        </is>
-      </c>
-      <c r="C1373" t="inlineStr">
-        <is>
-          <t>7702605101498</t>
-        </is>
-      </c>
+          <t>Hylo Gel</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr"/>
       <c r="D1373" t="inlineStr"/>
       <c r="E1373" t="n">
-        <v>4400</v>
+        <v>131600</v>
       </c>
       <c r="F1373" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="G1373" t="n">
         <v>0</v>
@@ -73632,25 +73628,25 @@
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>Ibuprofeno 800mg AG</t>
+          <t>IBUPROFENO 400MG/ GENFAR</t>
         </is>
       </c>
       <c r="C1374" t="inlineStr">
         <is>
-          <t>7706569000385</t>
+          <t>7702605101498</t>
         </is>
       </c>
       <c r="D1374" t="inlineStr"/>
       <c r="E1374" t="n">
-        <v>800</v>
+        <v>4400</v>
       </c>
       <c r="F1374" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G1374" t="n">
         <v>0</v>
@@ -73686,25 +73682,25 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
+          <t>Ibuprofeno 800mg AG</t>
         </is>
       </c>
       <c r="C1375" t="inlineStr">
         <is>
-          <t>7705959885229</t>
+          <t>7706569000385</t>
         </is>
       </c>
       <c r="D1375" t="inlineStr"/>
       <c r="E1375" t="n">
-        <v>17900</v>
+        <v>800</v>
       </c>
       <c r="F1375" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1375" t="n">
         <v>0</v>
@@ -73740,22 +73736,22 @@
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>ICE POWER 30 GR GEL COSMETICA</t>
+          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
         </is>
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>737186238889</t>
+          <t>7705959885229</t>
         </is>
       </c>
       <c r="D1376" t="inlineStr"/>
       <c r="E1376" t="n">
-        <v>12521.008403</v>
+        <v>17900</v>
       </c>
       <c r="F1376" t="n">
         <v>2</v>
@@ -73786,7 +73782,7 @@
       </c>
       <c r="M1376" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1376" t="inlineStr"/>
@@ -73794,21 +73790,25 @@
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
-        </is>
-      </c>
-      <c r="C1377" t="inlineStr"/>
+          <t>ICE POWER 30 GR GEL COSMETICA</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>737186238889</t>
+        </is>
+      </c>
       <c r="D1377" t="inlineStr"/>
       <c r="E1377" t="n">
-        <v>38900</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1377" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1377" t="n">
         <v>0</v>
@@ -73836,7 +73836,7 @@
       </c>
       <c r="M1377" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1377" t="inlineStr"/>
@@ -73844,12 +73844,12 @@
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
+          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
         </is>
       </c>
       <c r="C1378" t="inlineStr"/>
@@ -73894,21 +73894,21 @@
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
+          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
         </is>
       </c>
       <c r="C1379" t="inlineStr"/>
       <c r="D1379" t="inlineStr"/>
       <c r="E1379" t="n">
-        <v>8235.294118</v>
+        <v>38900</v>
       </c>
       <c r="F1379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1379" t="n">
         <v>0</v>
@@ -73936,7 +73936,7 @@
       </c>
       <c r="M1379" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1379" t="inlineStr"/>
@@ -73944,21 +73944,21 @@
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
+          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
         </is>
       </c>
       <c r="C1380" t="inlineStr"/>
       <c r="D1380" t="inlineStr"/>
       <c r="E1380" t="n">
-        <v>9831.932773</v>
+        <v>8235.294118</v>
       </c>
       <c r="F1380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1380" t="n">
         <v>0</v>
@@ -73994,21 +73994,21 @@
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
+          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
         </is>
       </c>
       <c r="C1381" t="inlineStr"/>
       <c r="D1381" t="inlineStr"/>
       <c r="E1381" t="n">
-        <v>4201.680672</v>
+        <v>9831.932773</v>
       </c>
       <c r="F1381" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1381" t="n">
         <v>0</v>
@@ -74044,12 +74044,12 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
+          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
         </is>
       </c>
       <c r="C1382" t="inlineStr"/>
@@ -74058,7 +74058,7 @@
         <v>4201.680672</v>
       </c>
       <c r="F1382" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1382" t="n">
         <v>0</v>
@@ -74094,18 +74094,18 @@
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>JABON PROTEX HERBAL 110GR</t>
+          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
         </is>
       </c>
       <c r="C1383" t="inlineStr"/>
       <c r="D1383" t="inlineStr"/>
       <c r="E1383" t="n">
-        <v>4537.815126</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1383" t="n">
         <v>2</v>
@@ -74144,22 +74144,18 @@
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>JARABE ZETYGRIP FCO 60ML</t>
-        </is>
-      </c>
-      <c r="C1384" t="inlineStr">
-        <is>
-          <t>7709805542830</t>
-        </is>
-      </c>
+          <t>JABON PROTEX HERBAL 110GR</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr"/>
       <c r="D1384" t="inlineStr"/>
       <c r="E1384" t="n">
-        <v>14000</v>
+        <v>4537.815126</v>
       </c>
       <c r="F1384" t="n">
         <v>2</v>
@@ -74190,7 +74186,7 @@
       </c>
       <c r="M1384" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1384" t="inlineStr"/>
@@ -74198,21 +74194,25 @@
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>JERINGA DE 50ML</t>
-        </is>
-      </c>
-      <c r="C1385" t="inlineStr"/>
+          <t>JARABE ZETYGRIP FCO 60ML</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>7709805542830</t>
+        </is>
+      </c>
       <c r="D1385" t="inlineStr"/>
       <c r="E1385" t="n">
-        <v>2500</v>
+        <v>14000</v>
       </c>
       <c r="F1385" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1385" t="n">
         <v>0</v>
@@ -74248,21 +74248,21 @@
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>Jeringa desechable estéril 20ml impormedicas</t>
+          <t>JERINGA DE 50ML</t>
         </is>
       </c>
       <c r="C1386" t="inlineStr"/>
       <c r="D1386" t="inlineStr"/>
       <c r="E1386" t="n">
-        <v>920</v>
+        <v>2500</v>
       </c>
       <c r="F1386" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G1386" t="n">
         <v>0</v>
@@ -74290,7 +74290,7 @@
       </c>
       <c r="M1386" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1386" t="inlineStr"/>
@@ -74298,21 +74298,21 @@
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
+          <t>Jeringa desechable estéril 20ml impormedicas</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr"/>
       <c r="D1387" t="inlineStr"/>
       <c r="E1387" t="n">
-        <v>1100</v>
+        <v>920</v>
       </c>
       <c r="F1387" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="G1387" t="n">
         <v>0</v>
@@ -74340,7 +74340,7 @@
       </c>
       <c r="M1387" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1387" t="inlineStr"/>
@@ -74348,21 +74348,21 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>Kelocate</t>
+          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
         </is>
       </c>
       <c r="C1388" t="inlineStr"/>
       <c r="D1388" t="inlineStr"/>
       <c r="E1388" t="n">
-        <v>180000</v>
+        <v>1100</v>
       </c>
       <c r="F1388" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G1388" t="n">
         <v>0</v>
@@ -74398,22 +74398,18 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
-        </is>
-      </c>
-      <c r="C1389" t="inlineStr">
-        <is>
-          <t>7702057073695</t>
-        </is>
-      </c>
+          <t>Kelocate</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr"/>
       <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="n">
-        <v>19500</v>
+        <v>180000</v>
       </c>
       <c r="F1389" t="n">
         <v>0</v>
@@ -74452,22 +74448,22 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
+          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
         </is>
       </c>
       <c r="C1390" t="inlineStr">
         <is>
-          <t>7709947559772</t>
+          <t>7702057073695</t>
         </is>
       </c>
       <c r="D1390" t="inlineStr"/>
       <c r="E1390" t="n">
-        <v>15000</v>
+        <v>19500</v>
       </c>
       <c r="F1390" t="n">
         <v>0</v>
@@ -74506,18 +74502,22 @@
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
-        </is>
-      </c>
-      <c r="C1391" t="inlineStr"/>
+          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>7709947559772</t>
+        </is>
+      </c>
       <c r="D1391" t="inlineStr"/>
       <c r="E1391" t="n">
-        <v>71000</v>
+        <v>15000</v>
       </c>
       <c r="F1391" t="n">
         <v>0</v>
@@ -74556,25 +74556,21 @@
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>Levotiroxina 100mcg MK</t>
-        </is>
-      </c>
-      <c r="C1392" t="inlineStr">
-        <is>
-          <t>7702057715908</t>
-        </is>
-      </c>
+          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr"/>
       <c r="D1392" t="inlineStr"/>
       <c r="E1392" t="n">
-        <v>27900</v>
+        <v>71000</v>
       </c>
       <c r="F1392" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1392" t="n">
         <v>0</v>
@@ -74610,21 +74606,25 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>LIMA MAYOMI 10/180</t>
-        </is>
-      </c>
-      <c r="C1393" t="inlineStr"/>
+          <t>Levotiroxina 100mcg MK</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>7702057715908</t>
+        </is>
+      </c>
       <c r="D1393" t="inlineStr"/>
       <c r="E1393" t="n">
-        <v>3900</v>
+        <v>27900</v>
       </c>
       <c r="F1393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1393" t="n">
         <v>0</v>
@@ -74660,21 +74660,21 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
+          <t>LIMA MAYOMI 10/180</t>
         </is>
       </c>
       <c r="C1394" t="inlineStr"/>
       <c r="D1394" t="inlineStr"/>
       <c r="E1394" t="n">
-        <v>16807</v>
+        <v>3900</v>
       </c>
       <c r="F1394" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1394" t="n">
         <v>0</v>
@@ -74702,7 +74702,7 @@
       </c>
       <c r="M1394" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1394" t="inlineStr"/>
@@ -74710,21 +74710,21 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
+          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
         </is>
       </c>
       <c r="C1395" t="inlineStr"/>
       <c r="D1395" t="inlineStr"/>
       <c r="E1395" t="n">
-        <v>15042.016807</v>
+        <v>16807</v>
       </c>
       <c r="F1395" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1395" t="n">
         <v>0</v>
@@ -74760,21 +74760,21 @@
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>LISTERINE CUIDADO TOTAL 180ML</t>
+          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
         </is>
       </c>
       <c r="C1396" t="inlineStr"/>
       <c r="D1396" t="inlineStr"/>
       <c r="E1396" t="n">
-        <v>16386.554622</v>
+        <v>15042.016807</v>
       </c>
       <c r="F1396" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1396" t="n">
         <v>0</v>
@@ -74810,21 +74810,21 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
+          <t>LISTERINE CUIDADO TOTAL 180ML</t>
         </is>
       </c>
       <c r="C1397" t="inlineStr"/>
       <c r="D1397" t="inlineStr"/>
       <c r="E1397" t="n">
-        <v>3500</v>
+        <v>16386.554622</v>
       </c>
       <c r="F1397" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G1397" t="n">
         <v>0</v>
@@ -74852,7 +74852,7 @@
       </c>
       <c r="M1397" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1397" t="inlineStr"/>
@@ -74860,12 +74860,12 @@
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
         </is>
       </c>
       <c r="C1398" t="inlineStr"/>
@@ -74874,7 +74874,7 @@
         <v>3500</v>
       </c>
       <c r="F1398" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G1398" t="n">
         <v>0</v>
@@ -74910,21 +74910,21 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
         </is>
       </c>
       <c r="C1399" t="inlineStr"/>
       <c r="D1399" t="inlineStr"/>
       <c r="E1399" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="F1399" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1399" t="n">
         <v>0</v>
@@ -74960,25 +74960,21 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>Losartan Tensofar 100 Mg</t>
-        </is>
-      </c>
-      <c r="C1400" t="inlineStr">
-        <is>
-          <t>7703546012119</t>
-        </is>
-      </c>
+          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr"/>
       <c r="D1400" t="inlineStr"/>
       <c r="E1400" t="n">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="F1400" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1400" t="n">
         <v>0</v>
@@ -75014,25 +75010,25 @@
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+          <t>Losartan Tensofar 100 Mg</t>
         </is>
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>7501007528939</t>
+          <t>7703546012119</t>
         </is>
       </c>
       <c r="D1401" t="inlineStr"/>
       <c r="E1401" t="n">
-        <v>18907.563025</v>
+        <v>5000</v>
       </c>
       <c r="F1401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1401" t="n">
         <v>0</v>
@@ -75060,7 +75056,7 @@
       </c>
       <c r="M1401" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1401" t="inlineStr"/>
@@ -75068,18 +75064,22 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>MANTECA DE CACAO LABIAL LIMON</t>
-        </is>
-      </c>
-      <c r="C1402" t="inlineStr"/>
+          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>7501007528939</t>
+        </is>
+      </c>
       <c r="D1402" t="inlineStr"/>
       <c r="E1402" t="n">
-        <v>3361.344538</v>
+        <v>18907.563025</v>
       </c>
       <c r="F1402" t="n">
         <v>0</v>
@@ -75118,12 +75118,12 @@
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
+          <t>MANTECA DE CACAO LABIAL LIMON</t>
         </is>
       </c>
       <c r="C1403" t="inlineStr"/>
@@ -75168,21 +75168,21 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>Mega sex</t>
+          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
         </is>
       </c>
       <c r="C1404" t="inlineStr"/>
       <c r="D1404" t="inlineStr"/>
       <c r="E1404" t="n">
-        <v>3200</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1404" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G1404" t="n">
         <v>0</v>
@@ -75210,7 +75210,7 @@
       </c>
       <c r="M1404" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1404" t="inlineStr"/>
@@ -75218,29 +75218,21 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>Melatonina 3mg</t>
-        </is>
-      </c>
-      <c r="C1405" t="inlineStr">
-        <is>
-          <t>7706849112906</t>
-        </is>
-      </c>
-      <c r="D1405" t="inlineStr">
-        <is>
-          <t>producto nuevo</t>
-        </is>
-      </c>
+          <t>Mega sex</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr"/>
+      <c r="D1405" t="inlineStr"/>
       <c r="E1405" t="n">
-        <v>52000</v>
+        <v>3200</v>
       </c>
       <c r="F1405" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G1405" t="n">
         <v>0</v>
@@ -75276,22 +75268,26 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
+          <t>Melatonina 3mg</t>
         </is>
       </c>
       <c r="C1406" t="inlineStr">
         <is>
-          <t>7707529435209</t>
-        </is>
-      </c>
-      <c r="D1406" t="inlineStr"/>
+          <t>7706849112906</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>producto nuevo</t>
+        </is>
+      </c>
       <c r="E1406" t="n">
-        <v>36000</v>
+        <v>52000</v>
       </c>
       <c r="F1406" t="n">
         <v>0</v>
@@ -75330,22 +75326,22 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>Meloxicam 15mg AG</t>
+          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
         </is>
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>7706569020437</t>
+          <t>7707529435209</t>
         </is>
       </c>
       <c r="D1407" t="inlineStr"/>
       <c r="E1407" t="n">
-        <v>1500</v>
+        <v>36000</v>
       </c>
       <c r="F1407" t="n">
         <v>0</v>
@@ -75384,21 +75380,25 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
-        </is>
-      </c>
-      <c r="C1408" t="inlineStr"/>
+          <t>Meloxicam 15mg AG</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>7706569020437</t>
+        </is>
+      </c>
       <c r="D1408" t="inlineStr"/>
       <c r="E1408" t="n">
-        <v>9700</v>
+        <v>1500</v>
       </c>
       <c r="F1408" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1408" t="n">
         <v>0</v>
@@ -75434,25 +75434,21 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>MELOXICAM COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1409" t="inlineStr">
-        <is>
-          <t>7703712036253</t>
-        </is>
-      </c>
+          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr"/>
       <c r="D1409" t="inlineStr"/>
       <c r="E1409" t="n">
-        <v>1300</v>
+        <v>9700</v>
       </c>
       <c r="F1409" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1409" t="n">
         <v>0</v>
@@ -75478,31 +75474,35 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1409" t="inlineStr"/>
+      <c r="M1409" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1409" t="inlineStr"/>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>metformina 850 mg pisa</t>
+          <t>MELOXICAM COASPHARMA</t>
         </is>
       </c>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>7501125188039</t>
+          <t>7703712036253</t>
         </is>
       </c>
       <c r="D1410" t="inlineStr"/>
       <c r="E1410" t="n">
-        <v>5500</v>
+        <v>1300</v>
       </c>
       <c r="F1410" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G1410" t="n">
         <v>0</v>
@@ -75528,35 +75528,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1410" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1410" t="inlineStr"/>
       <c r="N1410" t="inlineStr"/>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10MG RECIPE</t>
+          <t>metformina 850 mg pisa</t>
         </is>
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>7702195084355</t>
+          <t>7501125188039</t>
         </is>
       </c>
       <c r="D1411" t="inlineStr"/>
       <c r="E1411" t="n">
-        <v>1000</v>
+        <v>5500</v>
       </c>
       <c r="F1411" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G1411" t="n">
         <v>0</v>
@@ -75592,25 +75588,25 @@
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>MICROPOR 1X3 Y</t>
+          <t>METOCLOPRAMIDA 10MG RECIPE</t>
         </is>
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>7707282990205</t>
+          <t>7702195084355</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr"/>
       <c r="E1412" t="n">
-        <v>5300</v>
+        <v>1000</v>
       </c>
       <c r="F1412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1412" t="n">
         <v>0</v>
@@ -75646,25 +75642,25 @@
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>MICROPOR CINTA 1/2X5Y</t>
+          <t>MICROPOR 1X3 Y</t>
         </is>
       </c>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>7707282990182</t>
+          <t>7707282990205</t>
         </is>
       </c>
       <c r="D1413" t="inlineStr"/>
       <c r="E1413" t="n">
-        <v>3900</v>
+        <v>5300</v>
       </c>
       <c r="F1413" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G1413" t="n">
         <v>0</v>
@@ -75700,21 +75696,25 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>MICROPORE COLOR PIEL 2YARDAS</t>
-        </is>
-      </c>
-      <c r="C1414" t="inlineStr"/>
+          <t>MICROPOR CINTA 1/2X5Y</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>7707282990182</t>
+        </is>
+      </c>
       <c r="D1414" t="inlineStr"/>
       <c r="E1414" t="n">
-        <v>3700</v>
+        <v>3900</v>
       </c>
       <c r="F1414" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G1414" t="n">
         <v>0</v>
@@ -75750,18 +75750,18 @@
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
+          <t>MICROPORE COLOR PIEL 2YARDAS</t>
         </is>
       </c>
       <c r="C1415" t="inlineStr"/>
       <c r="D1415" t="inlineStr"/>
       <c r="E1415" t="n">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="F1415" t="n">
         <v>0</v>
@@ -75800,22 +75800,18 @@
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>MIELTERTOS JARABE X 240ML</t>
-        </is>
-      </c>
-      <c r="C1416" t="inlineStr">
-        <is>
-          <t>7707232095608</t>
-        </is>
-      </c>
+          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr"/>
       <c r="D1416" t="inlineStr"/>
       <c r="E1416" t="n">
-        <v>34500</v>
+        <v>4000</v>
       </c>
       <c r="F1416" t="n">
         <v>0</v>
@@ -75854,25 +75850,25 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
-        </is>
-      </c>
-      <c r="C1417" t="inlineStr"/>
-      <c r="D1417" t="inlineStr">
-        <is>
-          <t>subio precio hector</t>
-        </is>
-      </c>
+          <t>MIELTERTOS JARABE X 240ML</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>7707232095608</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr"/>
       <c r="E1417" t="n">
-        <v>22700</v>
+        <v>34500</v>
       </c>
       <c r="F1417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1417" t="n">
         <v>0</v>
@@ -75908,21 +75904,25 @@
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
+          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
         </is>
       </c>
       <c r="C1418" t="inlineStr"/>
-      <c r="D1418" t="inlineStr"/>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>subio precio hector</t>
+        </is>
+      </c>
       <c r="E1418" t="n">
-        <v>5500</v>
+        <v>22700</v>
       </c>
       <c r="F1418" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G1418" t="n">
         <v>0</v>
@@ -75958,21 +75958,21 @@
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>NEOSALDINA TABLETA X UND</t>
+          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
         </is>
       </c>
       <c r="C1419" t="inlineStr"/>
       <c r="D1419" t="inlineStr"/>
       <c r="E1419" t="n">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="F1419" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1419" t="n">
         <v>0</v>
@@ -76008,21 +76008,21 @@
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>NIFEDIPINO 30MG NOVAMED</t>
+          <t>NEOSALDINA TABLETA X UND</t>
         </is>
       </c>
       <c r="C1420" t="inlineStr"/>
       <c r="D1420" t="inlineStr"/>
       <c r="E1420" t="n">
-        <v>19000</v>
+        <v>2500</v>
       </c>
       <c r="F1420" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G1420" t="n">
         <v>0</v>
@@ -76058,21 +76058,21 @@
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
+          <t>NIFEDIPINO 30MG NOVAMED</t>
         </is>
       </c>
       <c r="C1421" t="inlineStr"/>
       <c r="D1421" t="inlineStr"/>
       <c r="E1421" t="n">
-        <v>23000</v>
+        <v>19000</v>
       </c>
       <c r="F1421" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1421" t="n">
         <v>0</v>
@@ -76108,21 +76108,21 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>NITOXIPAR X 6 TABLETAS</t>
+          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
         </is>
       </c>
       <c r="C1422" t="inlineStr"/>
       <c r="D1422" t="inlineStr"/>
       <c r="E1422" t="n">
-        <v>24500</v>
+        <v>23000</v>
       </c>
       <c r="F1422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1422" t="n">
         <v>0</v>
@@ -76158,21 +76158,21 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>NORAVER SPRAY CEREZA 120ML</t>
+          <t>NITOXIPAR X 6 TABLETAS</t>
         </is>
       </c>
       <c r="C1423" t="inlineStr"/>
       <c r="D1423" t="inlineStr"/>
       <c r="E1423" t="n">
-        <v>52900</v>
+        <v>24500</v>
       </c>
       <c r="F1423" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1423" t="n">
         <v>0</v>
@@ -76208,25 +76208,21 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
-        </is>
-      </c>
-      <c r="C1424" t="inlineStr">
-        <is>
-          <t>7702027041662</t>
-        </is>
-      </c>
+          <t>NORAVER SPRAY CEREZA 120ML</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr"/>
       <c r="D1424" t="inlineStr"/>
       <c r="E1424" t="n">
-        <v>6300</v>
+        <v>52900</v>
       </c>
       <c r="F1424" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1424" t="n">
         <v>0</v>
@@ -76262,18 +76258,22 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
-        </is>
-      </c>
-      <c r="C1425" t="inlineStr"/>
+          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>7702027041662</t>
+        </is>
+      </c>
       <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="n">
-        <v>8823.529412</v>
+        <v>6300</v>
       </c>
       <c r="F1425" t="n">
         <v>0</v>
@@ -76304,7 +76304,7 @@
       </c>
       <c r="M1425" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1425" t="inlineStr"/>
@@ -76312,7 +76312,7 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
@@ -76320,11 +76320,7 @@
           <t>NOSOTRAS JABON INTIMO X 200ML</t>
         </is>
       </c>
-      <c r="C1426" t="inlineStr">
-        <is>
-          <t>7702026158644</t>
-        </is>
-      </c>
+      <c r="C1426" t="inlineStr"/>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="n">
         <v>8823.529412</v>
@@ -76366,25 +76362,25 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JBE 120ML</t>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
         </is>
       </c>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>7707355053363</t>
+          <t>7702026158644</t>
         </is>
       </c>
       <c r="D1427" t="inlineStr"/>
       <c r="E1427" t="n">
-        <v>22700</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1427" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1427" t="n">
         <v>0</v>
@@ -76412,7 +76408,7 @@
       </c>
       <c r="M1427" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1427" t="inlineStr"/>
@@ -76420,25 +76416,25 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+          <t>NOXPIRIN JUNIOR JBE 120ML</t>
         </is>
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>7707355053356</t>
+          <t>7707355053363</t>
         </is>
       </c>
       <c r="D1428" t="inlineStr"/>
       <c r="E1428" t="n">
-        <v>17200</v>
+        <v>22700</v>
       </c>
       <c r="F1428" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1428" t="n">
         <v>0</v>
@@ -76474,21 +76470,25 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>NUTRIBELL ACEITE DE COCO</t>
-        </is>
-      </c>
-      <c r="C1429" t="inlineStr"/>
+          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>7707355053356</t>
+        </is>
+      </c>
       <c r="D1429" t="inlineStr"/>
       <c r="E1429" t="n">
-        <v>2700</v>
+        <v>17200</v>
       </c>
       <c r="F1429" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1429" t="n">
         <v>0</v>
@@ -76524,29 +76524,21 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Omega 3 6 9 suplemento totalmax</t>
-        </is>
-      </c>
-      <c r="C1430" t="inlineStr">
-        <is>
-          <t>7707529434974</t>
-        </is>
-      </c>
-      <c r="D1430" t="inlineStr">
-        <is>
-          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
-        </is>
-      </c>
+          <t>NUTRIBELL ACEITE DE COCO</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr"/>
+      <c r="D1430" t="inlineStr"/>
       <c r="E1430" t="n">
-        <v>35000</v>
+        <v>2700</v>
       </c>
       <c r="F1430" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1430" t="n">
         <v>0</v>
@@ -76582,21 +76574,29 @@
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1431" t="inlineStr"/>
-      <c r="D1431" t="inlineStr"/>
+          <t>Omega 3 6 9 suplemento totalmax</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>7707529434974</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
+        </is>
+      </c>
       <c r="E1431" t="n">
-        <v>5500</v>
+        <v>35000</v>
       </c>
       <c r="F1431" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1431" t="n">
         <v>0</v>
@@ -76632,22 +76632,18 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
-        </is>
-      </c>
-      <c r="C1432" t="inlineStr">
-        <is>
-          <t>7707529435940</t>
-        </is>
-      </c>
+          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr"/>
       <c r="D1432" t="inlineStr"/>
       <c r="E1432" t="n">
-        <v>35000</v>
+        <v>5500</v>
       </c>
       <c r="F1432" t="n">
         <v>0</v>
@@ -76686,21 +76682,25 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
-        </is>
-      </c>
-      <c r="C1433" t="inlineStr"/>
+          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>7707529435940</t>
+        </is>
+      </c>
       <c r="D1433" t="inlineStr"/>
       <c r="E1433" t="n">
-        <v>48000</v>
+        <v>35000</v>
       </c>
       <c r="F1433" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1433" t="n">
         <v>0</v>
@@ -76736,25 +76736,21 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>OROCAL CALCIO 600MG</t>
+          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
         </is>
       </c>
       <c r="C1434" t="inlineStr"/>
-      <c r="D1434" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="D1434" t="inlineStr"/>
       <c r="E1434" t="n">
-        <v>30500</v>
+        <v>48000</v>
       </c>
       <c r="F1434" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1434" t="n">
         <v>0</v>
@@ -76790,18 +76786,22 @@
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>PALA DE MADERA RASPACALLO</t>
+          <t>OROCAL CALCIO 600MG</t>
         </is>
       </c>
       <c r="C1435" t="inlineStr"/>
-      <c r="D1435" t="inlineStr"/>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E1435" t="n">
-        <v>4000</v>
+        <v>30500</v>
       </c>
       <c r="F1435" t="n">
         <v>1</v>
@@ -76840,21 +76840,21 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>PALO DE NARANJO X UNIDAD</t>
+          <t>PALA DE MADERA RASPACALLO</t>
         </is>
       </c>
       <c r="C1436" t="inlineStr"/>
       <c r="D1436" t="inlineStr"/>
       <c r="E1436" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="F1436" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G1436" t="n">
         <v>0</v>
@@ -76890,25 +76890,21 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
-        </is>
-      </c>
-      <c r="C1437" t="inlineStr">
-        <is>
-          <t>7704412170896</t>
-        </is>
-      </c>
+          <t>PALO DE NARANJO X UNIDAD</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr"/>
       <c r="D1437" t="inlineStr"/>
       <c r="E1437" t="n">
-        <v>6200</v>
+        <v>400</v>
       </c>
       <c r="F1437" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G1437" t="n">
         <v>0</v>
@@ -76944,18 +76940,22 @@
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
-        </is>
-      </c>
-      <c r="C1438" t="inlineStr"/>
+          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>7704412170896</t>
+        </is>
+      </c>
       <c r="D1438" t="inlineStr"/>
       <c r="E1438" t="n">
-        <v>14285.714286</v>
+        <v>6200</v>
       </c>
       <c r="F1438" t="n">
         <v>1</v>
@@ -76986,7 +76986,7 @@
       </c>
       <c r="M1438" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1438" t="inlineStr"/>
@@ -76994,18 +76994,18 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
+          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
         </is>
       </c>
       <c r="C1439" t="inlineStr"/>
       <c r="D1439" t="inlineStr"/>
       <c r="E1439" t="n">
-        <v>28991.596639</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1439" t="n">
         <v>1</v>
@@ -77044,18 +77044,18 @@
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
         </is>
       </c>
       <c r="C1440" t="inlineStr"/>
       <c r="D1440" t="inlineStr"/>
       <c r="E1440" t="n">
-        <v>41176.470588</v>
+        <v>28991.596639</v>
       </c>
       <c r="F1440" t="n">
         <v>1</v>
@@ -77094,22 +77094,18 @@
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>Pañales Winny Etapa 5 X PAQUETE</t>
-        </is>
-      </c>
-      <c r="C1441" t="inlineStr">
-        <is>
-          <t>7701021114174</t>
-        </is>
-      </c>
+          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr"/>
       <c r="D1441" t="inlineStr"/>
       <c r="E1441" t="n">
-        <v>41849</v>
+        <v>41176.470588</v>
       </c>
       <c r="F1441" t="n">
         <v>1</v>
@@ -77148,21 +77144,25 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>PAÑALWINNY ETA 5 X 16 UND</t>
-        </is>
-      </c>
-      <c r="C1442" t="inlineStr"/>
+          <t>Pañales Winny Etapa 5 X PAQUETE</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>7701021114174</t>
+        </is>
+      </c>
       <c r="D1442" t="inlineStr"/>
       <c r="E1442" t="n">
-        <v>24369.747899</v>
+        <v>41849</v>
       </c>
       <c r="F1442" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1442" t="n">
         <v>0</v>
@@ -77198,21 +77198,21 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>pañitos humedos pequeñin 100unidades</t>
+          <t>PAÑALWINNY ETA 5 X 16 UND</t>
         </is>
       </c>
       <c r="C1443" t="inlineStr"/>
       <c r="D1443" t="inlineStr"/>
       <c r="E1443" t="n">
-        <v>10925</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1443" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1443" t="n">
         <v>0</v>
@@ -77248,21 +77248,21 @@
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
+          <t>pañitos humedos pequeñin 100unidades</t>
         </is>
       </c>
       <c r="C1444" t="inlineStr"/>
       <c r="D1444" t="inlineStr"/>
       <c r="E1444" t="n">
-        <v>14900</v>
+        <v>10925</v>
       </c>
       <c r="F1444" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1444" t="n">
         <v>0</v>
@@ -77290,7 +77290,7 @@
       </c>
       <c r="M1444" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1444" t="inlineStr"/>
@@ -77298,21 +77298,21 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>Panotil B x 8ML</t>
+          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
         </is>
       </c>
       <c r="C1445" t="inlineStr"/>
       <c r="D1445" t="inlineStr"/>
       <c r="E1445" t="n">
-        <v>26400</v>
+        <v>14900</v>
       </c>
       <c r="F1445" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1445" t="n">
         <v>0</v>
@@ -77348,25 +77348,21 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>PANTENE ACONDICIONADOR</t>
-        </is>
-      </c>
-      <c r="C1446" t="inlineStr">
-        <is>
-          <t>7500435153683</t>
-        </is>
-      </c>
+          <t>Panotil B x 8ML</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr"/>
       <c r="D1446" t="inlineStr"/>
       <c r="E1446" t="n">
-        <v>1500</v>
+        <v>26400</v>
       </c>
       <c r="F1446" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1446" t="n">
         <v>0</v>
@@ -77402,21 +77398,25 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Parche Ocular Colostol</t>
-        </is>
-      </c>
-      <c r="C1447" t="inlineStr"/>
+          <t>PANTENE ACONDICIONADOR</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>7500435153683</t>
+        </is>
+      </c>
       <c r="D1447" t="inlineStr"/>
       <c r="E1447" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F1447" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G1447" t="n">
         <v>0</v>
@@ -77452,25 +77452,21 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
-        </is>
-      </c>
-      <c r="C1448" t="inlineStr">
-        <is>
-          <t>7501033957413</t>
-        </is>
-      </c>
+          <t>Parche Ocular Colostol</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr"/>
       <c r="D1448" t="inlineStr"/>
       <c r="E1448" t="n">
-        <v>10600</v>
+        <v>1300</v>
       </c>
       <c r="F1448" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G1448" t="n">
         <v>0</v>
@@ -77506,26 +77502,22 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
+          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
         </is>
       </c>
       <c r="C1449" t="inlineStr">
         <is>
-          <t>7501033961557</t>
-        </is>
-      </c>
-      <c r="D1449" t="inlineStr">
-        <is>
-          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
-        </is>
-      </c>
+          <t>7501033957413</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr"/>
       <c r="E1449" t="n">
-        <v>10900</v>
+        <v>10600</v>
       </c>
       <c r="F1449" t="n">
         <v>0</v>
@@ -77564,29 +77556,29 @@
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
         </is>
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>7501033957376</t>
+          <t>7501033961557</t>
         </is>
       </c>
       <c r="D1450" t="inlineStr">
         <is>
-          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
         </is>
       </c>
       <c r="E1450" t="n">
         <v>10900</v>
       </c>
       <c r="F1450" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1450" t="n">
         <v>0</v>
@@ -77622,21 +77614,29 @@
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>PEGANTE GLUE X 10GR X UND</t>
-        </is>
-      </c>
-      <c r="C1451" t="inlineStr"/>
-      <c r="D1451" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>7501033957376</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+        </is>
+      </c>
       <c r="E1451" t="n">
-        <v>2000</v>
+        <v>10900</v>
       </c>
       <c r="F1451" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1451" t="n">
         <v>0</v>
@@ -77672,21 +77672,21 @@
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>PEINETA COLA DE RATON METALICA</t>
+          <t>PEGANTE GLUE X 10GR X UND</t>
         </is>
       </c>
       <c r="C1452" t="inlineStr"/>
       <c r="D1452" t="inlineStr"/>
       <c r="E1452" t="n">
-        <v>4700</v>
+        <v>2000</v>
       </c>
       <c r="F1452" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1452" t="n">
         <v>0</v>
@@ -77722,18 +77722,18 @@
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>PERFILADORES DE CEJAS</t>
+          <t>PEINETA COLA DE RATON METALICA</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr"/>
       <c r="D1453" t="inlineStr"/>
       <c r="E1453" t="n">
-        <v>3900</v>
+        <v>4700</v>
       </c>
       <c r="F1453" t="n">
         <v>1</v>
@@ -77772,18 +77772,18 @@
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
+          <t>PERFILADORES DE CEJAS</t>
         </is>
       </c>
       <c r="C1454" t="inlineStr"/>
       <c r="D1454" t="inlineStr"/>
       <c r="E1454" t="n">
-        <v>27983.193277</v>
+        <v>3900</v>
       </c>
       <c r="F1454" t="n">
         <v>1</v>
@@ -77814,7 +77814,7 @@
       </c>
       <c r="M1454" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1454" t="inlineStr"/>
@@ -77822,21 +77822,21 @@
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>POPETAS SURTIDAS X UND</t>
+          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
         </is>
       </c>
       <c r="C1455" t="inlineStr"/>
       <c r="D1455" t="inlineStr"/>
       <c r="E1455" t="n">
-        <v>2521.008403</v>
+        <v>27983.193277</v>
       </c>
       <c r="F1455" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1455" t="n">
         <v>0</v>
@@ -77872,21 +77872,21 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+          <t>POPETAS SURTIDAS X UND</t>
         </is>
       </c>
       <c r="C1456" t="inlineStr"/>
       <c r="D1456" t="inlineStr"/>
       <c r="E1456" t="n">
-        <v>20500</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1456" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1456" t="n">
         <v>0</v>
@@ -77914,7 +77914,7 @@
       </c>
       <c r="M1456" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1456" t="inlineStr"/>
@@ -77922,26 +77922,18 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>privatos miel limon la francol 120ml</t>
-        </is>
-      </c>
-      <c r="C1457" t="inlineStr">
-        <is>
-          <t>7702207163948</t>
-        </is>
-      </c>
-      <c r="D1457" t="inlineStr">
-        <is>
-          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
-        </is>
-      </c>
+          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr"/>
+      <c r="D1457" t="inlineStr"/>
       <c r="E1457" t="n">
-        <v>35900</v>
+        <v>20500</v>
       </c>
       <c r="F1457" t="n">
         <v>0</v>
@@ -77980,21 +77972,29 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
-        </is>
-      </c>
-      <c r="C1458" t="inlineStr"/>
-      <c r="D1458" t="inlineStr"/>
+          <t>privatos miel limon la francol 120ml</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>7702207163948</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
+        </is>
+      </c>
       <c r="E1458" t="n">
-        <v>0</v>
+        <v>35900</v>
       </c>
       <c r="F1458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1458" t="n">
         <v>0</v>
@@ -78022,7 +78022,7 @@
       </c>
       <c r="M1458" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1458" t="inlineStr"/>
@@ -78030,21 +78030,21 @@
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>778</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>PROTECTOR NOSOTRAS LARGOS</t>
+          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
         </is>
       </c>
       <c r="C1459" t="inlineStr"/>
       <c r="D1459" t="inlineStr"/>
       <c r="E1459" t="n">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="F1459" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1459" t="n">
         <v>0</v>
@@ -78072,7 +78072,7 @@
       </c>
       <c r="M1459" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1459" t="inlineStr"/>
@@ -78080,18 +78080,18 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
+          <t>PROTECTOR NOSOTRAS LARGOS</t>
         </is>
       </c>
       <c r="C1460" t="inlineStr"/>
       <c r="D1460" t="inlineStr"/>
       <c r="E1460" t="n">
-        <v>8900</v>
+        <v>3700</v>
       </c>
       <c r="F1460" t="n">
         <v>1</v>
@@ -78130,21 +78130,21 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>Protector Solar Sunaid</t>
+          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr"/>
       <c r="D1461" t="inlineStr"/>
       <c r="E1461" t="n">
-        <v>158000</v>
+        <v>8900</v>
       </c>
       <c r="F1461" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1461" t="n">
         <v>0</v>
@@ -78180,25 +78180,21 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Prueba de embarazo esfero</t>
-        </is>
-      </c>
-      <c r="C1462" t="inlineStr">
-        <is>
-          <t>7709299854228</t>
-        </is>
-      </c>
+          <t>Protector Solar Sunaid</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr"/>
       <c r="D1462" t="inlineStr"/>
       <c r="E1462" t="n">
-        <v>16500</v>
+        <v>158000</v>
       </c>
       <c r="F1462" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1462" t="n">
         <v>0</v>
@@ -78234,25 +78230,25 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Prueba de embarazo HCG cassette begut</t>
+          <t>Prueba de embarazo esfero</t>
         </is>
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>7707282990953</t>
+          <t>7709299854228</t>
         </is>
       </c>
       <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="n">
-        <v>8900</v>
+        <v>16500</v>
       </c>
       <c r="F1463" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1463" t="n">
         <v>0</v>
@@ -78288,21 +78284,25 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>PUSHER METALICO</t>
-        </is>
-      </c>
-      <c r="C1464" t="inlineStr"/>
+          <t>Prueba de embarazo HCG cassette begut</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>7707282990953</t>
+        </is>
+      </c>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="n">
-        <v>4300</v>
+        <v>8900</v>
       </c>
       <c r="F1464" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1464" t="n">
         <v>0</v>
@@ -78338,25 +78338,21 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>Recolector de orina granandina</t>
-        </is>
-      </c>
-      <c r="C1465" t="inlineStr">
-        <is>
-          <t>7707233050590</t>
-        </is>
-      </c>
+          <t>PUSHER METALICO</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr"/>
       <c r="D1465" t="inlineStr"/>
       <c r="E1465" t="n">
-        <v>673</v>
+        <v>4300</v>
       </c>
       <c r="F1465" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="G1465" t="n">
         <v>0</v>
@@ -78384,7 +78380,7 @@
       </c>
       <c r="M1465" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1465" t="inlineStr"/>
@@ -78392,21 +78388,25 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
-        </is>
-      </c>
-      <c r="C1466" t="inlineStr"/>
+          <t>Recolector de orina granandina</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>7707233050590</t>
+        </is>
+      </c>
       <c r="D1466" t="inlineStr"/>
       <c r="E1466" t="n">
-        <v>3820</v>
+        <v>673</v>
       </c>
       <c r="F1466" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G1466" t="n">
         <v>0</v>
@@ -78434,7 +78434,7 @@
       </c>
       <c r="M1466" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1466" t="inlineStr"/>
@@ -78442,21 +78442,21 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>RegistroManual - Registro manual</t>
+          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
         </is>
       </c>
       <c r="C1467" t="inlineStr"/>
       <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="n">
-        <v>0</v>
+        <v>3820</v>
       </c>
       <c r="F1467" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1467" t="n">
         <v>0</v>
@@ -78484,7 +78484,7 @@
       </c>
       <c r="M1467" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1467" t="inlineStr"/>
@@ -78492,21 +78492,21 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>REMOVEDOR DE ESMALTE 60CC</t>
+          <t>RegistroManual - Registro manual</t>
         </is>
       </c>
       <c r="C1468" t="inlineStr"/>
       <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="F1468" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1468" t="n">
         <v>0</v>
@@ -78534,7 +78534,7 @@
       </c>
       <c r="M1468" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1468" t="inlineStr"/>
@@ -78542,25 +78542,21 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
-        </is>
-      </c>
-      <c r="C1469" t="inlineStr">
-        <is>
-          <t>7591005981270</t>
-        </is>
-      </c>
+          <t>REMOVEDOR DE ESMALTE 60CC</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr"/>
       <c r="D1469" t="inlineStr"/>
       <c r="E1469" t="n">
-        <v>9500</v>
+        <v>3500</v>
       </c>
       <c r="F1469" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1469" t="n">
         <v>0</v>
@@ -78596,22 +78592,22 @@
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
+          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
         </is>
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>7503051868245</t>
+          <t>7591005981270</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr"/>
       <c r="E1470" t="n">
-        <v>20900</v>
+        <v>9500</v>
       </c>
       <c r="F1470" t="n">
         <v>1</v>
@@ -78650,25 +78646,25 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
         </is>
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>7702057079642</t>
+          <t>7503051868245</t>
         </is>
       </c>
       <c r="D1471" t="inlineStr"/>
       <c r="E1471" t="n">
-        <v>13000</v>
+        <v>20900</v>
       </c>
       <c r="F1471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1471" t="n">
         <v>0</v>
@@ -78704,18 +78700,22 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Ryaltris Spray Nasal 240 dosis</t>
-        </is>
-      </c>
-      <c r="C1472" t="inlineStr"/>
+          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>7702057079642</t>
+        </is>
+      </c>
       <c r="D1472" t="inlineStr"/>
       <c r="E1472" t="n">
-        <v>216400</v>
+        <v>13000</v>
       </c>
       <c r="F1472" t="n">
         <v>0</v>
@@ -78754,25 +78754,21 @@
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
-        </is>
-      </c>
-      <c r="C1473" t="inlineStr">
-        <is>
-          <t>7706849116676</t>
-        </is>
-      </c>
+          <t>Ryaltris Spray Nasal 240 dosis</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr"/>
       <c r="D1473" t="inlineStr"/>
       <c r="E1473" t="n">
-        <v>31500</v>
+        <v>216400</v>
       </c>
       <c r="F1473" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1473" t="n">
         <v>0</v>
@@ -78808,21 +78804,25 @@
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>SCOBIT PURGANTE 60GR</t>
-        </is>
-      </c>
-      <c r="C1474" t="inlineStr"/>
+          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>7706849116676</t>
+        </is>
+      </c>
       <c r="D1474" t="inlineStr"/>
       <c r="E1474" t="n">
-        <v>15238.095238</v>
+        <v>31500</v>
       </c>
       <c r="F1474" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1474" t="n">
         <v>0</v>
@@ -78850,7 +78850,7 @@
       </c>
       <c r="M1474" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1474" t="inlineStr"/>
@@ -78858,21 +78858,21 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
+          <t>SCOBIT PURGANTE 60GR</t>
         </is>
       </c>
       <c r="C1475" t="inlineStr"/>
       <c r="D1475" t="inlineStr"/>
       <c r="E1475" t="n">
-        <v>6554.621849</v>
+        <v>15238.095238</v>
       </c>
       <c r="F1475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1475" t="n">
         <v>0</v>
@@ -78900,7 +78900,7 @@
       </c>
       <c r="M1475" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1475" t="inlineStr"/>
@@ -78908,25 +78908,21 @@
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>SHAMPOO PANTENE COLAGENO</t>
-        </is>
-      </c>
-      <c r="C1476" t="inlineStr">
-        <is>
-          <t>7500435191500</t>
-        </is>
-      </c>
+          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr"/>
       <c r="D1476" t="inlineStr"/>
       <c r="E1476" t="n">
-        <v>1429</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1476" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1476" t="n">
         <v>0</v>
@@ -78962,21 +78958,25 @@
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>SILDENAFIL 50MG TQ</t>
-        </is>
-      </c>
-      <c r="C1477" t="inlineStr"/>
+          <t>SHAMPOO PANTENE COLAGENO</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>7500435191500</t>
+        </is>
+      </c>
       <c r="D1477" t="inlineStr"/>
       <c r="E1477" t="n">
-        <v>5000</v>
+        <v>1429</v>
       </c>
       <c r="F1477" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1477" t="n">
         <v>0</v>
@@ -79004,7 +79004,7 @@
       </c>
       <c r="M1477" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1477" t="inlineStr"/>
@@ -79012,25 +79012,21 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>SILIMARINA 167MG EPANAT</t>
-        </is>
-      </c>
-      <c r="C1478" t="inlineStr">
-        <is>
-          <t>7706849115921</t>
-        </is>
-      </c>
+          <t>SILDENAFIL 50MG TQ</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr"/>
       <c r="D1478" t="inlineStr"/>
       <c r="E1478" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F1478" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G1478" t="n">
         <v>0</v>
@@ -79066,21 +79062,25 @@
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>SMECTA 3GR NARANJA S/B</t>
-        </is>
-      </c>
-      <c r="C1479" t="inlineStr"/>
+          <t>SILIMARINA 167MG EPANAT</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>7706849115921</t>
+        </is>
+      </c>
       <c r="D1479" t="inlineStr"/>
       <c r="E1479" t="n">
-        <v>8900</v>
+        <v>2000</v>
       </c>
       <c r="F1479" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G1479" t="n">
         <v>0</v>
@@ -79116,21 +79116,21 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>SONDA FOLEY 2 VIAS BAL #18</t>
+          <t>SMECTA 3GR NARANJA S/B</t>
         </is>
       </c>
       <c r="C1480" t="inlineStr"/>
       <c r="D1480" t="inlineStr"/>
       <c r="E1480" t="n">
-        <v>7500</v>
+        <v>8900</v>
       </c>
       <c r="F1480" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G1480" t="n">
         <v>0</v>
@@ -79166,21 +79166,21 @@
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>SONDA NELATON #6</t>
+          <t>SONDA FOLEY 2 VIAS BAL #18</t>
         </is>
       </c>
       <c r="C1481" t="inlineStr"/>
       <c r="D1481" t="inlineStr"/>
       <c r="E1481" t="n">
-        <v>2500</v>
+        <v>7500</v>
       </c>
       <c r="F1481" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1481" t="n">
         <v>0</v>
@@ -79216,21 +79216,21 @@
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>SPRAY NASAL MOMETASONA 18ML</t>
+          <t>SONDA NELATON #6</t>
         </is>
       </c>
       <c r="C1482" t="inlineStr"/>
       <c r="D1482" t="inlineStr"/>
       <c r="E1482" t="n">
-        <v>36900</v>
+        <v>2500</v>
       </c>
       <c r="F1482" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1482" t="n">
         <v>0</v>
@@ -79266,25 +79266,21 @@
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1483" t="inlineStr">
-        <is>
-          <t>7703712035034</t>
-        </is>
-      </c>
+          <t>SPRAY NASAL MOMETASONA 18ML</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr"/>
       <c r="D1483" t="inlineStr"/>
       <c r="E1483" t="n">
-        <v>14800</v>
+        <v>36900</v>
       </c>
       <c r="F1483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1483" t="n">
         <v>0</v>
@@ -79320,21 +79316,25 @@
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
-        </is>
-      </c>
-      <c r="C1484" t="inlineStr"/>
+          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>7703712035034</t>
+        </is>
+      </c>
       <c r="D1484" t="inlineStr"/>
       <c r="E1484" t="n">
-        <v>3781.512605</v>
+        <v>14800</v>
       </c>
       <c r="F1484" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1484" t="n">
         <v>0</v>
@@ -79362,7 +79362,7 @@
       </c>
       <c r="M1484" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1484" t="inlineStr"/>
@@ -79370,21 +79370,21 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
+          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
         </is>
       </c>
       <c r="C1485" t="inlineStr"/>
       <c r="D1485" t="inlineStr"/>
       <c r="E1485" t="n">
-        <v>5210.084034</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1485" t="n">
         <v>0</v>
@@ -79420,21 +79420,21 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
+          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
         </is>
       </c>
       <c r="C1486" t="inlineStr"/>
       <c r="D1486" t="inlineStr"/>
       <c r="E1486" t="n">
-        <v>8319.327730999999</v>
+        <v>5210.084034</v>
       </c>
       <c r="F1486" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1486" t="n">
         <v>0</v>
@@ -79470,18 +79470,18 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>SULZINC SUSP X 80ML HUMAX</t>
+          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
         </is>
       </c>
       <c r="C1487" t="inlineStr"/>
       <c r="D1487" t="inlineStr"/>
       <c r="E1487" t="n">
-        <v>22400</v>
+        <v>8319.327730999999</v>
       </c>
       <c r="F1487" t="n">
         <v>1</v>
@@ -79512,7 +79512,7 @@
       </c>
       <c r="M1487" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1487" t="inlineStr"/>
@@ -79520,21 +79520,21 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>SUNDARK FPS 60 CON TAPA</t>
+          <t>SULZINC SUSP X 80ML HUMAX</t>
         </is>
       </c>
       <c r="C1488" t="inlineStr"/>
       <c r="D1488" t="inlineStr"/>
       <c r="E1488" t="n">
-        <v>3781.512605</v>
+        <v>22400</v>
       </c>
       <c r="F1488" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1488" t="n">
         <v>0</v>
@@ -79562,7 +79562,7 @@
       </c>
       <c r="M1488" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1488" t="inlineStr"/>
@@ -79570,21 +79570,21 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>Synthroid 125 mcg</t>
+          <t>SUNDARK FPS 60 CON TAPA</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr"/>
       <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="n">
-        <v>178000</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1489" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1489" t="n">
         <v>0</v>
@@ -79612,7 +79612,7 @@
       </c>
       <c r="M1489" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1489" t="inlineStr"/>
@@ -79620,25 +79620,21 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>Talco medicado Neofungina 40gm</t>
-        </is>
-      </c>
-      <c r="C1490" t="inlineStr">
-        <is>
-          <t>7706142707106</t>
-        </is>
-      </c>
+          <t>Synthroid 125 mcg</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr"/>
       <c r="D1490" t="inlineStr"/>
       <c r="E1490" t="n">
-        <v>14900</v>
+        <v>178000</v>
       </c>
       <c r="F1490" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1490" t="n">
         <v>0</v>
@@ -79674,21 +79670,25 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
-        </is>
-      </c>
-      <c r="C1491" t="inlineStr"/>
+          <t>Talco medicado Neofungina 40gm</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>7706142707106</t>
+        </is>
+      </c>
       <c r="D1491" t="inlineStr"/>
       <c r="E1491" t="n">
-        <v>13300</v>
+        <v>14900</v>
       </c>
       <c r="F1491" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1491" t="n">
         <v>0</v>
@@ -79724,21 +79724,21 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
+          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
         </is>
       </c>
       <c r="C1492" t="inlineStr"/>
       <c r="D1492" t="inlineStr"/>
       <c r="E1492" t="n">
-        <v>4874</v>
+        <v>13300</v>
       </c>
       <c r="F1492" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G1492" t="n">
         <v>0</v>
@@ -79766,7 +79766,7 @@
       </c>
       <c r="M1492" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1492" t="inlineStr"/>
@@ -79774,21 +79774,21 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
+          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
         </is>
       </c>
       <c r="C1493" t="inlineStr"/>
       <c r="D1493" t="inlineStr"/>
       <c r="E1493" t="n">
-        <v>28800</v>
+        <v>4874</v>
       </c>
       <c r="F1493" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G1493" t="n">
         <v>0</v>
@@ -79816,7 +79816,7 @@
       </c>
       <c r="M1493" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1493" t="inlineStr"/>
@@ -79824,21 +79824,21 @@
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
+          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
         </is>
       </c>
       <c r="C1494" t="inlineStr"/>
       <c r="D1494" t="inlineStr"/>
       <c r="E1494" t="n">
-        <v>11596.638655</v>
+        <v>28800</v>
       </c>
       <c r="F1494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1494" t="n">
         <v>0</v>
@@ -79866,7 +79866,7 @@
       </c>
       <c r="M1494" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1494" t="inlineStr"/>
@@ -79874,21 +79874,21 @@
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>TIJERA DE DOBLAR METALICA</t>
+          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
         </is>
       </c>
       <c r="C1495" t="inlineStr"/>
       <c r="D1495" t="inlineStr"/>
       <c r="E1495" t="n">
-        <v>3500</v>
+        <v>11596.638655</v>
       </c>
       <c r="F1495" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1495" t="n">
         <v>0</v>
@@ -79916,7 +79916,7 @@
       </c>
       <c r="M1495" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1495" t="inlineStr"/>
@@ -79924,21 +79924,21 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+          <t>TIJERA DE DOBLAR METALICA</t>
         </is>
       </c>
       <c r="C1496" t="inlineStr"/>
       <c r="D1496" t="inlineStr"/>
       <c r="E1496" t="n">
-        <v>3781.512605</v>
+        <v>3500</v>
       </c>
       <c r="F1496" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1496" t="n">
         <v>0</v>
@@ -79966,7 +79966,7 @@
       </c>
       <c r="M1496" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1496" t="inlineStr"/>
@@ -79974,21 +79974,21 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+          <t>TINTURA DE RUIBARDO FCO 30ML</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr"/>
       <c r="D1497" t="inlineStr"/>
       <c r="E1497" t="n">
-        <v>29800</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1497" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1497" t="n">
         <v>0</v>
@@ -80016,7 +80016,7 @@
       </c>
       <c r="M1497" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1497" t="inlineStr"/>
@@ -80024,25 +80024,21 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
-        </is>
-      </c>
-      <c r="C1498" t="inlineStr">
-        <is>
-          <t>7702026149567</t>
-        </is>
-      </c>
+          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr"/>
       <c r="D1498" t="inlineStr"/>
       <c r="E1498" t="n">
-        <v>13500</v>
+        <v>29800</v>
       </c>
       <c r="F1498" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1498" t="n">
         <v>0</v>
@@ -80078,25 +80074,25 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>Toallas húmedas winny 24unidades</t>
+          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
         </is>
       </c>
       <c r="C1499" t="inlineStr">
         <is>
-          <t>7701021143655</t>
+          <t>7702026149567</t>
         </is>
       </c>
       <c r="D1499" t="inlineStr"/>
       <c r="E1499" t="n">
-        <v>4033.613445</v>
+        <v>13500</v>
       </c>
       <c r="F1499" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G1499" t="n">
         <v>0</v>
@@ -80124,7 +80120,7 @@
       </c>
       <c r="M1499" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1499" t="inlineStr"/>
@@ -80132,25 +80128,25 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>Toallas maternas maternity</t>
+          <t>Toallas húmedas winny 24unidades</t>
         </is>
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>7703252489526</t>
+          <t>7701021143655</t>
         </is>
       </c>
       <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="n">
-        <v>16900</v>
+        <v>4033.613445</v>
       </c>
       <c r="F1500" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G1500" t="n">
         <v>0</v>
@@ -80178,7 +80174,7 @@
       </c>
       <c r="M1500" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1500" t="inlineStr"/>
@@ -80186,25 +80182,25 @@
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>Toallas Nosotras Rapigel x Und</t>
+          <t>Toallas maternas maternity</t>
         </is>
       </c>
       <c r="C1501" t="inlineStr">
         <is>
-          <t>7702027416859</t>
+          <t>7703252489526</t>
         </is>
       </c>
       <c r="D1501" t="inlineStr"/>
       <c r="E1501" t="n">
-        <v>756.302521</v>
+        <v>16900</v>
       </c>
       <c r="F1501" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="G1501" t="n">
         <v>0</v>
@@ -80232,7 +80228,7 @@
       </c>
       <c r="M1501" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1501" t="inlineStr"/>
@@ -80240,21 +80236,25 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>TRAMADOL 50MG CAPSULA MP</t>
-        </is>
-      </c>
-      <c r="C1502" t="inlineStr"/>
+          <t>Toallas Nosotras Rapigel x Und</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>7702027416859</t>
+        </is>
+      </c>
       <c r="D1502" t="inlineStr"/>
       <c r="E1502" t="n">
-        <v>1500</v>
+        <v>756.302521</v>
       </c>
       <c r="F1502" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G1502" t="n">
         <v>0</v>
@@ -80282,7 +80282,7 @@
       </c>
       <c r="M1502" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1502" t="inlineStr"/>
@@ -80290,25 +80290,21 @@
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>Tramadol clorhidrato 100mg laquifar</t>
-        </is>
-      </c>
-      <c r="C1503" t="inlineStr">
-        <is>
-          <t>7707019426977</t>
-        </is>
-      </c>
+          <t>TRAMADOL 50MG CAPSULA MP</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr"/>
       <c r="D1503" t="inlineStr"/>
       <c r="E1503" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="F1503" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G1503" t="n">
         <v>0</v>
@@ -80344,21 +80340,25 @@
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>TRIGENTAX CREMA TBO X 20GR</t>
-        </is>
-      </c>
-      <c r="C1504" t="inlineStr"/>
+          <t>Tramadol clorhidrato 100mg laquifar</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>7707019426977</t>
+        </is>
+      </c>
       <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="n">
-        <v>33500</v>
+        <v>1600</v>
       </c>
       <c r="F1504" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1504" t="n">
         <v>0</v>
@@ -80394,21 +80394,21 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
+          <t>TRIGENTAX CREMA TBO X 20GR</t>
         </is>
       </c>
       <c r="C1505" t="inlineStr"/>
       <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="n">
-        <v>9000</v>
+        <v>33500</v>
       </c>
       <c r="F1505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1505" t="n">
         <v>0</v>
@@ -80444,21 +80444,21 @@
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
+          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
         </is>
       </c>
       <c r="C1506" t="inlineStr"/>
       <c r="D1506" t="inlineStr"/>
       <c r="E1506" t="n">
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="F1506" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1506" t="n">
         <v>0</v>
@@ -80494,12 +80494,12 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
+          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
         </is>
       </c>
       <c r="C1507" t="inlineStr"/>
@@ -80508,7 +80508,7 @@
         <v>10500</v>
       </c>
       <c r="F1507" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G1507" t="n">
         <v>0</v>
@@ -80544,21 +80544,21 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
+          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr"/>
       <c r="D1508" t="inlineStr"/>
       <c r="E1508" t="n">
-        <v>18800</v>
+        <v>10500</v>
       </c>
       <c r="F1508" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G1508" t="n">
         <v>0</v>
@@ -80594,21 +80594,21 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
+          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
         </is>
       </c>
       <c r="C1509" t="inlineStr"/>
       <c r="D1509" t="inlineStr"/>
       <c r="E1509" t="n">
-        <v>13800</v>
+        <v>18800</v>
       </c>
       <c r="F1509" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1509" t="n">
         <v>0</v>
@@ -80644,21 +80644,21 @@
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
+          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr"/>
       <c r="D1510" t="inlineStr"/>
       <c r="E1510" t="n">
-        <v>7900</v>
+        <v>13800</v>
       </c>
       <c r="F1510" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1510" t="n">
         <v>0</v>
@@ -80694,21 +80694,21 @@
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>VASELINA FC X 200GR YOMA</t>
+          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
         </is>
       </c>
       <c r="C1511" t="inlineStr"/>
       <c r="D1511" t="inlineStr"/>
       <c r="E1511" t="n">
-        <v>12521.008403</v>
+        <v>7900</v>
       </c>
       <c r="F1511" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1511" t="n">
         <v>0</v>
@@ -80736,7 +80736,7 @@
       </c>
       <c r="M1511" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1511" t="inlineStr"/>
@@ -80744,21 +80744,21 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
+          <t>VASELINA FC X 200GR YOMA</t>
         </is>
       </c>
       <c r="C1512" t="inlineStr"/>
       <c r="D1512" t="inlineStr"/>
       <c r="E1512" t="n">
-        <v>420.168067</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1512" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1512" t="n">
         <v>0</v>
@@ -80794,25 +80794,21 @@
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
-        </is>
-      </c>
-      <c r="C1513" t="inlineStr">
-        <is>
-          <t>7708480649803</t>
-        </is>
-      </c>
+          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr"/>
       <c r="D1513" t="inlineStr"/>
       <c r="E1513" t="n">
-        <v>28000</v>
+        <v>420.168067</v>
       </c>
       <c r="F1513" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1513" t="n">
         <v>0</v>
@@ -80840,7 +80836,7 @@
       </c>
       <c r="M1513" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1513" t="inlineStr"/>
@@ -80848,25 +80844,25 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>Venda Elastica 6x5 y piel</t>
-        </is>
-      </c>
-      <c r="C1514" t="inlineStr"/>
-      <c r="D1514" t="inlineStr">
-        <is>
-          <t>SUBIO A 6200 ANTES 5700</t>
-        </is>
-      </c>
+          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>7708480649803</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr"/>
       <c r="E1514" t="n">
-        <v>6200</v>
+        <v>28000</v>
       </c>
       <c r="F1514" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1514" t="n">
         <v>0</v>
@@ -80902,21 +80898,25 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
+          <t>Venda Elastica 6x5 y piel</t>
         </is>
       </c>
       <c r="C1515" t="inlineStr"/>
-      <c r="D1515" t="inlineStr"/>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>SUBIO A 6200 ANTES 5700</t>
+        </is>
+      </c>
       <c r="E1515" t="n">
-        <v>5500</v>
+        <v>6200</v>
       </c>
       <c r="F1515" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1515" t="n">
         <v>0</v>
@@ -80952,21 +80952,21 @@
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>Venta simple</t>
+          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
         </is>
       </c>
       <c r="C1516" t="inlineStr"/>
       <c r="D1516" t="inlineStr"/>
       <c r="E1516" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="F1516" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1516" t="n">
         <v>0</v>
@@ -80984,7 +80984,7 @@
       </c>
       <c r="K1516" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="L1516" t="inlineStr">
@@ -80992,27 +80992,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1516" t="inlineStr"/>
+      <c r="M1516" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1516" t="inlineStr"/>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
+          <t>Venta simple</t>
         </is>
       </c>
       <c r="C1517" t="inlineStr"/>
       <c r="D1517" t="inlineStr"/>
       <c r="E1517" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F1517" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1517" t="n">
         <v>0</v>
@@ -81030,7 +81034,7 @@
       </c>
       <c r="K1517" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="L1517" t="inlineStr">
@@ -81038,35 +81042,27 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1517" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1517" t="inlineStr"/>
       <c r="N1517" t="inlineStr"/>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
-        </is>
-      </c>
-      <c r="C1518" t="inlineStr">
-        <is>
-          <t>793969226467</t>
-        </is>
-      </c>
+          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr"/>
       <c r="D1518" t="inlineStr"/>
       <c r="E1518" t="n">
-        <v>17000</v>
+        <v>1000</v>
       </c>
       <c r="F1518" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1518" t="n">
         <v>0</v>
@@ -81089,7 +81085,7 @@
       </c>
       <c r="L1518" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="M1518" t="inlineStr">
@@ -81102,21 +81098,25 @@
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>VINO CEREBRAL JARABE X 1100ML</t>
-        </is>
-      </c>
-      <c r="C1519" t="inlineStr"/>
+          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>793969226467</t>
+        </is>
+      </c>
       <c r="D1519" t="inlineStr"/>
       <c r="E1519" t="n">
-        <v>48900</v>
+        <v>17000</v>
       </c>
       <c r="F1519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1519" t="n">
         <v>0</v>
@@ -81139,7 +81139,7 @@
       </c>
       <c r="L1519" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="M1519" t="inlineStr">
@@ -81152,21 +81152,21 @@
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
+          <t>VINO CEREBRAL JARABE X 1100ML</t>
         </is>
       </c>
       <c r="C1520" t="inlineStr"/>
       <c r="D1520" t="inlineStr"/>
       <c r="E1520" t="n">
-        <v>5400</v>
+        <v>48900</v>
       </c>
       <c r="F1520" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G1520" t="n">
         <v>0</v>
@@ -81202,21 +81202,21 @@
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
+          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
         </is>
       </c>
       <c r="C1521" t="inlineStr"/>
       <c r="D1521" t="inlineStr"/>
       <c r="E1521" t="n">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="F1521" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1521" t="n">
         <v>0</v>
@@ -81252,21 +81252,21 @@
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>WINNY PAÑAL ETP 6 X 30</t>
+          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
         </is>
       </c>
       <c r="C1522" t="inlineStr"/>
       <c r="D1522" t="inlineStr"/>
       <c r="E1522" t="n">
-        <v>57000</v>
+        <v>5500</v>
       </c>
       <c r="F1522" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G1522" t="n">
         <v>0</v>
@@ -81302,52 +81302,102 @@
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>YODO BLANCO FC X30ML</t>
+          <t>WINNY PAÑAL ETP 6 X 30</t>
         </is>
       </c>
       <c r="C1523" t="inlineStr"/>
       <c r="D1523" t="inlineStr"/>
       <c r="E1523" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1523" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1523" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1523" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1523" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1523" t="inlineStr"/>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>YODO BLANCO FC X30ML</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr"/>
+      <c r="D1524" t="inlineStr"/>
+      <c r="E1524" t="n">
         <v>6000</v>
       </c>
-      <c r="F1523" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1523" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1523" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1523" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1523" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="K1523" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="L1523" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="M1523" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="N1523" t="inlineStr"/>
+      <c r="F1524" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1524" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1524" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1524" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1524" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1524" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1524" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1524" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1524" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1524"/>
+  <dimension ref="A1:N1526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11165,7 +11165,7 @@
         <v>23000</v>
       </c>
       <c r="F202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -15107,7 +15107,7 @@
         <v>1900</v>
       </c>
       <c r="F275" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="G275" t="n">
         <v>0</v>
@@ -23577,7 +23577,7 @@
         <v>3300</v>
       </c>
       <c r="F434" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G434" t="n">
         <v>0</v>
@@ -30977,7 +30977,7 @@
         <v>1008.403361</v>
       </c>
       <c r="F572" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G572" t="n">
         <v>0</v>
@@ -42377,7 +42377,7 @@
         <v>2300</v>
       </c>
       <c r="F786" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="G786" t="n">
         <v>0</v>
@@ -59268,7 +59268,7 @@
         <v>19500</v>
       </c>
       <c r="F1101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1101" t="n">
         <v>0</v>
@@ -74606,25 +74606,21 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>Levotiroxina 100mcg MK</t>
-        </is>
-      </c>
-      <c r="C1393" t="inlineStr">
-        <is>
-          <t>7702057715908</t>
-        </is>
-      </c>
+          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr"/>
       <c r="D1393" t="inlineStr"/>
       <c r="E1393" t="n">
-        <v>27900</v>
+        <v>37900</v>
       </c>
       <c r="F1393" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1393" t="n">
         <v>0</v>
@@ -74660,21 +74656,25 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>LIMA MAYOMI 10/180</t>
-        </is>
-      </c>
-      <c r="C1394" t="inlineStr"/>
+          <t>Levotiroxina 100mcg MK</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>7702057715908</t>
+        </is>
+      </c>
       <c r="D1394" t="inlineStr"/>
       <c r="E1394" t="n">
-        <v>3900</v>
+        <v>27900</v>
       </c>
       <c r="F1394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1394" t="n">
         <v>0</v>
@@ -74710,21 +74710,21 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
+          <t>LIMA MAYOMI 10/180</t>
         </is>
       </c>
       <c r="C1395" t="inlineStr"/>
       <c r="D1395" t="inlineStr"/>
       <c r="E1395" t="n">
-        <v>16807</v>
+        <v>3900</v>
       </c>
       <c r="F1395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1395" t="n">
         <v>0</v>
@@ -74752,7 +74752,7 @@
       </c>
       <c r="M1395" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1395" t="inlineStr"/>
@@ -74760,21 +74760,21 @@
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
+          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
         </is>
       </c>
       <c r="C1396" t="inlineStr"/>
       <c r="D1396" t="inlineStr"/>
       <c r="E1396" t="n">
-        <v>15042.016807</v>
+        <v>16807</v>
       </c>
       <c r="F1396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1396" t="n">
         <v>0</v>
@@ -74810,21 +74810,21 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>LISTERINE CUIDADO TOTAL 180ML</t>
+          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
         </is>
       </c>
       <c r="C1397" t="inlineStr"/>
       <c r="D1397" t="inlineStr"/>
       <c r="E1397" t="n">
-        <v>16386.554622</v>
+        <v>15042.016807</v>
       </c>
       <c r="F1397" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1397" t="n">
         <v>0</v>
@@ -74860,21 +74860,21 @@
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
+          <t>LISTERINE CUIDADO TOTAL 180ML</t>
         </is>
       </c>
       <c r="C1398" t="inlineStr"/>
       <c r="D1398" t="inlineStr"/>
       <c r="E1398" t="n">
-        <v>3500</v>
+        <v>16386.554622</v>
       </c>
       <c r="F1398" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G1398" t="n">
         <v>0</v>
@@ -74902,7 +74902,7 @@
       </c>
       <c r="M1398" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1398" t="inlineStr"/>
@@ -74910,12 +74910,12 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
         </is>
       </c>
       <c r="C1399" t="inlineStr"/>
@@ -74924,7 +74924,7 @@
         <v>3500</v>
       </c>
       <c r="F1399" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G1399" t="n">
         <v>0</v>
@@ -74960,21 +74960,21 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
         </is>
       </c>
       <c r="C1400" t="inlineStr"/>
       <c r="D1400" t="inlineStr"/>
       <c r="E1400" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="F1400" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1400" t="n">
         <v>0</v>
@@ -75010,25 +75010,21 @@
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>Losartan Tensofar 100 Mg</t>
-        </is>
-      </c>
-      <c r="C1401" t="inlineStr">
-        <is>
-          <t>7703546012119</t>
-        </is>
-      </c>
+          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr"/>
       <c r="D1401" t="inlineStr"/>
       <c r="E1401" t="n">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="F1401" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1401" t="n">
         <v>0</v>
@@ -75064,25 +75060,25 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+          <t>Losartan Tensofar 100 Mg</t>
         </is>
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>7501007528939</t>
+          <t>7703546012119</t>
         </is>
       </c>
       <c r="D1402" t="inlineStr"/>
       <c r="E1402" t="n">
-        <v>18907.563025</v>
+        <v>5000</v>
       </c>
       <c r="F1402" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1402" t="n">
         <v>0</v>
@@ -75110,7 +75106,7 @@
       </c>
       <c r="M1402" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1402" t="inlineStr"/>
@@ -75118,18 +75114,22 @@
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>MANTECA DE CACAO LABIAL LIMON</t>
-        </is>
-      </c>
-      <c r="C1403" t="inlineStr"/>
+          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>7501007528939</t>
+        </is>
+      </c>
       <c r="D1403" t="inlineStr"/>
       <c r="E1403" t="n">
-        <v>3361.344538</v>
+        <v>18907.563025</v>
       </c>
       <c r="F1403" t="n">
         <v>0</v>
@@ -75168,12 +75168,12 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
+          <t>MANTECA DE CACAO LABIAL LIMON</t>
         </is>
       </c>
       <c r="C1404" t="inlineStr"/>
@@ -75218,21 +75218,21 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>Mega sex</t>
+          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
         </is>
       </c>
       <c r="C1405" t="inlineStr"/>
       <c r="D1405" t="inlineStr"/>
       <c r="E1405" t="n">
-        <v>3200</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1405" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G1405" t="n">
         <v>0</v>
@@ -75260,7 +75260,7 @@
       </c>
       <c r="M1405" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1405" t="inlineStr"/>
@@ -75268,29 +75268,21 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>Melatonina 3mg</t>
-        </is>
-      </c>
-      <c r="C1406" t="inlineStr">
-        <is>
-          <t>7706849112906</t>
-        </is>
-      </c>
-      <c r="D1406" t="inlineStr">
-        <is>
-          <t>producto nuevo</t>
-        </is>
-      </c>
+          <t>Mega sex</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr"/>
+      <c r="D1406" t="inlineStr"/>
       <c r="E1406" t="n">
-        <v>52000</v>
+        <v>3200</v>
       </c>
       <c r="F1406" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G1406" t="n">
         <v>0</v>
@@ -75326,22 +75318,26 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
+          <t>Melatonina 3mg</t>
         </is>
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>7707529435209</t>
-        </is>
-      </c>
-      <c r="D1407" t="inlineStr"/>
+          <t>7706849112906</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>producto nuevo</t>
+        </is>
+      </c>
       <c r="E1407" t="n">
-        <v>36000</v>
+        <v>52000</v>
       </c>
       <c r="F1407" t="n">
         <v>0</v>
@@ -75380,22 +75376,22 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>Meloxicam 15mg AG</t>
+          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
         </is>
       </c>
       <c r="C1408" t="inlineStr">
         <is>
-          <t>7706569020437</t>
+          <t>7707529435209</t>
         </is>
       </c>
       <c r="D1408" t="inlineStr"/>
       <c r="E1408" t="n">
-        <v>1500</v>
+        <v>36000</v>
       </c>
       <c r="F1408" t="n">
         <v>0</v>
@@ -75434,21 +75430,25 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
-        </is>
-      </c>
-      <c r="C1409" t="inlineStr"/>
+          <t>Meloxicam 15mg AG</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>7706569020437</t>
+        </is>
+      </c>
       <c r="D1409" t="inlineStr"/>
       <c r="E1409" t="n">
-        <v>9700</v>
+        <v>1500</v>
       </c>
       <c r="F1409" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1409" t="n">
         <v>0</v>
@@ -75484,25 +75484,21 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>MELOXICAM COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1410" t="inlineStr">
-        <is>
-          <t>7703712036253</t>
-        </is>
-      </c>
+          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr"/>
       <c r="D1410" t="inlineStr"/>
       <c r="E1410" t="n">
-        <v>1300</v>
+        <v>9700</v>
       </c>
       <c r="F1410" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1410" t="n">
         <v>0</v>
@@ -75528,31 +75524,35 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1410" t="inlineStr"/>
+      <c r="M1410" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1410" t="inlineStr"/>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>metformina 850 mg pisa</t>
+          <t>MELOXICAM COASPHARMA</t>
         </is>
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>7501125188039</t>
+          <t>7703712036253</t>
         </is>
       </c>
       <c r="D1411" t="inlineStr"/>
       <c r="E1411" t="n">
-        <v>5500</v>
+        <v>1300</v>
       </c>
       <c r="F1411" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G1411" t="n">
         <v>0</v>
@@ -75578,35 +75578,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1411" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1411" t="inlineStr"/>
       <c r="N1411" t="inlineStr"/>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10MG RECIPE</t>
+          <t>metformina 850 mg pisa</t>
         </is>
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>7702195084355</t>
+          <t>7501125188039</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr"/>
       <c r="E1412" t="n">
-        <v>1000</v>
+        <v>5500</v>
       </c>
       <c r="F1412" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G1412" t="n">
         <v>0</v>
@@ -75642,25 +75638,25 @@
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>MICROPOR 1X3 Y</t>
+          <t>METOCLOPRAMIDA 10MG RECIPE</t>
         </is>
       </c>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>7707282990205</t>
+          <t>7702195084355</t>
         </is>
       </c>
       <c r="D1413" t="inlineStr"/>
       <c r="E1413" t="n">
-        <v>5300</v>
+        <v>1000</v>
       </c>
       <c r="F1413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1413" t="n">
         <v>0</v>
@@ -75696,25 +75692,25 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>MICROPOR CINTA 1/2X5Y</t>
+          <t>MICROPOR 1X3 Y</t>
         </is>
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>7707282990182</t>
+          <t>7707282990205</t>
         </is>
       </c>
       <c r="D1414" t="inlineStr"/>
       <c r="E1414" t="n">
-        <v>3900</v>
+        <v>5300</v>
       </c>
       <c r="F1414" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G1414" t="n">
         <v>0</v>
@@ -75750,21 +75746,25 @@
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>MICROPORE COLOR PIEL 2YARDAS</t>
-        </is>
-      </c>
-      <c r="C1415" t="inlineStr"/>
+          <t>MICROPOR CINTA 1/2X5Y</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>7707282990182</t>
+        </is>
+      </c>
       <c r="D1415" t="inlineStr"/>
       <c r="E1415" t="n">
-        <v>3700</v>
+        <v>3900</v>
       </c>
       <c r="F1415" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G1415" t="n">
         <v>0</v>
@@ -75800,18 +75800,18 @@
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
+          <t>MICROPORE COLOR PIEL 2YARDAS</t>
         </is>
       </c>
       <c r="C1416" t="inlineStr"/>
       <c r="D1416" t="inlineStr"/>
       <c r="E1416" t="n">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="F1416" t="n">
         <v>0</v>
@@ -75850,22 +75850,18 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>MIELTERTOS JARABE X 240ML</t>
-        </is>
-      </c>
-      <c r="C1417" t="inlineStr">
-        <is>
-          <t>7707232095608</t>
-        </is>
-      </c>
+          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr"/>
       <c r="D1417" t="inlineStr"/>
       <c r="E1417" t="n">
-        <v>34500</v>
+        <v>4000</v>
       </c>
       <c r="F1417" t="n">
         <v>0</v>
@@ -75904,25 +75900,25 @@
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
-        </is>
-      </c>
-      <c r="C1418" t="inlineStr"/>
-      <c r="D1418" t="inlineStr">
-        <is>
-          <t>subio precio hector</t>
-        </is>
-      </c>
+          <t>MIELTERTOS JARABE X 240ML</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>7707232095608</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr"/>
       <c r="E1418" t="n">
-        <v>22700</v>
+        <v>34500</v>
       </c>
       <c r="F1418" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1418" t="n">
         <v>0</v>
@@ -75958,21 +75954,25 @@
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
+          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
         </is>
       </c>
       <c r="C1419" t="inlineStr"/>
-      <c r="D1419" t="inlineStr"/>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>subio precio hector</t>
+        </is>
+      </c>
       <c r="E1419" t="n">
-        <v>5500</v>
+        <v>22700</v>
       </c>
       <c r="F1419" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G1419" t="n">
         <v>0</v>
@@ -76008,21 +76008,21 @@
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>NEOSALDINA TABLETA X UND</t>
+          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
         </is>
       </c>
       <c r="C1420" t="inlineStr"/>
       <c r="D1420" t="inlineStr"/>
       <c r="E1420" t="n">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="F1420" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1420" t="n">
         <v>0</v>
@@ -76058,21 +76058,21 @@
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>NIFEDIPINO 30MG NOVAMED</t>
+          <t>NEOSALDINA TABLETA X UND</t>
         </is>
       </c>
       <c r="C1421" t="inlineStr"/>
       <c r="D1421" t="inlineStr"/>
       <c r="E1421" t="n">
-        <v>19000</v>
+        <v>2500</v>
       </c>
       <c r="F1421" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G1421" t="n">
         <v>0</v>
@@ -76108,21 +76108,21 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
+          <t>NIFEDIPINO 30MG NOVAMED</t>
         </is>
       </c>
       <c r="C1422" t="inlineStr"/>
       <c r="D1422" t="inlineStr"/>
       <c r="E1422" t="n">
-        <v>23000</v>
+        <v>19000</v>
       </c>
       <c r="F1422" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1422" t="n">
         <v>0</v>
@@ -76158,21 +76158,21 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>NITOXIPAR X 6 TABLETAS</t>
+          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
         </is>
       </c>
       <c r="C1423" t="inlineStr"/>
       <c r="D1423" t="inlineStr"/>
       <c r="E1423" t="n">
-        <v>24500</v>
+        <v>23000</v>
       </c>
       <c r="F1423" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1423" t="n">
         <v>0</v>
@@ -76208,21 +76208,21 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>NORAVER SPRAY CEREZA 120ML</t>
+          <t>NITOXIPAR X 6 TABLETAS</t>
         </is>
       </c>
       <c r="C1424" t="inlineStr"/>
       <c r="D1424" t="inlineStr"/>
       <c r="E1424" t="n">
-        <v>52900</v>
+        <v>24500</v>
       </c>
       <c r="F1424" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1424" t="n">
         <v>0</v>
@@ -76258,25 +76258,21 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
-        </is>
-      </c>
-      <c r="C1425" t="inlineStr">
-        <is>
-          <t>7702027041662</t>
-        </is>
-      </c>
+          <t>NORAVER SPRAY CEREZA 120ML</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr"/>
       <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="n">
-        <v>6300</v>
+        <v>52900</v>
       </c>
       <c r="F1425" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1425" t="n">
         <v>0</v>
@@ -76312,18 +76308,22 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
-        </is>
-      </c>
-      <c r="C1426" t="inlineStr"/>
+          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>7702027041662</t>
+        </is>
+      </c>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="n">
-        <v>8823.529412</v>
+        <v>6300</v>
       </c>
       <c r="F1426" t="n">
         <v>0</v>
@@ -76354,7 +76354,7 @@
       </c>
       <c r="M1426" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1426" t="inlineStr"/>
@@ -76362,7 +76362,7 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
@@ -76370,11 +76370,7 @@
           <t>NOSOTRAS JABON INTIMO X 200ML</t>
         </is>
       </c>
-      <c r="C1427" t="inlineStr">
-        <is>
-          <t>7702026158644</t>
-        </is>
-      </c>
+      <c r="C1427" t="inlineStr"/>
       <c r="D1427" t="inlineStr"/>
       <c r="E1427" t="n">
         <v>8823.529412</v>
@@ -76416,25 +76412,25 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JBE 120ML</t>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
         </is>
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>7707355053363</t>
+          <t>7702026158644</t>
         </is>
       </c>
       <c r="D1428" t="inlineStr"/>
       <c r="E1428" t="n">
-        <v>22700</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1428" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1428" t="n">
         <v>0</v>
@@ -76462,7 +76458,7 @@
       </c>
       <c r="M1428" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1428" t="inlineStr"/>
@@ -76470,25 +76466,25 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+          <t>NOXPIRIN JUNIOR JBE 120ML</t>
         </is>
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>7707355053356</t>
+          <t>7707355053363</t>
         </is>
       </c>
       <c r="D1429" t="inlineStr"/>
       <c r="E1429" t="n">
-        <v>17200</v>
+        <v>22700</v>
       </c>
       <c r="F1429" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1429" t="n">
         <v>0</v>
@@ -76524,21 +76520,25 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>NUTRIBELL ACEITE DE COCO</t>
-        </is>
-      </c>
-      <c r="C1430" t="inlineStr"/>
+          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>7707355053356</t>
+        </is>
+      </c>
       <c r="D1430" t="inlineStr"/>
       <c r="E1430" t="n">
-        <v>2700</v>
+        <v>17200</v>
       </c>
       <c r="F1430" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1430" t="n">
         <v>0</v>
@@ -76574,29 +76574,21 @@
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>Omega 3 6 9 suplemento totalmax</t>
-        </is>
-      </c>
-      <c r="C1431" t="inlineStr">
-        <is>
-          <t>7707529434974</t>
-        </is>
-      </c>
-      <c r="D1431" t="inlineStr">
-        <is>
-          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
-        </is>
-      </c>
+          <t>NUTRIBELL ACEITE DE COCO</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr"/>
+      <c r="D1431" t="inlineStr"/>
       <c r="E1431" t="n">
-        <v>35000</v>
+        <v>2700</v>
       </c>
       <c r="F1431" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1431" t="n">
         <v>0</v>
@@ -76632,21 +76624,29 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1432" t="inlineStr"/>
-      <c r="D1432" t="inlineStr"/>
+          <t>Omega 3 6 9 suplemento totalmax</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>7707529434974</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
+        </is>
+      </c>
       <c r="E1432" t="n">
-        <v>5500</v>
+        <v>35000</v>
       </c>
       <c r="F1432" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1432" t="n">
         <v>0</v>
@@ -76682,22 +76682,18 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
-        </is>
-      </c>
-      <c r="C1433" t="inlineStr">
-        <is>
-          <t>7707529435940</t>
-        </is>
-      </c>
+          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr"/>
       <c r="D1433" t="inlineStr"/>
       <c r="E1433" t="n">
-        <v>35000</v>
+        <v>5500</v>
       </c>
       <c r="F1433" t="n">
         <v>0</v>
@@ -76736,21 +76732,25 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
-        </is>
-      </c>
-      <c r="C1434" t="inlineStr"/>
+          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>7707529435940</t>
+        </is>
+      </c>
       <c r="D1434" t="inlineStr"/>
       <c r="E1434" t="n">
-        <v>48000</v>
+        <v>35000</v>
       </c>
       <c r="F1434" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1434" t="n">
         <v>0</v>
@@ -76786,25 +76786,21 @@
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>OROCAL CALCIO 600MG</t>
+          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
         </is>
       </c>
       <c r="C1435" t="inlineStr"/>
-      <c r="D1435" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="D1435" t="inlineStr"/>
       <c r="E1435" t="n">
-        <v>30500</v>
+        <v>48000</v>
       </c>
       <c r="F1435" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>
@@ -76840,18 +76836,22 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>PALA DE MADERA RASPACALLO</t>
+          <t>OROCAL CALCIO 600MG</t>
         </is>
       </c>
       <c r="C1436" t="inlineStr"/>
-      <c r="D1436" t="inlineStr"/>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E1436" t="n">
-        <v>4000</v>
+        <v>30500</v>
       </c>
       <c r="F1436" t="n">
         <v>1</v>
@@ -76890,21 +76890,21 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>PALO DE NARANJO X UNIDAD</t>
+          <t>PALA DE MADERA RASPACALLO</t>
         </is>
       </c>
       <c r="C1437" t="inlineStr"/>
       <c r="D1437" t="inlineStr"/>
       <c r="E1437" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="F1437" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G1437" t="n">
         <v>0</v>
@@ -76940,25 +76940,21 @@
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
-        </is>
-      </c>
-      <c r="C1438" t="inlineStr">
-        <is>
-          <t>7704412170896</t>
-        </is>
-      </c>
+          <t>PALO DE NARANJO X UNIDAD</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr"/>
       <c r="D1438" t="inlineStr"/>
       <c r="E1438" t="n">
-        <v>6200</v>
+        <v>400</v>
       </c>
       <c r="F1438" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G1438" t="n">
         <v>0</v>
@@ -76994,18 +76990,22 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
-        </is>
-      </c>
-      <c r="C1439" t="inlineStr"/>
+          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>7704412170896</t>
+        </is>
+      </c>
       <c r="D1439" t="inlineStr"/>
       <c r="E1439" t="n">
-        <v>14285.714286</v>
+        <v>6200</v>
       </c>
       <c r="F1439" t="n">
         <v>1</v>
@@ -77036,7 +77036,7 @@
       </c>
       <c r="M1439" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1439" t="inlineStr"/>
@@ -77044,18 +77044,18 @@
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
+          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
         </is>
       </c>
       <c r="C1440" t="inlineStr"/>
       <c r="D1440" t="inlineStr"/>
       <c r="E1440" t="n">
-        <v>28991.596639</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1440" t="n">
         <v>1</v>
@@ -77094,18 +77094,18 @@
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
         </is>
       </c>
       <c r="C1441" t="inlineStr"/>
       <c r="D1441" t="inlineStr"/>
       <c r="E1441" t="n">
-        <v>41176.470588</v>
+        <v>28991.596639</v>
       </c>
       <c r="F1441" t="n">
         <v>1</v>
@@ -77144,22 +77144,18 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>Pañales Winny Etapa 5 X PAQUETE</t>
-        </is>
-      </c>
-      <c r="C1442" t="inlineStr">
-        <is>
-          <t>7701021114174</t>
-        </is>
-      </c>
+          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr"/>
       <c r="D1442" t="inlineStr"/>
       <c r="E1442" t="n">
-        <v>41849</v>
+        <v>41176.470588</v>
       </c>
       <c r="F1442" t="n">
         <v>1</v>
@@ -77198,21 +77194,25 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>PAÑALWINNY ETA 5 X 16 UND</t>
-        </is>
-      </c>
-      <c r="C1443" t="inlineStr"/>
+          <t>Pañales Winny Etapa 5 X PAQUETE</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>7701021114174</t>
+        </is>
+      </c>
       <c r="D1443" t="inlineStr"/>
       <c r="E1443" t="n">
-        <v>24369.747899</v>
+        <v>41849</v>
       </c>
       <c r="F1443" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1443" t="n">
         <v>0</v>
@@ -77248,21 +77248,21 @@
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>pañitos humedos pequeñin 100unidades</t>
+          <t>PAÑALWINNY ETA 5 X 16 UND</t>
         </is>
       </c>
       <c r="C1444" t="inlineStr"/>
       <c r="D1444" t="inlineStr"/>
       <c r="E1444" t="n">
-        <v>10925</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1444" t="n">
         <v>0</v>
@@ -77298,21 +77298,21 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
+          <t>pañitos humedos pequeñin 100unidades</t>
         </is>
       </c>
       <c r="C1445" t="inlineStr"/>
       <c r="D1445" t="inlineStr"/>
       <c r="E1445" t="n">
-        <v>14900</v>
+        <v>10925</v>
       </c>
       <c r="F1445" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1445" t="n">
         <v>0</v>
@@ -77340,7 +77340,7 @@
       </c>
       <c r="M1445" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1445" t="inlineStr"/>
@@ -77348,21 +77348,21 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>Panotil B x 8ML</t>
+          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
         </is>
       </c>
       <c r="C1446" t="inlineStr"/>
       <c r="D1446" t="inlineStr"/>
       <c r="E1446" t="n">
-        <v>26400</v>
+        <v>14900</v>
       </c>
       <c r="F1446" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1446" t="n">
         <v>0</v>
@@ -77398,25 +77398,21 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>PANTENE ACONDICIONADOR</t>
-        </is>
-      </c>
-      <c r="C1447" t="inlineStr">
-        <is>
-          <t>7500435153683</t>
-        </is>
-      </c>
+          <t>Panotil B x 8ML</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr"/>
       <c r="D1447" t="inlineStr"/>
       <c r="E1447" t="n">
-        <v>1500</v>
+        <v>26400</v>
       </c>
       <c r="F1447" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1447" t="n">
         <v>0</v>
@@ -77452,21 +77448,25 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Parche Ocular Colostol</t>
-        </is>
-      </c>
-      <c r="C1448" t="inlineStr"/>
+          <t>PANTENE ACONDICIONADOR</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>7500435153683</t>
+        </is>
+      </c>
       <c r="D1448" t="inlineStr"/>
       <c r="E1448" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F1448" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G1448" t="n">
         <v>0</v>
@@ -77502,25 +77502,21 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
-        </is>
-      </c>
-      <c r="C1449" t="inlineStr">
-        <is>
-          <t>7501033957413</t>
-        </is>
-      </c>
+          <t>Parche Ocular Colostol</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr"/>
       <c r="D1449" t="inlineStr"/>
       <c r="E1449" t="n">
-        <v>10600</v>
+        <v>1300</v>
       </c>
       <c r="F1449" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G1449" t="n">
         <v>0</v>
@@ -77556,26 +77552,22 @@
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
+          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
         </is>
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>7501033961557</t>
-        </is>
-      </c>
-      <c r="D1450" t="inlineStr">
-        <is>
-          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
-        </is>
-      </c>
+          <t>7501033957413</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr"/>
       <c r="E1450" t="n">
-        <v>10900</v>
+        <v>10600</v>
       </c>
       <c r="F1450" t="n">
         <v>0</v>
@@ -77614,29 +77606,29 @@
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
         </is>
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>7501033957376</t>
+          <t>7501033961557</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr">
         <is>
-          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
         </is>
       </c>
       <c r="E1451" t="n">
         <v>10900</v>
       </c>
       <c r="F1451" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1451" t="n">
         <v>0</v>
@@ -77672,21 +77664,29 @@
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>PEGANTE GLUE X 10GR X UND</t>
-        </is>
-      </c>
-      <c r="C1452" t="inlineStr"/>
-      <c r="D1452" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>7501033957376</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+        </is>
+      </c>
       <c r="E1452" t="n">
-        <v>2000</v>
+        <v>10900</v>
       </c>
       <c r="F1452" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1452" t="n">
         <v>0</v>
@@ -77722,21 +77722,21 @@
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>PEINETA COLA DE RATON METALICA</t>
+          <t>PEGANTE GLUE X 10GR X UND</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr"/>
       <c r="D1453" t="inlineStr"/>
       <c r="E1453" t="n">
-        <v>4700</v>
+        <v>2000</v>
       </c>
       <c r="F1453" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1453" t="n">
         <v>0</v>
@@ -77772,18 +77772,18 @@
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>PERFILADORES DE CEJAS</t>
+          <t>PEINETA COLA DE RATON METALICA</t>
         </is>
       </c>
       <c r="C1454" t="inlineStr"/>
       <c r="D1454" t="inlineStr"/>
       <c r="E1454" t="n">
-        <v>3900</v>
+        <v>4700</v>
       </c>
       <c r="F1454" t="n">
         <v>1</v>
@@ -77822,18 +77822,18 @@
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
+          <t>PERFILADORES DE CEJAS</t>
         </is>
       </c>
       <c r="C1455" t="inlineStr"/>
       <c r="D1455" t="inlineStr"/>
       <c r="E1455" t="n">
-        <v>27983.193277</v>
+        <v>3900</v>
       </c>
       <c r="F1455" t="n">
         <v>1</v>
@@ -77864,7 +77864,7 @@
       </c>
       <c r="M1455" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1455" t="inlineStr"/>
@@ -77872,21 +77872,21 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>POPETAS SURTIDAS X UND</t>
+          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
         </is>
       </c>
       <c r="C1456" t="inlineStr"/>
       <c r="D1456" t="inlineStr"/>
       <c r="E1456" t="n">
-        <v>2521.008403</v>
+        <v>27983.193277</v>
       </c>
       <c r="F1456" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1456" t="n">
         <v>0</v>
@@ -77922,21 +77922,21 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+          <t>POPETAS SURTIDAS X UND</t>
         </is>
       </c>
       <c r="C1457" t="inlineStr"/>
       <c r="D1457" t="inlineStr"/>
       <c r="E1457" t="n">
-        <v>20500</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1457" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1457" t="n">
         <v>0</v>
@@ -77964,7 +77964,7 @@
       </c>
       <c r="M1457" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1457" t="inlineStr"/>
@@ -77972,29 +77972,21 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>privatos miel limon la francol 120ml</t>
-        </is>
-      </c>
-      <c r="C1458" t="inlineStr">
-        <is>
-          <t>7702207163948</t>
-        </is>
-      </c>
-      <c r="D1458" t="inlineStr">
-        <is>
-          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
-        </is>
-      </c>
+          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr"/>
+      <c r="D1458" t="inlineStr"/>
       <c r="E1458" t="n">
-        <v>35900</v>
+        <v>20500</v>
       </c>
       <c r="F1458" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1458" t="n">
         <v>0</v>
@@ -78030,21 +78022,29 @@
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
-        </is>
-      </c>
-      <c r="C1459" t="inlineStr"/>
-      <c r="D1459" t="inlineStr"/>
+          <t>privatos miel limon la francol 120ml</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>7702207163948</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
+        </is>
+      </c>
       <c r="E1459" t="n">
-        <v>0</v>
+        <v>35900</v>
       </c>
       <c r="F1459" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1459" t="n">
         <v>0</v>
@@ -78072,7 +78072,7 @@
       </c>
       <c r="M1459" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1459" t="inlineStr"/>
@@ -78080,21 +78080,21 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>778</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>PROTECTOR NOSOTRAS LARGOS</t>
+          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
         </is>
       </c>
       <c r="C1460" t="inlineStr"/>
       <c r="D1460" t="inlineStr"/>
       <c r="E1460" t="n">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="F1460" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1460" t="n">
         <v>0</v>
@@ -78122,7 +78122,7 @@
       </c>
       <c r="M1460" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1460" t="inlineStr"/>
@@ -78130,18 +78130,18 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
+          <t>PROTECTOR NOSOTRAS LARGOS</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr"/>
       <c r="D1461" t="inlineStr"/>
       <c r="E1461" t="n">
-        <v>8900</v>
+        <v>3700</v>
       </c>
       <c r="F1461" t="n">
         <v>1</v>
@@ -78180,21 +78180,21 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Protector Solar Sunaid</t>
+          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
         </is>
       </c>
       <c r="C1462" t="inlineStr"/>
       <c r="D1462" t="inlineStr"/>
       <c r="E1462" t="n">
-        <v>158000</v>
+        <v>8900</v>
       </c>
       <c r="F1462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1462" t="n">
         <v>0</v>
@@ -78230,25 +78230,21 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Prueba de embarazo esfero</t>
-        </is>
-      </c>
-      <c r="C1463" t="inlineStr">
-        <is>
-          <t>7709299854228</t>
-        </is>
-      </c>
+          <t>Protector Solar Sunaid</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr"/>
       <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="n">
-        <v>16500</v>
+        <v>158000</v>
       </c>
       <c r="F1463" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1463" t="n">
         <v>0</v>
@@ -78284,25 +78280,25 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>Prueba de embarazo HCG cassette begut</t>
+          <t>Prueba de embarazo esfero</t>
         </is>
       </c>
       <c r="C1464" t="inlineStr">
         <is>
-          <t>7707282990953</t>
+          <t>7709299854228</t>
         </is>
       </c>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="n">
-        <v>8900</v>
+        <v>16500</v>
       </c>
       <c r="F1464" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1464" t="n">
         <v>0</v>
@@ -78338,21 +78334,25 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>PUSHER METALICO</t>
-        </is>
-      </c>
-      <c r="C1465" t="inlineStr"/>
+          <t>Prueba de embarazo HCG cassette begut</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>7707282990953</t>
+        </is>
+      </c>
       <c r="D1465" t="inlineStr"/>
       <c r="E1465" t="n">
-        <v>4300</v>
+        <v>8900</v>
       </c>
       <c r="F1465" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1465" t="n">
         <v>0</v>
@@ -78388,25 +78388,21 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Recolector de orina granandina</t>
-        </is>
-      </c>
-      <c r="C1466" t="inlineStr">
-        <is>
-          <t>7707233050590</t>
-        </is>
-      </c>
+          <t>PUSHER METALICO</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr"/>
       <c r="D1466" t="inlineStr"/>
       <c r="E1466" t="n">
-        <v>673</v>
+        <v>4300</v>
       </c>
       <c r="F1466" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="G1466" t="n">
         <v>0</v>
@@ -78434,7 +78430,7 @@
       </c>
       <c r="M1466" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1466" t="inlineStr"/>
@@ -78442,21 +78438,21 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
+          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
         </is>
       </c>
       <c r="C1467" t="inlineStr"/>
       <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="n">
-        <v>3820</v>
+        <v>17900</v>
       </c>
       <c r="F1467" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1467" t="n">
         <v>0</v>
@@ -78492,21 +78488,25 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>RegistroManual - Registro manual</t>
-        </is>
-      </c>
-      <c r="C1468" t="inlineStr"/>
+          <t>Recolector de orina granandina</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>7707233050590</t>
+        </is>
+      </c>
       <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="n">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="F1468" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G1468" t="n">
         <v>0</v>
@@ -78542,21 +78542,21 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>REMOVEDOR DE ESMALTE 60CC</t>
+          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
         </is>
       </c>
       <c r="C1469" t="inlineStr"/>
       <c r="D1469" t="inlineStr"/>
       <c r="E1469" t="n">
-        <v>3500</v>
+        <v>3820</v>
       </c>
       <c r="F1469" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1469" t="n">
         <v>0</v>
@@ -78592,25 +78592,21 @@
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
-        </is>
-      </c>
-      <c r="C1470" t="inlineStr">
-        <is>
-          <t>7591005981270</t>
-        </is>
-      </c>
+          <t>RegistroManual - Registro manual</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr"/>
       <c r="D1470" t="inlineStr"/>
       <c r="E1470" t="n">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="F1470" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1470" t="n">
         <v>0</v>
@@ -78638,7 +78634,7 @@
       </c>
       <c r="M1470" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1470" t="inlineStr"/>
@@ -78646,25 +78642,21 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
-        </is>
-      </c>
-      <c r="C1471" t="inlineStr">
-        <is>
-          <t>7503051868245</t>
-        </is>
-      </c>
+          <t>REMOVEDOR DE ESMALTE 60CC</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr"/>
       <c r="D1471" t="inlineStr"/>
       <c r="E1471" t="n">
-        <v>20900</v>
+        <v>3500</v>
       </c>
       <c r="F1471" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1471" t="n">
         <v>0</v>
@@ -78700,25 +78692,25 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
         </is>
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>7702057079642</t>
+          <t>7591005981270</t>
         </is>
       </c>
       <c r="D1472" t="inlineStr"/>
       <c r="E1472" t="n">
-        <v>13000</v>
+        <v>9500</v>
       </c>
       <c r="F1472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1472" t="n">
         <v>0</v>
@@ -78754,21 +78746,25 @@
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>Ryaltris Spray Nasal 240 dosis</t>
-        </is>
-      </c>
-      <c r="C1473" t="inlineStr"/>
+          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>7503051868245</t>
+        </is>
+      </c>
       <c r="D1473" t="inlineStr"/>
       <c r="E1473" t="n">
-        <v>216400</v>
+        <v>20900</v>
       </c>
       <c r="F1473" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1473" t="n">
         <v>0</v>
@@ -78804,25 +78800,25 @@
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+          <t>RISPERIDONA 1MG X 20 TABL MK</t>
         </is>
       </c>
       <c r="C1474" t="inlineStr">
         <is>
-          <t>7706849116676</t>
+          <t>7702057079642</t>
         </is>
       </c>
       <c r="D1474" t="inlineStr"/>
       <c r="E1474" t="n">
-        <v>31500</v>
+        <v>13000</v>
       </c>
       <c r="F1474" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1474" t="n">
         <v>0</v>
@@ -78858,21 +78854,21 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>SCOBIT PURGANTE 60GR</t>
+          <t>Ryaltris Spray Nasal 240 dosis</t>
         </is>
       </c>
       <c r="C1475" t="inlineStr"/>
       <c r="D1475" t="inlineStr"/>
       <c r="E1475" t="n">
-        <v>15238.095238</v>
+        <v>216400</v>
       </c>
       <c r="F1475" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1475" t="n">
         <v>0</v>
@@ -78900,7 +78896,7 @@
       </c>
       <c r="M1475" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1475" t="inlineStr"/>
@@ -78908,21 +78904,25 @@
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
-        </is>
-      </c>
-      <c r="C1476" t="inlineStr"/>
+          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>7706849116676</t>
+        </is>
+      </c>
       <c r="D1476" t="inlineStr"/>
       <c r="E1476" t="n">
-        <v>6554.621849</v>
+        <v>31500</v>
       </c>
       <c r="F1476" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1476" t="n">
         <v>0</v>
@@ -78950,7 +78950,7 @@
       </c>
       <c r="M1476" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1476" t="inlineStr"/>
@@ -78958,25 +78958,21 @@
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>SHAMPOO PANTENE COLAGENO</t>
-        </is>
-      </c>
-      <c r="C1477" t="inlineStr">
-        <is>
-          <t>7500435191500</t>
-        </is>
-      </c>
+          <t>SCOBIT PURGANTE 60GR</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr"/>
       <c r="D1477" t="inlineStr"/>
       <c r="E1477" t="n">
-        <v>1429</v>
+        <v>15238.095238</v>
       </c>
       <c r="F1477" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1477" t="n">
         <v>0</v>
@@ -79004,7 +79000,7 @@
       </c>
       <c r="M1477" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1477" t="inlineStr"/>
@@ -79012,21 +79008,21 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>SILDENAFIL 50MG TQ</t>
+          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
         </is>
       </c>
       <c r="C1478" t="inlineStr"/>
       <c r="D1478" t="inlineStr"/>
       <c r="E1478" t="n">
-        <v>5000</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1478" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1478" t="n">
         <v>0</v>
@@ -79054,7 +79050,7 @@
       </c>
       <c r="M1478" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1478" t="inlineStr"/>
@@ -79062,25 +79058,25 @@
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>SILIMARINA 167MG EPANAT</t>
+          <t>SHAMPOO PANTENE COLAGENO</t>
         </is>
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>7706849115921</t>
+          <t>7500435191500</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr"/>
       <c r="E1479" t="n">
-        <v>2000</v>
+        <v>1429</v>
       </c>
       <c r="F1479" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="G1479" t="n">
         <v>0</v>
@@ -79108,7 +79104,7 @@
       </c>
       <c r="M1479" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1479" t="inlineStr"/>
@@ -79116,21 +79112,21 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>SMECTA 3GR NARANJA S/B</t>
+          <t>SILDENAFIL 50MG TQ</t>
         </is>
       </c>
       <c r="C1480" t="inlineStr"/>
       <c r="D1480" t="inlineStr"/>
       <c r="E1480" t="n">
-        <v>8900</v>
+        <v>5000</v>
       </c>
       <c r="F1480" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G1480" t="n">
         <v>0</v>
@@ -79166,21 +79162,25 @@
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>SONDA FOLEY 2 VIAS BAL #18</t>
-        </is>
-      </c>
-      <c r="C1481" t="inlineStr"/>
+          <t>SILIMARINA 167MG EPANAT</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>7706849115921</t>
+        </is>
+      </c>
       <c r="D1481" t="inlineStr"/>
       <c r="E1481" t="n">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="F1481" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="G1481" t="n">
         <v>0</v>
@@ -79216,21 +79216,21 @@
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>SONDA NELATON #6</t>
+          <t>SMECTA 3GR NARANJA S/B</t>
         </is>
       </c>
       <c r="C1482" t="inlineStr"/>
       <c r="D1482" t="inlineStr"/>
       <c r="E1482" t="n">
-        <v>2500</v>
+        <v>8900</v>
       </c>
       <c r="F1482" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1482" t="n">
         <v>0</v>
@@ -79266,21 +79266,21 @@
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>SPRAY NASAL MOMETASONA 18ML</t>
+          <t>SONDA FOLEY 2 VIAS BAL #18</t>
         </is>
       </c>
       <c r="C1483" t="inlineStr"/>
       <c r="D1483" t="inlineStr"/>
       <c r="E1483" t="n">
-        <v>36900</v>
+        <v>7500</v>
       </c>
       <c r="F1483" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1483" t="n">
         <v>0</v>
@@ -79316,25 +79316,21 @@
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1484" t="inlineStr">
-        <is>
-          <t>7703712035034</t>
-        </is>
-      </c>
+          <t>SONDA NELATON #6</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr"/>
       <c r="D1484" t="inlineStr"/>
       <c r="E1484" t="n">
-        <v>14800</v>
+        <v>2500</v>
       </c>
       <c r="F1484" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1484" t="n">
         <v>0</v>
@@ -79370,18 +79366,18 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
+          <t>SPRAY NASAL MOMETASONA 18ML</t>
         </is>
       </c>
       <c r="C1485" t="inlineStr"/>
       <c r="D1485" t="inlineStr"/>
       <c r="E1485" t="n">
-        <v>3781.512605</v>
+        <v>36900</v>
       </c>
       <c r="F1485" t="n">
         <v>1</v>
@@ -79412,7 +79408,7 @@
       </c>
       <c r="M1485" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1485" t="inlineStr"/>
@@ -79420,18 +79416,22 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
-        </is>
-      </c>
-      <c r="C1486" t="inlineStr"/>
+          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>7703712035034</t>
+        </is>
+      </c>
       <c r="D1486" t="inlineStr"/>
       <c r="E1486" t="n">
-        <v>5210.084034</v>
+        <v>14800</v>
       </c>
       <c r="F1486" t="n">
         <v>0</v>
@@ -79462,7 +79462,7 @@
       </c>
       <c r="M1486" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1486" t="inlineStr"/>
@@ -79470,18 +79470,18 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
+          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
         </is>
       </c>
       <c r="C1487" t="inlineStr"/>
       <c r="D1487" t="inlineStr"/>
       <c r="E1487" t="n">
-        <v>8319.327730999999</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1487" t="n">
         <v>1</v>
@@ -79520,21 +79520,21 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>SULZINC SUSP X 80ML HUMAX</t>
+          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
         </is>
       </c>
       <c r="C1488" t="inlineStr"/>
       <c r="D1488" t="inlineStr"/>
       <c r="E1488" t="n">
-        <v>22400</v>
+        <v>5210.084034</v>
       </c>
       <c r="F1488" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1488" t="n">
         <v>0</v>
@@ -79562,7 +79562,7 @@
       </c>
       <c r="M1488" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1488" t="inlineStr"/>
@@ -79570,21 +79570,21 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>SUNDARK FPS 60 CON TAPA</t>
+          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr"/>
       <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="n">
-        <v>3781.512605</v>
+        <v>8319.327730999999</v>
       </c>
       <c r="F1489" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1489" t="n">
         <v>0</v>
@@ -79620,21 +79620,21 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>Synthroid 125 mcg</t>
+          <t>SULZINC SUSP X 80ML HUMAX</t>
         </is>
       </c>
       <c r="C1490" t="inlineStr"/>
       <c r="D1490" t="inlineStr"/>
       <c r="E1490" t="n">
-        <v>178000</v>
+        <v>22400</v>
       </c>
       <c r="F1490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1490" t="n">
         <v>0</v>
@@ -79670,25 +79670,21 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Talco medicado Neofungina 40gm</t>
-        </is>
-      </c>
-      <c r="C1491" t="inlineStr">
-        <is>
-          <t>7706142707106</t>
-        </is>
-      </c>
+          <t>SUNDARK FPS 60 CON TAPA</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr"/>
       <c r="D1491" t="inlineStr"/>
       <c r="E1491" t="n">
-        <v>14900</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1491" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1491" t="n">
         <v>0</v>
@@ -79716,7 +79712,7 @@
       </c>
       <c r="M1491" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1491" t="inlineStr"/>
@@ -79724,18 +79720,18 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
+          <t>Synthroid 125 mcg</t>
         </is>
       </c>
       <c r="C1492" t="inlineStr"/>
       <c r="D1492" t="inlineStr"/>
       <c r="E1492" t="n">
-        <v>13300</v>
+        <v>178000</v>
       </c>
       <c r="F1492" t="n">
         <v>0</v>
@@ -79774,21 +79770,25 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
-        </is>
-      </c>
-      <c r="C1493" t="inlineStr"/>
+          <t>Talco medicado Neofungina 40gm</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>7706142707106</t>
+        </is>
+      </c>
       <c r="D1493" t="inlineStr"/>
       <c r="E1493" t="n">
-        <v>4874</v>
+        <v>14900</v>
       </c>
       <c r="F1493" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G1493" t="n">
         <v>0</v>
@@ -79816,7 +79816,7 @@
       </c>
       <c r="M1493" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1493" t="inlineStr"/>
@@ -79824,21 +79824,21 @@
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
+          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
         </is>
       </c>
       <c r="C1494" t="inlineStr"/>
       <c r="D1494" t="inlineStr"/>
       <c r="E1494" t="n">
-        <v>28800</v>
+        <v>13300</v>
       </c>
       <c r="F1494" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1494" t="n">
         <v>0</v>
@@ -79874,21 +79874,21 @@
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
+          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
         </is>
       </c>
       <c r="C1495" t="inlineStr"/>
       <c r="D1495" t="inlineStr"/>
       <c r="E1495" t="n">
-        <v>11596.638655</v>
+        <v>4874</v>
       </c>
       <c r="F1495" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G1495" t="n">
         <v>0</v>
@@ -79924,21 +79924,21 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>TIJERA DE DOBLAR METALICA</t>
+          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
         </is>
       </c>
       <c r="C1496" t="inlineStr"/>
       <c r="D1496" t="inlineStr"/>
       <c r="E1496" t="n">
-        <v>3500</v>
+        <v>28800</v>
       </c>
       <c r="F1496" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1496" t="n">
         <v>0</v>
@@ -79974,21 +79974,21 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr"/>
       <c r="D1497" t="inlineStr"/>
       <c r="E1497" t="n">
-        <v>3781.512605</v>
+        <v>11596.638655</v>
       </c>
       <c r="F1497" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1497" t="n">
         <v>0</v>
@@ -80024,21 +80024,21 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+          <t>TIJERA DE DOBLAR METALICA</t>
         </is>
       </c>
       <c r="C1498" t="inlineStr"/>
       <c r="D1498" t="inlineStr"/>
       <c r="E1498" t="n">
-        <v>29800</v>
+        <v>3500</v>
       </c>
       <c r="F1498" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1498" t="n">
         <v>0</v>
@@ -80074,22 +80074,18 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
-        </is>
-      </c>
-      <c r="C1499" t="inlineStr">
-        <is>
-          <t>7702026149567</t>
-        </is>
-      </c>
+          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr"/>
       <c r="D1499" t="inlineStr"/>
       <c r="E1499" t="n">
-        <v>13500</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1499" t="n">
         <v>2</v>
@@ -80120,7 +80116,7 @@
       </c>
       <c r="M1499" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1499" t="inlineStr"/>
@@ -80128,25 +80124,21 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>Toallas húmedas winny 24unidades</t>
-        </is>
-      </c>
-      <c r="C1500" t="inlineStr">
-        <is>
-          <t>7701021143655</t>
-        </is>
-      </c>
+          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr"/>
       <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="n">
-        <v>4033.613445</v>
+        <v>29800</v>
       </c>
       <c r="F1500" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G1500" t="n">
         <v>0</v>
@@ -80174,7 +80166,7 @@
       </c>
       <c r="M1500" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1500" t="inlineStr"/>
@@ -80182,25 +80174,25 @@
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>Toallas maternas maternity</t>
+          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
         </is>
       </c>
       <c r="C1501" t="inlineStr">
         <is>
-          <t>7703252489526</t>
+          <t>7702026149567</t>
         </is>
       </c>
       <c r="D1501" t="inlineStr"/>
       <c r="E1501" t="n">
-        <v>16900</v>
+        <v>13500</v>
       </c>
       <c r="F1501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1501" t="n">
         <v>0</v>
@@ -80236,25 +80228,25 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>Toallas Nosotras Rapigel x Und</t>
+          <t>Toallas húmedas winny 24unidades</t>
         </is>
       </c>
       <c r="C1502" t="inlineStr">
         <is>
-          <t>7702027416859</t>
+          <t>7701021143655</t>
         </is>
       </c>
       <c r="D1502" t="inlineStr"/>
       <c r="E1502" t="n">
-        <v>756.302521</v>
+        <v>4033.613445</v>
       </c>
       <c r="F1502" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="G1502" t="n">
         <v>0</v>
@@ -80290,21 +80282,25 @@
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>TRAMADOL 50MG CAPSULA MP</t>
-        </is>
-      </c>
-      <c r="C1503" t="inlineStr"/>
+          <t>Toallas maternas maternity</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>7703252489526</t>
+        </is>
+      </c>
       <c r="D1503" t="inlineStr"/>
       <c r="E1503" t="n">
-        <v>1500</v>
+        <v>16900</v>
       </c>
       <c r="F1503" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G1503" t="n">
         <v>0</v>
@@ -80340,25 +80336,25 @@
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>Tramadol clorhidrato 100mg laquifar</t>
+          <t>Toallas Nosotras Rapigel x Und</t>
         </is>
       </c>
       <c r="C1504" t="inlineStr">
         <is>
-          <t>7707019426977</t>
+          <t>7702027416859</t>
         </is>
       </c>
       <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="n">
-        <v>1600</v>
+        <v>756.302521</v>
       </c>
       <c r="F1504" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G1504" t="n">
         <v>0</v>
@@ -80386,7 +80382,7 @@
       </c>
       <c r="M1504" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1504" t="inlineStr"/>
@@ -80394,21 +80390,21 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>TRIGENTAX CREMA TBO X 20GR</t>
+          <t>TRAMADOL 50MG CAPSULA MP</t>
         </is>
       </c>
       <c r="C1505" t="inlineStr"/>
       <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="n">
-        <v>33500</v>
+        <v>1500</v>
       </c>
       <c r="F1505" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G1505" t="n">
         <v>0</v>
@@ -80444,21 +80440,25 @@
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
-        </is>
-      </c>
-      <c r="C1506" t="inlineStr"/>
+          <t>Tramadol clorhidrato 100mg laquifar</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>7707019426977</t>
+        </is>
+      </c>
       <c r="D1506" t="inlineStr"/>
       <c r="E1506" t="n">
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="F1506" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1506" t="n">
         <v>0</v>
@@ -80494,21 +80494,21 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
+          <t>TRIGENTAX CREMA TBO X 20GR</t>
         </is>
       </c>
       <c r="C1507" t="inlineStr"/>
       <c r="D1507" t="inlineStr"/>
       <c r="E1507" t="n">
-        <v>10500</v>
+        <v>33500</v>
       </c>
       <c r="F1507" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1507" t="n">
         <v>0</v>
@@ -80544,21 +80544,21 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
+          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr"/>
       <c r="D1508" t="inlineStr"/>
       <c r="E1508" t="n">
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="F1508" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G1508" t="n">
         <v>0</v>
@@ -80594,21 +80594,21 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
+          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
         </is>
       </c>
       <c r="C1509" t="inlineStr"/>
       <c r="D1509" t="inlineStr"/>
       <c r="E1509" t="n">
-        <v>18800</v>
+        <v>10500</v>
       </c>
       <c r="F1509" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1509" t="n">
         <v>0</v>
@@ -80644,21 +80644,21 @@
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
+          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr"/>
       <c r="D1510" t="inlineStr"/>
       <c r="E1510" t="n">
-        <v>13800</v>
+        <v>10500</v>
       </c>
       <c r="F1510" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G1510" t="n">
         <v>0</v>
@@ -80694,21 +80694,21 @@
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
+          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
         </is>
       </c>
       <c r="C1511" t="inlineStr"/>
       <c r="D1511" t="inlineStr"/>
       <c r="E1511" t="n">
-        <v>7900</v>
+        <v>18800</v>
       </c>
       <c r="F1511" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1511" t="n">
         <v>0</v>
@@ -80744,21 +80744,21 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>VASELINA FC X 200GR YOMA</t>
+          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
         </is>
       </c>
       <c r="C1512" t="inlineStr"/>
       <c r="D1512" t="inlineStr"/>
       <c r="E1512" t="n">
-        <v>12521.008403</v>
+        <v>13800</v>
       </c>
       <c r="F1512" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1512" t="n">
         <v>0</v>
@@ -80786,7 +80786,7 @@
       </c>
       <c r="M1512" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1512" t="inlineStr"/>
@@ -80794,21 +80794,21 @@
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
+          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
         </is>
       </c>
       <c r="C1513" t="inlineStr"/>
       <c r="D1513" t="inlineStr"/>
       <c r="E1513" t="n">
-        <v>420.168067</v>
+        <v>7900</v>
       </c>
       <c r="F1513" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1513" t="n">
         <v>0</v>
@@ -80836,7 +80836,7 @@
       </c>
       <c r="M1513" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1513" t="inlineStr"/>
@@ -80844,22 +80844,18 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
-        </is>
-      </c>
-      <c r="C1514" t="inlineStr">
-        <is>
-          <t>7708480649803</t>
-        </is>
-      </c>
+          <t>VASELINA FC X 200GR YOMA</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr"/>
       <c r="D1514" t="inlineStr"/>
       <c r="E1514" t="n">
-        <v>28000</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1514" t="n">
         <v>0</v>
@@ -80890,7 +80886,7 @@
       </c>
       <c r="M1514" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1514" t="inlineStr"/>
@@ -80898,25 +80894,21 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>Venda Elastica 6x5 y piel</t>
+          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
         </is>
       </c>
       <c r="C1515" t="inlineStr"/>
-      <c r="D1515" t="inlineStr">
-        <is>
-          <t>SUBIO A 6200 ANTES 5700</t>
-        </is>
-      </c>
+      <c r="D1515" t="inlineStr"/>
       <c r="E1515" t="n">
-        <v>6200</v>
+        <v>420.168067</v>
       </c>
       <c r="F1515" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1515" t="n">
         <v>0</v>
@@ -80944,7 +80936,7 @@
       </c>
       <c r="M1515" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1515" t="inlineStr"/>
@@ -80952,21 +80944,25 @@
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
-        </is>
-      </c>
-      <c r="C1516" t="inlineStr"/>
+          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>7708480649803</t>
+        </is>
+      </c>
       <c r="D1516" t="inlineStr"/>
       <c r="E1516" t="n">
-        <v>5500</v>
+        <v>28000</v>
       </c>
       <c r="F1516" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1516" t="n">
         <v>0</v>
@@ -81002,21 +80998,25 @@
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>Venta simple</t>
+          <t>Venda Elastica 6x5 y piel</t>
         </is>
       </c>
       <c r="C1517" t="inlineStr"/>
-      <c r="D1517" t="inlineStr"/>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>SUBIO A 6200 ANTES 5700</t>
+        </is>
+      </c>
       <c r="E1517" t="n">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="F1517" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1517" t="n">
         <v>0</v>
@@ -81034,7 +81034,7 @@
       </c>
       <c r="K1517" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="L1517" t="inlineStr">
@@ -81042,24 +81042,28 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1517" t="inlineStr"/>
+      <c r="M1517" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1517" t="inlineStr"/>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
+          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr"/>
       <c r="D1518" t="inlineStr"/>
       <c r="E1518" t="n">
-        <v>1000</v>
+        <v>5500</v>
       </c>
       <c r="F1518" t="n">
         <v>3</v>
@@ -81098,25 +81102,21 @@
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
-        </is>
-      </c>
-      <c r="C1519" t="inlineStr">
-        <is>
-          <t>793969226467</t>
-        </is>
-      </c>
+          <t>Venta simple</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr"/>
       <c r="D1519" t="inlineStr"/>
       <c r="E1519" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="F1519" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1519" t="n">
         <v>0</v>
@@ -81134,39 +81134,35 @@
       </c>
       <c r="K1519" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="L1519" t="inlineStr">
         <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="M1519" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1519" t="inlineStr"/>
       <c r="N1519" t="inlineStr"/>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>VINO CEREBRAL JARABE X 1100ML</t>
+          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
         </is>
       </c>
       <c r="C1520" t="inlineStr"/>
       <c r="D1520" t="inlineStr"/>
       <c r="E1520" t="n">
-        <v>48900</v>
+        <v>1000</v>
       </c>
       <c r="F1520" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1520" t="n">
         <v>0</v>
@@ -81202,21 +81198,25 @@
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
-        </is>
-      </c>
-      <c r="C1521" t="inlineStr"/>
+          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>793969226467</t>
+        </is>
+      </c>
       <c r="D1521" t="inlineStr"/>
       <c r="E1521" t="n">
-        <v>5400</v>
+        <v>17000</v>
       </c>
       <c r="F1521" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G1521" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
       </c>
       <c r="L1521" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="M1521" t="inlineStr">
@@ -81252,21 +81252,21 @@
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
+          <t>VINO CEREBRAL JARABE X 1100ML</t>
         </is>
       </c>
       <c r="C1522" t="inlineStr"/>
       <c r="D1522" t="inlineStr"/>
       <c r="E1522" t="n">
-        <v>5500</v>
+        <v>48900</v>
       </c>
       <c r="F1522" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G1522" t="n">
         <v>0</v>
@@ -81302,21 +81302,21 @@
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>WINNY PAÑAL ETP 6 X 30</t>
+          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
         </is>
       </c>
       <c r="C1523" t="inlineStr"/>
       <c r="D1523" t="inlineStr"/>
       <c r="E1523" t="n">
-        <v>57000</v>
+        <v>5400</v>
       </c>
       <c r="F1523" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G1523" t="n">
         <v>0</v>
@@ -81352,52 +81352,152 @@
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>YODO BLANCO FC X30ML</t>
+          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
         </is>
       </c>
       <c r="C1524" t="inlineStr"/>
       <c r="D1524" t="inlineStr"/>
       <c r="E1524" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F1524" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1524" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1524" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1524" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1524" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1524" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1524" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1524" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1524" t="inlineStr"/>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>WINNY PAÑAL ETP 6 X 30</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr"/>
+      <c r="D1525" t="inlineStr"/>
+      <c r="E1525" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F1525" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1525" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1525" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1525" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1525" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1525" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1525" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1525" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1525" t="inlineStr"/>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>YODO BLANCO FC X30ML</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr"/>
+      <c r="D1526" t="inlineStr"/>
+      <c r="E1526" t="n">
         <v>6000</v>
       </c>
-      <c r="F1524" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1524" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1524" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1524" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1524" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="K1524" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="L1524" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="M1524" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="N1524" t="inlineStr"/>
+      <c r="F1526" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1526" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1526" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1526" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1526" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1526" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1526" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1526" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1526" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -3901,7 +3901,7 @@
         <v>5800</v>
       </c>
       <c r="F66" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -10279,7 +10279,7 @@
         <v>4000</v>
       </c>
       <c r="F185" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -11115,7 +11115,7 @@
         <v>14900</v>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -14023,7 +14023,7 @@
         <v>672</v>
       </c>
       <c r="F255" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -14077,7 +14077,7 @@
         <v>840.336134</v>
       </c>
       <c r="F256" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -14771,7 +14771,7 @@
         <v>6000</v>
       </c>
       <c r="F269" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -17835,7 +17835,7 @@
         <v>1500</v>
       </c>
       <c r="F325" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G325" t="n">
         <v>0</v>
@@ -22741,7 +22741,7 @@
         <v>5000</v>
       </c>
       <c r="F418" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G418" t="n">
         <v>0</v>
@@ -23161,7 +23161,7 @@
         <v>2200</v>
       </c>
       <c r="F426" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G426" t="n">
         <v>0</v>
@@ -23577,7 +23577,7 @@
         <v>3300</v>
       </c>
       <c r="F434" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G434" t="n">
         <v>0</v>
@@ -30237,7 +30237,7 @@
         <v>9000</v>
       </c>
       <c r="F558" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G558" t="n">
         <v>0</v>
@@ -31845,7 +31845,7 @@
         <v>3000</v>
       </c>
       <c r="F588" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G588" t="n">
         <v>0</v>
@@ -31903,7 +31903,7 @@
         <v>2500</v>
       </c>
       <c r="F589" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G589" t="n">
         <v>0</v>
@@ -37285,7 +37285,7 @@
         <v>27563.02521</v>
       </c>
       <c r="F690" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G690" t="n">
         <v>0</v>
@@ -37879,7 +37879,7 @@
         <v>2857</v>
       </c>
       <c r="F701" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G701" t="n">
         <v>0</v>
@@ -39047,7 +39047,7 @@
         <v>2352.941176</v>
       </c>
       <c r="F723" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G723" t="n">
         <v>0</v>
@@ -43913,7 +43913,7 @@
         <v>27900</v>
       </c>
       <c r="F814" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G814" t="n">
         <v>0</v>
@@ -47569,7 +47569,7 @@
         <v>1800</v>
       </c>
       <c r="F882" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G882" t="n">
         <v>0</v>
@@ -49963,7 +49963,7 @@
         <v>1200</v>
       </c>
       <c r="F927" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G927" t="n">
         <v>0</v>
@@ -51543,7 +51543,7 @@
         <v>10500</v>
       </c>
       <c r="F957" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G957" t="n">
         <v>0</v>
@@ -55072,7 +55072,7 @@
         <v>3200</v>
       </c>
       <c r="F1023" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1023" t="n">
         <v>0</v>
@@ -62558,7 +62558,7 @@
         <v>20000</v>
       </c>
       <c r="F1162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1162" t="n">
         <v>0</v>
@@ -71236,7 +71236,7 @@
         <v>12000</v>
       </c>
       <c r="F1327" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1327" t="n">
         <v>0</v>
@@ -75282,7 +75282,7 @@
         <v>3200</v>
       </c>
       <c r="F1406" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1406" t="n">
         <v>0</v>
@@ -78506,7 +78506,7 @@
         <v>673</v>
       </c>
       <c r="F1468" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G1468" t="n">
         <v>0</v>
@@ -79180,7 +79180,7 @@
         <v>2000</v>
       </c>
       <c r="F1481" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G1481" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -14239,7 +14239,7 @@
         <v>840.336134</v>
       </c>
       <c r="F259" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G259" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
         <v>840</v>
       </c>
       <c r="F284" t="n">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G284" t="n">
         <v>0</v>
@@ -21715,7 +21715,7 @@
         <v>3500</v>
       </c>
       <c r="F399" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G399" t="n">
         <v>0</v>
@@ -22741,7 +22741,7 @@
         <v>5000</v>
       </c>
       <c r="F418" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G418" t="n">
         <v>0</v>
@@ -23365,7 +23365,7 @@
         <v>2000</v>
       </c>
       <c r="F430" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G430" t="n">
         <v>0</v>
@@ -27283,7 +27283,7 @@
         <v>2500</v>
       </c>
       <c r="F503" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G503" t="n">
         <v>0</v>
@@ -32725,7 +32725,7 @@
         <v>2900</v>
       </c>
       <c r="F604" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G604" t="n">
         <v>0</v>
@@ -33835,7 +33835,7 @@
         <v>1200</v>
       </c>
       <c r="F625" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="G625" t="n">
         <v>0</v>
@@ -41787,7 +41787,7 @@
         <v>5500</v>
       </c>
       <c r="F775" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G775" t="n">
         <v>0</v>
@@ -43191,7 +43191,7 @@
         <v>17000</v>
       </c>
       <c r="F801" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G801" t="n">
         <v>0</v>
@@ -46867,7 +46867,7 @@
         <v>3620</v>
       </c>
       <c r="F869" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G869" t="n">
         <v>0</v>
@@ -50595,7 +50595,7 @@
         <v>4400</v>
       </c>
       <c r="F939" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G939" t="n">
         <v>0</v>
@@ -51311,7 +51311,7 @@
         <v>2200</v>
       </c>
       <c r="F953" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G953" t="n">
         <v>0</v>
@@ -55616,7 +55616,7 @@
         <v>3900</v>
       </c>
       <c r="F1033" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G1033" t="n">
         <v>0</v>
@@ -59164,7 +59164,7 @@
         <v>13025.210084</v>
       </c>
       <c r="F1099" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1099" t="n">
         <v>0</v>
@@ -60622,7 +60622,7 @@
         <v>1900</v>
       </c>
       <c r="F1126" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G1126" t="n">
         <v>0</v>
@@ -61532,7 +61532,7 @@
         <v>11800</v>
       </c>
       <c r="F1143" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1143" t="n">
         <v>0</v>
@@ -63688,7 +63688,7 @@
         <v>4000</v>
       </c>
       <c r="F1183" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1183" t="n">
         <v>0</v>
@@ -69446,7 +69446,7 @@
         <v>19200</v>
       </c>
       <c r="F1292" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1292" t="n">
         <v>0</v>
@@ -69958,7 +69958,7 @@
         <v>8900</v>
       </c>
       <c r="F1302" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1302" t="n">
         <v>0</v>
@@ -70674,7 +70674,7 @@
         <v>300</v>
       </c>
       <c r="F1316" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G1316" t="n">
         <v>0</v>
@@ -72776,7 +72776,7 @@
         <v>3361.344538</v>
       </c>
       <c r="F1357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1357" t="n">
         <v>0</v>
@@ -75764,7 +75764,7 @@
         <v>3900</v>
       </c>
       <c r="F1415" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1415" t="n">
         <v>0</v>
@@ -76172,7 +76172,7 @@
         <v>23000</v>
       </c>
       <c r="F1423" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1423" t="n">
         <v>0</v>
@@ -81016,7 +81016,7 @@
         <v>6200</v>
       </c>
       <c r="F1517" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1517" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -6315,7 +6315,7 @@
         <v>15500</v>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -10279,7 +10279,7 @@
         <v>4000</v>
       </c>
       <c r="F185" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -11747,7 +11747,7 @@
         <v>4800</v>
       </c>
       <c r="F213" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -14771,7 +14771,7 @@
         <v>6000</v>
       </c>
       <c r="F269" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -18093,7 +18093,7 @@
         <v>6723</v>
       </c>
       <c r="F330" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G330" t="n">
         <v>0</v>
@@ -23365,7 +23365,7 @@
         <v>2000</v>
       </c>
       <c r="F430" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G430" t="n">
         <v>0</v>
@@ -26967,7 +26967,7 @@
         <v>504.2</v>
       </c>
       <c r="F497" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G497" t="n">
         <v>0</v>
@@ -31571,7 +31571,7 @@
         <v>2800</v>
       </c>
       <c r="F583" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G583" t="n">
         <v>0</v>
@@ -31845,7 +31845,7 @@
         <v>3000</v>
       </c>
       <c r="F588" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G588" t="n">
         <v>0</v>
@@ -42323,7 +42323,7 @@
         <v>5500</v>
       </c>
       <c r="F785" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G785" t="n">
         <v>0</v>
@@ -42377,7 +42377,7 @@
         <v>2300</v>
       </c>
       <c r="F786" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G786" t="n">
         <v>0</v>
@@ -48213,7 +48213,7 @@
         <v>5500</v>
       </c>
       <c r="F894" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G894" t="n">
         <v>0</v>
@@ -60348,7 +60348,7 @@
         <v>6300</v>
       </c>
       <c r="F1121" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G1121" t="n">
         <v>0</v>
@@ -62504,7 +62504,7 @@
         <v>14700</v>
       </c>
       <c r="F1161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1161" t="n">
         <v>0</v>
@@ -67686,7 +67686,7 @@
         <v>53700</v>
       </c>
       <c r="F1258" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1258" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -3901,7 +3901,7 @@
         <v>5800</v>
       </c>
       <c r="F66" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
         <v>840</v>
       </c>
       <c r="F284" t="n">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G284" t="n">
         <v>0</v>
@@ -17835,7 +17835,7 @@
         <v>1500</v>
       </c>
       <c r="F325" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G325" t="n">
         <v>0</v>
@@ -21715,7 +21715,7 @@
         <v>3500</v>
       </c>
       <c r="F399" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G399" t="n">
         <v>0</v>
@@ -22741,7 +22741,7 @@
         <v>5000</v>
       </c>
       <c r="F418" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G418" t="n">
         <v>0</v>
@@ -23365,7 +23365,7 @@
         <v>2000</v>
       </c>
       <c r="F430" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G430" t="n">
         <v>0</v>
@@ -32115,7 +32115,7 @@
         <v>2200</v>
       </c>
       <c r="F593" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G593" t="n">
         <v>0</v>
@@ -32555,7 +32555,7 @@
         <v>1700</v>
       </c>
       <c r="F601" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G601" t="n">
         <v>0</v>
@@ -32613,7 +32613,7 @@
         <v>2200</v>
       </c>
       <c r="F602" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G602" t="n">
         <v>0</v>
@@ -32941,7 +32941,7 @@
         <v>3700</v>
       </c>
       <c r="F608" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G608" t="n">
         <v>0</v>
@@ -33835,7 +33835,7 @@
         <v>1200</v>
       </c>
       <c r="F625" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G625" t="n">
         <v>0</v>
@@ -38727,7 +38727,7 @@
         <v>3781.512605</v>
       </c>
       <c r="F717" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G717" t="n">
         <v>0</v>
@@ -42377,7 +42377,7 @@
         <v>2300</v>
       </c>
       <c r="F786" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G786" t="n">
         <v>0</v>
@@ -43245,7 +43245,7 @@
         <v>6500</v>
       </c>
       <c r="F802" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G802" t="n">
         <v>0</v>
@@ -43635,7 +43635,7 @@
         <v>9700</v>
       </c>
       <c r="F809" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G809" t="n">
         <v>0</v>
@@ -44681,7 +44681,7 @@
         <v>21764.705882</v>
       </c>
       <c r="F828" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G828" t="n">
         <v>0</v>
@@ -46389,7 +46389,7 @@
         <v>3000</v>
       </c>
       <c r="F860" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G860" t="n">
         <v>0</v>
@@ -47569,7 +47569,7 @@
         <v>1800</v>
       </c>
       <c r="F882" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G882" t="n">
         <v>0</v>
@@ -48583,7 +48583,7 @@
         <v>3500</v>
       </c>
       <c r="F901" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G901" t="n">
         <v>0</v>
@@ -50275,7 +50275,7 @@
         <v>2300</v>
       </c>
       <c r="F933" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G933" t="n">
         <v>0</v>
@@ -50595,7 +50595,7 @@
         <v>4400</v>
       </c>
       <c r="F939" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G939" t="n">
         <v>0</v>
@@ -55616,7 +55616,7 @@
         <v>3900</v>
       </c>
       <c r="F1033" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G1033" t="n">
         <v>0</v>
@@ -55670,7 +55670,7 @@
         <v>3500</v>
       </c>
       <c r="F1034" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G1034" t="n">
         <v>0</v>
@@ -68784,7 +68784,7 @@
         <v>10800</v>
       </c>
       <c r="F1279" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1279" t="n">
         <v>0</v>
@@ -72472,7 +72472,7 @@
         <v>3800</v>
       </c>
       <c r="F1351" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1351" t="n">
         <v>0</v>
@@ -75282,7 +75282,7 @@
         <v>3200</v>
       </c>
       <c r="F1406" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1406" t="n">
         <v>0</v>
@@ -80508,7 +80508,7 @@
         <v>33500</v>
       </c>
       <c r="F1507" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1507" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -7325,7 +7325,7 @@
         <v>26000</v>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -31737,7 +31737,7 @@
         <v>2500</v>
       </c>
       <c r="F586" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G586" t="n">
         <v>0</v>
@@ -32775,7 +32775,7 @@
         <v>2800</v>
       </c>
       <c r="F605" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G605" t="n">
         <v>0</v>
@@ -37721,7 +37721,7 @@
         <v>2200</v>
       </c>
       <c r="F698" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G698" t="n">
         <v>0</v>
@@ -42377,7 +42377,7 @@
         <v>2300</v>
       </c>
       <c r="F786" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G786" t="n">
         <v>0</v>
@@ -46975,7 +46975,7 @@
         <v>2700</v>
       </c>
       <c r="F871" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G871" t="n">
         <v>0</v>
@@ -47569,7 +47569,7 @@
         <v>1800</v>
       </c>
       <c r="F882" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G882" t="n">
         <v>0</v>
@@ -49963,7 +49963,7 @@
         <v>1200</v>
       </c>
       <c r="F927" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G927" t="n">
         <v>0</v>
@@ -50595,7 +50595,7 @@
         <v>4400</v>
       </c>
       <c r="F939" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G939" t="n">
         <v>0</v>
@@ -55072,7 +55072,7 @@
         <v>3200</v>
       </c>
       <c r="F1023" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1023" t="n">
         <v>0</v>
@@ -57825,9 +57825,13 @@
           <t>´7707019334203</t>
         </is>
       </c>
-      <c r="D1074" t="inlineStr"/>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>SUBIO A 25900 ANTES 24200</t>
+        </is>
+      </c>
       <c r="E1074" t="n">
-        <v>24200</v>
+        <v>25900</v>
       </c>
       <c r="F1074" t="n">
         <v>1</v>
@@ -59380,7 +59384,7 @@
         <v>9000</v>
       </c>
       <c r="F1103" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1103" t="n">
         <v>0</v>
@@ -60950,7 +60954,7 @@
         <v>6134.453782</v>
       </c>
       <c r="F1132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1132" t="n">
         <v>0</v>
@@ -66908,7 +66912,7 @@
         <v>2500</v>
       </c>
       <c r="F1243" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1243" t="n">
         <v>0</v>
@@ -72472,7 +72476,7 @@
         <v>3800</v>
       </c>
       <c r="F1351" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G1351" t="n">
         <v>0</v>
@@ -75282,7 +75286,7 @@
         <v>3200</v>
       </c>
       <c r="F1406" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1406" t="n">
         <v>0</v>
@@ -75972,7 +75976,7 @@
         <v>22700</v>
       </c>
       <c r="F1419" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1419" t="n">
         <v>0</v>
@@ -80758,7 +80762,7 @@
         <v>13800</v>
       </c>
       <c r="F1512" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1512" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -2471,7 +2471,7 @@
         <v>6600</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -4579,7 +4579,7 @@
         <v>3361.344538</v>
       </c>
       <c r="F79" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -9785,7 +9785,7 @@
         <v>8900</v>
       </c>
       <c r="F176" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -10279,7 +10279,7 @@
         <v>4000</v>
       </c>
       <c r="F185" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -11635,7 +11635,7 @@
         <v>3200</v>
       </c>
       <c r="F211" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -14023,7 +14023,7 @@
         <v>672</v>
       </c>
       <c r="F255" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -14077,7 +14077,7 @@
         <v>840.336134</v>
       </c>
       <c r="F256" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -20195,7 +20195,7 @@
         <v>16800</v>
       </c>
       <c r="F371" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G371" t="n">
         <v>0</v>
@@ -20569,7 +20569,7 @@
         <v>18800</v>
       </c>
       <c r="F378" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G378" t="n">
         <v>0</v>
@@ -20731,7 +20731,7 @@
         <v>9000</v>
       </c>
       <c r="F381" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G381" t="n">
         <v>0</v>
@@ -23161,7 +23161,7 @@
         <v>2200</v>
       </c>
       <c r="F426" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G426" t="n">
         <v>0</v>
@@ -23261,7 +23261,7 @@
         <v>1900</v>
       </c>
       <c r="F428" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G428" t="n">
         <v>0</v>
@@ -26315,7 +26315,7 @@
         <v>1500</v>
       </c>
       <c r="F485" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G485" t="n">
         <v>0</v>
@@ -28459,7 +28459,7 @@
         <v>7200</v>
       </c>
       <c r="F525" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G525" t="n">
         <v>0</v>
@@ -31301,7 +31301,7 @@
         <v>3400</v>
       </c>
       <c r="F578" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G578" t="n">
         <v>0</v>
@@ -31845,7 +31845,7 @@
         <v>3000</v>
       </c>
       <c r="F588" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G588" t="n">
         <v>0</v>
@@ -34479,7 +34479,7 @@
         <v>8400</v>
       </c>
       <c r="F637" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G637" t="n">
         <v>0</v>
@@ -50275,7 +50275,7 @@
         <v>2300</v>
       </c>
       <c r="F933" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G933" t="n">
         <v>0</v>
@@ -55072,7 +55072,7 @@
         <v>3200</v>
       </c>
       <c r="F1023" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G1023" t="n">
         <v>0</v>
@@ -55670,7 +55670,7 @@
         <v>3500</v>
       </c>
       <c r="F1034" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G1034" t="n">
         <v>0</v>
@@ -56318,7 +56318,7 @@
         <v>14000</v>
       </c>
       <c r="F1046" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1046" t="n">
         <v>0</v>
@@ -57834,7 +57834,7 @@
         <v>25900</v>
       </c>
       <c r="F1074" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1074" t="n">
         <v>0</v>
@@ -58740,7 +58740,7 @@
         <v>2900</v>
       </c>
       <c r="F1091" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1091" t="n">
         <v>0</v>
@@ -60352,7 +60352,7 @@
         <v>6300</v>
       </c>
       <c r="F1121" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G1121" t="n">
         <v>0</v>
@@ -61428,7 +61428,7 @@
         <v>6900</v>
       </c>
       <c r="F1141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1141" t="n">
         <v>0</v>
@@ -64842,7 +64842,7 @@
         <v>9300</v>
       </c>
       <c r="F1204" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1204" t="n">
         <v>0</v>
@@ -66862,7 +66862,7 @@
         <v>2200</v>
       </c>
       <c r="F1242" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G1242" t="n">
         <v>0</v>
@@ -69962,7 +69962,7 @@
         <v>8900</v>
       </c>
       <c r="F1302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1302" t="n">
         <v>0</v>
@@ -75286,7 +75286,7 @@
         <v>3200</v>
       </c>
       <c r="F1406" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1406" t="n">
         <v>0</v>
@@ -81320,7 +81320,7 @@
         <v>5400</v>
       </c>
       <c r="F1523" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1523" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -6947,7 +6947,7 @@
         <v>29000</v>
       </c>
       <c r="F123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -10279,7 +10279,7 @@
         <v>4000</v>
       </c>
       <c r="F185" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -14023,7 +14023,7 @@
         <v>672</v>
       </c>
       <c r="F255" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -14941,7 +14941,7 @@
         <v>12300</v>
       </c>
       <c r="F272" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G272" t="n">
         <v>0</v>
@@ -15381,7 +15381,7 @@
         <v>7800</v>
       </c>
       <c r="F280" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
@@ -20731,7 +20731,7 @@
         <v>9000</v>
       </c>
       <c r="F381" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G381" t="n">
         <v>0</v>
@@ -22251,7 +22251,7 @@
         <v>7900</v>
       </c>
       <c r="F409" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G409" t="n">
         <v>0</v>
@@ -22575,7 +22575,7 @@
         <v>7000</v>
       </c>
       <c r="F415" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G415" t="n">
         <v>0</v>
@@ -29045,7 +29045,7 @@
         <v>12500</v>
       </c>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G536" t="n">
         <v>0</v>
@@ -30873,7 +30873,7 @@
         <v>1000</v>
       </c>
       <c r="F570" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G570" t="n">
         <v>0</v>
@@ -31301,7 +31301,7 @@
         <v>3400</v>
       </c>
       <c r="F578" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G578" t="n">
         <v>0</v>
@@ -31571,7 +31571,7 @@
         <v>2800</v>
       </c>
       <c r="F583" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G583" t="n">
         <v>0</v>
@@ -31625,7 +31625,7 @@
         <v>2800</v>
       </c>
       <c r="F584" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G584" t="n">
         <v>0</v>
@@ -32115,7 +32115,7 @@
         <v>2200</v>
       </c>
       <c r="F593" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G593" t="n">
         <v>0</v>
@@ -32725,7 +32725,7 @@
         <v>2900</v>
       </c>
       <c r="F604" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G604" t="n">
         <v>0</v>
@@ -33835,7 +33835,7 @@
         <v>1200</v>
       </c>
       <c r="F625" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G625" t="n">
         <v>0</v>
@@ -35123,7 +35123,7 @@
         <v>3500</v>
       </c>
       <c r="F649" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G649" t="n">
         <v>0</v>
@@ -39047,7 +39047,7 @@
         <v>2352.941176</v>
       </c>
       <c r="F723" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G723" t="n">
         <v>0</v>
@@ -42377,7 +42377,7 @@
         <v>2300</v>
       </c>
       <c r="F786" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G786" t="n">
         <v>0</v>
@@ -42705,7 +42705,7 @@
         <v>8900</v>
       </c>
       <c r="F792" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G792" t="n">
         <v>0</v>
@@ -44025,7 +44025,7 @@
         <v>20500</v>
       </c>
       <c r="F816" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G816" t="n">
         <v>0</v>
@@ -49963,7 +49963,7 @@
         <v>1200</v>
       </c>
       <c r="F927" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G927" t="n">
         <v>0</v>
@@ -58740,7 +58740,7 @@
         <v>2900</v>
       </c>
       <c r="F1091" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1091" t="n">
         <v>0</v>
@@ -64186,7 +64186,7 @@
         <v>4800</v>
       </c>
       <c r="F1192" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1192" t="n">
         <v>0</v>
@@ -71648,7 +71648,7 @@
         <v>2000</v>
       </c>
       <c r="F1335" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G1335" t="n">
         <v>0</v>
@@ -72934,7 +72934,7 @@
         <v>24369.747899</v>
       </c>
       <c r="F1360" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G1360" t="n">
         <v>0</v>
@@ -76026,7 +76026,7 @@
         <v>5500</v>
       </c>
       <c r="F1420" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G1420" t="n">
         <v>0</v>
@@ -78510,7 +78510,7 @@
         <v>673</v>
       </c>
       <c r="F1468" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G1468" t="n">
         <v>0</v>
@@ -79026,7 +79026,7 @@
         <v>6554.621849</v>
       </c>
       <c r="F1478" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1478" t="n">
         <v>0</v>
@@ -79184,7 +79184,7 @@
         <v>2000</v>
       </c>
       <c r="F1481" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G1481" t="n">
         <v>0</v>
@@ -81370,7 +81370,7 @@
         <v>5500</v>
       </c>
       <c r="F1524" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G1524" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -3901,7 +3901,7 @@
         <v>5800</v>
       </c>
       <c r="F66" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -10279,7 +10279,7 @@
         <v>4000</v>
       </c>
       <c r="F185" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -12461,7 +12461,7 @@
         <v>3000</v>
       </c>
       <c r="F226" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -14771,7 +14771,7 @@
         <v>6000</v>
       </c>
       <c r="F269" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
         <v>840</v>
       </c>
       <c r="F284" t="n">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="G284" t="n">
         <v>0</v>
@@ -17835,7 +17835,7 @@
         <v>1500</v>
       </c>
       <c r="F325" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G325" t="n">
         <v>0</v>
@@ -18093,7 +18093,7 @@
         <v>6723</v>
       </c>
       <c r="F330" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G330" t="n">
         <v>0</v>
@@ -20731,7 +20731,7 @@
         <v>9000</v>
       </c>
       <c r="F381" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G381" t="n">
         <v>0</v>
@@ -22741,7 +22741,7 @@
         <v>5000</v>
       </c>
       <c r="F418" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G418" t="n">
         <v>0</v>
@@ -23365,7 +23365,7 @@
         <v>2000</v>
       </c>
       <c r="F430" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G430" t="n">
         <v>0</v>
@@ -23631,7 +23631,7 @@
         <v>2900</v>
       </c>
       <c r="F435" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G435" t="n">
         <v>0</v>
@@ -23685,7 +23685,7 @@
         <v>2900</v>
       </c>
       <c r="F436" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G436" t="n">
         <v>0</v>
@@ -24063,7 +24063,7 @@
         <v>2500</v>
       </c>
       <c r="F443" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G443" t="n">
         <v>0</v>
@@ -31845,7 +31845,7 @@
         <v>3000</v>
       </c>
       <c r="F588" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G588" t="n">
         <v>0</v>
@@ -32613,7 +32613,7 @@
         <v>2200</v>
       </c>
       <c r="F602" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G602" t="n">
         <v>0</v>
@@ -40905,7 +40905,7 @@
         <v>4369.75</v>
       </c>
       <c r="F758" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G758" t="n">
         <v>0</v>
@@ -42323,7 +42323,7 @@
         <v>5500</v>
       </c>
       <c r="F785" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G785" t="n">
         <v>0</v>
@@ -42759,7 +42759,7 @@
         <v>19500</v>
       </c>
       <c r="F793" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G793" t="n">
         <v>0</v>
@@ -49963,7 +49963,7 @@
         <v>1200</v>
       </c>
       <c r="F927" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G927" t="n">
         <v>0</v>
@@ -55670,7 +55670,7 @@
         <v>3500</v>
       </c>
       <c r="F1034" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1034" t="n">
         <v>0</v>
@@ -58636,7 +58636,7 @@
         <v>1600</v>
       </c>
       <c r="F1089" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G1089" t="n">
         <v>0</v>
@@ -60626,7 +60626,7 @@
         <v>1900</v>
       </c>
       <c r="F1126" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G1126" t="n">
         <v>0</v>
@@ -64186,7 +64186,7 @@
         <v>4800</v>
       </c>
       <c r="F1192" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1192" t="n">
         <v>0</v>
@@ -64460,7 +64460,7 @@
         <v>2700</v>
       </c>
       <c r="F1197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1197" t="n">
         <v>0</v>
@@ -66862,7 +66862,7 @@
         <v>2200</v>
       </c>
       <c r="F1242" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1242" t="n">
         <v>0</v>
@@ -70732,7 +70732,7 @@
         <v>28900</v>
       </c>
       <c r="F1317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1317" t="n">
         <v>0</v>
@@ -72476,7 +72476,7 @@
         <v>3800</v>
       </c>
       <c r="F1351" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G1351" t="n">
         <v>0</v>
@@ -75286,7 +75286,7 @@
         <v>3200</v>
       </c>
       <c r="F1406" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1406" t="n">
         <v>0</v>
@@ -75976,7 +75976,7 @@
         <v>22700</v>
       </c>
       <c r="F1419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1419" t="n">
         <v>0</v>
@@ -78510,7 +78510,7 @@
         <v>673</v>
       </c>
       <c r="F1468" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G1468" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -14023,7 +14023,7 @@
         <v>672</v>
       </c>
       <c r="F255" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -22251,7 +22251,7 @@
         <v>7900</v>
       </c>
       <c r="F409" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G409" t="n">
         <v>0</v>
@@ -24645,7 +24645,7 @@
         <v>4000</v>
       </c>
       <c r="F454" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G454" t="n">
         <v>0</v>
@@ -24981,7 +24981,7 @@
         <v>9200</v>
       </c>
       <c r="F460" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G460" t="n">
         <v>0</v>
@@ -30237,7 +30237,7 @@
         <v>9000</v>
       </c>
       <c r="F558" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G558" t="n">
         <v>0</v>
@@ -31409,7 +31409,7 @@
         <v>3300</v>
       </c>
       <c r="F580" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G580" t="n">
         <v>0</v>
@@ -34001,7 +34001,7 @@
         <v>4033.613445</v>
       </c>
       <c r="F628" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G628" t="n">
         <v>0</v>
@@ -38149,7 +38149,7 @@
         <v>5882.352941</v>
       </c>
       <c r="F706" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G706" t="n">
         <v>0</v>
@@ -43519,7 +43519,7 @@
         <v>8900</v>
       </c>
       <c r="F807" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G807" t="n">
         <v>0</v>
@@ -43967,7 +43967,7 @@
         <v>16000</v>
       </c>
       <c r="F815" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G815" t="n">
         <v>0</v>
@@ -46389,7 +46389,7 @@
         <v>3000</v>
       </c>
       <c r="F860" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G860" t="n">
         <v>0</v>
@@ -52894,7 +52894,7 @@
         <v>1500</v>
       </c>
       <c r="F982" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G982" t="n">
         <v>0</v>
@@ -66862,7 +66862,7 @@
         <v>2200</v>
       </c>
       <c r="F1242" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G1242" t="n">
         <v>0</v>
@@ -70678,7 +70678,7 @@
         <v>300</v>
       </c>
       <c r="F1316" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G1316" t="n">
         <v>0</v>
@@ -74366,7 +74366,7 @@
         <v>1100</v>
       </c>
       <c r="F1388" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G1388" t="n">
         <v>0</v>
@@ -76026,7 +76026,7 @@
         <v>5500</v>
       </c>
       <c r="F1420" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1420" t="n">
         <v>0</v>
@@ -78510,7 +78510,7 @@
         <v>673</v>
       </c>
       <c r="F1468" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G1468" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -32330,13 +32330,9 @@
           <t>´7702123006800</t>
         </is>
       </c>
-      <c r="D597" t="inlineStr">
-        <is>
-          <t>Subió de $700 a $800</t>
-        </is>
-      </c>
+      <c r="D597" t="inlineStr"/>
       <c r="E597" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="F597" t="n">
         <v>94</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -3901,7 +3901,7 @@
         <v>5800</v>
       </c>
       <c r="F66" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -11115,7 +11115,7 @@
         <v>14900</v>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -14667,7 +14667,7 @@
         <v>8900</v>
       </c>
       <c r="F267" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G267" t="n">
         <v>0</v>
@@ -17835,7 +17835,7 @@
         <v>1500</v>
       </c>
       <c r="F325" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G325" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
         <v>14900</v>
       </c>
       <c r="F405" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G405" t="n">
         <v>0</v>
@@ -22741,7 +22741,7 @@
         <v>5000</v>
       </c>
       <c r="F418" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G418" t="n">
         <v>0</v>
@@ -23161,7 +23161,7 @@
         <v>2200</v>
       </c>
       <c r="F426" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G426" t="n">
         <v>0</v>
@@ -24171,7 +24171,7 @@
         <v>2500</v>
       </c>
       <c r="F445" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G445" t="n">
         <v>0</v>
@@ -24815,7 +24815,7 @@
         <v>9200</v>
       </c>
       <c r="F457" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G457" t="n">
         <v>0</v>
@@ -31355,7 +31355,7 @@
         <v>1200</v>
       </c>
       <c r="F579" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G579" t="n">
         <v>0</v>
@@ -31845,7 +31845,7 @@
         <v>3000</v>
       </c>
       <c r="F588" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G588" t="n">
         <v>0</v>
@@ -32335,7 +32335,7 @@
         <v>900</v>
       </c>
       <c r="F597" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G597" t="n">
         <v>0</v>
@@ -49601,7 +49601,7 @@
         <v>672.268908</v>
       </c>
       <c r="F920" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G920" t="n">
         <v>0</v>
@@ -51922,7 +51922,7 @@
         <v>9200</v>
       </c>
       <c r="F964" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G964" t="n">
         <v>0</v>
@@ -55666,7 +55666,7 @@
         <v>3500</v>
       </c>
       <c r="F1034" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1034" t="n">
         <v>0</v>
@@ -58736,7 +58736,7 @@
         <v>2900</v>
       </c>
       <c r="F1091" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1091" t="n">
         <v>0</v>
@@ -70420,7 +70420,7 @@
         <v>10084.033613</v>
       </c>
       <c r="F1311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1311" t="n">
         <v>0</v>
@@ -70624,7 +70624,7 @@
         <v>2521.008403</v>
       </c>
       <c r="F1315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1315" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1526"/>
+  <dimension ref="A1:N1527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11747,7 +11747,7 @@
         <v>4800</v>
       </c>
       <c r="F213" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -14023,7 +14023,7 @@
         <v>672</v>
       </c>
       <c r="F255" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -15273,7 +15273,7 @@
         <v>9600</v>
       </c>
       <c r="F278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G278" t="n">
         <v>0</v>
@@ -21171,7 +21171,7 @@
         <v>14700</v>
       </c>
       <c r="F389" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G389" t="n">
         <v>0</v>
@@ -30819,7 +30819,7 @@
         <v>2000</v>
       </c>
       <c r="F569" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G569" t="n">
         <v>0</v>
@@ -42261,7 +42261,7 @@
         <v>2000</v>
       </c>
       <c r="F784" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G784" t="n">
         <v>0</v>
@@ -47565,7 +47565,7 @@
         <v>1800</v>
       </c>
       <c r="F882" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G882" t="n">
         <v>0</v>
@@ -51365,7 +51365,7 @@
         <v>9200</v>
       </c>
       <c r="F954" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G954" t="n">
         <v>0</v>
@@ -60402,7 +60402,7 @@
         <v>1200</v>
       </c>
       <c r="F1122" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G1122" t="n">
         <v>0</v>
@@ -63688,7 +63688,7 @@
         <v>4000</v>
       </c>
       <c r="F1183" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1183" t="n">
         <v>0</v>
@@ -64950,7 +64950,7 @@
         <v>3100</v>
       </c>
       <c r="F1206" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1206" t="n">
         <v>0</v>
@@ -69550,7 +69550,7 @@
         <v>27900</v>
       </c>
       <c r="F1294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1294" t="n">
         <v>0</v>
@@ -70728,7 +70728,7 @@
         <v>28900</v>
       </c>
       <c r="F1317" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1317" t="n">
         <v>0</v>
@@ -71730,25 +71730,25 @@
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>EXTRACTOR DE LECHE MOBY</t>
+          <t>ETORICOXIB 120MG GENFAR</t>
         </is>
       </c>
       <c r="C1337" t="inlineStr">
         <is>
-          <t>7707233051436</t>
+          <t>7702605109371</t>
         </is>
       </c>
       <c r="D1337" t="inlineStr"/>
       <c r="E1337" t="n">
-        <v>14285.714286</v>
+        <v>48600</v>
       </c>
       <c r="F1337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1337" t="n">
         <v>0</v>
@@ -71776,7 +71776,7 @@
       </c>
       <c r="M1337" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1337" t="inlineStr"/>
@@ -71784,25 +71784,25 @@
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>FAMIIA MEGARROLLO PAPEL HIGUIEN</t>
+          <t>EXTRACTOR DE LECHE MOBY</t>
         </is>
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>7702026147471</t>
+          <t>7707233051436</t>
         </is>
       </c>
       <c r="D1338" t="inlineStr"/>
       <c r="E1338" t="n">
-        <v>3500</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1338" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1338" t="n">
         <v>0</v>
@@ -71830,7 +71830,7 @@
       </c>
       <c r="M1338" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1338" t="inlineStr"/>
@@ -71838,21 +71838,25 @@
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>Farma D 500 UI</t>
-        </is>
-      </c>
-      <c r="C1339" t="inlineStr"/>
+          <t>FAMIIA MEGARROLLO PAPEL HIGUIEN</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>7702026147471</t>
+        </is>
+      </c>
       <c r="D1339" t="inlineStr"/>
       <c r="E1339" t="n">
-        <v>74000</v>
+        <v>3500</v>
       </c>
       <c r="F1339" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G1339" t="n">
         <v>0</v>
@@ -71888,21 +71892,21 @@
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>FIBRA AMARILLA ARMONIZA X 450GR</t>
+          <t>Farma D 500 UI</t>
         </is>
       </c>
       <c r="C1340" t="inlineStr"/>
       <c r="D1340" t="inlineStr"/>
       <c r="E1340" t="n">
-        <v>28571.428571</v>
+        <v>74000</v>
       </c>
       <c r="F1340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1340" t="n">
         <v>0</v>
@@ -71930,7 +71934,7 @@
       </c>
       <c r="M1340" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1340" t="inlineStr"/>
@@ -71938,21 +71942,21 @@
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>FIBRA DE AVENA Y SALVADO DE TRIGO 450GR</t>
+          <t>FIBRA AMARILLA ARMONIZA X 450GR</t>
         </is>
       </c>
       <c r="C1341" t="inlineStr"/>
       <c r="D1341" t="inlineStr"/>
       <c r="E1341" t="n">
-        <v>30000</v>
+        <v>28571.428571</v>
       </c>
       <c r="F1341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1341" t="n">
         <v>0</v>
@@ -71980,7 +71984,7 @@
       </c>
       <c r="M1341" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1341" t="inlineStr"/>
@@ -71988,21 +71992,21 @@
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>FITOSTIMONE 15% GEL</t>
+          <t>FIBRA DE AVENA Y SALVADO DE TRIGO 450GR</t>
         </is>
       </c>
       <c r="C1342" t="inlineStr"/>
       <c r="D1342" t="inlineStr"/>
       <c r="E1342" t="n">
-        <v>48900</v>
+        <v>30000</v>
       </c>
       <c r="F1342" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1342" t="n">
         <v>0</v>
@@ -72038,25 +72042,21 @@
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG CJA X 10 UND EXPORF</t>
-        </is>
-      </c>
-      <c r="C1343" t="inlineStr">
-        <is>
-          <t>7703432421681</t>
-        </is>
-      </c>
+          <t>FITOSTIMONE 15% GEL</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr"/>
       <c r="D1343" t="inlineStr"/>
       <c r="E1343" t="n">
-        <v>18300</v>
+        <v>48900</v>
       </c>
       <c r="F1343" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G1343" t="n">
         <v>0</v>
@@ -72092,21 +72092,25 @@
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1344" t="inlineStr"/>
+          <t>FLUCONAZOL 200MG CJA X 10 UND EXPORF</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>7703432421681</t>
+        </is>
+      </c>
       <c r="D1344" t="inlineStr"/>
       <c r="E1344" t="n">
-        <v>16900</v>
+        <v>18300</v>
       </c>
       <c r="F1344" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G1344" t="n">
         <v>0</v>
@@ -72142,25 +72146,21 @@
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS. LA SANTE</t>
-        </is>
-      </c>
-      <c r="C1345" t="inlineStr">
-        <is>
-          <t>7703763480166</t>
-        </is>
-      </c>
+          <t>FLUCONAZOL 200MG X 4 CAPS DE GENFAR</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr"/>
       <c r="D1345" t="inlineStr"/>
       <c r="E1345" t="n">
-        <v>14700</v>
+        <v>16900</v>
       </c>
       <c r="F1345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1345" t="n">
         <v>0</v>
@@ -72196,25 +72196,25 @@
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS.NOVAMED</t>
+          <t>FLUCONAZOL 200MG X 4 CAPS. LA SANTE</t>
         </is>
       </c>
       <c r="C1346" t="inlineStr">
         <is>
-          <t>7703546927468</t>
+          <t>7703763480166</t>
         </is>
       </c>
       <c r="D1346" t="inlineStr"/>
       <c r="E1346" t="n">
-        <v>10900</v>
+        <v>14700</v>
       </c>
       <c r="F1346" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1346" t="n">
         <v>0</v>
@@ -72250,18 +72250,22 @@
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>Fluconazol Suspension</t>
-        </is>
-      </c>
-      <c r="C1347" t="inlineStr"/>
+          <t>FLUCONAZOL 200MG X 4 CAPS.NOVAMED</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>7703546927468</t>
+        </is>
+      </c>
       <c r="D1347" t="inlineStr"/>
       <c r="E1347" t="n">
-        <v>148000</v>
+        <v>10900</v>
       </c>
       <c r="F1347" t="n">
         <v>2</v>
@@ -72300,21 +72304,21 @@
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>FUNGI-FIN LOCION GOTAS TOPICA 20ML</t>
+          <t>Fluconazol Suspension</t>
         </is>
       </c>
       <c r="C1348" t="inlineStr"/>
       <c r="D1348" t="inlineStr"/>
       <c r="E1348" t="n">
-        <v>15966.386555</v>
+        <v>148000</v>
       </c>
       <c r="F1348" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1348" t="n">
         <v>0</v>
@@ -72342,7 +72346,7 @@
       </c>
       <c r="M1348" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1348" t="inlineStr"/>
@@ -72350,21 +72354,21 @@
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>GALLETA OREO PAQUETE X 6 UNDS</t>
+          <t>FUNGI-FIN LOCION GOTAS TOPICA 20ML</t>
         </is>
       </c>
       <c r="C1349" t="inlineStr"/>
       <c r="D1349" t="inlineStr"/>
       <c r="E1349" t="n">
-        <v>1932.773109</v>
+        <v>15966.386555</v>
       </c>
       <c r="F1349" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1349" t="n">
         <v>0</v>
@@ -72400,21 +72404,21 @@
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>GASEOSA PREMIO 400ML ROJO</t>
+          <t>GALLETA OREO PAQUETE X 6 UNDS</t>
         </is>
       </c>
       <c r="C1350" t="inlineStr"/>
       <c r="D1350" t="inlineStr"/>
       <c r="E1350" t="n">
-        <v>2941.176471</v>
+        <v>1932.773109</v>
       </c>
       <c r="F1350" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G1350" t="n">
         <v>0</v>
@@ -72450,29 +72454,21 @@
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>GASTROFAST ADVANCE</t>
-        </is>
-      </c>
-      <c r="C1351" t="inlineStr">
-        <is>
-          <t>7702057803254</t>
-        </is>
-      </c>
-      <c r="D1351" t="inlineStr">
-        <is>
-          <t>se subio A 3800 ANTES 3.600, LEYDI</t>
-        </is>
-      </c>
+          <t>GASEOSA PREMIO 400ML ROJO</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr"/>
+      <c r="D1351" t="inlineStr"/>
       <c r="E1351" t="n">
-        <v>3800</v>
+        <v>2941.176471</v>
       </c>
       <c r="F1351" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G1351" t="n">
         <v>0</v>
@@ -72500,7 +72496,7 @@
       </c>
       <c r="M1351" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1351" t="inlineStr"/>
@@ -72508,21 +72504,29 @@
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>GASTROFAST ADVANCE X 240 ML</t>
-        </is>
-      </c>
-      <c r="C1352" t="inlineStr"/>
-      <c r="D1352" t="inlineStr"/>
+          <t>GASTROFAST ADVANCE</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>7702057803254</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>se subio A 3800 ANTES 3.600, LEYDI</t>
+        </is>
+      </c>
       <c r="E1352" t="n">
-        <v>69500</v>
+        <v>3800</v>
       </c>
       <c r="F1352" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G1352" t="n">
         <v>0</v>
@@ -72558,25 +72562,21 @@
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>gatorade</t>
-        </is>
-      </c>
-      <c r="C1353" t="inlineStr">
-        <is>
-          <t>248656546</t>
-        </is>
-      </c>
+          <t>GASTROFAST ADVANCE X 240 ML</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr"/>
       <c r="D1353" t="inlineStr"/>
       <c r="E1353" t="n">
-        <v>3782</v>
+        <v>69500</v>
       </c>
       <c r="F1353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1353" t="n">
         <v>0</v>
@@ -72604,7 +72604,7 @@
       </c>
       <c r="M1353" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1353" t="inlineStr"/>
@@ -72612,21 +72612,25 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>GEL BACHUE 150GR</t>
-        </is>
-      </c>
-      <c r="C1354" t="inlineStr"/>
+          <t>gatorade</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>248656546</t>
+        </is>
+      </c>
       <c r="D1354" t="inlineStr"/>
       <c r="E1354" t="n">
-        <v>8800</v>
+        <v>3782</v>
       </c>
       <c r="F1354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1354" t="n">
         <v>0</v>
@@ -72654,7 +72658,7 @@
       </c>
       <c r="M1354" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1354" t="inlineStr"/>
@@ -72662,21 +72666,21 @@
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>GEMFIBROZILO 600 MG</t>
+          <t>GEL BACHUE 150GR</t>
         </is>
       </c>
       <c r="C1355" t="inlineStr"/>
       <c r="D1355" t="inlineStr"/>
       <c r="E1355" t="n">
-        <v>8300</v>
+        <v>8800</v>
       </c>
       <c r="F1355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1355" t="n">
         <v>0</v>
@@ -72712,21 +72716,21 @@
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>GLICERINA CARBONATADA X 20ML FCO YOMA</t>
+          <t>GEMFIBROZILO 600 MG</t>
         </is>
       </c>
       <c r="C1356" t="inlineStr"/>
       <c r="D1356" t="inlineStr"/>
       <c r="E1356" t="n">
-        <v>3900</v>
+        <v>8300</v>
       </c>
       <c r="F1356" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1356" t="n">
         <v>0</v>
@@ -72762,21 +72766,21 @@
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
+          <t>GLICERINA CARBONATADA X 20ML FCO YOMA</t>
         </is>
       </c>
       <c r="C1357" t="inlineStr"/>
       <c r="D1357" t="inlineStr"/>
       <c r="E1357" t="n">
-        <v>3361.344538</v>
+        <v>3900</v>
       </c>
       <c r="F1357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1357" t="n">
         <v>0</v>
@@ -72804,7 +72808,7 @@
       </c>
       <c r="M1357" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1357" t="inlineStr"/>
@@ -72812,21 +72816,21 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
+          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
         </is>
       </c>
       <c r="C1358" t="inlineStr"/>
       <c r="D1358" t="inlineStr"/>
       <c r="E1358" t="n">
-        <v>23109.243697</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1358" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G1358" t="n">
         <v>0</v>
@@ -72862,25 +72866,21 @@
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1359" t="inlineStr">
-        <is>
-          <t>7709195419279</t>
-        </is>
-      </c>
+          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr"/>
       <c r="D1359" t="inlineStr"/>
       <c r="E1359" t="n">
-        <v>24370</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1359" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1359" t="n">
         <v>0</v>
@@ -72916,21 +72916,25 @@
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1360" t="inlineStr"/>
+          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>7709195419279</t>
+        </is>
+      </c>
       <c r="D1360" t="inlineStr"/>
       <c r="E1360" t="n">
-        <v>24369.747899</v>
+        <v>24370</v>
       </c>
       <c r="F1360" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1360" t="n">
         <v>0</v>
@@ -72966,21 +72970,21 @@
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
+          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
         </is>
       </c>
       <c r="C1361" t="inlineStr"/>
       <c r="D1361" t="inlineStr"/>
       <c r="E1361" t="n">
-        <v>23109.243697</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1361" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G1361" t="n">
         <v>0</v>
@@ -73016,21 +73020,21 @@
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>HALLS BARRA SURTIDOS SABORES</t>
+          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
         </is>
       </c>
       <c r="C1362" t="inlineStr"/>
       <c r="D1362" t="inlineStr"/>
       <c r="E1362" t="n">
-        <v>2100.840336</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1362" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G1362" t="n">
         <v>0</v>
@@ -73066,21 +73070,21 @@
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>HALLS PEPA ROJO CEREZA X UND</t>
+          <t>HALLS BARRA SURTIDOS SABORES</t>
         </is>
       </c>
       <c r="C1363" t="inlineStr"/>
       <c r="D1363" t="inlineStr"/>
       <c r="E1363" t="n">
-        <v>336.134454</v>
+        <v>2100.840336</v>
       </c>
       <c r="F1363" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="G1363" t="n">
         <v>0</v>
@@ -73116,21 +73120,21 @@
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>HEPATODREN JARABE FCO X 240ML</t>
+          <t>HALLS PEPA ROJO CEREZA X UND</t>
         </is>
       </c>
       <c r="C1364" t="inlineStr"/>
       <c r="D1364" t="inlineStr"/>
       <c r="E1364" t="n">
-        <v>34500</v>
+        <v>336.134454</v>
       </c>
       <c r="F1364" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G1364" t="n">
         <v>0</v>
@@ -73158,7 +73162,7 @@
       </c>
       <c r="M1364" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1364" t="inlineStr"/>
@@ -73166,18 +73170,18 @@
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>HEPATODREN X 60 CAPSULAS</t>
+          <t>HEPATODREN JARABE FCO X 240ML</t>
         </is>
       </c>
       <c r="C1365" t="inlineStr"/>
       <c r="D1365" t="inlineStr"/>
       <c r="E1365" t="n">
-        <v>58300</v>
+        <v>34500</v>
       </c>
       <c r="F1365" t="n">
         <v>1</v>
@@ -73216,25 +73220,21 @@
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>Hidraplus 75 zinc uva 400ml</t>
-        </is>
-      </c>
-      <c r="C1366" t="inlineStr">
-        <is>
-          <t>7702057010928</t>
-        </is>
-      </c>
+          <t>HEPATODREN X 60 CAPSULAS</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr"/>
       <c r="D1366" t="inlineStr"/>
       <c r="E1366" t="n">
-        <v>10600</v>
+        <v>58300</v>
       </c>
       <c r="F1366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1366" t="n">
         <v>0</v>
@@ -73270,21 +73270,25 @@
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
-        </is>
-      </c>
-      <c r="C1367" t="inlineStr"/>
+          <t>Hidraplus 75 zinc uva 400ml</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>7702057010928</t>
+        </is>
+      </c>
       <c r="D1367" t="inlineStr"/>
       <c r="E1367" t="n">
-        <v>15900</v>
+        <v>10600</v>
       </c>
       <c r="F1367" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1367" t="n">
         <v>0</v>
@@ -73320,25 +73324,21 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
-        </is>
-      </c>
-      <c r="C1368" t="inlineStr">
-        <is>
-          <t>77099475597789</t>
-        </is>
-      </c>
+          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr"/>
       <c r="D1368" t="inlineStr"/>
       <c r="E1368" t="n">
-        <v>28000</v>
+        <v>15900</v>
       </c>
       <c r="F1368" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1368" t="n">
         <v>0</v>
@@ -73374,25 +73374,25 @@
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>Hidroxicina 0.25 JBE x 120 ML</t>
+          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
         </is>
       </c>
       <c r="C1369" t="inlineStr">
         <is>
-          <t>7707035540596</t>
+          <t>77099475597789</t>
         </is>
       </c>
       <c r="D1369" t="inlineStr"/>
       <c r="E1369" t="n">
-        <v>11000</v>
+        <v>28000</v>
       </c>
       <c r="F1369" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1369" t="n">
         <v>0</v>
@@ -73428,18 +73428,22 @@
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
-        </is>
-      </c>
-      <c r="C1370" t="inlineStr"/>
+          <t>Hidroxicina 0.25 JBE x 120 ML</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>7707035540596</t>
+        </is>
+      </c>
       <c r="D1370" t="inlineStr"/>
       <c r="E1370" t="n">
-        <v>4500</v>
+        <v>11000</v>
       </c>
       <c r="F1370" t="n">
         <v>2</v>
@@ -73478,21 +73482,21 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
+          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
         </is>
       </c>
       <c r="C1371" t="inlineStr"/>
       <c r="D1371" t="inlineStr"/>
       <c r="E1371" t="n">
-        <v>6900</v>
+        <v>4500</v>
       </c>
       <c r="F1371" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1371" t="n">
         <v>0</v>
@@ -73528,18 +73532,18 @@
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
+          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
         </is>
       </c>
       <c r="C1372" t="inlineStr"/>
       <c r="D1372" t="inlineStr"/>
       <c r="E1372" t="n">
-        <v>12000</v>
+        <v>6900</v>
       </c>
       <c r="F1372" t="n">
         <v>4</v>
@@ -73578,21 +73582,21 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>Hylo Gel</t>
+          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
         </is>
       </c>
       <c r="C1373" t="inlineStr"/>
       <c r="D1373" t="inlineStr"/>
       <c r="E1373" t="n">
-        <v>131600</v>
+        <v>12000</v>
       </c>
       <c r="F1373" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1373" t="n">
         <v>0</v>
@@ -73628,25 +73632,21 @@
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>IBUPROFENO 400MG/ GENFAR</t>
-        </is>
-      </c>
-      <c r="C1374" t="inlineStr">
-        <is>
-          <t>7702605101498</t>
-        </is>
-      </c>
+          <t>Hylo Gel</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr"/>
       <c r="D1374" t="inlineStr"/>
       <c r="E1374" t="n">
-        <v>4400</v>
+        <v>131600</v>
       </c>
       <c r="F1374" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="G1374" t="n">
         <v>0</v>
@@ -73682,25 +73682,25 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>Ibuprofeno 800mg AG</t>
+          <t>IBUPROFENO 400MG/ GENFAR</t>
         </is>
       </c>
       <c r="C1375" t="inlineStr">
         <is>
-          <t>7706569000385</t>
+          <t>7702605101498</t>
         </is>
       </c>
       <c r="D1375" t="inlineStr"/>
       <c r="E1375" t="n">
-        <v>800</v>
+        <v>4400</v>
       </c>
       <c r="F1375" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G1375" t="n">
         <v>0</v>
@@ -73736,25 +73736,25 @@
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
+          <t>Ibuprofeno 800mg AG</t>
         </is>
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>7705959885229</t>
+          <t>7706569000385</t>
         </is>
       </c>
       <c r="D1376" t="inlineStr"/>
       <c r="E1376" t="n">
-        <v>17900</v>
+        <v>800</v>
       </c>
       <c r="F1376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1376" t="n">
         <v>0</v>
@@ -73790,22 +73790,22 @@
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>ICE POWER 30 GR GEL COSMETICA</t>
+          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
         </is>
       </c>
       <c r="C1377" t="inlineStr">
         <is>
-          <t>737186238889</t>
+          <t>7705959885229</t>
         </is>
       </c>
       <c r="D1377" t="inlineStr"/>
       <c r="E1377" t="n">
-        <v>12521.008403</v>
+        <v>17900</v>
       </c>
       <c r="F1377" t="n">
         <v>2</v>
@@ -73836,7 +73836,7 @@
       </c>
       <c r="M1377" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1377" t="inlineStr"/>
@@ -73844,21 +73844,25 @@
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
-        </is>
-      </c>
-      <c r="C1378" t="inlineStr"/>
+          <t>ICE POWER 30 GR GEL COSMETICA</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>737186238889</t>
+        </is>
+      </c>
       <c r="D1378" t="inlineStr"/>
       <c r="E1378" t="n">
-        <v>38900</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1378" t="n">
         <v>0</v>
@@ -73886,7 +73890,7 @@
       </c>
       <c r="M1378" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1378" t="inlineStr"/>
@@ -73894,12 +73898,12 @@
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
+          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
         </is>
       </c>
       <c r="C1379" t="inlineStr"/>
@@ -73944,21 +73948,21 @@
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
+          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
         </is>
       </c>
       <c r="C1380" t="inlineStr"/>
       <c r="D1380" t="inlineStr"/>
       <c r="E1380" t="n">
-        <v>8235.294118</v>
+        <v>38900</v>
       </c>
       <c r="F1380" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1380" t="n">
         <v>0</v>
@@ -73986,7 +73990,7 @@
       </c>
       <c r="M1380" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1380" t="inlineStr"/>
@@ -73994,21 +73998,21 @@
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
+          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
         </is>
       </c>
       <c r="C1381" t="inlineStr"/>
       <c r="D1381" t="inlineStr"/>
       <c r="E1381" t="n">
-        <v>9831.932773</v>
+        <v>8235.294118</v>
       </c>
       <c r="F1381" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1381" t="n">
         <v>0</v>
@@ -74044,21 +74048,21 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
+          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
         </is>
       </c>
       <c r="C1382" t="inlineStr"/>
       <c r="D1382" t="inlineStr"/>
       <c r="E1382" t="n">
-        <v>4201.680672</v>
+        <v>9831.932773</v>
       </c>
       <c r="F1382" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1382" t="n">
         <v>0</v>
@@ -74094,12 +74098,12 @@
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
+          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
         </is>
       </c>
       <c r="C1383" t="inlineStr"/>
@@ -74108,7 +74112,7 @@
         <v>4201.680672</v>
       </c>
       <c r="F1383" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1383" t="n">
         <v>0</v>
@@ -74144,18 +74148,18 @@
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>JABON PROTEX HERBAL 110GR</t>
+          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
         </is>
       </c>
       <c r="C1384" t="inlineStr"/>
       <c r="D1384" t="inlineStr"/>
       <c r="E1384" t="n">
-        <v>4537.815126</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1384" t="n">
         <v>2</v>
@@ -74194,22 +74198,18 @@
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>JARABE ZETYGRIP FCO 60ML</t>
-        </is>
-      </c>
-      <c r="C1385" t="inlineStr">
-        <is>
-          <t>7709805542830</t>
-        </is>
-      </c>
+          <t>JABON PROTEX HERBAL 110GR</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr"/>
       <c r="D1385" t="inlineStr"/>
       <c r="E1385" t="n">
-        <v>14000</v>
+        <v>4537.815126</v>
       </c>
       <c r="F1385" t="n">
         <v>2</v>
@@ -74240,7 +74240,7 @@
       </c>
       <c r="M1385" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1385" t="inlineStr"/>
@@ -74248,21 +74248,25 @@
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>JERINGA DE 50ML</t>
-        </is>
-      </c>
-      <c r="C1386" t="inlineStr"/>
+          <t>JARABE ZETYGRIP FCO 60ML</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>7709805542830</t>
+        </is>
+      </c>
       <c r="D1386" t="inlineStr"/>
       <c r="E1386" t="n">
-        <v>2500</v>
+        <v>14000</v>
       </c>
       <c r="F1386" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1386" t="n">
         <v>0</v>
@@ -74298,21 +74302,21 @@
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>Jeringa desechable estéril 20ml impormedicas</t>
+          <t>JERINGA DE 50ML</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr"/>
       <c r="D1387" t="inlineStr"/>
       <c r="E1387" t="n">
-        <v>920</v>
+        <v>2500</v>
       </c>
       <c r="F1387" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G1387" t="n">
         <v>0</v>
@@ -74340,7 +74344,7 @@
       </c>
       <c r="M1387" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1387" t="inlineStr"/>
@@ -74348,21 +74352,21 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
+          <t>Jeringa desechable estéril 20ml impormedicas</t>
         </is>
       </c>
       <c r="C1388" t="inlineStr"/>
       <c r="D1388" t="inlineStr"/>
       <c r="E1388" t="n">
-        <v>1100</v>
+        <v>920</v>
       </c>
       <c r="F1388" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="G1388" t="n">
         <v>0</v>
@@ -74390,7 +74394,7 @@
       </c>
       <c r="M1388" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1388" t="inlineStr"/>
@@ -74398,21 +74402,21 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>Kelocate</t>
+          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
         </is>
       </c>
       <c r="C1389" t="inlineStr"/>
       <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="n">
-        <v>180000</v>
+        <v>1100</v>
       </c>
       <c r="F1389" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G1389" t="n">
         <v>0</v>
@@ -74448,22 +74452,18 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
-        </is>
-      </c>
-      <c r="C1390" t="inlineStr">
-        <is>
-          <t>7702057073695</t>
-        </is>
-      </c>
+          <t>Kelocate</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr"/>
       <c r="D1390" t="inlineStr"/>
       <c r="E1390" t="n">
-        <v>19500</v>
+        <v>180000</v>
       </c>
       <c r="F1390" t="n">
         <v>0</v>
@@ -74502,22 +74502,22 @@
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
+          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
         </is>
       </c>
       <c r="C1391" t="inlineStr">
         <is>
-          <t>7709947559772</t>
+          <t>7702057073695</t>
         </is>
       </c>
       <c r="D1391" t="inlineStr"/>
       <c r="E1391" t="n">
-        <v>15000</v>
+        <v>19500</v>
       </c>
       <c r="F1391" t="n">
         <v>0</v>
@@ -74556,18 +74556,22 @@
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
-        </is>
-      </c>
-      <c r="C1392" t="inlineStr"/>
+          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>7709947559772</t>
+        </is>
+      </c>
       <c r="D1392" t="inlineStr"/>
       <c r="E1392" t="n">
-        <v>71000</v>
+        <v>15000</v>
       </c>
       <c r="F1392" t="n">
         <v>0</v>
@@ -74606,21 +74610,21 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
+          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
         </is>
       </c>
       <c r="C1393" t="inlineStr"/>
       <c r="D1393" t="inlineStr"/>
       <c r="E1393" t="n">
-        <v>37900</v>
+        <v>71000</v>
       </c>
       <c r="F1393" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1393" t="n">
         <v>0</v>
@@ -74656,25 +74660,21 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>Levotiroxina 100mcg MK</t>
-        </is>
-      </c>
-      <c r="C1394" t="inlineStr">
-        <is>
-          <t>7702057715908</t>
-        </is>
-      </c>
+          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr"/>
       <c r="D1394" t="inlineStr"/>
       <c r="E1394" t="n">
-        <v>27900</v>
+        <v>37900</v>
       </c>
       <c r="F1394" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1394" t="n">
         <v>0</v>
@@ -74710,21 +74710,25 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>LIMA MAYOMI 10/180</t>
-        </is>
-      </c>
-      <c r="C1395" t="inlineStr"/>
+          <t>Levotiroxina 100mcg MK</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>7702057715908</t>
+        </is>
+      </c>
       <c r="D1395" t="inlineStr"/>
       <c r="E1395" t="n">
-        <v>3900</v>
+        <v>27900</v>
       </c>
       <c r="F1395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1395" t="n">
         <v>0</v>
@@ -74760,21 +74764,21 @@
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
+          <t>LIMA MAYOMI 10/180</t>
         </is>
       </c>
       <c r="C1396" t="inlineStr"/>
       <c r="D1396" t="inlineStr"/>
       <c r="E1396" t="n">
-        <v>16807</v>
+        <v>3900</v>
       </c>
       <c r="F1396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1396" t="n">
         <v>0</v>
@@ -74802,7 +74806,7 @@
       </c>
       <c r="M1396" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1396" t="inlineStr"/>
@@ -74810,21 +74814,21 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
+          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
         </is>
       </c>
       <c r="C1397" t="inlineStr"/>
       <c r="D1397" t="inlineStr"/>
       <c r="E1397" t="n">
-        <v>15042.016807</v>
+        <v>16807</v>
       </c>
       <c r="F1397" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1397" t="n">
         <v>0</v>
@@ -74860,21 +74864,21 @@
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>LISTERINE CUIDADO TOTAL 180ML</t>
+          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
         </is>
       </c>
       <c r="C1398" t="inlineStr"/>
       <c r="D1398" t="inlineStr"/>
       <c r="E1398" t="n">
-        <v>16386.554622</v>
+        <v>15042.016807</v>
       </c>
       <c r="F1398" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1398" t="n">
         <v>0</v>
@@ -74910,21 +74914,21 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
+          <t>LISTERINE CUIDADO TOTAL 180ML</t>
         </is>
       </c>
       <c r="C1399" t="inlineStr"/>
       <c r="D1399" t="inlineStr"/>
       <c r="E1399" t="n">
-        <v>3500</v>
+        <v>16386.554622</v>
       </c>
       <c r="F1399" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G1399" t="n">
         <v>0</v>
@@ -74952,7 +74956,7 @@
       </c>
       <c r="M1399" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1399" t="inlineStr"/>
@@ -74960,12 +74964,12 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
         </is>
       </c>
       <c r="C1400" t="inlineStr"/>
@@ -74974,7 +74978,7 @@
         <v>3500</v>
       </c>
       <c r="F1400" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G1400" t="n">
         <v>0</v>
@@ -75010,21 +75014,21 @@
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
         </is>
       </c>
       <c r="C1401" t="inlineStr"/>
       <c r="D1401" t="inlineStr"/>
       <c r="E1401" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="F1401" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1401" t="n">
         <v>0</v>
@@ -75060,25 +75064,21 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>Losartan Tensofar 100 Mg</t>
-        </is>
-      </c>
-      <c r="C1402" t="inlineStr">
-        <is>
-          <t>7703546012119</t>
-        </is>
-      </c>
+          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr"/>
       <c r="D1402" t="inlineStr"/>
       <c r="E1402" t="n">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="F1402" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1402" t="n">
         <v>0</v>
@@ -75114,25 +75114,25 @@
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+          <t>Losartan Tensofar 100 Mg</t>
         </is>
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>7501007528939</t>
+          <t>7703546012119</t>
         </is>
       </c>
       <c r="D1403" t="inlineStr"/>
       <c r="E1403" t="n">
-        <v>18907.563025</v>
+        <v>5000</v>
       </c>
       <c r="F1403" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1403" t="n">
         <v>0</v>
@@ -75160,7 +75160,7 @@
       </c>
       <c r="M1403" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1403" t="inlineStr"/>
@@ -75168,18 +75168,22 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>MANTECA DE CACAO LABIAL LIMON</t>
-        </is>
-      </c>
-      <c r="C1404" t="inlineStr"/>
+          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>7501007528939</t>
+        </is>
+      </c>
       <c r="D1404" t="inlineStr"/>
       <c r="E1404" t="n">
-        <v>3361.344538</v>
+        <v>18907.563025</v>
       </c>
       <c r="F1404" t="n">
         <v>0</v>
@@ -75218,12 +75222,12 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
+          <t>MANTECA DE CACAO LABIAL LIMON</t>
         </is>
       </c>
       <c r="C1405" t="inlineStr"/>
@@ -75268,21 +75272,21 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>Mega sex</t>
+          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
         </is>
       </c>
       <c r="C1406" t="inlineStr"/>
       <c r="D1406" t="inlineStr"/>
       <c r="E1406" t="n">
-        <v>3200</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1406" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G1406" t="n">
         <v>0</v>
@@ -75310,7 +75314,7 @@
       </c>
       <c r="M1406" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1406" t="inlineStr"/>
@@ -75318,29 +75322,21 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>Melatonina 3mg</t>
-        </is>
-      </c>
-      <c r="C1407" t="inlineStr">
-        <is>
-          <t>7706849112906</t>
-        </is>
-      </c>
-      <c r="D1407" t="inlineStr">
-        <is>
-          <t>producto nuevo</t>
-        </is>
-      </c>
+          <t>Mega sex</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr"/>
+      <c r="D1407" t="inlineStr"/>
       <c r="E1407" t="n">
-        <v>52000</v>
+        <v>3200</v>
       </c>
       <c r="F1407" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G1407" t="n">
         <v>0</v>
@@ -75376,22 +75372,26 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
+          <t>Melatonina 3mg</t>
         </is>
       </c>
       <c r="C1408" t="inlineStr">
         <is>
-          <t>7707529435209</t>
-        </is>
-      </c>
-      <c r="D1408" t="inlineStr"/>
+          <t>7706849112906</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>producto nuevo</t>
+        </is>
+      </c>
       <c r="E1408" t="n">
-        <v>36000</v>
+        <v>52000</v>
       </c>
       <c r="F1408" t="n">
         <v>0</v>
@@ -75430,22 +75430,22 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>Meloxicam 15mg AG</t>
+          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
         </is>
       </c>
       <c r="C1409" t="inlineStr">
         <is>
-          <t>7706569020437</t>
+          <t>7707529435209</t>
         </is>
       </c>
       <c r="D1409" t="inlineStr"/>
       <c r="E1409" t="n">
-        <v>1500</v>
+        <v>36000</v>
       </c>
       <c r="F1409" t="n">
         <v>0</v>
@@ -75484,21 +75484,25 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
-        </is>
-      </c>
-      <c r="C1410" t="inlineStr"/>
+          <t>Meloxicam 15mg AG</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>7706569020437</t>
+        </is>
+      </c>
       <c r="D1410" t="inlineStr"/>
       <c r="E1410" t="n">
-        <v>9700</v>
+        <v>1500</v>
       </c>
       <c r="F1410" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1410" t="n">
         <v>0</v>
@@ -75534,25 +75538,21 @@
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>MELOXICAM COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1411" t="inlineStr">
-        <is>
-          <t>7703712036253</t>
-        </is>
-      </c>
+          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr"/>
       <c r="D1411" t="inlineStr"/>
       <c r="E1411" t="n">
-        <v>1300</v>
+        <v>9700</v>
       </c>
       <c r="F1411" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1411" t="n">
         <v>0</v>
@@ -75578,31 +75578,35 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1411" t="inlineStr"/>
+      <c r="M1411" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1411" t="inlineStr"/>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>metformina 850 mg pisa</t>
+          <t>MELOXICAM COASPHARMA</t>
         </is>
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>7501125188039</t>
+          <t>7703712036253</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr"/>
       <c r="E1412" t="n">
-        <v>5500</v>
+        <v>1300</v>
       </c>
       <c r="F1412" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G1412" t="n">
         <v>0</v>
@@ -75628,35 +75632,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1412" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1412" t="inlineStr"/>
       <c r="N1412" t="inlineStr"/>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10MG RECIPE</t>
+          <t>metformina 850 mg pisa</t>
         </is>
       </c>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>7702195084355</t>
+          <t>7501125188039</t>
         </is>
       </c>
       <c r="D1413" t="inlineStr"/>
       <c r="E1413" t="n">
-        <v>1000</v>
+        <v>5500</v>
       </c>
       <c r="F1413" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G1413" t="n">
         <v>0</v>
@@ -75692,25 +75692,25 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>MICROPOR 1X3 Y</t>
+          <t>METOCLOPRAMIDA 10MG RECIPE</t>
         </is>
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>7707282990205</t>
+          <t>7702195084355</t>
         </is>
       </c>
       <c r="D1414" t="inlineStr"/>
       <c r="E1414" t="n">
-        <v>5300</v>
+        <v>1000</v>
       </c>
       <c r="F1414" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1414" t="n">
         <v>0</v>
@@ -75746,25 +75746,25 @@
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>MICROPOR CINTA 1/2X5Y</t>
+          <t>MICROPOR 1X3 Y</t>
         </is>
       </c>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>7707282990182</t>
+          <t>7707282990205</t>
         </is>
       </c>
       <c r="D1415" t="inlineStr"/>
       <c r="E1415" t="n">
-        <v>3900</v>
+        <v>5300</v>
       </c>
       <c r="F1415" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G1415" t="n">
         <v>0</v>
@@ -75800,21 +75800,25 @@
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>MICROPORE COLOR PIEL 2YARDAS</t>
-        </is>
-      </c>
-      <c r="C1416" t="inlineStr"/>
+          <t>MICROPOR CINTA 1/2X5Y</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>7707282990182</t>
+        </is>
+      </c>
       <c r="D1416" t="inlineStr"/>
       <c r="E1416" t="n">
-        <v>3700</v>
+        <v>3900</v>
       </c>
       <c r="F1416" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G1416" t="n">
         <v>0</v>
@@ -75850,18 +75854,18 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
+          <t>MICROPORE COLOR PIEL 2YARDAS</t>
         </is>
       </c>
       <c r="C1417" t="inlineStr"/>
       <c r="D1417" t="inlineStr"/>
       <c r="E1417" t="n">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="F1417" t="n">
         <v>0</v>
@@ -75900,22 +75904,18 @@
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>MIELTERTOS JARABE X 240ML</t>
-        </is>
-      </c>
-      <c r="C1418" t="inlineStr">
-        <is>
-          <t>7707232095608</t>
-        </is>
-      </c>
+          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr"/>
       <c r="D1418" t="inlineStr"/>
       <c r="E1418" t="n">
-        <v>34500</v>
+        <v>4000</v>
       </c>
       <c r="F1418" t="n">
         <v>0</v>
@@ -75954,25 +75954,25 @@
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
-        </is>
-      </c>
-      <c r="C1419" t="inlineStr"/>
-      <c r="D1419" t="inlineStr">
-        <is>
-          <t>subio precio hector</t>
-        </is>
-      </c>
+          <t>MIELTERTOS JARABE X 240ML</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>7707232095608</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr"/>
       <c r="E1419" t="n">
-        <v>22700</v>
+        <v>34500</v>
       </c>
       <c r="F1419" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1419" t="n">
         <v>0</v>
@@ -76008,21 +76008,25 @@
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
+          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
         </is>
       </c>
       <c r="C1420" t="inlineStr"/>
-      <c r="D1420" t="inlineStr"/>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>subio precio hector</t>
+        </is>
+      </c>
       <c r="E1420" t="n">
-        <v>5500</v>
+        <v>22700</v>
       </c>
       <c r="F1420" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G1420" t="n">
         <v>0</v>
@@ -76058,21 +76062,21 @@
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>NEOSALDINA TABLETA X UND</t>
+          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
         </is>
       </c>
       <c r="C1421" t="inlineStr"/>
       <c r="D1421" t="inlineStr"/>
       <c r="E1421" t="n">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="F1421" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1421" t="n">
         <v>0</v>
@@ -76108,21 +76112,21 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>NIFEDIPINO 30MG NOVAMED</t>
+          <t>NEOSALDINA TABLETA X UND</t>
         </is>
       </c>
       <c r="C1422" t="inlineStr"/>
       <c r="D1422" t="inlineStr"/>
       <c r="E1422" t="n">
-        <v>19000</v>
+        <v>2500</v>
       </c>
       <c r="F1422" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G1422" t="n">
         <v>0</v>
@@ -76158,21 +76162,21 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
+          <t>NIFEDIPINO 30MG NOVAMED</t>
         </is>
       </c>
       <c r="C1423" t="inlineStr"/>
       <c r="D1423" t="inlineStr"/>
       <c r="E1423" t="n">
-        <v>23000</v>
+        <v>19000</v>
       </c>
       <c r="F1423" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1423" t="n">
         <v>0</v>
@@ -76208,18 +76212,18 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>NITOXIPAR X 6 TABLETAS</t>
+          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
         </is>
       </c>
       <c r="C1424" t="inlineStr"/>
       <c r="D1424" t="inlineStr"/>
       <c r="E1424" t="n">
-        <v>24500</v>
+        <v>23000</v>
       </c>
       <c r="F1424" t="n">
         <v>3</v>
@@ -76258,21 +76262,21 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>NORAVER SPRAY CEREZA 120ML</t>
+          <t>NITOXIPAR X 6 TABLETAS</t>
         </is>
       </c>
       <c r="C1425" t="inlineStr"/>
       <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="n">
-        <v>52900</v>
+        <v>24500</v>
       </c>
       <c r="F1425" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1425" t="n">
         <v>0</v>
@@ -76308,25 +76312,21 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
-        </is>
-      </c>
-      <c r="C1426" t="inlineStr">
-        <is>
-          <t>7702027041662</t>
-        </is>
-      </c>
+          <t>NORAVER SPRAY CEREZA 120ML</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr"/>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="n">
-        <v>6300</v>
+        <v>52900</v>
       </c>
       <c r="F1426" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1426" t="n">
         <v>0</v>
@@ -76362,18 +76362,22 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
-        </is>
-      </c>
-      <c r="C1427" t="inlineStr"/>
+          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>7702027041662</t>
+        </is>
+      </c>
       <c r="D1427" t="inlineStr"/>
       <c r="E1427" t="n">
-        <v>8823.529412</v>
+        <v>6300</v>
       </c>
       <c r="F1427" t="n">
         <v>0</v>
@@ -76404,7 +76408,7 @@
       </c>
       <c r="M1427" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1427" t="inlineStr"/>
@@ -76412,7 +76416,7 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
@@ -76420,11 +76424,7 @@
           <t>NOSOTRAS JABON INTIMO X 200ML</t>
         </is>
       </c>
-      <c r="C1428" t="inlineStr">
-        <is>
-          <t>7702026158644</t>
-        </is>
-      </c>
+      <c r="C1428" t="inlineStr"/>
       <c r="D1428" t="inlineStr"/>
       <c r="E1428" t="n">
         <v>8823.529412</v>
@@ -76466,25 +76466,25 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JBE 120ML</t>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
         </is>
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>7707355053363</t>
+          <t>7702026158644</t>
         </is>
       </c>
       <c r="D1429" t="inlineStr"/>
       <c r="E1429" t="n">
-        <v>22700</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1429" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1429" t="n">
         <v>0</v>
@@ -76512,7 +76512,7 @@
       </c>
       <c r="M1429" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1429" t="inlineStr"/>
@@ -76520,25 +76520,25 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+          <t>NOXPIRIN JUNIOR JBE 120ML</t>
         </is>
       </c>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>7707355053356</t>
+          <t>7707355053363</t>
         </is>
       </c>
       <c r="D1430" t="inlineStr"/>
       <c r="E1430" t="n">
-        <v>17200</v>
+        <v>22700</v>
       </c>
       <c r="F1430" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1430" t="n">
         <v>0</v>
@@ -76574,21 +76574,25 @@
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>NUTRIBELL ACEITE DE COCO</t>
-        </is>
-      </c>
-      <c r="C1431" t="inlineStr"/>
+          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>7707355053356</t>
+        </is>
+      </c>
       <c r="D1431" t="inlineStr"/>
       <c r="E1431" t="n">
-        <v>2700</v>
+        <v>17200</v>
       </c>
       <c r="F1431" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1431" t="n">
         <v>0</v>
@@ -76624,29 +76628,21 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Omega 3 6 9 suplemento totalmax</t>
-        </is>
-      </c>
-      <c r="C1432" t="inlineStr">
-        <is>
-          <t>7707529434974</t>
-        </is>
-      </c>
-      <c r="D1432" t="inlineStr">
-        <is>
-          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
-        </is>
-      </c>
+          <t>NUTRIBELL ACEITE DE COCO</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr"/>
+      <c r="D1432" t="inlineStr"/>
       <c r="E1432" t="n">
-        <v>35000</v>
+        <v>2700</v>
       </c>
       <c r="F1432" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1432" t="n">
         <v>0</v>
@@ -76682,21 +76678,29 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1433" t="inlineStr"/>
-      <c r="D1433" t="inlineStr"/>
+          <t>Omega 3 6 9 suplemento totalmax</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>7707529434974</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
+        </is>
+      </c>
       <c r="E1433" t="n">
-        <v>5500</v>
+        <v>35000</v>
       </c>
       <c r="F1433" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1433" t="n">
         <v>0</v>
@@ -76732,22 +76736,18 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
-        </is>
-      </c>
-      <c r="C1434" t="inlineStr">
-        <is>
-          <t>7707529435940</t>
-        </is>
-      </c>
+          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr"/>
       <c r="D1434" t="inlineStr"/>
       <c r="E1434" t="n">
-        <v>35000</v>
+        <v>5500</v>
       </c>
       <c r="F1434" t="n">
         <v>0</v>
@@ -76786,21 +76786,25 @@
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
-        </is>
-      </c>
-      <c r="C1435" t="inlineStr"/>
+          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>7707529435940</t>
+        </is>
+      </c>
       <c r="D1435" t="inlineStr"/>
       <c r="E1435" t="n">
-        <v>48000</v>
+        <v>35000</v>
       </c>
       <c r="F1435" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>
@@ -76836,25 +76840,21 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>OROCAL CALCIO 600MG</t>
+          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
         </is>
       </c>
       <c r="C1436" t="inlineStr"/>
-      <c r="D1436" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="D1436" t="inlineStr"/>
       <c r="E1436" t="n">
-        <v>30500</v>
+        <v>48000</v>
       </c>
       <c r="F1436" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1436" t="n">
         <v>0</v>
@@ -76890,18 +76890,22 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>PALA DE MADERA RASPACALLO</t>
+          <t>OROCAL CALCIO 600MG</t>
         </is>
       </c>
       <c r="C1437" t="inlineStr"/>
-      <c r="D1437" t="inlineStr"/>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E1437" t="n">
-        <v>4000</v>
+        <v>30500</v>
       </c>
       <c r="F1437" t="n">
         <v>1</v>
@@ -76940,21 +76944,21 @@
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>PALO DE NARANJO X UNIDAD</t>
+          <t>PALA DE MADERA RASPACALLO</t>
         </is>
       </c>
       <c r="C1438" t="inlineStr"/>
       <c r="D1438" t="inlineStr"/>
       <c r="E1438" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="F1438" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G1438" t="n">
         <v>0</v>
@@ -76990,25 +76994,21 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
-        </is>
-      </c>
-      <c r="C1439" t="inlineStr">
-        <is>
-          <t>7704412170896</t>
-        </is>
-      </c>
+          <t>PALO DE NARANJO X UNIDAD</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr"/>
       <c r="D1439" t="inlineStr"/>
       <c r="E1439" t="n">
-        <v>6200</v>
+        <v>400</v>
       </c>
       <c r="F1439" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G1439" t="n">
         <v>0</v>
@@ -77044,18 +77044,22 @@
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
-        </is>
-      </c>
-      <c r="C1440" t="inlineStr"/>
+          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>7704412170896</t>
+        </is>
+      </c>
       <c r="D1440" t="inlineStr"/>
       <c r="E1440" t="n">
-        <v>14285.714286</v>
+        <v>6200</v>
       </c>
       <c r="F1440" t="n">
         <v>1</v>
@@ -77086,7 +77090,7 @@
       </c>
       <c r="M1440" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1440" t="inlineStr"/>
@@ -77094,18 +77098,18 @@
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
+          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
         </is>
       </c>
       <c r="C1441" t="inlineStr"/>
       <c r="D1441" t="inlineStr"/>
       <c r="E1441" t="n">
-        <v>28991.596639</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1441" t="n">
         <v>1</v>
@@ -77144,18 +77148,18 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
         </is>
       </c>
       <c r="C1442" t="inlineStr"/>
       <c r="D1442" t="inlineStr"/>
       <c r="E1442" t="n">
-        <v>41176.470588</v>
+        <v>28991.596639</v>
       </c>
       <c r="F1442" t="n">
         <v>1</v>
@@ -77194,22 +77198,18 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>Pañales Winny Etapa 5 X PAQUETE</t>
-        </is>
-      </c>
-      <c r="C1443" t="inlineStr">
-        <is>
-          <t>7701021114174</t>
-        </is>
-      </c>
+          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr"/>
       <c r="D1443" t="inlineStr"/>
       <c r="E1443" t="n">
-        <v>41849</v>
+        <v>41176.470588</v>
       </c>
       <c r="F1443" t="n">
         <v>1</v>
@@ -77248,21 +77248,25 @@
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>PAÑALWINNY ETA 5 X 16 UND</t>
-        </is>
-      </c>
-      <c r="C1444" t="inlineStr"/>
+          <t>Pañales Winny Etapa 5 X PAQUETE</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>7701021114174</t>
+        </is>
+      </c>
       <c r="D1444" t="inlineStr"/>
       <c r="E1444" t="n">
-        <v>24369.747899</v>
+        <v>41849</v>
       </c>
       <c r="F1444" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1444" t="n">
         <v>0</v>
@@ -77298,21 +77302,21 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>pañitos humedos pequeñin 100unidades</t>
+          <t>PAÑALWINNY ETA 5 X 16 UND</t>
         </is>
       </c>
       <c r="C1445" t="inlineStr"/>
       <c r="D1445" t="inlineStr"/>
       <c r="E1445" t="n">
-        <v>10925</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1445" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1445" t="n">
         <v>0</v>
@@ -77348,21 +77352,21 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
+          <t>pañitos humedos pequeñin 100unidades</t>
         </is>
       </c>
       <c r="C1446" t="inlineStr"/>
       <c r="D1446" t="inlineStr"/>
       <c r="E1446" t="n">
-        <v>14900</v>
+        <v>10925</v>
       </c>
       <c r="F1446" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1446" t="n">
         <v>0</v>
@@ -77390,7 +77394,7 @@
       </c>
       <c r="M1446" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1446" t="inlineStr"/>
@@ -77398,21 +77402,21 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>Panotil B x 8ML</t>
+          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
         </is>
       </c>
       <c r="C1447" t="inlineStr"/>
       <c r="D1447" t="inlineStr"/>
       <c r="E1447" t="n">
-        <v>26400</v>
+        <v>14900</v>
       </c>
       <c r="F1447" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1447" t="n">
         <v>0</v>
@@ -77448,25 +77452,21 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>PANTENE ACONDICIONADOR</t>
-        </is>
-      </c>
-      <c r="C1448" t="inlineStr">
-        <is>
-          <t>7500435153683</t>
-        </is>
-      </c>
+          <t>Panotil B x 8ML</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr"/>
       <c r="D1448" t="inlineStr"/>
       <c r="E1448" t="n">
-        <v>1500</v>
+        <v>26400</v>
       </c>
       <c r="F1448" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1448" t="n">
         <v>0</v>
@@ -77502,21 +77502,25 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>Parche Ocular Colostol</t>
-        </is>
-      </c>
-      <c r="C1449" t="inlineStr"/>
+          <t>PANTENE ACONDICIONADOR</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>7500435153683</t>
+        </is>
+      </c>
       <c r="D1449" t="inlineStr"/>
       <c r="E1449" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F1449" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G1449" t="n">
         <v>0</v>
@@ -77552,25 +77556,21 @@
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
-        </is>
-      </c>
-      <c r="C1450" t="inlineStr">
-        <is>
-          <t>7501033957413</t>
-        </is>
-      </c>
+          <t>Parche Ocular Colostol</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr"/>
       <c r="D1450" t="inlineStr"/>
       <c r="E1450" t="n">
-        <v>10600</v>
+        <v>1300</v>
       </c>
       <c r="F1450" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G1450" t="n">
         <v>0</v>
@@ -77606,26 +77606,22 @@
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
+          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
         </is>
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>7501033961557</t>
-        </is>
-      </c>
-      <c r="D1451" t="inlineStr">
-        <is>
-          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
-        </is>
-      </c>
+          <t>7501033957413</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr"/>
       <c r="E1451" t="n">
-        <v>10900</v>
+        <v>10600</v>
       </c>
       <c r="F1451" t="n">
         <v>0</v>
@@ -77664,29 +77660,29 @@
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
         </is>
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>7501033957376</t>
+          <t>7501033961557</t>
         </is>
       </c>
       <c r="D1452" t="inlineStr">
         <is>
-          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
         </is>
       </c>
       <c r="E1452" t="n">
         <v>10900</v>
       </c>
       <c r="F1452" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1452" t="n">
         <v>0</v>
@@ -77722,21 +77718,29 @@
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>PEGANTE GLUE X 10GR X UND</t>
-        </is>
-      </c>
-      <c r="C1453" t="inlineStr"/>
-      <c r="D1453" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>7501033957376</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+        </is>
+      </c>
       <c r="E1453" t="n">
-        <v>2000</v>
+        <v>10900</v>
       </c>
       <c r="F1453" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1453" t="n">
         <v>0</v>
@@ -77772,21 +77776,21 @@
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>PEINETA COLA DE RATON METALICA</t>
+          <t>PEGANTE GLUE X 10GR X UND</t>
         </is>
       </c>
       <c r="C1454" t="inlineStr"/>
       <c r="D1454" t="inlineStr"/>
       <c r="E1454" t="n">
-        <v>4700</v>
+        <v>2000</v>
       </c>
       <c r="F1454" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1454" t="n">
         <v>0</v>
@@ -77822,18 +77826,18 @@
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>PERFILADORES DE CEJAS</t>
+          <t>PEINETA COLA DE RATON METALICA</t>
         </is>
       </c>
       <c r="C1455" t="inlineStr"/>
       <c r="D1455" t="inlineStr"/>
       <c r="E1455" t="n">
-        <v>3900</v>
+        <v>4700</v>
       </c>
       <c r="F1455" t="n">
         <v>1</v>
@@ -77872,18 +77876,18 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
+          <t>PERFILADORES DE CEJAS</t>
         </is>
       </c>
       <c r="C1456" t="inlineStr"/>
       <c r="D1456" t="inlineStr"/>
       <c r="E1456" t="n">
-        <v>27983.193277</v>
+        <v>3900</v>
       </c>
       <c r="F1456" t="n">
         <v>1</v>
@@ -77914,7 +77918,7 @@
       </c>
       <c r="M1456" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1456" t="inlineStr"/>
@@ -77922,21 +77926,21 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>POPETAS SURTIDAS X UND</t>
+          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
         </is>
       </c>
       <c r="C1457" t="inlineStr"/>
       <c r="D1457" t="inlineStr"/>
       <c r="E1457" t="n">
-        <v>2521.008403</v>
+        <v>27983.193277</v>
       </c>
       <c r="F1457" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1457" t="n">
         <v>0</v>
@@ -77972,21 +77976,21 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+          <t>POPETAS SURTIDAS X UND</t>
         </is>
       </c>
       <c r="C1458" t="inlineStr"/>
       <c r="D1458" t="inlineStr"/>
       <c r="E1458" t="n">
-        <v>20500</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1458" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1458" t="n">
         <v>0</v>
@@ -78014,7 +78018,7 @@
       </c>
       <c r="M1458" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1458" t="inlineStr"/>
@@ -78022,29 +78026,21 @@
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>privatos miel limon la francol 120ml</t>
-        </is>
-      </c>
-      <c r="C1459" t="inlineStr">
-        <is>
-          <t>7702207163948</t>
-        </is>
-      </c>
-      <c r="D1459" t="inlineStr">
-        <is>
-          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
-        </is>
-      </c>
+          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr"/>
+      <c r="D1459" t="inlineStr"/>
       <c r="E1459" t="n">
-        <v>35900</v>
+        <v>20500</v>
       </c>
       <c r="F1459" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1459" t="n">
         <v>0</v>
@@ -78080,21 +78076,29 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
-        </is>
-      </c>
-      <c r="C1460" t="inlineStr"/>
-      <c r="D1460" t="inlineStr"/>
+          <t>privatos miel limon la francol 120ml</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>7702207163948</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
+        </is>
+      </c>
       <c r="E1460" t="n">
-        <v>0</v>
+        <v>35900</v>
       </c>
       <c r="F1460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1460" t="n">
         <v>0</v>
@@ -78122,7 +78126,7 @@
       </c>
       <c r="M1460" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1460" t="inlineStr"/>
@@ -78130,21 +78134,21 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>778</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>PROTECTOR NOSOTRAS LARGOS</t>
+          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr"/>
       <c r="D1461" t="inlineStr"/>
       <c r="E1461" t="n">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="F1461" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1461" t="n">
         <v>0</v>
@@ -78172,7 +78176,7 @@
       </c>
       <c r="M1461" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1461" t="inlineStr"/>
@@ -78180,18 +78184,18 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
+          <t>PROTECTOR NOSOTRAS LARGOS</t>
         </is>
       </c>
       <c r="C1462" t="inlineStr"/>
       <c r="D1462" t="inlineStr"/>
       <c r="E1462" t="n">
-        <v>8900</v>
+        <v>3700</v>
       </c>
       <c r="F1462" t="n">
         <v>1</v>
@@ -78230,21 +78234,21 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Protector Solar Sunaid</t>
+          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
         </is>
       </c>
       <c r="C1463" t="inlineStr"/>
       <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="n">
-        <v>158000</v>
+        <v>8900</v>
       </c>
       <c r="F1463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1463" t="n">
         <v>0</v>
@@ -78280,25 +78284,21 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>Prueba de embarazo esfero</t>
-        </is>
-      </c>
-      <c r="C1464" t="inlineStr">
-        <is>
-          <t>7709299854228</t>
-        </is>
-      </c>
+          <t>Protector Solar Sunaid</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr"/>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="n">
-        <v>16500</v>
+        <v>158000</v>
       </c>
       <c r="F1464" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1464" t="n">
         <v>0</v>
@@ -78334,25 +78334,25 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>Prueba de embarazo HCG cassette begut</t>
+          <t>Prueba de embarazo esfero</t>
         </is>
       </c>
       <c r="C1465" t="inlineStr">
         <is>
-          <t>7707282990953</t>
+          <t>7709299854228</t>
         </is>
       </c>
       <c r="D1465" t="inlineStr"/>
       <c r="E1465" t="n">
-        <v>8900</v>
+        <v>16500</v>
       </c>
       <c r="F1465" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G1465" t="n">
         <v>0</v>
@@ -78388,21 +78388,25 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>PUSHER METALICO</t>
-        </is>
-      </c>
-      <c r="C1466" t="inlineStr"/>
+          <t>Prueba de embarazo HCG cassette begut</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>7707282990953</t>
+        </is>
+      </c>
       <c r="D1466" t="inlineStr"/>
       <c r="E1466" t="n">
-        <v>4300</v>
+        <v>8900</v>
       </c>
       <c r="F1466" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1466" t="n">
         <v>0</v>
@@ -78438,21 +78442,21 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
+          <t>PUSHER METALICO</t>
         </is>
       </c>
       <c r="C1467" t="inlineStr"/>
       <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="n">
-        <v>17900</v>
+        <v>4300</v>
       </c>
       <c r="F1467" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1467" t="n">
         <v>0</v>
@@ -78488,25 +78492,21 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>Recolector de orina granandina</t>
-        </is>
-      </c>
-      <c r="C1468" t="inlineStr">
-        <is>
-          <t>7707233050590</t>
-        </is>
-      </c>
+          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr"/>
       <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="n">
-        <v>673</v>
+        <v>17900</v>
       </c>
       <c r="F1468" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="G1468" t="n">
         <v>0</v>
@@ -78534,7 +78534,7 @@
       </c>
       <c r="M1468" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1468" t="inlineStr"/>
@@ -78542,21 +78542,25 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
-        </is>
-      </c>
-      <c r="C1469" t="inlineStr"/>
+          <t>Recolector de orina granandina</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>7707233050590</t>
+        </is>
+      </c>
       <c r="D1469" t="inlineStr"/>
       <c r="E1469" t="n">
-        <v>3820</v>
+        <v>673</v>
       </c>
       <c r="F1469" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G1469" t="n">
         <v>0</v>
@@ -78584,7 +78588,7 @@
       </c>
       <c r="M1469" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1469" t="inlineStr"/>
@@ -78592,21 +78596,21 @@
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>RegistroManual - Registro manual</t>
+          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
         </is>
       </c>
       <c r="C1470" t="inlineStr"/>
       <c r="D1470" t="inlineStr"/>
       <c r="E1470" t="n">
-        <v>0</v>
+        <v>3820</v>
       </c>
       <c r="F1470" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1470" t="n">
         <v>0</v>
@@ -78634,7 +78638,7 @@
       </c>
       <c r="M1470" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1470" t="inlineStr"/>
@@ -78642,21 +78646,21 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>REMOVEDOR DE ESMALTE 60CC</t>
+          <t>RegistroManual - Registro manual</t>
         </is>
       </c>
       <c r="C1471" t="inlineStr"/>
       <c r="D1471" t="inlineStr"/>
       <c r="E1471" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="F1471" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1471" t="n">
         <v>0</v>
@@ -78684,7 +78688,7 @@
       </c>
       <c r="M1471" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1471" t="inlineStr"/>
@@ -78692,25 +78696,21 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
-        </is>
-      </c>
-      <c r="C1472" t="inlineStr">
-        <is>
-          <t>7591005981270</t>
-        </is>
-      </c>
+          <t>REMOVEDOR DE ESMALTE 60CC</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr"/>
       <c r="D1472" t="inlineStr"/>
       <c r="E1472" t="n">
-        <v>9500</v>
+        <v>3500</v>
       </c>
       <c r="F1472" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1472" t="n">
         <v>0</v>
@@ -78746,22 +78746,22 @@
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
+          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
         </is>
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>7503051868245</t>
+          <t>7591005981270</t>
         </is>
       </c>
       <c r="D1473" t="inlineStr"/>
       <c r="E1473" t="n">
-        <v>20900</v>
+        <v>9500</v>
       </c>
       <c r="F1473" t="n">
         <v>1</v>
@@ -78800,25 +78800,25 @@
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
         </is>
       </c>
       <c r="C1474" t="inlineStr">
         <is>
-          <t>7702057079642</t>
+          <t>7503051868245</t>
         </is>
       </c>
       <c r="D1474" t="inlineStr"/>
       <c r="E1474" t="n">
-        <v>13000</v>
+        <v>20900</v>
       </c>
       <c r="F1474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1474" t="n">
         <v>0</v>
@@ -78854,18 +78854,22 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>Ryaltris Spray Nasal 240 dosis</t>
-        </is>
-      </c>
-      <c r="C1475" t="inlineStr"/>
+          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>7702057079642</t>
+        </is>
+      </c>
       <c r="D1475" t="inlineStr"/>
       <c r="E1475" t="n">
-        <v>216400</v>
+        <v>13000</v>
       </c>
       <c r="F1475" t="n">
         <v>0</v>
@@ -78904,25 +78908,21 @@
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
-        </is>
-      </c>
-      <c r="C1476" t="inlineStr">
-        <is>
-          <t>7706849116676</t>
-        </is>
-      </c>
+          <t>Ryaltris Spray Nasal 240 dosis</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr"/>
       <c r="D1476" t="inlineStr"/>
       <c r="E1476" t="n">
-        <v>31500</v>
+        <v>216400</v>
       </c>
       <c r="F1476" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1476" t="n">
         <v>0</v>
@@ -78958,21 +78958,25 @@
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>SCOBIT PURGANTE 60GR</t>
-        </is>
-      </c>
-      <c r="C1477" t="inlineStr"/>
+          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>7706849116676</t>
+        </is>
+      </c>
       <c r="D1477" t="inlineStr"/>
       <c r="E1477" t="n">
-        <v>15238.095238</v>
+        <v>31500</v>
       </c>
       <c r="F1477" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1477" t="n">
         <v>0</v>
@@ -79000,7 +79004,7 @@
       </c>
       <c r="M1477" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1477" t="inlineStr"/>
@@ -79008,21 +79012,21 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
+          <t>SCOBIT PURGANTE 60GR</t>
         </is>
       </c>
       <c r="C1478" t="inlineStr"/>
       <c r="D1478" t="inlineStr"/>
       <c r="E1478" t="n">
-        <v>6554.621849</v>
+        <v>15238.095238</v>
       </c>
       <c r="F1478" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1478" t="n">
         <v>0</v>
@@ -79050,7 +79054,7 @@
       </c>
       <c r="M1478" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1478" t="inlineStr"/>
@@ -79058,25 +79062,21 @@
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>SHAMPOO PANTENE COLAGENO</t>
-        </is>
-      </c>
-      <c r="C1479" t="inlineStr">
-        <is>
-          <t>7500435191500</t>
-        </is>
-      </c>
+          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr"/>
       <c r="D1479" t="inlineStr"/>
       <c r="E1479" t="n">
-        <v>1429</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1479" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1479" t="n">
         <v>0</v>
@@ -79112,21 +79112,25 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>SILDENAFIL 50MG TQ</t>
-        </is>
-      </c>
-      <c r="C1480" t="inlineStr"/>
+          <t>SHAMPOO PANTENE COLAGENO</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>7500435191500</t>
+        </is>
+      </c>
       <c r="D1480" t="inlineStr"/>
       <c r="E1480" t="n">
-        <v>5000</v>
+        <v>1429</v>
       </c>
       <c r="F1480" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1480" t="n">
         <v>0</v>
@@ -79154,7 +79158,7 @@
       </c>
       <c r="M1480" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1480" t="inlineStr"/>
@@ -79162,25 +79166,21 @@
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>SILIMARINA 167MG EPANAT</t>
-        </is>
-      </c>
-      <c r="C1481" t="inlineStr">
-        <is>
-          <t>7706849115921</t>
-        </is>
-      </c>
+          <t>SILDENAFIL 50MG TQ</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr"/>
       <c r="D1481" t="inlineStr"/>
       <c r="E1481" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F1481" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G1481" t="n">
         <v>0</v>
@@ -79216,21 +79216,25 @@
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>SMECTA 3GR NARANJA S/B</t>
-        </is>
-      </c>
-      <c r="C1482" t="inlineStr"/>
+          <t>SILIMARINA 167MG EPANAT</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>7706849115921</t>
+        </is>
+      </c>
       <c r="D1482" t="inlineStr"/>
       <c r="E1482" t="n">
-        <v>8900</v>
+        <v>2000</v>
       </c>
       <c r="F1482" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G1482" t="n">
         <v>0</v>
@@ -79266,21 +79270,21 @@
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>SONDA FOLEY 2 VIAS BAL #18</t>
+          <t>SMECTA 3GR NARANJA S/B</t>
         </is>
       </c>
       <c r="C1483" t="inlineStr"/>
       <c r="D1483" t="inlineStr"/>
       <c r="E1483" t="n">
-        <v>7500</v>
+        <v>8900</v>
       </c>
       <c r="F1483" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G1483" t="n">
         <v>0</v>
@@ -79316,21 +79320,21 @@
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>SONDA NELATON #6</t>
+          <t>SONDA FOLEY 2 VIAS BAL #18</t>
         </is>
       </c>
       <c r="C1484" t="inlineStr"/>
       <c r="D1484" t="inlineStr"/>
       <c r="E1484" t="n">
-        <v>2500</v>
+        <v>7500</v>
       </c>
       <c r="F1484" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1484" t="n">
         <v>0</v>
@@ -79366,21 +79370,21 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>SPRAY NASAL MOMETASONA 18ML</t>
+          <t>SONDA NELATON #6</t>
         </is>
       </c>
       <c r="C1485" t="inlineStr"/>
       <c r="D1485" t="inlineStr"/>
       <c r="E1485" t="n">
-        <v>36900</v>
+        <v>2500</v>
       </c>
       <c r="F1485" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1485" t="n">
         <v>0</v>
@@ -79416,25 +79420,21 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1486" t="inlineStr">
-        <is>
-          <t>7703712035034</t>
-        </is>
-      </c>
+          <t>SPRAY NASAL MOMETASONA 18ML</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr"/>
       <c r="D1486" t="inlineStr"/>
       <c r="E1486" t="n">
-        <v>14800</v>
+        <v>36900</v>
       </c>
       <c r="F1486" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1486" t="n">
         <v>0</v>
@@ -79470,21 +79470,25 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
-        </is>
-      </c>
-      <c r="C1487" t="inlineStr"/>
+          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>7703712035034</t>
+        </is>
+      </c>
       <c r="D1487" t="inlineStr"/>
       <c r="E1487" t="n">
-        <v>3781.512605</v>
+        <v>14800</v>
       </c>
       <c r="F1487" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1487" t="n">
         <v>0</v>
@@ -79512,7 +79516,7 @@
       </c>
       <c r="M1487" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1487" t="inlineStr"/>
@@ -79520,21 +79524,21 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
+          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
         </is>
       </c>
       <c r="C1488" t="inlineStr"/>
       <c r="D1488" t="inlineStr"/>
       <c r="E1488" t="n">
-        <v>5210.084034</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1488" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1488" t="n">
         <v>0</v>
@@ -79570,21 +79574,21 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
+          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr"/>
       <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="n">
-        <v>8319.327730999999</v>
+        <v>5210.084034</v>
       </c>
       <c r="F1489" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1489" t="n">
         <v>0</v>
@@ -79620,18 +79624,18 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>SULZINC SUSP X 80ML HUMAX</t>
+          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
         </is>
       </c>
       <c r="C1490" t="inlineStr"/>
       <c r="D1490" t="inlineStr"/>
       <c r="E1490" t="n">
-        <v>22400</v>
+        <v>8319.327730999999</v>
       </c>
       <c r="F1490" t="n">
         <v>1</v>
@@ -79662,7 +79666,7 @@
       </c>
       <c r="M1490" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1490" t="inlineStr"/>
@@ -79670,21 +79674,21 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>SUNDARK FPS 60 CON TAPA</t>
+          <t>SULZINC SUSP X 80ML HUMAX</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr"/>
       <c r="D1491" t="inlineStr"/>
       <c r="E1491" t="n">
-        <v>3781.512605</v>
+        <v>22400</v>
       </c>
       <c r="F1491" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1491" t="n">
         <v>0</v>
@@ -79712,7 +79716,7 @@
       </c>
       <c r="M1491" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1491" t="inlineStr"/>
@@ -79720,21 +79724,21 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>Synthroid 125 mcg</t>
+          <t>SUNDARK FPS 60 CON TAPA</t>
         </is>
       </c>
       <c r="C1492" t="inlineStr"/>
       <c r="D1492" t="inlineStr"/>
       <c r="E1492" t="n">
-        <v>178000</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1492" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1492" t="n">
         <v>0</v>
@@ -79762,7 +79766,7 @@
       </c>
       <c r="M1492" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1492" t="inlineStr"/>
@@ -79770,25 +79774,21 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>Talco medicado Neofungina 40gm</t>
-        </is>
-      </c>
-      <c r="C1493" t="inlineStr">
-        <is>
-          <t>7706142707106</t>
-        </is>
-      </c>
+          <t>Synthroid 125 mcg</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr"/>
       <c r="D1493" t="inlineStr"/>
       <c r="E1493" t="n">
-        <v>14900</v>
+        <v>178000</v>
       </c>
       <c r="F1493" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1493" t="n">
         <v>0</v>
@@ -79824,21 +79824,25 @@
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
-        </is>
-      </c>
-      <c r="C1494" t="inlineStr"/>
+          <t>Talco medicado Neofungina 40gm</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>7706142707106</t>
+        </is>
+      </c>
       <c r="D1494" t="inlineStr"/>
       <c r="E1494" t="n">
-        <v>13300</v>
+        <v>14900</v>
       </c>
       <c r="F1494" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1494" t="n">
         <v>0</v>
@@ -79874,21 +79878,21 @@
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
+          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
         </is>
       </c>
       <c r="C1495" t="inlineStr"/>
       <c r="D1495" t="inlineStr"/>
       <c r="E1495" t="n">
-        <v>4874</v>
+        <v>13300</v>
       </c>
       <c r="F1495" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G1495" t="n">
         <v>0</v>
@@ -79916,7 +79920,7 @@
       </c>
       <c r="M1495" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1495" t="inlineStr"/>
@@ -79924,21 +79928,21 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
+          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
         </is>
       </c>
       <c r="C1496" t="inlineStr"/>
       <c r="D1496" t="inlineStr"/>
       <c r="E1496" t="n">
-        <v>28800</v>
+        <v>4874</v>
       </c>
       <c r="F1496" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G1496" t="n">
         <v>0</v>
@@ -79966,7 +79970,7 @@
       </c>
       <c r="M1496" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1496" t="inlineStr"/>
@@ -79974,21 +79978,21 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
+          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr"/>
       <c r="D1497" t="inlineStr"/>
       <c r="E1497" t="n">
-        <v>11596.638655</v>
+        <v>28800</v>
       </c>
       <c r="F1497" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1497" t="n">
         <v>0</v>
@@ -80016,7 +80020,7 @@
       </c>
       <c r="M1497" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1497" t="inlineStr"/>
@@ -80024,21 +80028,21 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>TIJERA DE DOBLAR METALICA</t>
+          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
         </is>
       </c>
       <c r="C1498" t="inlineStr"/>
       <c r="D1498" t="inlineStr"/>
       <c r="E1498" t="n">
-        <v>3500</v>
+        <v>11596.638655</v>
       </c>
       <c r="F1498" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1498" t="n">
         <v>0</v>
@@ -80066,7 +80070,7 @@
       </c>
       <c r="M1498" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1498" t="inlineStr"/>
@@ -80074,21 +80078,21 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+          <t>TIJERA DE DOBLAR METALICA</t>
         </is>
       </c>
       <c r="C1499" t="inlineStr"/>
       <c r="D1499" t="inlineStr"/>
       <c r="E1499" t="n">
-        <v>3781.512605</v>
+        <v>3500</v>
       </c>
       <c r="F1499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1499" t="n">
         <v>0</v>
@@ -80116,7 +80120,7 @@
       </c>
       <c r="M1499" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1499" t="inlineStr"/>
@@ -80124,21 +80128,21 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+          <t>TINTURA DE RUIBARDO FCO 30ML</t>
         </is>
       </c>
       <c r="C1500" t="inlineStr"/>
       <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="n">
-        <v>29800</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1500" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1500" t="n">
         <v>0</v>
@@ -80166,7 +80170,7 @@
       </c>
       <c r="M1500" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1500" t="inlineStr"/>
@@ -80174,25 +80178,21 @@
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
-        </is>
-      </c>
-      <c r="C1501" t="inlineStr">
-        <is>
-          <t>7702026149567</t>
-        </is>
-      </c>
+          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr"/>
       <c r="D1501" t="inlineStr"/>
       <c r="E1501" t="n">
-        <v>13500</v>
+        <v>29800</v>
       </c>
       <c r="F1501" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1501" t="n">
         <v>0</v>
@@ -80228,25 +80228,25 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>Toallas húmedas winny 24unidades</t>
+          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
         </is>
       </c>
       <c r="C1502" t="inlineStr">
         <is>
-          <t>7701021143655</t>
+          <t>7702026149567</t>
         </is>
       </c>
       <c r="D1502" t="inlineStr"/>
       <c r="E1502" t="n">
-        <v>4033.613445</v>
+        <v>13500</v>
       </c>
       <c r="F1502" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G1502" t="n">
         <v>0</v>
@@ -80274,7 +80274,7 @@
       </c>
       <c r="M1502" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1502" t="inlineStr"/>
@@ -80282,25 +80282,25 @@
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>Toallas maternas maternity</t>
+          <t>Toallas húmedas winny 24unidades</t>
         </is>
       </c>
       <c r="C1503" t="inlineStr">
         <is>
-          <t>7703252489526</t>
+          <t>7701021143655</t>
         </is>
       </c>
       <c r="D1503" t="inlineStr"/>
       <c r="E1503" t="n">
-        <v>16900</v>
+        <v>4033.613445</v>
       </c>
       <c r="F1503" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G1503" t="n">
         <v>0</v>
@@ -80328,7 +80328,7 @@
       </c>
       <c r="M1503" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1503" t="inlineStr"/>
@@ -80336,25 +80336,25 @@
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>Toallas Nosotras Rapigel x Und</t>
+          <t>Toallas maternas maternity</t>
         </is>
       </c>
       <c r="C1504" t="inlineStr">
         <is>
-          <t>7702027416859</t>
+          <t>7703252489526</t>
         </is>
       </c>
       <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="n">
-        <v>756.302521</v>
+        <v>16900</v>
       </c>
       <c r="F1504" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="G1504" t="n">
         <v>0</v>
@@ -80382,7 +80382,7 @@
       </c>
       <c r="M1504" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1504" t="inlineStr"/>
@@ -80390,21 +80390,25 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>TRAMADOL 50MG CAPSULA MP</t>
-        </is>
-      </c>
-      <c r="C1505" t="inlineStr"/>
+          <t>Toallas Nosotras Rapigel x Und</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>7702027416859</t>
+        </is>
+      </c>
       <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="n">
-        <v>1500</v>
+        <v>756.302521</v>
       </c>
       <c r="F1505" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G1505" t="n">
         <v>0</v>
@@ -80432,7 +80436,7 @@
       </c>
       <c r="M1505" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1505" t="inlineStr"/>
@@ -80440,25 +80444,21 @@
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>Tramadol clorhidrato 100mg laquifar</t>
-        </is>
-      </c>
-      <c r="C1506" t="inlineStr">
-        <is>
-          <t>7707019426977</t>
-        </is>
-      </c>
+          <t>TRAMADOL 50MG CAPSULA MP</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr"/>
       <c r="D1506" t="inlineStr"/>
       <c r="E1506" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="F1506" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G1506" t="n">
         <v>0</v>
@@ -80494,18 +80494,22 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>TRIGENTAX CREMA TBO X 20GR</t>
-        </is>
-      </c>
-      <c r="C1507" t="inlineStr"/>
+          <t>Tramadol clorhidrato 100mg laquifar</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>7707019426977</t>
+        </is>
+      </c>
       <c r="D1507" t="inlineStr"/>
       <c r="E1507" t="n">
-        <v>33500</v>
+        <v>1600</v>
       </c>
       <c r="F1507" t="n">
         <v>0</v>
@@ -80544,21 +80548,21 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
+          <t>TRIGENTAX CREMA TBO X 20GR</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr"/>
       <c r="D1508" t="inlineStr"/>
       <c r="E1508" t="n">
-        <v>9000</v>
+        <v>33500</v>
       </c>
       <c r="F1508" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1508" t="n">
         <v>0</v>
@@ -80594,21 +80598,21 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
+          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
         </is>
       </c>
       <c r="C1509" t="inlineStr"/>
       <c r="D1509" t="inlineStr"/>
       <c r="E1509" t="n">
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="F1509" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1509" t="n">
         <v>0</v>
@@ -80644,12 +80648,12 @@
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
+          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr"/>
@@ -80658,7 +80662,7 @@
         <v>10500</v>
       </c>
       <c r="F1510" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G1510" t="n">
         <v>0</v>
@@ -80694,21 +80698,21 @@
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
+          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
         </is>
       </c>
       <c r="C1511" t="inlineStr"/>
       <c r="D1511" t="inlineStr"/>
       <c r="E1511" t="n">
-        <v>18800</v>
+        <v>10500</v>
       </c>
       <c r="F1511" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G1511" t="n">
         <v>0</v>
@@ -80744,21 +80748,21 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
+          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
         </is>
       </c>
       <c r="C1512" t="inlineStr"/>
       <c r="D1512" t="inlineStr"/>
       <c r="E1512" t="n">
-        <v>13800</v>
+        <v>18800</v>
       </c>
       <c r="F1512" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1512" t="n">
         <v>0</v>
@@ -80794,21 +80798,21 @@
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
+          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
         </is>
       </c>
       <c r="C1513" t="inlineStr"/>
       <c r="D1513" t="inlineStr"/>
       <c r="E1513" t="n">
-        <v>7900</v>
+        <v>13800</v>
       </c>
       <c r="F1513" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1513" t="n">
         <v>0</v>
@@ -80844,21 +80848,21 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>VASELINA FC X 200GR YOMA</t>
+          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
         </is>
       </c>
       <c r="C1514" t="inlineStr"/>
       <c r="D1514" t="inlineStr"/>
       <c r="E1514" t="n">
-        <v>12521.008403</v>
+        <v>7900</v>
       </c>
       <c r="F1514" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1514" t="n">
         <v>0</v>
@@ -80886,7 +80890,7 @@
       </c>
       <c r="M1514" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1514" t="inlineStr"/>
@@ -80894,21 +80898,21 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
+          <t>VASELINA FC X 200GR YOMA</t>
         </is>
       </c>
       <c r="C1515" t="inlineStr"/>
       <c r="D1515" t="inlineStr"/>
       <c r="E1515" t="n">
-        <v>420.168067</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1515" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1515" t="n">
         <v>0</v>
@@ -80944,25 +80948,21 @@
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
-        </is>
-      </c>
-      <c r="C1516" t="inlineStr">
-        <is>
-          <t>7708480649803</t>
-        </is>
-      </c>
+          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr"/>
       <c r="D1516" t="inlineStr"/>
       <c r="E1516" t="n">
-        <v>28000</v>
+        <v>420.168067</v>
       </c>
       <c r="F1516" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1516" t="n">
         <v>0</v>
@@ -80990,7 +80990,7 @@
       </c>
       <c r="M1516" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1516" t="inlineStr"/>
@@ -80998,25 +80998,25 @@
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>Venda Elastica 6x5 y piel</t>
-        </is>
-      </c>
-      <c r="C1517" t="inlineStr"/>
-      <c r="D1517" t="inlineStr">
-        <is>
-          <t>SUBIO A 6200 ANTES 5700</t>
-        </is>
-      </c>
+          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>7708480649803</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr"/>
       <c r="E1517" t="n">
-        <v>6200</v>
+        <v>28000</v>
       </c>
       <c r="F1517" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1517" t="n">
         <v>0</v>
@@ -81052,18 +81052,22 @@
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
+          <t>Venda Elastica 6x5 y piel</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr"/>
-      <c r="D1518" t="inlineStr"/>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>SUBIO A 6200 ANTES 5700</t>
+        </is>
+      </c>
       <c r="E1518" t="n">
-        <v>5500</v>
+        <v>6200</v>
       </c>
       <c r="F1518" t="n">
         <v>3</v>
@@ -81102,21 +81106,21 @@
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>Venta simple</t>
+          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
         </is>
       </c>
       <c r="C1519" t="inlineStr"/>
       <c r="D1519" t="inlineStr"/>
       <c r="E1519" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="F1519" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1519" t="n">
         <v>0</v>
@@ -81134,7 +81138,7 @@
       </c>
       <c r="K1519" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="L1519" t="inlineStr">
@@ -81142,27 +81146,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1519" t="inlineStr"/>
+      <c r="M1519" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1519" t="inlineStr"/>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
+          <t>Venta simple</t>
         </is>
       </c>
       <c r="C1520" t="inlineStr"/>
       <c r="D1520" t="inlineStr"/>
       <c r="E1520" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F1520" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1520" t="n">
         <v>0</v>
@@ -81180,7 +81188,7 @@
       </c>
       <c r="K1520" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="L1520" t="inlineStr">
@@ -81188,35 +81196,27 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1520" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1520" t="inlineStr"/>
       <c r="N1520" t="inlineStr"/>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
-        </is>
-      </c>
-      <c r="C1521" t="inlineStr">
-        <is>
-          <t>793969226467</t>
-        </is>
-      </c>
+          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr"/>
       <c r="D1521" t="inlineStr"/>
       <c r="E1521" t="n">
-        <v>17000</v>
+        <v>1000</v>
       </c>
       <c r="F1521" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1521" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
       </c>
       <c r="L1521" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="M1521" t="inlineStr">
@@ -81252,21 +81252,25 @@
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>VINO CEREBRAL JARABE X 1100ML</t>
-        </is>
-      </c>
-      <c r="C1522" t="inlineStr"/>
+          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>793969226467</t>
+        </is>
+      </c>
       <c r="D1522" t="inlineStr"/>
       <c r="E1522" t="n">
-        <v>48900</v>
+        <v>17000</v>
       </c>
       <c r="F1522" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1522" t="n">
         <v>0</v>
@@ -81289,7 +81293,7 @@
       </c>
       <c r="L1522" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="M1522" t="inlineStr">
@@ -81302,21 +81306,21 @@
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
+          <t>VINO CEREBRAL JARABE X 1100ML</t>
         </is>
       </c>
       <c r="C1523" t="inlineStr"/>
       <c r="D1523" t="inlineStr"/>
       <c r="E1523" t="n">
-        <v>5400</v>
+        <v>48900</v>
       </c>
       <c r="F1523" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G1523" t="n">
         <v>0</v>
@@ -81352,21 +81356,21 @@
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
+          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
         </is>
       </c>
       <c r="C1524" t="inlineStr"/>
       <c r="D1524" t="inlineStr"/>
       <c r="E1524" t="n">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="F1524" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G1524" t="n">
         <v>0</v>
@@ -81402,21 +81406,21 @@
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>WINNY PAÑAL ETP 6 X 30</t>
+          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
         </is>
       </c>
       <c r="C1525" t="inlineStr"/>
       <c r="D1525" t="inlineStr"/>
       <c r="E1525" t="n">
-        <v>57000</v>
+        <v>5500</v>
       </c>
       <c r="F1525" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G1525" t="n">
         <v>0</v>
@@ -81452,52 +81456,102 @@
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>YODO BLANCO FC X30ML</t>
+          <t>WINNY PAÑAL ETP 6 X 30</t>
         </is>
       </c>
       <c r="C1526" t="inlineStr"/>
       <c r="D1526" t="inlineStr"/>
       <c r="E1526" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F1526" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1526" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1526" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1526" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1526" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1526" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1526" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1526" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1526" t="inlineStr"/>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>YODO BLANCO FC X30ML</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr"/>
+      <c r="D1527" t="inlineStr"/>
+      <c r="E1527" t="n">
         <v>6000</v>
       </c>
-      <c r="F1526" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1526" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1526" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1526" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1526" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="K1526" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="L1526" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="M1526" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="N1526" t="inlineStr"/>
+      <c r="F1527" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1527" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1527" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1527" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1527" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1527" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1527" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1527" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1527" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1527"/>
+  <dimension ref="A1:N1529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69328,18 +69328,22 @@
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>Citrato de calcio / Vitamina D3 600 MG/400UI (1500MG) Granulos Caja x 15 Sobres</t>
-        </is>
-      </c>
-      <c r="C1290" t="inlineStr"/>
+          <t>CINTA DE PAPEL QUIRURGICO HIPOALERGICO 1/2 PROLATEX</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>7709414102654</t>
+        </is>
+      </c>
       <c r="D1290" t="inlineStr"/>
       <c r="E1290" t="n">
-        <v>53000</v>
+        <v>6000</v>
       </c>
       <c r="F1290" t="n">
         <v>0</v>
@@ -69378,21 +69382,21 @@
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>769</t>
         </is>
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>CLENOX 40MG 1J/PRELLE.</t>
+          <t>Citrato de calcio / Vitamina D3 600 MG/400UI (1500MG) Granulos Caja x 15 Sobres</t>
         </is>
       </c>
       <c r="C1291" t="inlineStr"/>
       <c r="D1291" t="inlineStr"/>
       <c r="E1291" t="n">
-        <v>17800</v>
+        <v>53000</v>
       </c>
       <c r="F1291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1291" t="n">
         <v>0</v>
@@ -69428,25 +69432,21 @@
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>CLINBAC CLINDAMICINA 300MG CAPS</t>
-        </is>
-      </c>
-      <c r="C1292" t="inlineStr">
-        <is>
-          <t>7707019413816</t>
-        </is>
-      </c>
+          <t>CLENOX 40MG 1J/PRELLE.</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr"/>
       <c r="D1292" t="inlineStr"/>
       <c r="E1292" t="n">
-        <v>19200</v>
+        <v>17800</v>
       </c>
       <c r="F1292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1292" t="n">
         <v>0</v>
@@ -69482,21 +69482,25 @@
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>CLINDABACT CLOTRI+CLIND CJA X 3 OVULOS</t>
-        </is>
-      </c>
-      <c r="C1293" t="inlineStr"/>
+          <t>CLINBAC CLINDAMICINA 300MG CAPS</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>7707019413816</t>
+        </is>
+      </c>
       <c r="D1293" t="inlineStr"/>
       <c r="E1293" t="n">
-        <v>35700</v>
+        <v>19200</v>
       </c>
       <c r="F1293" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1293" t="n">
         <v>0</v>
@@ -69532,25 +69536,21 @@
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>CLOBETASOL 0,05% TRIDIRTEX CREMA X 40GR</t>
-        </is>
-      </c>
-      <c r="C1294" t="inlineStr">
-        <is>
-          <t>7709740450351</t>
-        </is>
-      </c>
+          <t>CLINDABACT CLOTRI+CLIND CJA X 3 OVULOS</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr"/>
       <c r="D1294" t="inlineStr"/>
       <c r="E1294" t="n">
-        <v>27900</v>
+        <v>35700</v>
       </c>
       <c r="F1294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1294" t="n">
         <v>0</v>
@@ -69586,25 +69586,25 @@
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>Clotrimazol 1% 40gr AG</t>
+          <t>CLOBETASOL 0,05% TRIDIRTEX CREMA X 40GR</t>
         </is>
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>7706569001191</t>
+          <t>7709740450351</t>
         </is>
       </c>
       <c r="D1295" t="inlineStr"/>
       <c r="E1295" t="n">
-        <v>19000</v>
+        <v>27900</v>
       </c>
       <c r="F1295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1295" t="n">
         <v>0</v>
@@ -69640,25 +69640,25 @@
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>CLOTRIMAZOL 1% CREMA TOPICA DE VITALIS</t>
+          <t>Clotrimazol 1% 40gr AG</t>
         </is>
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>7709990212204</t>
+          <t>7706569001191</t>
         </is>
       </c>
       <c r="D1296" t="inlineStr"/>
       <c r="E1296" t="n">
-        <v>14500</v>
+        <v>19000</v>
       </c>
       <c r="F1296" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1296" t="n">
         <v>0</v>
@@ -69694,21 +69694,25 @@
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>COLAGENO HIDROLIZADO EN POLVO 700GR ARMONIZA</t>
-        </is>
-      </c>
-      <c r="C1297" t="inlineStr"/>
+          <t>CLOTRIMAZOL 1% CREMA TOPICA DE VITALIS</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>7709990212204</t>
+        </is>
+      </c>
       <c r="D1297" t="inlineStr"/>
       <c r="E1297" t="n">
-        <v>56000</v>
+        <v>14500</v>
       </c>
       <c r="F1297" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1297" t="n">
         <v>0</v>
@@ -69744,21 +69748,21 @@
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>Colchicina Coas</t>
+          <t>COLAGENO HIDROLIZADO EN POLVO 700GR ARMONIZA</t>
         </is>
       </c>
       <c r="C1298" t="inlineStr"/>
       <c r="D1298" t="inlineStr"/>
       <c r="E1298" t="n">
-        <v>3900</v>
+        <v>56000</v>
       </c>
       <c r="F1298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1298" t="n">
         <v>0</v>
@@ -69794,18 +69798,18 @@
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>CONDON DUO LUBRICADO X 3 UND</t>
+          <t>Colchicina Coas</t>
         </is>
       </c>
       <c r="C1299" t="inlineStr"/>
       <c r="D1299" t="inlineStr"/>
       <c r="E1299" t="n">
-        <v>16500</v>
+        <v>3900</v>
       </c>
       <c r="F1299" t="n">
         <v>1</v>
@@ -69844,18 +69848,18 @@
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
+          <t>CONDON DUO LUBRICADO X 3 UND</t>
         </is>
       </c>
       <c r="C1300" t="inlineStr"/>
       <c r="D1300" t="inlineStr"/>
       <c r="E1300" t="n">
-        <v>8900</v>
+        <v>16500</v>
       </c>
       <c r="F1300" t="n">
         <v>1</v>
@@ -69894,7 +69898,7 @@
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="B1301" t="inlineStr">
@@ -69908,7 +69912,7 @@
         <v>8900</v>
       </c>
       <c r="F1301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1301" t="n">
         <v>0</v>
@@ -69944,12 +69948,12 @@
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>CONDON PIEL SABORES CJA X 3 UNDS</t>
+          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
         </is>
       </c>
       <c r="C1302" t="inlineStr"/>
@@ -69994,25 +69998,21 @@
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>CONDON PRUDENCE EFEC.RETARDX3UNDS</t>
-        </is>
-      </c>
-      <c r="C1303" t="inlineStr">
-        <is>
-          <t>77309632510504387</t>
-        </is>
-      </c>
+          <t>CONDON PIEL SABORES CJA X 3 UNDS</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr"/>
       <c r="D1303" t="inlineStr"/>
       <c r="E1303" t="n">
-        <v>12200</v>
+        <v>8900</v>
       </c>
       <c r="F1303" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1303" t="n">
         <v>0</v>
@@ -70048,25 +70048,25 @@
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>CONDON PRUDENCE EXTRA GRANDE ULT SENSIBX3UND</t>
+          <t>CONDON PRUDENCE EFEC.RETARDX3UNDS</t>
         </is>
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>7730963250343</t>
+          <t>77309632510504387</t>
         </is>
       </c>
       <c r="D1304" t="inlineStr"/>
       <c r="E1304" t="n">
-        <v>13800</v>
+        <v>12200</v>
       </c>
       <c r="F1304" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1304" t="n">
         <v>0</v>
@@ -70102,25 +70102,25 @@
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>CONTENT MEDICAL PAÑAL TALLA L X UND</t>
-        </is>
-      </c>
-      <c r="C1305" t="inlineStr"/>
-      <c r="D1305" t="inlineStr">
-        <is>
-          <t>pañal adulto no paga iva articulo 424</t>
-        </is>
-      </c>
+          <t>CONDON PRUDENCE EXTRA GRANDE ULT SENSIBX3UND</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>7730963250343</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr"/>
       <c r="E1305" t="n">
-        <v>4800</v>
+        <v>13800</v>
       </c>
       <c r="F1305" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G1305" t="n">
         <v>0</v>
@@ -70156,21 +70156,25 @@
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>CONTENT MEDICAL PAÑAL TALLA M X UND</t>
+          <t>CONTENT MEDICAL PAÑAL TALLA L X UND</t>
         </is>
       </c>
       <c r="C1306" t="inlineStr"/>
-      <c r="D1306" t="inlineStr"/>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>pañal adulto no paga iva articulo 424</t>
+        </is>
+      </c>
       <c r="E1306" t="n">
-        <v>3697.478992</v>
+        <v>4800</v>
       </c>
       <c r="F1306" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G1306" t="n">
         <v>0</v>
@@ -70198,7 +70202,7 @@
       </c>
       <c r="M1306" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1306" t="inlineStr"/>
@@ -70206,21 +70210,21 @@
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 100 UNDS</t>
+          <t>CONTENT MEDICAL PAÑAL TALLA M X UND</t>
         </is>
       </c>
       <c r="C1307" t="inlineStr"/>
       <c r="D1307" t="inlineStr"/>
       <c r="E1307" t="n">
-        <v>8500</v>
+        <v>3697.478992</v>
       </c>
       <c r="F1307" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G1307" t="n">
         <v>0</v>
@@ -70248,7 +70252,7 @@
       </c>
       <c r="M1307" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1307" t="inlineStr"/>
@@ -70256,18 +70260,18 @@
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 50 UNDS</t>
+          <t>COPITOS YOKY X 100 UNDS</t>
         </is>
       </c>
       <c r="C1308" t="inlineStr"/>
       <c r="D1308" t="inlineStr"/>
       <c r="E1308" t="n">
-        <v>6400</v>
+        <v>8500</v>
       </c>
       <c r="F1308" t="n">
         <v>3</v>
@@ -70306,21 +70310,21 @@
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 60 UNDS</t>
+          <t>COPITOS YOKY X 50 UNDS</t>
         </is>
       </c>
       <c r="C1309" t="inlineStr"/>
       <c r="D1309" t="inlineStr"/>
       <c r="E1309" t="n">
-        <v>7142.857143</v>
+        <v>6400</v>
       </c>
       <c r="F1309" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1309" t="n">
         <v>0</v>
@@ -70348,7 +70352,7 @@
       </c>
       <c r="M1309" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1309" t="inlineStr"/>
@@ -70356,21 +70360,21 @@
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>CORTA CUTICULA TRIM METALICO</t>
+          <t>COPITOS YOKY X 60 UNDS</t>
         </is>
       </c>
       <c r="C1310" t="inlineStr"/>
       <c r="D1310" t="inlineStr"/>
       <c r="E1310" t="n">
-        <v>16000</v>
+        <v>7142.857143</v>
       </c>
       <c r="F1310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1310" t="n">
         <v>0</v>
@@ -70398,7 +70402,7 @@
       </c>
       <c r="M1310" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1310" t="inlineStr"/>
@@ -70406,21 +70410,21 @@
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>CREMA ARNICA PROTECTORA 12GR ICE POWER</t>
+          <t>CORTA CUTICULA TRIM METALICO</t>
         </is>
       </c>
       <c r="C1311" t="inlineStr"/>
       <c r="D1311" t="inlineStr"/>
       <c r="E1311" t="n">
-        <v>10084.033613</v>
+        <v>16000</v>
       </c>
       <c r="F1311" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1311" t="n">
         <v>0</v>
@@ -70448,7 +70452,7 @@
       </c>
       <c r="M1311" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1311" t="inlineStr"/>
@@ -70456,21 +70460,21 @@
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>CREMA BENLIC DE 40GR</t>
+          <t>CREMA ARNICA PROTECTORA 12GR ICE POWER</t>
         </is>
       </c>
       <c r="C1312" t="inlineStr"/>
       <c r="D1312" t="inlineStr"/>
       <c r="E1312" t="n">
-        <v>28900</v>
+        <v>10084.033613</v>
       </c>
       <c r="F1312" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1312" t="n">
         <v>0</v>
@@ -70498,7 +70502,7 @@
       </c>
       <c r="M1312" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1312" t="inlineStr"/>
@@ -70506,18 +70510,18 @@
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>CREMA CASTAÑO DE INDIAS X 12GR ARMONIZA</t>
+          <t>CREMA BENLIC DE 40GR</t>
         </is>
       </c>
       <c r="C1313" t="inlineStr"/>
       <c r="D1313" t="inlineStr"/>
       <c r="E1313" t="n">
-        <v>9000</v>
+        <v>28900</v>
       </c>
       <c r="F1313" t="n">
         <v>1</v>
@@ -70556,25 +70560,21 @@
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>Crema Colgate triple acción xtra blancura 60ml</t>
-        </is>
-      </c>
-      <c r="C1314" t="inlineStr">
-        <is>
-          <t>7702010111587</t>
-        </is>
-      </c>
+          <t>CREMA CASTAÑO DE INDIAS X 12GR ARMONIZA</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr"/>
       <c r="D1314" t="inlineStr"/>
       <c r="E1314" t="n">
-        <v>5630.252101</v>
+        <v>9000</v>
       </c>
       <c r="F1314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1314" t="n">
         <v>0</v>
@@ -70602,7 +70602,7 @@
       </c>
       <c r="M1314" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1314" t="inlineStr"/>
@@ -70610,21 +70610,25 @@
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>CREMA PONDS CLARANT B3 X SACHETS</t>
-        </is>
-      </c>
-      <c r="C1315" t="inlineStr"/>
+          <t>Crema Colgate triple acción xtra blancura 60ml</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>7702010111587</t>
+        </is>
+      </c>
       <c r="D1315" t="inlineStr"/>
       <c r="E1315" t="n">
-        <v>2521.008403</v>
+        <v>5630.252101</v>
       </c>
       <c r="F1315" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1315" t="n">
         <v>0</v>
@@ -70660,21 +70664,21 @@
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>CURAS LARGAS RESIST AL AGUA</t>
+          <t>CREMA PONDS CLARANT B3 X SACHETS</t>
         </is>
       </c>
       <c r="C1316" t="inlineStr"/>
       <c r="D1316" t="inlineStr"/>
       <c r="E1316" t="n">
-        <v>300</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1316" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="G1316" t="n">
         <v>0</v>
@@ -70702,7 +70706,7 @@
       </c>
       <c r="M1316" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1316" t="inlineStr"/>
@@ -70710,25 +70714,21 @@
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>CYCLOFEM AMPOLLA INYECTABLE .PROFAMILIA</t>
-        </is>
-      </c>
-      <c r="C1317" t="inlineStr">
-        <is>
-          <t>7703689000448</t>
-        </is>
-      </c>
+          <t>CURAS LARGAS RESIST AL AGUA</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr"/>
       <c r="D1317" t="inlineStr"/>
       <c r="E1317" t="n">
-        <v>28900</v>
+        <v>300</v>
       </c>
       <c r="F1317" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="G1317" t="n">
         <v>0</v>
@@ -70764,25 +70764,25 @@
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>CYCLOFEMINA AMPOLLA 0.5ML</t>
+          <t>CYCLOFEM AMPOLLA INYECTABLE .PROFAMILIA</t>
         </is>
       </c>
       <c r="C1318" t="inlineStr">
         <is>
-          <t>7707271451410</t>
+          <t>7703689000448</t>
         </is>
       </c>
       <c r="D1318" t="inlineStr"/>
       <c r="E1318" t="n">
-        <v>33900</v>
+        <v>28900</v>
       </c>
       <c r="F1318" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1318" t="n">
         <v>0</v>
@@ -70818,25 +70818,25 @@
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>Desonida bussie 0.1% crema 15gr</t>
+          <t>CYCLOFEMINA AMPOLLA 0.5ML</t>
         </is>
       </c>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>7702195210587</t>
+          <t>7707271451410</t>
         </is>
       </c>
       <c r="D1319" t="inlineStr"/>
       <c r="E1319" t="n">
-        <v>19000</v>
+        <v>33900</v>
       </c>
       <c r="F1319" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1319" t="n">
         <v>0</v>
@@ -70872,25 +70872,25 @@
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>Diclofenaco gel vitalis 50gr</t>
+          <t>Desonida bussie 0.1% crema 15gr</t>
         </is>
       </c>
       <c r="C1320" t="inlineStr">
         <is>
-          <t>7709141546059</t>
+          <t>7702195210587</t>
         </is>
       </c>
       <c r="D1320" t="inlineStr"/>
       <c r="E1320" t="n">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="F1320" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1320" t="n">
         <v>0</v>
@@ -70916,31 +70916,35 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1320" t="inlineStr"/>
+      <c r="M1320" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1320" t="inlineStr"/>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>Diclofenaco sódico 100mg +hidróxido de aluminio200mg colmed</t>
+          <t>Diclofenaco gel vitalis 50gr</t>
         </is>
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>7703153020286</t>
+          <t>7709141546059</t>
         </is>
       </c>
       <c r="D1321" t="inlineStr"/>
       <c r="E1321" t="n">
-        <v>19200</v>
+        <v>16000</v>
       </c>
       <c r="F1321" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1321" t="n">
         <v>0</v>
@@ -70966,31 +70970,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1321" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1321" t="inlineStr"/>
       <c r="N1321" t="inlineStr"/>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>DICLOFENACOXUND75MG/3MLAMPCOMERCIAL VITALIS</t>
-        </is>
-      </c>
-      <c r="C1322" t="inlineStr"/>
+          <t>Diclofenaco sódico 100mg +hidróxido de aluminio200mg colmed</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>7703153020286</t>
+        </is>
+      </c>
       <c r="D1322" t="inlineStr"/>
       <c r="E1322" t="n">
-        <v>5500</v>
+        <v>19200</v>
       </c>
       <c r="F1322" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1322" t="n">
         <v>0</v>
@@ -71026,18 +71030,18 @@
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>DIFENZ DESPIGMENTADOR CREMA TUBO X 1 UND</t>
+          <t>DICLOFENACOXUND75MG/3MLAMPCOMERCIAL VITALIS</t>
         </is>
       </c>
       <c r="C1323" t="inlineStr"/>
       <c r="D1323" t="inlineStr"/>
       <c r="E1323" t="n">
-        <v>163300</v>
+        <v>5500</v>
       </c>
       <c r="F1323" t="n">
         <v>1</v>
@@ -71076,21 +71080,21 @@
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>DIPIORNA 500MG TABLETA X 10 DE ECAR</t>
+          <t>DIFENZ DESPIGMENTADOR CREMA TUBO X 1 UND</t>
         </is>
       </c>
       <c r="C1324" t="inlineStr"/>
       <c r="D1324" t="inlineStr"/>
       <c r="E1324" t="n">
-        <v>7900</v>
+        <v>163300</v>
       </c>
       <c r="F1324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1324" t="n">
         <v>0</v>
@@ -71126,21 +71130,25 @@
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>DIPIRONA 500MG TABLETA X 10 DE ECAR</t>
-        </is>
-      </c>
-      <c r="C1325" t="inlineStr"/>
+          <t>DIOSMINA HESPERIDINA 450MG 50MG GENFAR</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>7705959013370</t>
+        </is>
+      </c>
       <c r="D1325" t="inlineStr"/>
       <c r="E1325" t="n">
-        <v>7900</v>
+        <v>42000</v>
       </c>
       <c r="F1325" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1325" t="n">
         <v>0</v>
@@ -71176,18 +71184,18 @@
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>DOMICILIO</t>
+          <t>DIPIORNA 500MG TABLETA X 10 DE ECAR</t>
         </is>
       </c>
       <c r="C1326" t="inlineStr"/>
       <c r="D1326" t="inlineStr"/>
       <c r="E1326" t="n">
-        <v>3000</v>
+        <v>7900</v>
       </c>
       <c r="F1326" t="n">
         <v>0</v>
@@ -71216,24 +71224,28 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1326" t="inlineStr"/>
+      <c r="M1326" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1326" t="inlineStr"/>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>DOXICICLINA 100MG X 10 TABL GENFAR</t>
+          <t>DIPIRONA 500MG TABLETA X 10 DE ECAR</t>
         </is>
       </c>
       <c r="C1327" t="inlineStr"/>
       <c r="D1327" t="inlineStr"/>
       <c r="E1327" t="n">
-        <v>12000</v>
+        <v>7900</v>
       </c>
       <c r="F1327" t="n">
         <v>5</v>
@@ -71272,21 +71284,21 @@
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>DUCHA INTIMA DESECHABLE VINAGRE</t>
+          <t>DOMICILIO</t>
         </is>
       </c>
       <c r="C1328" t="inlineStr"/>
       <c r="D1328" t="inlineStr"/>
       <c r="E1328" t="n">
-        <v>24800</v>
+        <v>3000</v>
       </c>
       <c r="F1328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1328" t="n">
         <v>0</v>
@@ -71312,35 +71324,27 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1328" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1328" t="inlineStr"/>
       <c r="N1328" t="inlineStr"/>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>E ala proel maléate 20mg medicbrand</t>
-        </is>
-      </c>
-      <c r="C1329" t="inlineStr">
-        <is>
-          <t>7703712035997</t>
-        </is>
-      </c>
+          <t>DOXICICLINA 100MG X 10 TABL GENFAR</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr"/>
       <c r="D1329" t="inlineStr"/>
       <c r="E1329" t="n">
-        <v>1250</v>
+        <v>12000</v>
       </c>
       <c r="F1329" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1329" t="n">
         <v>0</v>
@@ -71376,22 +71380,18 @@
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>Enalapril 20 mg MK</t>
-        </is>
-      </c>
-      <c r="C1330" t="inlineStr">
-        <is>
-          <t>7702057716578</t>
-        </is>
-      </c>
+          <t>DUCHA INTIMA DESECHABLE VINAGRE</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr"/>
       <c r="D1330" t="inlineStr"/>
       <c r="E1330" t="n">
-        <v>4700</v>
+        <v>24800</v>
       </c>
       <c r="F1330" t="n">
         <v>1</v>
@@ -71430,21 +71430,25 @@
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>ENALAPRIL 20MG TABLETA COAS</t>
-        </is>
-      </c>
-      <c r="C1331" t="inlineStr"/>
+          <t>E ala proel maléate 20mg medicbrand</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>7703712035997</t>
+        </is>
+      </c>
       <c r="D1331" t="inlineStr"/>
       <c r="E1331" t="n">
-        <v>3000</v>
+        <v>1250</v>
       </c>
       <c r="F1331" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1331" t="n">
         <v>0</v>
@@ -71480,18 +71484,22 @@
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>ENSURE ADVANCE VAINILLA 400GR</t>
-        </is>
-      </c>
-      <c r="C1332" t="inlineStr"/>
+          <t>Enalapril 20 mg MK</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>7702057716578</t>
+        </is>
+      </c>
       <c r="D1332" t="inlineStr"/>
       <c r="E1332" t="n">
-        <v>85900</v>
+        <v>4700</v>
       </c>
       <c r="F1332" t="n">
         <v>1</v>
@@ -71530,21 +71538,21 @@
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>ENTRETENEDOR BEBE</t>
+          <t>ENALAPRIL 20MG TABLETA COAS</t>
         </is>
       </c>
       <c r="C1333" t="inlineStr"/>
       <c r="D1333" t="inlineStr"/>
       <c r="E1333" t="n">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="F1333" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1333" t="n">
         <v>0</v>
@@ -71580,18 +71588,18 @@
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>ESMALTE BRILLO ACRILICO BRESCIA</t>
+          <t>ENSURE ADVANCE VAINILLA 400GR</t>
         </is>
       </c>
       <c r="C1334" t="inlineStr"/>
       <c r="D1334" t="inlineStr"/>
       <c r="E1334" t="n">
-        <v>11500</v>
+        <v>85900</v>
       </c>
       <c r="F1334" t="n">
         <v>1</v>
@@ -71630,21 +71638,21 @@
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>ESOMEPRAZOL 20MG NOVAMED</t>
+          <t>ENTRETENEDOR BEBE</t>
         </is>
       </c>
       <c r="C1335" t="inlineStr"/>
       <c r="D1335" t="inlineStr"/>
       <c r="E1335" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="F1335" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G1335" t="n">
         <v>0</v>
@@ -71680,18 +71688,18 @@
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>ESPASMOK HIOS +DIPIRO 5ML AMP BLASKOV</t>
+          <t>ESMALTE BRILLO ACRILICO BRESCIA</t>
         </is>
       </c>
       <c r="C1336" t="inlineStr"/>
       <c r="D1336" t="inlineStr"/>
       <c r="E1336" t="n">
-        <v>12000</v>
+        <v>11500</v>
       </c>
       <c r="F1336" t="n">
         <v>1</v>
@@ -71730,25 +71738,21 @@
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>ETORICOXIB 120MG GENFAR</t>
-        </is>
-      </c>
-      <c r="C1337" t="inlineStr">
-        <is>
-          <t>7702605109371</t>
-        </is>
-      </c>
+          <t>ESOMEPRAZOL 20MG NOVAMED</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr"/>
       <c r="D1337" t="inlineStr"/>
       <c r="E1337" t="n">
-        <v>48600</v>
+        <v>2000</v>
       </c>
       <c r="F1337" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G1337" t="n">
         <v>0</v>
@@ -71784,22 +71788,18 @@
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>EXTRACTOR DE LECHE MOBY</t>
-        </is>
-      </c>
-      <c r="C1338" t="inlineStr">
-        <is>
-          <t>7707233051436</t>
-        </is>
-      </c>
+          <t>ESPASMOK HIOS +DIPIRO 5ML AMP BLASKOV</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr"/>
       <c r="D1338" t="inlineStr"/>
       <c r="E1338" t="n">
-        <v>14285.714286</v>
+        <v>12000</v>
       </c>
       <c r="F1338" t="n">
         <v>1</v>
@@ -71830,7 +71830,7 @@
       </c>
       <c r="M1338" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1338" t="inlineStr"/>
@@ -71838,25 +71838,25 @@
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>FAMIIA MEGARROLLO PAPEL HIGUIEN</t>
+          <t>ETORICOXIB 120MG GENFAR</t>
         </is>
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>7702026147471</t>
+          <t>7702605109371</t>
         </is>
       </c>
       <c r="D1339" t="inlineStr"/>
       <c r="E1339" t="n">
-        <v>3500</v>
+        <v>48600</v>
       </c>
       <c r="F1339" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G1339" t="n">
         <v>0</v>
@@ -71892,21 +71892,25 @@
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>Farma D 500 UI</t>
-        </is>
-      </c>
-      <c r="C1340" t="inlineStr"/>
+          <t>EXTRACTOR DE LECHE MOBY</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>7707233051436</t>
+        </is>
+      </c>
       <c r="D1340" t="inlineStr"/>
       <c r="E1340" t="n">
-        <v>74000</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1340" t="n">
         <v>0</v>
@@ -71934,7 +71938,7 @@
       </c>
       <c r="M1340" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1340" t="inlineStr"/>
@@ -71942,21 +71946,25 @@
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>FIBRA AMARILLA ARMONIZA X 450GR</t>
-        </is>
-      </c>
-      <c r="C1341" t="inlineStr"/>
+          <t>FAMIIA MEGARROLLO PAPEL HIGUIEN</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>7702026147471</t>
+        </is>
+      </c>
       <c r="D1341" t="inlineStr"/>
       <c r="E1341" t="n">
-        <v>28571.428571</v>
+        <v>3500</v>
       </c>
       <c r="F1341" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G1341" t="n">
         <v>0</v>
@@ -71984,7 +71992,7 @@
       </c>
       <c r="M1341" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1341" t="inlineStr"/>
@@ -71992,18 +72000,18 @@
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>FIBRA DE AVENA Y SALVADO DE TRIGO 450GR</t>
+          <t>Farma D 500 UI</t>
         </is>
       </c>
       <c r="C1342" t="inlineStr"/>
       <c r="D1342" t="inlineStr"/>
       <c r="E1342" t="n">
-        <v>30000</v>
+        <v>74000</v>
       </c>
       <c r="F1342" t="n">
         <v>0</v>
@@ -72042,21 +72050,21 @@
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>FITOSTIMONE 15% GEL</t>
+          <t>FIBRA AMARILLA ARMONIZA X 450GR</t>
         </is>
       </c>
       <c r="C1343" t="inlineStr"/>
       <c r="D1343" t="inlineStr"/>
       <c r="E1343" t="n">
-        <v>48900</v>
+        <v>28571.428571</v>
       </c>
       <c r="F1343" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1343" t="n">
         <v>0</v>
@@ -72084,7 +72092,7 @@
       </c>
       <c r="M1343" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1343" t="inlineStr"/>
@@ -72092,25 +72100,21 @@
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG CJA X 10 UND EXPORF</t>
-        </is>
-      </c>
-      <c r="C1344" t="inlineStr">
-        <is>
-          <t>7703432421681</t>
-        </is>
-      </c>
+          <t>FIBRA DE AVENA Y SALVADO DE TRIGO 450GR</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr"/>
       <c r="D1344" t="inlineStr"/>
       <c r="E1344" t="n">
-        <v>18300</v>
+        <v>30000</v>
       </c>
       <c r="F1344" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G1344" t="n">
         <v>0</v>
@@ -72146,18 +72150,18 @@
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS DE GENFAR</t>
+          <t>FITOSTIMONE 15% GEL</t>
         </is>
       </c>
       <c r="C1345" t="inlineStr"/>
       <c r="D1345" t="inlineStr"/>
       <c r="E1345" t="n">
-        <v>16900</v>
+        <v>48900</v>
       </c>
       <c r="F1345" t="n">
         <v>2</v>
@@ -72196,25 +72200,25 @@
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS. LA SANTE</t>
+          <t>FLUCONAZOL 200MG CJA X 10 UND EXPORF</t>
         </is>
       </c>
       <c r="C1346" t="inlineStr">
         <is>
-          <t>7703763480166</t>
+          <t>7703432421681</t>
         </is>
       </c>
       <c r="D1346" t="inlineStr"/>
       <c r="E1346" t="n">
-        <v>14700</v>
+        <v>18300</v>
       </c>
       <c r="F1346" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G1346" t="n">
         <v>0</v>
@@ -72250,22 +72254,18 @@
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS.NOVAMED</t>
-        </is>
-      </c>
-      <c r="C1347" t="inlineStr">
-        <is>
-          <t>7703546927468</t>
-        </is>
-      </c>
+          <t>FLUCONAZOL 200MG X 4 CAPS DE GENFAR</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr"/>
       <c r="D1347" t="inlineStr"/>
       <c r="E1347" t="n">
-        <v>10900</v>
+        <v>16900</v>
       </c>
       <c r="F1347" t="n">
         <v>2</v>
@@ -72304,21 +72304,25 @@
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>Fluconazol Suspension</t>
-        </is>
-      </c>
-      <c r="C1348" t="inlineStr"/>
+          <t>FLUCONAZOL 200MG X 4 CAPS. LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>7703763480166</t>
+        </is>
+      </c>
       <c r="D1348" t="inlineStr"/>
       <c r="E1348" t="n">
-        <v>148000</v>
+        <v>14700</v>
       </c>
       <c r="F1348" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1348" t="n">
         <v>0</v>
@@ -72354,21 +72358,25 @@
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>FUNGI-FIN LOCION GOTAS TOPICA 20ML</t>
-        </is>
-      </c>
-      <c r="C1349" t="inlineStr"/>
+          <t>FLUCONAZOL 200MG X 4 CAPS.NOVAMED</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>7703546927468</t>
+        </is>
+      </c>
       <c r="D1349" t="inlineStr"/>
       <c r="E1349" t="n">
-        <v>15966.386555</v>
+        <v>10900</v>
       </c>
       <c r="F1349" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1349" t="n">
         <v>0</v>
@@ -72396,7 +72404,7 @@
       </c>
       <c r="M1349" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1349" t="inlineStr"/>
@@ -72404,21 +72412,21 @@
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>GALLETA OREO PAQUETE X 6 UNDS</t>
+          <t>Fluconazol Suspension</t>
         </is>
       </c>
       <c r="C1350" t="inlineStr"/>
       <c r="D1350" t="inlineStr"/>
       <c r="E1350" t="n">
-        <v>1932.773109</v>
+        <v>148000</v>
       </c>
       <c r="F1350" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1350" t="n">
         <v>0</v>
@@ -72446,7 +72454,7 @@
       </c>
       <c r="M1350" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1350" t="inlineStr"/>
@@ -72454,21 +72462,21 @@
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>GASEOSA PREMIO 400ML ROJO</t>
+          <t>FUNGI-FIN LOCION GOTAS TOPICA 20ML</t>
         </is>
       </c>
       <c r="C1351" t="inlineStr"/>
       <c r="D1351" t="inlineStr"/>
       <c r="E1351" t="n">
-        <v>2941.176471</v>
+        <v>15966.386555</v>
       </c>
       <c r="F1351" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G1351" t="n">
         <v>0</v>
@@ -72504,29 +72512,21 @@
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>GASTROFAST ADVANCE</t>
-        </is>
-      </c>
-      <c r="C1352" t="inlineStr">
-        <is>
-          <t>7702057803254</t>
-        </is>
-      </c>
-      <c r="D1352" t="inlineStr">
-        <is>
-          <t>se subio A 3800 ANTES 3.600, LEYDI</t>
-        </is>
-      </c>
+          <t>GALLETA OREO PAQUETE X 6 UNDS</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr"/>
+      <c r="D1352" t="inlineStr"/>
       <c r="E1352" t="n">
-        <v>3800</v>
+        <v>1932.773109</v>
       </c>
       <c r="F1352" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G1352" t="n">
         <v>0</v>
@@ -72554,7 +72554,7 @@
       </c>
       <c r="M1352" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1352" t="inlineStr"/>
@@ -72562,21 +72562,21 @@
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>GASTROFAST ADVANCE X 240 ML</t>
+          <t>GASEOSA PREMIO 400ML ROJO</t>
         </is>
       </c>
       <c r="C1353" t="inlineStr"/>
       <c r="D1353" t="inlineStr"/>
       <c r="E1353" t="n">
-        <v>69500</v>
+        <v>2941.176471</v>
       </c>
       <c r="F1353" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G1353" t="n">
         <v>0</v>
@@ -72604,7 +72604,7 @@
       </c>
       <c r="M1353" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1353" t="inlineStr"/>
@@ -72612,25 +72612,29 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>gatorade</t>
+          <t>GASTROFAST ADVANCE</t>
         </is>
       </c>
       <c r="C1354" t="inlineStr">
         <is>
-          <t>248656546</t>
-        </is>
-      </c>
-      <c r="D1354" t="inlineStr"/>
+          <t>7702057803254</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>se subio A 3800 ANTES 3.600, LEYDI</t>
+        </is>
+      </c>
       <c r="E1354" t="n">
-        <v>3782</v>
+        <v>3800</v>
       </c>
       <c r="F1354" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G1354" t="n">
         <v>0</v>
@@ -72658,7 +72662,7 @@
       </c>
       <c r="M1354" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1354" t="inlineStr"/>
@@ -72666,18 +72670,18 @@
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>GEL BACHUE 150GR</t>
+          <t>GASTROFAST ADVANCE X 240 ML</t>
         </is>
       </c>
       <c r="C1355" t="inlineStr"/>
       <c r="D1355" t="inlineStr"/>
       <c r="E1355" t="n">
-        <v>8800</v>
+        <v>69500</v>
       </c>
       <c r="F1355" t="n">
         <v>1</v>
@@ -72716,21 +72720,25 @@
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>GEMFIBROZILO 600 MG</t>
-        </is>
-      </c>
-      <c r="C1356" t="inlineStr"/>
+          <t>gatorade</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>248656546</t>
+        </is>
+      </c>
       <c r="D1356" t="inlineStr"/>
       <c r="E1356" t="n">
-        <v>8300</v>
+        <v>3782</v>
       </c>
       <c r="F1356" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1356" t="n">
         <v>0</v>
@@ -72758,7 +72766,7 @@
       </c>
       <c r="M1356" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1356" t="inlineStr"/>
@@ -72766,18 +72774,18 @@
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>GLICERINA CARBONATADA X 20ML FCO YOMA</t>
+          <t>GEL BACHUE 150GR</t>
         </is>
       </c>
       <c r="C1357" t="inlineStr"/>
       <c r="D1357" t="inlineStr"/>
       <c r="E1357" t="n">
-        <v>3900</v>
+        <v>8800</v>
       </c>
       <c r="F1357" t="n">
         <v>1</v>
@@ -72816,21 +72824,21 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
+          <t>GEMFIBROZILO 600 MG</t>
         </is>
       </c>
       <c r="C1358" t="inlineStr"/>
       <c r="D1358" t="inlineStr"/>
       <c r="E1358" t="n">
-        <v>3361.344538</v>
+        <v>8300</v>
       </c>
       <c r="F1358" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1358" t="n">
         <v>0</v>
@@ -72858,7 +72866,7 @@
       </c>
       <c r="M1358" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1358" t="inlineStr"/>
@@ -72866,21 +72874,21 @@
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
+          <t>GLICERINA CARBONATADA X 20ML FCO YOMA</t>
         </is>
       </c>
       <c r="C1359" t="inlineStr"/>
       <c r="D1359" t="inlineStr"/>
       <c r="E1359" t="n">
-        <v>23109.243697</v>
+        <v>3900</v>
       </c>
       <c r="F1359" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="G1359" t="n">
         <v>0</v>
@@ -72908,7 +72916,7 @@
       </c>
       <c r="M1359" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1359" t="inlineStr"/>
@@ -72916,25 +72924,21 @@
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1360" t="inlineStr">
-        <is>
-          <t>7709195419279</t>
-        </is>
-      </c>
+          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr"/>
       <c r="D1360" t="inlineStr"/>
       <c r="E1360" t="n">
-        <v>24370</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1360" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1360" t="n">
         <v>0</v>
@@ -72970,21 +72974,21 @@
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
+          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
         </is>
       </c>
       <c r="C1361" t="inlineStr"/>
       <c r="D1361" t="inlineStr"/>
       <c r="E1361" t="n">
-        <v>24369.747899</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1361" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G1361" t="n">
         <v>0</v>
@@ -73020,21 +73024,25 @@
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
-        </is>
-      </c>
-      <c r="C1362" t="inlineStr"/>
+          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>7709195419279</t>
+        </is>
+      </c>
       <c r="D1362" t="inlineStr"/>
       <c r="E1362" t="n">
-        <v>23109.243697</v>
+        <v>24370</v>
       </c>
       <c r="F1362" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G1362" t="n">
         <v>0</v>
@@ -73070,21 +73078,21 @@
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>HALLS BARRA SURTIDOS SABORES</t>
+          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
         </is>
       </c>
       <c r="C1363" t="inlineStr"/>
       <c r="D1363" t="inlineStr"/>
       <c r="E1363" t="n">
-        <v>2100.840336</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1363" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="G1363" t="n">
         <v>0</v>
@@ -73120,21 +73128,21 @@
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>HALLS PEPA ROJO CEREZA X UND</t>
+          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
         </is>
       </c>
       <c r="C1364" t="inlineStr"/>
       <c r="D1364" t="inlineStr"/>
       <c r="E1364" t="n">
-        <v>336.134454</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1364" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G1364" t="n">
         <v>0</v>
@@ -73170,21 +73178,21 @@
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>HEPATODREN JARABE FCO X 240ML</t>
+          <t>HALLS BARRA SURTIDOS SABORES</t>
         </is>
       </c>
       <c r="C1365" t="inlineStr"/>
       <c r="D1365" t="inlineStr"/>
       <c r="E1365" t="n">
-        <v>34500</v>
+        <v>2100.840336</v>
       </c>
       <c r="F1365" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G1365" t="n">
         <v>0</v>
@@ -73212,7 +73220,7 @@
       </c>
       <c r="M1365" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1365" t="inlineStr"/>
@@ -73220,21 +73228,21 @@
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>HEPATODREN X 60 CAPSULAS</t>
+          <t>HALLS PEPA ROJO CEREZA X UND</t>
         </is>
       </c>
       <c r="C1366" t="inlineStr"/>
       <c r="D1366" t="inlineStr"/>
       <c r="E1366" t="n">
-        <v>58300</v>
+        <v>336.134454</v>
       </c>
       <c r="F1366" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G1366" t="n">
         <v>0</v>
@@ -73262,7 +73270,7 @@
       </c>
       <c r="M1366" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1366" t="inlineStr"/>
@@ -73270,25 +73278,21 @@
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>Hidraplus 75 zinc uva 400ml</t>
-        </is>
-      </c>
-      <c r="C1367" t="inlineStr">
-        <is>
-          <t>7702057010928</t>
-        </is>
-      </c>
+          <t>HEPATODREN JARABE FCO X 240ML</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr"/>
       <c r="D1367" t="inlineStr"/>
       <c r="E1367" t="n">
-        <v>10600</v>
+        <v>34500</v>
       </c>
       <c r="F1367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1367" t="n">
         <v>0</v>
@@ -73324,21 +73328,21 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
+          <t>HEPATODREN X 60 CAPSULAS</t>
         </is>
       </c>
       <c r="C1368" t="inlineStr"/>
       <c r="D1368" t="inlineStr"/>
       <c r="E1368" t="n">
-        <v>15900</v>
+        <v>58300</v>
       </c>
       <c r="F1368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1368" t="n">
         <v>0</v>
@@ -73374,22 +73378,22 @@
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
+          <t>Hidraplus 75 zinc uva 400ml</t>
         </is>
       </c>
       <c r="C1369" t="inlineStr">
         <is>
-          <t>77099475597789</t>
+          <t>7702057010928</t>
         </is>
       </c>
       <c r="D1369" t="inlineStr"/>
       <c r="E1369" t="n">
-        <v>28000</v>
+        <v>10600</v>
       </c>
       <c r="F1369" t="n">
         <v>0</v>
@@ -73428,22 +73432,18 @@
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>Hidroxicina 0.25 JBE x 120 ML</t>
-        </is>
-      </c>
-      <c r="C1370" t="inlineStr">
-        <is>
-          <t>7707035540596</t>
-        </is>
-      </c>
+          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr"/>
       <c r="D1370" t="inlineStr"/>
       <c r="E1370" t="n">
-        <v>11000</v>
+        <v>15900</v>
       </c>
       <c r="F1370" t="n">
         <v>2</v>
@@ -73482,21 +73482,25 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
-        </is>
-      </c>
-      <c r="C1371" t="inlineStr"/>
+          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>77099475597789</t>
+        </is>
+      </c>
       <c r="D1371" t="inlineStr"/>
       <c r="E1371" t="n">
-        <v>4500</v>
+        <v>28000</v>
       </c>
       <c r="F1371" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1371" t="n">
         <v>0</v>
@@ -73532,21 +73536,25 @@
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1372" t="inlineStr"/>
+          <t>Hidroxicina 0.25 JBE x 120 ML</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>7707035540596</t>
+        </is>
+      </c>
       <c r="D1372" t="inlineStr"/>
       <c r="E1372" t="n">
-        <v>6900</v>
+        <v>11000</v>
       </c>
       <c r="F1372" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1372" t="n">
         <v>0</v>
@@ -73582,21 +73590,21 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
+          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
         </is>
       </c>
       <c r="C1373" t="inlineStr"/>
       <c r="D1373" t="inlineStr"/>
       <c r="E1373" t="n">
-        <v>12000</v>
+        <v>4500</v>
       </c>
       <c r="F1373" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1373" t="n">
         <v>0</v>
@@ -73632,21 +73640,21 @@
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>Hylo Gel</t>
+          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
         </is>
       </c>
       <c r="C1374" t="inlineStr"/>
       <c r="D1374" t="inlineStr"/>
       <c r="E1374" t="n">
-        <v>131600</v>
+        <v>6900</v>
       </c>
       <c r="F1374" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1374" t="n">
         <v>0</v>
@@ -73682,25 +73690,21 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>IBUPROFENO 400MG/ GENFAR</t>
-        </is>
-      </c>
-      <c r="C1375" t="inlineStr">
-        <is>
-          <t>7702605101498</t>
-        </is>
-      </c>
+          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr"/>
       <c r="D1375" t="inlineStr"/>
       <c r="E1375" t="n">
-        <v>4400</v>
+        <v>12000</v>
       </c>
       <c r="F1375" t="n">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="G1375" t="n">
         <v>0</v>
@@ -73736,22 +73740,18 @@
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>Ibuprofeno 800mg AG</t>
-        </is>
-      </c>
-      <c r="C1376" t="inlineStr">
-        <is>
-          <t>7706569000385</t>
-        </is>
-      </c>
+          <t>Hylo Gel</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr"/>
       <c r="D1376" t="inlineStr"/>
       <c r="E1376" t="n">
-        <v>800</v>
+        <v>131600</v>
       </c>
       <c r="F1376" t="n">
         <v>0</v>
@@ -73790,25 +73790,25 @@
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
+          <t>IBUPROFENO 400MG/ GENFAR</t>
         </is>
       </c>
       <c r="C1377" t="inlineStr">
         <is>
-          <t>7705959885229</t>
+          <t>7702605101498</t>
         </is>
       </c>
       <c r="D1377" t="inlineStr"/>
       <c r="E1377" t="n">
-        <v>17900</v>
+        <v>4400</v>
       </c>
       <c r="F1377" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="G1377" t="n">
         <v>0</v>
@@ -73844,25 +73844,25 @@
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>ICE POWER 30 GR GEL COSMETICA</t>
+          <t>Ibuprofeno 800mg AG</t>
         </is>
       </c>
       <c r="C1378" t="inlineStr">
         <is>
-          <t>737186238889</t>
+          <t>7706569000385</t>
         </is>
       </c>
       <c r="D1378" t="inlineStr"/>
       <c r="E1378" t="n">
-        <v>12521.008403</v>
+        <v>800</v>
       </c>
       <c r="F1378" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1378" t="n">
         <v>0</v>
@@ -73890,7 +73890,7 @@
       </c>
       <c r="M1378" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1378" t="inlineStr"/>
@@ -73898,21 +73898,25 @@
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
-        </is>
-      </c>
-      <c r="C1379" t="inlineStr"/>
+          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>7705959885229</t>
+        </is>
+      </c>
       <c r="D1379" t="inlineStr"/>
       <c r="E1379" t="n">
-        <v>38900</v>
+        <v>17900</v>
       </c>
       <c r="F1379" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1379" t="n">
         <v>0</v>
@@ -73948,21 +73952,25 @@
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
-        </is>
-      </c>
-      <c r="C1380" t="inlineStr"/>
+          <t>ICE POWER 30 GR GEL COSMETICA</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>737186238889</t>
+        </is>
+      </c>
       <c r="D1380" t="inlineStr"/>
       <c r="E1380" t="n">
-        <v>38900</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1380" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1380" t="n">
         <v>0</v>
@@ -73990,7 +73998,7 @@
       </c>
       <c r="M1380" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1380" t="inlineStr"/>
@@ -73998,21 +74006,21 @@
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
+          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
         </is>
       </c>
       <c r="C1381" t="inlineStr"/>
       <c r="D1381" t="inlineStr"/>
       <c r="E1381" t="n">
-        <v>8235.294118</v>
+        <v>38900</v>
       </c>
       <c r="F1381" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1381" t="n">
         <v>0</v>
@@ -74040,7 +74048,7 @@
       </c>
       <c r="M1381" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1381" t="inlineStr"/>
@@ -74048,18 +74056,18 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
+          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
         </is>
       </c>
       <c r="C1382" t="inlineStr"/>
       <c r="D1382" t="inlineStr"/>
       <c r="E1382" t="n">
-        <v>9831.932773</v>
+        <v>38900</v>
       </c>
       <c r="F1382" t="n">
         <v>1</v>
@@ -74090,7 +74098,7 @@
       </c>
       <c r="M1382" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1382" t="inlineStr"/>
@@ -74098,21 +74106,21 @@
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
+          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
         </is>
       </c>
       <c r="C1383" t="inlineStr"/>
       <c r="D1383" t="inlineStr"/>
       <c r="E1383" t="n">
-        <v>4201.680672</v>
+        <v>8235.294118</v>
       </c>
       <c r="F1383" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1383" t="n">
         <v>0</v>
@@ -74148,21 +74156,21 @@
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
+          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
         </is>
       </c>
       <c r="C1384" t="inlineStr"/>
       <c r="D1384" t="inlineStr"/>
       <c r="E1384" t="n">
-        <v>4201.680672</v>
+        <v>9831.932773</v>
       </c>
       <c r="F1384" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1384" t="n">
         <v>0</v>
@@ -74198,21 +74206,21 @@
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>JABON PROTEX HERBAL 110GR</t>
+          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
         </is>
       </c>
       <c r="C1385" t="inlineStr"/>
       <c r="D1385" t="inlineStr"/>
       <c r="E1385" t="n">
-        <v>4537.815126</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1385" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1385" t="n">
         <v>0</v>
@@ -74248,22 +74256,18 @@
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>JARABE ZETYGRIP FCO 60ML</t>
-        </is>
-      </c>
-      <c r="C1386" t="inlineStr">
-        <is>
-          <t>7709805542830</t>
-        </is>
-      </c>
+          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr"/>
       <c r="D1386" t="inlineStr"/>
       <c r="E1386" t="n">
-        <v>14000</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1386" t="n">
         <v>2</v>
@@ -74294,7 +74298,7 @@
       </c>
       <c r="M1386" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1386" t="inlineStr"/>
@@ -74302,21 +74306,21 @@
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>JERINGA DE 50ML</t>
+          <t>JABON PROTEX HERBAL 110GR</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr"/>
       <c r="D1387" t="inlineStr"/>
       <c r="E1387" t="n">
-        <v>2500</v>
+        <v>4537.815126</v>
       </c>
       <c r="F1387" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1387" t="n">
         <v>0</v>
@@ -74344,7 +74348,7 @@
       </c>
       <c r="M1387" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1387" t="inlineStr"/>
@@ -74352,21 +74356,25 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>Jeringa desechable estéril 20ml impormedicas</t>
-        </is>
-      </c>
-      <c r="C1388" t="inlineStr"/>
+          <t>JARABE ZETYGRIP FCO 60ML</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>7709805542830</t>
+        </is>
+      </c>
       <c r="D1388" t="inlineStr"/>
       <c r="E1388" t="n">
-        <v>920</v>
+        <v>14000</v>
       </c>
       <c r="F1388" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G1388" t="n">
         <v>0</v>
@@ -74394,7 +74402,7 @@
       </c>
       <c r="M1388" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1388" t="inlineStr"/>
@@ -74402,21 +74410,21 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
+          <t>JERINGA DE 50ML</t>
         </is>
       </c>
       <c r="C1389" t="inlineStr"/>
       <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="n">
-        <v>1100</v>
+        <v>2500</v>
       </c>
       <c r="F1389" t="n">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="G1389" t="n">
         <v>0</v>
@@ -74452,21 +74460,21 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>Kelocate</t>
+          <t>Jeringa desechable estéril 20ml impormedicas</t>
         </is>
       </c>
       <c r="C1390" t="inlineStr"/>
       <c r="D1390" t="inlineStr"/>
       <c r="E1390" t="n">
-        <v>180000</v>
+        <v>920</v>
       </c>
       <c r="F1390" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G1390" t="n">
         <v>0</v>
@@ -74494,7 +74502,7 @@
       </c>
       <c r="M1390" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1390" t="inlineStr"/>
@@ -74502,25 +74510,21 @@
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
-        </is>
-      </c>
-      <c r="C1391" t="inlineStr">
-        <is>
-          <t>7702057073695</t>
-        </is>
-      </c>
+          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr"/>
       <c r="D1391" t="inlineStr"/>
       <c r="E1391" t="n">
-        <v>19500</v>
+        <v>1100</v>
       </c>
       <c r="F1391" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G1391" t="n">
         <v>0</v>
@@ -74556,22 +74560,18 @@
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
-        </is>
-      </c>
-      <c r="C1392" t="inlineStr">
-        <is>
-          <t>7709947559772</t>
-        </is>
-      </c>
+          <t>Kelocate</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr"/>
       <c r="D1392" t="inlineStr"/>
       <c r="E1392" t="n">
-        <v>15000</v>
+        <v>180000</v>
       </c>
       <c r="F1392" t="n">
         <v>0</v>
@@ -74610,18 +74610,22 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
-        </is>
-      </c>
-      <c r="C1393" t="inlineStr"/>
+          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>7702057073695</t>
+        </is>
+      </c>
       <c r="D1393" t="inlineStr"/>
       <c r="E1393" t="n">
-        <v>71000</v>
+        <v>19500</v>
       </c>
       <c r="F1393" t="n">
         <v>0</v>
@@ -74660,21 +74664,25 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
-        </is>
-      </c>
-      <c r="C1394" t="inlineStr"/>
+          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>7709947559772</t>
+        </is>
+      </c>
       <c r="D1394" t="inlineStr"/>
       <c r="E1394" t="n">
-        <v>37900</v>
+        <v>15000</v>
       </c>
       <c r="F1394" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1394" t="n">
         <v>0</v>
@@ -74710,25 +74718,21 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>Levotiroxina 100mcg MK</t>
-        </is>
-      </c>
-      <c r="C1395" t="inlineStr">
-        <is>
-          <t>7702057715908</t>
-        </is>
-      </c>
+          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr"/>
       <c r="D1395" t="inlineStr"/>
       <c r="E1395" t="n">
-        <v>27900</v>
+        <v>71000</v>
       </c>
       <c r="F1395" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1395" t="n">
         <v>0</v>
@@ -74764,18 +74768,18 @@
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>LIMA MAYOMI 10/180</t>
+          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
         </is>
       </c>
       <c r="C1396" t="inlineStr"/>
       <c r="D1396" t="inlineStr"/>
       <c r="E1396" t="n">
-        <v>3900</v>
+        <v>37900</v>
       </c>
       <c r="F1396" t="n">
         <v>1</v>
@@ -74814,21 +74818,25 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
-        </is>
-      </c>
-      <c r="C1397" t="inlineStr"/>
+          <t>Levotiroxina 100mcg MK</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>7702057715908</t>
+        </is>
+      </c>
       <c r="D1397" t="inlineStr"/>
       <c r="E1397" t="n">
-        <v>16807</v>
+        <v>27900</v>
       </c>
       <c r="F1397" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1397" t="n">
         <v>0</v>
@@ -74856,7 +74864,7 @@
       </c>
       <c r="M1397" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1397" t="inlineStr"/>
@@ -74864,18 +74872,18 @@
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
+          <t>LIMA MAYOMI 10/180</t>
         </is>
       </c>
       <c r="C1398" t="inlineStr"/>
       <c r="D1398" t="inlineStr"/>
       <c r="E1398" t="n">
-        <v>15042.016807</v>
+        <v>3900</v>
       </c>
       <c r="F1398" t="n">
         <v>1</v>
@@ -74906,7 +74914,7 @@
       </c>
       <c r="M1398" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1398" t="inlineStr"/>
@@ -74914,21 +74922,21 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>LISTERINE CUIDADO TOTAL 180ML</t>
+          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
         </is>
       </c>
       <c r="C1399" t="inlineStr"/>
       <c r="D1399" t="inlineStr"/>
       <c r="E1399" t="n">
-        <v>16386.554622</v>
+        <v>16807</v>
       </c>
       <c r="F1399" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1399" t="n">
         <v>0</v>
@@ -74964,21 +74972,21 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
+          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
         </is>
       </c>
       <c r="C1400" t="inlineStr"/>
       <c r="D1400" t="inlineStr"/>
       <c r="E1400" t="n">
-        <v>3500</v>
+        <v>15042.016807</v>
       </c>
       <c r="F1400" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G1400" t="n">
         <v>0</v>
@@ -75006,7 +75014,7 @@
       </c>
       <c r="M1400" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1400" t="inlineStr"/>
@@ -75014,21 +75022,21 @@
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+          <t>LISTERINE CUIDADO TOTAL 180ML</t>
         </is>
       </c>
       <c r="C1401" t="inlineStr"/>
       <c r="D1401" t="inlineStr"/>
       <c r="E1401" t="n">
-        <v>3500</v>
+        <v>16386.554622</v>
       </c>
       <c r="F1401" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1401" t="n">
         <v>0</v>
@@ -75056,7 +75064,7 @@
       </c>
       <c r="M1401" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1401" t="inlineStr"/>
@@ -75064,21 +75072,21 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
         </is>
       </c>
       <c r="C1402" t="inlineStr"/>
       <c r="D1402" t="inlineStr"/>
       <c r="E1402" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="F1402" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="G1402" t="n">
         <v>0</v>
@@ -75114,22 +75122,18 @@
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>Losartan Tensofar 100 Mg</t>
-        </is>
-      </c>
-      <c r="C1403" t="inlineStr">
-        <is>
-          <t>7703546012119</t>
-        </is>
-      </c>
+          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr"/>
       <c r="D1403" t="inlineStr"/>
       <c r="E1403" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="F1403" t="n">
         <v>1</v>
@@ -75168,25 +75172,21 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
-        </is>
-      </c>
-      <c r="C1404" t="inlineStr">
-        <is>
-          <t>7501007528939</t>
-        </is>
-      </c>
+          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr"/>
       <c r="D1404" t="inlineStr"/>
       <c r="E1404" t="n">
-        <v>18907.563025</v>
+        <v>4500</v>
       </c>
       <c r="F1404" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1404" t="n">
         <v>0</v>
@@ -75214,7 +75214,7 @@
       </c>
       <c r="M1404" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1404" t="inlineStr"/>
@@ -75222,21 +75222,25 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>MANTECA DE CACAO LABIAL LIMON</t>
-        </is>
-      </c>
-      <c r="C1405" t="inlineStr"/>
+          <t>Losartan Tensofar 100 Mg</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>7703546012119</t>
+        </is>
+      </c>
       <c r="D1405" t="inlineStr"/>
       <c r="E1405" t="n">
-        <v>3361.344538</v>
+        <v>5000</v>
       </c>
       <c r="F1405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1405" t="n">
         <v>0</v>
@@ -75264,7 +75268,7 @@
       </c>
       <c r="M1405" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1405" t="inlineStr"/>
@@ -75272,18 +75276,22 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
-        </is>
-      </c>
-      <c r="C1406" t="inlineStr"/>
+          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>7501007528939</t>
+        </is>
+      </c>
       <c r="D1406" t="inlineStr"/>
       <c r="E1406" t="n">
-        <v>3361.344538</v>
+        <v>18907.563025</v>
       </c>
       <c r="F1406" t="n">
         <v>0</v>
@@ -75322,21 +75330,21 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>Mega sex</t>
+          <t>MANTECA DE CACAO LABIAL LIMON</t>
         </is>
       </c>
       <c r="C1407" t="inlineStr"/>
       <c r="D1407" t="inlineStr"/>
       <c r="E1407" t="n">
-        <v>3200</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1407" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G1407" t="n">
         <v>0</v>
@@ -75364,7 +75372,7 @@
       </c>
       <c r="M1407" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1407" t="inlineStr"/>
@@ -75372,26 +75380,18 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>Melatonina 3mg</t>
-        </is>
-      </c>
-      <c r="C1408" t="inlineStr">
-        <is>
-          <t>7706849112906</t>
-        </is>
-      </c>
-      <c r="D1408" t="inlineStr">
-        <is>
-          <t>producto nuevo</t>
-        </is>
-      </c>
+          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr"/>
+      <c r="D1408" t="inlineStr"/>
       <c r="E1408" t="n">
-        <v>52000</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1408" t="n">
         <v>0</v>
@@ -75422,7 +75422,7 @@
       </c>
       <c r="M1408" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1408" t="inlineStr"/>
@@ -75430,25 +75430,21 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
-        </is>
-      </c>
-      <c r="C1409" t="inlineStr">
-        <is>
-          <t>7707529435209</t>
-        </is>
-      </c>
+          <t>Mega sex</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr"/>
       <c r="D1409" t="inlineStr"/>
       <c r="E1409" t="n">
-        <v>36000</v>
+        <v>3200</v>
       </c>
       <c r="F1409" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G1409" t="n">
         <v>0</v>
@@ -75484,22 +75480,26 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>Meloxicam 15mg AG</t>
+          <t>Melatonina 3mg</t>
         </is>
       </c>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>7706569020437</t>
-        </is>
-      </c>
-      <c r="D1410" t="inlineStr"/>
+          <t>7706849112906</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>producto nuevo</t>
+        </is>
+      </c>
       <c r="E1410" t="n">
-        <v>1500</v>
+        <v>52000</v>
       </c>
       <c r="F1410" t="n">
         <v>0</v>
@@ -75538,21 +75538,25 @@
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
-        </is>
-      </c>
-      <c r="C1411" t="inlineStr"/>
+          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>7707529435209</t>
+        </is>
+      </c>
       <c r="D1411" t="inlineStr"/>
       <c r="E1411" t="n">
-        <v>9700</v>
+        <v>36000</v>
       </c>
       <c r="F1411" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1411" t="n">
         <v>0</v>
@@ -75588,22 +75592,22 @@
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>MELOXICAM COASPHARMA</t>
+          <t>Meloxicam 15mg AG</t>
         </is>
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>7703712036253</t>
+          <t>7706569020437</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr"/>
       <c r="E1412" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F1412" t="n">
         <v>0</v>
@@ -75632,31 +75636,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1412" t="inlineStr"/>
+      <c r="M1412" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1412" t="inlineStr"/>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>metformina 850 mg pisa</t>
-        </is>
-      </c>
-      <c r="C1413" t="inlineStr">
-        <is>
-          <t>7501125188039</t>
-        </is>
-      </c>
+          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr"/>
       <c r="D1413" t="inlineStr"/>
       <c r="E1413" t="n">
-        <v>5500</v>
+        <v>9700</v>
       </c>
       <c r="F1413" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G1413" t="n">
         <v>0</v>
@@ -75692,25 +75696,25 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10MG RECIPE</t>
+          <t>MELOXICAM COASPHARMA</t>
         </is>
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>7702195084355</t>
+          <t>7703712036253</t>
         </is>
       </c>
       <c r="D1414" t="inlineStr"/>
       <c r="E1414" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="F1414" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1414" t="n">
         <v>0</v>
@@ -75736,35 +75740,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1414" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1414" t="inlineStr"/>
       <c r="N1414" t="inlineStr"/>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>MICROPOR 1X3 Y</t>
+          <t>metformina 850 mg pisa</t>
         </is>
       </c>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>7707282990205</t>
+          <t>7501125188039</t>
         </is>
       </c>
       <c r="D1415" t="inlineStr"/>
       <c r="E1415" t="n">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="F1415" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G1415" t="n">
         <v>0</v>
@@ -75800,25 +75800,25 @@
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>MICROPOR CINTA 1/2X5Y</t>
+          <t>METOCLOPRAMIDA 10MG RECIPE</t>
         </is>
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>7707282990182</t>
+          <t>7702195084355</t>
         </is>
       </c>
       <c r="D1416" t="inlineStr"/>
       <c r="E1416" t="n">
-        <v>3900</v>
+        <v>1000</v>
       </c>
       <c r="F1416" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G1416" t="n">
         <v>0</v>
@@ -75854,21 +75854,25 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>MICROPORE COLOR PIEL 2YARDAS</t>
-        </is>
-      </c>
-      <c r="C1417" t="inlineStr"/>
+          <t>MICROPOR 1X3 Y</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>7707282990205</t>
+        </is>
+      </c>
       <c r="D1417" t="inlineStr"/>
       <c r="E1417" t="n">
-        <v>3700</v>
+        <v>5300</v>
       </c>
       <c r="F1417" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1417" t="n">
         <v>0</v>
@@ -75904,21 +75908,25 @@
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
-        </is>
-      </c>
-      <c r="C1418" t="inlineStr"/>
+          <t>MICROPOR CINTA 1/2X5Y</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>7707282990182</t>
+        </is>
+      </c>
       <c r="D1418" t="inlineStr"/>
       <c r="E1418" t="n">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="F1418" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G1418" t="n">
         <v>0</v>
@@ -75954,22 +75962,18 @@
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>MIELTERTOS JARABE X 240ML</t>
-        </is>
-      </c>
-      <c r="C1419" t="inlineStr">
-        <is>
-          <t>7707232095608</t>
-        </is>
-      </c>
+          <t>MICROPORE COLOR PIEL 2YARDAS</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr"/>
       <c r="D1419" t="inlineStr"/>
       <c r="E1419" t="n">
-        <v>34500</v>
+        <v>3700</v>
       </c>
       <c r="F1419" t="n">
         <v>0</v>
@@ -76008,25 +76012,21 @@
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
+          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
         </is>
       </c>
       <c r="C1420" t="inlineStr"/>
-      <c r="D1420" t="inlineStr">
-        <is>
-          <t>subio precio hector</t>
-        </is>
-      </c>
+      <c r="D1420" t="inlineStr"/>
       <c r="E1420" t="n">
-        <v>22700</v>
+        <v>4000</v>
       </c>
       <c r="F1420" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1420" t="n">
         <v>0</v>
@@ -76062,21 +76062,25 @@
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
-        </is>
-      </c>
-      <c r="C1421" t="inlineStr"/>
+          <t>MIELTERTOS JARABE X 240ML</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>7707232095608</t>
+        </is>
+      </c>
       <c r="D1421" t="inlineStr"/>
       <c r="E1421" t="n">
-        <v>5500</v>
+        <v>34500</v>
       </c>
       <c r="F1421" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G1421" t="n">
         <v>0</v>
@@ -76112,21 +76116,25 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>NEOSALDINA TABLETA X UND</t>
+          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
         </is>
       </c>
       <c r="C1422" t="inlineStr"/>
-      <c r="D1422" t="inlineStr"/>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>subio precio hector</t>
+        </is>
+      </c>
       <c r="E1422" t="n">
-        <v>2500</v>
+        <v>22700</v>
       </c>
       <c r="F1422" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G1422" t="n">
         <v>0</v>
@@ -76162,21 +76170,21 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>NIFEDIPINO 30MG NOVAMED</t>
+          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
         </is>
       </c>
       <c r="C1423" t="inlineStr"/>
       <c r="D1423" t="inlineStr"/>
       <c r="E1423" t="n">
-        <v>19000</v>
+        <v>5500</v>
       </c>
       <c r="F1423" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G1423" t="n">
         <v>0</v>
@@ -76212,21 +76220,21 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
+          <t>NEOSALDINA TABLETA X UND</t>
         </is>
       </c>
       <c r="C1424" t="inlineStr"/>
       <c r="D1424" t="inlineStr"/>
       <c r="E1424" t="n">
-        <v>23000</v>
+        <v>2500</v>
       </c>
       <c r="F1424" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G1424" t="n">
         <v>0</v>
@@ -76262,21 +76270,21 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>NITOXIPAR X 6 TABLETAS</t>
+          <t>NIFEDIPINO 30MG NOVAMED</t>
         </is>
       </c>
       <c r="C1425" t="inlineStr"/>
       <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="n">
-        <v>24500</v>
+        <v>19000</v>
       </c>
       <c r="F1425" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1425" t="n">
         <v>0</v>
@@ -76312,21 +76320,21 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>NORAVER SPRAY CEREZA 120ML</t>
+          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
         </is>
       </c>
       <c r="C1426" t="inlineStr"/>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="n">
-        <v>52900</v>
+        <v>23000</v>
       </c>
       <c r="F1426" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1426" t="n">
         <v>0</v>
@@ -76362,25 +76370,21 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
-        </is>
-      </c>
-      <c r="C1427" t="inlineStr">
-        <is>
-          <t>7702027041662</t>
-        </is>
-      </c>
+          <t>NITOXIPAR X 6 TABLETAS</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr"/>
       <c r="D1427" t="inlineStr"/>
       <c r="E1427" t="n">
-        <v>6300</v>
+        <v>24500</v>
       </c>
       <c r="F1427" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1427" t="n">
         <v>0</v>
@@ -76416,21 +76420,21 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+          <t>NORAVER SPRAY CEREZA 120ML</t>
         </is>
       </c>
       <c r="C1428" t="inlineStr"/>
       <c r="D1428" t="inlineStr"/>
       <c r="E1428" t="n">
-        <v>8823.529412</v>
+        <v>52900</v>
       </c>
       <c r="F1428" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1428" t="n">
         <v>0</v>
@@ -76458,7 +76462,7 @@
       </c>
       <c r="M1428" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1428" t="inlineStr"/>
@@ -76466,22 +76470,22 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
         </is>
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>7702026158644</t>
+          <t>7702027041662</t>
         </is>
       </c>
       <c r="D1429" t="inlineStr"/>
       <c r="E1429" t="n">
-        <v>8823.529412</v>
+        <v>6300</v>
       </c>
       <c r="F1429" t="n">
         <v>0</v>
@@ -76512,7 +76516,7 @@
       </c>
       <c r="M1429" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1429" t="inlineStr"/>
@@ -76520,25 +76524,21 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JBE 120ML</t>
-        </is>
-      </c>
-      <c r="C1430" t="inlineStr">
-        <is>
-          <t>7707355053363</t>
-        </is>
-      </c>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr"/>
       <c r="D1430" t="inlineStr"/>
       <c r="E1430" t="n">
-        <v>22700</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1430" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1430" t="n">
         <v>0</v>
@@ -76566,7 +76566,7 @@
       </c>
       <c r="M1430" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1430" t="inlineStr"/>
@@ -76574,22 +76574,22 @@
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
         </is>
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>7707355053356</t>
+          <t>7702026158644</t>
         </is>
       </c>
       <c r="D1431" t="inlineStr"/>
       <c r="E1431" t="n">
-        <v>17200</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1431" t="n">
         <v>0</v>
@@ -76620,7 +76620,7 @@
       </c>
       <c r="M1431" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1431" t="inlineStr"/>
@@ -76628,18 +76628,22 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>NUTRIBELL ACEITE DE COCO</t>
-        </is>
-      </c>
-      <c r="C1432" t="inlineStr"/>
+          <t>NOXPIRIN JUNIOR JBE 120ML</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>7707355053363</t>
+        </is>
+      </c>
       <c r="D1432" t="inlineStr"/>
       <c r="E1432" t="n">
-        <v>2700</v>
+        <v>22700</v>
       </c>
       <c r="F1432" t="n">
         <v>1</v>
@@ -76678,29 +76682,25 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Omega 3 6 9 suplemento totalmax</t>
+          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
         </is>
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>7707529434974</t>
-        </is>
-      </c>
-      <c r="D1433" t="inlineStr">
-        <is>
-          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
-        </is>
-      </c>
+          <t>7707355053356</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr"/>
       <c r="E1433" t="n">
-        <v>35000</v>
+        <v>17200</v>
       </c>
       <c r="F1433" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1433" t="n">
         <v>0</v>
@@ -76736,21 +76736,21 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
+          <t>NUTRIBELL ACEITE DE COCO</t>
         </is>
       </c>
       <c r="C1434" t="inlineStr"/>
       <c r="D1434" t="inlineStr"/>
       <c r="E1434" t="n">
-        <v>5500</v>
+        <v>2700</v>
       </c>
       <c r="F1434" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1434" t="n">
         <v>0</v>
@@ -76786,25 +76786,29 @@
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
+          <t>Omega 3 6 9 suplemento totalmax</t>
         </is>
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>7707529435940</t>
-        </is>
-      </c>
-      <c r="D1435" t="inlineStr"/>
+          <t>7707529434974</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
+        </is>
+      </c>
       <c r="E1435" t="n">
         <v>35000</v>
       </c>
       <c r="F1435" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>
@@ -76840,21 +76844,21 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
+          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
         </is>
       </c>
       <c r="C1436" t="inlineStr"/>
       <c r="D1436" t="inlineStr"/>
       <c r="E1436" t="n">
-        <v>48000</v>
+        <v>5500</v>
       </c>
       <c r="F1436" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1436" t="n">
         <v>0</v>
@@ -76890,25 +76894,25 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>OROCAL CALCIO 600MG</t>
-        </is>
-      </c>
-      <c r="C1437" t="inlineStr"/>
-      <c r="D1437" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>7707529435940</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr"/>
       <c r="E1437" t="n">
-        <v>30500</v>
+        <v>35000</v>
       </c>
       <c r="F1437" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1437" t="n">
         <v>0</v>
@@ -76944,21 +76948,21 @@
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>PALA DE MADERA RASPACALLO</t>
+          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
         </is>
       </c>
       <c r="C1438" t="inlineStr"/>
       <c r="D1438" t="inlineStr"/>
       <c r="E1438" t="n">
-        <v>4000</v>
+        <v>48000</v>
       </c>
       <c r="F1438" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1438" t="n">
         <v>0</v>
@@ -76994,21 +76998,25 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>PALO DE NARANJO X UNIDAD</t>
+          <t>OROCAL CALCIO 600MG</t>
         </is>
       </c>
       <c r="C1439" t="inlineStr"/>
-      <c r="D1439" t="inlineStr"/>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E1439" t="n">
-        <v>400</v>
+        <v>30500</v>
       </c>
       <c r="F1439" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G1439" t="n">
         <v>0</v>
@@ -77044,22 +77052,18 @@
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
-        </is>
-      </c>
-      <c r="C1440" t="inlineStr">
-        <is>
-          <t>7704412170896</t>
-        </is>
-      </c>
+          <t>PALA DE MADERA RASPACALLO</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr"/>
       <c r="D1440" t="inlineStr"/>
       <c r="E1440" t="n">
-        <v>6200</v>
+        <v>4000</v>
       </c>
       <c r="F1440" t="n">
         <v>1</v>
@@ -77098,21 +77102,21 @@
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
+          <t>PALO DE NARANJO X UNIDAD</t>
         </is>
       </c>
       <c r="C1441" t="inlineStr"/>
       <c r="D1441" t="inlineStr"/>
       <c r="E1441" t="n">
-        <v>14285.714286</v>
+        <v>400</v>
       </c>
       <c r="F1441" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G1441" t="n">
         <v>0</v>
@@ -77140,7 +77144,7 @@
       </c>
       <c r="M1441" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1441" t="inlineStr"/>
@@ -77148,18 +77152,22 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
-        </is>
-      </c>
-      <c r="C1442" t="inlineStr"/>
+          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>7704412170896</t>
+        </is>
+      </c>
       <c r="D1442" t="inlineStr"/>
       <c r="E1442" t="n">
-        <v>28991.596639</v>
+        <v>6200</v>
       </c>
       <c r="F1442" t="n">
         <v>1</v>
@@ -77190,7 +77198,7 @@
       </c>
       <c r="M1442" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1442" t="inlineStr"/>
@@ -77198,18 +77206,18 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
         </is>
       </c>
       <c r="C1443" t="inlineStr"/>
       <c r="D1443" t="inlineStr"/>
       <c r="E1443" t="n">
-        <v>41176.470588</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1443" t="n">
         <v>1</v>
@@ -77248,22 +77256,18 @@
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>Pañales Winny Etapa 5 X PAQUETE</t>
-        </is>
-      </c>
-      <c r="C1444" t="inlineStr">
-        <is>
-          <t>7701021114174</t>
-        </is>
-      </c>
+          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr"/>
       <c r="D1444" t="inlineStr"/>
       <c r="E1444" t="n">
-        <v>41849</v>
+        <v>28991.596639</v>
       </c>
       <c r="F1444" t="n">
         <v>1</v>
@@ -77302,21 +77306,21 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>PAÑALWINNY ETA 5 X 16 UND</t>
+          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
         </is>
       </c>
       <c r="C1445" t="inlineStr"/>
       <c r="D1445" t="inlineStr"/>
       <c r="E1445" t="n">
-        <v>24369.747899</v>
+        <v>41176.470588</v>
       </c>
       <c r="F1445" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1445" t="n">
         <v>0</v>
@@ -77352,21 +77356,25 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>pañitos humedos pequeñin 100unidades</t>
-        </is>
-      </c>
-      <c r="C1446" t="inlineStr"/>
+          <t>Pañales Winny Etapa 5 X PAQUETE</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>7701021114174</t>
+        </is>
+      </c>
       <c r="D1446" t="inlineStr"/>
       <c r="E1446" t="n">
-        <v>10925</v>
+        <v>41849</v>
       </c>
       <c r="F1446" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1446" t="n">
         <v>0</v>
@@ -77402,18 +77410,18 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
+          <t>PAÑALWINNY ETA 5 X 16 UND</t>
         </is>
       </c>
       <c r="C1447" t="inlineStr"/>
       <c r="D1447" t="inlineStr"/>
       <c r="E1447" t="n">
-        <v>14900</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1447" t="n">
         <v>2</v>
@@ -77444,7 +77452,7 @@
       </c>
       <c r="M1447" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1447" t="inlineStr"/>
@@ -77452,21 +77460,21 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Panotil B x 8ML</t>
+          <t>pañitos humedos pequeñin 100unidades</t>
         </is>
       </c>
       <c r="C1448" t="inlineStr"/>
       <c r="D1448" t="inlineStr"/>
       <c r="E1448" t="n">
-        <v>26400</v>
+        <v>10925</v>
       </c>
       <c r="F1448" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1448" t="n">
         <v>0</v>
@@ -77494,7 +77502,7 @@
       </c>
       <c r="M1448" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1448" t="inlineStr"/>
@@ -77502,25 +77510,21 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>PANTENE ACONDICIONADOR</t>
-        </is>
-      </c>
-      <c r="C1449" t="inlineStr">
-        <is>
-          <t>7500435153683</t>
-        </is>
-      </c>
+          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr"/>
       <c r="D1449" t="inlineStr"/>
       <c r="E1449" t="n">
-        <v>1500</v>
+        <v>14900</v>
       </c>
       <c r="F1449" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G1449" t="n">
         <v>0</v>
@@ -77556,21 +77560,21 @@
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Parche Ocular Colostol</t>
+          <t>Panotil B x 8ML</t>
         </is>
       </c>
       <c r="C1450" t="inlineStr"/>
       <c r="D1450" t="inlineStr"/>
       <c r="E1450" t="n">
-        <v>1300</v>
+        <v>26400</v>
       </c>
       <c r="F1450" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G1450" t="n">
         <v>0</v>
@@ -77606,25 +77610,25 @@
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
+          <t>PANTENE ACONDICIONADOR</t>
         </is>
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>7501033957413</t>
+          <t>7500435153683</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr"/>
       <c r="E1451" t="n">
-        <v>10600</v>
+        <v>1500</v>
       </c>
       <c r="F1451" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1451" t="n">
         <v>0</v>
@@ -77660,29 +77664,21 @@
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
-        </is>
-      </c>
-      <c r="C1452" t="inlineStr">
-        <is>
-          <t>7501033961557</t>
-        </is>
-      </c>
-      <c r="D1452" t="inlineStr">
-        <is>
-          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
-        </is>
-      </c>
+          <t>Parche Ocular Colostol</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr"/>
+      <c r="D1452" t="inlineStr"/>
       <c r="E1452" t="n">
-        <v>10900</v>
+        <v>1300</v>
       </c>
       <c r="F1452" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G1452" t="n">
         <v>0</v>
@@ -77718,29 +77714,25 @@
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>7501033957376</t>
-        </is>
-      </c>
-      <c r="D1453" t="inlineStr">
-        <is>
-          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
-        </is>
-      </c>
+          <t>7501033957413</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr"/>
       <c r="E1453" t="n">
-        <v>10900</v>
+        <v>10600</v>
       </c>
       <c r="F1453" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1453" t="n">
         <v>0</v>
@@ -77776,21 +77768,29 @@
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>PEGANTE GLUE X 10GR X UND</t>
-        </is>
-      </c>
-      <c r="C1454" t="inlineStr"/>
-      <c r="D1454" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>7501033961557</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
+        </is>
+      </c>
       <c r="E1454" t="n">
-        <v>2000</v>
+        <v>10900</v>
       </c>
       <c r="F1454" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1454" t="n">
         <v>0</v>
@@ -77826,21 +77826,29 @@
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>PEINETA COLA DE RATON METALICA</t>
-        </is>
-      </c>
-      <c r="C1455" t="inlineStr"/>
-      <c r="D1455" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>7501033957376</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+        </is>
+      </c>
       <c r="E1455" t="n">
-        <v>4700</v>
+        <v>10900</v>
       </c>
       <c r="F1455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1455" t="n">
         <v>0</v>
@@ -77876,21 +77884,21 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>PERFILADORES DE CEJAS</t>
+          <t>PEGANTE GLUE X 10GR X UND</t>
         </is>
       </c>
       <c r="C1456" t="inlineStr"/>
       <c r="D1456" t="inlineStr"/>
       <c r="E1456" t="n">
-        <v>3900</v>
+        <v>2000</v>
       </c>
       <c r="F1456" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1456" t="n">
         <v>0</v>
@@ -77926,18 +77934,18 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
+          <t>PEINETA COLA DE RATON METALICA</t>
         </is>
       </c>
       <c r="C1457" t="inlineStr"/>
       <c r="D1457" t="inlineStr"/>
       <c r="E1457" t="n">
-        <v>27983.193277</v>
+        <v>4700</v>
       </c>
       <c r="F1457" t="n">
         <v>1</v>
@@ -77968,7 +77976,7 @@
       </c>
       <c r="M1457" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1457" t="inlineStr"/>
@@ -77976,21 +77984,21 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>POPETAS SURTIDAS X UND</t>
+          <t>PERFILADORES DE CEJAS</t>
         </is>
       </c>
       <c r="C1458" t="inlineStr"/>
       <c r="D1458" t="inlineStr"/>
       <c r="E1458" t="n">
-        <v>2521.008403</v>
+        <v>3900</v>
       </c>
       <c r="F1458" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1458" t="n">
         <v>0</v>
@@ -78018,7 +78026,7 @@
       </c>
       <c r="M1458" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1458" t="inlineStr"/>
@@ -78026,21 +78034,21 @@
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
         </is>
       </c>
       <c r="C1459" t="inlineStr"/>
       <c r="D1459" t="inlineStr"/>
       <c r="E1459" t="n">
-        <v>20500</v>
+        <v>27983.193277</v>
       </c>
       <c r="F1459" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1459" t="n">
         <v>0</v>
@@ -78068,7 +78076,7 @@
       </c>
       <c r="M1459" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1459" t="inlineStr"/>
@@ -78076,29 +78084,21 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>privatos miel limon la francol 120ml</t>
-        </is>
-      </c>
-      <c r="C1460" t="inlineStr">
-        <is>
-          <t>7702207163948</t>
-        </is>
-      </c>
-      <c r="D1460" t="inlineStr">
-        <is>
-          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
-        </is>
-      </c>
+          <t>POPETAS SURTIDAS X UND</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr"/>
+      <c r="D1460" t="inlineStr"/>
       <c r="E1460" t="n">
-        <v>35900</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1460" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1460" t="n">
         <v>0</v>
@@ -78126,7 +78126,7 @@
       </c>
       <c r="M1460" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1460" t="inlineStr"/>
@@ -78134,18 +78134,18 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
+          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr"/>
       <c r="D1461" t="inlineStr"/>
       <c r="E1461" t="n">
-        <v>0</v>
+        <v>20500</v>
       </c>
       <c r="F1461" t="n">
         <v>0</v>
@@ -78176,7 +78176,7 @@
       </c>
       <c r="M1461" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1461" t="inlineStr"/>
@@ -78184,18 +78184,26 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>PROTECTOR NOSOTRAS LARGOS</t>
-        </is>
-      </c>
-      <c r="C1462" t="inlineStr"/>
-      <c r="D1462" t="inlineStr"/>
+          <t>privatos miel limon la francol 120ml</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>7702207163948</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
+        </is>
+      </c>
       <c r="E1462" t="n">
-        <v>3700</v>
+        <v>35900</v>
       </c>
       <c r="F1462" t="n">
         <v>1</v>
@@ -78234,21 +78242,21 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>778</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
+          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
         </is>
       </c>
       <c r="C1463" t="inlineStr"/>
       <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="n">
-        <v>8900</v>
+        <v>0</v>
       </c>
       <c r="F1463" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1463" t="n">
         <v>0</v>
@@ -78276,7 +78284,7 @@
       </c>
       <c r="M1463" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1463" t="inlineStr"/>
@@ -78284,21 +78292,21 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>Protector Solar Sunaid</t>
+          <t>PROTECTOR NOSOTRAS LARGOS</t>
         </is>
       </c>
       <c r="C1464" t="inlineStr"/>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="n">
-        <v>158000</v>
+        <v>3700</v>
       </c>
       <c r="F1464" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1464" t="n">
         <v>0</v>
@@ -78334,25 +78342,21 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>Prueba de embarazo esfero</t>
-        </is>
-      </c>
-      <c r="C1465" t="inlineStr">
-        <is>
-          <t>7709299854228</t>
-        </is>
-      </c>
+          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr"/>
       <c r="D1465" t="inlineStr"/>
       <c r="E1465" t="n">
-        <v>16500</v>
+        <v>8900</v>
       </c>
       <c r="F1465" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1465" t="n">
         <v>0</v>
@@ -78388,25 +78392,21 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Prueba de embarazo HCG cassette begut</t>
-        </is>
-      </c>
-      <c r="C1466" t="inlineStr">
-        <is>
-          <t>7707282990953</t>
-        </is>
-      </c>
+          <t>Protector Solar Sunaid</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr"/>
       <c r="D1466" t="inlineStr"/>
       <c r="E1466" t="n">
-        <v>8900</v>
+        <v>158000</v>
       </c>
       <c r="F1466" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G1466" t="n">
         <v>0</v>
@@ -78442,21 +78442,25 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>PUSHER METALICO</t>
-        </is>
-      </c>
-      <c r="C1467" t="inlineStr"/>
+          <t>Prueba de embarazo esfero</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>7709299854228</t>
+        </is>
+      </c>
       <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="n">
-        <v>4300</v>
+        <v>16500</v>
       </c>
       <c r="F1467" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1467" t="n">
         <v>0</v>
@@ -78492,21 +78496,25 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
-        </is>
-      </c>
-      <c r="C1468" t="inlineStr"/>
+          <t>Prueba de embarazo HCG cassette begut</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>7707282990953</t>
+        </is>
+      </c>
       <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="n">
-        <v>17900</v>
+        <v>8900</v>
       </c>
       <c r="F1468" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1468" t="n">
         <v>0</v>
@@ -78542,25 +78550,21 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>Recolector de orina granandina</t>
-        </is>
-      </c>
-      <c r="C1469" t="inlineStr">
-        <is>
-          <t>7707233050590</t>
-        </is>
-      </c>
+          <t>PUSHER METALICO</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr"/>
       <c r="D1469" t="inlineStr"/>
       <c r="E1469" t="n">
-        <v>673</v>
+        <v>4300</v>
       </c>
       <c r="F1469" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G1469" t="n">
         <v>0</v>
@@ -78588,7 +78592,7 @@
       </c>
       <c r="M1469" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1469" t="inlineStr"/>
@@ -78596,21 +78600,21 @@
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
+          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
         </is>
       </c>
       <c r="C1470" t="inlineStr"/>
       <c r="D1470" t="inlineStr"/>
       <c r="E1470" t="n">
-        <v>3820</v>
+        <v>17900</v>
       </c>
       <c r="F1470" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1470" t="n">
         <v>0</v>
@@ -78646,21 +78650,25 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>RegistroManual - Registro manual</t>
-        </is>
-      </c>
-      <c r="C1471" t="inlineStr"/>
+          <t>Recolector de orina granandina</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>7707233050590</t>
+        </is>
+      </c>
       <c r="D1471" t="inlineStr"/>
       <c r="E1471" t="n">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="F1471" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G1471" t="n">
         <v>0</v>
@@ -78696,21 +78704,21 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>REMOVEDOR DE ESMALTE 60CC</t>
+          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
         </is>
       </c>
       <c r="C1472" t="inlineStr"/>
       <c r="D1472" t="inlineStr"/>
       <c r="E1472" t="n">
-        <v>3500</v>
+        <v>3820</v>
       </c>
       <c r="F1472" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1472" t="n">
         <v>0</v>
@@ -78746,25 +78754,21 @@
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
-        </is>
-      </c>
-      <c r="C1473" t="inlineStr">
-        <is>
-          <t>7591005981270</t>
-        </is>
-      </c>
+          <t>RegistroManual - Registro manual</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr"/>
       <c r="D1473" t="inlineStr"/>
       <c r="E1473" t="n">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="F1473" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1473" t="n">
         <v>0</v>
@@ -78792,7 +78796,7 @@
       </c>
       <c r="M1473" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1473" t="inlineStr"/>
@@ -78800,25 +78804,21 @@
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
-        </is>
-      </c>
-      <c r="C1474" t="inlineStr">
-        <is>
-          <t>7503051868245</t>
-        </is>
-      </c>
+          <t>REMOVEDOR DE ESMALTE 60CC</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr"/>
       <c r="D1474" t="inlineStr"/>
       <c r="E1474" t="n">
-        <v>20900</v>
+        <v>3500</v>
       </c>
       <c r="F1474" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1474" t="n">
         <v>0</v>
@@ -78854,25 +78854,25 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
         </is>
       </c>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>7702057079642</t>
+          <t>7591005981270</t>
         </is>
       </c>
       <c r="D1475" t="inlineStr"/>
       <c r="E1475" t="n">
-        <v>13000</v>
+        <v>9500</v>
       </c>
       <c r="F1475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1475" t="n">
         <v>0</v>
@@ -78908,21 +78908,25 @@
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Ryaltris Spray Nasal 240 dosis</t>
-        </is>
-      </c>
-      <c r="C1476" t="inlineStr"/>
+          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>7503051868245</t>
+        </is>
+      </c>
       <c r="D1476" t="inlineStr"/>
       <c r="E1476" t="n">
-        <v>216400</v>
+        <v>20900</v>
       </c>
       <c r="F1476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1476" t="n">
         <v>0</v>
@@ -78958,25 +78962,25 @@
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+          <t>RISPERIDONA 1MG X 20 TABL MK</t>
         </is>
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>7706849116676</t>
+          <t>7702057079642</t>
         </is>
       </c>
       <c r="D1477" t="inlineStr"/>
       <c r="E1477" t="n">
-        <v>31500</v>
+        <v>13000</v>
       </c>
       <c r="F1477" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1477" t="n">
         <v>0</v>
@@ -79012,21 +79016,21 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>SCOBIT PURGANTE 60GR</t>
+          <t>Ryaltris Spray Nasal 240 dosis</t>
         </is>
       </c>
       <c r="C1478" t="inlineStr"/>
       <c r="D1478" t="inlineStr"/>
       <c r="E1478" t="n">
-        <v>15238.095238</v>
+        <v>216400</v>
       </c>
       <c r="F1478" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1478" t="n">
         <v>0</v>
@@ -79054,7 +79058,7 @@
       </c>
       <c r="M1478" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1478" t="inlineStr"/>
@@ -79062,21 +79066,25 @@
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
-        </is>
-      </c>
-      <c r="C1479" t="inlineStr"/>
+          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>7706849116676</t>
+        </is>
+      </c>
       <c r="D1479" t="inlineStr"/>
       <c r="E1479" t="n">
-        <v>6554.621849</v>
+        <v>31500</v>
       </c>
       <c r="F1479" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1479" t="n">
         <v>0</v>
@@ -79104,7 +79112,7 @@
       </c>
       <c r="M1479" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1479" t="inlineStr"/>
@@ -79112,25 +79120,21 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>SHAMPOO PANTENE COLAGENO</t>
-        </is>
-      </c>
-      <c r="C1480" t="inlineStr">
-        <is>
-          <t>7500435191500</t>
-        </is>
-      </c>
+          <t>SCOBIT PURGANTE 60GR</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr"/>
       <c r="D1480" t="inlineStr"/>
       <c r="E1480" t="n">
-        <v>1429</v>
+        <v>15238.095238</v>
       </c>
       <c r="F1480" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1480" t="n">
         <v>0</v>
@@ -79158,7 +79162,7 @@
       </c>
       <c r="M1480" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1480" t="inlineStr"/>
@@ -79166,21 +79170,21 @@
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>SILDENAFIL 50MG TQ</t>
+          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
         </is>
       </c>
       <c r="C1481" t="inlineStr"/>
       <c r="D1481" t="inlineStr"/>
       <c r="E1481" t="n">
-        <v>5000</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1481" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1481" t="n">
         <v>0</v>
@@ -79208,7 +79212,7 @@
       </c>
       <c r="M1481" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1481" t="inlineStr"/>
@@ -79216,25 +79220,25 @@
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>SILIMARINA 167MG EPANAT</t>
+          <t>SHAMPOO PANTENE COLAGENO</t>
         </is>
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>7706849115921</t>
+          <t>7500435191500</t>
         </is>
       </c>
       <c r="D1482" t="inlineStr"/>
       <c r="E1482" t="n">
-        <v>2000</v>
+        <v>1429</v>
       </c>
       <c r="F1482" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G1482" t="n">
         <v>0</v>
@@ -79262,7 +79266,7 @@
       </c>
       <c r="M1482" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1482" t="inlineStr"/>
@@ -79270,21 +79274,21 @@
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>SMECTA 3GR NARANJA S/B</t>
+          <t>SILDENAFIL 50MG TQ</t>
         </is>
       </c>
       <c r="C1483" t="inlineStr"/>
       <c r="D1483" t="inlineStr"/>
       <c r="E1483" t="n">
-        <v>8900</v>
+        <v>5000</v>
       </c>
       <c r="F1483" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G1483" t="n">
         <v>0</v>
@@ -79320,21 +79324,25 @@
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>SONDA FOLEY 2 VIAS BAL #18</t>
-        </is>
-      </c>
-      <c r="C1484" t="inlineStr"/>
+          <t>SILIMARINA 167MG EPANAT</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>7706849115921</t>
+        </is>
+      </c>
       <c r="D1484" t="inlineStr"/>
       <c r="E1484" t="n">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="F1484" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="G1484" t="n">
         <v>0</v>
@@ -79370,21 +79378,21 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>SONDA NELATON #6</t>
+          <t>SMECTA 3GR NARANJA S/B</t>
         </is>
       </c>
       <c r="C1485" t="inlineStr"/>
       <c r="D1485" t="inlineStr"/>
       <c r="E1485" t="n">
-        <v>2500</v>
+        <v>8900</v>
       </c>
       <c r="F1485" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1485" t="n">
         <v>0</v>
@@ -79420,21 +79428,21 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>SPRAY NASAL MOMETASONA 18ML</t>
+          <t>SONDA FOLEY 2 VIAS BAL #18</t>
         </is>
       </c>
       <c r="C1486" t="inlineStr"/>
       <c r="D1486" t="inlineStr"/>
       <c r="E1486" t="n">
-        <v>36900</v>
+        <v>7500</v>
       </c>
       <c r="F1486" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1486" t="n">
         <v>0</v>
@@ -79470,25 +79478,21 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1487" t="inlineStr">
-        <is>
-          <t>7703712035034</t>
-        </is>
-      </c>
+          <t>SONDA NELATON #6</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr"/>
       <c r="D1487" t="inlineStr"/>
       <c r="E1487" t="n">
-        <v>14800</v>
+        <v>2500</v>
       </c>
       <c r="F1487" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1487" t="n">
         <v>0</v>
@@ -79524,18 +79528,18 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
+          <t>SPRAY NASAL MOMETASONA 18ML</t>
         </is>
       </c>
       <c r="C1488" t="inlineStr"/>
       <c r="D1488" t="inlineStr"/>
       <c r="E1488" t="n">
-        <v>3781.512605</v>
+        <v>36900</v>
       </c>
       <c r="F1488" t="n">
         <v>1</v>
@@ -79566,7 +79570,7 @@
       </c>
       <c r="M1488" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1488" t="inlineStr"/>
@@ -79574,18 +79578,22 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
-        </is>
-      </c>
-      <c r="C1489" t="inlineStr"/>
+          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>7703712035034</t>
+        </is>
+      </c>
       <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="n">
-        <v>5210.084034</v>
+        <v>14800</v>
       </c>
       <c r="F1489" t="n">
         <v>0</v>
@@ -79616,7 +79624,7 @@
       </c>
       <c r="M1489" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1489" t="inlineStr"/>
@@ -79624,18 +79632,18 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
+          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
         </is>
       </c>
       <c r="C1490" t="inlineStr"/>
       <c r="D1490" t="inlineStr"/>
       <c r="E1490" t="n">
-        <v>8319.327730999999</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1490" t="n">
         <v>1</v>
@@ -79674,21 +79682,21 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>SULZINC SUSP X 80ML HUMAX</t>
+          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr"/>
       <c r="D1491" t="inlineStr"/>
       <c r="E1491" t="n">
-        <v>22400</v>
+        <v>5210.084034</v>
       </c>
       <c r="F1491" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1491" t="n">
         <v>0</v>
@@ -79716,7 +79724,7 @@
       </c>
       <c r="M1491" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1491" t="inlineStr"/>
@@ -79724,21 +79732,21 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>SUNDARK FPS 60 CON TAPA</t>
+          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
         </is>
       </c>
       <c r="C1492" t="inlineStr"/>
       <c r="D1492" t="inlineStr"/>
       <c r="E1492" t="n">
-        <v>3781.512605</v>
+        <v>8319.327730999999</v>
       </c>
       <c r="F1492" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1492" t="n">
         <v>0</v>
@@ -79774,21 +79782,21 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>Synthroid 125 mcg</t>
+          <t>SULZINC SUSP X 80ML HUMAX</t>
         </is>
       </c>
       <c r="C1493" t="inlineStr"/>
       <c r="D1493" t="inlineStr"/>
       <c r="E1493" t="n">
-        <v>178000</v>
+        <v>22400</v>
       </c>
       <c r="F1493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1493" t="n">
         <v>0</v>
@@ -79824,25 +79832,21 @@
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>Talco medicado Neofungina 40gm</t>
-        </is>
-      </c>
-      <c r="C1494" t="inlineStr">
-        <is>
-          <t>7706142707106</t>
-        </is>
-      </c>
+          <t>SUNDARK FPS 60 CON TAPA</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr"/>
       <c r="D1494" t="inlineStr"/>
       <c r="E1494" t="n">
-        <v>14900</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1494" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1494" t="n">
         <v>0</v>
@@ -79870,7 +79874,7 @@
       </c>
       <c r="M1494" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1494" t="inlineStr"/>
@@ -79878,18 +79882,18 @@
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
+          <t>Synthroid 125 mcg</t>
         </is>
       </c>
       <c r="C1495" t="inlineStr"/>
       <c r="D1495" t="inlineStr"/>
       <c r="E1495" t="n">
-        <v>13300</v>
+        <v>178000</v>
       </c>
       <c r="F1495" t="n">
         <v>0</v>
@@ -79928,21 +79932,25 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
-        </is>
-      </c>
-      <c r="C1496" t="inlineStr"/>
+          <t>Talco medicado Neofungina 40gm</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>7706142707106</t>
+        </is>
+      </c>
       <c r="D1496" t="inlineStr"/>
       <c r="E1496" t="n">
-        <v>4874</v>
+        <v>14900</v>
       </c>
       <c r="F1496" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G1496" t="n">
         <v>0</v>
@@ -79970,7 +79978,7 @@
       </c>
       <c r="M1496" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1496" t="inlineStr"/>
@@ -79978,21 +79986,21 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
+          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr"/>
       <c r="D1497" t="inlineStr"/>
       <c r="E1497" t="n">
-        <v>28800</v>
+        <v>13300</v>
       </c>
       <c r="F1497" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1497" t="n">
         <v>0</v>
@@ -80028,21 +80036,21 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
+          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
         </is>
       </c>
       <c r="C1498" t="inlineStr"/>
       <c r="D1498" t="inlineStr"/>
       <c r="E1498" t="n">
-        <v>11596.638655</v>
+        <v>4874</v>
       </c>
       <c r="F1498" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G1498" t="n">
         <v>0</v>
@@ -80078,21 +80086,21 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>TIJERA DE DOBLAR METALICA</t>
+          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
         </is>
       </c>
       <c r="C1499" t="inlineStr"/>
       <c r="D1499" t="inlineStr"/>
       <c r="E1499" t="n">
-        <v>3500</v>
+        <v>28800</v>
       </c>
       <c r="F1499" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1499" t="n">
         <v>0</v>
@@ -80128,21 +80136,21 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
         </is>
       </c>
       <c r="C1500" t="inlineStr"/>
       <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="n">
-        <v>3781.512605</v>
+        <v>11596.638655</v>
       </c>
       <c r="F1500" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1500" t="n">
         <v>0</v>
@@ -80178,21 +80186,21 @@
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+          <t>TIJERA DE DOBLAR METALICA</t>
         </is>
       </c>
       <c r="C1501" t="inlineStr"/>
       <c r="D1501" t="inlineStr"/>
       <c r="E1501" t="n">
-        <v>29800</v>
+        <v>3500</v>
       </c>
       <c r="F1501" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1501" t="n">
         <v>0</v>
@@ -80228,22 +80236,18 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
-        </is>
-      </c>
-      <c r="C1502" t="inlineStr">
-        <is>
-          <t>7702026149567</t>
-        </is>
-      </c>
+          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr"/>
       <c r="D1502" t="inlineStr"/>
       <c r="E1502" t="n">
-        <v>13500</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1502" t="n">
         <v>2</v>
@@ -80274,7 +80278,7 @@
       </c>
       <c r="M1502" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1502" t="inlineStr"/>
@@ -80282,25 +80286,21 @@
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>Toallas húmedas winny 24unidades</t>
-        </is>
-      </c>
-      <c r="C1503" t="inlineStr">
-        <is>
-          <t>7701021143655</t>
-        </is>
-      </c>
+          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr"/>
       <c r="D1503" t="inlineStr"/>
       <c r="E1503" t="n">
-        <v>4033.613445</v>
+        <v>29800</v>
       </c>
       <c r="F1503" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G1503" t="n">
         <v>0</v>
@@ -80328,7 +80328,7 @@
       </c>
       <c r="M1503" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1503" t="inlineStr"/>
@@ -80336,25 +80336,25 @@
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>Toallas maternas maternity</t>
+          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
         </is>
       </c>
       <c r="C1504" t="inlineStr">
         <is>
-          <t>7703252489526</t>
+          <t>7702026149567</t>
         </is>
       </c>
       <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="n">
-        <v>16900</v>
+        <v>13500</v>
       </c>
       <c r="F1504" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1504" t="n">
         <v>0</v>
@@ -80390,25 +80390,25 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>Toallas Nosotras Rapigel x Und</t>
+          <t>Toallas húmedas winny 24unidades</t>
         </is>
       </c>
       <c r="C1505" t="inlineStr">
         <is>
-          <t>7702027416859</t>
+          <t>7701021143655</t>
         </is>
       </c>
       <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="n">
-        <v>756.302521</v>
+        <v>4033.613445</v>
       </c>
       <c r="F1505" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="G1505" t="n">
         <v>0</v>
@@ -80444,21 +80444,25 @@
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>TRAMADOL 50MG CAPSULA MP</t>
-        </is>
-      </c>
-      <c r="C1506" t="inlineStr"/>
+          <t>Toallas maternas maternity</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>7703252489526</t>
+        </is>
+      </c>
       <c r="D1506" t="inlineStr"/>
       <c r="E1506" t="n">
-        <v>1500</v>
+        <v>16900</v>
       </c>
       <c r="F1506" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G1506" t="n">
         <v>0</v>
@@ -80494,25 +80498,25 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>Tramadol clorhidrato 100mg laquifar</t>
+          <t>Toallas Nosotras Rapigel x Und</t>
         </is>
       </c>
       <c r="C1507" t="inlineStr">
         <is>
-          <t>7707019426977</t>
+          <t>7702027416859</t>
         </is>
       </c>
       <c r="D1507" t="inlineStr"/>
       <c r="E1507" t="n">
-        <v>1600</v>
+        <v>756.302521</v>
       </c>
       <c r="F1507" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G1507" t="n">
         <v>0</v>
@@ -80540,7 +80544,7 @@
       </c>
       <c r="M1507" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1507" t="inlineStr"/>
@@ -80548,21 +80552,21 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>TRIGENTAX CREMA TBO X 20GR</t>
+          <t>TRAMADOL 50MG CAPSULA MP</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr"/>
       <c r="D1508" t="inlineStr"/>
       <c r="E1508" t="n">
-        <v>33500</v>
+        <v>1500</v>
       </c>
       <c r="F1508" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G1508" t="n">
         <v>0</v>
@@ -80598,21 +80602,25 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
-        </is>
-      </c>
-      <c r="C1509" t="inlineStr"/>
+          <t>Tramadol clorhidrato 100mg laquifar</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>7707019426977</t>
+        </is>
+      </c>
       <c r="D1509" t="inlineStr"/>
       <c r="E1509" t="n">
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="F1509" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1509" t="n">
         <v>0</v>
@@ -80648,21 +80656,21 @@
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
+          <t>TRIGENTAX CREMA TBO X 20GR</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr"/>
       <c r="D1510" t="inlineStr"/>
       <c r="E1510" t="n">
-        <v>10500</v>
+        <v>33500</v>
       </c>
       <c r="F1510" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1510" t="n">
         <v>0</v>
@@ -80698,21 +80706,21 @@
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
+          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
         </is>
       </c>
       <c r="C1511" t="inlineStr"/>
       <c r="D1511" t="inlineStr"/>
       <c r="E1511" t="n">
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="F1511" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G1511" t="n">
         <v>0</v>
@@ -80748,21 +80756,21 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
+          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
         </is>
       </c>
       <c r="C1512" t="inlineStr"/>
       <c r="D1512" t="inlineStr"/>
       <c r="E1512" t="n">
-        <v>18800</v>
+        <v>10500</v>
       </c>
       <c r="F1512" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1512" t="n">
         <v>0</v>
@@ -80798,21 +80806,21 @@
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
+          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
         </is>
       </c>
       <c r="C1513" t="inlineStr"/>
       <c r="D1513" t="inlineStr"/>
       <c r="E1513" t="n">
-        <v>13800</v>
+        <v>10500</v>
       </c>
       <c r="F1513" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G1513" t="n">
         <v>0</v>
@@ -80848,21 +80856,21 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
+          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
         </is>
       </c>
       <c r="C1514" t="inlineStr"/>
       <c r="D1514" t="inlineStr"/>
       <c r="E1514" t="n">
-        <v>7900</v>
+        <v>18800</v>
       </c>
       <c r="F1514" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1514" t="n">
         <v>0</v>
@@ -80898,21 +80906,21 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>VASELINA FC X 200GR YOMA</t>
+          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
         </is>
       </c>
       <c r="C1515" t="inlineStr"/>
       <c r="D1515" t="inlineStr"/>
       <c r="E1515" t="n">
-        <v>12521.008403</v>
+        <v>13800</v>
       </c>
       <c r="F1515" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1515" t="n">
         <v>0</v>
@@ -80940,7 +80948,7 @@
       </c>
       <c r="M1515" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1515" t="inlineStr"/>
@@ -80948,21 +80956,21 @@
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
+          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
         </is>
       </c>
       <c r="C1516" t="inlineStr"/>
       <c r="D1516" t="inlineStr"/>
       <c r="E1516" t="n">
-        <v>420.168067</v>
+        <v>7900</v>
       </c>
       <c r="F1516" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1516" t="n">
         <v>0</v>
@@ -80990,7 +80998,7 @@
       </c>
       <c r="M1516" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1516" t="inlineStr"/>
@@ -80998,22 +81006,18 @@
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
-        </is>
-      </c>
-      <c r="C1517" t="inlineStr">
-        <is>
-          <t>7708480649803</t>
-        </is>
-      </c>
+          <t>VASELINA FC X 200GR YOMA</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr"/>
       <c r="D1517" t="inlineStr"/>
       <c r="E1517" t="n">
-        <v>28000</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1517" t="n">
         <v>0</v>
@@ -81044,7 +81048,7 @@
       </c>
       <c r="M1517" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1517" t="inlineStr"/>
@@ -81052,25 +81056,21 @@
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>Venda Elastica 6x5 y piel</t>
+          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr"/>
-      <c r="D1518" t="inlineStr">
-        <is>
-          <t>SUBIO A 6200 ANTES 5700</t>
-        </is>
-      </c>
+      <c r="D1518" t="inlineStr"/>
       <c r="E1518" t="n">
-        <v>6200</v>
+        <v>420.168067</v>
       </c>
       <c r="F1518" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1518" t="n">
         <v>0</v>
@@ -81098,7 +81098,7 @@
       </c>
       <c r="M1518" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1518" t="inlineStr"/>
@@ -81106,21 +81106,25 @@
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
-        </is>
-      </c>
-      <c r="C1519" t="inlineStr"/>
+          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>7708480649803</t>
+        </is>
+      </c>
       <c r="D1519" t="inlineStr"/>
       <c r="E1519" t="n">
-        <v>5500</v>
+        <v>28000</v>
       </c>
       <c r="F1519" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1519" t="n">
         <v>0</v>
@@ -81156,21 +81160,25 @@
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>Venta simple</t>
+          <t>Venda Elastica 6x5 y piel</t>
         </is>
       </c>
       <c r="C1520" t="inlineStr"/>
-      <c r="D1520" t="inlineStr"/>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>SUBIO A 6200 ANTES 5700</t>
+        </is>
+      </c>
       <c r="E1520" t="n">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="F1520" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1520" t="n">
         <v>0</v>
@@ -81188,7 +81196,7 @@
       </c>
       <c r="K1520" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="L1520" t="inlineStr">
@@ -81196,24 +81204,28 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1520" t="inlineStr"/>
+      <c r="M1520" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1520" t="inlineStr"/>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
+          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
         </is>
       </c>
       <c r="C1521" t="inlineStr"/>
       <c r="D1521" t="inlineStr"/>
       <c r="E1521" t="n">
-        <v>1000</v>
+        <v>5500</v>
       </c>
       <c r="F1521" t="n">
         <v>3</v>
@@ -81252,25 +81264,21 @@
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
-        </is>
-      </c>
-      <c r="C1522" t="inlineStr">
-        <is>
-          <t>793969226467</t>
-        </is>
-      </c>
+          <t>Venta simple</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr"/>
       <c r="D1522" t="inlineStr"/>
       <c r="E1522" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="F1522" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1522" t="n">
         <v>0</v>
@@ -81288,39 +81296,35 @@
       </c>
       <c r="K1522" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="L1522" t="inlineStr">
         <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="M1522" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1522" t="inlineStr"/>
       <c r="N1522" t="inlineStr"/>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>VINO CEREBRAL JARABE X 1100ML</t>
+          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
         </is>
       </c>
       <c r="C1523" t="inlineStr"/>
       <c r="D1523" t="inlineStr"/>
       <c r="E1523" t="n">
-        <v>48900</v>
+        <v>1000</v>
       </c>
       <c r="F1523" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1523" t="n">
         <v>0</v>
@@ -81356,21 +81360,25 @@
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
-        </is>
-      </c>
-      <c r="C1524" t="inlineStr"/>
+          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>793969226467</t>
+        </is>
+      </c>
       <c r="D1524" t="inlineStr"/>
       <c r="E1524" t="n">
-        <v>5400</v>
+        <v>17000</v>
       </c>
       <c r="F1524" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G1524" t="n">
         <v>0</v>
@@ -81393,7 +81401,7 @@
       </c>
       <c r="L1524" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="M1524" t="inlineStr">
@@ -81406,21 +81414,21 @@
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
+          <t>VINO CEREBRAL JARABE X 1100ML</t>
         </is>
       </c>
       <c r="C1525" t="inlineStr"/>
       <c r="D1525" t="inlineStr"/>
       <c r="E1525" t="n">
-        <v>5500</v>
+        <v>48900</v>
       </c>
       <c r="F1525" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G1525" t="n">
         <v>0</v>
@@ -81456,21 +81464,21 @@
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>WINNY PAÑAL ETP 6 X 30</t>
+          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
         </is>
       </c>
       <c r="C1526" t="inlineStr"/>
       <c r="D1526" t="inlineStr"/>
       <c r="E1526" t="n">
-        <v>57000</v>
+        <v>5400</v>
       </c>
       <c r="F1526" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G1526" t="n">
         <v>0</v>
@@ -81506,52 +81514,152 @@
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>YODO BLANCO FC X30ML</t>
+          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
         </is>
       </c>
       <c r="C1527" t="inlineStr"/>
       <c r="D1527" t="inlineStr"/>
       <c r="E1527" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F1527" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1527" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1527" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1527" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1527" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1527" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1527" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1527" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1527" t="inlineStr"/>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>WINNY PAÑAL ETP 6 X 30</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr"/>
+      <c r="D1528" t="inlineStr"/>
+      <c r="E1528" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F1528" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1528" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1528" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1528" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1528" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1528" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1528" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1528" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1528" t="inlineStr"/>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>YODO BLANCO FC X30ML</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr"/>
+      <c r="D1529" t="inlineStr"/>
+      <c r="E1529" t="n">
         <v>6000</v>
       </c>
-      <c r="F1527" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1527" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1527" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1527" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1527" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="K1527" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="L1527" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="M1527" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="N1527" t="inlineStr"/>
+      <c r="F1529" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1529" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1529" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1529" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1529" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1529" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1529" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1529" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1529" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1529"/>
+  <dimension ref="A1:N1532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68874,21 +68874,25 @@
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>CERA EGO POTE X 60ML</t>
-        </is>
-      </c>
-      <c r="C1281" t="inlineStr"/>
+          <t>CEPILLO NIÑO KIDS VERDE MEDIO</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>6971831832020</t>
+        </is>
+      </c>
       <c r="D1281" t="inlineStr"/>
       <c r="E1281" t="n">
-        <v>6800</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1281" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1281" t="n">
         <v>0</v>
@@ -68916,7 +68920,7 @@
       </c>
       <c r="M1281" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1281" t="inlineStr"/>
@@ -68924,21 +68928,21 @@
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>CERA PROQUIDENT ORTD</t>
+          <t>CERA EGO POTE X 60ML</t>
         </is>
       </c>
       <c r="C1282" t="inlineStr"/>
       <c r="D1282" t="inlineStr"/>
       <c r="E1282" t="n">
-        <v>6554.621849</v>
+        <v>6800</v>
       </c>
       <c r="F1282" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1282" t="n">
         <v>0</v>
@@ -68966,7 +68970,7 @@
       </c>
       <c r="M1282" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1282" t="inlineStr"/>
@@ -68974,21 +68978,21 @@
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>CHA-P JARABE ARMONIZA 500ML</t>
+          <t>CERA PROQUIDENT ORTD</t>
         </is>
       </c>
       <c r="C1283" t="inlineStr"/>
       <c r="D1283" t="inlineStr"/>
       <c r="E1283" t="n">
-        <v>38000</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1283" t="n">
         <v>0</v>
@@ -69016,7 +69020,7 @@
       </c>
       <c r="M1283" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1283" t="inlineStr"/>
@@ -69024,21 +69028,21 @@
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>CHAPSTICK LABIAL CEREZA</t>
+          <t>CHA-P JARABE ARMONIZA 500ML</t>
         </is>
       </c>
       <c r="C1284" t="inlineStr"/>
       <c r="D1284" t="inlineStr"/>
       <c r="E1284" t="n">
-        <v>17563.02521</v>
+        <v>38000</v>
       </c>
       <c r="F1284" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1284" t="n">
         <v>0</v>
@@ -69066,7 +69070,7 @@
       </c>
       <c r="M1284" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1284" t="inlineStr"/>
@@ -69074,21 +69078,21 @@
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>CHICLE TRIDENT SURTIDOS SABORES X PAQUE</t>
+          <t>CHAPSTICK LABIAL CEREZA</t>
         </is>
       </c>
       <c r="C1285" t="inlineStr"/>
       <c r="D1285" t="inlineStr"/>
       <c r="E1285" t="n">
-        <v>2016.806723</v>
+        <v>17563.02521</v>
       </c>
       <c r="F1285" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G1285" t="n">
         <v>0</v>
@@ -69124,21 +69128,21 @@
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>CHOCOLATINA JUMBO MANI 17GR X 1 UND</t>
+          <t>CHICLE TRIDENT SURTIDOS SABORES X PAQUE</t>
         </is>
       </c>
       <c r="C1286" t="inlineStr"/>
       <c r="D1286" t="inlineStr"/>
       <c r="E1286" t="n">
-        <v>1680.672269</v>
+        <v>2016.806723</v>
       </c>
       <c r="F1286" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G1286" t="n">
         <v>0</v>
@@ -69174,21 +69178,21 @@
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>CHUPO SILICONA GRANDE</t>
+          <t>CHOCOLATINA JUMBO MANI 17GR X 1 UND</t>
         </is>
       </c>
       <c r="C1287" t="inlineStr"/>
       <c r="D1287" t="inlineStr"/>
       <c r="E1287" t="n">
-        <v>4500</v>
+        <v>1680.672269</v>
       </c>
       <c r="F1287" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G1287" t="n">
         <v>0</v>
@@ -69216,7 +69220,7 @@
       </c>
       <c r="M1287" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1287" t="inlineStr"/>
@@ -69224,21 +69228,21 @@
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>Cianocobalamina</t>
+          <t>CHUPO SILICONA GRANDE</t>
         </is>
       </c>
       <c r="C1288" t="inlineStr"/>
       <c r="D1288" t="inlineStr"/>
       <c r="E1288" t="n">
-        <v>6500</v>
+        <v>4500</v>
       </c>
       <c r="F1288" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1288" t="n">
         <v>0</v>
@@ -69274,25 +69278,21 @@
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>Cicaderm crema protector cutáneo 60gm NF</t>
-        </is>
-      </c>
-      <c r="C1289" t="inlineStr">
-        <is>
-          <t>7707173600091</t>
-        </is>
-      </c>
+          <t>Cianocobalamina</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr"/>
       <c r="D1289" t="inlineStr"/>
       <c r="E1289" t="n">
-        <v>57000</v>
+        <v>6500</v>
       </c>
       <c r="F1289" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1289" t="n">
         <v>0</v>
@@ -69328,25 +69328,25 @@
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>CINTA DE PAPEL QUIRURGICO HIPOALERGICO 1/2 PROLATEX</t>
+          <t>Cicaderm crema protector cutáneo 60gm NF</t>
         </is>
       </c>
       <c r="C1290" t="inlineStr">
         <is>
-          <t>7709414102654</t>
+          <t>7707173600091</t>
         </is>
       </c>
       <c r="D1290" t="inlineStr"/>
       <c r="E1290" t="n">
-        <v>6000</v>
+        <v>57000</v>
       </c>
       <c r="F1290" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1290" t="n">
         <v>0</v>
@@ -69382,18 +69382,22 @@
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Citrato de calcio / Vitamina D3 600 MG/400UI (1500MG) Granulos Caja x 15 Sobres</t>
-        </is>
-      </c>
-      <c r="C1291" t="inlineStr"/>
+          <t>CINTA DE PAPEL QUIRURGICO HIPOALERGICO 1/2 PROLATEX</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>7709414102654</t>
+        </is>
+      </c>
       <c r="D1291" t="inlineStr"/>
       <c r="E1291" t="n">
-        <v>53000</v>
+        <v>6000</v>
       </c>
       <c r="F1291" t="n">
         <v>0</v>
@@ -69432,21 +69436,21 @@
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>769</t>
         </is>
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>CLENOX 40MG 1J/PRELLE.</t>
+          <t>Citrato de calcio / Vitamina D3 600 MG/400UI (1500MG) Granulos Caja x 15 Sobres</t>
         </is>
       </c>
       <c r="C1292" t="inlineStr"/>
       <c r="D1292" t="inlineStr"/>
       <c r="E1292" t="n">
-        <v>17800</v>
+        <v>53000</v>
       </c>
       <c r="F1292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1292" t="n">
         <v>0</v>
@@ -69482,25 +69486,21 @@
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>CLINBAC CLINDAMICINA 300MG CAPS</t>
-        </is>
-      </c>
-      <c r="C1293" t="inlineStr">
-        <is>
-          <t>7707019413816</t>
-        </is>
-      </c>
+          <t>CLENOX 40MG 1J/PRELLE.</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr"/>
       <c r="D1293" t="inlineStr"/>
       <c r="E1293" t="n">
-        <v>19200</v>
+        <v>17800</v>
       </c>
       <c r="F1293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1293" t="n">
         <v>0</v>
@@ -69536,21 +69536,25 @@
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>CLINDABACT CLOTRI+CLIND CJA X 3 OVULOS</t>
-        </is>
-      </c>
-      <c r="C1294" t="inlineStr"/>
+          <t>CLINBAC CLINDAMICINA 300MG CAPS</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>7707019413816</t>
+        </is>
+      </c>
       <c r="D1294" t="inlineStr"/>
       <c r="E1294" t="n">
-        <v>35700</v>
+        <v>19200</v>
       </c>
       <c r="F1294" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1294" t="n">
         <v>0</v>
@@ -69586,25 +69590,21 @@
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>CLOBETASOL 0,05% TRIDIRTEX CREMA X 40GR</t>
-        </is>
-      </c>
-      <c r="C1295" t="inlineStr">
-        <is>
-          <t>7709740450351</t>
-        </is>
-      </c>
+          <t>CLINDABACT CLOTRI+CLIND CJA X 3 OVULOS</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr"/>
       <c r="D1295" t="inlineStr"/>
       <c r="E1295" t="n">
-        <v>27900</v>
+        <v>35700</v>
       </c>
       <c r="F1295" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1295" t="n">
         <v>0</v>
@@ -69640,25 +69640,25 @@
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>Clotrimazol 1% 40gr AG</t>
+          <t>CLOBETASOL 0,05% TRIDIRTEX CREMA X 40GR</t>
         </is>
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>7706569001191</t>
+          <t>7709740450351</t>
         </is>
       </c>
       <c r="D1296" t="inlineStr"/>
       <c r="E1296" t="n">
-        <v>19000</v>
+        <v>27900</v>
       </c>
       <c r="F1296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1296" t="n">
         <v>0</v>
@@ -69694,25 +69694,25 @@
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>CLOTRIMAZOL 1% CREMA TOPICA DE VITALIS</t>
+          <t>Clotrimazol 1% 40gr AG</t>
         </is>
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>7709990212204</t>
+          <t>7706569001191</t>
         </is>
       </c>
       <c r="D1297" t="inlineStr"/>
       <c r="E1297" t="n">
-        <v>14500</v>
+        <v>19000</v>
       </c>
       <c r="F1297" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1297" t="n">
         <v>0</v>
@@ -69748,21 +69748,25 @@
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>COLAGENO HIDROLIZADO EN POLVO 700GR ARMONIZA</t>
-        </is>
-      </c>
-      <c r="C1298" t="inlineStr"/>
+          <t>CLOTRIMAZOL 1% CREMA TOPICA DE VITALIS</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>7709990212204</t>
+        </is>
+      </c>
       <c r="D1298" t="inlineStr"/>
       <c r="E1298" t="n">
-        <v>56000</v>
+        <v>14500</v>
       </c>
       <c r="F1298" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1298" t="n">
         <v>0</v>
@@ -69798,21 +69802,21 @@
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>Colchicina Coas</t>
+          <t>COLAGENO HIDROLIZADO EN POLVO 700GR ARMONIZA</t>
         </is>
       </c>
       <c r="C1299" t="inlineStr"/>
       <c r="D1299" t="inlineStr"/>
       <c r="E1299" t="n">
-        <v>3900</v>
+        <v>56000</v>
       </c>
       <c r="F1299" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1299" t="n">
         <v>0</v>
@@ -69848,18 +69852,18 @@
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>CONDON DUO LUBRICADO X 3 UND</t>
+          <t>Colchicina Coas</t>
         </is>
       </c>
       <c r="C1300" t="inlineStr"/>
       <c r="D1300" t="inlineStr"/>
       <c r="E1300" t="n">
-        <v>16500</v>
+        <v>3900</v>
       </c>
       <c r="F1300" t="n">
         <v>1</v>
@@ -69898,18 +69902,18 @@
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
+          <t>CONDON DUO LUBRICADO X 3 UND</t>
         </is>
       </c>
       <c r="C1301" t="inlineStr"/>
       <c r="D1301" t="inlineStr"/>
       <c r="E1301" t="n">
-        <v>8900</v>
+        <v>16500</v>
       </c>
       <c r="F1301" t="n">
         <v>1</v>
@@ -69948,7 +69952,7 @@
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="B1302" t="inlineStr">
@@ -69962,7 +69966,7 @@
         <v>8900</v>
       </c>
       <c r="F1302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1302" t="n">
         <v>0</v>
@@ -69998,12 +70002,12 @@
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>CONDON PIEL SABORES CJA X 3 UNDS</t>
+          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
         </is>
       </c>
       <c r="C1303" t="inlineStr"/>
@@ -70048,25 +70052,21 @@
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>CONDON PRUDENCE EFEC.RETARDX3UNDS</t>
-        </is>
-      </c>
-      <c r="C1304" t="inlineStr">
-        <is>
-          <t>77309632510504387</t>
-        </is>
-      </c>
+          <t>CONDON PIEL SABORES CJA X 3 UNDS</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr"/>
       <c r="D1304" t="inlineStr"/>
       <c r="E1304" t="n">
-        <v>12200</v>
+        <v>8900</v>
       </c>
       <c r="F1304" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1304" t="n">
         <v>0</v>
@@ -70102,25 +70102,25 @@
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>CONDON PRUDENCE EXTRA GRANDE ULT SENSIBX3UND</t>
+          <t>CONDON PRUDENCE EFEC.RETARDX3UNDS</t>
         </is>
       </c>
       <c r="C1305" t="inlineStr">
         <is>
-          <t>7730963250343</t>
+          <t>77309632510504387</t>
         </is>
       </c>
       <c r="D1305" t="inlineStr"/>
       <c r="E1305" t="n">
-        <v>13800</v>
+        <v>12200</v>
       </c>
       <c r="F1305" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1305" t="n">
         <v>0</v>
@@ -70156,25 +70156,25 @@
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>CONTENT MEDICAL PAÑAL TALLA L X UND</t>
-        </is>
-      </c>
-      <c r="C1306" t="inlineStr"/>
-      <c r="D1306" t="inlineStr">
-        <is>
-          <t>pañal adulto no paga iva articulo 424</t>
-        </is>
-      </c>
+          <t>CONDON PRUDENCE EXTRA GRANDE ULT SENSIBX3UND</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>7730963250343</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr"/>
       <c r="E1306" t="n">
-        <v>4800</v>
+        <v>13800</v>
       </c>
       <c r="F1306" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G1306" t="n">
         <v>0</v>
@@ -70210,21 +70210,25 @@
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>CONTENT MEDICAL PAÑAL TALLA M X UND</t>
+          <t>CONTENT MEDICAL PAÑAL TALLA L X UND</t>
         </is>
       </c>
       <c r="C1307" t="inlineStr"/>
-      <c r="D1307" t="inlineStr"/>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>pañal adulto no paga iva articulo 424</t>
+        </is>
+      </c>
       <c r="E1307" t="n">
-        <v>3697.478992</v>
+        <v>4800</v>
       </c>
       <c r="F1307" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G1307" t="n">
         <v>0</v>
@@ -70252,7 +70256,7 @@
       </c>
       <c r="M1307" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1307" t="inlineStr"/>
@@ -70260,21 +70264,21 @@
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 100 UNDS</t>
+          <t>CONTENT MEDICAL PAÑAL TALLA M X UND</t>
         </is>
       </c>
       <c r="C1308" t="inlineStr"/>
       <c r="D1308" t="inlineStr"/>
       <c r="E1308" t="n">
-        <v>8500</v>
+        <v>3697.478992</v>
       </c>
       <c r="F1308" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G1308" t="n">
         <v>0</v>
@@ -70302,7 +70306,7 @@
       </c>
       <c r="M1308" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1308" t="inlineStr"/>
@@ -70310,18 +70314,18 @@
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 50 UNDS</t>
+          <t>COPITOS YOKY X 100 UNDS</t>
         </is>
       </c>
       <c r="C1309" t="inlineStr"/>
       <c r="D1309" t="inlineStr"/>
       <c r="E1309" t="n">
-        <v>6400</v>
+        <v>8500</v>
       </c>
       <c r="F1309" t="n">
         <v>3</v>
@@ -70360,21 +70364,21 @@
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 60 UNDS</t>
+          <t>COPITOS YOKY X 50 UNDS</t>
         </is>
       </c>
       <c r="C1310" t="inlineStr"/>
       <c r="D1310" t="inlineStr"/>
       <c r="E1310" t="n">
-        <v>7142.857143</v>
+        <v>6400</v>
       </c>
       <c r="F1310" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1310" t="n">
         <v>0</v>
@@ -70402,7 +70406,7 @@
       </c>
       <c r="M1310" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1310" t="inlineStr"/>
@@ -70410,21 +70414,21 @@
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>CORTA CUTICULA TRIM METALICO</t>
+          <t>COPITOS YOKY X 60 UNDS</t>
         </is>
       </c>
       <c r="C1311" t="inlineStr"/>
       <c r="D1311" t="inlineStr"/>
       <c r="E1311" t="n">
-        <v>16000</v>
+        <v>7142.857143</v>
       </c>
       <c r="F1311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1311" t="n">
         <v>0</v>
@@ -70452,7 +70456,7 @@
       </c>
       <c r="M1311" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1311" t="inlineStr"/>
@@ -70460,21 +70464,21 @@
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>CREMA ARNICA PROTECTORA 12GR ICE POWER</t>
+          <t>CORTA CUTICULA TRIM METALICO</t>
         </is>
       </c>
       <c r="C1312" t="inlineStr"/>
       <c r="D1312" t="inlineStr"/>
       <c r="E1312" t="n">
-        <v>10084.033613</v>
+        <v>16000</v>
       </c>
       <c r="F1312" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1312" t="n">
         <v>0</v>
@@ -70502,7 +70506,7 @@
       </c>
       <c r="M1312" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1312" t="inlineStr"/>
@@ -70510,21 +70514,21 @@
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>CREMA BENLIC DE 40GR</t>
+          <t>CREMA ARNICA PROTECTORA 12GR ICE POWER</t>
         </is>
       </c>
       <c r="C1313" t="inlineStr"/>
       <c r="D1313" t="inlineStr"/>
       <c r="E1313" t="n">
-        <v>28900</v>
+        <v>10084.033613</v>
       </c>
       <c r="F1313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1313" t="n">
         <v>0</v>
@@ -70552,7 +70556,7 @@
       </c>
       <c r="M1313" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1313" t="inlineStr"/>
@@ -70560,18 +70564,18 @@
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>CREMA CASTAÑO DE INDIAS X 12GR ARMONIZA</t>
+          <t>CREMA BENLIC DE 40GR</t>
         </is>
       </c>
       <c r="C1314" t="inlineStr"/>
       <c r="D1314" t="inlineStr"/>
       <c r="E1314" t="n">
-        <v>9000</v>
+        <v>28900</v>
       </c>
       <c r="F1314" t="n">
         <v>1</v>
@@ -70610,25 +70614,21 @@
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>Crema Colgate triple acción xtra blancura 60ml</t>
-        </is>
-      </c>
-      <c r="C1315" t="inlineStr">
-        <is>
-          <t>7702010111587</t>
-        </is>
-      </c>
+          <t>CREMA CASTAÑO DE INDIAS X 12GR ARMONIZA</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr"/>
       <c r="D1315" t="inlineStr"/>
       <c r="E1315" t="n">
-        <v>5630.252101</v>
+        <v>9000</v>
       </c>
       <c r="F1315" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1315" t="n">
         <v>0</v>
@@ -70656,7 +70656,7 @@
       </c>
       <c r="M1315" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1315" t="inlineStr"/>
@@ -70664,21 +70664,25 @@
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>CREMA PONDS CLARANT B3 X SACHETS</t>
-        </is>
-      </c>
-      <c r="C1316" t="inlineStr"/>
+          <t>Crema Colgate triple acción xtra blancura 60ml</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>7702010111587</t>
+        </is>
+      </c>
       <c r="D1316" t="inlineStr"/>
       <c r="E1316" t="n">
-        <v>2521.008403</v>
+        <v>5630.252101</v>
       </c>
       <c r="F1316" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1316" t="n">
         <v>0</v>
@@ -70714,21 +70718,21 @@
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>CURAS LARGAS RESIST AL AGUA</t>
+          <t>CREMA PONDS CLARANT B3 X SACHETS</t>
         </is>
       </c>
       <c r="C1317" t="inlineStr"/>
       <c r="D1317" t="inlineStr"/>
       <c r="E1317" t="n">
-        <v>300</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1317" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="G1317" t="n">
         <v>0</v>
@@ -70756,7 +70760,7 @@
       </c>
       <c r="M1317" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1317" t="inlineStr"/>
@@ -70764,25 +70768,21 @@
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>CYCLOFEM AMPOLLA INYECTABLE .PROFAMILIA</t>
-        </is>
-      </c>
-      <c r="C1318" t="inlineStr">
-        <is>
-          <t>7703689000448</t>
-        </is>
-      </c>
+          <t>CURAS LARGAS RESIST AL AGUA</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr"/>
       <c r="D1318" t="inlineStr"/>
       <c r="E1318" t="n">
-        <v>28900</v>
+        <v>300</v>
       </c>
       <c r="F1318" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="G1318" t="n">
         <v>0</v>
@@ -70818,25 +70818,25 @@
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>CYCLOFEMINA AMPOLLA 0.5ML</t>
+          <t>CYCLOFEM AMPOLLA INYECTABLE .PROFAMILIA</t>
         </is>
       </c>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>7707271451410</t>
+          <t>7703689000448</t>
         </is>
       </c>
       <c r="D1319" t="inlineStr"/>
       <c r="E1319" t="n">
-        <v>33900</v>
+        <v>28900</v>
       </c>
       <c r="F1319" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1319" t="n">
         <v>0</v>
@@ -70872,25 +70872,25 @@
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>Desonida bussie 0.1% crema 15gr</t>
+          <t>CYCLOFEMINA AMPOLLA 0.5ML</t>
         </is>
       </c>
       <c r="C1320" t="inlineStr">
         <is>
-          <t>7702195210587</t>
+          <t>7707271451410</t>
         </is>
       </c>
       <c r="D1320" t="inlineStr"/>
       <c r="E1320" t="n">
-        <v>19000</v>
+        <v>33900</v>
       </c>
       <c r="F1320" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1320" t="n">
         <v>0</v>
@@ -70926,25 +70926,25 @@
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>Diclofenaco gel vitalis 50gr</t>
+          <t>Desonida bussie 0.1% crema 15gr</t>
         </is>
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>7709141546059</t>
+          <t>7702195210587</t>
         </is>
       </c>
       <c r="D1321" t="inlineStr"/>
       <c r="E1321" t="n">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="F1321" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1321" t="n">
         <v>0</v>
@@ -70970,31 +70970,35 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1321" t="inlineStr"/>
+      <c r="M1321" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1321" t="inlineStr"/>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>Diclofenaco sódico 100mg +hidróxido de aluminio200mg colmed</t>
+          <t>Diclofenaco gel vitalis 50gr</t>
         </is>
       </c>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>7703153020286</t>
+          <t>7709141546059</t>
         </is>
       </c>
       <c r="D1322" t="inlineStr"/>
       <c r="E1322" t="n">
-        <v>19200</v>
+        <v>16000</v>
       </c>
       <c r="F1322" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1322" t="n">
         <v>0</v>
@@ -71020,31 +71024,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1322" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1322" t="inlineStr"/>
       <c r="N1322" t="inlineStr"/>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>DICLOFENACOXUND75MG/3MLAMPCOMERCIAL VITALIS</t>
-        </is>
-      </c>
-      <c r="C1323" t="inlineStr"/>
+          <t>Diclofenaco sódico 100mg +hidróxido de aluminio200mg colmed</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>7703153020286</t>
+        </is>
+      </c>
       <c r="D1323" t="inlineStr"/>
       <c r="E1323" t="n">
-        <v>5500</v>
+        <v>19200</v>
       </c>
       <c r="F1323" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1323" t="n">
         <v>0</v>
@@ -71080,18 +71084,18 @@
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>DIFENZ DESPIGMENTADOR CREMA TUBO X 1 UND</t>
+          <t>DICLOFENACOXUND75MG/3MLAMPCOMERCIAL VITALIS</t>
         </is>
       </c>
       <c r="C1324" t="inlineStr"/>
       <c r="D1324" t="inlineStr"/>
       <c r="E1324" t="n">
-        <v>163300</v>
+        <v>5500</v>
       </c>
       <c r="F1324" t="n">
         <v>1</v>
@@ -71130,25 +71134,21 @@
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>DIOSMINA HESPERIDINA 450MG 50MG GENFAR</t>
-        </is>
-      </c>
-      <c r="C1325" t="inlineStr">
-        <is>
-          <t>7705959013370</t>
-        </is>
-      </c>
+          <t>DIFENZ DESPIGMENTADOR CREMA TUBO X 1 UND</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr"/>
       <c r="D1325" t="inlineStr"/>
       <c r="E1325" t="n">
-        <v>42000</v>
+        <v>163300</v>
       </c>
       <c r="F1325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1325" t="n">
         <v>0</v>
@@ -71184,18 +71184,22 @@
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>DIPIORNA 500MG TABLETA X 10 DE ECAR</t>
-        </is>
-      </c>
-      <c r="C1326" t="inlineStr"/>
+          <t>DIOSMINA HESPERIDINA 450MG 50MG GENFAR</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>7705959013370</t>
+        </is>
+      </c>
       <c r="D1326" t="inlineStr"/>
       <c r="E1326" t="n">
-        <v>7900</v>
+        <v>42000</v>
       </c>
       <c r="F1326" t="n">
         <v>0</v>
@@ -71234,12 +71238,12 @@
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>DIPIRONA 500MG TABLETA X 10 DE ECAR</t>
+          <t>DIPIORNA 500MG TABLETA X 10 DE ECAR</t>
         </is>
       </c>
       <c r="C1327" t="inlineStr"/>
@@ -71248,7 +71252,7 @@
         <v>7900</v>
       </c>
       <c r="F1327" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1327" t="n">
         <v>0</v>
@@ -71284,21 +71288,21 @@
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>DOMICILIO</t>
+          <t>DIPIRONA 500MG TABLETA X 10 DE ECAR</t>
         </is>
       </c>
       <c r="C1328" t="inlineStr"/>
       <c r="D1328" t="inlineStr"/>
       <c r="E1328" t="n">
-        <v>3000</v>
+        <v>7900</v>
       </c>
       <c r="F1328" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1328" t="n">
         <v>0</v>
@@ -71324,27 +71328,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1328" t="inlineStr"/>
+      <c r="M1328" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1328" t="inlineStr"/>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>DOXICICLINA 100MG X 10 TABL GENFAR</t>
+          <t>DOMICILIO</t>
         </is>
       </c>
       <c r="C1329" t="inlineStr"/>
       <c r="D1329" t="inlineStr"/>
       <c r="E1329" t="n">
-        <v>12000</v>
+        <v>3000</v>
       </c>
       <c r="F1329" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1329" t="n">
         <v>0</v>
@@ -71370,31 +71378,27 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1329" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1329" t="inlineStr"/>
       <c r="N1329" t="inlineStr"/>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>DUCHA INTIMA DESECHABLE VINAGRE</t>
+          <t>DOXICICLINA 100MG X 10 TABL GENFAR</t>
         </is>
       </c>
       <c r="C1330" t="inlineStr"/>
       <c r="D1330" t="inlineStr"/>
       <c r="E1330" t="n">
-        <v>24800</v>
+        <v>12000</v>
       </c>
       <c r="F1330" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1330" t="n">
         <v>0</v>
@@ -71430,25 +71434,21 @@
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>E ala proel maléate 20mg medicbrand</t>
-        </is>
-      </c>
-      <c r="C1331" t="inlineStr">
-        <is>
-          <t>7703712035997</t>
-        </is>
-      </c>
+          <t>DUCHA INTIMA DESECHABLE VINAGRE</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr"/>
       <c r="D1331" t="inlineStr"/>
       <c r="E1331" t="n">
-        <v>1250</v>
+        <v>24800</v>
       </c>
       <c r="F1331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1331" t="n">
         <v>0</v>
@@ -71484,25 +71484,25 @@
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>Enalapril 20 mg MK</t>
+          <t>E ala proel maléate 20mg medicbrand</t>
         </is>
       </c>
       <c r="C1332" t="inlineStr">
         <is>
-          <t>7702057716578</t>
+          <t>7703712035997</t>
         </is>
       </c>
       <c r="D1332" t="inlineStr"/>
       <c r="E1332" t="n">
-        <v>4700</v>
+        <v>1250</v>
       </c>
       <c r="F1332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1332" t="n">
         <v>0</v>
@@ -71538,21 +71538,25 @@
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>ENALAPRIL 20MG TABLETA COAS</t>
-        </is>
-      </c>
-      <c r="C1333" t="inlineStr"/>
+          <t>Enalapril 20 mg MK</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>7702057716578</t>
+        </is>
+      </c>
       <c r="D1333" t="inlineStr"/>
       <c r="E1333" t="n">
-        <v>3000</v>
+        <v>4700</v>
       </c>
       <c r="F1333" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1333" t="n">
         <v>0</v>
@@ -71588,21 +71592,21 @@
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>ENSURE ADVANCE VAINILLA 400GR</t>
+          <t>ENALAPRIL 20MG TABLETA COAS</t>
         </is>
       </c>
       <c r="C1334" t="inlineStr"/>
       <c r="D1334" t="inlineStr"/>
       <c r="E1334" t="n">
-        <v>85900</v>
+        <v>3000</v>
       </c>
       <c r="F1334" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1334" t="n">
         <v>0</v>
@@ -71638,18 +71642,18 @@
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>ENTRETENEDOR BEBE</t>
+          <t>ENSURE ADVANCE VAINILLA 400GR</t>
         </is>
       </c>
       <c r="C1335" t="inlineStr"/>
       <c r="D1335" t="inlineStr"/>
       <c r="E1335" t="n">
-        <v>9000</v>
+        <v>85900</v>
       </c>
       <c r="F1335" t="n">
         <v>1</v>
@@ -71688,18 +71692,18 @@
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>ESMALTE BRILLO ACRILICO BRESCIA</t>
+          <t>ENTRETENEDOR BEBE</t>
         </is>
       </c>
       <c r="C1336" t="inlineStr"/>
       <c r="D1336" t="inlineStr"/>
       <c r="E1336" t="n">
-        <v>11500</v>
+        <v>9000</v>
       </c>
       <c r="F1336" t="n">
         <v>1</v>
@@ -71738,21 +71742,21 @@
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>ESOMEPRAZOL 20MG NOVAMED</t>
+          <t>ESMALTE BRILLO ACRILICO BRESCIA</t>
         </is>
       </c>
       <c r="C1337" t="inlineStr"/>
       <c r="D1337" t="inlineStr"/>
       <c r="E1337" t="n">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="F1337" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G1337" t="n">
         <v>0</v>
@@ -71788,21 +71792,21 @@
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>ESPASMOK HIOS +DIPIRO 5ML AMP BLASKOV</t>
+          <t>ESOMEPRAZOL 20MG NOVAMED</t>
         </is>
       </c>
       <c r="C1338" t="inlineStr"/>
       <c r="D1338" t="inlineStr"/>
       <c r="E1338" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="F1338" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G1338" t="n">
         <v>0</v>
@@ -71838,25 +71842,21 @@
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>ETORICOXIB 120MG GENFAR</t>
-        </is>
-      </c>
-      <c r="C1339" t="inlineStr">
-        <is>
-          <t>7702605109371</t>
-        </is>
-      </c>
+          <t>ESPASMOK HIOS +DIPIRO 5ML AMP BLASKOV</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr"/>
       <c r="D1339" t="inlineStr"/>
       <c r="E1339" t="n">
-        <v>48600</v>
+        <v>12000</v>
       </c>
       <c r="F1339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1339" t="n">
         <v>0</v>
@@ -71892,25 +71892,25 @@
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>EXTRACTOR DE LECHE MOBY</t>
+          <t>ETORICOXIB 120MG GENFAR</t>
         </is>
       </c>
       <c r="C1340" t="inlineStr">
         <is>
-          <t>7707233051436</t>
+          <t>7702605109371</t>
         </is>
       </c>
       <c r="D1340" t="inlineStr"/>
       <c r="E1340" t="n">
-        <v>14285.714286</v>
+        <v>48600</v>
       </c>
       <c r="F1340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1340" t="n">
         <v>0</v>
@@ -71938,7 +71938,7 @@
       </c>
       <c r="M1340" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1340" t="inlineStr"/>
@@ -71946,25 +71946,25 @@
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>FAMIIA MEGARROLLO PAPEL HIGUIEN</t>
+          <t>EXTRACTOR DE LECHE MOBY</t>
         </is>
       </c>
       <c r="C1341" t="inlineStr">
         <is>
-          <t>7702026147471</t>
+          <t>7707233051436</t>
         </is>
       </c>
       <c r="D1341" t="inlineStr"/>
       <c r="E1341" t="n">
-        <v>3500</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1341" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1341" t="n">
         <v>0</v>
@@ -71992,7 +71992,7 @@
       </c>
       <c r="M1341" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1341" t="inlineStr"/>
@@ -72000,21 +72000,25 @@
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>Farma D 500 UI</t>
-        </is>
-      </c>
-      <c r="C1342" t="inlineStr"/>
+          <t>FAMIIA MEGARROLLO PAPEL HIGUIEN</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>7702026147471</t>
+        </is>
+      </c>
       <c r="D1342" t="inlineStr"/>
       <c r="E1342" t="n">
-        <v>74000</v>
+        <v>3500</v>
       </c>
       <c r="F1342" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G1342" t="n">
         <v>0</v>
@@ -72050,21 +72054,21 @@
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>FIBRA AMARILLA ARMONIZA X 450GR</t>
+          <t>Farma D 500 UI</t>
         </is>
       </c>
       <c r="C1343" t="inlineStr"/>
       <c r="D1343" t="inlineStr"/>
       <c r="E1343" t="n">
-        <v>28571.428571</v>
+        <v>74000</v>
       </c>
       <c r="F1343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1343" t="n">
         <v>0</v>
@@ -72092,7 +72096,7 @@
       </c>
       <c r="M1343" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1343" t="inlineStr"/>
@@ -72100,21 +72104,21 @@
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>FIBRA DE AVENA Y SALVADO DE TRIGO 450GR</t>
+          <t>FIBRA AMARILLA ARMONIZA X 450GR</t>
         </is>
       </c>
       <c r="C1344" t="inlineStr"/>
       <c r="D1344" t="inlineStr"/>
       <c r="E1344" t="n">
-        <v>30000</v>
+        <v>28571.428571</v>
       </c>
       <c r="F1344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1344" t="n">
         <v>0</v>
@@ -72142,7 +72146,7 @@
       </c>
       <c r="M1344" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1344" t="inlineStr"/>
@@ -72150,21 +72154,21 @@
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>FITOSTIMONE 15% GEL</t>
+          <t>FIBRA DE AVENA Y SALVADO DE TRIGO 450GR</t>
         </is>
       </c>
       <c r="C1345" t="inlineStr"/>
       <c r="D1345" t="inlineStr"/>
       <c r="E1345" t="n">
-        <v>48900</v>
+        <v>30000</v>
       </c>
       <c r="F1345" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1345" t="n">
         <v>0</v>
@@ -72200,25 +72204,21 @@
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG CJA X 10 UND EXPORF</t>
-        </is>
-      </c>
-      <c r="C1346" t="inlineStr">
-        <is>
-          <t>7703432421681</t>
-        </is>
-      </c>
+          <t>FITOSTIMONE 15% GEL</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr"/>
       <c r="D1346" t="inlineStr"/>
       <c r="E1346" t="n">
-        <v>18300</v>
+        <v>48900</v>
       </c>
       <c r="F1346" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G1346" t="n">
         <v>0</v>
@@ -72254,21 +72254,25 @@
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1347" t="inlineStr"/>
+          <t>FLUCONAZOL 200MG CJA X 10 UND EXPORF</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>7703432421681</t>
+        </is>
+      </c>
       <c r="D1347" t="inlineStr"/>
       <c r="E1347" t="n">
-        <v>16900</v>
+        <v>18300</v>
       </c>
       <c r="F1347" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G1347" t="n">
         <v>0</v>
@@ -72304,25 +72308,21 @@
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS. LA SANTE</t>
-        </is>
-      </c>
-      <c r="C1348" t="inlineStr">
-        <is>
-          <t>7703763480166</t>
-        </is>
-      </c>
+          <t>FLUCONAZOL 200MG X 4 CAPS DE GENFAR</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr"/>
       <c r="D1348" t="inlineStr"/>
       <c r="E1348" t="n">
-        <v>14700</v>
+        <v>16900</v>
       </c>
       <c r="F1348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1348" t="n">
         <v>0</v>
@@ -72358,25 +72358,25 @@
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS.NOVAMED</t>
+          <t>FLUCONAZOL 200MG X 4 CAPS. LA SANTE</t>
         </is>
       </c>
       <c r="C1349" t="inlineStr">
         <is>
-          <t>7703546927468</t>
+          <t>7703763480166</t>
         </is>
       </c>
       <c r="D1349" t="inlineStr"/>
       <c r="E1349" t="n">
-        <v>10900</v>
+        <v>14700</v>
       </c>
       <c r="F1349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1349" t="n">
         <v>0</v>
@@ -72412,18 +72412,22 @@
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>Fluconazol Suspension</t>
-        </is>
-      </c>
-      <c r="C1350" t="inlineStr"/>
+          <t>FLUCONAZOL 200MG X 4 CAPS.NOVAMED</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>7703546927468</t>
+        </is>
+      </c>
       <c r="D1350" t="inlineStr"/>
       <c r="E1350" t="n">
-        <v>148000</v>
+        <v>10900</v>
       </c>
       <c r="F1350" t="n">
         <v>2</v>
@@ -72462,21 +72466,21 @@
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>FUNGI-FIN LOCION GOTAS TOPICA 20ML</t>
+          <t>Fluconazol Suspension</t>
         </is>
       </c>
       <c r="C1351" t="inlineStr"/>
       <c r="D1351" t="inlineStr"/>
       <c r="E1351" t="n">
-        <v>15966.386555</v>
+        <v>148000</v>
       </c>
       <c r="F1351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1351" t="n">
         <v>0</v>
@@ -72504,7 +72508,7 @@
       </c>
       <c r="M1351" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1351" t="inlineStr"/>
@@ -72512,21 +72516,21 @@
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>GALLETA OREO PAQUETE X 6 UNDS</t>
+          <t>FUNGI-FIN LOCION GOTAS TOPICA 20ML</t>
         </is>
       </c>
       <c r="C1352" t="inlineStr"/>
       <c r="D1352" t="inlineStr"/>
       <c r="E1352" t="n">
-        <v>1932.773109</v>
+        <v>15966.386555</v>
       </c>
       <c r="F1352" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1352" t="n">
         <v>0</v>
@@ -72562,21 +72566,21 @@
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>GASEOSA PREMIO 400ML ROJO</t>
+          <t>GALLETA OREO PAQUETE X 6 UNDS</t>
         </is>
       </c>
       <c r="C1353" t="inlineStr"/>
       <c r="D1353" t="inlineStr"/>
       <c r="E1353" t="n">
-        <v>2941.176471</v>
+        <v>1932.773109</v>
       </c>
       <c r="F1353" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G1353" t="n">
         <v>0</v>
@@ -72612,29 +72616,21 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>GASTROFAST ADVANCE</t>
-        </is>
-      </c>
-      <c r="C1354" t="inlineStr">
-        <is>
-          <t>7702057803254</t>
-        </is>
-      </c>
-      <c r="D1354" t="inlineStr">
-        <is>
-          <t>se subio A 3800 ANTES 3.600, LEYDI</t>
-        </is>
-      </c>
+          <t>GASEOSA PREMIO 400ML ROJO</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr"/>
+      <c r="D1354" t="inlineStr"/>
       <c r="E1354" t="n">
-        <v>3800</v>
+        <v>2941.176471</v>
       </c>
       <c r="F1354" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G1354" t="n">
         <v>0</v>
@@ -72662,7 +72658,7 @@
       </c>
       <c r="M1354" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1354" t="inlineStr"/>
@@ -72670,21 +72666,29 @@
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>GASTROFAST ADVANCE X 240 ML</t>
-        </is>
-      </c>
-      <c r="C1355" t="inlineStr"/>
-      <c r="D1355" t="inlineStr"/>
+          <t>GASTROFAST ADVANCE</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>7702057803254</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>se subio A 3800 ANTES 3.600, LEYDI</t>
+        </is>
+      </c>
       <c r="E1355" t="n">
-        <v>69500</v>
+        <v>3800</v>
       </c>
       <c r="F1355" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G1355" t="n">
         <v>0</v>
@@ -72720,25 +72724,21 @@
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>gatorade</t>
-        </is>
-      </c>
-      <c r="C1356" t="inlineStr">
-        <is>
-          <t>248656546</t>
-        </is>
-      </c>
+          <t>GASTROFAST ADVANCE X 240 ML</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr"/>
       <c r="D1356" t="inlineStr"/>
       <c r="E1356" t="n">
-        <v>3782</v>
+        <v>69500</v>
       </c>
       <c r="F1356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1356" t="n">
         <v>0</v>
@@ -72766,7 +72766,7 @@
       </c>
       <c r="M1356" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1356" t="inlineStr"/>
@@ -72774,21 +72774,25 @@
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>GEL BACHUE 150GR</t>
-        </is>
-      </c>
-      <c r="C1357" t="inlineStr"/>
+          <t>gatorade</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>248656546</t>
+        </is>
+      </c>
       <c r="D1357" t="inlineStr"/>
       <c r="E1357" t="n">
-        <v>8800</v>
+        <v>3782</v>
       </c>
       <c r="F1357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1357" t="n">
         <v>0</v>
@@ -72816,7 +72820,7 @@
       </c>
       <c r="M1357" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1357" t="inlineStr"/>
@@ -72824,21 +72828,21 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>GEMFIBROZILO 600 MG</t>
+          <t>GEL BACHUE 150GR</t>
         </is>
       </c>
       <c r="C1358" t="inlineStr"/>
       <c r="D1358" t="inlineStr"/>
       <c r="E1358" t="n">
-        <v>8300</v>
+        <v>8800</v>
       </c>
       <c r="F1358" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1358" t="n">
         <v>0</v>
@@ -72874,21 +72878,21 @@
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>GLICERINA CARBONATADA X 20ML FCO YOMA</t>
+          <t>GEMFIBROZILO 600 MG</t>
         </is>
       </c>
       <c r="C1359" t="inlineStr"/>
       <c r="D1359" t="inlineStr"/>
       <c r="E1359" t="n">
-        <v>3900</v>
+        <v>8300</v>
       </c>
       <c r="F1359" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1359" t="n">
         <v>0</v>
@@ -72924,21 +72928,21 @@
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
+          <t>GLICERINA CARBONATADA X 20ML FCO YOMA</t>
         </is>
       </c>
       <c r="C1360" t="inlineStr"/>
       <c r="D1360" t="inlineStr"/>
       <c r="E1360" t="n">
-        <v>3361.344538</v>
+        <v>3900</v>
       </c>
       <c r="F1360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1360" t="n">
         <v>0</v>
@@ -72966,7 +72970,7 @@
       </c>
       <c r="M1360" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1360" t="inlineStr"/>
@@ -72974,21 +72978,21 @@
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
+          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
         </is>
       </c>
       <c r="C1361" t="inlineStr"/>
       <c r="D1361" t="inlineStr"/>
       <c r="E1361" t="n">
-        <v>23109.243697</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1361" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G1361" t="n">
         <v>0</v>
@@ -73024,25 +73028,21 @@
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1362" t="inlineStr">
-        <is>
-          <t>7709195419279</t>
-        </is>
-      </c>
+          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr"/>
       <c r="D1362" t="inlineStr"/>
       <c r="E1362" t="n">
-        <v>24370</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1362" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1362" t="n">
         <v>0</v>
@@ -73078,21 +73078,25 @@
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1363" t="inlineStr"/>
+          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>7709195419279</t>
+        </is>
+      </c>
       <c r="D1363" t="inlineStr"/>
       <c r="E1363" t="n">
-        <v>24369.747899</v>
+        <v>24370</v>
       </c>
       <c r="F1363" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1363" t="n">
         <v>0</v>
@@ -73128,21 +73132,21 @@
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
+          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
         </is>
       </c>
       <c r="C1364" t="inlineStr"/>
       <c r="D1364" t="inlineStr"/>
       <c r="E1364" t="n">
-        <v>23109.243697</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1364" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G1364" t="n">
         <v>0</v>
@@ -73178,21 +73182,21 @@
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>HALLS BARRA SURTIDOS SABORES</t>
+          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
         </is>
       </c>
       <c r="C1365" t="inlineStr"/>
       <c r="D1365" t="inlineStr"/>
       <c r="E1365" t="n">
-        <v>2100.840336</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1365" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G1365" t="n">
         <v>0</v>
@@ -73228,21 +73232,21 @@
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>HALLS PEPA ROJO CEREZA X UND</t>
+          <t>HALLS BARRA SURTIDOS SABORES</t>
         </is>
       </c>
       <c r="C1366" t="inlineStr"/>
       <c r="D1366" t="inlineStr"/>
       <c r="E1366" t="n">
-        <v>336.134454</v>
+        <v>2100.840336</v>
       </c>
       <c r="F1366" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="G1366" t="n">
         <v>0</v>
@@ -73278,21 +73282,21 @@
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>HEPATODREN JARABE FCO X 240ML</t>
+          <t>HALLS PEPA ROJO CEREZA X UND</t>
         </is>
       </c>
       <c r="C1367" t="inlineStr"/>
       <c r="D1367" t="inlineStr"/>
       <c r="E1367" t="n">
-        <v>34500</v>
+        <v>336.134454</v>
       </c>
       <c r="F1367" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G1367" t="n">
         <v>0</v>
@@ -73320,7 +73324,7 @@
       </c>
       <c r="M1367" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1367" t="inlineStr"/>
@@ -73328,18 +73332,18 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>HEPATODREN X 60 CAPSULAS</t>
+          <t>HEPATODREN JARABE FCO X 240ML</t>
         </is>
       </c>
       <c r="C1368" t="inlineStr"/>
       <c r="D1368" t="inlineStr"/>
       <c r="E1368" t="n">
-        <v>58300</v>
+        <v>34500</v>
       </c>
       <c r="F1368" t="n">
         <v>1</v>
@@ -73378,25 +73382,21 @@
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>Hidraplus 75 zinc uva 400ml</t>
-        </is>
-      </c>
-      <c r="C1369" t="inlineStr">
-        <is>
-          <t>7702057010928</t>
-        </is>
-      </c>
+          <t>HEPATODREN X 60 CAPSULAS</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr"/>
       <c r="D1369" t="inlineStr"/>
       <c r="E1369" t="n">
-        <v>10600</v>
+        <v>58300</v>
       </c>
       <c r="F1369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1369" t="n">
         <v>0</v>
@@ -73432,21 +73432,25 @@
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
-        </is>
-      </c>
-      <c r="C1370" t="inlineStr"/>
+          <t>Hidraplus 75 zinc uva 400ml</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>7702057010928</t>
+        </is>
+      </c>
       <c r="D1370" t="inlineStr"/>
       <c r="E1370" t="n">
-        <v>15900</v>
+        <v>10600</v>
       </c>
       <c r="F1370" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1370" t="n">
         <v>0</v>
@@ -73482,25 +73486,21 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
-        </is>
-      </c>
-      <c r="C1371" t="inlineStr">
-        <is>
-          <t>77099475597789</t>
-        </is>
-      </c>
+          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr"/>
       <c r="D1371" t="inlineStr"/>
       <c r="E1371" t="n">
-        <v>28000</v>
+        <v>15900</v>
       </c>
       <c r="F1371" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1371" t="n">
         <v>0</v>
@@ -73536,25 +73536,25 @@
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>Hidroxicina 0.25 JBE x 120 ML</t>
+          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
         </is>
       </c>
       <c r="C1372" t="inlineStr">
         <is>
-          <t>7707035540596</t>
+          <t>77099475597789</t>
         </is>
       </c>
       <c r="D1372" t="inlineStr"/>
       <c r="E1372" t="n">
-        <v>11000</v>
+        <v>28000</v>
       </c>
       <c r="F1372" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1372" t="n">
         <v>0</v>
@@ -73590,18 +73590,22 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
-        </is>
-      </c>
-      <c r="C1373" t="inlineStr"/>
+          <t>Hidroxicina 0.25 JBE x 120 ML</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>7707035540596</t>
+        </is>
+      </c>
       <c r="D1373" t="inlineStr"/>
       <c r="E1373" t="n">
-        <v>4500</v>
+        <v>11000</v>
       </c>
       <c r="F1373" t="n">
         <v>2</v>
@@ -73640,21 +73644,21 @@
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
+          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
         </is>
       </c>
       <c r="C1374" t="inlineStr"/>
       <c r="D1374" t="inlineStr"/>
       <c r="E1374" t="n">
-        <v>6900</v>
+        <v>4500</v>
       </c>
       <c r="F1374" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1374" t="n">
         <v>0</v>
@@ -73690,18 +73694,18 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
+          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
         </is>
       </c>
       <c r="C1375" t="inlineStr"/>
       <c r="D1375" t="inlineStr"/>
       <c r="E1375" t="n">
-        <v>12000</v>
+        <v>6900</v>
       </c>
       <c r="F1375" t="n">
         <v>4</v>
@@ -73740,21 +73744,21 @@
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>Hylo Gel</t>
+          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
         </is>
       </c>
       <c r="C1376" t="inlineStr"/>
       <c r="D1376" t="inlineStr"/>
       <c r="E1376" t="n">
-        <v>131600</v>
+        <v>12000</v>
       </c>
       <c r="F1376" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1376" t="n">
         <v>0</v>
@@ -73790,25 +73794,21 @@
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>IBUPROFENO 400MG/ GENFAR</t>
-        </is>
-      </c>
-      <c r="C1377" t="inlineStr">
-        <is>
-          <t>7702605101498</t>
-        </is>
-      </c>
+          <t>Hylo Gel</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr"/>
       <c r="D1377" t="inlineStr"/>
       <c r="E1377" t="n">
-        <v>4400</v>
+        <v>131600</v>
       </c>
       <c r="F1377" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="G1377" t="n">
         <v>0</v>
@@ -73844,25 +73844,25 @@
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>Ibuprofeno 800mg AG</t>
+          <t>IBUPROFENO 400MG/ GENFAR</t>
         </is>
       </c>
       <c r="C1378" t="inlineStr">
         <is>
-          <t>7706569000385</t>
+          <t>7702605101498</t>
         </is>
       </c>
       <c r="D1378" t="inlineStr"/>
       <c r="E1378" t="n">
-        <v>800</v>
+        <v>4400</v>
       </c>
       <c r="F1378" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G1378" t="n">
         <v>0</v>
@@ -73898,25 +73898,25 @@
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
+          <t>Ibuprofeno 800mg AG</t>
         </is>
       </c>
       <c r="C1379" t="inlineStr">
         <is>
-          <t>7705959885229</t>
+          <t>7706569000385</t>
         </is>
       </c>
       <c r="D1379" t="inlineStr"/>
       <c r="E1379" t="n">
-        <v>17900</v>
+        <v>800</v>
       </c>
       <c r="F1379" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1379" t="n">
         <v>0</v>
@@ -73952,22 +73952,22 @@
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>ICE POWER 30 GR GEL COSMETICA</t>
+          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
         </is>
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>737186238889</t>
+          <t>7705959885229</t>
         </is>
       </c>
       <c r="D1380" t="inlineStr"/>
       <c r="E1380" t="n">
-        <v>12521.008403</v>
+        <v>17900</v>
       </c>
       <c r="F1380" t="n">
         <v>2</v>
@@ -73998,7 +73998,7 @@
       </c>
       <c r="M1380" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1380" t="inlineStr"/>
@@ -74006,21 +74006,25 @@
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
-        </is>
-      </c>
-      <c r="C1381" t="inlineStr"/>
+          <t>ICE POWER 30 GR GEL COSMETICA</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>737186238889</t>
+        </is>
+      </c>
       <c r="D1381" t="inlineStr"/>
       <c r="E1381" t="n">
-        <v>38900</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1381" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1381" t="n">
         <v>0</v>
@@ -74048,7 +74052,7 @@
       </c>
       <c r="M1381" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1381" t="inlineStr"/>
@@ -74056,12 +74060,12 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
+          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
         </is>
       </c>
       <c r="C1382" t="inlineStr"/>
@@ -74106,21 +74110,21 @@
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
+          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
         </is>
       </c>
       <c r="C1383" t="inlineStr"/>
       <c r="D1383" t="inlineStr"/>
       <c r="E1383" t="n">
-        <v>8235.294118</v>
+        <v>38900</v>
       </c>
       <c r="F1383" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1383" t="n">
         <v>0</v>
@@ -74148,7 +74152,7 @@
       </c>
       <c r="M1383" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1383" t="inlineStr"/>
@@ -74156,21 +74160,21 @@
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
+          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
         </is>
       </c>
       <c r="C1384" t="inlineStr"/>
       <c r="D1384" t="inlineStr"/>
       <c r="E1384" t="n">
-        <v>9831.932773</v>
+        <v>8235.294118</v>
       </c>
       <c r="F1384" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1384" t="n">
         <v>0</v>
@@ -74206,21 +74210,21 @@
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
+          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
         </is>
       </c>
       <c r="C1385" t="inlineStr"/>
       <c r="D1385" t="inlineStr"/>
       <c r="E1385" t="n">
-        <v>4201.680672</v>
+        <v>9831.932773</v>
       </c>
       <c r="F1385" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1385" t="n">
         <v>0</v>
@@ -74256,12 +74260,12 @@
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
+          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
         </is>
       </c>
       <c r="C1386" t="inlineStr"/>
@@ -74270,7 +74274,7 @@
         <v>4201.680672</v>
       </c>
       <c r="F1386" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1386" t="n">
         <v>0</v>
@@ -74306,18 +74310,18 @@
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>JABON PROTEX HERBAL 110GR</t>
+          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr"/>
       <c r="D1387" t="inlineStr"/>
       <c r="E1387" t="n">
-        <v>4537.815126</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1387" t="n">
         <v>2</v>
@@ -74356,22 +74360,18 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>JARABE ZETYGRIP FCO 60ML</t>
-        </is>
-      </c>
-      <c r="C1388" t="inlineStr">
-        <is>
-          <t>7709805542830</t>
-        </is>
-      </c>
+          <t>JABON PROTEX HERBAL 110GR</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr"/>
       <c r="D1388" t="inlineStr"/>
       <c r="E1388" t="n">
-        <v>14000</v>
+        <v>4537.815126</v>
       </c>
       <c r="F1388" t="n">
         <v>2</v>
@@ -74402,7 +74402,7 @@
       </c>
       <c r="M1388" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1388" t="inlineStr"/>
@@ -74410,21 +74410,25 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>JERINGA DE 50ML</t>
-        </is>
-      </c>
-      <c r="C1389" t="inlineStr"/>
+          <t>JARABE ZETYGRIP FCO 60ML</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>7709805542830</t>
+        </is>
+      </c>
       <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="n">
-        <v>2500</v>
+        <v>14000</v>
       </c>
       <c r="F1389" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1389" t="n">
         <v>0</v>
@@ -74460,21 +74464,21 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>Jeringa desechable estéril 20ml impormedicas</t>
+          <t>JERINGA DE 50ML</t>
         </is>
       </c>
       <c r="C1390" t="inlineStr"/>
       <c r="D1390" t="inlineStr"/>
       <c r="E1390" t="n">
-        <v>920</v>
+        <v>2500</v>
       </c>
       <c r="F1390" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G1390" t="n">
         <v>0</v>
@@ -74502,7 +74506,7 @@
       </c>
       <c r="M1390" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1390" t="inlineStr"/>
@@ -74510,21 +74514,21 @@
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
+          <t>Jeringa desechable estéril 20ml impormedicas</t>
         </is>
       </c>
       <c r="C1391" t="inlineStr"/>
       <c r="D1391" t="inlineStr"/>
       <c r="E1391" t="n">
-        <v>1100</v>
+        <v>920</v>
       </c>
       <c r="F1391" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="G1391" t="n">
         <v>0</v>
@@ -74552,7 +74556,7 @@
       </c>
       <c r="M1391" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1391" t="inlineStr"/>
@@ -74560,21 +74564,21 @@
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>Kelocate</t>
+          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
         </is>
       </c>
       <c r="C1392" t="inlineStr"/>
       <c r="D1392" t="inlineStr"/>
       <c r="E1392" t="n">
-        <v>180000</v>
+        <v>1100</v>
       </c>
       <c r="F1392" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G1392" t="n">
         <v>0</v>
@@ -74610,22 +74614,18 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
-        </is>
-      </c>
-      <c r="C1393" t="inlineStr">
-        <is>
-          <t>7702057073695</t>
-        </is>
-      </c>
+          <t>Kelocate</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr"/>
       <c r="D1393" t="inlineStr"/>
       <c r="E1393" t="n">
-        <v>19500</v>
+        <v>180000</v>
       </c>
       <c r="F1393" t="n">
         <v>0</v>
@@ -74664,22 +74664,22 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
+          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
         </is>
       </c>
       <c r="C1394" t="inlineStr">
         <is>
-          <t>7709947559772</t>
+          <t>7702057073695</t>
         </is>
       </c>
       <c r="D1394" t="inlineStr"/>
       <c r="E1394" t="n">
-        <v>15000</v>
+        <v>19500</v>
       </c>
       <c r="F1394" t="n">
         <v>0</v>
@@ -74718,18 +74718,22 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
-        </is>
-      </c>
-      <c r="C1395" t="inlineStr"/>
+          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>7709947559772</t>
+        </is>
+      </c>
       <c r="D1395" t="inlineStr"/>
       <c r="E1395" t="n">
-        <v>71000</v>
+        <v>15000</v>
       </c>
       <c r="F1395" t="n">
         <v>0</v>
@@ -74768,21 +74772,21 @@
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
+          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
         </is>
       </c>
       <c r="C1396" t="inlineStr"/>
       <c r="D1396" t="inlineStr"/>
       <c r="E1396" t="n">
-        <v>37900</v>
+        <v>71000</v>
       </c>
       <c r="F1396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1396" t="n">
         <v>0</v>
@@ -74818,25 +74822,21 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>Levotiroxina 100mcg MK</t>
-        </is>
-      </c>
-      <c r="C1397" t="inlineStr">
-        <is>
-          <t>7702057715908</t>
-        </is>
-      </c>
+          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr"/>
       <c r="D1397" t="inlineStr"/>
       <c r="E1397" t="n">
-        <v>27900</v>
+        <v>37900</v>
       </c>
       <c r="F1397" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1397" t="n">
         <v>0</v>
@@ -74872,21 +74872,25 @@
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>LIMA MAYOMI 10/180</t>
-        </is>
-      </c>
-      <c r="C1398" t="inlineStr"/>
+          <t>Levotiroxina 100mcg MK</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>7702057715908</t>
+        </is>
+      </c>
       <c r="D1398" t="inlineStr"/>
       <c r="E1398" t="n">
-        <v>3900</v>
+        <v>27900</v>
       </c>
       <c r="F1398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1398" t="n">
         <v>0</v>
@@ -74922,21 +74926,21 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
+          <t>LIMA MAYOMI 10/180</t>
         </is>
       </c>
       <c r="C1399" t="inlineStr"/>
       <c r="D1399" t="inlineStr"/>
       <c r="E1399" t="n">
-        <v>16807</v>
+        <v>3900</v>
       </c>
       <c r="F1399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1399" t="n">
         <v>0</v>
@@ -74964,7 +74968,7 @@
       </c>
       <c r="M1399" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1399" t="inlineStr"/>
@@ -74972,21 +74976,21 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
+          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
         </is>
       </c>
       <c r="C1400" t="inlineStr"/>
       <c r="D1400" t="inlineStr"/>
       <c r="E1400" t="n">
-        <v>15042.016807</v>
+        <v>16807</v>
       </c>
       <c r="F1400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1400" t="n">
         <v>0</v>
@@ -75022,21 +75026,21 @@
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>LISTERINE CUIDADO TOTAL 180ML</t>
+          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
         </is>
       </c>
       <c r="C1401" t="inlineStr"/>
       <c r="D1401" t="inlineStr"/>
       <c r="E1401" t="n">
-        <v>16386.554622</v>
+        <v>15042.016807</v>
       </c>
       <c r="F1401" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1401" t="n">
         <v>0</v>
@@ -75072,21 +75076,21 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
+          <t>LISTERINE CUIDADO TOTAL 180ML</t>
         </is>
       </c>
       <c r="C1402" t="inlineStr"/>
       <c r="D1402" t="inlineStr"/>
       <c r="E1402" t="n">
-        <v>3500</v>
+        <v>16386.554622</v>
       </c>
       <c r="F1402" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G1402" t="n">
         <v>0</v>
@@ -75114,7 +75118,7 @@
       </c>
       <c r="M1402" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1402" t="inlineStr"/>
@@ -75122,12 +75126,12 @@
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
         </is>
       </c>
       <c r="C1403" t="inlineStr"/>
@@ -75136,7 +75140,7 @@
         <v>3500</v>
       </c>
       <c r="F1403" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G1403" t="n">
         <v>0</v>
@@ -75172,21 +75176,21 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
         </is>
       </c>
       <c r="C1404" t="inlineStr"/>
       <c r="D1404" t="inlineStr"/>
       <c r="E1404" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="F1404" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1404" t="n">
         <v>0</v>
@@ -75222,25 +75226,21 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>Losartan Tensofar 100 Mg</t>
-        </is>
-      </c>
-      <c r="C1405" t="inlineStr">
-        <is>
-          <t>7703546012119</t>
-        </is>
-      </c>
+          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr"/>
       <c r="D1405" t="inlineStr"/>
       <c r="E1405" t="n">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="F1405" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1405" t="n">
         <v>0</v>
@@ -75276,25 +75276,25 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+          <t>Losartan Tensofar 100 Mg</t>
         </is>
       </c>
       <c r="C1406" t="inlineStr">
         <is>
-          <t>7501007528939</t>
+          <t>7703546012119</t>
         </is>
       </c>
       <c r="D1406" t="inlineStr"/>
       <c r="E1406" t="n">
-        <v>18907.563025</v>
+        <v>5000</v>
       </c>
       <c r="F1406" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1406" t="n">
         <v>0</v>
@@ -75322,7 +75322,7 @@
       </c>
       <c r="M1406" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1406" t="inlineStr"/>
@@ -75330,18 +75330,22 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>MANTECA DE CACAO LABIAL LIMON</t>
-        </is>
-      </c>
-      <c r="C1407" t="inlineStr"/>
+          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>7501007528939</t>
+        </is>
+      </c>
       <c r="D1407" t="inlineStr"/>
       <c r="E1407" t="n">
-        <v>3361.344538</v>
+        <v>18907.563025</v>
       </c>
       <c r="F1407" t="n">
         <v>0</v>
@@ -75380,12 +75384,12 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
+          <t>MANTECA DE CACAO LABIAL LIMON</t>
         </is>
       </c>
       <c r="C1408" t="inlineStr"/>
@@ -75430,21 +75434,21 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>Mega sex</t>
+          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
         </is>
       </c>
       <c r="C1409" t="inlineStr"/>
       <c r="D1409" t="inlineStr"/>
       <c r="E1409" t="n">
-        <v>3200</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1409" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G1409" t="n">
         <v>0</v>
@@ -75472,7 +75476,7 @@
       </c>
       <c r="M1409" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1409" t="inlineStr"/>
@@ -75480,29 +75484,21 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>Melatonina 3mg</t>
-        </is>
-      </c>
-      <c r="C1410" t="inlineStr">
-        <is>
-          <t>7706849112906</t>
-        </is>
-      </c>
-      <c r="D1410" t="inlineStr">
-        <is>
-          <t>producto nuevo</t>
-        </is>
-      </c>
+          <t>Mega sex</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr"/>
+      <c r="D1410" t="inlineStr"/>
       <c r="E1410" t="n">
-        <v>52000</v>
+        <v>3200</v>
       </c>
       <c r="F1410" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G1410" t="n">
         <v>0</v>
@@ -75538,22 +75534,26 @@
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
+          <t>Melatonina 3mg</t>
         </is>
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>7707529435209</t>
-        </is>
-      </c>
-      <c r="D1411" t="inlineStr"/>
+          <t>7706849112906</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>producto nuevo</t>
+        </is>
+      </c>
       <c r="E1411" t="n">
-        <v>36000</v>
+        <v>52000</v>
       </c>
       <c r="F1411" t="n">
         <v>0</v>
@@ -75592,22 +75592,22 @@
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>Meloxicam 15mg AG</t>
+          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
         </is>
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>7706569020437</t>
+          <t>7707529435209</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr"/>
       <c r="E1412" t="n">
-        <v>1500</v>
+        <v>36000</v>
       </c>
       <c r="F1412" t="n">
         <v>0</v>
@@ -75646,21 +75646,25 @@
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
-        </is>
-      </c>
-      <c r="C1413" t="inlineStr"/>
+          <t>Meloxicam 15mg AG</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>7706569020437</t>
+        </is>
+      </c>
       <c r="D1413" t="inlineStr"/>
       <c r="E1413" t="n">
-        <v>9700</v>
+        <v>1500</v>
       </c>
       <c r="F1413" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1413" t="n">
         <v>0</v>
@@ -75696,25 +75700,21 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>MELOXICAM COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1414" t="inlineStr">
-        <is>
-          <t>7703712036253</t>
-        </is>
-      </c>
+          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr"/>
       <c r="D1414" t="inlineStr"/>
       <c r="E1414" t="n">
-        <v>1300</v>
+        <v>9700</v>
       </c>
       <c r="F1414" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1414" t="n">
         <v>0</v>
@@ -75740,31 +75740,35 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1414" t="inlineStr"/>
+      <c r="M1414" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1414" t="inlineStr"/>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>metformina 850 mg pisa</t>
+          <t>MELOXICAM COASPHARMA</t>
         </is>
       </c>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>7501125188039</t>
+          <t>7703712036253</t>
         </is>
       </c>
       <c r="D1415" t="inlineStr"/>
       <c r="E1415" t="n">
-        <v>5500</v>
+        <v>1300</v>
       </c>
       <c r="F1415" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G1415" t="n">
         <v>0</v>
@@ -75790,35 +75794,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1415" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1415" t="inlineStr"/>
       <c r="N1415" t="inlineStr"/>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10MG RECIPE</t>
+          <t>metformina 850 mg pisa</t>
         </is>
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>7702195084355</t>
+          <t>7501125188039</t>
         </is>
       </c>
       <c r="D1416" t="inlineStr"/>
       <c r="E1416" t="n">
-        <v>1000</v>
+        <v>5500</v>
       </c>
       <c r="F1416" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G1416" t="n">
         <v>0</v>
@@ -75854,25 +75854,25 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>MICROPOR 1X3 Y</t>
+          <t>METOCLOPRAMIDA 10MG RECIPE</t>
         </is>
       </c>
       <c r="C1417" t="inlineStr">
         <is>
-          <t>7707282990205</t>
+          <t>7702195084355</t>
         </is>
       </c>
       <c r="D1417" t="inlineStr"/>
       <c r="E1417" t="n">
-        <v>5300</v>
+        <v>1000</v>
       </c>
       <c r="F1417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1417" t="n">
         <v>0</v>
@@ -75908,25 +75908,25 @@
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>MICROPOR CINTA 1/2X5Y</t>
+          <t>MICROPOR 1X3 Y</t>
         </is>
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>7707282990182</t>
+          <t>7707282990205</t>
         </is>
       </c>
       <c r="D1418" t="inlineStr"/>
       <c r="E1418" t="n">
-        <v>3900</v>
+        <v>5300</v>
       </c>
       <c r="F1418" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G1418" t="n">
         <v>0</v>
@@ -75962,21 +75962,25 @@
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>MICROPORE COLOR PIEL 2YARDAS</t>
-        </is>
-      </c>
-      <c r="C1419" t="inlineStr"/>
+          <t>MICROPOR CINTA 1/2X5Y</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>7707282990182</t>
+        </is>
+      </c>
       <c r="D1419" t="inlineStr"/>
       <c r="E1419" t="n">
-        <v>3700</v>
+        <v>3900</v>
       </c>
       <c r="F1419" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G1419" t="n">
         <v>0</v>
@@ -76012,18 +76016,18 @@
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
+          <t>MICROPORE COLOR PIEL 2YARDAS</t>
         </is>
       </c>
       <c r="C1420" t="inlineStr"/>
       <c r="D1420" t="inlineStr"/>
       <c r="E1420" t="n">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="F1420" t="n">
         <v>0</v>
@@ -76062,22 +76066,18 @@
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>MIELTERTOS JARABE X 240ML</t>
-        </is>
-      </c>
-      <c r="C1421" t="inlineStr">
-        <is>
-          <t>7707232095608</t>
-        </is>
-      </c>
+          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr"/>
       <c r="D1421" t="inlineStr"/>
       <c r="E1421" t="n">
-        <v>34500</v>
+        <v>4000</v>
       </c>
       <c r="F1421" t="n">
         <v>0</v>
@@ -76116,25 +76116,25 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
-        </is>
-      </c>
-      <c r="C1422" t="inlineStr"/>
-      <c r="D1422" t="inlineStr">
-        <is>
-          <t>subio precio hector</t>
-        </is>
-      </c>
+          <t>MIELTERTOS JARABE X 240ML</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>7707232095608</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr"/>
       <c r="E1422" t="n">
-        <v>22700</v>
+        <v>34500</v>
       </c>
       <c r="F1422" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1422" t="n">
         <v>0</v>
@@ -76170,21 +76170,21 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
+          <t>MOÑAS PARA EL PELO COLOR YIMEIJIA</t>
         </is>
       </c>
       <c r="C1423" t="inlineStr"/>
       <c r="D1423" t="inlineStr"/>
       <c r="E1423" t="n">
-        <v>5500</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1423" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G1423" t="n">
         <v>0</v>
@@ -76212,7 +76212,7 @@
       </c>
       <c r="M1423" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1423" t="inlineStr"/>
@@ -76220,21 +76220,25 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>NEOSALDINA TABLETA X UND</t>
+          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
         </is>
       </c>
       <c r="C1424" t="inlineStr"/>
-      <c r="D1424" t="inlineStr"/>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>subio precio hector</t>
+        </is>
+      </c>
       <c r="E1424" t="n">
-        <v>2500</v>
+        <v>22700</v>
       </c>
       <c r="F1424" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G1424" t="n">
         <v>0</v>
@@ -76270,21 +76274,21 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>NIFEDIPINO 30MG NOVAMED</t>
+          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
         </is>
       </c>
       <c r="C1425" t="inlineStr"/>
       <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="n">
-        <v>19000</v>
+        <v>5500</v>
       </c>
       <c r="F1425" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G1425" t="n">
         <v>0</v>
@@ -76320,21 +76324,21 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
+          <t>NEOSALDINA TABLETA X UND</t>
         </is>
       </c>
       <c r="C1426" t="inlineStr"/>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="n">
-        <v>23000</v>
+        <v>2500</v>
       </c>
       <c r="F1426" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G1426" t="n">
         <v>0</v>
@@ -76370,21 +76374,21 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>NITOXIPAR X 6 TABLETAS</t>
+          <t>NIFEDIPINO 30MG NOVAMED</t>
         </is>
       </c>
       <c r="C1427" t="inlineStr"/>
       <c r="D1427" t="inlineStr"/>
       <c r="E1427" t="n">
-        <v>24500</v>
+        <v>19000</v>
       </c>
       <c r="F1427" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1427" t="n">
         <v>0</v>
@@ -76420,21 +76424,21 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>NORAVER SPRAY CEREZA 120ML</t>
+          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
         </is>
       </c>
       <c r="C1428" t="inlineStr"/>
       <c r="D1428" t="inlineStr"/>
       <c r="E1428" t="n">
-        <v>52900</v>
+        <v>23000</v>
       </c>
       <c r="F1428" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1428" t="n">
         <v>0</v>
@@ -76470,25 +76474,21 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
-        </is>
-      </c>
-      <c r="C1429" t="inlineStr">
-        <is>
-          <t>7702027041662</t>
-        </is>
-      </c>
+          <t>NITOXIPAR X 6 TABLETAS</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr"/>
       <c r="D1429" t="inlineStr"/>
       <c r="E1429" t="n">
-        <v>6300</v>
+        <v>24500</v>
       </c>
       <c r="F1429" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1429" t="n">
         <v>0</v>
@@ -76524,21 +76524,21 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+          <t>NORAVER SPRAY CEREZA 120ML</t>
         </is>
       </c>
       <c r="C1430" t="inlineStr"/>
       <c r="D1430" t="inlineStr"/>
       <c r="E1430" t="n">
-        <v>8823.529412</v>
+        <v>52900</v>
       </c>
       <c r="F1430" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1430" t="n">
         <v>0</v>
@@ -76566,7 +76566,7 @@
       </c>
       <c r="M1430" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1430" t="inlineStr"/>
@@ -76574,22 +76574,22 @@
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
         </is>
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>7702026158644</t>
+          <t>7702027041662</t>
         </is>
       </c>
       <c r="D1431" t="inlineStr"/>
       <c r="E1431" t="n">
-        <v>8823.529412</v>
+        <v>6300</v>
       </c>
       <c r="F1431" t="n">
         <v>0</v>
@@ -76620,7 +76620,7 @@
       </c>
       <c r="M1431" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1431" t="inlineStr"/>
@@ -76628,25 +76628,21 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JBE 120ML</t>
-        </is>
-      </c>
-      <c r="C1432" t="inlineStr">
-        <is>
-          <t>7707355053363</t>
-        </is>
-      </c>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr"/>
       <c r="D1432" t="inlineStr"/>
       <c r="E1432" t="n">
-        <v>22700</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1432" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1432" t="n">
         <v>0</v>
@@ -76674,7 +76670,7 @@
       </c>
       <c r="M1432" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1432" t="inlineStr"/>
@@ -76682,22 +76678,22 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
         </is>
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>7707355053356</t>
+          <t>7702026158644</t>
         </is>
       </c>
       <c r="D1433" t="inlineStr"/>
       <c r="E1433" t="n">
-        <v>17200</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1433" t="n">
         <v>0</v>
@@ -76728,7 +76724,7 @@
       </c>
       <c r="M1433" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1433" t="inlineStr"/>
@@ -76736,18 +76732,22 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>NUTRIBELL ACEITE DE COCO</t>
-        </is>
-      </c>
-      <c r="C1434" t="inlineStr"/>
+          <t>NOXPIRIN JUNIOR JBE 120ML</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>7707355053363</t>
+        </is>
+      </c>
       <c r="D1434" t="inlineStr"/>
       <c r="E1434" t="n">
-        <v>2700</v>
+        <v>22700</v>
       </c>
       <c r="F1434" t="n">
         <v>1</v>
@@ -76786,29 +76786,25 @@
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Omega 3 6 9 suplemento totalmax</t>
+          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
         </is>
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>7707529434974</t>
-        </is>
-      </c>
-      <c r="D1435" t="inlineStr">
-        <is>
-          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
-        </is>
-      </c>
+          <t>7707355053356</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr"/>
       <c r="E1435" t="n">
-        <v>35000</v>
+        <v>17200</v>
       </c>
       <c r="F1435" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>
@@ -76844,21 +76840,21 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
+          <t>NUTRIBELL ACEITE DE COCO</t>
         </is>
       </c>
       <c r="C1436" t="inlineStr"/>
       <c r="D1436" t="inlineStr"/>
       <c r="E1436" t="n">
-        <v>5500</v>
+        <v>2700</v>
       </c>
       <c r="F1436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1436" t="n">
         <v>0</v>
@@ -76894,25 +76890,29 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
+          <t>Omega 3 6 9 suplemento totalmax</t>
         </is>
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>7707529435940</t>
-        </is>
-      </c>
-      <c r="D1437" t="inlineStr"/>
+          <t>7707529434974</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
+        </is>
+      </c>
       <c r="E1437" t="n">
         <v>35000</v>
       </c>
       <c r="F1437" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1437" t="n">
         <v>0</v>
@@ -76948,21 +76948,21 @@
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
+          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
         </is>
       </c>
       <c r="C1438" t="inlineStr"/>
       <c r="D1438" t="inlineStr"/>
       <c r="E1438" t="n">
-        <v>48000</v>
+        <v>5500</v>
       </c>
       <c r="F1438" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1438" t="n">
         <v>0</v>
@@ -76998,25 +76998,25 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>OROCAL CALCIO 600MG</t>
-        </is>
-      </c>
-      <c r="C1439" t="inlineStr"/>
-      <c r="D1439" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>7707529435940</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr"/>
       <c r="E1439" t="n">
-        <v>30500</v>
+        <v>35000</v>
       </c>
       <c r="F1439" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1439" t="n">
         <v>0</v>
@@ -77052,21 +77052,21 @@
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>PALA DE MADERA RASPACALLO</t>
+          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
         </is>
       </c>
       <c r="C1440" t="inlineStr"/>
       <c r="D1440" t="inlineStr"/>
       <c r="E1440" t="n">
-        <v>4000</v>
+        <v>48000</v>
       </c>
       <c r="F1440" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1440" t="n">
         <v>0</v>
@@ -77102,21 +77102,25 @@
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>PALO DE NARANJO X UNIDAD</t>
+          <t>OROCAL CALCIO 600MG</t>
         </is>
       </c>
       <c r="C1441" t="inlineStr"/>
-      <c r="D1441" t="inlineStr"/>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E1441" t="n">
-        <v>400</v>
+        <v>30500</v>
       </c>
       <c r="F1441" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G1441" t="n">
         <v>0</v>
@@ -77152,22 +77156,18 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
-        </is>
-      </c>
-      <c r="C1442" t="inlineStr">
-        <is>
-          <t>7704412170896</t>
-        </is>
-      </c>
+          <t>PALA DE MADERA RASPACALLO</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr"/>
       <c r="D1442" t="inlineStr"/>
       <c r="E1442" t="n">
-        <v>6200</v>
+        <v>4000</v>
       </c>
       <c r="F1442" t="n">
         <v>1</v>
@@ -77206,21 +77206,21 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
+          <t>PALO DE NARANJO X UNIDAD</t>
         </is>
       </c>
       <c r="C1443" t="inlineStr"/>
       <c r="D1443" t="inlineStr"/>
       <c r="E1443" t="n">
-        <v>14285.714286</v>
+        <v>400</v>
       </c>
       <c r="F1443" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G1443" t="n">
         <v>0</v>
@@ -77248,7 +77248,7 @@
       </c>
       <c r="M1443" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1443" t="inlineStr"/>
@@ -77256,18 +77256,22 @@
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
-        </is>
-      </c>
-      <c r="C1444" t="inlineStr"/>
+          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>7704412170896</t>
+        </is>
+      </c>
       <c r="D1444" t="inlineStr"/>
       <c r="E1444" t="n">
-        <v>28991.596639</v>
+        <v>6200</v>
       </c>
       <c r="F1444" t="n">
         <v>1</v>
@@ -77298,7 +77302,7 @@
       </c>
       <c r="M1444" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1444" t="inlineStr"/>
@@ -77306,18 +77310,18 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
         </is>
       </c>
       <c r="C1445" t="inlineStr"/>
       <c r="D1445" t="inlineStr"/>
       <c r="E1445" t="n">
-        <v>41176.470588</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1445" t="n">
         <v>1</v>
@@ -77356,22 +77360,18 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>Pañales Winny Etapa 5 X PAQUETE</t>
-        </is>
-      </c>
-      <c r="C1446" t="inlineStr">
-        <is>
-          <t>7701021114174</t>
-        </is>
-      </c>
+          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr"/>
       <c r="D1446" t="inlineStr"/>
       <c r="E1446" t="n">
-        <v>41849</v>
+        <v>28991.596639</v>
       </c>
       <c r="F1446" t="n">
         <v>1</v>
@@ -77410,21 +77410,21 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>PAÑALWINNY ETA 5 X 16 UND</t>
+          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
         </is>
       </c>
       <c r="C1447" t="inlineStr"/>
       <c r="D1447" t="inlineStr"/>
       <c r="E1447" t="n">
-        <v>24369.747899</v>
+        <v>41176.470588</v>
       </c>
       <c r="F1447" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1447" t="n">
         <v>0</v>
@@ -77460,21 +77460,25 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>pañitos humedos pequeñin 100unidades</t>
-        </is>
-      </c>
-      <c r="C1448" t="inlineStr"/>
+          <t>Pañales Winny Etapa 5 X PAQUETE</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>7701021114174</t>
+        </is>
+      </c>
       <c r="D1448" t="inlineStr"/>
       <c r="E1448" t="n">
-        <v>10925</v>
+        <v>41849</v>
       </c>
       <c r="F1448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1448" t="n">
         <v>0</v>
@@ -77510,18 +77514,18 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
+          <t>PAÑALWINNY ETA 5 X 16 UND</t>
         </is>
       </c>
       <c r="C1449" t="inlineStr"/>
       <c r="D1449" t="inlineStr"/>
       <c r="E1449" t="n">
-        <v>14900</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1449" t="n">
         <v>2</v>
@@ -77552,7 +77556,7 @@
       </c>
       <c r="M1449" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1449" t="inlineStr"/>
@@ -77560,21 +77564,21 @@
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Panotil B x 8ML</t>
+          <t>pañitos humedos pequeñin 100unidades</t>
         </is>
       </c>
       <c r="C1450" t="inlineStr"/>
       <c r="D1450" t="inlineStr"/>
       <c r="E1450" t="n">
-        <v>26400</v>
+        <v>10925</v>
       </c>
       <c r="F1450" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1450" t="n">
         <v>0</v>
@@ -77602,7 +77606,7 @@
       </c>
       <c r="M1450" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1450" t="inlineStr"/>
@@ -77610,25 +77614,21 @@
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>PANTENE ACONDICIONADOR</t>
-        </is>
-      </c>
-      <c r="C1451" t="inlineStr">
-        <is>
-          <t>7500435153683</t>
-        </is>
-      </c>
+          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr"/>
       <c r="D1451" t="inlineStr"/>
       <c r="E1451" t="n">
-        <v>1500</v>
+        <v>14900</v>
       </c>
       <c r="F1451" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G1451" t="n">
         <v>0</v>
@@ -77664,21 +77664,21 @@
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Parche Ocular Colostol</t>
+          <t>Panotil B x 8ML</t>
         </is>
       </c>
       <c r="C1452" t="inlineStr"/>
       <c r="D1452" t="inlineStr"/>
       <c r="E1452" t="n">
-        <v>1300</v>
+        <v>26400</v>
       </c>
       <c r="F1452" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G1452" t="n">
         <v>0</v>
@@ -77714,25 +77714,25 @@
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
+          <t>PANTENE ACONDICIONADOR</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>7501033957413</t>
+          <t>7500435153683</t>
         </is>
       </c>
       <c r="D1453" t="inlineStr"/>
       <c r="E1453" t="n">
-        <v>10600</v>
+        <v>1500</v>
       </c>
       <c r="F1453" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1453" t="n">
         <v>0</v>
@@ -77768,26 +77768,22 @@
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
+          <t>PARCHE ACNE FIGURAS</t>
         </is>
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>7501033961557</t>
-        </is>
-      </c>
-      <c r="D1454" t="inlineStr">
-        <is>
-          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
-        </is>
-      </c>
+          <t>6971622250767</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr"/>
       <c r="E1454" t="n">
-        <v>10900</v>
+        <v>5882.352941</v>
       </c>
       <c r="F1454" t="n">
         <v>0</v>
@@ -77818,7 +77814,7 @@
       </c>
       <c r="M1454" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1454" t="inlineStr"/>
@@ -77826,29 +77822,21 @@
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
-        </is>
-      </c>
-      <c r="C1455" t="inlineStr">
-        <is>
-          <t>7501033957376</t>
-        </is>
-      </c>
-      <c r="D1455" t="inlineStr">
-        <is>
-          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
-        </is>
-      </c>
+          <t>Parche Ocular Colostol</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr"/>
+      <c r="D1455" t="inlineStr"/>
       <c r="E1455" t="n">
-        <v>10900</v>
+        <v>1300</v>
       </c>
       <c r="F1455" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G1455" t="n">
         <v>0</v>
@@ -77884,21 +77872,25 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>PEGANTE GLUE X 10GR X UND</t>
-        </is>
-      </c>
-      <c r="C1456" t="inlineStr"/>
+          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>7501033957413</t>
+        </is>
+      </c>
       <c r="D1456" t="inlineStr"/>
       <c r="E1456" t="n">
-        <v>2000</v>
+        <v>10600</v>
       </c>
       <c r="F1456" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1456" t="n">
         <v>0</v>
@@ -77934,21 +77926,29 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>PEINETA COLA DE RATON METALICA</t>
-        </is>
-      </c>
-      <c r="C1457" t="inlineStr"/>
-      <c r="D1457" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>7501033961557</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
+        </is>
+      </c>
       <c r="E1457" t="n">
-        <v>4700</v>
+        <v>10900</v>
       </c>
       <c r="F1457" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1457" t="n">
         <v>0</v>
@@ -77984,21 +77984,29 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>PERFILADORES DE CEJAS</t>
-        </is>
-      </c>
-      <c r="C1458" t="inlineStr"/>
-      <c r="D1458" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>7501033957376</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+        </is>
+      </c>
       <c r="E1458" t="n">
-        <v>3900</v>
+        <v>10900</v>
       </c>
       <c r="F1458" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1458" t="n">
         <v>0</v>
@@ -78034,21 +78042,21 @@
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
+          <t>PEGANTE GLUE X 10GR X UND</t>
         </is>
       </c>
       <c r="C1459" t="inlineStr"/>
       <c r="D1459" t="inlineStr"/>
       <c r="E1459" t="n">
-        <v>27983.193277</v>
+        <v>2000</v>
       </c>
       <c r="F1459" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1459" t="n">
         <v>0</v>
@@ -78076,7 +78084,7 @@
       </c>
       <c r="M1459" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1459" t="inlineStr"/>
@@ -78084,21 +78092,21 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>POPETAS SURTIDAS X UND</t>
+          <t>PEINETA COLA DE RATON METALICA</t>
         </is>
       </c>
       <c r="C1460" t="inlineStr"/>
       <c r="D1460" t="inlineStr"/>
       <c r="E1460" t="n">
-        <v>2521.008403</v>
+        <v>4700</v>
       </c>
       <c r="F1460" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1460" t="n">
         <v>0</v>
@@ -78126,7 +78134,7 @@
       </c>
       <c r="M1460" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1460" t="inlineStr"/>
@@ -78134,21 +78142,21 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+          <t>PERFILADORES DE CEJAS</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr"/>
       <c r="D1461" t="inlineStr"/>
       <c r="E1461" t="n">
-        <v>20500</v>
+        <v>3900</v>
       </c>
       <c r="F1461" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1461" t="n">
         <v>0</v>
@@ -78184,26 +78192,18 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>privatos miel limon la francol 120ml</t>
-        </is>
-      </c>
-      <c r="C1462" t="inlineStr">
-        <is>
-          <t>7702207163948</t>
-        </is>
-      </c>
-      <c r="D1462" t="inlineStr">
-        <is>
-          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
-        </is>
-      </c>
+          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr"/>
+      <c r="D1462" t="inlineStr"/>
       <c r="E1462" t="n">
-        <v>35900</v>
+        <v>27983.193277</v>
       </c>
       <c r="F1462" t="n">
         <v>1</v>
@@ -78234,7 +78234,7 @@
       </c>
       <c r="M1462" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1462" t="inlineStr"/>
@@ -78242,21 +78242,21 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
+          <t>POPETAS SURTIDAS X UND</t>
         </is>
       </c>
       <c r="C1463" t="inlineStr"/>
       <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="n">
-        <v>0</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1463" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1463" t="n">
         <v>0</v>
@@ -78292,21 +78292,21 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>PROTECTOR NOSOTRAS LARGOS</t>
+          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
         </is>
       </c>
       <c r="C1464" t="inlineStr"/>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="n">
-        <v>3700</v>
+        <v>20500</v>
       </c>
       <c r="F1464" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1464" t="n">
         <v>0</v>
@@ -78342,18 +78342,26 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
-        </is>
-      </c>
-      <c r="C1465" t="inlineStr"/>
-      <c r="D1465" t="inlineStr"/>
+          <t>privatos miel limon la francol 120ml</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>7702207163948</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
+        </is>
+      </c>
       <c r="E1465" t="n">
-        <v>8900</v>
+        <v>35900</v>
       </c>
       <c r="F1465" t="n">
         <v>1</v>
@@ -78392,18 +78400,18 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>778</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Protector Solar Sunaid</t>
+          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
         </is>
       </c>
       <c r="C1466" t="inlineStr"/>
       <c r="D1466" t="inlineStr"/>
       <c r="E1466" t="n">
-        <v>158000</v>
+        <v>0</v>
       </c>
       <c r="F1466" t="n">
         <v>0</v>
@@ -78434,7 +78442,7 @@
       </c>
       <c r="M1466" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1466" t="inlineStr"/>
@@ -78442,25 +78450,21 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>Prueba de embarazo esfero</t>
-        </is>
-      </c>
-      <c r="C1467" t="inlineStr">
-        <is>
-          <t>7709299854228</t>
-        </is>
-      </c>
+          <t>PROTECTOR NOSOTRAS LARGOS</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr"/>
       <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="n">
-        <v>16500</v>
+        <v>3700</v>
       </c>
       <c r="F1467" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1467" t="n">
         <v>0</v>
@@ -78496,25 +78500,21 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>Prueba de embarazo HCG cassette begut</t>
-        </is>
-      </c>
-      <c r="C1468" t="inlineStr">
-        <is>
-          <t>7707282990953</t>
-        </is>
-      </c>
+          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr"/>
       <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="n">
         <v>8900</v>
       </c>
       <c r="F1468" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G1468" t="n">
         <v>0</v>
@@ -78550,21 +78550,21 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>PUSHER METALICO</t>
+          <t>Protector Solar Sunaid</t>
         </is>
       </c>
       <c r="C1469" t="inlineStr"/>
       <c r="D1469" t="inlineStr"/>
       <c r="E1469" t="n">
-        <v>4300</v>
+        <v>158000</v>
       </c>
       <c r="F1469" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1469" t="n">
         <v>0</v>
@@ -78600,21 +78600,25 @@
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
-        </is>
-      </c>
-      <c r="C1470" t="inlineStr"/>
+          <t>Prueba de embarazo esfero</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>7709299854228</t>
+        </is>
+      </c>
       <c r="D1470" t="inlineStr"/>
       <c r="E1470" t="n">
-        <v>17900</v>
+        <v>16500</v>
       </c>
       <c r="F1470" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1470" t="n">
         <v>0</v>
@@ -78650,25 +78654,25 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>Recolector de orina granandina</t>
+          <t>Prueba de embarazo HCG cassette begut</t>
         </is>
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>7707233050590</t>
+          <t>7707282990953</t>
         </is>
       </c>
       <c r="D1471" t="inlineStr"/>
       <c r="E1471" t="n">
-        <v>673</v>
+        <v>8900</v>
       </c>
       <c r="F1471" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="G1471" t="n">
         <v>0</v>
@@ -78696,7 +78700,7 @@
       </c>
       <c r="M1471" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1471" t="inlineStr"/>
@@ -78704,21 +78708,21 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
+          <t>PUSHER METALICO</t>
         </is>
       </c>
       <c r="C1472" t="inlineStr"/>
       <c r="D1472" t="inlineStr"/>
       <c r="E1472" t="n">
-        <v>3820</v>
+        <v>4300</v>
       </c>
       <c r="F1472" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1472" t="n">
         <v>0</v>
@@ -78754,21 +78758,21 @@
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>RegistroManual - Registro manual</t>
+          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
         </is>
       </c>
       <c r="C1473" t="inlineStr"/>
       <c r="D1473" t="inlineStr"/>
       <c r="E1473" t="n">
-        <v>0</v>
+        <v>17900</v>
       </c>
       <c r="F1473" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1473" t="n">
         <v>0</v>
@@ -78796,7 +78800,7 @@
       </c>
       <c r="M1473" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1473" t="inlineStr"/>
@@ -78804,21 +78808,25 @@
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>REMOVEDOR DE ESMALTE 60CC</t>
-        </is>
-      </c>
-      <c r="C1474" t="inlineStr"/>
+          <t>Recolector de orina granandina</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>7707233050590</t>
+        </is>
+      </c>
       <c r="D1474" t="inlineStr"/>
       <c r="E1474" t="n">
-        <v>3500</v>
+        <v>673</v>
       </c>
       <c r="F1474" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="G1474" t="n">
         <v>0</v>
@@ -78846,7 +78854,7 @@
       </c>
       <c r="M1474" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1474" t="inlineStr"/>
@@ -78854,25 +78862,21 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
-        </is>
-      </c>
-      <c r="C1475" t="inlineStr">
-        <is>
-          <t>7591005981270</t>
-        </is>
-      </c>
+          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr"/>
       <c r="D1475" t="inlineStr"/>
       <c r="E1475" t="n">
-        <v>9500</v>
+        <v>3820</v>
       </c>
       <c r="F1475" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1475" t="n">
         <v>0</v>
@@ -78908,25 +78912,21 @@
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
-        </is>
-      </c>
-      <c r="C1476" t="inlineStr">
-        <is>
-          <t>7503051868245</t>
-        </is>
-      </c>
+          <t>RegistroManual - Registro manual</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr"/>
       <c r="D1476" t="inlineStr"/>
       <c r="E1476" t="n">
-        <v>20900</v>
+        <v>0</v>
       </c>
       <c r="F1476" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1476" t="n">
         <v>0</v>
@@ -78954,7 +78954,7 @@
       </c>
       <c r="M1476" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1476" t="inlineStr"/>
@@ -78962,25 +78962,21 @@
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1MG X 20 TABL MK</t>
-        </is>
-      </c>
-      <c r="C1477" t="inlineStr">
-        <is>
-          <t>7702057079642</t>
-        </is>
-      </c>
+          <t>REMOVEDOR DE ESMALTE 60CC</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr"/>
       <c r="D1477" t="inlineStr"/>
       <c r="E1477" t="n">
-        <v>13000</v>
+        <v>3500</v>
       </c>
       <c r="F1477" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1477" t="n">
         <v>0</v>
@@ -79016,21 +79012,25 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>Ryaltris Spray Nasal 240 dosis</t>
-        </is>
-      </c>
-      <c r="C1478" t="inlineStr"/>
+          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>7591005981270</t>
+        </is>
+      </c>
       <c r="D1478" t="inlineStr"/>
       <c r="E1478" t="n">
-        <v>216400</v>
+        <v>9500</v>
       </c>
       <c r="F1478" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1478" t="n">
         <v>0</v>
@@ -79066,22 +79066,22 @@
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
         </is>
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>7706849116676</t>
+          <t>7503051868245</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr"/>
       <c r="E1479" t="n">
-        <v>31500</v>
+        <v>20900</v>
       </c>
       <c r="F1479" t="n">
         <v>1</v>
@@ -79120,21 +79120,25 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>SCOBIT PURGANTE 60GR</t>
-        </is>
-      </c>
-      <c r="C1480" t="inlineStr"/>
+          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>7702057079642</t>
+        </is>
+      </c>
       <c r="D1480" t="inlineStr"/>
       <c r="E1480" t="n">
-        <v>15238.095238</v>
+        <v>13000</v>
       </c>
       <c r="F1480" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1480" t="n">
         <v>0</v>
@@ -79162,7 +79166,7 @@
       </c>
       <c r="M1480" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1480" t="inlineStr"/>
@@ -79170,21 +79174,21 @@
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
+          <t>Ryaltris Spray Nasal 240 dosis</t>
         </is>
       </c>
       <c r="C1481" t="inlineStr"/>
       <c r="D1481" t="inlineStr"/>
       <c r="E1481" t="n">
-        <v>6554.621849</v>
+        <v>216400</v>
       </c>
       <c r="F1481" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1481" t="n">
         <v>0</v>
@@ -79212,7 +79216,7 @@
       </c>
       <c r="M1481" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1481" t="inlineStr"/>
@@ -79220,25 +79224,25 @@
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>SHAMPOO PANTENE COLAGENO</t>
+          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
         </is>
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>7500435191500</t>
+          <t>7706849116676</t>
         </is>
       </c>
       <c r="D1482" t="inlineStr"/>
       <c r="E1482" t="n">
-        <v>1429</v>
+        <v>31500</v>
       </c>
       <c r="F1482" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1482" t="n">
         <v>0</v>
@@ -79266,7 +79270,7 @@
       </c>
       <c r="M1482" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1482" t="inlineStr"/>
@@ -79274,21 +79278,21 @@
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>SILDENAFIL 50MG TQ</t>
+          <t>SCOBIT PURGANTE 60GR</t>
         </is>
       </c>
       <c r="C1483" t="inlineStr"/>
       <c r="D1483" t="inlineStr"/>
       <c r="E1483" t="n">
-        <v>5000</v>
+        <v>15238.095238</v>
       </c>
       <c r="F1483" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1483" t="n">
         <v>0</v>
@@ -79316,7 +79320,7 @@
       </c>
       <c r="M1483" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1483" t="inlineStr"/>
@@ -79324,25 +79328,21 @@
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>SILIMARINA 167MG EPANAT</t>
-        </is>
-      </c>
-      <c r="C1484" t="inlineStr">
-        <is>
-          <t>7706849115921</t>
-        </is>
-      </c>
+          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr"/>
       <c r="D1484" t="inlineStr"/>
       <c r="E1484" t="n">
-        <v>2000</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1484" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G1484" t="n">
         <v>0</v>
@@ -79370,7 +79370,7 @@
       </c>
       <c r="M1484" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1484" t="inlineStr"/>
@@ -79378,21 +79378,25 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>SMECTA 3GR NARANJA S/B</t>
-        </is>
-      </c>
-      <c r="C1485" t="inlineStr"/>
+          <t>SHAMPOO PANTENE COLAGENO</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>7500435191500</t>
+        </is>
+      </c>
       <c r="D1485" t="inlineStr"/>
       <c r="E1485" t="n">
-        <v>8900</v>
+        <v>1429</v>
       </c>
       <c r="F1485" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G1485" t="n">
         <v>0</v>
@@ -79420,7 +79424,7 @@
       </c>
       <c r="M1485" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1485" t="inlineStr"/>
@@ -79428,21 +79432,21 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>SONDA FOLEY 2 VIAS BAL #18</t>
+          <t>SILDENAFIL 50MG TQ</t>
         </is>
       </c>
       <c r="C1486" t="inlineStr"/>
       <c r="D1486" t="inlineStr"/>
       <c r="E1486" t="n">
-        <v>7500</v>
+        <v>5000</v>
       </c>
       <c r="F1486" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1486" t="n">
         <v>0</v>
@@ -79478,21 +79482,25 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>SONDA NELATON #6</t>
-        </is>
-      </c>
-      <c r="C1487" t="inlineStr"/>
+          <t>SILIMARINA 167MG EPANAT</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>7706849115921</t>
+        </is>
+      </c>
       <c r="D1487" t="inlineStr"/>
       <c r="E1487" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="F1487" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G1487" t="n">
         <v>0</v>
@@ -79528,21 +79536,21 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>SPRAY NASAL MOMETASONA 18ML</t>
+          <t>SMECTA 3GR NARANJA S/B</t>
         </is>
       </c>
       <c r="C1488" t="inlineStr"/>
       <c r="D1488" t="inlineStr"/>
       <c r="E1488" t="n">
-        <v>36900</v>
+        <v>8900</v>
       </c>
       <c r="F1488" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G1488" t="n">
         <v>0</v>
@@ -79578,25 +79586,21 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1489" t="inlineStr">
-        <is>
-          <t>7703712035034</t>
-        </is>
-      </c>
+          <t>SONDA FOLEY 2 VIAS BAL #18</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr"/>
       <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="n">
-        <v>14800</v>
+        <v>7500</v>
       </c>
       <c r="F1489" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1489" t="n">
         <v>0</v>
@@ -79632,21 +79636,21 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
+          <t>SONDA NELATON #6</t>
         </is>
       </c>
       <c r="C1490" t="inlineStr"/>
       <c r="D1490" t="inlineStr"/>
       <c r="E1490" t="n">
-        <v>3781.512605</v>
+        <v>2500</v>
       </c>
       <c r="F1490" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1490" t="n">
         <v>0</v>
@@ -79674,7 +79678,7 @@
       </c>
       <c r="M1490" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1490" t="inlineStr"/>
@@ -79682,21 +79686,21 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
+          <t>SPRAY NASAL MOMETASONA 18ML</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr"/>
       <c r="D1491" t="inlineStr"/>
       <c r="E1491" t="n">
-        <v>5210.084034</v>
+        <v>36900</v>
       </c>
       <c r="F1491" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1491" t="n">
         <v>0</v>
@@ -79724,7 +79728,7 @@
       </c>
       <c r="M1491" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1491" t="inlineStr"/>
@@ -79732,21 +79736,25 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
-        </is>
-      </c>
-      <c r="C1492" t="inlineStr"/>
+          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>7703712035034</t>
+        </is>
+      </c>
       <c r="D1492" t="inlineStr"/>
       <c r="E1492" t="n">
-        <v>8319.327730999999</v>
+        <v>14800</v>
       </c>
       <c r="F1492" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1492" t="n">
         <v>0</v>
@@ -79774,7 +79782,7 @@
       </c>
       <c r="M1492" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1492" t="inlineStr"/>
@@ -79782,18 +79790,18 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>SULZINC SUSP X 80ML HUMAX</t>
+          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
         </is>
       </c>
       <c r="C1493" t="inlineStr"/>
       <c r="D1493" t="inlineStr"/>
       <c r="E1493" t="n">
-        <v>22400</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1493" t="n">
         <v>1</v>
@@ -79824,7 +79832,7 @@
       </c>
       <c r="M1493" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1493" t="inlineStr"/>
@@ -79832,21 +79840,21 @@
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>SUNDARK FPS 60 CON TAPA</t>
+          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
         </is>
       </c>
       <c r="C1494" t="inlineStr"/>
       <c r="D1494" t="inlineStr"/>
       <c r="E1494" t="n">
-        <v>3781.512605</v>
+        <v>5210.084034</v>
       </c>
       <c r="F1494" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G1494" t="n">
         <v>0</v>
@@ -79882,21 +79890,21 @@
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>Synthroid 125 mcg</t>
+          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
         </is>
       </c>
       <c r="C1495" t="inlineStr"/>
       <c r="D1495" t="inlineStr"/>
       <c r="E1495" t="n">
-        <v>178000</v>
+        <v>8319.327730999999</v>
       </c>
       <c r="F1495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1495" t="n">
         <v>0</v>
@@ -79924,7 +79932,7 @@
       </c>
       <c r="M1495" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1495" t="inlineStr"/>
@@ -79932,25 +79940,21 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>Talco medicado Neofungina 40gm</t>
-        </is>
-      </c>
-      <c r="C1496" t="inlineStr">
-        <is>
-          <t>7706142707106</t>
-        </is>
-      </c>
+          <t>SULZINC SUSP X 80ML HUMAX</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr"/>
       <c r="D1496" t="inlineStr"/>
       <c r="E1496" t="n">
-        <v>14900</v>
+        <v>22400</v>
       </c>
       <c r="F1496" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1496" t="n">
         <v>0</v>
@@ -79986,21 +79990,21 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
+          <t>SUNDARK FPS 60 CON TAPA</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr"/>
       <c r="D1497" t="inlineStr"/>
       <c r="E1497" t="n">
-        <v>13300</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1497" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1497" t="n">
         <v>0</v>
@@ -80028,7 +80032,7 @@
       </c>
       <c r="M1497" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1497" t="inlineStr"/>
@@ -80036,21 +80040,21 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
+          <t>Synthroid 125 mcg</t>
         </is>
       </c>
       <c r="C1498" t="inlineStr"/>
       <c r="D1498" t="inlineStr"/>
       <c r="E1498" t="n">
-        <v>4874</v>
+        <v>178000</v>
       </c>
       <c r="F1498" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G1498" t="n">
         <v>0</v>
@@ -80078,7 +80082,7 @@
       </c>
       <c r="M1498" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1498" t="inlineStr"/>
@@ -80086,21 +80090,25 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
-        </is>
-      </c>
-      <c r="C1499" t="inlineStr"/>
+          <t>Talco medicado Neofungina 40gm</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>7706142707106</t>
+        </is>
+      </c>
       <c r="D1499" t="inlineStr"/>
       <c r="E1499" t="n">
-        <v>28800</v>
+        <v>14900</v>
       </c>
       <c r="F1499" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1499" t="n">
         <v>0</v>
@@ -80136,18 +80144,18 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
+          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
         </is>
       </c>
       <c r="C1500" t="inlineStr"/>
       <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="n">
-        <v>11596.638655</v>
+        <v>13300</v>
       </c>
       <c r="F1500" t="n">
         <v>0</v>
@@ -80178,7 +80186,7 @@
       </c>
       <c r="M1500" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1500" t="inlineStr"/>
@@ -80186,21 +80194,21 @@
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>TIJERA DE DOBLAR METALICA</t>
+          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
         </is>
       </c>
       <c r="C1501" t="inlineStr"/>
       <c r="D1501" t="inlineStr"/>
       <c r="E1501" t="n">
-        <v>3500</v>
+        <v>4874</v>
       </c>
       <c r="F1501" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="G1501" t="n">
         <v>0</v>
@@ -80228,7 +80236,7 @@
       </c>
       <c r="M1501" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1501" t="inlineStr"/>
@@ -80236,21 +80244,21 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
         </is>
       </c>
       <c r="C1502" t="inlineStr"/>
       <c r="D1502" t="inlineStr"/>
       <c r="E1502" t="n">
-        <v>3781.512605</v>
+        <v>28800</v>
       </c>
       <c r="F1502" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1502" t="n">
         <v>0</v>
@@ -80278,7 +80286,7 @@
       </c>
       <c r="M1502" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1502" t="inlineStr"/>
@@ -80286,18 +80294,18 @@
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
         </is>
       </c>
       <c r="C1503" t="inlineStr"/>
       <c r="D1503" t="inlineStr"/>
       <c r="E1503" t="n">
-        <v>29800</v>
+        <v>11596.638655</v>
       </c>
       <c r="F1503" t="n">
         <v>0</v>
@@ -80328,7 +80336,7 @@
       </c>
       <c r="M1503" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1503" t="inlineStr"/>
@@ -80336,25 +80344,21 @@
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
-        </is>
-      </c>
-      <c r="C1504" t="inlineStr">
-        <is>
-          <t>7702026149567</t>
-        </is>
-      </c>
+          <t>TIJERA DE DOBLAR METALICA</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr"/>
       <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="n">
-        <v>13500</v>
+        <v>3500</v>
       </c>
       <c r="F1504" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1504" t="n">
         <v>0</v>
@@ -80390,25 +80394,21 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>Toallas húmedas winny 24unidades</t>
-        </is>
-      </c>
-      <c r="C1505" t="inlineStr">
-        <is>
-          <t>7701021143655</t>
-        </is>
-      </c>
+          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr"/>
       <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="n">
-        <v>4033.613445</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1505" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G1505" t="n">
         <v>0</v>
@@ -80444,25 +80444,21 @@
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>Toallas maternas maternity</t>
-        </is>
-      </c>
-      <c r="C1506" t="inlineStr">
-        <is>
-          <t>7703252489526</t>
-        </is>
-      </c>
+          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr"/>
       <c r="D1506" t="inlineStr"/>
       <c r="E1506" t="n">
-        <v>16900</v>
+        <v>29800</v>
       </c>
       <c r="F1506" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1506" t="n">
         <v>0</v>
@@ -80498,25 +80494,25 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>Toallas Nosotras Rapigel x Und</t>
+          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
         </is>
       </c>
       <c r="C1507" t="inlineStr">
         <is>
-          <t>7702027416859</t>
+          <t>7702026149567</t>
         </is>
       </c>
       <c r="D1507" t="inlineStr"/>
       <c r="E1507" t="n">
-        <v>756.302521</v>
+        <v>13500</v>
       </c>
       <c r="F1507" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="G1507" t="n">
         <v>0</v>
@@ -80544,7 +80540,7 @@
       </c>
       <c r="M1507" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1507" t="inlineStr"/>
@@ -80552,21 +80548,25 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>TRAMADOL 50MG CAPSULA MP</t>
-        </is>
-      </c>
-      <c r="C1508" t="inlineStr"/>
+          <t>Toallas húmedas winny 24unidades</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>7701021143655</t>
+        </is>
+      </c>
       <c r="D1508" t="inlineStr"/>
       <c r="E1508" t="n">
-        <v>1500</v>
+        <v>4033.613445</v>
       </c>
       <c r="F1508" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G1508" t="n">
         <v>0</v>
@@ -80594,7 +80594,7 @@
       </c>
       <c r="M1508" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1508" t="inlineStr"/>
@@ -80602,25 +80602,25 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>Tramadol clorhidrato 100mg laquifar</t>
+          <t>Toallas maternas maternity</t>
         </is>
       </c>
       <c r="C1509" t="inlineStr">
         <is>
-          <t>7707019426977</t>
+          <t>7703252489526</t>
         </is>
       </c>
       <c r="D1509" t="inlineStr"/>
       <c r="E1509" t="n">
-        <v>1600</v>
+        <v>16900</v>
       </c>
       <c r="F1509" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1509" t="n">
         <v>0</v>
@@ -80656,21 +80656,25 @@
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>TRIGENTAX CREMA TBO X 20GR</t>
-        </is>
-      </c>
-      <c r="C1510" t="inlineStr"/>
+          <t>Toallas Nosotras Rapigel x Und</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>7702027416859</t>
+        </is>
+      </c>
       <c r="D1510" t="inlineStr"/>
       <c r="E1510" t="n">
-        <v>33500</v>
+        <v>756.302521</v>
       </c>
       <c r="F1510" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G1510" t="n">
         <v>0</v>
@@ -80698,7 +80702,7 @@
       </c>
       <c r="M1510" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1510" t="inlineStr"/>
@@ -80706,21 +80710,21 @@
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
+          <t>TRAMADOL 50MG CAPSULA MP</t>
         </is>
       </c>
       <c r="C1511" t="inlineStr"/>
       <c r="D1511" t="inlineStr"/>
       <c r="E1511" t="n">
-        <v>9000</v>
+        <v>1500</v>
       </c>
       <c r="F1511" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G1511" t="n">
         <v>0</v>
@@ -80756,21 +80760,25 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
-        </is>
-      </c>
-      <c r="C1512" t="inlineStr"/>
+          <t>Tramadol clorhidrato 100mg laquifar</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>7707019426977</t>
+        </is>
+      </c>
       <c r="D1512" t="inlineStr"/>
       <c r="E1512" t="n">
-        <v>10500</v>
+        <v>1600</v>
       </c>
       <c r="F1512" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1512" t="n">
         <v>0</v>
@@ -80806,21 +80814,21 @@
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
+          <t>TRIGENTAX CREMA TBO X 20GR</t>
         </is>
       </c>
       <c r="C1513" t="inlineStr"/>
       <c r="D1513" t="inlineStr"/>
       <c r="E1513" t="n">
-        <v>10500</v>
+        <v>33500</v>
       </c>
       <c r="F1513" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G1513" t="n">
         <v>0</v>
@@ -80856,21 +80864,21 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
+          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
         </is>
       </c>
       <c r="C1514" t="inlineStr"/>
       <c r="D1514" t="inlineStr"/>
       <c r="E1514" t="n">
-        <v>18800</v>
+        <v>9000</v>
       </c>
       <c r="F1514" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1514" t="n">
         <v>0</v>
@@ -80906,18 +80914,18 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
+          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
         </is>
       </c>
       <c r="C1515" t="inlineStr"/>
       <c r="D1515" t="inlineStr"/>
       <c r="E1515" t="n">
-        <v>13800</v>
+        <v>10500</v>
       </c>
       <c r="F1515" t="n">
         <v>4</v>
@@ -80956,21 +80964,21 @@
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
+          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
         </is>
       </c>
       <c r="C1516" t="inlineStr"/>
       <c r="D1516" t="inlineStr"/>
       <c r="E1516" t="n">
-        <v>7900</v>
+        <v>10500</v>
       </c>
       <c r="F1516" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G1516" t="n">
         <v>0</v>
@@ -81006,21 +81014,21 @@
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>VASELINA FC X 200GR YOMA</t>
+          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
         </is>
       </c>
       <c r="C1517" t="inlineStr"/>
       <c r="D1517" t="inlineStr"/>
       <c r="E1517" t="n">
-        <v>12521.008403</v>
+        <v>18800</v>
       </c>
       <c r="F1517" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1517" t="n">
         <v>0</v>
@@ -81048,7 +81056,7 @@
       </c>
       <c r="M1517" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1517" t="inlineStr"/>
@@ -81056,21 +81064,21 @@
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
+          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr"/>
       <c r="D1518" t="inlineStr"/>
       <c r="E1518" t="n">
-        <v>420.168067</v>
+        <v>13800</v>
       </c>
       <c r="F1518" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1518" t="n">
         <v>0</v>
@@ -81098,7 +81106,7 @@
       </c>
       <c r="M1518" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1518" t="inlineStr"/>
@@ -81106,25 +81114,21 @@
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
-        </is>
-      </c>
-      <c r="C1519" t="inlineStr">
-        <is>
-          <t>7708480649803</t>
-        </is>
-      </c>
+          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr"/>
       <c r="D1519" t="inlineStr"/>
       <c r="E1519" t="n">
-        <v>28000</v>
+        <v>7900</v>
       </c>
       <c r="F1519" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1519" t="n">
         <v>0</v>
@@ -81160,25 +81164,21 @@
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>Venda Elastica 6x5 y piel</t>
+          <t>VASELINA FC X 200GR YOMA</t>
         </is>
       </c>
       <c r="C1520" t="inlineStr"/>
-      <c r="D1520" t="inlineStr">
-        <is>
-          <t>SUBIO A 6200 ANTES 5700</t>
-        </is>
-      </c>
+      <c r="D1520" t="inlineStr"/>
       <c r="E1520" t="n">
-        <v>6200</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1520" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1520" t="n">
         <v>0</v>
@@ -81206,7 +81206,7 @@
       </c>
       <c r="M1520" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1520" t="inlineStr"/>
@@ -81214,21 +81214,21 @@
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
+          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
         </is>
       </c>
       <c r="C1521" t="inlineStr"/>
       <c r="D1521" t="inlineStr"/>
       <c r="E1521" t="n">
-        <v>5500</v>
+        <v>420.168067</v>
       </c>
       <c r="F1521" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1521" t="n">
         <v>0</v>
@@ -81256,7 +81256,7 @@
       </c>
       <c r="M1521" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1521" t="inlineStr"/>
@@ -81264,18 +81264,22 @@
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>Venta simple</t>
-        </is>
-      </c>
-      <c r="C1522" t="inlineStr"/>
+          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>7708480649803</t>
+        </is>
+      </c>
       <c r="D1522" t="inlineStr"/>
       <c r="E1522" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="F1522" t="n">
         <v>0</v>
@@ -81296,7 +81300,7 @@
       </c>
       <c r="K1522" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="L1522" t="inlineStr">
@@ -81304,24 +81308,32 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1522" t="inlineStr"/>
+      <c r="M1522" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1522" t="inlineStr"/>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
+          <t>Venda Elastica 6x5 y piel</t>
         </is>
       </c>
       <c r="C1523" t="inlineStr"/>
-      <c r="D1523" t="inlineStr"/>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>SUBIO A 6200 ANTES 5700</t>
+        </is>
+      </c>
       <c r="E1523" t="n">
-        <v>1000</v>
+        <v>6200</v>
       </c>
       <c r="F1523" t="n">
         <v>3</v>
@@ -81360,25 +81372,21 @@
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
-        </is>
-      </c>
-      <c r="C1524" t="inlineStr">
-        <is>
-          <t>793969226467</t>
-        </is>
-      </c>
+          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr"/>
       <c r="D1524" t="inlineStr"/>
       <c r="E1524" t="n">
-        <v>17000</v>
+        <v>5500</v>
       </c>
       <c r="F1524" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1524" t="n">
         <v>0</v>
@@ -81401,7 +81409,7 @@
       </c>
       <c r="L1524" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="M1524" t="inlineStr">
@@ -81414,21 +81422,21 @@
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>VINO CEREBRAL JARABE X 1100ML</t>
+          <t>Venta simple</t>
         </is>
       </c>
       <c r="C1525" t="inlineStr"/>
       <c r="D1525" t="inlineStr"/>
       <c r="E1525" t="n">
-        <v>48900</v>
+        <v>0</v>
       </c>
       <c r="F1525" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1525" t="n">
         <v>0</v>
@@ -81446,7 +81454,7 @@
       </c>
       <c r="K1525" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="L1525" t="inlineStr">
@@ -81454,31 +81462,27 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1525" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1525" t="inlineStr"/>
       <c r="N1525" t="inlineStr"/>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
+          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
         </is>
       </c>
       <c r="C1526" t="inlineStr"/>
       <c r="D1526" t="inlineStr"/>
       <c r="E1526" t="n">
-        <v>5400</v>
+        <v>1000</v>
       </c>
       <c r="F1526" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G1526" t="n">
         <v>0</v>
@@ -81514,21 +81518,25 @@
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
-        </is>
-      </c>
-      <c r="C1527" t="inlineStr"/>
+          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>793969226467</t>
+        </is>
+      </c>
       <c r="D1527" t="inlineStr"/>
       <c r="E1527" t="n">
-        <v>5500</v>
+        <v>17000</v>
       </c>
       <c r="F1527" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G1527" t="n">
         <v>0</v>
@@ -81551,7 +81559,7 @@
       </c>
       <c r="L1527" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="M1527" t="inlineStr">
@@ -81564,21 +81572,21 @@
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>WINNY PAÑAL ETP 6 X 30</t>
+          <t>VINO CEREBRAL JARABE X 1100ML</t>
         </is>
       </c>
       <c r="C1528" t="inlineStr"/>
       <c r="D1528" t="inlineStr"/>
       <c r="E1528" t="n">
-        <v>57000</v>
+        <v>48900</v>
       </c>
       <c r="F1528" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1528" t="n">
         <v>0</v>
@@ -81614,52 +81622,202 @@
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>YODO BLANCO FC X30ML</t>
+          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
         </is>
       </c>
       <c r="C1529" t="inlineStr"/>
       <c r="D1529" t="inlineStr"/>
       <c r="E1529" t="n">
+        <v>5400</v>
+      </c>
+      <c r="F1529" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1529" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1529" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1529" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1529" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1529" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1529" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1529" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1529" t="inlineStr"/>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr"/>
+      <c r="D1530" t="inlineStr"/>
+      <c r="E1530" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F1530" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1530" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1530" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1530" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1530" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1530" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1530" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1530" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1530" t="inlineStr"/>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>WINNY PAÑAL ETP 6 X 30</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr"/>
+      <c r="D1531" t="inlineStr"/>
+      <c r="E1531" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F1531" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1531" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1531" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1531" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1531" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1531" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1531" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1531" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1531" t="inlineStr"/>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>YODO BLANCO FC X30ML</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr"/>
+      <c r="D1532" t="inlineStr"/>
+      <c r="E1532" t="n">
         <v>6000</v>
       </c>
-      <c r="F1529" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1529" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1529" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1529" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1529" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="K1529" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="L1529" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="M1529" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="N1529" t="inlineStr"/>
+      <c r="F1532" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1532" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1532" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1532" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1532" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1532" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1532" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1532" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1532" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1532"/>
+  <dimension ref="A1:N1534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5289,7 +5289,7 @@
         <v>10840.336134</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -10167,7 +10167,7 @@
         <v>2500</v>
       </c>
       <c r="F183" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
         <v>840</v>
       </c>
       <c r="F284" t="n">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G284" t="n">
         <v>0</v>
@@ -15759,7 +15759,7 @@
         <v>6500</v>
       </c>
       <c r="F287" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G287" t="n">
         <v>0</v>
@@ -24171,7 +24171,7 @@
         <v>2500</v>
       </c>
       <c r="F445" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G445" t="n">
         <v>0</v>
@@ -24757,7 +24757,7 @@
         <v>9200</v>
       </c>
       <c r="F456" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G456" t="n">
         <v>0</v>
@@ -24981,7 +24981,7 @@
         <v>9200</v>
       </c>
       <c r="F460" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G460" t="n">
         <v>0</v>
@@ -25259,7 +25259,7 @@
         <v>10900</v>
       </c>
       <c r="F465" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G465" t="n">
         <v>0</v>
@@ -27915,7 +27915,7 @@
         <v>33445.38</v>
       </c>
       <c r="F515" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G515" t="n">
         <v>0</v>
@@ -29200,10 +29200,10 @@
       </c>
       <c r="D539" t="inlineStr"/>
       <c r="E539" t="n">
-        <v>16722.689076</v>
+        <v>18403.361345</v>
       </c>
       <c r="F539" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G539" t="n">
         <v>0</v>
@@ -31571,7 +31571,7 @@
         <v>2800</v>
       </c>
       <c r="F583" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G583" t="n">
         <v>0</v>
@@ -32771,7 +32771,7 @@
         <v>2800</v>
       </c>
       <c r="F605" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G605" t="n">
         <v>0</v>
@@ -32879,7 +32879,7 @@
         <v>8800</v>
       </c>
       <c r="F607" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G607" t="n">
         <v>0</v>
@@ -37875,7 +37875,7 @@
         <v>2857</v>
       </c>
       <c r="F701" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G701" t="n">
         <v>0</v>
@@ -38723,7 +38723,7 @@
         <v>3781.512605</v>
       </c>
       <c r="F717" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G717" t="n">
         <v>0</v>
@@ -43963,7 +43963,7 @@
         <v>16000</v>
       </c>
       <c r="F815" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G815" t="n">
         <v>0</v>
@@ -45795,7 +45795,7 @@
         <v>7900</v>
       </c>
       <c r="F849" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G849" t="n">
         <v>0</v>
@@ -47511,7 +47511,7 @@
         <v>13000</v>
       </c>
       <c r="F881" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G881" t="n">
         <v>0</v>
@@ -50753,7 +50753,7 @@
         <v>1681</v>
       </c>
       <c r="F942" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G942" t="n">
         <v>0</v>
@@ -52890,7 +52890,7 @@
         <v>1500</v>
       </c>
       <c r="F982" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G982" t="n">
         <v>0</v>
@@ -53384,7 +53384,7 @@
         <v>14500</v>
       </c>
       <c r="F991" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G991" t="n">
         <v>0</v>
@@ -55284,7 +55284,7 @@
         <v>12352.941176</v>
       </c>
       <c r="F1027" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1027" t="n">
         <v>0</v>
@@ -55612,7 +55612,7 @@
         <v>3900</v>
       </c>
       <c r="F1033" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G1033" t="n">
         <v>0</v>
@@ -57028,7 +57028,7 @@
         <v>52000</v>
       </c>
       <c r="F1059" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1059" t="n">
         <v>0</v>
@@ -60348,7 +60348,7 @@
         <v>6300</v>
       </c>
       <c r="F1121" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G1121" t="n">
         <v>0</v>
@@ -64838,7 +64838,7 @@
         <v>9300</v>
       </c>
       <c r="F1204" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1204" t="n">
         <v>0</v>
@@ -65648,7 +65648,7 @@
         <v>6302.521008</v>
       </c>
       <c r="F1219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1219" t="n">
         <v>0</v>
@@ -67894,7 +67894,7 @@
         <v>17600</v>
       </c>
       <c r="F1262" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1262" t="n">
         <v>0</v>
@@ -74260,21 +74260,21 @@
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
+          <t>Jabon liquido manos mi dia</t>
         </is>
       </c>
       <c r="C1386" t="inlineStr"/>
       <c r="D1386" t="inlineStr"/>
       <c r="E1386" t="n">
-        <v>4201.680672</v>
+        <v>5882.352941</v>
       </c>
       <c r="F1386" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1386" t="n">
         <v>0</v>
@@ -74310,12 +74310,12 @@
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
+          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr"/>
@@ -74324,7 +74324,7 @@
         <v>4201.680672</v>
       </c>
       <c r="F1387" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1387" t="n">
         <v>0</v>
@@ -74360,18 +74360,18 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>JABON PROTEX HERBAL 110GR</t>
+          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
         </is>
       </c>
       <c r="C1388" t="inlineStr"/>
       <c r="D1388" t="inlineStr"/>
       <c r="E1388" t="n">
-        <v>4537.815126</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1388" t="n">
         <v>2</v>
@@ -74410,22 +74410,18 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>JARABE ZETYGRIP FCO 60ML</t>
-        </is>
-      </c>
-      <c r="C1389" t="inlineStr">
-        <is>
-          <t>7709805542830</t>
-        </is>
-      </c>
+          <t>JABON PROTEX HERBAL 110GR</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr"/>
       <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="n">
-        <v>14000</v>
+        <v>4537.815126</v>
       </c>
       <c r="F1389" t="n">
         <v>2</v>
@@ -74456,7 +74452,7 @@
       </c>
       <c r="M1389" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1389" t="inlineStr"/>
@@ -74464,21 +74460,25 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>JERINGA DE 50ML</t>
-        </is>
-      </c>
-      <c r="C1390" t="inlineStr"/>
+          <t>JARABE ZETYGRIP FCO 60ML</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>7709805542830</t>
+        </is>
+      </c>
       <c r="D1390" t="inlineStr"/>
       <c r="E1390" t="n">
-        <v>2500</v>
+        <v>14000</v>
       </c>
       <c r="F1390" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1390" t="n">
         <v>0</v>
@@ -74514,21 +74514,21 @@
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>Jeringa desechable estéril 20ml impormedicas</t>
+          <t>JERINGA DE 50ML</t>
         </is>
       </c>
       <c r="C1391" t="inlineStr"/>
       <c r="D1391" t="inlineStr"/>
       <c r="E1391" t="n">
-        <v>920</v>
+        <v>2500</v>
       </c>
       <c r="F1391" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G1391" t="n">
         <v>0</v>
@@ -74556,7 +74556,7 @@
       </c>
       <c r="M1391" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1391" t="inlineStr"/>
@@ -74564,21 +74564,21 @@
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
+          <t>Jeringa desechable estéril 20ml impormedicas</t>
         </is>
       </c>
       <c r="C1392" t="inlineStr"/>
       <c r="D1392" t="inlineStr"/>
       <c r="E1392" t="n">
-        <v>1100</v>
+        <v>920</v>
       </c>
       <c r="F1392" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="G1392" t="n">
         <v>0</v>
@@ -74606,7 +74606,7 @@
       </c>
       <c r="M1392" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1392" t="inlineStr"/>
@@ -74614,21 +74614,21 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>Kelocate</t>
+          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
         </is>
       </c>
       <c r="C1393" t="inlineStr"/>
       <c r="D1393" t="inlineStr"/>
       <c r="E1393" t="n">
-        <v>180000</v>
+        <v>1100</v>
       </c>
       <c r="F1393" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G1393" t="n">
         <v>0</v>
@@ -74664,22 +74664,18 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
-        </is>
-      </c>
-      <c r="C1394" t="inlineStr">
-        <is>
-          <t>7702057073695</t>
-        </is>
-      </c>
+          <t>Kelocate</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr"/>
       <c r="D1394" t="inlineStr"/>
       <c r="E1394" t="n">
-        <v>19500</v>
+        <v>180000</v>
       </c>
       <c r="F1394" t="n">
         <v>0</v>
@@ -74718,22 +74714,22 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
+          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
         </is>
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>7709947559772</t>
+          <t>7702057073695</t>
         </is>
       </c>
       <c r="D1395" t="inlineStr"/>
       <c r="E1395" t="n">
-        <v>15000</v>
+        <v>19500</v>
       </c>
       <c r="F1395" t="n">
         <v>0</v>
@@ -74772,18 +74768,22 @@
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
-        </is>
-      </c>
-      <c r="C1396" t="inlineStr"/>
+          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>7709947559772</t>
+        </is>
+      </c>
       <c r="D1396" t="inlineStr"/>
       <c r="E1396" t="n">
-        <v>71000</v>
+        <v>15000</v>
       </c>
       <c r="F1396" t="n">
         <v>0</v>
@@ -74822,21 +74822,21 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
+          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
         </is>
       </c>
       <c r="C1397" t="inlineStr"/>
       <c r="D1397" t="inlineStr"/>
       <c r="E1397" t="n">
-        <v>37900</v>
+        <v>71000</v>
       </c>
       <c r="F1397" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1397" t="n">
         <v>0</v>
@@ -74872,25 +74872,21 @@
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>Levotiroxina 100mcg MK</t>
-        </is>
-      </c>
-      <c r="C1398" t="inlineStr">
-        <is>
-          <t>7702057715908</t>
-        </is>
-      </c>
+          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr"/>
       <c r="D1398" t="inlineStr"/>
       <c r="E1398" t="n">
-        <v>27900</v>
+        <v>37900</v>
       </c>
       <c r="F1398" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1398" t="n">
         <v>0</v>
@@ -74926,21 +74922,25 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>LIMA MAYOMI 10/180</t>
-        </is>
-      </c>
-      <c r="C1399" t="inlineStr"/>
+          <t>Levotiroxina 100mcg MK</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>7702057715908</t>
+        </is>
+      </c>
       <c r="D1399" t="inlineStr"/>
       <c r="E1399" t="n">
-        <v>3900</v>
+        <v>27900</v>
       </c>
       <c r="F1399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1399" t="n">
         <v>0</v>
@@ -74976,21 +74976,21 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
+          <t>LIMA MAYOMI 10/180</t>
         </is>
       </c>
       <c r="C1400" t="inlineStr"/>
       <c r="D1400" t="inlineStr"/>
       <c r="E1400" t="n">
-        <v>16807</v>
+        <v>3900</v>
       </c>
       <c r="F1400" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1400" t="n">
         <v>0</v>
@@ -75018,7 +75018,7 @@
       </c>
       <c r="M1400" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1400" t="inlineStr"/>
@@ -75026,21 +75026,21 @@
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
+          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
         </is>
       </c>
       <c r="C1401" t="inlineStr"/>
       <c r="D1401" t="inlineStr"/>
       <c r="E1401" t="n">
-        <v>15042.016807</v>
+        <v>16807</v>
       </c>
       <c r="F1401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1401" t="n">
         <v>0</v>
@@ -75076,21 +75076,21 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>LISTERINE CUIDADO TOTAL 180ML</t>
+          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
         </is>
       </c>
       <c r="C1402" t="inlineStr"/>
       <c r="D1402" t="inlineStr"/>
       <c r="E1402" t="n">
-        <v>16386.554622</v>
+        <v>15042.016807</v>
       </c>
       <c r="F1402" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1402" t="n">
         <v>0</v>
@@ -75126,21 +75126,21 @@
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
+          <t>LISTERINE CUIDADO TOTAL 180ML</t>
         </is>
       </c>
       <c r="C1403" t="inlineStr"/>
       <c r="D1403" t="inlineStr"/>
       <c r="E1403" t="n">
-        <v>3500</v>
+        <v>16386.554622</v>
       </c>
       <c r="F1403" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G1403" t="n">
         <v>0</v>
@@ -75168,7 +75168,7 @@
       </c>
       <c r="M1403" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1403" t="inlineStr"/>
@@ -75176,12 +75176,12 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
         </is>
       </c>
       <c r="C1404" t="inlineStr"/>
@@ -75190,7 +75190,7 @@
         <v>3500</v>
       </c>
       <c r="F1404" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G1404" t="n">
         <v>0</v>
@@ -75226,21 +75226,21 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
         </is>
       </c>
       <c r="C1405" t="inlineStr"/>
       <c r="D1405" t="inlineStr"/>
       <c r="E1405" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="F1405" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1405" t="n">
         <v>0</v>
@@ -75276,25 +75276,21 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>Losartan Tensofar 100 Mg</t>
-        </is>
-      </c>
-      <c r="C1406" t="inlineStr">
-        <is>
-          <t>7703546012119</t>
-        </is>
-      </c>
+          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr"/>
       <c r="D1406" t="inlineStr"/>
       <c r="E1406" t="n">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="F1406" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1406" t="n">
         <v>0</v>
@@ -75330,25 +75326,25 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+          <t>Losartan Tensofar 100 Mg</t>
         </is>
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>7501007528939</t>
+          <t>7703546012119</t>
         </is>
       </c>
       <c r="D1407" t="inlineStr"/>
       <c r="E1407" t="n">
-        <v>18907.563025</v>
+        <v>5000</v>
       </c>
       <c r="F1407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1407" t="n">
         <v>0</v>
@@ -75376,7 +75372,7 @@
       </c>
       <c r="M1407" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1407" t="inlineStr"/>
@@ -75384,18 +75380,22 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>MANTECA DE CACAO LABIAL LIMON</t>
-        </is>
-      </c>
-      <c r="C1408" t="inlineStr"/>
+          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>7501007528939</t>
+        </is>
+      </c>
       <c r="D1408" t="inlineStr"/>
       <c r="E1408" t="n">
-        <v>3361.344538</v>
+        <v>18907.563025</v>
       </c>
       <c r="F1408" t="n">
         <v>0</v>
@@ -75434,12 +75434,12 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
+          <t>MANTECA DE CACAO LABIAL LIMON</t>
         </is>
       </c>
       <c r="C1409" t="inlineStr"/>
@@ -75484,21 +75484,21 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>Mega sex</t>
+          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
         </is>
       </c>
       <c r="C1410" t="inlineStr"/>
       <c r="D1410" t="inlineStr"/>
       <c r="E1410" t="n">
-        <v>3200</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1410" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G1410" t="n">
         <v>0</v>
@@ -75526,7 +75526,7 @@
       </c>
       <c r="M1410" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1410" t="inlineStr"/>
@@ -75534,29 +75534,21 @@
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>Melatonina 3mg</t>
-        </is>
-      </c>
-      <c r="C1411" t="inlineStr">
-        <is>
-          <t>7706849112906</t>
-        </is>
-      </c>
-      <c r="D1411" t="inlineStr">
-        <is>
-          <t>producto nuevo</t>
-        </is>
-      </c>
+          <t>Mega sex</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr"/>
+      <c r="D1411" t="inlineStr"/>
       <c r="E1411" t="n">
-        <v>52000</v>
+        <v>3200</v>
       </c>
       <c r="F1411" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G1411" t="n">
         <v>0</v>
@@ -75592,22 +75584,26 @@
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
+          <t>Melatonina 3mg</t>
         </is>
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>7707529435209</t>
-        </is>
-      </c>
-      <c r="D1412" t="inlineStr"/>
+          <t>7706849112906</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>producto nuevo</t>
+        </is>
+      </c>
       <c r="E1412" t="n">
-        <v>36000</v>
+        <v>52000</v>
       </c>
       <c r="F1412" t="n">
         <v>0</v>
@@ -75646,22 +75642,22 @@
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>Meloxicam 15mg AG</t>
+          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
         </is>
       </c>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>7706569020437</t>
+          <t>7707529435209</t>
         </is>
       </c>
       <c r="D1413" t="inlineStr"/>
       <c r="E1413" t="n">
-        <v>1500</v>
+        <v>36000</v>
       </c>
       <c r="F1413" t="n">
         <v>0</v>
@@ -75700,21 +75696,25 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
-        </is>
-      </c>
-      <c r="C1414" t="inlineStr"/>
+          <t>Meloxicam 15mg AG</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>7706569020437</t>
+        </is>
+      </c>
       <c r="D1414" t="inlineStr"/>
       <c r="E1414" t="n">
-        <v>9700</v>
+        <v>1500</v>
       </c>
       <c r="F1414" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1414" t="n">
         <v>0</v>
@@ -75750,25 +75750,21 @@
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>MELOXICAM COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1415" t="inlineStr">
-        <is>
-          <t>7703712036253</t>
-        </is>
-      </c>
+          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr"/>
       <c r="D1415" t="inlineStr"/>
       <c r="E1415" t="n">
-        <v>1300</v>
+        <v>9700</v>
       </c>
       <c r="F1415" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1415" t="n">
         <v>0</v>
@@ -75794,31 +75790,35 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1415" t="inlineStr"/>
+      <c r="M1415" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1415" t="inlineStr"/>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>metformina 850 mg pisa</t>
+          <t>MELOXICAM COASPHARMA</t>
         </is>
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>7501125188039</t>
+          <t>7703712036253</t>
         </is>
       </c>
       <c r="D1416" t="inlineStr"/>
       <c r="E1416" t="n">
-        <v>5500</v>
+        <v>1300</v>
       </c>
       <c r="F1416" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G1416" t="n">
         <v>0</v>
@@ -75844,35 +75844,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1416" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1416" t="inlineStr"/>
       <c r="N1416" t="inlineStr"/>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10MG RECIPE</t>
+          <t>metformina 850 mg pisa</t>
         </is>
       </c>
       <c r="C1417" t="inlineStr">
         <is>
-          <t>7702195084355</t>
+          <t>7501125188039</t>
         </is>
       </c>
       <c r="D1417" t="inlineStr"/>
       <c r="E1417" t="n">
-        <v>1000</v>
+        <v>5500</v>
       </c>
       <c r="F1417" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G1417" t="n">
         <v>0</v>
@@ -75908,25 +75904,25 @@
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>MICROPOR 1X3 Y</t>
+          <t>METOCLOPRAMIDA 10MG RECIPE</t>
         </is>
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>7707282990205</t>
+          <t>7702195084355</t>
         </is>
       </c>
       <c r="D1418" t="inlineStr"/>
       <c r="E1418" t="n">
-        <v>5300</v>
+        <v>1000</v>
       </c>
       <c r="F1418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1418" t="n">
         <v>0</v>
@@ -75962,25 +75958,25 @@
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>MICROPOR CINTA 1/2X5Y</t>
+          <t>MICROPOR 1X3 Y</t>
         </is>
       </c>
       <c r="C1419" t="inlineStr">
         <is>
-          <t>7707282990182</t>
+          <t>7707282990205</t>
         </is>
       </c>
       <c r="D1419" t="inlineStr"/>
       <c r="E1419" t="n">
-        <v>3900</v>
+        <v>5300</v>
       </c>
       <c r="F1419" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G1419" t="n">
         <v>0</v>
@@ -76016,21 +76012,25 @@
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>MICROPORE COLOR PIEL 2YARDAS</t>
-        </is>
-      </c>
-      <c r="C1420" t="inlineStr"/>
+          <t>MICROPOR CINTA 1/2X5Y</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>7707282990182</t>
+        </is>
+      </c>
       <c r="D1420" t="inlineStr"/>
       <c r="E1420" t="n">
-        <v>3700</v>
+        <v>3900</v>
       </c>
       <c r="F1420" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G1420" t="n">
         <v>0</v>
@@ -76066,18 +76066,18 @@
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
+          <t>MICROPORE COLOR PIEL 2YARDAS</t>
         </is>
       </c>
       <c r="C1421" t="inlineStr"/>
       <c r="D1421" t="inlineStr"/>
       <c r="E1421" t="n">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="F1421" t="n">
         <v>0</v>
@@ -76116,22 +76116,18 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>MIELTERTOS JARABE X 240ML</t>
-        </is>
-      </c>
-      <c r="C1422" t="inlineStr">
-        <is>
-          <t>7707232095608</t>
-        </is>
-      </c>
+          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr"/>
       <c r="D1422" t="inlineStr"/>
       <c r="E1422" t="n">
-        <v>34500</v>
+        <v>4000</v>
       </c>
       <c r="F1422" t="n">
         <v>0</v>
@@ -76170,18 +76166,22 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>MOÑAS PARA EL PELO COLOR YIMEIJIA</t>
-        </is>
-      </c>
-      <c r="C1423" t="inlineStr"/>
+          <t>MIELTERTOS JARABE X 240ML</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>7707232095608</t>
+        </is>
+      </c>
       <c r="D1423" t="inlineStr"/>
       <c r="E1423" t="n">
-        <v>4201.680672</v>
+        <v>34500</v>
       </c>
       <c r="F1423" t="n">
         <v>0</v>
@@ -76212,7 +76212,7 @@
       </c>
       <c r="M1423" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1423" t="inlineStr"/>
@@ -76220,25 +76220,21 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
+          <t>MOÑAS PARA EL PELO COLOR YIMEIJIA</t>
         </is>
       </c>
       <c r="C1424" t="inlineStr"/>
-      <c r="D1424" t="inlineStr">
-        <is>
-          <t>subio precio hector</t>
-        </is>
-      </c>
+      <c r="D1424" t="inlineStr"/>
       <c r="E1424" t="n">
-        <v>22700</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1424" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1424" t="n">
         <v>0</v>
@@ -76266,7 +76262,7 @@
       </c>
       <c r="M1424" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1424" t="inlineStr"/>
@@ -76274,21 +76270,25 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
+          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
         </is>
       </c>
       <c r="C1425" t="inlineStr"/>
-      <c r="D1425" t="inlineStr"/>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>subio precio hector</t>
+        </is>
+      </c>
       <c r="E1425" t="n">
-        <v>5500</v>
+        <v>22700</v>
       </c>
       <c r="F1425" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G1425" t="n">
         <v>0</v>
@@ -76324,21 +76324,21 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>NEOSALDINA TABLETA X UND</t>
+          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
         </is>
       </c>
       <c r="C1426" t="inlineStr"/>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="n">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="F1426" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1426" t="n">
         <v>0</v>
@@ -76374,21 +76374,21 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>NIFEDIPINO 30MG NOVAMED</t>
+          <t>NEOSALDINA TABLETA X UND</t>
         </is>
       </c>
       <c r="C1427" t="inlineStr"/>
       <c r="D1427" t="inlineStr"/>
       <c r="E1427" t="n">
-        <v>19000</v>
+        <v>2500</v>
       </c>
       <c r="F1427" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G1427" t="n">
         <v>0</v>
@@ -76424,21 +76424,21 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
+          <t>NIFEDIPINO 30MG NOVAMED</t>
         </is>
       </c>
       <c r="C1428" t="inlineStr"/>
       <c r="D1428" t="inlineStr"/>
       <c r="E1428" t="n">
-        <v>23000</v>
+        <v>19000</v>
       </c>
       <c r="F1428" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1428" t="n">
         <v>0</v>
@@ -76474,18 +76474,18 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>NITOXIPAR X 6 TABLETAS</t>
+          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
         </is>
       </c>
       <c r="C1429" t="inlineStr"/>
       <c r="D1429" t="inlineStr"/>
       <c r="E1429" t="n">
-        <v>24500</v>
+        <v>23000</v>
       </c>
       <c r="F1429" t="n">
         <v>3</v>
@@ -76524,21 +76524,21 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>NORAVER SPRAY CEREZA 120ML</t>
+          <t>NITOXIPAR X 6 TABLETAS</t>
         </is>
       </c>
       <c r="C1430" t="inlineStr"/>
       <c r="D1430" t="inlineStr"/>
       <c r="E1430" t="n">
-        <v>52900</v>
+        <v>24500</v>
       </c>
       <c r="F1430" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1430" t="n">
         <v>0</v>
@@ -76574,25 +76574,21 @@
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
-        </is>
-      </c>
-      <c r="C1431" t="inlineStr">
-        <is>
-          <t>7702027041662</t>
-        </is>
-      </c>
+          <t>NORAVER SPRAY CEREZA 120ML</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr"/>
       <c r="D1431" t="inlineStr"/>
       <c r="E1431" t="n">
-        <v>6300</v>
+        <v>52900</v>
       </c>
       <c r="F1431" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1431" t="n">
         <v>0</v>
@@ -76628,18 +76624,22 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
-        </is>
-      </c>
-      <c r="C1432" t="inlineStr"/>
+          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>7702027041662</t>
+        </is>
+      </c>
       <c r="D1432" t="inlineStr"/>
       <c r="E1432" t="n">
-        <v>8823.529412</v>
+        <v>6300</v>
       </c>
       <c r="F1432" t="n">
         <v>0</v>
@@ -76670,7 +76670,7 @@
       </c>
       <c r="M1432" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1432" t="inlineStr"/>
@@ -76678,7 +76678,7 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
@@ -76686,11 +76686,7 @@
           <t>NOSOTRAS JABON INTIMO X 200ML</t>
         </is>
       </c>
-      <c r="C1433" t="inlineStr">
-        <is>
-          <t>7702026158644</t>
-        </is>
-      </c>
+      <c r="C1433" t="inlineStr"/>
       <c r="D1433" t="inlineStr"/>
       <c r="E1433" t="n">
         <v>8823.529412</v>
@@ -76732,25 +76728,25 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JBE 120ML</t>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
         </is>
       </c>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>7707355053363</t>
+          <t>7702026158644</t>
         </is>
       </c>
       <c r="D1434" t="inlineStr"/>
       <c r="E1434" t="n">
-        <v>22700</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1434" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1434" t="n">
         <v>0</v>
@@ -76778,7 +76774,7 @@
       </c>
       <c r="M1434" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1434" t="inlineStr"/>
@@ -76786,25 +76782,25 @@
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+          <t>NOXPIRIN JUNIOR JBE 120ML</t>
         </is>
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>7707355053356</t>
+          <t>7707355053363</t>
         </is>
       </c>
       <c r="D1435" t="inlineStr"/>
       <c r="E1435" t="n">
-        <v>17200</v>
+        <v>22700</v>
       </c>
       <c r="F1435" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>
@@ -76840,21 +76836,25 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>NUTRIBELL ACEITE DE COCO</t>
-        </is>
-      </c>
-      <c r="C1436" t="inlineStr"/>
+          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>7707355053356</t>
+        </is>
+      </c>
       <c r="D1436" t="inlineStr"/>
       <c r="E1436" t="n">
-        <v>2700</v>
+        <v>17200</v>
       </c>
       <c r="F1436" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1436" t="n">
         <v>0</v>
@@ -76890,29 +76890,21 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>Omega 3 6 9 suplemento totalmax</t>
-        </is>
-      </c>
-      <c r="C1437" t="inlineStr">
-        <is>
-          <t>7707529434974</t>
-        </is>
-      </c>
-      <c r="D1437" t="inlineStr">
-        <is>
-          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
-        </is>
-      </c>
+          <t>NUTRIBELL ACEITE DE COCO</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr"/>
+      <c r="D1437" t="inlineStr"/>
       <c r="E1437" t="n">
-        <v>35000</v>
+        <v>2700</v>
       </c>
       <c r="F1437" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1437" t="n">
         <v>0</v>
@@ -76948,21 +76940,29 @@
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1438" t="inlineStr"/>
-      <c r="D1438" t="inlineStr"/>
+          <t>Omega 3 6 9 suplemento totalmax</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>7707529434974</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
+        </is>
+      </c>
       <c r="E1438" t="n">
-        <v>5500</v>
+        <v>35000</v>
       </c>
       <c r="F1438" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1438" t="n">
         <v>0</v>
@@ -76998,22 +76998,18 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
-        </is>
-      </c>
-      <c r="C1439" t="inlineStr">
-        <is>
-          <t>7707529435940</t>
-        </is>
-      </c>
+          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr"/>
       <c r="D1439" t="inlineStr"/>
       <c r="E1439" t="n">
-        <v>35000</v>
+        <v>5500</v>
       </c>
       <c r="F1439" t="n">
         <v>0</v>
@@ -77052,21 +77048,25 @@
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
-        </is>
-      </c>
-      <c r="C1440" t="inlineStr"/>
+          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>7707529435940</t>
+        </is>
+      </c>
       <c r="D1440" t="inlineStr"/>
       <c r="E1440" t="n">
-        <v>48000</v>
+        <v>35000</v>
       </c>
       <c r="F1440" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1440" t="n">
         <v>0</v>
@@ -77102,25 +77102,21 @@
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>OROCAL CALCIO 600MG</t>
+          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
         </is>
       </c>
       <c r="C1441" t="inlineStr"/>
-      <c r="D1441" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="D1441" t="inlineStr"/>
       <c r="E1441" t="n">
-        <v>30500</v>
+        <v>48000</v>
       </c>
       <c r="F1441" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1441" t="n">
         <v>0</v>
@@ -77156,18 +77152,22 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>PALA DE MADERA RASPACALLO</t>
+          <t>OROCAL CALCIO 600MG</t>
         </is>
       </c>
       <c r="C1442" t="inlineStr"/>
-      <c r="D1442" t="inlineStr"/>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E1442" t="n">
-        <v>4000</v>
+        <v>30500</v>
       </c>
       <c r="F1442" t="n">
         <v>1</v>
@@ -77206,21 +77206,21 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>PALO DE NARANJO X UNIDAD</t>
+          <t>PALA DE MADERA RASPACALLO</t>
         </is>
       </c>
       <c r="C1443" t="inlineStr"/>
       <c r="D1443" t="inlineStr"/>
       <c r="E1443" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="F1443" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G1443" t="n">
         <v>0</v>
@@ -77256,25 +77256,21 @@
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
-        </is>
-      </c>
-      <c r="C1444" t="inlineStr">
-        <is>
-          <t>7704412170896</t>
-        </is>
-      </c>
+          <t>PALO DE NARANJO X UNIDAD</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr"/>
       <c r="D1444" t="inlineStr"/>
       <c r="E1444" t="n">
-        <v>6200</v>
+        <v>400</v>
       </c>
       <c r="F1444" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G1444" t="n">
         <v>0</v>
@@ -77310,18 +77306,22 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
-        </is>
-      </c>
-      <c r="C1445" t="inlineStr"/>
+          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>7704412170896</t>
+        </is>
+      </c>
       <c r="D1445" t="inlineStr"/>
       <c r="E1445" t="n">
-        <v>14285.714286</v>
+        <v>6200</v>
       </c>
       <c r="F1445" t="n">
         <v>1</v>
@@ -77352,7 +77352,7 @@
       </c>
       <c r="M1445" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1445" t="inlineStr"/>
@@ -77360,18 +77360,18 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
+          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
         </is>
       </c>
       <c r="C1446" t="inlineStr"/>
       <c r="D1446" t="inlineStr"/>
       <c r="E1446" t="n">
-        <v>28991.596639</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1446" t="n">
         <v>1</v>
@@ -77410,18 +77410,18 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
         </is>
       </c>
       <c r="C1447" t="inlineStr"/>
       <c r="D1447" t="inlineStr"/>
       <c r="E1447" t="n">
-        <v>41176.470588</v>
+        <v>28991.596639</v>
       </c>
       <c r="F1447" t="n">
         <v>1</v>
@@ -77460,22 +77460,18 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Pañales Winny Etapa 5 X PAQUETE</t>
-        </is>
-      </c>
-      <c r="C1448" t="inlineStr">
-        <is>
-          <t>7701021114174</t>
-        </is>
-      </c>
+          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr"/>
       <c r="D1448" t="inlineStr"/>
       <c r="E1448" t="n">
-        <v>41849</v>
+        <v>41176.470588</v>
       </c>
       <c r="F1448" t="n">
         <v>1</v>
@@ -77514,21 +77510,25 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>PAÑALWINNY ETA 5 X 16 UND</t>
-        </is>
-      </c>
-      <c r="C1449" t="inlineStr"/>
+          <t>Pañales Winny Etapa 5 X PAQUETE</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>7701021114174</t>
+        </is>
+      </c>
       <c r="D1449" t="inlineStr"/>
       <c r="E1449" t="n">
-        <v>24369.747899</v>
+        <v>41849</v>
       </c>
       <c r="F1449" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1449" t="n">
         <v>0</v>
@@ -77564,21 +77564,21 @@
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>pañitos humedos pequeñin 100unidades</t>
+          <t>PAÑALWINNY ETA 5 X 16 UND</t>
         </is>
       </c>
       <c r="C1450" t="inlineStr"/>
       <c r="D1450" t="inlineStr"/>
       <c r="E1450" t="n">
-        <v>10925</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1450" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1450" t="n">
         <v>0</v>
@@ -77614,21 +77614,21 @@
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
+          <t>pañitos humedos pequeñin 100unidades</t>
         </is>
       </c>
       <c r="C1451" t="inlineStr"/>
       <c r="D1451" t="inlineStr"/>
       <c r="E1451" t="n">
-        <v>14900</v>
+        <v>10925</v>
       </c>
       <c r="F1451" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1451" t="n">
         <v>0</v>
@@ -77656,7 +77656,7 @@
       </c>
       <c r="M1451" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1451" t="inlineStr"/>
@@ -77664,21 +77664,21 @@
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Panotil B x 8ML</t>
+          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
         </is>
       </c>
       <c r="C1452" t="inlineStr"/>
       <c r="D1452" t="inlineStr"/>
       <c r="E1452" t="n">
-        <v>26400</v>
+        <v>14900</v>
       </c>
       <c r="F1452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1452" t="n">
         <v>0</v>
@@ -77714,25 +77714,21 @@
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>PANTENE ACONDICIONADOR</t>
-        </is>
-      </c>
-      <c r="C1453" t="inlineStr">
-        <is>
-          <t>7500435153683</t>
-        </is>
-      </c>
+          <t>Panotil B x 8ML</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr"/>
       <c r="D1453" t="inlineStr"/>
       <c r="E1453" t="n">
-        <v>1500</v>
+        <v>26400</v>
       </c>
       <c r="F1453" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1453" t="n">
         <v>0</v>
@@ -77768,25 +77764,25 @@
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>PARCHE ACNE FIGURAS</t>
+          <t>PANTENE ACONDICIONADOR</t>
         </is>
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>6971622250767</t>
+          <t>7500435153683</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr"/>
       <c r="E1454" t="n">
-        <v>5882.352941</v>
+        <v>1500</v>
       </c>
       <c r="F1454" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1454" t="n">
         <v>0</v>
@@ -77814,7 +77810,7 @@
       </c>
       <c r="M1454" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1454" t="inlineStr"/>
@@ -77822,21 +77818,25 @@
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>Parche Ocular Colostol</t>
-        </is>
-      </c>
-      <c r="C1455" t="inlineStr"/>
+          <t>PARCHE ACNE FIGURAS</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>6971622250767</t>
+        </is>
+      </c>
       <c r="D1455" t="inlineStr"/>
       <c r="E1455" t="n">
-        <v>1300</v>
+        <v>5882.352941</v>
       </c>
       <c r="F1455" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G1455" t="n">
         <v>0</v>
@@ -77864,7 +77864,7 @@
       </c>
       <c r="M1455" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1455" t="inlineStr"/>
@@ -77872,25 +77872,21 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
-        </is>
-      </c>
-      <c r="C1456" t="inlineStr">
-        <is>
-          <t>7501033957413</t>
-        </is>
-      </c>
+          <t>Parche Ocular Colostol</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr"/>
       <c r="D1456" t="inlineStr"/>
       <c r="E1456" t="n">
-        <v>10600</v>
+        <v>1300</v>
       </c>
       <c r="F1456" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G1456" t="n">
         <v>0</v>
@@ -77926,26 +77922,22 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
+          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
         </is>
       </c>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>7501033961557</t>
-        </is>
-      </c>
-      <c r="D1457" t="inlineStr">
-        <is>
-          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
-        </is>
-      </c>
+          <t>7501033957413</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr"/>
       <c r="E1457" t="n">
-        <v>10900</v>
+        <v>10600</v>
       </c>
       <c r="F1457" t="n">
         <v>0</v>
@@ -77984,29 +77976,29 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
         </is>
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>7501033957376</t>
+          <t>7501033961557</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">
         <is>
-          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
         </is>
       </c>
       <c r="E1458" t="n">
         <v>10900</v>
       </c>
       <c r="F1458" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1458" t="n">
         <v>0</v>
@@ -78042,21 +78034,29 @@
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>PEGANTE GLUE X 10GR X UND</t>
-        </is>
-      </c>
-      <c r="C1459" t="inlineStr"/>
-      <c r="D1459" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>7501033957376</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+        </is>
+      </c>
       <c r="E1459" t="n">
-        <v>2000</v>
+        <v>10900</v>
       </c>
       <c r="F1459" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1459" t="n">
         <v>0</v>
@@ -78092,21 +78092,21 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>PEINETA COLA DE RATON METALICA</t>
+          <t>PEGANTE GLUE X 10GR X UND</t>
         </is>
       </c>
       <c r="C1460" t="inlineStr"/>
       <c r="D1460" t="inlineStr"/>
       <c r="E1460" t="n">
-        <v>4700</v>
+        <v>2000</v>
       </c>
       <c r="F1460" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1460" t="n">
         <v>0</v>
@@ -78142,18 +78142,18 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>PERFILADORES DE CEJAS</t>
+          <t>PEINETA COLA DE RATON METALICA</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr"/>
       <c r="D1461" t="inlineStr"/>
       <c r="E1461" t="n">
-        <v>3900</v>
+        <v>4700</v>
       </c>
       <c r="F1461" t="n">
         <v>1</v>
@@ -78192,18 +78192,18 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
+          <t>PERFILADORES DE CEJAS</t>
         </is>
       </c>
       <c r="C1462" t="inlineStr"/>
       <c r="D1462" t="inlineStr"/>
       <c r="E1462" t="n">
-        <v>27983.193277</v>
+        <v>3900</v>
       </c>
       <c r="F1462" t="n">
         <v>1</v>
@@ -78234,7 +78234,7 @@
       </c>
       <c r="M1462" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1462" t="inlineStr"/>
@@ -78242,21 +78242,21 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>POPETAS SURTIDAS X UND</t>
+          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
         </is>
       </c>
       <c r="C1463" t="inlineStr"/>
       <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="n">
-        <v>2521.008403</v>
+        <v>27983.193277</v>
       </c>
       <c r="F1463" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1463" t="n">
         <v>0</v>
@@ -78292,21 +78292,21 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+          <t>POPETAS SURTIDAS X UND</t>
         </is>
       </c>
       <c r="C1464" t="inlineStr"/>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="n">
-        <v>20500</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1464" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1464" t="n">
         <v>0</v>
@@ -78334,7 +78334,7 @@
       </c>
       <c r="M1464" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1464" t="inlineStr"/>
@@ -78342,29 +78342,21 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>privatos miel limon la francol 120ml</t>
-        </is>
-      </c>
-      <c r="C1465" t="inlineStr">
-        <is>
-          <t>7702207163948</t>
-        </is>
-      </c>
-      <c r="D1465" t="inlineStr">
-        <is>
-          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
-        </is>
-      </c>
+          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr"/>
+      <c r="D1465" t="inlineStr"/>
       <c r="E1465" t="n">
-        <v>35900</v>
+        <v>20500</v>
       </c>
       <c r="F1465" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1465" t="n">
         <v>0</v>
@@ -78400,21 +78392,29 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
-        </is>
-      </c>
-      <c r="C1466" t="inlineStr"/>
-      <c r="D1466" t="inlineStr"/>
+          <t>privatos miel limon la francol 120ml</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>7702207163948</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
+        </is>
+      </c>
       <c r="E1466" t="n">
-        <v>0</v>
+        <v>35900</v>
       </c>
       <c r="F1466" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1466" t="n">
         <v>0</v>
@@ -78442,7 +78442,7 @@
       </c>
       <c r="M1466" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1466" t="inlineStr"/>
@@ -78450,21 +78450,21 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>778</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>PROTECTOR NOSOTRAS LARGOS</t>
+          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
         </is>
       </c>
       <c r="C1467" t="inlineStr"/>
       <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="n">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="F1467" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1467" t="n">
         <v>0</v>
@@ -78492,7 +78492,7 @@
       </c>
       <c r="M1467" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1467" t="inlineStr"/>
@@ -78500,18 +78500,18 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
+          <t>PROTECTOR NOSOTRAS LARGOS</t>
         </is>
       </c>
       <c r="C1468" t="inlineStr"/>
       <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="n">
-        <v>8900</v>
+        <v>3700</v>
       </c>
       <c r="F1468" t="n">
         <v>1</v>
@@ -78550,21 +78550,21 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>Protector Solar Sunaid</t>
+          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
         </is>
       </c>
       <c r="C1469" t="inlineStr"/>
       <c r="D1469" t="inlineStr"/>
       <c r="E1469" t="n">
-        <v>158000</v>
+        <v>8900</v>
       </c>
       <c r="F1469" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1469" t="n">
         <v>0</v>
@@ -78600,25 +78600,21 @@
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>Prueba de embarazo esfero</t>
-        </is>
-      </c>
-      <c r="C1470" t="inlineStr">
-        <is>
-          <t>7709299854228</t>
-        </is>
-      </c>
+          <t>Protector Solar Sunaid</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr"/>
       <c r="D1470" t="inlineStr"/>
       <c r="E1470" t="n">
-        <v>16500</v>
+        <v>158000</v>
       </c>
       <c r="F1470" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1470" t="n">
         <v>0</v>
@@ -78654,25 +78650,25 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>Prueba de embarazo HCG cassette begut</t>
+          <t>Prueba de embarazo esfero</t>
         </is>
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>7707282990953</t>
+          <t>7709299854228</t>
         </is>
       </c>
       <c r="D1471" t="inlineStr"/>
       <c r="E1471" t="n">
-        <v>8900</v>
+        <v>16500</v>
       </c>
       <c r="F1471" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G1471" t="n">
         <v>0</v>
@@ -78708,21 +78704,25 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>PUSHER METALICO</t>
-        </is>
-      </c>
-      <c r="C1472" t="inlineStr"/>
+          <t>Prueba de embarazo HCG cassette begut</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>7707282990953</t>
+        </is>
+      </c>
       <c r="D1472" t="inlineStr"/>
       <c r="E1472" t="n">
-        <v>4300</v>
+        <v>8900</v>
       </c>
       <c r="F1472" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1472" t="n">
         <v>0</v>
@@ -78758,21 +78758,21 @@
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
+          <t>PUSHER METALICO</t>
         </is>
       </c>
       <c r="C1473" t="inlineStr"/>
       <c r="D1473" t="inlineStr"/>
       <c r="E1473" t="n">
-        <v>17900</v>
+        <v>4300</v>
       </c>
       <c r="F1473" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1473" t="n">
         <v>0</v>
@@ -78808,25 +78808,21 @@
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>Recolector de orina granandina</t>
-        </is>
-      </c>
-      <c r="C1474" t="inlineStr">
-        <is>
-          <t>7707233050590</t>
-        </is>
-      </c>
+          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr"/>
       <c r="D1474" t="inlineStr"/>
       <c r="E1474" t="n">
-        <v>673</v>
+        <v>17900</v>
       </c>
       <c r="F1474" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="G1474" t="n">
         <v>0</v>
@@ -78854,7 +78850,7 @@
       </c>
       <c r="M1474" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1474" t="inlineStr"/>
@@ -78862,21 +78858,25 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
-        </is>
-      </c>
-      <c r="C1475" t="inlineStr"/>
+          <t>Recolector de orina granandina</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>7707233050590</t>
+        </is>
+      </c>
       <c r="D1475" t="inlineStr"/>
       <c r="E1475" t="n">
-        <v>3820</v>
+        <v>673</v>
       </c>
       <c r="F1475" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G1475" t="n">
         <v>0</v>
@@ -78904,7 +78904,7 @@
       </c>
       <c r="M1475" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1475" t="inlineStr"/>
@@ -78912,21 +78912,21 @@
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>RegistroManual - Registro manual</t>
+          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
         </is>
       </c>
       <c r="C1476" t="inlineStr"/>
       <c r="D1476" t="inlineStr"/>
       <c r="E1476" t="n">
-        <v>0</v>
+        <v>3820</v>
       </c>
       <c r="F1476" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1476" t="n">
         <v>0</v>
@@ -78954,7 +78954,7 @@
       </c>
       <c r="M1476" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1476" t="inlineStr"/>
@@ -78962,21 +78962,21 @@
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>REMOVEDOR DE ESMALTE 60CC</t>
+          <t>RegistroManual - Registro manual</t>
         </is>
       </c>
       <c r="C1477" t="inlineStr"/>
       <c r="D1477" t="inlineStr"/>
       <c r="E1477" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="F1477" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1477" t="n">
         <v>0</v>
@@ -79004,7 +79004,7 @@
       </c>
       <c r="M1477" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1477" t="inlineStr"/>
@@ -79012,25 +79012,21 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
-        </is>
-      </c>
-      <c r="C1478" t="inlineStr">
-        <is>
-          <t>7591005981270</t>
-        </is>
-      </c>
+          <t>REMOVEDOR DE ESMALTE 60CC</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr"/>
       <c r="D1478" t="inlineStr"/>
       <c r="E1478" t="n">
-        <v>9500</v>
+        <v>3500</v>
       </c>
       <c r="F1478" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1478" t="n">
         <v>0</v>
@@ -79066,22 +79062,22 @@
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
+          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
         </is>
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>7503051868245</t>
+          <t>7591005981270</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr"/>
       <c r="E1479" t="n">
-        <v>20900</v>
+        <v>9500</v>
       </c>
       <c r="F1479" t="n">
         <v>1</v>
@@ -79120,25 +79116,25 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
         </is>
       </c>
       <c r="C1480" t="inlineStr">
         <is>
-          <t>7702057079642</t>
+          <t>7503051868245</t>
         </is>
       </c>
       <c r="D1480" t="inlineStr"/>
       <c r="E1480" t="n">
-        <v>13000</v>
+        <v>20900</v>
       </c>
       <c r="F1480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1480" t="n">
         <v>0</v>
@@ -79174,18 +79170,22 @@
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>Ryaltris Spray Nasal 240 dosis</t>
-        </is>
-      </c>
-      <c r="C1481" t="inlineStr"/>
+          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>7702057079642</t>
+        </is>
+      </c>
       <c r="D1481" t="inlineStr"/>
       <c r="E1481" t="n">
-        <v>216400</v>
+        <v>13000</v>
       </c>
       <c r="F1481" t="n">
         <v>0</v>
@@ -79224,25 +79224,21 @@
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
-        </is>
-      </c>
-      <c r="C1482" t="inlineStr">
-        <is>
-          <t>7706849116676</t>
-        </is>
-      </c>
+          <t>Ryaltris Spray Nasal 240 dosis</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr"/>
       <c r="D1482" t="inlineStr"/>
       <c r="E1482" t="n">
-        <v>31500</v>
+        <v>216400</v>
       </c>
       <c r="F1482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1482" t="n">
         <v>0</v>
@@ -79278,21 +79274,25 @@
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>SCOBIT PURGANTE 60GR</t>
-        </is>
-      </c>
-      <c r="C1483" t="inlineStr"/>
+          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>7706849116676</t>
+        </is>
+      </c>
       <c r="D1483" t="inlineStr"/>
       <c r="E1483" t="n">
-        <v>15238.095238</v>
+        <v>31500</v>
       </c>
       <c r="F1483" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1483" t="n">
         <v>0</v>
@@ -79320,7 +79320,7 @@
       </c>
       <c r="M1483" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1483" t="inlineStr"/>
@@ -79328,21 +79328,21 @@
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
+          <t>SCOBIT PURGANTE 60GR</t>
         </is>
       </c>
       <c r="C1484" t="inlineStr"/>
       <c r="D1484" t="inlineStr"/>
       <c r="E1484" t="n">
-        <v>6554.621849</v>
+        <v>15238.095238</v>
       </c>
       <c r="F1484" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1484" t="n">
         <v>0</v>
@@ -79370,7 +79370,7 @@
       </c>
       <c r="M1484" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1484" t="inlineStr"/>
@@ -79378,25 +79378,21 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>SHAMPOO PANTENE COLAGENO</t>
-        </is>
-      </c>
-      <c r="C1485" t="inlineStr">
-        <is>
-          <t>7500435191500</t>
-        </is>
-      </c>
+          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr"/>
       <c r="D1485" t="inlineStr"/>
       <c r="E1485" t="n">
-        <v>1429</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1485" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1485" t="n">
         <v>0</v>
@@ -79432,21 +79428,25 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>SILDENAFIL 50MG TQ</t>
-        </is>
-      </c>
-      <c r="C1486" t="inlineStr"/>
+          <t>SHAMPOO PANTENE COLAGENO</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>7500435191500</t>
+        </is>
+      </c>
       <c r="D1486" t="inlineStr"/>
       <c r="E1486" t="n">
-        <v>5000</v>
+        <v>1429</v>
       </c>
       <c r="F1486" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1486" t="n">
         <v>0</v>
@@ -79474,7 +79474,7 @@
       </c>
       <c r="M1486" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1486" t="inlineStr"/>
@@ -79482,25 +79482,21 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>SILIMARINA 167MG EPANAT</t>
-        </is>
-      </c>
-      <c r="C1487" t="inlineStr">
-        <is>
-          <t>7706849115921</t>
-        </is>
-      </c>
+          <t>SILDENAFIL 50MG TQ</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr"/>
       <c r="D1487" t="inlineStr"/>
       <c r="E1487" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F1487" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G1487" t="n">
         <v>0</v>
@@ -79536,21 +79532,25 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>SMECTA 3GR NARANJA S/B</t>
-        </is>
-      </c>
-      <c r="C1488" t="inlineStr"/>
+          <t>SILIMARINA 167MG EPANAT</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>7706849115921</t>
+        </is>
+      </c>
       <c r="D1488" t="inlineStr"/>
       <c r="E1488" t="n">
-        <v>8900</v>
+        <v>2000</v>
       </c>
       <c r="F1488" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G1488" t="n">
         <v>0</v>
@@ -79586,21 +79586,21 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>SONDA FOLEY 2 VIAS BAL #18</t>
+          <t>SMECTA 3GR NARANJA S/B</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr"/>
       <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="n">
-        <v>7500</v>
+        <v>8900</v>
       </c>
       <c r="F1489" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G1489" t="n">
         <v>0</v>
@@ -79636,21 +79636,21 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>SONDA NELATON #6</t>
+          <t>SONDA FOLEY 2 VIAS BAL #18</t>
         </is>
       </c>
       <c r="C1490" t="inlineStr"/>
       <c r="D1490" t="inlineStr"/>
       <c r="E1490" t="n">
-        <v>2500</v>
+        <v>7500</v>
       </c>
       <c r="F1490" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1490" t="n">
         <v>0</v>
@@ -79686,21 +79686,21 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>SPRAY NASAL MOMETASONA 18ML</t>
+          <t>SONDA NELATON #6</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr"/>
       <c r="D1491" t="inlineStr"/>
       <c r="E1491" t="n">
-        <v>36900</v>
+        <v>2500</v>
       </c>
       <c r="F1491" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1491" t="n">
         <v>0</v>
@@ -79736,25 +79736,21 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1492" t="inlineStr">
-        <is>
-          <t>7703712035034</t>
-        </is>
-      </c>
+          <t>SPRAY NASAL MOMETASONA 18ML</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr"/>
       <c r="D1492" t="inlineStr"/>
       <c r="E1492" t="n">
-        <v>14800</v>
+        <v>36900</v>
       </c>
       <c r="F1492" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1492" t="n">
         <v>0</v>
@@ -79790,21 +79786,21 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
+          <t>suerox mora azul x630ml</t>
         </is>
       </c>
       <c r="C1493" t="inlineStr"/>
       <c r="D1493" t="inlineStr"/>
       <c r="E1493" t="n">
-        <v>3781.512605</v>
+        <v>5882.352941</v>
       </c>
       <c r="F1493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1493" t="n">
         <v>0</v>
@@ -79840,18 +79836,22 @@
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
-        </is>
-      </c>
-      <c r="C1494" t="inlineStr"/>
+          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>7703712035034</t>
+        </is>
+      </c>
       <c r="D1494" t="inlineStr"/>
       <c r="E1494" t="n">
-        <v>5210.084034</v>
+        <v>14800</v>
       </c>
       <c r="F1494" t="n">
         <v>0</v>
@@ -79882,7 +79882,7 @@
       </c>
       <c r="M1494" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1494" t="inlineStr"/>
@@ -79890,18 +79890,18 @@
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
+          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
         </is>
       </c>
       <c r="C1495" t="inlineStr"/>
       <c r="D1495" t="inlineStr"/>
       <c r="E1495" t="n">
-        <v>8319.327730999999</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1495" t="n">
         <v>1</v>
@@ -79940,21 +79940,21 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>SULZINC SUSP X 80ML HUMAX</t>
+          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
         </is>
       </c>
       <c r="C1496" t="inlineStr"/>
       <c r="D1496" t="inlineStr"/>
       <c r="E1496" t="n">
-        <v>22400</v>
+        <v>5210.084034</v>
       </c>
       <c r="F1496" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1496" t="n">
         <v>0</v>
@@ -79982,7 +79982,7 @@
       </c>
       <c r="M1496" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1496" t="inlineStr"/>
@@ -79990,21 +79990,21 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>SUNDARK FPS 60 CON TAPA</t>
+          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr"/>
       <c r="D1497" t="inlineStr"/>
       <c r="E1497" t="n">
-        <v>3781.512605</v>
+        <v>8319.327730999999</v>
       </c>
       <c r="F1497" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1497" t="n">
         <v>0</v>
@@ -80040,21 +80040,21 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>Synthroid 125 mcg</t>
+          <t>SULZINC SUSP X 80ML HUMAX</t>
         </is>
       </c>
       <c r="C1498" t="inlineStr"/>
       <c r="D1498" t="inlineStr"/>
       <c r="E1498" t="n">
-        <v>178000</v>
+        <v>22400</v>
       </c>
       <c r="F1498" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1498" t="n">
         <v>0</v>
@@ -80090,25 +80090,21 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>Talco medicado Neofungina 40gm</t>
-        </is>
-      </c>
-      <c r="C1499" t="inlineStr">
-        <is>
-          <t>7706142707106</t>
-        </is>
-      </c>
+          <t>SUNDARK FPS 60 CON TAPA</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr"/>
       <c r="D1499" t="inlineStr"/>
       <c r="E1499" t="n">
-        <v>14900</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1499" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1499" t="n">
         <v>0</v>
@@ -80136,7 +80132,7 @@
       </c>
       <c r="M1499" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1499" t="inlineStr"/>
@@ -80144,18 +80140,18 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
+          <t>Synthroid 125 mcg</t>
         </is>
       </c>
       <c r="C1500" t="inlineStr"/>
       <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="n">
-        <v>13300</v>
+        <v>178000</v>
       </c>
       <c r="F1500" t="n">
         <v>0</v>
@@ -80194,21 +80190,25 @@
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
-        </is>
-      </c>
-      <c r="C1501" t="inlineStr"/>
+          <t>Talco medicado Neofungina 40gm</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>7706142707106</t>
+        </is>
+      </c>
       <c r="D1501" t="inlineStr"/>
       <c r="E1501" t="n">
-        <v>4874</v>
+        <v>14900</v>
       </c>
       <c r="F1501" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G1501" t="n">
         <v>0</v>
@@ -80236,7 +80236,7 @@
       </c>
       <c r="M1501" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1501" t="inlineStr"/>
@@ -80244,21 +80244,21 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
+          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
         </is>
       </c>
       <c r="C1502" t="inlineStr"/>
       <c r="D1502" t="inlineStr"/>
       <c r="E1502" t="n">
-        <v>28800</v>
+        <v>13300</v>
       </c>
       <c r="F1502" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1502" t="n">
         <v>0</v>
@@ -80294,21 +80294,21 @@
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
+          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
         </is>
       </c>
       <c r="C1503" t="inlineStr"/>
       <c r="D1503" t="inlineStr"/>
       <c r="E1503" t="n">
-        <v>11596.638655</v>
+        <v>4874</v>
       </c>
       <c r="F1503" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G1503" t="n">
         <v>0</v>
@@ -80344,21 +80344,21 @@
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>TIJERA DE DOBLAR METALICA</t>
+          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
         </is>
       </c>
       <c r="C1504" t="inlineStr"/>
       <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="n">
-        <v>3500</v>
+        <v>28800</v>
       </c>
       <c r="F1504" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1504" t="n">
         <v>0</v>
@@ -80394,21 +80394,21 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
         </is>
       </c>
       <c r="C1505" t="inlineStr"/>
       <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="n">
-        <v>3781.512605</v>
+        <v>11596.638655</v>
       </c>
       <c r="F1505" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1505" t="n">
         <v>0</v>
@@ -80444,21 +80444,21 @@
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+          <t>TIJERA DE DOBLAR METALICA</t>
         </is>
       </c>
       <c r="C1506" t="inlineStr"/>
       <c r="D1506" t="inlineStr"/>
       <c r="E1506" t="n">
-        <v>29800</v>
+        <v>3500</v>
       </c>
       <c r="F1506" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1506" t="n">
         <v>0</v>
@@ -80494,22 +80494,18 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
-        </is>
-      </c>
-      <c r="C1507" t="inlineStr">
-        <is>
-          <t>7702026149567</t>
-        </is>
-      </c>
+          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr"/>
       <c r="D1507" t="inlineStr"/>
       <c r="E1507" t="n">
-        <v>13500</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1507" t="n">
         <v>2</v>
@@ -80540,7 +80536,7 @@
       </c>
       <c r="M1507" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1507" t="inlineStr"/>
@@ -80548,25 +80544,21 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>Toallas húmedas winny 24unidades</t>
-        </is>
-      </c>
-      <c r="C1508" t="inlineStr">
-        <is>
-          <t>7701021143655</t>
-        </is>
-      </c>
+          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr"/>
       <c r="D1508" t="inlineStr"/>
       <c r="E1508" t="n">
-        <v>4033.613445</v>
+        <v>29800</v>
       </c>
       <c r="F1508" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G1508" t="n">
         <v>0</v>
@@ -80594,7 +80586,7 @@
       </c>
       <c r="M1508" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1508" t="inlineStr"/>
@@ -80602,25 +80594,25 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>Toallas maternas maternity</t>
+          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
         </is>
       </c>
       <c r="C1509" t="inlineStr">
         <is>
-          <t>7703252489526</t>
+          <t>7702026149567</t>
         </is>
       </c>
       <c r="D1509" t="inlineStr"/>
       <c r="E1509" t="n">
-        <v>16900</v>
+        <v>13500</v>
       </c>
       <c r="F1509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1509" t="n">
         <v>0</v>
@@ -80656,25 +80648,25 @@
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>Toallas Nosotras Rapigel x Und</t>
+          <t>Toallas húmedas winny 24unidades</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr">
         <is>
-          <t>7702027416859</t>
+          <t>7701021143655</t>
         </is>
       </c>
       <c r="D1510" t="inlineStr"/>
       <c r="E1510" t="n">
-        <v>756.302521</v>
+        <v>4033.613445</v>
       </c>
       <c r="F1510" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="G1510" t="n">
         <v>0</v>
@@ -80710,21 +80702,25 @@
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>TRAMADOL 50MG CAPSULA MP</t>
-        </is>
-      </c>
-      <c r="C1511" t="inlineStr"/>
+          <t>Toallas maternas maternity</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>7703252489526</t>
+        </is>
+      </c>
       <c r="D1511" t="inlineStr"/>
       <c r="E1511" t="n">
-        <v>1500</v>
+        <v>16900</v>
       </c>
       <c r="F1511" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G1511" t="n">
         <v>0</v>
@@ -80760,25 +80756,25 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>Tramadol clorhidrato 100mg laquifar</t>
+          <t>Toallas Nosotras Rapigel x Und</t>
         </is>
       </c>
       <c r="C1512" t="inlineStr">
         <is>
-          <t>7707019426977</t>
+          <t>7702027416859</t>
         </is>
       </c>
       <c r="D1512" t="inlineStr"/>
       <c r="E1512" t="n">
-        <v>1600</v>
+        <v>756.302521</v>
       </c>
       <c r="F1512" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G1512" t="n">
         <v>0</v>
@@ -80806,7 +80802,7 @@
       </c>
       <c r="M1512" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1512" t="inlineStr"/>
@@ -80814,21 +80810,21 @@
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>TRIGENTAX CREMA TBO X 20GR</t>
+          <t>TRAMADOL 50MG CAPSULA MP</t>
         </is>
       </c>
       <c r="C1513" t="inlineStr"/>
       <c r="D1513" t="inlineStr"/>
       <c r="E1513" t="n">
-        <v>33500</v>
+        <v>1500</v>
       </c>
       <c r="F1513" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G1513" t="n">
         <v>0</v>
@@ -80864,21 +80860,25 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
-        </is>
-      </c>
-      <c r="C1514" t="inlineStr"/>
+          <t>Tramadol clorhidrato 100mg laquifar</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>7707019426977</t>
+        </is>
+      </c>
       <c r="D1514" t="inlineStr"/>
       <c r="E1514" t="n">
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="F1514" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1514" t="n">
         <v>0</v>
@@ -80914,21 +80914,21 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
+          <t>TRIGENTAX CREMA TBO X 20GR</t>
         </is>
       </c>
       <c r="C1515" t="inlineStr"/>
       <c r="D1515" t="inlineStr"/>
       <c r="E1515" t="n">
-        <v>10500</v>
+        <v>33500</v>
       </c>
       <c r="F1515" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1515" t="n">
         <v>0</v>
@@ -80964,21 +80964,21 @@
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
+          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
         </is>
       </c>
       <c r="C1516" t="inlineStr"/>
       <c r="D1516" t="inlineStr"/>
       <c r="E1516" t="n">
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="F1516" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G1516" t="n">
         <v>0</v>
@@ -81014,21 +81014,21 @@
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
+          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
         </is>
       </c>
       <c r="C1517" t="inlineStr"/>
       <c r="D1517" t="inlineStr"/>
       <c r="E1517" t="n">
-        <v>18800</v>
+        <v>10500</v>
       </c>
       <c r="F1517" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1517" t="n">
         <v>0</v>
@@ -81064,21 +81064,21 @@
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
+          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr"/>
       <c r="D1518" t="inlineStr"/>
       <c r="E1518" t="n">
-        <v>13800</v>
+        <v>10500</v>
       </c>
       <c r="F1518" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G1518" t="n">
         <v>0</v>
@@ -81114,21 +81114,21 @@
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
+          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
         </is>
       </c>
       <c r="C1519" t="inlineStr"/>
       <c r="D1519" t="inlineStr"/>
       <c r="E1519" t="n">
-        <v>7900</v>
+        <v>18800</v>
       </c>
       <c r="F1519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1519" t="n">
         <v>0</v>
@@ -81164,21 +81164,21 @@
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>VASELINA FC X 200GR YOMA</t>
+          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
         </is>
       </c>
       <c r="C1520" t="inlineStr"/>
       <c r="D1520" t="inlineStr"/>
       <c r="E1520" t="n">
-        <v>12521.008403</v>
+        <v>13800</v>
       </c>
       <c r="F1520" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1520" t="n">
         <v>0</v>
@@ -81206,7 +81206,7 @@
       </c>
       <c r="M1520" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1520" t="inlineStr"/>
@@ -81214,21 +81214,21 @@
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
+          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
         </is>
       </c>
       <c r="C1521" t="inlineStr"/>
       <c r="D1521" t="inlineStr"/>
       <c r="E1521" t="n">
-        <v>420.168067</v>
+        <v>7900</v>
       </c>
       <c r="F1521" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1521" t="n">
         <v>0</v>
@@ -81256,7 +81256,7 @@
       </c>
       <c r="M1521" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1521" t="inlineStr"/>
@@ -81264,22 +81264,18 @@
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
-        </is>
-      </c>
-      <c r="C1522" t="inlineStr">
-        <is>
-          <t>7708480649803</t>
-        </is>
-      </c>
+          <t>VASELINA FC X 200GR YOMA</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr"/>
       <c r="D1522" t="inlineStr"/>
       <c r="E1522" t="n">
-        <v>28000</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1522" t="n">
         <v>0</v>
@@ -81310,7 +81306,7 @@
       </c>
       <c r="M1522" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1522" t="inlineStr"/>
@@ -81318,25 +81314,21 @@
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>Venda Elastica 6x5 y piel</t>
+          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
         </is>
       </c>
       <c r="C1523" t="inlineStr"/>
-      <c r="D1523" t="inlineStr">
-        <is>
-          <t>SUBIO A 6200 ANTES 5700</t>
-        </is>
-      </c>
+      <c r="D1523" t="inlineStr"/>
       <c r="E1523" t="n">
-        <v>6200</v>
+        <v>420.168067</v>
       </c>
       <c r="F1523" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1523" t="n">
         <v>0</v>
@@ -81364,7 +81356,7 @@
       </c>
       <c r="M1523" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1523" t="inlineStr"/>
@@ -81372,21 +81364,25 @@
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
-        </is>
-      </c>
-      <c r="C1524" t="inlineStr"/>
+          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>7708480649803</t>
+        </is>
+      </c>
       <c r="D1524" t="inlineStr"/>
       <c r="E1524" t="n">
-        <v>5500</v>
+        <v>28000</v>
       </c>
       <c r="F1524" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1524" t="n">
         <v>0</v>
@@ -81422,21 +81418,25 @@
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Venta simple</t>
+          <t>Venda Elastica 6x5 y piel</t>
         </is>
       </c>
       <c r="C1525" t="inlineStr"/>
-      <c r="D1525" t="inlineStr"/>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>SUBIO A 6200 ANTES 5700</t>
+        </is>
+      </c>
       <c r="E1525" t="n">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="F1525" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1525" t="n">
         <v>0</v>
@@ -81454,7 +81454,7 @@
       </c>
       <c r="K1525" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="L1525" t="inlineStr">
@@ -81462,24 +81462,28 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1525" t="inlineStr"/>
+      <c r="M1525" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1525" t="inlineStr"/>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
+          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
         </is>
       </c>
       <c r="C1526" t="inlineStr"/>
       <c r="D1526" t="inlineStr"/>
       <c r="E1526" t="n">
-        <v>1000</v>
+        <v>5500</v>
       </c>
       <c r="F1526" t="n">
         <v>3</v>
@@ -81518,25 +81522,21 @@
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
-        </is>
-      </c>
-      <c r="C1527" t="inlineStr">
-        <is>
-          <t>793969226467</t>
-        </is>
-      </c>
+          <t>Venta simple</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr"/>
       <c r="D1527" t="inlineStr"/>
       <c r="E1527" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="F1527" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1527" t="n">
         <v>0</v>
@@ -81554,39 +81554,35 @@
       </c>
       <c r="K1527" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="L1527" t="inlineStr">
         <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="M1527" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1527" t="inlineStr"/>
       <c r="N1527" t="inlineStr"/>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>VINO CEREBRAL JARABE X 1100ML</t>
+          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
         </is>
       </c>
       <c r="C1528" t="inlineStr"/>
       <c r="D1528" t="inlineStr"/>
       <c r="E1528" t="n">
-        <v>48900</v>
+        <v>1000</v>
       </c>
       <c r="F1528" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1528" t="n">
         <v>0</v>
@@ -81622,21 +81618,25 @@
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
-        </is>
-      </c>
-      <c r="C1529" t="inlineStr"/>
+          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>793969226467</t>
+        </is>
+      </c>
       <c r="D1529" t="inlineStr"/>
       <c r="E1529" t="n">
-        <v>5400</v>
+        <v>17000</v>
       </c>
       <c r="F1529" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G1529" t="n">
         <v>0</v>
@@ -81659,7 +81659,7 @@
       </c>
       <c r="L1529" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="M1529" t="inlineStr">
@@ -81672,21 +81672,21 @@
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
+          <t>VINO CEREBRAL JARABE X 1100ML</t>
         </is>
       </c>
       <c r="C1530" t="inlineStr"/>
       <c r="D1530" t="inlineStr"/>
       <c r="E1530" t="n">
-        <v>5500</v>
+        <v>48900</v>
       </c>
       <c r="F1530" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G1530" t="n">
         <v>0</v>
@@ -81722,21 +81722,21 @@
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>WINNY PAÑAL ETP 6 X 30</t>
+          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
         </is>
       </c>
       <c r="C1531" t="inlineStr"/>
       <c r="D1531" t="inlineStr"/>
       <c r="E1531" t="n">
-        <v>57000</v>
+        <v>5400</v>
       </c>
       <c r="F1531" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G1531" t="n">
         <v>0</v>
@@ -81772,52 +81772,152 @@
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>YODO BLANCO FC X30ML</t>
+          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
         </is>
       </c>
       <c r="C1532" t="inlineStr"/>
       <c r="D1532" t="inlineStr"/>
       <c r="E1532" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F1532" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1532" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1532" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1532" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1532" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1532" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1532" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1532" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1532" t="inlineStr"/>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>WINNY PAÑAL ETP 6 X 30</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr"/>
+      <c r="D1533" t="inlineStr"/>
+      <c r="E1533" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F1533" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1533" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1533" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1533" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1533" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1533" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1533" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1533" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1533" t="inlineStr"/>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>YODO BLANCO FC X30ML</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr"/>
+      <c r="D1534" t="inlineStr"/>
+      <c r="E1534" t="n">
         <v>6000</v>
       </c>
-      <c r="F1532" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1532" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1532" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1532" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1532" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="K1532" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="L1532" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="M1532" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="N1532" t="inlineStr"/>
+      <c r="F1534" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1534" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1534" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1534" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1534" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1534" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1534" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1534" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1534" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -5343,7 +5343,7 @@
         <v>4034</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -16739,7 +16739,7 @@
         <v>15800</v>
       </c>
       <c r="F305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G305" t="n">
         <v>0</v>
@@ -24873,7 +24873,7 @@
         <v>9200</v>
       </c>
       <c r="F458" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G458" t="n">
         <v>0</v>
@@ -31243,7 +31243,7 @@
         <v>2700</v>
       </c>
       <c r="F577" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G577" t="n">
         <v>0</v>
@@ -31571,7 +31571,7 @@
         <v>2800</v>
       </c>
       <c r="F583" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G583" t="n">
         <v>0</v>
@@ -31625,7 +31625,7 @@
         <v>2800</v>
       </c>
       <c r="F584" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G584" t="n">
         <v>0</v>
@@ -50271,7 +50271,7 @@
         <v>2300</v>
       </c>
       <c r="F933" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G933" t="n">
         <v>0</v>
@@ -51307,7 +51307,7 @@
         <v>2200</v>
       </c>
       <c r="F953" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G953" t="n">
         <v>0</v>
@@ -51365,7 +51365,7 @@
         <v>9200</v>
       </c>
       <c r="F954" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G954" t="n">
         <v>0</v>
@@ -68784,7 +68784,7 @@
         <v>10800</v>
       </c>
       <c r="F1279" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1279" t="n">
         <v>0</v>
@@ -70782,7 +70782,7 @@
         <v>300</v>
       </c>
       <c r="F1318" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G1318" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -6369,7 +6369,7 @@
         <v>19800</v>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -10167,7 +10167,7 @@
         <v>2500</v>
       </c>
       <c r="F183" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -10279,7 +10279,7 @@
         <v>4000</v>
       </c>
       <c r="F185" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -12515,7 +12515,7 @@
         <v>2600</v>
       </c>
       <c r="F227" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -13915,7 +13915,7 @@
         <v>840</v>
       </c>
       <c r="F253" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G253" t="n">
         <v>0</v>
@@ -14185,7 +14185,7 @@
         <v>840</v>
       </c>
       <c r="F258" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -15107,7 +15107,7 @@
         <v>1900</v>
       </c>
       <c r="F275" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G275" t="n">
         <v>0</v>
@@ -17835,7 +17835,7 @@
         <v>1500</v>
       </c>
       <c r="F325" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G325" t="n">
         <v>0</v>
@@ -20731,7 +20731,7 @@
         <v>9000</v>
       </c>
       <c r="F381" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G381" t="n">
         <v>0</v>
@@ -23365,7 +23365,7 @@
         <v>2000</v>
       </c>
       <c r="F430" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G430" t="n">
         <v>0</v>
@@ -24757,7 +24757,7 @@
         <v>9200</v>
       </c>
       <c r="F456" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G456" t="n">
         <v>0</v>
@@ -27915,7 +27915,7 @@
         <v>33445.38</v>
       </c>
       <c r="F515" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G515" t="n">
         <v>0</v>
@@ -30445,7 +30445,7 @@
         <v>3781.51</v>
       </c>
       <c r="F562" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G562" t="n">
         <v>0</v>
@@ -30819,7 +30819,7 @@
         <v>2000</v>
       </c>
       <c r="F569" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G569" t="n">
         <v>0</v>
@@ -31845,7 +31845,7 @@
         <v>3000</v>
       </c>
       <c r="F588" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G588" t="n">
         <v>0</v>
@@ -33831,7 +33831,7 @@
         <v>1200</v>
       </c>
       <c r="F625" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G625" t="n">
         <v>0</v>
@@ -38665,7 +38665,7 @@
         <v>2437</v>
       </c>
       <c r="F716" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G716" t="n">
         <v>0</v>
@@ -42319,7 +42319,7 @@
         <v>5500</v>
       </c>
       <c r="F785" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G785" t="n">
         <v>0</v>
@@ -43187,7 +43187,7 @@
         <v>17000</v>
       </c>
       <c r="F801" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G801" t="n">
         <v>0</v>
@@ -44021,7 +44021,7 @@
         <v>20500</v>
       </c>
       <c r="F816" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G816" t="n">
         <v>0</v>
@@ -44133,7 +44133,7 @@
         <v>17800</v>
       </c>
       <c r="F818" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G818" t="n">
         <v>0</v>
@@ -44295,7 +44295,7 @@
         <v>7000</v>
       </c>
       <c r="F821" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G821" t="n">
         <v>0</v>
@@ -46971,7 +46971,7 @@
         <v>2700</v>
       </c>
       <c r="F871" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G871" t="n">
         <v>0</v>
@@ -50903,7 +50903,7 @@
         <v>2000</v>
       </c>
       <c r="F945" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G945" t="n">
         <v>0</v>
@@ -54012,7 +54012,7 @@
         <v>800</v>
       </c>
       <c r="F1003" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1003" t="n">
         <v>0</v>
@@ -70890,7 +70890,7 @@
         <v>33900</v>
       </c>
       <c r="F1320" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1320" t="n">
         <v>0</v>
@@ -75548,7 +75548,7 @@
         <v>3200</v>
       </c>
       <c r="F1411" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G1411" t="n">
         <v>0</v>
@@ -81486,7 +81486,7 @@
         <v>5500</v>
       </c>
       <c r="F1526" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1526" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -11747,7 +11747,7 @@
         <v>4800</v>
       </c>
       <c r="F213" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -13097,7 +13097,7 @@
         <v>3800</v>
       </c>
       <c r="F238" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -20731,7 +20731,7 @@
         <v>9000</v>
       </c>
       <c r="F381" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G381" t="n">
         <v>0</v>
@@ -23161,7 +23161,7 @@
         <v>2200</v>
       </c>
       <c r="F426" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G426" t="n">
         <v>0</v>
@@ -24171,7 +24171,7 @@
         <v>2500</v>
       </c>
       <c r="F445" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G445" t="n">
         <v>0</v>
@@ -34475,7 +34475,7 @@
         <v>8400</v>
       </c>
       <c r="F637" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G637" t="n">
         <v>0</v>
@@ -38665,7 +38665,7 @@
         <v>2437</v>
       </c>
       <c r="F716" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G716" t="n">
         <v>0</v>
@@ -43187,7 +43187,7 @@
         <v>17000</v>
       </c>
       <c r="F801" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G801" t="n">
         <v>0</v>
@@ -52890,7 +52890,7 @@
         <v>1500</v>
       </c>
       <c r="F982" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G982" t="n">
         <v>0</v>
@@ -69554,7 +69554,7 @@
         <v>19200</v>
       </c>
       <c r="F1294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1294" t="n">
         <v>0</v>
@@ -69866,7 +69866,7 @@
         <v>3900</v>
       </c>
       <c r="F1300" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1300" t="n">
         <v>0</v>
@@ -71806,7 +71806,7 @@
         <v>2000</v>
       </c>
       <c r="F1338" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G1338" t="n">
         <v>0</v>
@@ -76288,7 +76288,7 @@
         <v>22700</v>
       </c>
       <c r="F1425" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1425" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -14941,7 +14941,7 @@
         <v>12300</v>
       </c>
       <c r="F272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G272" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
         <v>840</v>
       </c>
       <c r="F284" t="n">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G284" t="n">
         <v>0</v>
@@ -15705,7 +15705,7 @@
         <v>840.336134</v>
       </c>
       <c r="F286" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G286" t="n">
         <v>0</v>
@@ -16627,7 +16627,7 @@
         <v>3800</v>
       </c>
       <c r="F303" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G303" t="n">
         <v>0</v>
@@ -22251,7 +22251,7 @@
         <v>7900</v>
       </c>
       <c r="F409" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G409" t="n">
         <v>0</v>
@@ -30819,7 +30819,7 @@
         <v>2000</v>
       </c>
       <c r="F569" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G569" t="n">
         <v>0</v>
@@ -31571,7 +31571,7 @@
         <v>2800</v>
       </c>
       <c r="F583" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G583" t="n">
         <v>0</v>
@@ -42319,7 +42319,7 @@
         <v>5500</v>
       </c>
       <c r="F785" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G785" t="n">
         <v>0</v>
@@ -55824,7 +55824,7 @@
         <v>12184.87</v>
       </c>
       <c r="F1037" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1037" t="n">
         <v>0</v>
@@ -58736,7 +58736,7 @@
         <v>2900</v>
       </c>
       <c r="F1091" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1091" t="n">
         <v>0</v>
@@ -79600,7 +79600,7 @@
         <v>8900</v>
       </c>
       <c r="F1489" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1489" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -3901,7 +3901,7 @@
         <v>5800</v>
       </c>
       <c r="F66" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -10167,7 +10167,7 @@
         <v>2500</v>
       </c>
       <c r="F183" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -10279,7 +10279,7 @@
         <v>4000</v>
       </c>
       <c r="F185" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -11909,7 +11909,7 @@
         <v>12400</v>
       </c>
       <c r="F216" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -14023,7 +14023,7 @@
         <v>672</v>
       </c>
       <c r="F255" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -14185,7 +14185,7 @@
         <v>840</v>
       </c>
       <c r="F258" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -14509,7 +14509,7 @@
         <v>200</v>
       </c>
       <c r="F264" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -15107,7 +15107,7 @@
         <v>1900</v>
       </c>
       <c r="F275" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G275" t="n">
         <v>0</v>
@@ -21715,7 +21715,7 @@
         <v>3500</v>
       </c>
       <c r="F399" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G399" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
         <v>14900</v>
       </c>
       <c r="F405" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G405" t="n">
         <v>0</v>
@@ -22741,7 +22741,7 @@
         <v>5000</v>
       </c>
       <c r="F418" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G418" t="n">
         <v>0</v>
@@ -23365,7 +23365,7 @@
         <v>2000</v>
       </c>
       <c r="F430" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G430" t="n">
         <v>0</v>
@@ -24645,7 +24645,7 @@
         <v>4000</v>
       </c>
       <c r="F454" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G454" t="n">
         <v>0</v>
@@ -26967,7 +26967,7 @@
         <v>504.2</v>
       </c>
       <c r="F497" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G497" t="n">
         <v>0</v>
@@ -27915,7 +27915,7 @@
         <v>33445.38</v>
       </c>
       <c r="F515" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G515" t="n">
         <v>0</v>
@@ -32879,7 +32879,7 @@
         <v>8800</v>
       </c>
       <c r="F607" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G607" t="n">
         <v>0</v>
@@ -39043,7 +39043,7 @@
         <v>2352.941176</v>
       </c>
       <c r="F723" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G723" t="n">
         <v>0</v>
@@ -42373,7 +42373,7 @@
         <v>2300</v>
       </c>
       <c r="F786" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G786" t="n">
         <v>0</v>
@@ -55612,7 +55612,7 @@
         <v>3900</v>
       </c>
       <c r="F1033" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G1033" t="n">
         <v>0</v>
@@ -55990,7 +55990,7 @@
         <v>3500</v>
       </c>
       <c r="F1040" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1040" t="n">
         <v>0</v>
@@ -61532,7 +61532,7 @@
         <v>11800</v>
       </c>
       <c r="F1143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1143" t="n">
         <v>0</v>
@@ -64182,7 +64182,7 @@
         <v>4800</v>
       </c>
       <c r="F1192" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1192" t="n">
         <v>0</v>
@@ -70890,7 +70890,7 @@
         <v>33900</v>
       </c>
       <c r="F1320" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1320" t="n">
         <v>0</v>
@@ -72688,7 +72688,7 @@
         <v>3800</v>
       </c>
       <c r="F1355" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G1355" t="n">
         <v>0</v>
@@ -78876,7 +78876,7 @@
         <v>673</v>
       </c>
       <c r="F1475" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G1475" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1534"/>
+  <dimension ref="A1:N1539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2255,7 +2255,7 @@
         <v>3529.411765</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -4633,7 +4633,7 @@
         <v>1400</v>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -18243,7 +18243,7 @@
         <v>3361.344538</v>
       </c>
       <c r="F333" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G333" t="n">
         <v>0</v>
@@ -18293,7 +18293,7 @@
         <v>12000</v>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G334" t="n">
         <v>0</v>
@@ -18943,7 +18943,7 @@
         <v>9800</v>
       </c>
       <c r="F347" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G347" t="n">
         <v>0</v>
@@ -27121,7 +27121,7 @@
         <v>10800</v>
       </c>
       <c r="F500" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G500" t="n">
         <v>0</v>
@@ -33939,7 +33939,7 @@
         <v>2352.94</v>
       </c>
       <c r="F627" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G627" t="n">
         <v>0</v>
@@ -34209,7 +34209,7 @@
         <v>3613.445378</v>
       </c>
       <c r="F632" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G632" t="n">
         <v>0</v>
@@ -36907,7 +36907,7 @@
         <v>3277.310924</v>
       </c>
       <c r="F683" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G683" t="n">
         <v>0</v>
@@ -45629,7 +45629,7 @@
         <v>8235.290000000001</v>
       </c>
       <c r="F846" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G846" t="n">
         <v>0</v>
@@ -48417,7 +48417,7 @@
         <v>1000</v>
       </c>
       <c r="F898" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G898" t="n">
         <v>0</v>
@@ -49493,7 +49493,7 @@
         <v>2100</v>
       </c>
       <c r="F918" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G918" t="n">
         <v>0</v>
@@ -50699,7 +50699,7 @@
         <v>3613.445378</v>
       </c>
       <c r="F941" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G941" t="n">
         <v>0</v>
@@ -54806,7 +54806,7 @@
         <v>6900</v>
       </c>
       <c r="F1018" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1018" t="n">
         <v>0</v>
@@ -68200,21 +68200,21 @@
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1543</t>
         </is>
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>BOLSAS INYECTOLOGIA</t>
+          <t>BOLSA BLANCA</t>
         </is>
       </c>
       <c r="C1268" t="inlineStr"/>
       <c r="D1268" t="inlineStr"/>
       <c r="E1268" t="n">
-        <v>840.336134</v>
+        <v>1000</v>
       </c>
       <c r="F1268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1268" t="n">
         <v>0</v>
@@ -68242,7 +68242,7 @@
       </c>
       <c r="M1268" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1268" t="inlineStr"/>
@@ -68250,29 +68250,21 @@
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>BROMHEXINA MG/ML MUCOTROP NIÑO</t>
-        </is>
-      </c>
-      <c r="C1269" t="inlineStr">
-        <is>
-          <t>7703038067450</t>
-        </is>
-      </c>
-      <c r="D1269" t="inlineStr">
-        <is>
-          <t>SE SUBE PRECIO A 17000 ANTES ESTABA EN 15000/MODIF LEYDI</t>
-        </is>
-      </c>
+          <t>BOLSAS INYECTOLOGIA</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr"/>
+      <c r="D1269" t="inlineStr"/>
       <c r="E1269" t="n">
-        <v>17000</v>
+        <v>840.336134</v>
       </c>
       <c r="F1269" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1269" t="n">
         <v>0</v>
@@ -68300,7 +68292,7 @@
       </c>
       <c r="M1269" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1269" t="inlineStr"/>
@@ -68308,21 +68300,29 @@
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>BRONQUISAN JALEA ADULTO JARABE 240ML</t>
-        </is>
-      </c>
-      <c r="C1270" t="inlineStr"/>
-      <c r="D1270" t="inlineStr"/>
+          <t>BROMHEXINA MG/ML MUCOTROP NIÑO</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>7703038067450</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>SE SUBE PRECIO A 17000 ANTES ESTABA EN 15000/MODIF LEYDI</t>
+        </is>
+      </c>
       <c r="E1270" t="n">
-        <v>19900</v>
+        <v>17000</v>
       </c>
       <c r="F1270" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1270" t="n">
         <v>0</v>
@@ -68358,18 +68358,18 @@
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>Bronsinex JBE x 120ML</t>
+          <t>BRONQUISAN JALEA ADULTO JARABE 240ML</t>
         </is>
       </c>
       <c r="C1271" t="inlineStr"/>
       <c r="D1271" t="inlineStr"/>
       <c r="E1271" t="n">
-        <v>17000</v>
+        <v>19900</v>
       </c>
       <c r="F1271" t="n">
         <v>1</v>
@@ -68408,25 +68408,21 @@
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>CAJA DE BEDOYECTA X 3 AMPOLLA</t>
-        </is>
-      </c>
-      <c r="C1272" t="inlineStr">
-        <is>
-          <t>7707288826935</t>
-        </is>
-      </c>
+          <t>Bronsinex JBE x 120ML</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr"/>
       <c r="D1272" t="inlineStr"/>
       <c r="E1272" t="n">
-        <v>58000</v>
+        <v>17000</v>
       </c>
       <c r="F1272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1272" t="n">
         <v>0</v>
@@ -68462,21 +68458,25 @@
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>CALADERM CLEAR PLUS 120GR</t>
-        </is>
-      </c>
-      <c r="C1273" t="inlineStr"/>
+          <t>CAJA DE BEDOYECTA X 3 AMPOLLA</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>7707288826935</t>
+        </is>
+      </c>
       <c r="D1273" t="inlineStr"/>
       <c r="E1273" t="n">
-        <v>22268.907563</v>
+        <v>58000</v>
       </c>
       <c r="F1273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1273" t="n">
         <v>0</v>
@@ -68504,7 +68504,7 @@
       </c>
       <c r="M1273" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1273" t="inlineStr"/>
@@ -68512,25 +68512,21 @@
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>CAPILAR POLIMERO ROSADO 20ML</t>
-        </is>
-      </c>
-      <c r="C1274" t="inlineStr">
-        <is>
-          <t>7701168181244</t>
-        </is>
-      </c>
+          <t>CALADERM CLEAR PLUS 120GR</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr"/>
       <c r="D1274" t="inlineStr"/>
       <c r="E1274" t="n">
-        <v>4300</v>
+        <v>22268.907563</v>
       </c>
       <c r="F1274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1274" t="n">
         <v>0</v>
@@ -68558,7 +68554,7 @@
       </c>
       <c r="M1274" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1274" t="inlineStr"/>
@@ -68566,25 +68562,25 @@
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>CARVEDIDOL 6,25MG MEPHIS</t>
+          <t>CAPILAR POLIMERO ROSADO 20ML</t>
         </is>
       </c>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>7704412376328</t>
+          <t>7701168181244</t>
         </is>
       </c>
       <c r="D1275" t="inlineStr"/>
       <c r="E1275" t="n">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="F1275" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1275" t="n">
         <v>0</v>
@@ -68620,21 +68616,25 @@
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>CARVEDILOL 6.25MG SOBRE X 10 TABLE DE L.S</t>
-        </is>
-      </c>
-      <c r="C1276" t="inlineStr"/>
+          <t>CARVEDIDOL 6,25MG MEPHIS</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>7704412376328</t>
+        </is>
+      </c>
       <c r="D1276" t="inlineStr"/>
       <c r="E1276" t="n">
-        <v>5900</v>
+        <v>4400</v>
       </c>
       <c r="F1276" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1276" t="n">
         <v>0</v>
@@ -68670,21 +68670,21 @@
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>CAUCHO PARA EL CABELLO AKARELLA YUMBO</t>
+          <t>CARVEDILOL 6.25MG SOBRE X 10 TABLE DE L.S</t>
         </is>
       </c>
       <c r="C1277" t="inlineStr"/>
       <c r="D1277" t="inlineStr"/>
       <c r="E1277" t="n">
-        <v>2800</v>
+        <v>5900</v>
       </c>
       <c r="F1277" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1277" t="n">
         <v>0</v>
@@ -68720,21 +68720,21 @@
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>CAUCHOS AKARELA PASTEL ROSADO</t>
+          <t>CAUCHO PARA EL CABELLO AKARELLA YUMBO</t>
         </is>
       </c>
       <c r="C1278" t="inlineStr"/>
       <c r="D1278" t="inlineStr"/>
       <c r="E1278" t="n">
-        <v>1512.605042</v>
+        <v>2800</v>
       </c>
       <c r="F1278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1278" t="n">
         <v>0</v>
@@ -68762,7 +68762,7 @@
       </c>
       <c r="M1278" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1278" t="inlineStr"/>
@@ -68770,21 +68770,21 @@
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>CEFALEXINA 500MG CAPSULAS DE LA SANTE</t>
+          <t>CAUCHOS AKARELA PASTEL ROSADO</t>
         </is>
       </c>
       <c r="C1279" t="inlineStr"/>
       <c r="D1279" t="inlineStr"/>
       <c r="E1279" t="n">
-        <v>10800</v>
+        <v>1512.605042</v>
       </c>
       <c r="F1279" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G1279" t="n">
         <v>0</v>
@@ -68812,7 +68812,7 @@
       </c>
       <c r="M1279" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1279" t="inlineStr"/>
@@ -68820,25 +68820,21 @@
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>Cefalexina 500mg laproff</t>
-        </is>
-      </c>
-      <c r="C1280" t="inlineStr">
-        <is>
-          <t>7703038612636</t>
-        </is>
-      </c>
+          <t>CEFALEXINA 500MG CAPSULAS DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr"/>
       <c r="D1280" t="inlineStr"/>
       <c r="E1280" t="n">
-        <v>10000</v>
+        <v>10800</v>
       </c>
       <c r="F1280" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G1280" t="n">
         <v>0</v>
@@ -68874,22 +68870,22 @@
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>CEPILLO NIÑO KIDS VERDE MEDIO</t>
+          <t>Cefalexina 500mg laproff</t>
         </is>
       </c>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>6971831832020</t>
+          <t>7703038612636</t>
         </is>
       </c>
       <c r="D1281" t="inlineStr"/>
       <c r="E1281" t="n">
-        <v>3781.512605</v>
+        <v>10000</v>
       </c>
       <c r="F1281" t="n">
         <v>0</v>
@@ -68920,7 +68916,7 @@
       </c>
       <c r="M1281" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1281" t="inlineStr"/>
@@ -68928,21 +68924,21 @@
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>CERA EGO POTE X 60ML</t>
+          <t>CEPILLO DENTAL NIÑO</t>
         </is>
       </c>
       <c r="C1282" t="inlineStr"/>
       <c r="D1282" t="inlineStr"/>
       <c r="E1282" t="n">
-        <v>6800</v>
+        <v>4500</v>
       </c>
       <c r="F1282" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1282" t="n">
         <v>0</v>
@@ -68978,18 +68974,22 @@
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>CERA PROQUIDENT ORTD</t>
-        </is>
-      </c>
-      <c r="C1283" t="inlineStr"/>
+          <t>CEPILLO NIÑO KIDS VERDE MEDIO</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>6971831832020</t>
+        </is>
+      </c>
       <c r="D1283" t="inlineStr"/>
       <c r="E1283" t="n">
-        <v>6554.621849</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1283" t="n">
         <v>0</v>
@@ -69028,21 +69028,21 @@
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>CHA-P JARABE ARMONIZA 500ML</t>
+          <t>CERA EGO POTE X 60ML</t>
         </is>
       </c>
       <c r="C1284" t="inlineStr"/>
       <c r="D1284" t="inlineStr"/>
       <c r="E1284" t="n">
-        <v>38000</v>
+        <v>6800</v>
       </c>
       <c r="F1284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1284" t="n">
         <v>0</v>
@@ -69078,21 +69078,21 @@
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>CHAPSTICK LABIAL CEREZA</t>
+          <t>CERA PROQUIDENT ORTD</t>
         </is>
       </c>
       <c r="C1285" t="inlineStr"/>
       <c r="D1285" t="inlineStr"/>
       <c r="E1285" t="n">
-        <v>17563.02521</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1285" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1285" t="n">
         <v>0</v>
@@ -69128,21 +69128,21 @@
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>CHICLE TRIDENT SURTIDOS SABORES X PAQUE</t>
+          <t>CHA-P JARABE ARMONIZA 500ML</t>
         </is>
       </c>
       <c r="C1286" t="inlineStr"/>
       <c r="D1286" t="inlineStr"/>
       <c r="E1286" t="n">
-        <v>2016.806723</v>
+        <v>38000</v>
       </c>
       <c r="F1286" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G1286" t="n">
         <v>0</v>
@@ -69170,7 +69170,7 @@
       </c>
       <c r="M1286" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1286" t="inlineStr"/>
@@ -69178,21 +69178,21 @@
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>CHOCOLATINA JUMBO MANI 17GR X 1 UND</t>
+          <t>CHAPSTICK LABIAL CEREZA</t>
         </is>
       </c>
       <c r="C1287" t="inlineStr"/>
       <c r="D1287" t="inlineStr"/>
       <c r="E1287" t="n">
-        <v>1680.672269</v>
+        <v>17563.02521</v>
       </c>
       <c r="F1287" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G1287" t="n">
         <v>0</v>
@@ -69228,21 +69228,21 @@
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>CHUPO SILICONA GRANDE</t>
+          <t>CHICLE TRIDENT SURTIDOS SABORES X PAQUE</t>
         </is>
       </c>
       <c r="C1288" t="inlineStr"/>
       <c r="D1288" t="inlineStr"/>
       <c r="E1288" t="n">
-        <v>4500</v>
+        <v>2016.806723</v>
       </c>
       <c r="F1288" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G1288" t="n">
         <v>0</v>
@@ -69270,7 +69270,7 @@
       </c>
       <c r="M1288" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1288" t="inlineStr"/>
@@ -69278,21 +69278,21 @@
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>Cianocobalamina</t>
+          <t>CHOCOLATINA JUMBO MANI 17GR X 1 UND</t>
         </is>
       </c>
       <c r="C1289" t="inlineStr"/>
       <c r="D1289" t="inlineStr"/>
       <c r="E1289" t="n">
-        <v>6500</v>
+        <v>1680.672269</v>
       </c>
       <c r="F1289" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G1289" t="n">
         <v>0</v>
@@ -69320,7 +69320,7 @@
       </c>
       <c r="M1289" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1289" t="inlineStr"/>
@@ -69328,25 +69328,21 @@
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>Cicaderm crema protector cutáneo 60gm NF</t>
-        </is>
-      </c>
-      <c r="C1290" t="inlineStr">
-        <is>
-          <t>7707173600091</t>
-        </is>
-      </c>
+          <t>CHUPO SILICONA GRANDE</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr"/>
       <c r="D1290" t="inlineStr"/>
       <c r="E1290" t="n">
-        <v>57000</v>
+        <v>4500</v>
       </c>
       <c r="F1290" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1290" t="n">
         <v>0</v>
@@ -69382,22 +69378,18 @@
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>CINTA DE PAPEL QUIRURGICO HIPOALERGICO 1/2 PROLATEX</t>
-        </is>
-      </c>
-      <c r="C1291" t="inlineStr">
-        <is>
-          <t>7709414102654</t>
-        </is>
-      </c>
+          <t>Cianocobalamina</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr"/>
       <c r="D1291" t="inlineStr"/>
       <c r="E1291" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="F1291" t="n">
         <v>0</v>
@@ -69436,21 +69428,25 @@
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>Citrato de calcio / Vitamina D3 600 MG/400UI (1500MG) Granulos Caja x 15 Sobres</t>
-        </is>
-      </c>
-      <c r="C1292" t="inlineStr"/>
+          <t>Cicaderm crema protector cutáneo 60gm NF</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>7707173600091</t>
+        </is>
+      </c>
       <c r="D1292" t="inlineStr"/>
       <c r="E1292" t="n">
-        <v>53000</v>
+        <v>57000</v>
       </c>
       <c r="F1292" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1292" t="n">
         <v>0</v>
@@ -69486,21 +69482,25 @@
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>CLENOX 40MG 1J/PRELLE.</t>
-        </is>
-      </c>
-      <c r="C1293" t="inlineStr"/>
+          <t>CINTA DE PAPEL QUIRURGICO HIPOALERGICO 1/2 PROLATEX</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>7709414102654</t>
+        </is>
+      </c>
       <c r="D1293" t="inlineStr"/>
       <c r="E1293" t="n">
-        <v>17800</v>
+        <v>6000</v>
       </c>
       <c r="F1293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1293" t="n">
         <v>0</v>
@@ -69536,25 +69536,21 @@
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>769</t>
         </is>
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>CLINBAC CLINDAMICINA 300MG CAPS</t>
-        </is>
-      </c>
-      <c r="C1294" t="inlineStr">
-        <is>
-          <t>7707019413816</t>
-        </is>
-      </c>
+          <t>Citrato de calcio / Vitamina D3 600 MG/400UI (1500MG) Granulos Caja x 15 Sobres</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr"/>
       <c r="D1294" t="inlineStr"/>
       <c r="E1294" t="n">
-        <v>19200</v>
+        <v>53000</v>
       </c>
       <c r="F1294" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1294" t="n">
         <v>0</v>
@@ -69590,21 +69586,21 @@
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>CLINDABACT CLOTRI+CLIND CJA X 3 OVULOS</t>
+          <t>CLENOX 40MG 1J/PRELLE.</t>
         </is>
       </c>
       <c r="C1295" t="inlineStr"/>
       <c r="D1295" t="inlineStr"/>
       <c r="E1295" t="n">
-        <v>35700</v>
+        <v>17800</v>
       </c>
       <c r="F1295" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1295" t="n">
         <v>0</v>
@@ -69640,25 +69636,25 @@
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>CLOBETASOL 0,05% TRIDIRTEX CREMA X 40GR</t>
+          <t>CLINBAC CLINDAMICINA 300MG CAPS</t>
         </is>
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>7709740450351</t>
+          <t>7707019413816</t>
         </is>
       </c>
       <c r="D1296" t="inlineStr"/>
       <c r="E1296" t="n">
-        <v>27900</v>
+        <v>19200</v>
       </c>
       <c r="F1296" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1296" t="n">
         <v>0</v>
@@ -69694,25 +69690,21 @@
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>Clotrimazol 1% 40gr AG</t>
-        </is>
-      </c>
-      <c r="C1297" t="inlineStr">
-        <is>
-          <t>7706569001191</t>
-        </is>
-      </c>
+          <t>CLINDABACT CLOTRI+CLIND CJA X 3 OVULOS</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr"/>
       <c r="D1297" t="inlineStr"/>
       <c r="E1297" t="n">
-        <v>19000</v>
+        <v>35700</v>
       </c>
       <c r="F1297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1297" t="n">
         <v>0</v>
@@ -69748,25 +69740,25 @@
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>CLOTRIMAZOL 1% CREMA TOPICA DE VITALIS</t>
+          <t>CLOBETASOL 0,05% TRIDIRTEX CREMA X 40GR</t>
         </is>
       </c>
       <c r="C1298" t="inlineStr">
         <is>
-          <t>7709990212204</t>
+          <t>7709740450351</t>
         </is>
       </c>
       <c r="D1298" t="inlineStr"/>
       <c r="E1298" t="n">
-        <v>14500</v>
+        <v>27900</v>
       </c>
       <c r="F1298" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1298" t="n">
         <v>0</v>
@@ -69802,21 +69794,25 @@
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>COLAGENO HIDROLIZADO EN POLVO 700GR ARMONIZA</t>
-        </is>
-      </c>
-      <c r="C1299" t="inlineStr"/>
+          <t>Clotrimazol 1% 40gr AG</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>7706569001191</t>
+        </is>
+      </c>
       <c r="D1299" t="inlineStr"/>
       <c r="E1299" t="n">
-        <v>56000</v>
+        <v>19000</v>
       </c>
       <c r="F1299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1299" t="n">
         <v>0</v>
@@ -69852,21 +69848,25 @@
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>Colchicina Coas</t>
-        </is>
-      </c>
-      <c r="C1300" t="inlineStr"/>
+          <t>CLOTRIMAZOL 1% CREMA TOPICA DE VITALIS</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>7709990212204</t>
+        </is>
+      </c>
       <c r="D1300" t="inlineStr"/>
       <c r="E1300" t="n">
-        <v>3900</v>
+        <v>14500</v>
       </c>
       <c r="F1300" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1300" t="n">
         <v>0</v>
@@ -69902,21 +69902,21 @@
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>CONDON DUO LUBRICADO X 3 UND</t>
+          <t>COLAGENO HIDROLIZADO EN POLVO 700GR ARMONIZA</t>
         </is>
       </c>
       <c r="C1301" t="inlineStr"/>
       <c r="D1301" t="inlineStr"/>
       <c r="E1301" t="n">
-        <v>16500</v>
+        <v>56000</v>
       </c>
       <c r="F1301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1301" t="n">
         <v>0</v>
@@ -69952,21 +69952,21 @@
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
+          <t>Colchicina Coas</t>
         </is>
       </c>
       <c r="C1302" t="inlineStr"/>
       <c r="D1302" t="inlineStr"/>
       <c r="E1302" t="n">
-        <v>8900</v>
+        <v>3900</v>
       </c>
       <c r="F1302" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1302" t="n">
         <v>0</v>
@@ -70002,21 +70002,21 @@
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
+          <t>CONDON DUO LUBRICADO X 3 UND</t>
         </is>
       </c>
       <c r="C1303" t="inlineStr"/>
       <c r="D1303" t="inlineStr"/>
       <c r="E1303" t="n">
-        <v>8900</v>
+        <v>16500</v>
       </c>
       <c r="F1303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1303" t="n">
         <v>0</v>
@@ -70052,12 +70052,12 @@
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>CONDON PIEL SABORES CJA X 3 UNDS</t>
+          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
         </is>
       </c>
       <c r="C1304" t="inlineStr"/>
@@ -70066,7 +70066,7 @@
         <v>8900</v>
       </c>
       <c r="F1304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1304" t="n">
         <v>0</v>
@@ -70102,25 +70102,21 @@
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>CONDON PRUDENCE EFEC.RETARDX3UNDS</t>
-        </is>
-      </c>
-      <c r="C1305" t="inlineStr">
-        <is>
-          <t>77309632510504387</t>
-        </is>
-      </c>
+          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr"/>
       <c r="D1305" t="inlineStr"/>
       <c r="E1305" t="n">
-        <v>12200</v>
+        <v>8900</v>
       </c>
       <c r="F1305" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1305" t="n">
         <v>0</v>
@@ -70156,25 +70152,21 @@
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>CONDON PRUDENCE EXTRA GRANDE ULT SENSIBX3UND</t>
-        </is>
-      </c>
-      <c r="C1306" t="inlineStr">
-        <is>
-          <t>7730963250343</t>
-        </is>
-      </c>
+          <t>CONDON PIEL SABORES CJA X 3 UNDS</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr"/>
       <c r="D1306" t="inlineStr"/>
       <c r="E1306" t="n">
-        <v>13800</v>
+        <v>8900</v>
       </c>
       <c r="F1306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1306" t="n">
         <v>0</v>
@@ -70210,25 +70202,25 @@
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>CONTENT MEDICAL PAÑAL TALLA L X UND</t>
-        </is>
-      </c>
-      <c r="C1307" t="inlineStr"/>
-      <c r="D1307" t="inlineStr">
-        <is>
-          <t>pañal adulto no paga iva articulo 424</t>
-        </is>
-      </c>
+          <t>CONDON PRUDENCE EFEC.RETARDX3UNDS</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>77309632510504387</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr"/>
       <c r="E1307" t="n">
-        <v>4800</v>
+        <v>12200</v>
       </c>
       <c r="F1307" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1307" t="n">
         <v>0</v>
@@ -70264,21 +70256,25 @@
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>CONTENT MEDICAL PAÑAL TALLA M X UND</t>
-        </is>
-      </c>
-      <c r="C1308" t="inlineStr"/>
+          <t>CONDON PRUDENCE EXTRA GRANDE ULT SENSIBX3UND</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>7730963250343</t>
+        </is>
+      </c>
       <c r="D1308" t="inlineStr"/>
       <c r="E1308" t="n">
-        <v>3697.478992</v>
+        <v>13800</v>
       </c>
       <c r="F1308" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G1308" t="n">
         <v>0</v>
@@ -70306,7 +70302,7 @@
       </c>
       <c r="M1308" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1308" t="inlineStr"/>
@@ -70314,21 +70310,25 @@
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 100 UNDS</t>
+          <t>CONTENT MEDICAL PAÑAL TALLA L X UND</t>
         </is>
       </c>
       <c r="C1309" t="inlineStr"/>
-      <c r="D1309" t="inlineStr"/>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>pañal adulto no paga iva articulo 424</t>
+        </is>
+      </c>
       <c r="E1309" t="n">
-        <v>8500</v>
+        <v>4800</v>
       </c>
       <c r="F1309" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1309" t="n">
         <v>0</v>
@@ -70364,21 +70364,21 @@
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 50 UNDS</t>
+          <t>CONTENT MEDICAL PAÑAL TALLA M X UND</t>
         </is>
       </c>
       <c r="C1310" t="inlineStr"/>
       <c r="D1310" t="inlineStr"/>
       <c r="E1310" t="n">
-        <v>6400</v>
+        <v>3697.478992</v>
       </c>
       <c r="F1310" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G1310" t="n">
         <v>0</v>
@@ -70406,7 +70406,7 @@
       </c>
       <c r="M1310" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1310" t="inlineStr"/>
@@ -70414,21 +70414,21 @@
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 60 UNDS</t>
+          <t>COPITOS YOKY X 100 UNDS</t>
         </is>
       </c>
       <c r="C1311" t="inlineStr"/>
       <c r="D1311" t="inlineStr"/>
       <c r="E1311" t="n">
-        <v>7142.857143</v>
+        <v>8500</v>
       </c>
       <c r="F1311" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1311" t="n">
         <v>0</v>
@@ -70456,7 +70456,7 @@
       </c>
       <c r="M1311" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1311" t="inlineStr"/>
@@ -70464,21 +70464,21 @@
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>CORTA CUTICULA TRIM METALICO</t>
+          <t>COPITOS YOKY X 50 UNDS</t>
         </is>
       </c>
       <c r="C1312" t="inlineStr"/>
       <c r="D1312" t="inlineStr"/>
       <c r="E1312" t="n">
-        <v>16000</v>
+        <v>6400</v>
       </c>
       <c r="F1312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1312" t="n">
         <v>0</v>
@@ -70514,21 +70514,21 @@
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>CREMA ARNICA PROTECTORA 12GR ICE POWER</t>
+          <t>COPITOS YOKY X 60 UNDS</t>
         </is>
       </c>
       <c r="C1313" t="inlineStr"/>
       <c r="D1313" t="inlineStr"/>
       <c r="E1313" t="n">
-        <v>10084.033613</v>
+        <v>7142.857143</v>
       </c>
       <c r="F1313" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1313" t="n">
         <v>0</v>
@@ -70564,18 +70564,18 @@
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>CREMA BENLIC DE 40GR</t>
+          <t>CORTA CUTICULA TRIM METALICO</t>
         </is>
       </c>
       <c r="C1314" t="inlineStr"/>
       <c r="D1314" t="inlineStr"/>
       <c r="E1314" t="n">
-        <v>28900</v>
+        <v>16000</v>
       </c>
       <c r="F1314" t="n">
         <v>1</v>
@@ -70614,21 +70614,21 @@
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>CREMA CASTAÑO DE INDIAS X 12GR ARMONIZA</t>
+          <t>CREMA ARNICA PROTECTORA 12GR ICE POWER</t>
         </is>
       </c>
       <c r="C1315" t="inlineStr"/>
       <c r="D1315" t="inlineStr"/>
       <c r="E1315" t="n">
-        <v>9000</v>
+        <v>10084.033613</v>
       </c>
       <c r="F1315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1315" t="n">
         <v>0</v>
@@ -70656,7 +70656,7 @@
       </c>
       <c r="M1315" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1315" t="inlineStr"/>
@@ -70664,25 +70664,21 @@
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>Crema Colgate triple acción xtra blancura 60ml</t>
-        </is>
-      </c>
-      <c r="C1316" t="inlineStr">
-        <is>
-          <t>7702010111587</t>
-        </is>
-      </c>
+          <t>CREMA BENLIC DE 40GR</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr"/>
       <c r="D1316" t="inlineStr"/>
       <c r="E1316" t="n">
-        <v>5630.252101</v>
+        <v>28900</v>
       </c>
       <c r="F1316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1316" t="n">
         <v>0</v>
@@ -70710,7 +70706,7 @@
       </c>
       <c r="M1316" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1316" t="inlineStr"/>
@@ -70718,21 +70714,21 @@
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>CREMA PONDS CLARANT B3 X SACHETS</t>
+          <t>CREMA CASTAÑO DE INDIAS X 12GR ARMONIZA</t>
         </is>
       </c>
       <c r="C1317" t="inlineStr"/>
       <c r="D1317" t="inlineStr"/>
       <c r="E1317" t="n">
-        <v>2521.008403</v>
+        <v>9000</v>
       </c>
       <c r="F1317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1317" t="n">
         <v>0</v>
@@ -70760,7 +70756,7 @@
       </c>
       <c r="M1317" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1317" t="inlineStr"/>
@@ -70768,21 +70764,25 @@
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>CURAS LARGAS RESIST AL AGUA</t>
-        </is>
-      </c>
-      <c r="C1318" t="inlineStr"/>
+          <t>Crema Colgate triple acción xtra blancura 60ml</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>7702010111587</t>
+        </is>
+      </c>
       <c r="D1318" t="inlineStr"/>
       <c r="E1318" t="n">
-        <v>300</v>
+        <v>5630.252101</v>
       </c>
       <c r="F1318" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="G1318" t="n">
         <v>0</v>
@@ -70810,7 +70810,7 @@
       </c>
       <c r="M1318" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1318" t="inlineStr"/>
@@ -70818,25 +70818,21 @@
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>CYCLOFEM AMPOLLA INYECTABLE .PROFAMILIA</t>
-        </is>
-      </c>
-      <c r="C1319" t="inlineStr">
-        <is>
-          <t>7703689000448</t>
-        </is>
-      </c>
+          <t>CREMA PONDS CLARANT B3 X SACHETS</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr"/>
       <c r="D1319" t="inlineStr"/>
       <c r="E1319" t="n">
-        <v>28900</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1319" t="n">
         <v>0</v>
@@ -70864,7 +70860,7 @@
       </c>
       <c r="M1319" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1319" t="inlineStr"/>
@@ -70872,25 +70868,21 @@
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>CYCLOFEMINA AMPOLLA 0.5ML</t>
-        </is>
-      </c>
-      <c r="C1320" t="inlineStr">
-        <is>
-          <t>7707271451410</t>
-        </is>
-      </c>
+          <t>CURAS LARGAS RESIST AL AGUA</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr"/>
       <c r="D1320" t="inlineStr"/>
       <c r="E1320" t="n">
-        <v>33900</v>
+        <v>300</v>
       </c>
       <c r="F1320" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="G1320" t="n">
         <v>0</v>
@@ -70926,22 +70918,22 @@
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>Desonida bussie 0.1% crema 15gr</t>
+          <t>CYCLOFEM AMPOLLA INYECTABLE .PROFAMILIA</t>
         </is>
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>7702195210587</t>
+          <t>7703689000448</t>
         </is>
       </c>
       <c r="D1321" t="inlineStr"/>
       <c r="E1321" t="n">
-        <v>19000</v>
+        <v>28900</v>
       </c>
       <c r="F1321" t="n">
         <v>1</v>
@@ -70980,22 +70972,22 @@
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>Diclofenaco gel vitalis 50gr</t>
+          <t>CYCLOFEMINA AMPOLLA 0.5ML</t>
         </is>
       </c>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>7709141546059</t>
+          <t>7707271451410</t>
         </is>
       </c>
       <c r="D1322" t="inlineStr"/>
       <c r="E1322" t="n">
-        <v>16000</v>
+        <v>33900</v>
       </c>
       <c r="F1322" t="n">
         <v>3</v>
@@ -71024,31 +71016,35 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1322" t="inlineStr"/>
+      <c r="M1322" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1322" t="inlineStr"/>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>Diclofenaco sódico 100mg +hidróxido de aluminio200mg colmed</t>
+          <t>Desonida bussie 0.1% crema 15gr</t>
         </is>
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>7703153020286</t>
+          <t>7702195210587</t>
         </is>
       </c>
       <c r="D1323" t="inlineStr"/>
       <c r="E1323" t="n">
-        <v>19200</v>
+        <v>19000</v>
       </c>
       <c r="F1323" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G1323" t="n">
         <v>0</v>
@@ -71084,21 +71080,25 @@
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>DICLOFENACOXUND75MG/3MLAMPCOMERCIAL VITALIS</t>
-        </is>
-      </c>
-      <c r="C1324" t="inlineStr"/>
+          <t>Diclofenaco gel vitalis 50gr</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>7709141546059</t>
+        </is>
+      </c>
       <c r="D1324" t="inlineStr"/>
       <c r="E1324" t="n">
-        <v>5500</v>
+        <v>16000</v>
       </c>
       <c r="F1324" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1324" t="n">
         <v>0</v>
@@ -71124,31 +71124,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1324" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1324" t="inlineStr"/>
       <c r="N1324" t="inlineStr"/>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>DIFENZ DESPIGMENTADOR CREMA TUBO X 1 UND</t>
-        </is>
-      </c>
-      <c r="C1325" t="inlineStr"/>
+          <t>Diclofenaco sódico 100mg +hidróxido de aluminio200mg colmed</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>7703153020286</t>
+        </is>
+      </c>
       <c r="D1325" t="inlineStr"/>
       <c r="E1325" t="n">
-        <v>163300</v>
+        <v>19200</v>
       </c>
       <c r="F1325" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1325" t="n">
         <v>0</v>
@@ -71184,25 +71184,21 @@
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>DIOSMINA HESPERIDINA 450MG 50MG GENFAR</t>
-        </is>
-      </c>
-      <c r="C1326" t="inlineStr">
-        <is>
-          <t>7705959013370</t>
-        </is>
-      </c>
+          <t>DICLOFENACOXUND75MG/3MLAMPCOMERCIAL VITALIS</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr"/>
       <c r="D1326" t="inlineStr"/>
       <c r="E1326" t="n">
-        <v>42000</v>
+        <v>5500</v>
       </c>
       <c r="F1326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1326" t="n">
         <v>0</v>
@@ -71238,21 +71234,21 @@
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>DIPIORNA 500MG TABLETA X 10 DE ECAR</t>
+          <t>DIFENZ DESPIGMENTADOR CREMA TUBO X 1 UND</t>
         </is>
       </c>
       <c r="C1327" t="inlineStr"/>
       <c r="D1327" t="inlineStr"/>
       <c r="E1327" t="n">
-        <v>7900</v>
+        <v>163300</v>
       </c>
       <c r="F1327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1327" t="n">
         <v>0</v>
@@ -71288,21 +71284,25 @@
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>DIPIRONA 500MG TABLETA X 10 DE ECAR</t>
-        </is>
-      </c>
-      <c r="C1328" t="inlineStr"/>
+          <t>DIOSMINA HESPERIDINA 450MG 50MG GENFAR</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>7705959013370</t>
+        </is>
+      </c>
       <c r="D1328" t="inlineStr"/>
       <c r="E1328" t="n">
-        <v>7900</v>
+        <v>42000</v>
       </c>
       <c r="F1328" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1328" t="n">
         <v>0</v>
@@ -71338,18 +71338,18 @@
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>DOMICILIO</t>
+          <t>DIPIORNA 500MG TABLETA X 10 DE ECAR</t>
         </is>
       </c>
       <c r="C1329" t="inlineStr"/>
       <c r="D1329" t="inlineStr"/>
       <c r="E1329" t="n">
-        <v>3000</v>
+        <v>7900</v>
       </c>
       <c r="F1329" t="n">
         <v>0</v>
@@ -71378,24 +71378,28 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1329" t="inlineStr"/>
+      <c r="M1329" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1329" t="inlineStr"/>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>DOXICICLINA 100MG X 10 TABL GENFAR</t>
+          <t>DIPIRONA 500MG TABLETA X 10 DE ECAR</t>
         </is>
       </c>
       <c r="C1330" t="inlineStr"/>
       <c r="D1330" t="inlineStr"/>
       <c r="E1330" t="n">
-        <v>12000</v>
+        <v>7900</v>
       </c>
       <c r="F1330" t="n">
         <v>5</v>
@@ -71434,21 +71438,21 @@
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>DUCHA INTIMA DESECHABLE VINAGRE</t>
+          <t>DOMICILIO</t>
         </is>
       </c>
       <c r="C1331" t="inlineStr"/>
       <c r="D1331" t="inlineStr"/>
       <c r="E1331" t="n">
-        <v>24800</v>
+        <v>3000</v>
       </c>
       <c r="F1331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1331" t="n">
         <v>0</v>
@@ -71474,35 +71478,27 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1331" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1331" t="inlineStr"/>
       <c r="N1331" t="inlineStr"/>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>E ala proel maléate 20mg medicbrand</t>
-        </is>
-      </c>
-      <c r="C1332" t="inlineStr">
-        <is>
-          <t>7703712035997</t>
-        </is>
-      </c>
+          <t>DOXICICLINA 100MG X 10 TABL GENFAR</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr"/>
       <c r="D1332" t="inlineStr"/>
       <c r="E1332" t="n">
-        <v>1250</v>
+        <v>12000</v>
       </c>
       <c r="F1332" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1332" t="n">
         <v>0</v>
@@ -71538,22 +71534,18 @@
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>Enalapril 20 mg MK</t>
-        </is>
-      </c>
-      <c r="C1333" t="inlineStr">
-        <is>
-          <t>7702057716578</t>
-        </is>
-      </c>
+          <t>DUCHA INTIMA DESECHABLE VINAGRE</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr"/>
       <c r="D1333" t="inlineStr"/>
       <c r="E1333" t="n">
-        <v>4700</v>
+        <v>24800</v>
       </c>
       <c r="F1333" t="n">
         <v>1</v>
@@ -71592,21 +71584,25 @@
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>ENALAPRIL 20MG TABLETA COAS</t>
-        </is>
-      </c>
-      <c r="C1334" t="inlineStr"/>
+          <t>E ala proel maléate 20mg medicbrand</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>7703712035997</t>
+        </is>
+      </c>
       <c r="D1334" t="inlineStr"/>
       <c r="E1334" t="n">
-        <v>3000</v>
+        <v>1250</v>
       </c>
       <c r="F1334" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1334" t="n">
         <v>0</v>
@@ -71642,18 +71638,22 @@
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>ENSURE ADVANCE VAINILLA 400GR</t>
-        </is>
-      </c>
-      <c r="C1335" t="inlineStr"/>
+          <t>Enalapril 20 mg MK</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>7702057716578</t>
+        </is>
+      </c>
       <c r="D1335" t="inlineStr"/>
       <c r="E1335" t="n">
-        <v>85900</v>
+        <v>4700</v>
       </c>
       <c r="F1335" t="n">
         <v>1</v>
@@ -71692,21 +71692,21 @@
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>ENTRETENEDOR BEBE</t>
+          <t>ENALAPRIL 20MG TABLETA COAS</t>
         </is>
       </c>
       <c r="C1336" t="inlineStr"/>
       <c r="D1336" t="inlineStr"/>
       <c r="E1336" t="n">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="F1336" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1336" t="n">
         <v>0</v>
@@ -71742,18 +71742,18 @@
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>ESMALTE BRILLO ACRILICO BRESCIA</t>
+          <t>ENSURE ADVANCE VAINILLA 400GR</t>
         </is>
       </c>
       <c r="C1337" t="inlineStr"/>
       <c r="D1337" t="inlineStr"/>
       <c r="E1337" t="n">
-        <v>11500</v>
+        <v>85900</v>
       </c>
       <c r="F1337" t="n">
         <v>1</v>
@@ -71792,21 +71792,21 @@
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>ESOMEPRAZOL 20MG NOVAMED</t>
+          <t>ENTRETENEDOR BEBE</t>
         </is>
       </c>
       <c r="C1338" t="inlineStr"/>
       <c r="D1338" t="inlineStr"/>
       <c r="E1338" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="F1338" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="G1338" t="n">
         <v>0</v>
@@ -71842,18 +71842,18 @@
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>ESPASMOK HIOS +DIPIRO 5ML AMP BLASKOV</t>
+          <t>ESMALTE BRILLO ACRILICO BRESCIA</t>
         </is>
       </c>
       <c r="C1339" t="inlineStr"/>
       <c r="D1339" t="inlineStr"/>
       <c r="E1339" t="n">
-        <v>12000</v>
+        <v>11500</v>
       </c>
       <c r="F1339" t="n">
         <v>1</v>
@@ -71892,25 +71892,21 @@
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>ETORICOXIB 120MG GENFAR</t>
-        </is>
-      </c>
-      <c r="C1340" t="inlineStr">
-        <is>
-          <t>7702605109371</t>
-        </is>
-      </c>
+          <t>ESOMEPRAZOL 20MG NOVAMED</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr"/>
       <c r="D1340" t="inlineStr"/>
       <c r="E1340" t="n">
-        <v>48600</v>
+        <v>2000</v>
       </c>
       <c r="F1340" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G1340" t="n">
         <v>0</v>
@@ -71946,22 +71942,18 @@
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>EXTRACTOR DE LECHE MOBY</t>
-        </is>
-      </c>
-      <c r="C1341" t="inlineStr">
-        <is>
-          <t>7707233051436</t>
-        </is>
-      </c>
+          <t>ESPASMOK HIOS +DIPIRO 5ML AMP BLASKOV</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr"/>
       <c r="D1341" t="inlineStr"/>
       <c r="E1341" t="n">
-        <v>14285.714286</v>
+        <v>12000</v>
       </c>
       <c r="F1341" t="n">
         <v>1</v>
@@ -71992,7 +71984,7 @@
       </c>
       <c r="M1341" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1341" t="inlineStr"/>
@@ -72000,25 +71992,25 @@
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>FAMIIA MEGARROLLO PAPEL HIGUIEN</t>
+          <t>ETORICOXIB 120MG GENFAR</t>
         </is>
       </c>
       <c r="C1342" t="inlineStr">
         <is>
-          <t>7702026147471</t>
+          <t>7702605109371</t>
         </is>
       </c>
       <c r="D1342" t="inlineStr"/>
       <c r="E1342" t="n">
-        <v>3500</v>
+        <v>48600</v>
       </c>
       <c r="F1342" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G1342" t="n">
         <v>0</v>
@@ -72054,21 +72046,25 @@
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>Farma D 500 UI</t>
-        </is>
-      </c>
-      <c r="C1343" t="inlineStr"/>
+          <t>EXTRACTOR DE LECHE MOBY</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>7707233051436</t>
+        </is>
+      </c>
       <c r="D1343" t="inlineStr"/>
       <c r="E1343" t="n">
-        <v>74000</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1343" t="n">
         <v>0</v>
@@ -72096,7 +72092,7 @@
       </c>
       <c r="M1343" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1343" t="inlineStr"/>
@@ -72104,21 +72100,25 @@
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>FIBRA AMARILLA ARMONIZA X 450GR</t>
-        </is>
-      </c>
-      <c r="C1344" t="inlineStr"/>
+          <t>FAMIIA MEGARROLLO PAPEL HIGUIEN</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>7702026147471</t>
+        </is>
+      </c>
       <c r="D1344" t="inlineStr"/>
       <c r="E1344" t="n">
-        <v>28571.428571</v>
+        <v>3500</v>
       </c>
       <c r="F1344" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G1344" t="n">
         <v>0</v>
@@ -72146,7 +72146,7 @@
       </c>
       <c r="M1344" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1344" t="inlineStr"/>
@@ -72154,18 +72154,18 @@
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>FIBRA DE AVENA Y SALVADO DE TRIGO 450GR</t>
+          <t>Farma D 500 UI</t>
         </is>
       </c>
       <c r="C1345" t="inlineStr"/>
       <c r="D1345" t="inlineStr"/>
       <c r="E1345" t="n">
-        <v>30000</v>
+        <v>74000</v>
       </c>
       <c r="F1345" t="n">
         <v>0</v>
@@ -72204,21 +72204,21 @@
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>FITOSTIMONE 15% GEL</t>
+          <t>FIBRA AMARILLA ARMONIZA X 450GR</t>
         </is>
       </c>
       <c r="C1346" t="inlineStr"/>
       <c r="D1346" t="inlineStr"/>
       <c r="E1346" t="n">
-        <v>48900</v>
+        <v>28571.428571</v>
       </c>
       <c r="F1346" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1346" t="n">
         <v>0</v>
@@ -72246,7 +72246,7 @@
       </c>
       <c r="M1346" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1346" t="inlineStr"/>
@@ -72254,25 +72254,21 @@
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG CJA X 10 UND EXPORF</t>
-        </is>
-      </c>
-      <c r="C1347" t="inlineStr">
-        <is>
-          <t>7703432421681</t>
-        </is>
-      </c>
+          <t>FIBRA DE AVENA Y SALVADO DE TRIGO 450GR</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr"/>
       <c r="D1347" t="inlineStr"/>
       <c r="E1347" t="n">
-        <v>18300</v>
+        <v>30000</v>
       </c>
       <c r="F1347" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G1347" t="n">
         <v>0</v>
@@ -72308,18 +72304,18 @@
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS DE GENFAR</t>
+          <t>FITOSTIMONE 15% GEL</t>
         </is>
       </c>
       <c r="C1348" t="inlineStr"/>
       <c r="D1348" t="inlineStr"/>
       <c r="E1348" t="n">
-        <v>16900</v>
+        <v>48900</v>
       </c>
       <c r="F1348" t="n">
         <v>2</v>
@@ -72358,25 +72354,25 @@
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS. LA SANTE</t>
+          <t>FLUCONAZOL 200MG CJA X 10 UND EXPORF</t>
         </is>
       </c>
       <c r="C1349" t="inlineStr">
         <is>
-          <t>7703763480166</t>
+          <t>7703432421681</t>
         </is>
       </c>
       <c r="D1349" t="inlineStr"/>
       <c r="E1349" t="n">
-        <v>14700</v>
+        <v>18300</v>
       </c>
       <c r="F1349" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G1349" t="n">
         <v>0</v>
@@ -72412,22 +72408,18 @@
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS.NOVAMED</t>
-        </is>
-      </c>
-      <c r="C1350" t="inlineStr">
-        <is>
-          <t>7703546927468</t>
-        </is>
-      </c>
+          <t>FLUCONAZOL 200MG X 4 CAPS DE GENFAR</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr"/>
       <c r="D1350" t="inlineStr"/>
       <c r="E1350" t="n">
-        <v>10900</v>
+        <v>16900</v>
       </c>
       <c r="F1350" t="n">
         <v>2</v>
@@ -72466,21 +72458,25 @@
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>Fluconazol Suspension</t>
-        </is>
-      </c>
-      <c r="C1351" t="inlineStr"/>
+          <t>FLUCONAZOL 200MG X 4 CAPS. LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>7703763480166</t>
+        </is>
+      </c>
       <c r="D1351" t="inlineStr"/>
       <c r="E1351" t="n">
-        <v>148000</v>
+        <v>14700</v>
       </c>
       <c r="F1351" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1351" t="n">
         <v>0</v>
@@ -72516,21 +72512,25 @@
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>FUNGI-FIN LOCION GOTAS TOPICA 20ML</t>
-        </is>
-      </c>
-      <c r="C1352" t="inlineStr"/>
+          <t>FLUCONAZOL 200MG X 4 CAPS.NOVAMED</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>7703546927468</t>
+        </is>
+      </c>
       <c r="D1352" t="inlineStr"/>
       <c r="E1352" t="n">
-        <v>15966.386555</v>
+        <v>10900</v>
       </c>
       <c r="F1352" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1352" t="n">
         <v>0</v>
@@ -72558,7 +72558,7 @@
       </c>
       <c r="M1352" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1352" t="inlineStr"/>
@@ -72566,21 +72566,21 @@
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>GALLETA OREO PAQUETE X 6 UNDS</t>
+          <t>Fluconazol Suspension</t>
         </is>
       </c>
       <c r="C1353" t="inlineStr"/>
       <c r="D1353" t="inlineStr"/>
       <c r="E1353" t="n">
-        <v>1932.773109</v>
+        <v>148000</v>
       </c>
       <c r="F1353" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1353" t="n">
         <v>0</v>
@@ -72608,7 +72608,7 @@
       </c>
       <c r="M1353" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1353" t="inlineStr"/>
@@ -72616,21 +72616,21 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>GASEOSA PREMIO 400ML ROJO</t>
+          <t>FUNGI-FIN LOCION GOTAS TOPICA 20ML</t>
         </is>
       </c>
       <c r="C1354" t="inlineStr"/>
       <c r="D1354" t="inlineStr"/>
       <c r="E1354" t="n">
-        <v>2941.176471</v>
+        <v>15966.386555</v>
       </c>
       <c r="F1354" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G1354" t="n">
         <v>0</v>
@@ -72666,29 +72666,21 @@
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>GASTROFAST ADVANCE</t>
-        </is>
-      </c>
-      <c r="C1355" t="inlineStr">
-        <is>
-          <t>7702057803254</t>
-        </is>
-      </c>
-      <c r="D1355" t="inlineStr">
-        <is>
-          <t>se subio A 3800 ANTES 3.600, LEYDI</t>
-        </is>
-      </c>
+          <t>GALLETA OREO PAQUETE X 6 UNDS</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr"/>
+      <c r="D1355" t="inlineStr"/>
       <c r="E1355" t="n">
-        <v>3800</v>
+        <v>1932.773109</v>
       </c>
       <c r="F1355" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G1355" t="n">
         <v>0</v>
@@ -72716,7 +72708,7 @@
       </c>
       <c r="M1355" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1355" t="inlineStr"/>
@@ -72724,21 +72716,21 @@
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>GASTROFAST ADVANCE X 240 ML</t>
+          <t>GASEOSA PREMIO 400ML ROJO</t>
         </is>
       </c>
       <c r="C1356" t="inlineStr"/>
       <c r="D1356" t="inlineStr"/>
       <c r="E1356" t="n">
-        <v>69500</v>
+        <v>2941.176471</v>
       </c>
       <c r="F1356" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G1356" t="n">
         <v>0</v>
@@ -72766,7 +72758,7 @@
       </c>
       <c r="M1356" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1356" t="inlineStr"/>
@@ -72774,25 +72766,29 @@
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>gatorade</t>
+          <t>GASTROFAST ADVANCE</t>
         </is>
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>248656546</t>
-        </is>
-      </c>
-      <c r="D1357" t="inlineStr"/>
+          <t>7702057803254</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>se subio A 3800 ANTES 3.600, LEYDI</t>
+        </is>
+      </c>
       <c r="E1357" t="n">
-        <v>3782</v>
+        <v>3800</v>
       </c>
       <c r="F1357" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G1357" t="n">
         <v>0</v>
@@ -72820,7 +72816,7 @@
       </c>
       <c r="M1357" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1357" t="inlineStr"/>
@@ -72828,18 +72824,18 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>GEL BACHUE 150GR</t>
+          <t>GASTROFAST ADVANCE X 240 ML</t>
         </is>
       </c>
       <c r="C1358" t="inlineStr"/>
       <c r="D1358" t="inlineStr"/>
       <c r="E1358" t="n">
-        <v>8800</v>
+        <v>69500</v>
       </c>
       <c r="F1358" t="n">
         <v>1</v>
@@ -72878,21 +72874,25 @@
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>GEMFIBROZILO 600 MG</t>
-        </is>
-      </c>
-      <c r="C1359" t="inlineStr"/>
+          <t>gatorade</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>248656546</t>
+        </is>
+      </c>
       <c r="D1359" t="inlineStr"/>
       <c r="E1359" t="n">
-        <v>8300</v>
+        <v>3782</v>
       </c>
       <c r="F1359" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1359" t="n">
         <v>0</v>
@@ -72920,7 +72920,7 @@
       </c>
       <c r="M1359" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1359" t="inlineStr"/>
@@ -72928,18 +72928,18 @@
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>GLICERINA CARBONATADA X 20ML FCO YOMA</t>
+          <t>GEL BACHUE 150GR</t>
         </is>
       </c>
       <c r="C1360" t="inlineStr"/>
       <c r="D1360" t="inlineStr"/>
       <c r="E1360" t="n">
-        <v>3900</v>
+        <v>8800</v>
       </c>
       <c r="F1360" t="n">
         <v>1</v>
@@ -72978,21 +72978,21 @@
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
+          <t>GEMFIBROZILO 600 MG</t>
         </is>
       </c>
       <c r="C1361" t="inlineStr"/>
       <c r="D1361" t="inlineStr"/>
       <c r="E1361" t="n">
-        <v>3361.344538</v>
+        <v>8300</v>
       </c>
       <c r="F1361" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1361" t="n">
         <v>0</v>
@@ -73020,7 +73020,7 @@
       </c>
       <c r="M1361" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1361" t="inlineStr"/>
@@ -73028,21 +73028,21 @@
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
+          <t>GLICERINA CARBONATADA X 20ML FCO YOMA</t>
         </is>
       </c>
       <c r="C1362" t="inlineStr"/>
       <c r="D1362" t="inlineStr"/>
       <c r="E1362" t="n">
-        <v>23109.243697</v>
+        <v>3900</v>
       </c>
       <c r="F1362" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="G1362" t="n">
         <v>0</v>
@@ -73070,7 +73070,7 @@
       </c>
       <c r="M1362" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1362" t="inlineStr"/>
@@ -73078,25 +73078,21 @@
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1363" t="inlineStr">
-        <is>
-          <t>7709195419279</t>
-        </is>
-      </c>
+          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr"/>
       <c r="D1363" t="inlineStr"/>
       <c r="E1363" t="n">
-        <v>24370</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1363" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1363" t="n">
         <v>0</v>
@@ -73132,21 +73128,21 @@
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
+          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
         </is>
       </c>
       <c r="C1364" t="inlineStr"/>
       <c r="D1364" t="inlineStr"/>
       <c r="E1364" t="n">
-        <v>24369.747899</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1364" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G1364" t="n">
         <v>0</v>
@@ -73182,21 +73178,25 @@
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
-        </is>
-      </c>
-      <c r="C1365" t="inlineStr"/>
+          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>7709195419279</t>
+        </is>
+      </c>
       <c r="D1365" t="inlineStr"/>
       <c r="E1365" t="n">
-        <v>23109.243697</v>
+        <v>24370</v>
       </c>
       <c r="F1365" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G1365" t="n">
         <v>0</v>
@@ -73232,21 +73232,21 @@
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>HALLS BARRA SURTIDOS SABORES</t>
+          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
         </is>
       </c>
       <c r="C1366" t="inlineStr"/>
       <c r="D1366" t="inlineStr"/>
       <c r="E1366" t="n">
-        <v>2100.840336</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1366" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="G1366" t="n">
         <v>0</v>
@@ -73282,21 +73282,21 @@
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>HALLS PEPA ROJO CEREZA X UND</t>
+          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
         </is>
       </c>
       <c r="C1367" t="inlineStr"/>
       <c r="D1367" t="inlineStr"/>
       <c r="E1367" t="n">
-        <v>336.134454</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1367" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G1367" t="n">
         <v>0</v>
@@ -73332,21 +73332,21 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>HEPATODREN JARABE FCO X 240ML</t>
+          <t>HALLS BARRA SURTIDOS SABORES</t>
         </is>
       </c>
       <c r="C1368" t="inlineStr"/>
       <c r="D1368" t="inlineStr"/>
       <c r="E1368" t="n">
-        <v>34500</v>
+        <v>2100.840336</v>
       </c>
       <c r="F1368" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G1368" t="n">
         <v>0</v>
@@ -73374,7 +73374,7 @@
       </c>
       <c r="M1368" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1368" t="inlineStr"/>
@@ -73382,21 +73382,21 @@
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>HEPATODREN X 60 CAPSULAS</t>
+          <t>HALLS PEPA ROJO CEREZA X UND</t>
         </is>
       </c>
       <c r="C1369" t="inlineStr"/>
       <c r="D1369" t="inlineStr"/>
       <c r="E1369" t="n">
-        <v>58300</v>
+        <v>336.134454</v>
       </c>
       <c r="F1369" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G1369" t="n">
         <v>0</v>
@@ -73424,7 +73424,7 @@
       </c>
       <c r="M1369" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1369" t="inlineStr"/>
@@ -73432,25 +73432,21 @@
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>Hidraplus 75 zinc uva 400ml</t>
-        </is>
-      </c>
-      <c r="C1370" t="inlineStr">
-        <is>
-          <t>7702057010928</t>
-        </is>
-      </c>
+          <t>HEPATODREN JARABE FCO X 240ML</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr"/>
       <c r="D1370" t="inlineStr"/>
       <c r="E1370" t="n">
-        <v>10600</v>
+        <v>34500</v>
       </c>
       <c r="F1370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1370" t="n">
         <v>0</v>
@@ -73486,21 +73482,21 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
+          <t>HEPATODREN X 60 CAPSULAS</t>
         </is>
       </c>
       <c r="C1371" t="inlineStr"/>
       <c r="D1371" t="inlineStr"/>
       <c r="E1371" t="n">
-        <v>15900</v>
+        <v>58300</v>
       </c>
       <c r="F1371" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1371" t="n">
         <v>0</v>
@@ -73536,22 +73532,22 @@
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
+          <t>Hidraplus 75 zinc uva 400ml</t>
         </is>
       </c>
       <c r="C1372" t="inlineStr">
         <is>
-          <t>77099475597789</t>
+          <t>7702057010928</t>
         </is>
       </c>
       <c r="D1372" t="inlineStr"/>
       <c r="E1372" t="n">
-        <v>28000</v>
+        <v>10600</v>
       </c>
       <c r="F1372" t="n">
         <v>0</v>
@@ -73590,22 +73586,18 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>Hidroxicina 0.25 JBE x 120 ML</t>
-        </is>
-      </c>
-      <c r="C1373" t="inlineStr">
-        <is>
-          <t>7707035540596</t>
-        </is>
-      </c>
+          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr"/>
       <c r="D1373" t="inlineStr"/>
       <c r="E1373" t="n">
-        <v>11000</v>
+        <v>15900</v>
       </c>
       <c r="F1373" t="n">
         <v>2</v>
@@ -73644,21 +73636,25 @@
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
-        </is>
-      </c>
-      <c r="C1374" t="inlineStr"/>
+          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>77099475597789</t>
+        </is>
+      </c>
       <c r="D1374" t="inlineStr"/>
       <c r="E1374" t="n">
-        <v>4500</v>
+        <v>28000</v>
       </c>
       <c r="F1374" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1374" t="n">
         <v>0</v>
@@ -73694,21 +73690,25 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1375" t="inlineStr"/>
+          <t>Hidroxicina 0.25 JBE x 120 ML</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>7707035540596</t>
+        </is>
+      </c>
       <c r="D1375" t="inlineStr"/>
       <c r="E1375" t="n">
-        <v>6900</v>
+        <v>11000</v>
       </c>
       <c r="F1375" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1375" t="n">
         <v>0</v>
@@ -73744,21 +73744,21 @@
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
+          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
         </is>
       </c>
       <c r="C1376" t="inlineStr"/>
       <c r="D1376" t="inlineStr"/>
       <c r="E1376" t="n">
-        <v>12000</v>
+        <v>4500</v>
       </c>
       <c r="F1376" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1376" t="n">
         <v>0</v>
@@ -73794,21 +73794,21 @@
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>Hylo Gel</t>
+          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
         </is>
       </c>
       <c r="C1377" t="inlineStr"/>
       <c r="D1377" t="inlineStr"/>
       <c r="E1377" t="n">
-        <v>131600</v>
+        <v>6900</v>
       </c>
       <c r="F1377" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1377" t="n">
         <v>0</v>
@@ -73844,25 +73844,21 @@
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>IBUPROFENO 400MG/ GENFAR</t>
-        </is>
-      </c>
-      <c r="C1378" t="inlineStr">
-        <is>
-          <t>7702605101498</t>
-        </is>
-      </c>
+          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr"/>
       <c r="D1378" t="inlineStr"/>
       <c r="E1378" t="n">
-        <v>4400</v>
+        <v>12000</v>
       </c>
       <c r="F1378" t="n">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="G1378" t="n">
         <v>0</v>
@@ -73898,22 +73894,18 @@
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>Ibuprofeno 800mg AG</t>
-        </is>
-      </c>
-      <c r="C1379" t="inlineStr">
-        <is>
-          <t>7706569000385</t>
-        </is>
-      </c>
+          <t>Hylo Gel</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr"/>
       <c r="D1379" t="inlineStr"/>
       <c r="E1379" t="n">
-        <v>800</v>
+        <v>131600</v>
       </c>
       <c r="F1379" t="n">
         <v>0</v>
@@ -73952,25 +73944,25 @@
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
+          <t>IBUPROFENO 400MG/ GENFAR</t>
         </is>
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>7705959885229</t>
+          <t>7702605101498</t>
         </is>
       </c>
       <c r="D1380" t="inlineStr"/>
       <c r="E1380" t="n">
-        <v>17900</v>
+        <v>4400</v>
       </c>
       <c r="F1380" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="G1380" t="n">
         <v>0</v>
@@ -74006,25 +73998,25 @@
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>ICE POWER 30 GR GEL COSMETICA</t>
+          <t>Ibuprofeno 800mg AG</t>
         </is>
       </c>
       <c r="C1381" t="inlineStr">
         <is>
-          <t>737186238889</t>
+          <t>7706569000385</t>
         </is>
       </c>
       <c r="D1381" t="inlineStr"/>
       <c r="E1381" t="n">
-        <v>12521.008403</v>
+        <v>800</v>
       </c>
       <c r="F1381" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1381" t="n">
         <v>0</v>
@@ -74052,7 +74044,7 @@
       </c>
       <c r="M1381" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1381" t="inlineStr"/>
@@ -74060,21 +74052,25 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
-        </is>
-      </c>
-      <c r="C1382" t="inlineStr"/>
+          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>7705959885229</t>
+        </is>
+      </c>
       <c r="D1382" t="inlineStr"/>
       <c r="E1382" t="n">
-        <v>38900</v>
+        <v>17900</v>
       </c>
       <c r="F1382" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1382" t="n">
         <v>0</v>
@@ -74110,21 +74106,25 @@
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
-        </is>
-      </c>
-      <c r="C1383" t="inlineStr"/>
+          <t>ICE POWER 30 GR GEL COSMETICA</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>737186238889</t>
+        </is>
+      </c>
       <c r="D1383" t="inlineStr"/>
       <c r="E1383" t="n">
-        <v>38900</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1383" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1383" t="n">
         <v>0</v>
@@ -74152,7 +74152,7 @@
       </c>
       <c r="M1383" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1383" t="inlineStr"/>
@@ -74160,21 +74160,21 @@
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
+          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
         </is>
       </c>
       <c r="C1384" t="inlineStr"/>
       <c r="D1384" t="inlineStr"/>
       <c r="E1384" t="n">
-        <v>8235.294118</v>
+        <v>38900</v>
       </c>
       <c r="F1384" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1384" t="n">
         <v>0</v>
@@ -74202,7 +74202,7 @@
       </c>
       <c r="M1384" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1384" t="inlineStr"/>
@@ -74210,18 +74210,18 @@
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
+          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
         </is>
       </c>
       <c r="C1385" t="inlineStr"/>
       <c r="D1385" t="inlineStr"/>
       <c r="E1385" t="n">
-        <v>9831.932773</v>
+        <v>38900</v>
       </c>
       <c r="F1385" t="n">
         <v>1</v>
@@ -74252,7 +74252,7 @@
       </c>
       <c r="M1385" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1385" t="inlineStr"/>
@@ -74260,21 +74260,21 @@
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>Jabon liquido manos mi dia</t>
+          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
         </is>
       </c>
       <c r="C1386" t="inlineStr"/>
       <c r="D1386" t="inlineStr"/>
       <c r="E1386" t="n">
-        <v>5882.352941</v>
+        <v>8235.294118</v>
       </c>
       <c r="F1386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1386" t="n">
         <v>0</v>
@@ -74310,21 +74310,21 @@
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
+          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr"/>
       <c r="D1387" t="inlineStr"/>
       <c r="E1387" t="n">
-        <v>4201.680672</v>
+        <v>9831.932773</v>
       </c>
       <c r="F1387" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1387" t="n">
         <v>0</v>
@@ -74360,18 +74360,18 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
+          <t>Jabon liquido manos mi dia</t>
         </is>
       </c>
       <c r="C1388" t="inlineStr"/>
       <c r="D1388" t="inlineStr"/>
       <c r="E1388" t="n">
-        <v>4201.680672</v>
+        <v>5882.352941</v>
       </c>
       <c r="F1388" t="n">
         <v>2</v>
@@ -74410,21 +74410,21 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>JABON PROTEX HERBAL 110GR</t>
+          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
         </is>
       </c>
       <c r="C1389" t="inlineStr"/>
       <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="n">
-        <v>4537.815126</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1389" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1389" t="n">
         <v>0</v>
@@ -74460,22 +74460,18 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>JARABE ZETYGRIP FCO 60ML</t>
-        </is>
-      </c>
-      <c r="C1390" t="inlineStr">
-        <is>
-          <t>7709805542830</t>
-        </is>
-      </c>
+          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr"/>
       <c r="D1390" t="inlineStr"/>
       <c r="E1390" t="n">
-        <v>14000</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1390" t="n">
         <v>2</v>
@@ -74506,7 +74502,7 @@
       </c>
       <c r="M1390" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1390" t="inlineStr"/>
@@ -74514,21 +74510,21 @@
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>JERINGA DE 50ML</t>
+          <t>JABON PROTEX HERBAL 110GR</t>
         </is>
       </c>
       <c r="C1391" t="inlineStr"/>
       <c r="D1391" t="inlineStr"/>
       <c r="E1391" t="n">
-        <v>2500</v>
+        <v>4537.815126</v>
       </c>
       <c r="F1391" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1391" t="n">
         <v>0</v>
@@ -74556,7 +74552,7 @@
       </c>
       <c r="M1391" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1391" t="inlineStr"/>
@@ -74564,21 +74560,25 @@
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>Jeringa desechable estéril 20ml impormedicas</t>
-        </is>
-      </c>
-      <c r="C1392" t="inlineStr"/>
+          <t>JARABE ZETYGRIP FCO 60ML</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>7709805542830</t>
+        </is>
+      </c>
       <c r="D1392" t="inlineStr"/>
       <c r="E1392" t="n">
-        <v>920</v>
+        <v>14000</v>
       </c>
       <c r="F1392" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G1392" t="n">
         <v>0</v>
@@ -74606,7 +74606,7 @@
       </c>
       <c r="M1392" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1392" t="inlineStr"/>
@@ -74614,21 +74614,21 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
+          <t>JERINGA DE 50ML</t>
         </is>
       </c>
       <c r="C1393" t="inlineStr"/>
       <c r="D1393" t="inlineStr"/>
       <c r="E1393" t="n">
-        <v>1100</v>
+        <v>2500</v>
       </c>
       <c r="F1393" t="n">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="G1393" t="n">
         <v>0</v>
@@ -74664,21 +74664,21 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>Kelocate</t>
+          <t>Jeringa desechable estéril 20ml impormedicas</t>
         </is>
       </c>
       <c r="C1394" t="inlineStr"/>
       <c r="D1394" t="inlineStr"/>
       <c r="E1394" t="n">
-        <v>180000</v>
+        <v>920</v>
       </c>
       <c r="F1394" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G1394" t="n">
         <v>0</v>
@@ -74706,7 +74706,7 @@
       </c>
       <c r="M1394" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1394" t="inlineStr"/>
@@ -74714,25 +74714,21 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
-        </is>
-      </c>
-      <c r="C1395" t="inlineStr">
-        <is>
-          <t>7702057073695</t>
-        </is>
-      </c>
+          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr"/>
       <c r="D1395" t="inlineStr"/>
       <c r="E1395" t="n">
-        <v>19500</v>
+        <v>1100</v>
       </c>
       <c r="F1395" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G1395" t="n">
         <v>0</v>
@@ -74768,22 +74764,18 @@
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
-        </is>
-      </c>
-      <c r="C1396" t="inlineStr">
-        <is>
-          <t>7709947559772</t>
-        </is>
-      </c>
+          <t>Kelocate</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr"/>
       <c r="D1396" t="inlineStr"/>
       <c r="E1396" t="n">
-        <v>15000</v>
+        <v>180000</v>
       </c>
       <c r="F1396" t="n">
         <v>0</v>
@@ -74822,18 +74814,22 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
-        </is>
-      </c>
-      <c r="C1397" t="inlineStr"/>
+          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>7702057073695</t>
+        </is>
+      </c>
       <c r="D1397" t="inlineStr"/>
       <c r="E1397" t="n">
-        <v>71000</v>
+        <v>19500</v>
       </c>
       <c r="F1397" t="n">
         <v>0</v>
@@ -74872,21 +74868,25 @@
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
-        </is>
-      </c>
-      <c r="C1398" t="inlineStr"/>
+          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>7709947559772</t>
+        </is>
+      </c>
       <c r="D1398" t="inlineStr"/>
       <c r="E1398" t="n">
-        <v>37900</v>
+        <v>15000</v>
       </c>
       <c r="F1398" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1398" t="n">
         <v>0</v>
@@ -74922,25 +74922,21 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>Levotiroxina 100mcg MK</t>
-        </is>
-      </c>
-      <c r="C1399" t="inlineStr">
-        <is>
-          <t>7702057715908</t>
-        </is>
-      </c>
+          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr"/>
       <c r="D1399" t="inlineStr"/>
       <c r="E1399" t="n">
-        <v>27900</v>
+        <v>71000</v>
       </c>
       <c r="F1399" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1399" t="n">
         <v>0</v>
@@ -74976,18 +74972,18 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>LIMA MAYOMI 10/180</t>
+          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
         </is>
       </c>
       <c r="C1400" t="inlineStr"/>
       <c r="D1400" t="inlineStr"/>
       <c r="E1400" t="n">
-        <v>3900</v>
+        <v>37900</v>
       </c>
       <c r="F1400" t="n">
         <v>1</v>
@@ -75026,21 +75022,25 @@
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
-        </is>
-      </c>
-      <c r="C1401" t="inlineStr"/>
+          <t>Levotiroxina 100mcg MK</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>7702057715908</t>
+        </is>
+      </c>
       <c r="D1401" t="inlineStr"/>
       <c r="E1401" t="n">
-        <v>16807</v>
+        <v>27900</v>
       </c>
       <c r="F1401" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1401" t="n">
         <v>0</v>
@@ -75068,7 +75068,7 @@
       </c>
       <c r="M1401" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1401" t="inlineStr"/>
@@ -75076,18 +75076,18 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
+          <t>LIMA MAYOMI 10/180</t>
         </is>
       </c>
       <c r="C1402" t="inlineStr"/>
       <c r="D1402" t="inlineStr"/>
       <c r="E1402" t="n">
-        <v>15042.016807</v>
+        <v>3900</v>
       </c>
       <c r="F1402" t="n">
         <v>1</v>
@@ -75118,7 +75118,7 @@
       </c>
       <c r="M1402" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1402" t="inlineStr"/>
@@ -75126,21 +75126,21 @@
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>LISTERINE CUIDADO TOTAL 180ML</t>
+          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
         </is>
       </c>
       <c r="C1403" t="inlineStr"/>
       <c r="D1403" t="inlineStr"/>
       <c r="E1403" t="n">
-        <v>16386.554622</v>
+        <v>16807</v>
       </c>
       <c r="F1403" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1403" t="n">
         <v>0</v>
@@ -75176,21 +75176,21 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
+          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
         </is>
       </c>
       <c r="C1404" t="inlineStr"/>
       <c r="D1404" t="inlineStr"/>
       <c r="E1404" t="n">
-        <v>3500</v>
+        <v>15042.016807</v>
       </c>
       <c r="F1404" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G1404" t="n">
         <v>0</v>
@@ -75218,7 +75218,7 @@
       </c>
       <c r="M1404" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1404" t="inlineStr"/>
@@ -75226,21 +75226,21 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+          <t>LISTERINE CUIDADO TOTAL 180ML</t>
         </is>
       </c>
       <c r="C1405" t="inlineStr"/>
       <c r="D1405" t="inlineStr"/>
       <c r="E1405" t="n">
-        <v>3500</v>
+        <v>16386.554622</v>
       </c>
       <c r="F1405" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1405" t="n">
         <v>0</v>
@@ -75268,7 +75268,7 @@
       </c>
       <c r="M1405" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1405" t="inlineStr"/>
@@ -75276,21 +75276,21 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
         </is>
       </c>
       <c r="C1406" t="inlineStr"/>
       <c r="D1406" t="inlineStr"/>
       <c r="E1406" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="F1406" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="G1406" t="n">
         <v>0</v>
@@ -75326,22 +75326,18 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>Losartan Tensofar 100 Mg</t>
-        </is>
-      </c>
-      <c r="C1407" t="inlineStr">
-        <is>
-          <t>7703546012119</t>
-        </is>
-      </c>
+          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr"/>
       <c r="D1407" t="inlineStr"/>
       <c r="E1407" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="F1407" t="n">
         <v>1</v>
@@ -75380,25 +75376,21 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
-        </is>
-      </c>
-      <c r="C1408" t="inlineStr">
-        <is>
-          <t>7501007528939</t>
-        </is>
-      </c>
+          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr"/>
       <c r="D1408" t="inlineStr"/>
       <c r="E1408" t="n">
-        <v>18907.563025</v>
+        <v>4500</v>
       </c>
       <c r="F1408" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1408" t="n">
         <v>0</v>
@@ -75426,7 +75418,7 @@
       </c>
       <c r="M1408" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1408" t="inlineStr"/>
@@ -75434,21 +75426,25 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>MANTECA DE CACAO LABIAL LIMON</t>
-        </is>
-      </c>
-      <c r="C1409" t="inlineStr"/>
+          <t>Losartan Tensofar 100 Mg</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>7703546012119</t>
+        </is>
+      </c>
       <c r="D1409" t="inlineStr"/>
       <c r="E1409" t="n">
-        <v>3361.344538</v>
+        <v>5000</v>
       </c>
       <c r="F1409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1409" t="n">
         <v>0</v>
@@ -75476,7 +75472,7 @@
       </c>
       <c r="M1409" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1409" t="inlineStr"/>
@@ -75484,18 +75480,22 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
-        </is>
-      </c>
-      <c r="C1410" t="inlineStr"/>
+          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>7501007528939</t>
+        </is>
+      </c>
       <c r="D1410" t="inlineStr"/>
       <c r="E1410" t="n">
-        <v>3361.344538</v>
+        <v>18907.563025</v>
       </c>
       <c r="F1410" t="n">
         <v>0</v>
@@ -75534,21 +75534,21 @@
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>Mega sex</t>
+          <t>MANTECA DE CACAO LABIAL LIMON</t>
         </is>
       </c>
       <c r="C1411" t="inlineStr"/>
       <c r="D1411" t="inlineStr"/>
       <c r="E1411" t="n">
-        <v>3200</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1411" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1411" t="n">
         <v>0</v>
@@ -75576,7 +75576,7 @@
       </c>
       <c r="M1411" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1411" t="inlineStr"/>
@@ -75584,26 +75584,18 @@
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>Melatonina 3mg</t>
-        </is>
-      </c>
-      <c r="C1412" t="inlineStr">
-        <is>
-          <t>7706849112906</t>
-        </is>
-      </c>
-      <c r="D1412" t="inlineStr">
-        <is>
-          <t>producto nuevo</t>
-        </is>
-      </c>
+          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr"/>
+      <c r="D1412" t="inlineStr"/>
       <c r="E1412" t="n">
-        <v>52000</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1412" t="n">
         <v>0</v>
@@ -75634,7 +75626,7 @@
       </c>
       <c r="M1412" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1412" t="inlineStr"/>
@@ -75642,25 +75634,21 @@
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
-        </is>
-      </c>
-      <c r="C1413" t="inlineStr">
-        <is>
-          <t>7707529435209</t>
-        </is>
-      </c>
+          <t>Mega sex</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr"/>
       <c r="D1413" t="inlineStr"/>
       <c r="E1413" t="n">
-        <v>36000</v>
+        <v>3200</v>
       </c>
       <c r="F1413" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G1413" t="n">
         <v>0</v>
@@ -75696,22 +75684,26 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>Meloxicam 15mg AG</t>
+          <t>Melatonina 3mg</t>
         </is>
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>7706569020437</t>
-        </is>
-      </c>
-      <c r="D1414" t="inlineStr"/>
+          <t>7706849112906</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>producto nuevo</t>
+        </is>
+      </c>
       <c r="E1414" t="n">
-        <v>1500</v>
+        <v>52000</v>
       </c>
       <c r="F1414" t="n">
         <v>0</v>
@@ -75750,21 +75742,25 @@
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
-        </is>
-      </c>
-      <c r="C1415" t="inlineStr"/>
+          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>7707529435209</t>
+        </is>
+      </c>
       <c r="D1415" t="inlineStr"/>
       <c r="E1415" t="n">
-        <v>9700</v>
+        <v>36000</v>
       </c>
       <c r="F1415" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1415" t="n">
         <v>0</v>
@@ -75800,22 +75796,22 @@
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>MELOXICAM COASPHARMA</t>
+          <t>Meloxicam 15mg AG</t>
         </is>
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>7703712036253</t>
+          <t>7706569020437</t>
         </is>
       </c>
       <c r="D1416" t="inlineStr"/>
       <c r="E1416" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F1416" t="n">
         <v>0</v>
@@ -75844,31 +75840,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1416" t="inlineStr"/>
+      <c r="M1416" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1416" t="inlineStr"/>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>metformina 850 mg pisa</t>
-        </is>
-      </c>
-      <c r="C1417" t="inlineStr">
-        <is>
-          <t>7501125188039</t>
-        </is>
-      </c>
+          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr"/>
       <c r="D1417" t="inlineStr"/>
       <c r="E1417" t="n">
-        <v>5500</v>
+        <v>9700</v>
       </c>
       <c r="F1417" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G1417" t="n">
         <v>0</v>
@@ -75904,25 +75900,25 @@
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10MG RECIPE</t>
+          <t>MELOXICAM COASPHARMA</t>
         </is>
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>7702195084355</t>
+          <t>7703712036253</t>
         </is>
       </c>
       <c r="D1418" t="inlineStr"/>
       <c r="E1418" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="F1418" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1418" t="n">
         <v>0</v>
@@ -75948,35 +75944,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1418" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1418" t="inlineStr"/>
       <c r="N1418" t="inlineStr"/>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>MICROPOR 1X3 Y</t>
+          <t>metformina 850 mg pisa</t>
         </is>
       </c>
       <c r="C1419" t="inlineStr">
         <is>
-          <t>7707282990205</t>
+          <t>7501125188039</t>
         </is>
       </c>
       <c r="D1419" t="inlineStr"/>
       <c r="E1419" t="n">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="F1419" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G1419" t="n">
         <v>0</v>
@@ -76012,25 +76004,25 @@
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>MICROPOR CINTA 1/2X5Y</t>
+          <t>METOCLOPRAMIDA 10MG RECIPE</t>
         </is>
       </c>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>7707282990182</t>
+          <t>7702195084355</t>
         </is>
       </c>
       <c r="D1420" t="inlineStr"/>
       <c r="E1420" t="n">
-        <v>3900</v>
+        <v>1000</v>
       </c>
       <c r="F1420" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G1420" t="n">
         <v>0</v>
@@ -76066,21 +76058,25 @@
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>MICROPORE COLOR PIEL 2YARDAS</t>
-        </is>
-      </c>
-      <c r="C1421" t="inlineStr"/>
+          <t>MICROPOR 1X3 Y</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>7707282990205</t>
+        </is>
+      </c>
       <c r="D1421" t="inlineStr"/>
       <c r="E1421" t="n">
-        <v>3700</v>
+        <v>5300</v>
       </c>
       <c r="F1421" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1421" t="n">
         <v>0</v>
@@ -76116,21 +76112,25 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
-        </is>
-      </c>
-      <c r="C1422" t="inlineStr"/>
+          <t>MICROPOR CINTA 1/2X5Y</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>7707282990182</t>
+        </is>
+      </c>
       <c r="D1422" t="inlineStr"/>
       <c r="E1422" t="n">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="F1422" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G1422" t="n">
         <v>0</v>
@@ -76166,25 +76166,21 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>MIELTERTOS JARABE X 240ML</t>
-        </is>
-      </c>
-      <c r="C1423" t="inlineStr">
-        <is>
-          <t>7707232095608</t>
-        </is>
-      </c>
+          <t>MICROPORE COLOR PIEL 2YARDAS</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr"/>
       <c r="D1423" t="inlineStr"/>
       <c r="E1423" t="n">
-        <v>34500</v>
+        <v>3700</v>
       </c>
       <c r="F1423" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G1423" t="n">
         <v>0</v>
@@ -76220,18 +76216,18 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>MOÑAS PARA EL PELO COLOR YIMEIJIA</t>
+          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
         </is>
       </c>
       <c r="C1424" t="inlineStr"/>
       <c r="D1424" t="inlineStr"/>
       <c r="E1424" t="n">
-        <v>4201.680672</v>
+        <v>4000</v>
       </c>
       <c r="F1424" t="n">
         <v>0</v>
@@ -76262,7 +76258,7 @@
       </c>
       <c r="M1424" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1424" t="inlineStr"/>
@@ -76270,25 +76266,25 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
-        </is>
-      </c>
-      <c r="C1425" t="inlineStr"/>
-      <c r="D1425" t="inlineStr">
-        <is>
-          <t>subio precio hector</t>
-        </is>
-      </c>
+          <t>MIELTERTOS JARABE X 240ML</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>7707232095608</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="n">
-        <v>22700</v>
+        <v>34500</v>
       </c>
       <c r="F1425" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1425" t="n">
         <v>0</v>
@@ -76324,21 +76320,21 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
+          <t>MOÑA CAUCHO TELEFONO</t>
         </is>
       </c>
       <c r="C1426" t="inlineStr"/>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="n">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="F1426" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G1426" t="n">
         <v>0</v>
@@ -76374,21 +76370,21 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>NEOSALDINA TABLETA X UND</t>
+          <t>MOÑAS PARA EL PELO COLOR YIMEIJIA</t>
         </is>
       </c>
       <c r="C1427" t="inlineStr"/>
       <c r="D1427" t="inlineStr"/>
       <c r="E1427" t="n">
-        <v>2500</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1427" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G1427" t="n">
         <v>0</v>
@@ -76416,7 +76412,7 @@
       </c>
       <c r="M1427" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1427" t="inlineStr"/>
@@ -76424,21 +76420,25 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>NIFEDIPINO 30MG NOVAMED</t>
+          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
         </is>
       </c>
       <c r="C1428" t="inlineStr"/>
-      <c r="D1428" t="inlineStr"/>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>subio precio hector</t>
+        </is>
+      </c>
       <c r="E1428" t="n">
-        <v>19000</v>
+        <v>22700</v>
       </c>
       <c r="F1428" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1428" t="n">
         <v>0</v>
@@ -76474,21 +76474,21 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
+          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
         </is>
       </c>
       <c r="C1429" t="inlineStr"/>
       <c r="D1429" t="inlineStr"/>
       <c r="E1429" t="n">
-        <v>23000</v>
+        <v>5500</v>
       </c>
       <c r="F1429" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G1429" t="n">
         <v>0</v>
@@ -76524,21 +76524,21 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>NITOXIPAR X 6 TABLETAS</t>
+          <t>NEOSALDINA TABLETA X UND</t>
         </is>
       </c>
       <c r="C1430" t="inlineStr"/>
       <c r="D1430" t="inlineStr"/>
       <c r="E1430" t="n">
-        <v>24500</v>
+        <v>2500</v>
       </c>
       <c r="F1430" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G1430" t="n">
         <v>0</v>
@@ -76574,21 +76574,21 @@
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>NORAVER SPRAY CEREZA 120ML</t>
+          <t>NIFEDIPINO 30MG NOVAMED</t>
         </is>
       </c>
       <c r="C1431" t="inlineStr"/>
       <c r="D1431" t="inlineStr"/>
       <c r="E1431" t="n">
-        <v>52900</v>
+        <v>19000</v>
       </c>
       <c r="F1431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1431" t="n">
         <v>0</v>
@@ -76624,25 +76624,21 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
-        </is>
-      </c>
-      <c r="C1432" t="inlineStr">
-        <is>
-          <t>7702027041662</t>
-        </is>
-      </c>
+          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr"/>
       <c r="D1432" t="inlineStr"/>
       <c r="E1432" t="n">
-        <v>6300</v>
+        <v>23000</v>
       </c>
       <c r="F1432" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1432" t="n">
         <v>0</v>
@@ -76678,21 +76674,21 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+          <t>NITOXIPAR X 6 TABLETAS</t>
         </is>
       </c>
       <c r="C1433" t="inlineStr"/>
       <c r="D1433" t="inlineStr"/>
       <c r="E1433" t="n">
-        <v>8823.529412</v>
+        <v>24500</v>
       </c>
       <c r="F1433" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1433" t="n">
         <v>0</v>
@@ -76720,7 +76716,7 @@
       </c>
       <c r="M1433" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1433" t="inlineStr"/>
@@ -76728,25 +76724,21 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
-        </is>
-      </c>
-      <c r="C1434" t="inlineStr">
-        <is>
-          <t>7702026158644</t>
-        </is>
-      </c>
+          <t>NORAVER SPRAY CEREZA 120ML</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr"/>
       <c r="D1434" t="inlineStr"/>
       <c r="E1434" t="n">
-        <v>8823.529412</v>
+        <v>52900</v>
       </c>
       <c r="F1434" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1434" t="n">
         <v>0</v>
@@ -76774,7 +76766,7 @@
       </c>
       <c r="M1434" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1434" t="inlineStr"/>
@@ -76782,25 +76774,25 @@
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JBE 120ML</t>
+          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
         </is>
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>7707355053363</t>
+          <t>7702027041662</t>
         </is>
       </c>
       <c r="D1435" t="inlineStr"/>
       <c r="E1435" t="n">
-        <v>22700</v>
+        <v>6300</v>
       </c>
       <c r="F1435" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>
@@ -76836,22 +76828,18 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
-        </is>
-      </c>
-      <c r="C1436" t="inlineStr">
-        <is>
-          <t>7707355053356</t>
-        </is>
-      </c>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr"/>
       <c r="D1436" t="inlineStr"/>
       <c r="E1436" t="n">
-        <v>17200</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1436" t="n">
         <v>0</v>
@@ -76882,7 +76870,7 @@
       </c>
       <c r="M1436" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1436" t="inlineStr"/>
@@ -76890,21 +76878,25 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>NUTRIBELL ACEITE DE COCO</t>
-        </is>
-      </c>
-      <c r="C1437" t="inlineStr"/>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>7702026158644</t>
+        </is>
+      </c>
       <c r="D1437" t="inlineStr"/>
       <c r="E1437" t="n">
-        <v>2700</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1437" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1437" t="n">
         <v>0</v>
@@ -76932,7 +76924,7 @@
       </c>
       <c r="M1437" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1437" t="inlineStr"/>
@@ -76940,29 +76932,25 @@
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Omega 3 6 9 suplemento totalmax</t>
+          <t>NOXPIRIN JUNIOR JBE 120ML</t>
         </is>
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>7707529434974</t>
-        </is>
-      </c>
-      <c r="D1438" t="inlineStr">
-        <is>
-          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
-        </is>
-      </c>
+          <t>7707355053363</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr"/>
       <c r="E1438" t="n">
-        <v>35000</v>
+        <v>22700</v>
       </c>
       <c r="F1438" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1438" t="n">
         <v>0</v>
@@ -76998,18 +76986,22 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1439" t="inlineStr"/>
+          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>7707355053356</t>
+        </is>
+      </c>
       <c r="D1439" t="inlineStr"/>
       <c r="E1439" t="n">
-        <v>5500</v>
+        <v>17200</v>
       </c>
       <c r="F1439" t="n">
         <v>0</v>
@@ -77048,25 +77040,21 @@
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
-        </is>
-      </c>
-      <c r="C1440" t="inlineStr">
-        <is>
-          <t>7707529435940</t>
-        </is>
-      </c>
+          <t>NUTRIBELL ACEITE DE COCO</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr"/>
       <c r="D1440" t="inlineStr"/>
       <c r="E1440" t="n">
-        <v>35000</v>
+        <v>2700</v>
       </c>
       <c r="F1440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1440" t="n">
         <v>0</v>
@@ -77102,21 +77090,29 @@
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
-        </is>
-      </c>
-      <c r="C1441" t="inlineStr"/>
-      <c r="D1441" t="inlineStr"/>
+          <t>Omega 3 6 9 suplemento totalmax</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>7707529434974</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
+        </is>
+      </c>
       <c r="E1441" t="n">
-        <v>48000</v>
+        <v>35000</v>
       </c>
       <c r="F1441" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1441" t="n">
         <v>0</v>
@@ -77152,25 +77148,21 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>OROCAL CALCIO 600MG</t>
+          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
         </is>
       </c>
       <c r="C1442" t="inlineStr"/>
-      <c r="D1442" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="D1442" t="inlineStr"/>
       <c r="E1442" t="n">
-        <v>30500</v>
+        <v>5500</v>
       </c>
       <c r="F1442" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1442" t="n">
         <v>0</v>
@@ -77206,21 +77198,25 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>PALA DE MADERA RASPACALLO</t>
-        </is>
-      </c>
-      <c r="C1443" t="inlineStr"/>
+          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>7707529435940</t>
+        </is>
+      </c>
       <c r="D1443" t="inlineStr"/>
       <c r="E1443" t="n">
-        <v>4000</v>
+        <v>35000</v>
       </c>
       <c r="F1443" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1443" t="n">
         <v>0</v>
@@ -77256,21 +77252,21 @@
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>PALO DE NARANJO X UNIDAD</t>
+          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
         </is>
       </c>
       <c r="C1444" t="inlineStr"/>
       <c r="D1444" t="inlineStr"/>
       <c r="E1444" t="n">
-        <v>400</v>
+        <v>48000</v>
       </c>
       <c r="F1444" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G1444" t="n">
         <v>0</v>
@@ -77306,22 +77302,22 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
-        </is>
-      </c>
-      <c r="C1445" t="inlineStr">
-        <is>
-          <t>7704412170896</t>
-        </is>
-      </c>
-      <c r="D1445" t="inlineStr"/>
+          <t>OROCAL CALCIO 600MG</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr"/>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E1445" t="n">
-        <v>6200</v>
+        <v>30500</v>
       </c>
       <c r="F1445" t="n">
         <v>1</v>
@@ -77360,18 +77356,18 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
+          <t>PALA DE MADERA RASPACALLO</t>
         </is>
       </c>
       <c r="C1446" t="inlineStr"/>
       <c r="D1446" t="inlineStr"/>
       <c r="E1446" t="n">
-        <v>14285.714286</v>
+        <v>4000</v>
       </c>
       <c r="F1446" t="n">
         <v>1</v>
@@ -77402,7 +77398,7 @@
       </c>
       <c r="M1446" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1446" t="inlineStr"/>
@@ -77410,21 +77406,21 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
+          <t>PALO DE NARANJO X UNIDAD</t>
         </is>
       </c>
       <c r="C1447" t="inlineStr"/>
       <c r="D1447" t="inlineStr"/>
       <c r="E1447" t="n">
-        <v>28991.596639</v>
+        <v>400</v>
       </c>
       <c r="F1447" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G1447" t="n">
         <v>0</v>
@@ -77452,7 +77448,7 @@
       </c>
       <c r="M1447" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1447" t="inlineStr"/>
@@ -77460,18 +77456,22 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
-        </is>
-      </c>
-      <c r="C1448" t="inlineStr"/>
+          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>7704412170896</t>
+        </is>
+      </c>
       <c r="D1448" t="inlineStr"/>
       <c r="E1448" t="n">
-        <v>41176.470588</v>
+        <v>6200</v>
       </c>
       <c r="F1448" t="n">
         <v>1</v>
@@ -77502,7 +77502,7 @@
       </c>
       <c r="M1448" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1448" t="inlineStr"/>
@@ -77510,22 +77510,18 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>Pañales Winny Etapa 5 X PAQUETE</t>
-        </is>
-      </c>
-      <c r="C1449" t="inlineStr">
-        <is>
-          <t>7701021114174</t>
-        </is>
-      </c>
+          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr"/>
       <c r="D1449" t="inlineStr"/>
       <c r="E1449" t="n">
-        <v>41849</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1449" t="n">
         <v>1</v>
@@ -77564,21 +77560,21 @@
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>PAÑALWINNY ETA 5 X 16 UND</t>
+          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
         </is>
       </c>
       <c r="C1450" t="inlineStr"/>
       <c r="D1450" t="inlineStr"/>
       <c r="E1450" t="n">
-        <v>24369.747899</v>
+        <v>28991.596639</v>
       </c>
       <c r="F1450" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1450" t="n">
         <v>0</v>
@@ -77614,21 +77610,21 @@
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>pañitos humedos pequeñin 100unidades</t>
+          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
         </is>
       </c>
       <c r="C1451" t="inlineStr"/>
       <c r="D1451" t="inlineStr"/>
       <c r="E1451" t="n">
-        <v>10925</v>
+        <v>41176.470588</v>
       </c>
       <c r="F1451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1451" t="n">
         <v>0</v>
@@ -77664,21 +77660,25 @@
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1452" t="inlineStr"/>
+          <t>Pañales Winny Etapa 5 X PAQUETE</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>7701021114174</t>
+        </is>
+      </c>
       <c r="D1452" t="inlineStr"/>
       <c r="E1452" t="n">
-        <v>14900</v>
+        <v>41849</v>
       </c>
       <c r="F1452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1452" t="n">
         <v>0</v>
@@ -77706,7 +77706,7 @@
       </c>
       <c r="M1452" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1452" t="inlineStr"/>
@@ -77714,21 +77714,21 @@
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Panotil B x 8ML</t>
+          <t>PAÑALWINNY ETA 5 X 16 UND</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr"/>
       <c r="D1453" t="inlineStr"/>
       <c r="E1453" t="n">
-        <v>26400</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1453" t="n">
         <v>0</v>
@@ -77756,7 +77756,7 @@
       </c>
       <c r="M1453" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1453" t="inlineStr"/>
@@ -77764,25 +77764,21 @@
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>PANTENE ACONDICIONADOR</t>
-        </is>
-      </c>
-      <c r="C1454" t="inlineStr">
-        <is>
-          <t>7500435153683</t>
-        </is>
-      </c>
+          <t>pañitos humedos pequeñin 100unidades</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr"/>
       <c r="D1454" t="inlineStr"/>
       <c r="E1454" t="n">
-        <v>1500</v>
+        <v>10925</v>
       </c>
       <c r="F1454" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G1454" t="n">
         <v>0</v>
@@ -77810,7 +77806,7 @@
       </c>
       <c r="M1454" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1454" t="inlineStr"/>
@@ -77818,25 +77814,21 @@
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>PARCHE ACNE FIGURAS</t>
-        </is>
-      </c>
-      <c r="C1455" t="inlineStr">
-        <is>
-          <t>6971622250767</t>
-        </is>
-      </c>
+          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr"/>
       <c r="D1455" t="inlineStr"/>
       <c r="E1455" t="n">
-        <v>5882.352941</v>
+        <v>14900</v>
       </c>
       <c r="F1455" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1455" t="n">
         <v>0</v>
@@ -77864,7 +77856,7 @@
       </c>
       <c r="M1455" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1455" t="inlineStr"/>
@@ -77872,21 +77864,21 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Parche Ocular Colostol</t>
+          <t>Panotil B x 8ML</t>
         </is>
       </c>
       <c r="C1456" t="inlineStr"/>
       <c r="D1456" t="inlineStr"/>
       <c r="E1456" t="n">
-        <v>1300</v>
+        <v>26400</v>
       </c>
       <c r="F1456" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G1456" t="n">
         <v>0</v>
@@ -77922,25 +77914,25 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
+          <t>PANTENE ACONDICIONADOR</t>
         </is>
       </c>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>7501033957413</t>
+          <t>7500435153683</t>
         </is>
       </c>
       <c r="D1457" t="inlineStr"/>
       <c r="E1457" t="n">
-        <v>10600</v>
+        <v>1500</v>
       </c>
       <c r="F1457" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1457" t="n">
         <v>0</v>
@@ -77976,26 +77968,22 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
+          <t>PARCHE ACNE FIGURAS</t>
         </is>
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>7501033961557</t>
-        </is>
-      </c>
-      <c r="D1458" t="inlineStr">
-        <is>
-          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
-        </is>
-      </c>
+          <t>6971622250767</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr"/>
       <c r="E1458" t="n">
-        <v>10900</v>
+        <v>5882.352941</v>
       </c>
       <c r="F1458" t="n">
         <v>0</v>
@@ -78026,7 +78014,7 @@
       </c>
       <c r="M1458" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1458" t="inlineStr"/>
@@ -78034,29 +78022,21 @@
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
-        </is>
-      </c>
-      <c r="C1459" t="inlineStr">
-        <is>
-          <t>7501033957376</t>
-        </is>
-      </c>
-      <c r="D1459" t="inlineStr">
-        <is>
-          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
-        </is>
-      </c>
+          <t>Parche Ocular Colostol</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr"/>
+      <c r="D1459" t="inlineStr"/>
       <c r="E1459" t="n">
-        <v>10900</v>
+        <v>1300</v>
       </c>
       <c r="F1459" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G1459" t="n">
         <v>0</v>
@@ -78092,21 +78072,21 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>PEGANTE GLUE X 10GR X UND</t>
+          <t>PARCHE PARA EL ACNE</t>
         </is>
       </c>
       <c r="C1460" t="inlineStr"/>
       <c r="D1460" t="inlineStr"/>
       <c r="E1460" t="n">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="F1460" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1460" t="n">
         <v>0</v>
@@ -78142,21 +78122,25 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>PEINETA COLA DE RATON METALICA</t>
-        </is>
-      </c>
-      <c r="C1461" t="inlineStr"/>
+          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>7501033957413</t>
+        </is>
+      </c>
       <c r="D1461" t="inlineStr"/>
       <c r="E1461" t="n">
-        <v>4700</v>
+        <v>10600</v>
       </c>
       <c r="F1461" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1461" t="n">
         <v>0</v>
@@ -78192,21 +78176,29 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>PERFILADORES DE CEJAS</t>
-        </is>
-      </c>
-      <c r="C1462" t="inlineStr"/>
-      <c r="D1462" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>7501033961557</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
+        </is>
+      </c>
       <c r="E1462" t="n">
-        <v>3900</v>
+        <v>10900</v>
       </c>
       <c r="F1462" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1462" t="n">
         <v>0</v>
@@ -78242,21 +78234,29 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
-        </is>
-      </c>
-      <c r="C1463" t="inlineStr"/>
-      <c r="D1463" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>7501033957376</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+        </is>
+      </c>
       <c r="E1463" t="n">
-        <v>27983.193277</v>
+        <v>10900</v>
       </c>
       <c r="F1463" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1463" t="n">
         <v>0</v>
@@ -78284,7 +78284,7 @@
       </c>
       <c r="M1463" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1463" t="inlineStr"/>
@@ -78292,21 +78292,21 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>POPETAS SURTIDAS X UND</t>
+          <t>PEGANTE GLUE X 10GR X UND</t>
         </is>
       </c>
       <c r="C1464" t="inlineStr"/>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="n">
-        <v>2521.008403</v>
+        <v>2000</v>
       </c>
       <c r="F1464" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1464" t="n">
         <v>0</v>
@@ -78334,7 +78334,7 @@
       </c>
       <c r="M1464" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1464" t="inlineStr"/>
@@ -78342,21 +78342,21 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+          <t>PEINETA COLA DE RATON METALICA</t>
         </is>
       </c>
       <c r="C1465" t="inlineStr"/>
       <c r="D1465" t="inlineStr"/>
       <c r="E1465" t="n">
-        <v>20500</v>
+        <v>4700</v>
       </c>
       <c r="F1465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1465" t="n">
         <v>0</v>
@@ -78392,26 +78392,18 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>privatos miel limon la francol 120ml</t>
-        </is>
-      </c>
-      <c r="C1466" t="inlineStr">
-        <is>
-          <t>7702207163948</t>
-        </is>
-      </c>
-      <c r="D1466" t="inlineStr">
-        <is>
-          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
-        </is>
-      </c>
+          <t>PERFILADORES DE CEJAS</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr"/>
+      <c r="D1466" t="inlineStr"/>
       <c r="E1466" t="n">
-        <v>35900</v>
+        <v>3900</v>
       </c>
       <c r="F1466" t="n">
         <v>1</v>
@@ -78450,21 +78442,21 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
+          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
         </is>
       </c>
       <c r="C1467" t="inlineStr"/>
       <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="n">
-        <v>0</v>
+        <v>27983.193277</v>
       </c>
       <c r="F1467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1467" t="n">
         <v>0</v>
@@ -78500,21 +78492,21 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>PROTECTOR NOSOTRAS LARGOS</t>
+          <t>POPETAS SURTIDAS X UND</t>
         </is>
       </c>
       <c r="C1468" t="inlineStr"/>
       <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="n">
-        <v>3700</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1468" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1468" t="n">
         <v>0</v>
@@ -78542,7 +78534,7 @@
       </c>
       <c r="M1468" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1468" t="inlineStr"/>
@@ -78550,21 +78542,21 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
+          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
         </is>
       </c>
       <c r="C1469" t="inlineStr"/>
       <c r="D1469" t="inlineStr"/>
       <c r="E1469" t="n">
-        <v>8900</v>
+        <v>20500</v>
       </c>
       <c r="F1469" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1469" t="n">
         <v>0</v>
@@ -78600,21 +78592,29 @@
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>Protector Solar Sunaid</t>
-        </is>
-      </c>
-      <c r="C1470" t="inlineStr"/>
-      <c r="D1470" t="inlineStr"/>
+          <t>privatos miel limon la francol 120ml</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>7702207163948</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
+        </is>
+      </c>
       <c r="E1470" t="n">
-        <v>158000</v>
+        <v>35900</v>
       </c>
       <c r="F1470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1470" t="n">
         <v>0</v>
@@ -78650,25 +78650,21 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>778</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>Prueba de embarazo esfero</t>
-        </is>
-      </c>
-      <c r="C1471" t="inlineStr">
-        <is>
-          <t>7709299854228</t>
-        </is>
-      </c>
+          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr"/>
       <c r="D1471" t="inlineStr"/>
       <c r="E1471" t="n">
-        <v>16500</v>
+        <v>0</v>
       </c>
       <c r="F1471" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1471" t="n">
         <v>0</v>
@@ -78696,7 +78692,7 @@
       </c>
       <c r="M1471" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1471" t="inlineStr"/>
@@ -78704,25 +78700,21 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Prueba de embarazo HCG cassette begut</t>
-        </is>
-      </c>
-      <c r="C1472" t="inlineStr">
-        <is>
-          <t>7707282990953</t>
-        </is>
-      </c>
+          <t>PROTECTOR NOSOTRAS LARGOS</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr"/>
       <c r="D1472" t="inlineStr"/>
       <c r="E1472" t="n">
-        <v>8900</v>
+        <v>3700</v>
       </c>
       <c r="F1472" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G1472" t="n">
         <v>0</v>
@@ -78758,18 +78750,18 @@
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>PUSHER METALICO</t>
+          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
         </is>
       </c>
       <c r="C1473" t="inlineStr"/>
       <c r="D1473" t="inlineStr"/>
       <c r="E1473" t="n">
-        <v>4300</v>
+        <v>8900</v>
       </c>
       <c r="F1473" t="n">
         <v>1</v>
@@ -78808,21 +78800,21 @@
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
+          <t>Protector Solar Sunaid</t>
         </is>
       </c>
       <c r="C1474" t="inlineStr"/>
       <c r="D1474" t="inlineStr"/>
       <c r="E1474" t="n">
-        <v>17900</v>
+        <v>158000</v>
       </c>
       <c r="F1474" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1474" t="n">
         <v>0</v>
@@ -78858,25 +78850,25 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>Recolector de orina granandina</t>
+          <t>Prueba de embarazo esfero</t>
         </is>
       </c>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>7707233050590</t>
+          <t>7709299854228</t>
         </is>
       </c>
       <c r="D1475" t="inlineStr"/>
       <c r="E1475" t="n">
-        <v>673</v>
+        <v>16500</v>
       </c>
       <c r="F1475" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="G1475" t="n">
         <v>0</v>
@@ -78904,7 +78896,7 @@
       </c>
       <c r="M1475" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1475" t="inlineStr"/>
@@ -78912,21 +78904,25 @@
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
-        </is>
-      </c>
-      <c r="C1476" t="inlineStr"/>
+          <t>Prueba de embarazo HCG cassette begut</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>7707282990953</t>
+        </is>
+      </c>
       <c r="D1476" t="inlineStr"/>
       <c r="E1476" t="n">
-        <v>3820</v>
+        <v>8900</v>
       </c>
       <c r="F1476" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G1476" t="n">
         <v>0</v>
@@ -78962,21 +78958,21 @@
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>RegistroManual - Registro manual</t>
+          <t>PUSHER METALICO</t>
         </is>
       </c>
       <c r="C1477" t="inlineStr"/>
       <c r="D1477" t="inlineStr"/>
       <c r="E1477" t="n">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="F1477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1477" t="n">
         <v>0</v>
@@ -79004,7 +79000,7 @@
       </c>
       <c r="M1477" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1477" t="inlineStr"/>
@@ -79012,21 +79008,21 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>REMOVEDOR DE ESMALTE 60CC</t>
+          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
         </is>
       </c>
       <c r="C1478" t="inlineStr"/>
       <c r="D1478" t="inlineStr"/>
       <c r="E1478" t="n">
-        <v>3500</v>
+        <v>17900</v>
       </c>
       <c r="F1478" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1478" t="n">
         <v>0</v>
@@ -79062,25 +79058,25 @@
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
+          <t>Recolector de orina granandina</t>
         </is>
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>7591005981270</t>
+          <t>7707233050590</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr"/>
       <c r="E1479" t="n">
-        <v>9500</v>
+        <v>673</v>
       </c>
       <c r="F1479" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G1479" t="n">
         <v>0</v>
@@ -79108,7 +79104,7 @@
       </c>
       <c r="M1479" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1479" t="inlineStr"/>
@@ -79116,25 +79112,21 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
-        </is>
-      </c>
-      <c r="C1480" t="inlineStr">
-        <is>
-          <t>7503051868245</t>
-        </is>
-      </c>
+          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr"/>
       <c r="D1480" t="inlineStr"/>
       <c r="E1480" t="n">
-        <v>20900</v>
+        <v>3820</v>
       </c>
       <c r="F1480" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1480" t="n">
         <v>0</v>
@@ -79170,22 +79162,18 @@
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1MG X 20 TABL MK</t>
-        </is>
-      </c>
-      <c r="C1481" t="inlineStr">
-        <is>
-          <t>7702057079642</t>
-        </is>
-      </c>
+          <t>RegistroManual - Registro manual</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr"/>
       <c r="D1481" t="inlineStr"/>
       <c r="E1481" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="F1481" t="n">
         <v>0</v>
@@ -79216,7 +79204,7 @@
       </c>
       <c r="M1481" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1481" t="inlineStr"/>
@@ -79224,21 +79212,21 @@
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>Ryaltris Spray Nasal 240 dosis</t>
+          <t>REMOVEDOR DE ESMALTE 60CC</t>
         </is>
       </c>
       <c r="C1482" t="inlineStr"/>
       <c r="D1482" t="inlineStr"/>
       <c r="E1482" t="n">
-        <v>216400</v>
+        <v>3500</v>
       </c>
       <c r="F1482" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1482" t="n">
         <v>0</v>
@@ -79274,22 +79262,22 @@
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
         </is>
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>7706849116676</t>
+          <t>7591005981270</t>
         </is>
       </c>
       <c r="D1483" t="inlineStr"/>
       <c r="E1483" t="n">
-        <v>31500</v>
+        <v>9500</v>
       </c>
       <c r="F1483" t="n">
         <v>1</v>
@@ -79328,21 +79316,25 @@
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>SCOBIT PURGANTE 60GR</t>
-        </is>
-      </c>
-      <c r="C1484" t="inlineStr"/>
+          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>7503051868245</t>
+        </is>
+      </c>
       <c r="D1484" t="inlineStr"/>
       <c r="E1484" t="n">
-        <v>15238.095238</v>
+        <v>20900</v>
       </c>
       <c r="F1484" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1484" t="n">
         <v>0</v>
@@ -79370,7 +79362,7 @@
       </c>
       <c r="M1484" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1484" t="inlineStr"/>
@@ -79378,21 +79370,25 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
-        </is>
-      </c>
-      <c r="C1485" t="inlineStr"/>
+          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>7702057079642</t>
+        </is>
+      </c>
       <c r="D1485" t="inlineStr"/>
       <c r="E1485" t="n">
-        <v>6554.621849</v>
+        <v>13000</v>
       </c>
       <c r="F1485" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1485" t="n">
         <v>0</v>
@@ -79420,7 +79416,7 @@
       </c>
       <c r="M1485" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1485" t="inlineStr"/>
@@ -79428,25 +79424,21 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>SHAMPOO PANTENE COLAGENO</t>
-        </is>
-      </c>
-      <c r="C1486" t="inlineStr">
-        <is>
-          <t>7500435191500</t>
-        </is>
-      </c>
+          <t>Ryaltris Spray Nasal 240 dosis</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr"/>
       <c r="D1486" t="inlineStr"/>
       <c r="E1486" t="n">
-        <v>1429</v>
+        <v>216400</v>
       </c>
       <c r="F1486" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1486" t="n">
         <v>0</v>
@@ -79474,7 +79466,7 @@
       </c>
       <c r="M1486" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1486" t="inlineStr"/>
@@ -79482,21 +79474,25 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>SILDENAFIL 50MG TQ</t>
-        </is>
-      </c>
-      <c r="C1487" t="inlineStr"/>
+          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>7706849116676</t>
+        </is>
+      </c>
       <c r="D1487" t="inlineStr"/>
       <c r="E1487" t="n">
-        <v>5000</v>
+        <v>31500</v>
       </c>
       <c r="F1487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1487" t="n">
         <v>0</v>
@@ -79532,25 +79528,21 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>SILIMARINA 167MG EPANAT</t>
-        </is>
-      </c>
-      <c r="C1488" t="inlineStr">
-        <is>
-          <t>7706849115921</t>
-        </is>
-      </c>
+          <t>SCOBIT PURGANTE 60GR</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr"/>
       <c r="D1488" t="inlineStr"/>
       <c r="E1488" t="n">
-        <v>2000</v>
+        <v>15238.095238</v>
       </c>
       <c r="F1488" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="G1488" t="n">
         <v>0</v>
@@ -79578,7 +79570,7 @@
       </c>
       <c r="M1488" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1488" t="inlineStr"/>
@@ -79586,21 +79578,21 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>SMECTA 3GR NARANJA S/B</t>
+          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr"/>
       <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="n">
-        <v>8900</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1489" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G1489" t="n">
         <v>0</v>
@@ -79628,7 +79620,7 @@
       </c>
       <c r="M1489" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1489" t="inlineStr"/>
@@ -79636,21 +79628,25 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>SONDA FOLEY 2 VIAS BAL #18</t>
-        </is>
-      </c>
-      <c r="C1490" t="inlineStr"/>
+          <t>SHAMPOO PANTENE COLAGENO</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>7500435191500</t>
+        </is>
+      </c>
       <c r="D1490" t="inlineStr"/>
       <c r="E1490" t="n">
-        <v>7500</v>
+        <v>1429</v>
       </c>
       <c r="F1490" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1490" t="n">
         <v>0</v>
@@ -79678,7 +79674,7 @@
       </c>
       <c r="M1490" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1490" t="inlineStr"/>
@@ -79686,21 +79682,21 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>SONDA NELATON #6</t>
+          <t>SILDENAFIL 50MG TQ</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr"/>
       <c r="D1491" t="inlineStr"/>
       <c r="E1491" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="F1491" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1491" t="n">
         <v>0</v>
@@ -79736,21 +79732,25 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>SPRAY NASAL MOMETASONA 18ML</t>
-        </is>
-      </c>
-      <c r="C1492" t="inlineStr"/>
+          <t>SILIMARINA 167MG EPANAT</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>7706849115921</t>
+        </is>
+      </c>
       <c r="D1492" t="inlineStr"/>
       <c r="E1492" t="n">
-        <v>36900</v>
+        <v>2000</v>
       </c>
       <c r="F1492" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G1492" t="n">
         <v>0</v>
@@ -79786,21 +79786,21 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>suerox mora azul x630ml</t>
+          <t>SMECTA 3GR NARANJA S/B</t>
         </is>
       </c>
       <c r="C1493" t="inlineStr"/>
       <c r="D1493" t="inlineStr"/>
       <c r="E1493" t="n">
-        <v>5882.352941</v>
+        <v>8900</v>
       </c>
       <c r="F1493" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G1493" t="n">
         <v>0</v>
@@ -79828,7 +79828,7 @@
       </c>
       <c r="M1493" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1493" t="inlineStr"/>
@@ -79836,25 +79836,21 @@
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1494" t="inlineStr">
-        <is>
-          <t>7703712035034</t>
-        </is>
-      </c>
+          <t>SONDA FOLEY 2 VIAS BAL #18</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr"/>
       <c r="D1494" t="inlineStr"/>
       <c r="E1494" t="n">
-        <v>14800</v>
+        <v>7500</v>
       </c>
       <c r="F1494" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1494" t="n">
         <v>0</v>
@@ -79890,21 +79886,21 @@
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
+          <t>SONDA NELATON #6</t>
         </is>
       </c>
       <c r="C1495" t="inlineStr"/>
       <c r="D1495" t="inlineStr"/>
       <c r="E1495" t="n">
-        <v>3781.512605</v>
+        <v>2500</v>
       </c>
       <c r="F1495" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1495" t="n">
         <v>0</v>
@@ -79932,7 +79928,7 @@
       </c>
       <c r="M1495" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1495" t="inlineStr"/>
@@ -79940,21 +79936,21 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
+          <t>SPRAY NASAL MOMETASONA 18ML</t>
         </is>
       </c>
       <c r="C1496" t="inlineStr"/>
       <c r="D1496" t="inlineStr"/>
       <c r="E1496" t="n">
-        <v>5210.084034</v>
+        <v>36900</v>
       </c>
       <c r="F1496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1496" t="n">
         <v>0</v>
@@ -79982,7 +79978,7 @@
       </c>
       <c r="M1496" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1496" t="inlineStr"/>
@@ -79990,21 +79986,21 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
+          <t>suerox mora azul x630ml</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr"/>
       <c r="D1497" t="inlineStr"/>
       <c r="E1497" t="n">
-        <v>8319.327730999999</v>
+        <v>5882.352941</v>
       </c>
       <c r="F1497" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1497" t="n">
         <v>0</v>
@@ -80040,21 +80036,25 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>SULZINC SUSP X 80ML HUMAX</t>
-        </is>
-      </c>
-      <c r="C1498" t="inlineStr"/>
+          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>7703712035034</t>
+        </is>
+      </c>
       <c r="D1498" t="inlineStr"/>
       <c r="E1498" t="n">
-        <v>22400</v>
+        <v>14800</v>
       </c>
       <c r="F1498" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1498" t="n">
         <v>0</v>
@@ -80090,12 +80090,12 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>SUNDARK FPS 60 CON TAPA</t>
+          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
         </is>
       </c>
       <c r="C1499" t="inlineStr"/>
@@ -80104,7 +80104,7 @@
         <v>3781.512605</v>
       </c>
       <c r="F1499" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1499" t="n">
         <v>0</v>
@@ -80140,18 +80140,18 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>Synthroid 125 mcg</t>
+          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
         </is>
       </c>
       <c r="C1500" t="inlineStr"/>
       <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="n">
-        <v>178000</v>
+        <v>5210.084034</v>
       </c>
       <c r="F1500" t="n">
         <v>0</v>
@@ -80182,7 +80182,7 @@
       </c>
       <c r="M1500" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1500" t="inlineStr"/>
@@ -80190,25 +80190,21 @@
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>Talco medicado Neofungina 40gm</t>
-        </is>
-      </c>
-      <c r="C1501" t="inlineStr">
-        <is>
-          <t>7706142707106</t>
-        </is>
-      </c>
+          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr"/>
       <c r="D1501" t="inlineStr"/>
       <c r="E1501" t="n">
-        <v>14900</v>
+        <v>8319.327730999999</v>
       </c>
       <c r="F1501" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1501" t="n">
         <v>0</v>
@@ -80236,7 +80232,7 @@
       </c>
       <c r="M1501" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1501" t="inlineStr"/>
@@ -80244,21 +80240,21 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
+          <t>SULZINC SUSP X 80ML HUMAX</t>
         </is>
       </c>
       <c r="C1502" t="inlineStr"/>
       <c r="D1502" t="inlineStr"/>
       <c r="E1502" t="n">
-        <v>13300</v>
+        <v>22400</v>
       </c>
       <c r="F1502" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1502" t="n">
         <v>0</v>
@@ -80294,21 +80290,21 @@
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
+          <t>SUNDARK FPS 60 CON TAPA</t>
         </is>
       </c>
       <c r="C1503" t="inlineStr"/>
       <c r="D1503" t="inlineStr"/>
       <c r="E1503" t="n">
-        <v>4874</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1503" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G1503" t="n">
         <v>0</v>
@@ -80344,21 +80340,21 @@
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
+          <t>Synthroid 125 mcg</t>
         </is>
       </c>
       <c r="C1504" t="inlineStr"/>
       <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="n">
-        <v>28800</v>
+        <v>178000</v>
       </c>
       <c r="F1504" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1504" t="n">
         <v>0</v>
@@ -80394,21 +80390,25 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
-        </is>
-      </c>
-      <c r="C1505" t="inlineStr"/>
+          <t>Talco medicado Neofungina 40gm</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>7706142707106</t>
+        </is>
+      </c>
       <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="n">
-        <v>11596.638655</v>
+        <v>14900</v>
       </c>
       <c r="F1505" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1505" t="n">
         <v>0</v>
@@ -80436,7 +80436,7 @@
       </c>
       <c r="M1505" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1505" t="inlineStr"/>
@@ -80444,21 +80444,21 @@
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>TIJERA DE DOBLAR METALICA</t>
+          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
         </is>
       </c>
       <c r="C1506" t="inlineStr"/>
       <c r="D1506" t="inlineStr"/>
       <c r="E1506" t="n">
-        <v>3500</v>
+        <v>13300</v>
       </c>
       <c r="F1506" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1506" t="n">
         <v>0</v>
@@ -80494,21 +80494,21 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
         </is>
       </c>
       <c r="C1507" t="inlineStr"/>
       <c r="D1507" t="inlineStr"/>
       <c r="E1507" t="n">
-        <v>3781.512605</v>
+        <v>4874</v>
       </c>
       <c r="F1507" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G1507" t="n">
         <v>0</v>
@@ -80544,21 +80544,21 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr"/>
       <c r="D1508" t="inlineStr"/>
       <c r="E1508" t="n">
-        <v>29800</v>
+        <v>28800</v>
       </c>
       <c r="F1508" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1508" t="n">
         <v>0</v>
@@ -80594,22 +80594,18 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
-        </is>
-      </c>
-      <c r="C1509" t="inlineStr">
-        <is>
-          <t>7702026149567</t>
-        </is>
-      </c>
+          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr"/>
       <c r="D1509" t="inlineStr"/>
       <c r="E1509" t="n">
-        <v>13500</v>
+        <v>11596.638655</v>
       </c>
       <c r="F1509" t="n">
         <v>2</v>
@@ -80640,7 +80636,7 @@
       </c>
       <c r="M1509" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1509" t="inlineStr"/>
@@ -80648,25 +80644,21 @@
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>Toallas húmedas winny 24unidades</t>
-        </is>
-      </c>
-      <c r="C1510" t="inlineStr">
-        <is>
-          <t>7701021143655</t>
-        </is>
-      </c>
+          <t>TIJERA DE DOBLAR METALICA</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr"/>
       <c r="D1510" t="inlineStr"/>
       <c r="E1510" t="n">
-        <v>4033.613445</v>
+        <v>3500</v>
       </c>
       <c r="F1510" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G1510" t="n">
         <v>0</v>
@@ -80694,7 +80686,7 @@
       </c>
       <c r="M1510" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1510" t="inlineStr"/>
@@ -80702,25 +80694,21 @@
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>Toallas maternas maternity</t>
-        </is>
-      </c>
-      <c r="C1511" t="inlineStr">
-        <is>
-          <t>7703252489526</t>
-        </is>
-      </c>
+          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr"/>
       <c r="D1511" t="inlineStr"/>
       <c r="E1511" t="n">
-        <v>16900</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1511" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1511" t="n">
         <v>0</v>
@@ -80748,7 +80736,7 @@
       </c>
       <c r="M1511" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1511" t="inlineStr"/>
@@ -80756,25 +80744,21 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>Toallas Nosotras Rapigel x Und</t>
-        </is>
-      </c>
-      <c r="C1512" t="inlineStr">
-        <is>
-          <t>7702027416859</t>
-        </is>
-      </c>
+          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr"/>
       <c r="D1512" t="inlineStr"/>
       <c r="E1512" t="n">
-        <v>756.302521</v>
+        <v>29800</v>
       </c>
       <c r="F1512" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G1512" t="n">
         <v>0</v>
@@ -80802,7 +80786,7 @@
       </c>
       <c r="M1512" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1512" t="inlineStr"/>
@@ -80810,21 +80794,25 @@
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>TRAMADOL 50MG CAPSULA MP</t>
-        </is>
-      </c>
-      <c r="C1513" t="inlineStr"/>
+          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>7702026149567</t>
+        </is>
+      </c>
       <c r="D1513" t="inlineStr"/>
       <c r="E1513" t="n">
-        <v>1500</v>
+        <v>13500</v>
       </c>
       <c r="F1513" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G1513" t="n">
         <v>0</v>
@@ -80860,25 +80848,25 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>Tramadol clorhidrato 100mg laquifar</t>
+          <t>Toallas húmedas winny 24unidades</t>
         </is>
       </c>
       <c r="C1514" t="inlineStr">
         <is>
-          <t>7707019426977</t>
+          <t>7701021143655</t>
         </is>
       </c>
       <c r="D1514" t="inlineStr"/>
       <c r="E1514" t="n">
-        <v>1600</v>
+        <v>4033.613445</v>
       </c>
       <c r="F1514" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G1514" t="n">
         <v>0</v>
@@ -80906,7 +80894,7 @@
       </c>
       <c r="M1514" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1514" t="inlineStr"/>
@@ -80914,21 +80902,25 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>TRIGENTAX CREMA TBO X 20GR</t>
-        </is>
-      </c>
-      <c r="C1515" t="inlineStr"/>
+          <t>Toallas maternas maternity</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>7703252489526</t>
+        </is>
+      </c>
       <c r="D1515" t="inlineStr"/>
       <c r="E1515" t="n">
-        <v>33500</v>
+        <v>16900</v>
       </c>
       <c r="F1515" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1515" t="n">
         <v>0</v>
@@ -80964,21 +80956,25 @@
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
-        </is>
-      </c>
-      <c r="C1516" t="inlineStr"/>
+          <t>Toallas Nosotras Rapigel x Und</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>7702027416859</t>
+        </is>
+      </c>
       <c r="D1516" t="inlineStr"/>
       <c r="E1516" t="n">
-        <v>9000</v>
+        <v>756.302521</v>
       </c>
       <c r="F1516" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="G1516" t="n">
         <v>0</v>
@@ -81006,7 +81002,7 @@
       </c>
       <c r="M1516" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1516" t="inlineStr"/>
@@ -81014,21 +81010,21 @@
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
+          <t>TRAMADOL 50MG CAPSULA MP</t>
         </is>
       </c>
       <c r="C1517" t="inlineStr"/>
       <c r="D1517" t="inlineStr"/>
       <c r="E1517" t="n">
-        <v>10500</v>
+        <v>1500</v>
       </c>
       <c r="F1517" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G1517" t="n">
         <v>0</v>
@@ -81064,21 +81060,25 @@
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
-        </is>
-      </c>
-      <c r="C1518" t="inlineStr"/>
+          <t>Tramadol clorhidrato 100mg laquifar</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>7707019426977</t>
+        </is>
+      </c>
       <c r="D1518" t="inlineStr"/>
       <c r="E1518" t="n">
-        <v>10500</v>
+        <v>1600</v>
       </c>
       <c r="F1518" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G1518" t="n">
         <v>0</v>
@@ -81114,21 +81114,21 @@
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
+          <t>TRIGENTAX CREMA TBO X 20GR</t>
         </is>
       </c>
       <c r="C1519" t="inlineStr"/>
       <c r="D1519" t="inlineStr"/>
       <c r="E1519" t="n">
-        <v>18800</v>
+        <v>33500</v>
       </c>
       <c r="F1519" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1519" t="n">
         <v>0</v>
@@ -81164,21 +81164,21 @@
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
+          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
         </is>
       </c>
       <c r="C1520" t="inlineStr"/>
       <c r="D1520" t="inlineStr"/>
       <c r="E1520" t="n">
-        <v>13800</v>
+        <v>9000</v>
       </c>
       <c r="F1520" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1520" t="n">
         <v>0</v>
@@ -81214,21 +81214,21 @@
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
+          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
         </is>
       </c>
       <c r="C1521" t="inlineStr"/>
       <c r="D1521" t="inlineStr"/>
       <c r="E1521" t="n">
-        <v>7900</v>
+        <v>10500</v>
       </c>
       <c r="F1521" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1521" t="n">
         <v>0</v>
@@ -81264,21 +81264,21 @@
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>VASELINA FC X 200GR YOMA</t>
+          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
         </is>
       </c>
       <c r="C1522" t="inlineStr"/>
       <c r="D1522" t="inlineStr"/>
       <c r="E1522" t="n">
-        <v>12521.008403</v>
+        <v>10500</v>
       </c>
       <c r="F1522" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G1522" t="n">
         <v>0</v>
@@ -81306,7 +81306,7 @@
       </c>
       <c r="M1522" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1522" t="inlineStr"/>
@@ -81314,18 +81314,18 @@
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
+          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
         </is>
       </c>
       <c r="C1523" t="inlineStr"/>
       <c r="D1523" t="inlineStr"/>
       <c r="E1523" t="n">
-        <v>420.168067</v>
+        <v>18800</v>
       </c>
       <c r="F1523" t="n">
         <v>1</v>
@@ -81356,7 +81356,7 @@
       </c>
       <c r="M1523" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1523" t="inlineStr"/>
@@ -81364,25 +81364,21 @@
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
-        </is>
-      </c>
-      <c r="C1524" t="inlineStr">
-        <is>
-          <t>7708480649803</t>
-        </is>
-      </c>
+          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr"/>
       <c r="D1524" t="inlineStr"/>
       <c r="E1524" t="n">
-        <v>28000</v>
+        <v>13800</v>
       </c>
       <c r="F1524" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1524" t="n">
         <v>0</v>
@@ -81418,25 +81414,21 @@
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Venda Elastica 6x5 y piel</t>
+          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
         </is>
       </c>
       <c r="C1525" t="inlineStr"/>
-      <c r="D1525" t="inlineStr">
-        <is>
-          <t>SUBIO A 6200 ANTES 5700</t>
-        </is>
-      </c>
+      <c r="D1525" t="inlineStr"/>
       <c r="E1525" t="n">
-        <v>6200</v>
+        <v>7900</v>
       </c>
       <c r="F1525" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1525" t="n">
         <v>0</v>
@@ -81472,21 +81464,21 @@
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
+          <t>VASELINA FC X 200GR YOMA</t>
         </is>
       </c>
       <c r="C1526" t="inlineStr"/>
       <c r="D1526" t="inlineStr"/>
       <c r="E1526" t="n">
-        <v>5500</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1526" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1526" t="n">
         <v>0</v>
@@ -81514,7 +81506,7 @@
       </c>
       <c r="M1526" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1526" t="inlineStr"/>
@@ -81522,21 +81514,21 @@
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>Venta simple</t>
+          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
         </is>
       </c>
       <c r="C1527" t="inlineStr"/>
       <c r="D1527" t="inlineStr"/>
       <c r="E1527" t="n">
-        <v>0</v>
+        <v>420.168067</v>
       </c>
       <c r="F1527" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1527" t="n">
         <v>0</v>
@@ -81554,7 +81546,7 @@
       </c>
       <c r="K1527" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="L1527" t="inlineStr">
@@ -81562,27 +81554,35 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1527" t="inlineStr"/>
+      <c r="M1527" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
       <c r="N1527" t="inlineStr"/>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
-        </is>
-      </c>
-      <c r="C1528" t="inlineStr"/>
+          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>7708480649803</t>
+        </is>
+      </c>
       <c r="D1528" t="inlineStr"/>
       <c r="E1528" t="n">
-        <v>1000</v>
+        <v>28000</v>
       </c>
       <c r="F1528" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1528" t="n">
         <v>0</v>
@@ -81618,25 +81618,25 @@
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
-        </is>
-      </c>
-      <c r="C1529" t="inlineStr">
-        <is>
-          <t>793969226467</t>
-        </is>
-      </c>
-      <c r="D1529" t="inlineStr"/>
+          <t>Venda Elastica 6x5 y piel</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr"/>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>SUBIO A 6200 ANTES 5700</t>
+        </is>
+      </c>
       <c r="E1529" t="n">
-        <v>17000</v>
+        <v>6200</v>
       </c>
       <c r="F1529" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1529" t="n">
         <v>0</v>
@@ -81659,7 +81659,7 @@
       </c>
       <c r="L1529" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="M1529" t="inlineStr">
@@ -81672,18 +81672,18 @@
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>VINO CEREBRAL JARABE X 1100ML</t>
+          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
         </is>
       </c>
       <c r="C1530" t="inlineStr"/>
       <c r="D1530" t="inlineStr"/>
       <c r="E1530" t="n">
-        <v>48900</v>
+        <v>5500</v>
       </c>
       <c r="F1530" t="n">
         <v>2</v>
@@ -81722,21 +81722,21 @@
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
+          <t>Venta simple</t>
         </is>
       </c>
       <c r="C1531" t="inlineStr"/>
       <c r="D1531" t="inlineStr"/>
       <c r="E1531" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="F1531" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G1531" t="n">
         <v>0</v>
@@ -81754,7 +81754,7 @@
       </c>
       <c r="K1531" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="L1531" t="inlineStr">
@@ -81762,31 +81762,27 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1531" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1531" t="inlineStr"/>
       <c r="N1531" t="inlineStr"/>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
+          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
         </is>
       </c>
       <c r="C1532" t="inlineStr"/>
       <c r="D1532" t="inlineStr"/>
       <c r="E1532" t="n">
-        <v>5500</v>
+        <v>1000</v>
       </c>
       <c r="F1532" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G1532" t="n">
         <v>0</v>
@@ -81822,21 +81818,25 @@
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>WINNY PAÑAL ETP 6 X 30</t>
-        </is>
-      </c>
-      <c r="C1533" t="inlineStr"/>
+          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>793969226467</t>
+        </is>
+      </c>
       <c r="D1533" t="inlineStr"/>
       <c r="E1533" t="n">
-        <v>57000</v>
+        <v>17000</v>
       </c>
       <c r="F1533" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1533" t="n">
         <v>0</v>
@@ -81859,7 +81859,7 @@
       </c>
       <c r="L1533" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="M1533" t="inlineStr">
@@ -81872,52 +81872,302 @@
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>YODO BLANCO FC X30ML</t>
+          <t>VINO CEREBRAL JARABE X 1100ML</t>
         </is>
       </c>
       <c r="C1534" t="inlineStr"/>
       <c r="D1534" t="inlineStr"/>
       <c r="E1534" t="n">
+        <v>48900</v>
+      </c>
+      <c r="F1534" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1534" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1534" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1534" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1534" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1534" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1534" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1534" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1534" t="inlineStr"/>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>VIOXIN ENJUAGUE BUCAL 0.12% CLORH 120ML</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr"/>
+      <c r="D1535" t="inlineStr"/>
+      <c r="E1535" t="n">
+        <v>22900</v>
+      </c>
+      <c r="F1535" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1535" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1535" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1535" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1535" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1535" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1535" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1535" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1535" t="inlineStr"/>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr"/>
+      <c r="D1536" t="inlineStr"/>
+      <c r="E1536" t="n">
+        <v>5400</v>
+      </c>
+      <c r="F1536" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1536" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1536" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1536" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1536" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1536" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1536" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1536" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1536" t="inlineStr"/>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr"/>
+      <c r="D1537" t="inlineStr"/>
+      <c r="E1537" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F1537" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1537" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1537" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1537" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1537" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1537" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1537" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1537" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1537" t="inlineStr"/>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>WINNY PAÑAL ETP 6 X 30</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr"/>
+      <c r="D1538" t="inlineStr"/>
+      <c r="E1538" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F1538" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1538" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1538" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1538" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1538" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1538" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1538" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1538" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1538" t="inlineStr"/>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>YODO BLANCO FC X30ML</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr"/>
+      <c r="D1539" t="inlineStr"/>
+      <c r="E1539" t="n">
         <v>6000</v>
       </c>
-      <c r="F1534" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1534" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1534" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1534" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1534" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="K1534" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="L1534" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="M1534" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="N1534" t="inlineStr"/>
+      <c r="F1539" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1539" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1539" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1539" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1539" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1539" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1539" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1539" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1539" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -13097,7 +13097,7 @@
         <v>3800</v>
       </c>
       <c r="F238" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -14771,7 +14771,7 @@
         <v>6000</v>
       </c>
       <c r="F269" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -22251,7 +22251,7 @@
         <v>7900</v>
       </c>
       <c r="F409" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G409" t="n">
         <v>0</v>
@@ -31625,7 +31625,7 @@
         <v>2800</v>
       </c>
       <c r="F584" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G584" t="n">
         <v>0</v>
@@ -31845,7 +31845,7 @@
         <v>3000</v>
       </c>
       <c r="F588" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G588" t="n">
         <v>0</v>
@@ -32335,7 +32335,7 @@
         <v>900</v>
       </c>
       <c r="F597" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G597" t="n">
         <v>0</v>
@@ -32721,7 +32721,7 @@
         <v>2900</v>
       </c>
       <c r="F604" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G604" t="n">
         <v>0</v>
@@ -33573,7 +33573,7 @@
         <v>13900</v>
       </c>
       <c r="F620" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G620" t="n">
         <v>0</v>
@@ -55990,7 +55990,7 @@
         <v>3500</v>
       </c>
       <c r="F1040" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1040" t="n">
         <v>0</v>
@@ -58898,7 +58898,7 @@
         <v>3400</v>
       </c>
       <c r="F1094" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1094" t="n">
         <v>0</v>
@@ -60020,7 +60020,7 @@
         <v>17300</v>
       </c>
       <c r="F1115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1115" t="n">
         <v>0</v>
@@ -60568,7 +60568,7 @@
         <v>9000</v>
       </c>
       <c r="F1125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1125" t="n">
         <v>0</v>
@@ -71498,7 +71498,7 @@
         <v>12000</v>
       </c>
       <c r="F1332" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1332" t="n">
         <v>0</v>
@@ -71656,7 +71656,7 @@
         <v>4700</v>
       </c>
       <c r="F1335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1335" t="n">
         <v>0</v>
@@ -76688,7 +76688,7 @@
         <v>24500</v>
       </c>
       <c r="F1433" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1433" t="n">
         <v>0</v>
@@ -77932,7 +77932,7 @@
         <v>1500</v>
       </c>
       <c r="F1457" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1457" t="n">
         <v>0</v>
@@ -79646,7 +79646,7 @@
         <v>1429</v>
       </c>
       <c r="F1490" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1490" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -8837,7 +8837,7 @@
         <v>20000</v>
       </c>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -10279,7 +10279,7 @@
         <v>4000</v>
       </c>
       <c r="F185" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -11635,7 +11635,7 @@
         <v>3200</v>
       </c>
       <c r="F211" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -13969,7 +13969,7 @@
         <v>672</v>
       </c>
       <c r="F254" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -14077,7 +14077,7 @@
         <v>840.336134</v>
       </c>
       <c r="F256" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -15215,7 +15215,7 @@
         <v>4000</v>
       </c>
       <c r="F277" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G277" t="n">
         <v>0</v>
@@ -20731,7 +20731,7 @@
         <v>9000</v>
       </c>
       <c r="F381" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G381" t="n">
         <v>0</v>
@@ -23261,7 +23261,7 @@
         <v>1900</v>
       </c>
       <c r="F428" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G428" t="n">
         <v>0</v>
@@ -23365,7 +23365,7 @@
         <v>2000</v>
       </c>
       <c r="F430" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G430" t="n">
         <v>0</v>
@@ -23473,7 +23473,7 @@
         <v>2400</v>
       </c>
       <c r="F432" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G432" t="n">
         <v>0</v>
@@ -23631,7 +23631,7 @@
         <v>2900</v>
       </c>
       <c r="F435" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G435" t="n">
         <v>0</v>
@@ -31903,7 +31903,7 @@
         <v>2500</v>
       </c>
       <c r="F589" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G589" t="n">
         <v>0</v>
@@ -32721,7 +32721,7 @@
         <v>2900</v>
       </c>
       <c r="F604" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G604" t="n">
         <v>0</v>
@@ -32879,7 +32879,7 @@
         <v>8800</v>
       </c>
       <c r="F607" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G607" t="n">
         <v>0</v>
@@ -32937,7 +32937,7 @@
         <v>3700</v>
       </c>
       <c r="F608" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G608" t="n">
         <v>0</v>
@@ -34367,7 +34367,7 @@
         <v>2800</v>
       </c>
       <c r="F635" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G635" t="n">
         <v>0</v>
@@ -42373,7 +42373,7 @@
         <v>2300</v>
       </c>
       <c r="F786" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G786" t="n">
         <v>0</v>
@@ -50591,7 +50591,7 @@
         <v>4400</v>
       </c>
       <c r="F939" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G939" t="n">
         <v>0</v>
@@ -50903,7 +50903,7 @@
         <v>2000</v>
       </c>
       <c r="F945" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G945" t="n">
         <v>0</v>
@@ -51307,7 +51307,7 @@
         <v>2200</v>
       </c>
       <c r="F953" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G953" t="n">
         <v>0</v>
@@ -54752,7 +54752,7 @@
         <v>4800</v>
       </c>
       <c r="F1017" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1017" t="n">
         <v>0</v>
@@ -55612,7 +55612,7 @@
         <v>3900</v>
       </c>
       <c r="F1033" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1033" t="n">
         <v>0</v>
@@ -63036,7 +63036,7 @@
         <v>1000</v>
       </c>
       <c r="F1171" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G1171" t="n">
         <v>0</v>
@@ -64182,7 +64182,7 @@
         <v>4800</v>
       </c>
       <c r="F1192" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1192" t="n">
         <v>0</v>
@@ -64838,7 +64838,7 @@
         <v>9300</v>
       </c>
       <c r="F1204" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1204" t="n">
         <v>0</v>
@@ -68834,7 +68834,7 @@
         <v>10800</v>
       </c>
       <c r="F1280" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1280" t="n">
         <v>0</v>
@@ -70016,7 +70016,7 @@
         <v>16500</v>
       </c>
       <c r="F1303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1303" t="n">
         <v>0</v>
@@ -70990,7 +70990,7 @@
         <v>33900</v>
       </c>
       <c r="F1322" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1322" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1539"/>
+  <dimension ref="A1:N1544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9049,7 +9049,7 @@
         <v>23800</v>
       </c>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -13259,7 +13259,7 @@
         <v>8900</v>
       </c>
       <c r="F241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -13753,7 +13753,7 @@
         <v>4500</v>
       </c>
       <c r="F250" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -43685,7 +43685,7 @@
         <v>8800</v>
       </c>
       <c r="F810" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G810" t="n">
         <v>0</v>
@@ -51598,7 +51598,7 @@
         <v>24900</v>
       </c>
       <c r="F958" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G958" t="n">
         <v>0</v>
@@ -59380,7 +59380,7 @@
         <v>9000</v>
       </c>
       <c r="F1103" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G1103" t="n">
         <v>0</v>
@@ -61004,7 +61004,7 @@
         <v>4000</v>
       </c>
       <c r="F1133" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G1133" t="n">
         <v>0</v>
@@ -63850,7 +63850,7 @@
         <v>19900</v>
       </c>
       <c r="F1186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1186" t="n">
         <v>0</v>
@@ -65274,7 +65274,7 @@
         <v>14000</v>
       </c>
       <c r="F1212" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1212" t="n">
         <v>0</v>
@@ -67478,7 +67478,7 @@
         <v>20000</v>
       </c>
       <c r="F1254" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1254" t="n">
         <v>0</v>
@@ -67988,25 +67988,21 @@
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>Biocicar Crema Topica x 60 gr</t>
-        </is>
-      </c>
-      <c r="C1264" t="inlineStr">
-        <is>
-          <t>7703234100968</t>
-        </is>
-      </c>
+          <t>BILAXTEN 20MG X 10 COMPRIMIDOS FAES FARMA</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr"/>
       <c r="D1264" t="inlineStr"/>
       <c r="E1264" t="n">
-        <v>42000</v>
+        <v>10500</v>
       </c>
       <c r="F1264" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1264" t="n">
         <v>0</v>
@@ -68042,22 +68038,22 @@
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>BISACUDILO 5MG X 10 TABL. HUMAX</t>
+          <t>Biocicar Crema Topica x 60 gr</t>
         </is>
       </c>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>77072888220247</t>
+          <t>7703234100968</t>
         </is>
       </c>
       <c r="D1265" t="inlineStr"/>
       <c r="E1265" t="n">
-        <v>4000</v>
+        <v>42000</v>
       </c>
       <c r="F1265" t="n">
         <v>0</v>
@@ -68096,21 +68092,25 @@
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>BISACUDILO 5MG X SOBRE DE RECIPE</t>
-        </is>
-      </c>
-      <c r="C1266" t="inlineStr"/>
+          <t>BISACUDILO 5MG X 10 TABL. HUMAX</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>77072888220247</t>
+        </is>
+      </c>
       <c r="D1266" t="inlineStr"/>
       <c r="E1266" t="n">
-        <v>6900</v>
+        <v>4000</v>
       </c>
       <c r="F1266" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1266" t="n">
         <v>0</v>
@@ -68146,25 +68146,21 @@
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>BISGLICINATO DE MAGNESIO X 60 CAPS</t>
-        </is>
-      </c>
-      <c r="C1267" t="inlineStr">
-        <is>
-          <t>610985519338</t>
-        </is>
-      </c>
+          <t>BISACUDILO 5MG X SOBRE DE RECIPE</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr"/>
       <c r="D1267" t="inlineStr"/>
       <c r="E1267" t="n">
-        <v>48000</v>
+        <v>6900</v>
       </c>
       <c r="F1267" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1267" t="n">
         <v>0</v>
@@ -68200,18 +68196,22 @@
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>BOLSA BLANCA</t>
-        </is>
-      </c>
-      <c r="C1268" t="inlineStr"/>
+          <t>BISGLICINATO DE MAGNESIO X 60 CAPS</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>610985519338</t>
+        </is>
+      </c>
       <c r="D1268" t="inlineStr"/>
       <c r="E1268" t="n">
-        <v>1000</v>
+        <v>48000</v>
       </c>
       <c r="F1268" t="n">
         <v>1</v>
@@ -68250,21 +68250,21 @@
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1543</t>
         </is>
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>BOLSAS INYECTOLOGIA</t>
+          <t>BOLSA BLANCA</t>
         </is>
       </c>
       <c r="C1269" t="inlineStr"/>
       <c r="D1269" t="inlineStr"/>
       <c r="E1269" t="n">
-        <v>840.336134</v>
+        <v>1000</v>
       </c>
       <c r="F1269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1269" t="n">
         <v>0</v>
@@ -68292,7 +68292,7 @@
       </c>
       <c r="M1269" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1269" t="inlineStr"/>
@@ -68300,29 +68300,21 @@
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>BROMHEXINA MG/ML MUCOTROP NIÑO</t>
-        </is>
-      </c>
-      <c r="C1270" t="inlineStr">
-        <is>
-          <t>7703038067450</t>
-        </is>
-      </c>
-      <c r="D1270" t="inlineStr">
-        <is>
-          <t>SE SUBE PRECIO A 17000 ANTES ESTABA EN 15000/MODIF LEYDI</t>
-        </is>
-      </c>
+          <t>BOLSAS INYECTOLOGIA</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr"/>
+      <c r="D1270" t="inlineStr"/>
       <c r="E1270" t="n">
-        <v>17000</v>
+        <v>840.336134</v>
       </c>
       <c r="F1270" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1270" t="n">
         <v>0</v>
@@ -68350,7 +68342,7 @@
       </c>
       <c r="M1270" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1270" t="inlineStr"/>
@@ -68358,21 +68350,29 @@
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>BRONQUISAN JALEA ADULTO JARABE 240ML</t>
-        </is>
-      </c>
-      <c r="C1271" t="inlineStr"/>
-      <c r="D1271" t="inlineStr"/>
+          <t>BROMHEXINA MG/ML MUCOTROP NIÑO</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>7703038067450</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>SE SUBE PRECIO A 17000 ANTES ESTABA EN 15000/MODIF LEYDI</t>
+        </is>
+      </c>
       <c r="E1271" t="n">
-        <v>19900</v>
+        <v>17000</v>
       </c>
       <c r="F1271" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1271" t="n">
         <v>0</v>
@@ -68408,18 +68408,18 @@
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>Bronsinex JBE x 120ML</t>
+          <t>BRONQUISAN JALEA ADULTO JARABE 240ML</t>
         </is>
       </c>
       <c r="C1272" t="inlineStr"/>
       <c r="D1272" t="inlineStr"/>
       <c r="E1272" t="n">
-        <v>17000</v>
+        <v>19900</v>
       </c>
       <c r="F1272" t="n">
         <v>1</v>
@@ -68458,25 +68458,21 @@
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>CAJA DE BEDOYECTA X 3 AMPOLLA</t>
-        </is>
-      </c>
-      <c r="C1273" t="inlineStr">
-        <is>
-          <t>7707288826935</t>
-        </is>
-      </c>
+          <t>Bronsinex JBE x 120ML</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr"/>
       <c r="D1273" t="inlineStr"/>
       <c r="E1273" t="n">
-        <v>58000</v>
+        <v>17000</v>
       </c>
       <c r="F1273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1273" t="n">
         <v>0</v>
@@ -68512,21 +68508,25 @@
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>CALADERM CLEAR PLUS 120GR</t>
-        </is>
-      </c>
-      <c r="C1274" t="inlineStr"/>
+          <t>CAJA DE BEDOYECTA X 3 AMPOLLA</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>7707288826935</t>
+        </is>
+      </c>
       <c r="D1274" t="inlineStr"/>
       <c r="E1274" t="n">
-        <v>22268.907563</v>
+        <v>58000</v>
       </c>
       <c r="F1274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1274" t="n">
         <v>0</v>
@@ -68554,7 +68554,7 @@
       </c>
       <c r="M1274" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1274" t="inlineStr"/>
@@ -68562,25 +68562,21 @@
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>CAPILAR POLIMERO ROSADO 20ML</t>
-        </is>
-      </c>
-      <c r="C1275" t="inlineStr">
-        <is>
-          <t>7701168181244</t>
-        </is>
-      </c>
+          <t>CALADERM CLEAR PLUS 120GR</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr"/>
       <c r="D1275" t="inlineStr"/>
       <c r="E1275" t="n">
-        <v>4300</v>
+        <v>22268.907563</v>
       </c>
       <c r="F1275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1275" t="n">
         <v>0</v>
@@ -68608,7 +68604,7 @@
       </c>
       <c r="M1275" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1275" t="inlineStr"/>
@@ -68616,25 +68612,25 @@
     <row r="1276">
       <c r="A1276" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>CARVEDIDOL 6,25MG MEPHIS</t>
+          <t>CAPILAR POLIMERO ROSADO 20ML</t>
         </is>
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>7704412376328</t>
+          <t>7701168181244</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr"/>
       <c r="E1276" t="n">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="F1276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1276" t="n">
         <v>0</v>
@@ -68670,21 +68666,25 @@
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>CARVEDILOL 6.25MG SOBRE X 10 TABLE DE L.S</t>
-        </is>
-      </c>
-      <c r="C1277" t="inlineStr"/>
+          <t>CARVEDIDOL 6,25MG MEPHIS</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>7704412376328</t>
+        </is>
+      </c>
       <c r="D1277" t="inlineStr"/>
       <c r="E1277" t="n">
-        <v>5900</v>
+        <v>4400</v>
       </c>
       <c r="F1277" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1277" t="n">
         <v>0</v>
@@ -68720,21 +68720,21 @@
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>CAUCHO PARA EL CABELLO AKARELLA YUMBO</t>
+          <t>CARVEDILOL 6.25MG SOBRE X 10 TABLE DE L.S</t>
         </is>
       </c>
       <c r="C1278" t="inlineStr"/>
       <c r="D1278" t="inlineStr"/>
       <c r="E1278" t="n">
-        <v>2800</v>
+        <v>5900</v>
       </c>
       <c r="F1278" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1278" t="n">
         <v>0</v>
@@ -68770,21 +68770,21 @@
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>CAUCHOS AKARELA PASTEL ROSADO</t>
+          <t>CAUCHO PARA EL CABELLO AKARELLA YUMBO</t>
         </is>
       </c>
       <c r="C1279" t="inlineStr"/>
       <c r="D1279" t="inlineStr"/>
       <c r="E1279" t="n">
-        <v>1512.605042</v>
+        <v>2800</v>
       </c>
       <c r="F1279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1279" t="n">
         <v>0</v>
@@ -68812,7 +68812,7 @@
       </c>
       <c r="M1279" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1279" t="inlineStr"/>
@@ -68820,21 +68820,21 @@
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>CEFALEXINA 500MG CAPSULAS DE LA SANTE</t>
+          <t>CAUCHOS AKARELA PASTEL ROSADO</t>
         </is>
       </c>
       <c r="C1280" t="inlineStr"/>
       <c r="D1280" t="inlineStr"/>
       <c r="E1280" t="n">
-        <v>10800</v>
+        <v>1512.605042</v>
       </c>
       <c r="F1280" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G1280" t="n">
         <v>0</v>
@@ -68862,7 +68862,7 @@
       </c>
       <c r="M1280" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1280" t="inlineStr"/>
@@ -68870,25 +68870,21 @@
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>Cefalexina 500mg laproff</t>
-        </is>
-      </c>
-      <c r="C1281" t="inlineStr">
-        <is>
-          <t>7703038612636</t>
-        </is>
-      </c>
+          <t>CEFALEXINA 500MG CAPSULAS DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr"/>
       <c r="D1281" t="inlineStr"/>
       <c r="E1281" t="n">
-        <v>10000</v>
+        <v>10800</v>
       </c>
       <c r="F1281" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G1281" t="n">
         <v>0</v>
@@ -68924,21 +68920,25 @@
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>CEPILLO DENTAL NIÑO</t>
-        </is>
-      </c>
-      <c r="C1282" t="inlineStr"/>
+          <t>Cefalexina 500mg laproff</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>7703038612636</t>
+        </is>
+      </c>
       <c r="D1282" t="inlineStr"/>
       <c r="E1282" t="n">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="F1282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1282" t="n">
         <v>0</v>
@@ -68974,25 +68974,21 @@
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>CEPILLO NIÑO KIDS VERDE MEDIO</t>
-        </is>
-      </c>
-      <c r="C1283" t="inlineStr">
-        <is>
-          <t>6971831832020</t>
-        </is>
-      </c>
+          <t>CEPILLO DENTAL NIÑO</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr"/>
       <c r="D1283" t="inlineStr"/>
       <c r="E1283" t="n">
-        <v>3781.512605</v>
+        <v>4500</v>
       </c>
       <c r="F1283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1283" t="n">
         <v>0</v>
@@ -69020,7 +69016,7 @@
       </c>
       <c r="M1283" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1283" t="inlineStr"/>
@@ -69028,21 +69024,25 @@
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>CERA EGO POTE X 60ML</t>
-        </is>
-      </c>
-      <c r="C1284" t="inlineStr"/>
+          <t>CEPILLO NIÑO KIDS VERDE MEDIO</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>6971831832020</t>
+        </is>
+      </c>
       <c r="D1284" t="inlineStr"/>
       <c r="E1284" t="n">
-        <v>6800</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1284" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1284" t="n">
         <v>0</v>
@@ -69070,7 +69070,7 @@
       </c>
       <c r="M1284" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1284" t="inlineStr"/>
@@ -69078,21 +69078,21 @@
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>CERA PROQUIDENT ORTD</t>
+          <t>CERA EGO POTE X 60ML</t>
         </is>
       </c>
       <c r="C1285" t="inlineStr"/>
       <c r="D1285" t="inlineStr"/>
       <c r="E1285" t="n">
-        <v>6554.621849</v>
+        <v>6800</v>
       </c>
       <c r="F1285" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1285" t="n">
         <v>0</v>
@@ -69120,7 +69120,7 @@
       </c>
       <c r="M1285" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1285" t="inlineStr"/>
@@ -69128,21 +69128,21 @@
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>CHA-P JARABE ARMONIZA 500ML</t>
+          <t>CERA PROQUIDENT ORTD</t>
         </is>
       </c>
       <c r="C1286" t="inlineStr"/>
       <c r="D1286" t="inlineStr"/>
       <c r="E1286" t="n">
-        <v>38000</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1286" t="n">
         <v>0</v>
@@ -69170,7 +69170,7 @@
       </c>
       <c r="M1286" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1286" t="inlineStr"/>
@@ -69178,21 +69178,21 @@
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>CHAPSTICK LABIAL CEREZA</t>
+          <t>CHA-P JARABE ARMONIZA 500ML</t>
         </is>
       </c>
       <c r="C1287" t="inlineStr"/>
       <c r="D1287" t="inlineStr"/>
       <c r="E1287" t="n">
-        <v>17563.02521</v>
+        <v>38000</v>
       </c>
       <c r="F1287" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1287" t="n">
         <v>0</v>
@@ -69220,7 +69220,7 @@
       </c>
       <c r="M1287" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1287" t="inlineStr"/>
@@ -69228,21 +69228,21 @@
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>CHICLE TRIDENT SURTIDOS SABORES X PAQUE</t>
+          <t>CHAPSTICK LABIAL CEREZA</t>
         </is>
       </c>
       <c r="C1288" t="inlineStr"/>
       <c r="D1288" t="inlineStr"/>
       <c r="E1288" t="n">
-        <v>2016.806723</v>
+        <v>17563.02521</v>
       </c>
       <c r="F1288" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G1288" t="n">
         <v>0</v>
@@ -69278,21 +69278,21 @@
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>CHOCOLATINA JUMBO MANI 17GR X 1 UND</t>
+          <t>CHICLE TRIDENT SURTIDOS SABORES X PAQUE</t>
         </is>
       </c>
       <c r="C1289" t="inlineStr"/>
       <c r="D1289" t="inlineStr"/>
       <c r="E1289" t="n">
-        <v>1680.672269</v>
+        <v>2016.806723</v>
       </c>
       <c r="F1289" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G1289" t="n">
         <v>0</v>
@@ -69328,21 +69328,21 @@
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>CHUPO SILICONA GRANDE</t>
+          <t>CHOCOLATINA JUMBO MANI 17GR X 1 UND</t>
         </is>
       </c>
       <c r="C1290" t="inlineStr"/>
       <c r="D1290" t="inlineStr"/>
       <c r="E1290" t="n">
-        <v>4500</v>
+        <v>1680.672269</v>
       </c>
       <c r="F1290" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G1290" t="n">
         <v>0</v>
@@ -69370,7 +69370,7 @@
       </c>
       <c r="M1290" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1290" t="inlineStr"/>
@@ -69378,21 +69378,21 @@
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>Cianocobalamina</t>
+          <t>CHUPO SILICONA GRANDE</t>
         </is>
       </c>
       <c r="C1291" t="inlineStr"/>
       <c r="D1291" t="inlineStr"/>
       <c r="E1291" t="n">
-        <v>6500</v>
+        <v>4500</v>
       </c>
       <c r="F1291" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1291" t="n">
         <v>0</v>
@@ -69428,25 +69428,21 @@
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>Cicaderm crema protector cutáneo 60gm NF</t>
-        </is>
-      </c>
-      <c r="C1292" t="inlineStr">
-        <is>
-          <t>7707173600091</t>
-        </is>
-      </c>
+          <t>Cianocobalamina</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr"/>
       <c r="D1292" t="inlineStr"/>
       <c r="E1292" t="n">
-        <v>57000</v>
+        <v>6500</v>
       </c>
       <c r="F1292" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1292" t="n">
         <v>0</v>
@@ -69482,25 +69478,25 @@
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>CINTA DE PAPEL QUIRURGICO HIPOALERGICO 1/2 PROLATEX</t>
+          <t>Cicaderm crema protector cutáneo 60gm NF</t>
         </is>
       </c>
       <c r="C1293" t="inlineStr">
         <is>
-          <t>7709414102654</t>
+          <t>7707173600091</t>
         </is>
       </c>
       <c r="D1293" t="inlineStr"/>
       <c r="E1293" t="n">
-        <v>6000</v>
+        <v>57000</v>
       </c>
       <c r="F1293" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1293" t="n">
         <v>0</v>
@@ -69536,18 +69532,22 @@
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>Citrato de calcio / Vitamina D3 600 MG/400UI (1500MG) Granulos Caja x 15 Sobres</t>
-        </is>
-      </c>
-      <c r="C1294" t="inlineStr"/>
+          <t>CINTA DE PAPEL QUIRURGICO HIPOALERGICO 1/2 PROLATEX</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>7709414102654</t>
+        </is>
+      </c>
       <c r="D1294" t="inlineStr"/>
       <c r="E1294" t="n">
-        <v>53000</v>
+        <v>6000</v>
       </c>
       <c r="F1294" t="n">
         <v>0</v>
@@ -69586,21 +69586,21 @@
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>769</t>
         </is>
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>CLENOX 40MG 1J/PRELLE.</t>
+          <t>Citrato de calcio / Vitamina D3 600 MG/400UI (1500MG) Granulos Caja x 15 Sobres</t>
         </is>
       </c>
       <c r="C1295" t="inlineStr"/>
       <c r="D1295" t="inlineStr"/>
       <c r="E1295" t="n">
-        <v>17800</v>
+        <v>53000</v>
       </c>
       <c r="F1295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1295" t="n">
         <v>0</v>
@@ -69636,25 +69636,21 @@
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>CLINBAC CLINDAMICINA 300MG CAPS</t>
-        </is>
-      </c>
-      <c r="C1296" t="inlineStr">
-        <is>
-          <t>7707019413816</t>
-        </is>
-      </c>
+          <t>CLENOX 40MG 1J/PRELLE.</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr"/>
       <c r="D1296" t="inlineStr"/>
       <c r="E1296" t="n">
-        <v>19200</v>
+        <v>17800</v>
       </c>
       <c r="F1296" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1296" t="n">
         <v>0</v>
@@ -69690,18 +69686,22 @@
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>CLINDABACT CLOTRI+CLIND CJA X 3 OVULOS</t>
-        </is>
-      </c>
-      <c r="C1297" t="inlineStr"/>
+          <t>CLINBAC CLINDAMICINA 300MG CAPS</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>7707019413816</t>
+        </is>
+      </c>
       <c r="D1297" t="inlineStr"/>
       <c r="E1297" t="n">
-        <v>35700</v>
+        <v>19200</v>
       </c>
       <c r="F1297" t="n">
         <v>2</v>
@@ -69740,25 +69740,21 @@
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>CLOBETASOL 0,05% TRIDIRTEX CREMA X 40GR</t>
-        </is>
-      </c>
-      <c r="C1298" t="inlineStr">
-        <is>
-          <t>7709740450351</t>
-        </is>
-      </c>
+          <t>CLINDABACT CLOTRI+CLIND CJA X 3 OVULOS</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr"/>
       <c r="D1298" t="inlineStr"/>
       <c r="E1298" t="n">
-        <v>27900</v>
+        <v>35700</v>
       </c>
       <c r="F1298" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1298" t="n">
         <v>0</v>
@@ -69794,25 +69790,25 @@
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>Clotrimazol 1% 40gr AG</t>
+          <t>CLOBETASOL 0,05% TRIDIRTEX CREMA X 40GR</t>
         </is>
       </c>
       <c r="C1299" t="inlineStr">
         <is>
-          <t>7706569001191</t>
+          <t>7709740450351</t>
         </is>
       </c>
       <c r="D1299" t="inlineStr"/>
       <c r="E1299" t="n">
-        <v>19000</v>
+        <v>27900</v>
       </c>
       <c r="F1299" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1299" t="n">
         <v>0</v>
@@ -69848,25 +69844,25 @@
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>CLOTRIMAZOL 1% CREMA TOPICA DE VITALIS</t>
+          <t>Clotrimazol 1% 40gr AG</t>
         </is>
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>7709990212204</t>
+          <t>7706569001191</t>
         </is>
       </c>
       <c r="D1300" t="inlineStr"/>
       <c r="E1300" t="n">
-        <v>14500</v>
+        <v>19000</v>
       </c>
       <c r="F1300" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1300" t="n">
         <v>0</v>
@@ -69902,21 +69898,25 @@
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>COLAGENO HIDROLIZADO EN POLVO 700GR ARMONIZA</t>
-        </is>
-      </c>
-      <c r="C1301" t="inlineStr"/>
+          <t>CLOTRIMAZOL 1% CREMA TOPICA DE VITALIS</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>7709990212204</t>
+        </is>
+      </c>
       <c r="D1301" t="inlineStr"/>
       <c r="E1301" t="n">
-        <v>56000</v>
+        <v>14500</v>
       </c>
       <c r="F1301" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1301" t="n">
         <v>0</v>
@@ -69952,21 +69952,21 @@
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>Colchicina Coas</t>
+          <t>COLAGENO HIDROLIZADO EN POLVO 700GR ARMONIZA</t>
         </is>
       </c>
       <c r="C1302" t="inlineStr"/>
       <c r="D1302" t="inlineStr"/>
       <c r="E1302" t="n">
-        <v>3900</v>
+        <v>56000</v>
       </c>
       <c r="F1302" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G1302" t="n">
         <v>0</v>
@@ -70002,21 +70002,21 @@
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>CONDON DUO LUBRICADO X 3 UND</t>
+          <t>Colchicina Coas</t>
         </is>
       </c>
       <c r="C1303" t="inlineStr"/>
       <c r="D1303" t="inlineStr"/>
       <c r="E1303" t="n">
-        <v>16500</v>
+        <v>3900</v>
       </c>
       <c r="F1303" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G1303" t="n">
         <v>0</v>
@@ -70052,21 +70052,21 @@
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
+          <t>CONDON DUO LUBRICADO X 3 UND</t>
         </is>
       </c>
       <c r="C1304" t="inlineStr"/>
       <c r="D1304" t="inlineStr"/>
       <c r="E1304" t="n">
-        <v>8900</v>
+        <v>16500</v>
       </c>
       <c r="F1304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1304" t="n">
         <v>0</v>
@@ -70102,7 +70102,7 @@
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="B1305" t="inlineStr">
@@ -70116,7 +70116,7 @@
         <v>8900</v>
       </c>
       <c r="F1305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1305" t="n">
         <v>0</v>
@@ -70152,12 +70152,12 @@
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>CONDON PIEL SABORES CJA X 3 UNDS</t>
+          <t>CONDON PIEL EXCITANTE X 3 UNDS</t>
         </is>
       </c>
       <c r="C1306" t="inlineStr"/>
@@ -70202,25 +70202,21 @@
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>CONDON PRUDENCE EFEC.RETARDX3UNDS</t>
-        </is>
-      </c>
-      <c r="C1307" t="inlineStr">
-        <is>
-          <t>77309632510504387</t>
-        </is>
-      </c>
+          <t>CONDON PIEL SABORES CJA X 3 UNDS</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr"/>
       <c r="D1307" t="inlineStr"/>
       <c r="E1307" t="n">
-        <v>12200</v>
+        <v>8900</v>
       </c>
       <c r="F1307" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1307" t="n">
         <v>0</v>
@@ -70256,25 +70252,25 @@
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>CONDON PRUDENCE EXTRA GRANDE ULT SENSIBX3UND</t>
+          <t>CONDON PRUDENCE EFEC.RETARDX3UNDS</t>
         </is>
       </c>
       <c r="C1308" t="inlineStr">
         <is>
-          <t>7730963250343</t>
+          <t>77309632510504387</t>
         </is>
       </c>
       <c r="D1308" t="inlineStr"/>
       <c r="E1308" t="n">
-        <v>13800</v>
+        <v>12200</v>
       </c>
       <c r="F1308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1308" t="n">
         <v>0</v>
@@ -70310,25 +70306,25 @@
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>CONTENT MEDICAL PAÑAL TALLA L X UND</t>
-        </is>
-      </c>
-      <c r="C1309" t="inlineStr"/>
-      <c r="D1309" t="inlineStr">
-        <is>
-          <t>pañal adulto no paga iva articulo 424</t>
-        </is>
-      </c>
+          <t>CONDON PRUDENCE EXTRA GRANDE ULT SENSIBX3UND</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>7730963250343</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr"/>
       <c r="E1309" t="n">
-        <v>4800</v>
+        <v>13800</v>
       </c>
       <c r="F1309" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G1309" t="n">
         <v>0</v>
@@ -70364,21 +70360,25 @@
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>CONTENT MEDICAL PAÑAL TALLA M X UND</t>
+          <t>CONTENT MEDICAL PAÑAL TALLA L X UND</t>
         </is>
       </c>
       <c r="C1310" t="inlineStr"/>
-      <c r="D1310" t="inlineStr"/>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>pañal adulto no paga iva articulo 424</t>
+        </is>
+      </c>
       <c r="E1310" t="n">
-        <v>3697.478992</v>
+        <v>4800</v>
       </c>
       <c r="F1310" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G1310" t="n">
         <v>0</v>
@@ -70406,7 +70406,7 @@
       </c>
       <c r="M1310" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1310" t="inlineStr"/>
@@ -70414,21 +70414,21 @@
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 100 UNDS</t>
+          <t>CONTENT MEDICAL PAÑAL TALLA M X UND</t>
         </is>
       </c>
       <c r="C1311" t="inlineStr"/>
       <c r="D1311" t="inlineStr"/>
       <c r="E1311" t="n">
-        <v>8500</v>
+        <v>3697.478992</v>
       </c>
       <c r="F1311" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G1311" t="n">
         <v>0</v>
@@ -70456,7 +70456,7 @@
       </c>
       <c r="M1311" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1311" t="inlineStr"/>
@@ -70464,18 +70464,18 @@
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 50 UNDS</t>
+          <t>COPITOS YOKY X 100 UNDS</t>
         </is>
       </c>
       <c r="C1312" t="inlineStr"/>
       <c r="D1312" t="inlineStr"/>
       <c r="E1312" t="n">
-        <v>6400</v>
+        <v>8500</v>
       </c>
       <c r="F1312" t="n">
         <v>3</v>
@@ -70514,21 +70514,21 @@
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>COPITOS YOKY X 60 UNDS</t>
+          <t>COPITOS YOKY X 50 UNDS</t>
         </is>
       </c>
       <c r="C1313" t="inlineStr"/>
       <c r="D1313" t="inlineStr"/>
       <c r="E1313" t="n">
-        <v>7142.857143</v>
+        <v>6400</v>
       </c>
       <c r="F1313" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1313" t="n">
         <v>0</v>
@@ -70556,7 +70556,7 @@
       </c>
       <c r="M1313" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1313" t="inlineStr"/>
@@ -70564,21 +70564,21 @@
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>CORTA CUTICULA TRIM METALICO</t>
+          <t>COPITOS YOKY X 60 UNDS</t>
         </is>
       </c>
       <c r="C1314" t="inlineStr"/>
       <c r="D1314" t="inlineStr"/>
       <c r="E1314" t="n">
-        <v>16000</v>
+        <v>7142.857143</v>
       </c>
       <c r="F1314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1314" t="n">
         <v>0</v>
@@ -70606,7 +70606,7 @@
       </c>
       <c r="M1314" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1314" t="inlineStr"/>
@@ -70614,21 +70614,21 @@
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>CREMA ARNICA PROTECTORA 12GR ICE POWER</t>
+          <t>CORTA CUTICULA TRIM METALICO</t>
         </is>
       </c>
       <c r="C1315" t="inlineStr"/>
       <c r="D1315" t="inlineStr"/>
       <c r="E1315" t="n">
-        <v>10084.033613</v>
+        <v>16000</v>
       </c>
       <c r="F1315" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1315" t="n">
         <v>0</v>
@@ -70656,7 +70656,7 @@
       </c>
       <c r="M1315" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1315" t="inlineStr"/>
@@ -70664,21 +70664,21 @@
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>CREMA BENLIC DE 40GR</t>
+          <t>CREMA ARNICA PROTECTORA 12GR ICE POWER</t>
         </is>
       </c>
       <c r="C1316" t="inlineStr"/>
       <c r="D1316" t="inlineStr"/>
       <c r="E1316" t="n">
-        <v>28900</v>
+        <v>10084.033613</v>
       </c>
       <c r="F1316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1316" t="n">
         <v>0</v>
@@ -70706,7 +70706,7 @@
       </c>
       <c r="M1316" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1316" t="inlineStr"/>
@@ -70714,18 +70714,18 @@
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>CREMA CASTAÑO DE INDIAS X 12GR ARMONIZA</t>
+          <t>CREMA BENLIC DE 40GR</t>
         </is>
       </c>
       <c r="C1317" t="inlineStr"/>
       <c r="D1317" t="inlineStr"/>
       <c r="E1317" t="n">
-        <v>9000</v>
+        <v>28900</v>
       </c>
       <c r="F1317" t="n">
         <v>1</v>
@@ -70764,25 +70764,21 @@
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>Crema Colgate triple acción xtra blancura 60ml</t>
-        </is>
-      </c>
-      <c r="C1318" t="inlineStr">
-        <is>
-          <t>7702010111587</t>
-        </is>
-      </c>
+          <t>CREMA CASTAÑO DE INDIAS X 12GR ARMONIZA</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr"/>
       <c r="D1318" t="inlineStr"/>
       <c r="E1318" t="n">
-        <v>5630.252101</v>
+        <v>9000</v>
       </c>
       <c r="F1318" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1318" t="n">
         <v>0</v>
@@ -70810,7 +70806,7 @@
       </c>
       <c r="M1318" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1318" t="inlineStr"/>
@@ -70818,21 +70814,25 @@
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>CREMA PONDS CLARANT B3 X SACHETS</t>
-        </is>
-      </c>
-      <c r="C1319" t="inlineStr"/>
+          <t>Crema Colgate triple acción xtra blancura 60ml</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>7702010111587</t>
+        </is>
+      </c>
       <c r="D1319" t="inlineStr"/>
       <c r="E1319" t="n">
-        <v>2521.008403</v>
+        <v>5630.252101</v>
       </c>
       <c r="F1319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1319" t="n">
         <v>0</v>
@@ -70868,21 +70868,21 @@
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>CURAS LARGAS RESIST AL AGUA</t>
+          <t>CREMA PONDS CLARANT B3 X SACHETS</t>
         </is>
       </c>
       <c r="C1320" t="inlineStr"/>
       <c r="D1320" t="inlineStr"/>
       <c r="E1320" t="n">
-        <v>300</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1320" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="G1320" t="n">
         <v>0</v>
@@ -70910,7 +70910,7 @@
       </c>
       <c r="M1320" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1320" t="inlineStr"/>
@@ -70918,25 +70918,21 @@
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>CYCLOFEM AMPOLLA INYECTABLE .PROFAMILIA</t>
-        </is>
-      </c>
-      <c r="C1321" t="inlineStr">
-        <is>
-          <t>7703689000448</t>
-        </is>
-      </c>
+          <t>CURAS LARGAS RESIST AL AGUA</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr"/>
       <c r="D1321" t="inlineStr"/>
       <c r="E1321" t="n">
-        <v>28900</v>
+        <v>300</v>
       </c>
       <c r="F1321" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="G1321" t="n">
         <v>0</v>
@@ -70972,25 +70968,25 @@
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>CYCLOFEMINA AMPOLLA 0.5ML</t>
+          <t>CYCLOFEM AMPOLLA INYECTABLE .PROFAMILIA</t>
         </is>
       </c>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>7707271451410</t>
+          <t>7703689000448</t>
         </is>
       </c>
       <c r="D1322" t="inlineStr"/>
       <c r="E1322" t="n">
-        <v>33900</v>
+        <v>28900</v>
       </c>
       <c r="F1322" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1322" t="n">
         <v>0</v>
@@ -71026,25 +71022,25 @@
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>Desonida bussie 0.1% crema 15gr</t>
+          <t>CYCLOFEMINA AMPOLLA 0.5ML</t>
         </is>
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>7702195210587</t>
+          <t>7707271451410</t>
         </is>
       </c>
       <c r="D1323" t="inlineStr"/>
       <c r="E1323" t="n">
-        <v>19000</v>
+        <v>33900</v>
       </c>
       <c r="F1323" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1323" t="n">
         <v>0</v>
@@ -71080,25 +71076,25 @@
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>Diclofenaco gel vitalis 50gr</t>
+          <t>Desonida bussie 0.1% crema 15gr</t>
         </is>
       </c>
       <c r="C1324" t="inlineStr">
         <is>
-          <t>7709141546059</t>
+          <t>7702195210587</t>
         </is>
       </c>
       <c r="D1324" t="inlineStr"/>
       <c r="E1324" t="n">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="F1324" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1324" t="n">
         <v>0</v>
@@ -71124,31 +71120,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1324" t="inlineStr"/>
+      <c r="M1324" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1324" t="inlineStr"/>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>Diclofenaco sódico 100mg +hidróxido de aluminio200mg colmed</t>
-        </is>
-      </c>
-      <c r="C1325" t="inlineStr">
-        <is>
-          <t>7703153020286</t>
-        </is>
-      </c>
+          <t>DESOTOPIC 0.1%TUBO X 15 GR DESONIDA</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr"/>
       <c r="D1325" t="inlineStr"/>
       <c r="E1325" t="n">
-        <v>19200</v>
+        <v>20500</v>
       </c>
       <c r="F1325" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1325" t="n">
         <v>0</v>
@@ -71184,21 +71180,25 @@
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>781</t>
         </is>
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>DICLOFENACOXUND75MG/3MLAMPCOMERCIAL VITALIS</t>
-        </is>
-      </c>
-      <c r="C1326" t="inlineStr"/>
+          <t>Diclofenaco gel vitalis 50gr</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>7709141546059</t>
+        </is>
+      </c>
       <c r="D1326" t="inlineStr"/>
       <c r="E1326" t="n">
-        <v>5500</v>
+        <v>16000</v>
       </c>
       <c r="F1326" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1326" t="n">
         <v>0</v>
@@ -71224,31 +71224,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1326" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1326" t="inlineStr"/>
       <c r="N1326" t="inlineStr"/>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>DIFENZ DESPIGMENTADOR CREMA TUBO X 1 UND</t>
-        </is>
-      </c>
-      <c r="C1327" t="inlineStr"/>
+          <t>Diclofenaco sódico 100mg +hidróxido de aluminio200mg colmed</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>7703153020286</t>
+        </is>
+      </c>
       <c r="D1327" t="inlineStr"/>
       <c r="E1327" t="n">
-        <v>163300</v>
+        <v>19200</v>
       </c>
       <c r="F1327" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1327" t="n">
         <v>0</v>
@@ -71284,25 +71284,21 @@
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>DIOSMINA HESPERIDINA 450MG 50MG GENFAR</t>
-        </is>
-      </c>
-      <c r="C1328" t="inlineStr">
-        <is>
-          <t>7705959013370</t>
-        </is>
-      </c>
+          <t>DICLOFENACOXUND75MG/3MLAMPCOMERCIAL VITALIS</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr"/>
       <c r="D1328" t="inlineStr"/>
       <c r="E1328" t="n">
-        <v>42000</v>
+        <v>5500</v>
       </c>
       <c r="F1328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1328" t="n">
         <v>0</v>
@@ -71338,21 +71334,21 @@
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>DIPIORNA 500MG TABLETA X 10 DE ECAR</t>
+          <t>DIFENZ DESPIGMENTADOR CREMA TUBO X 1 UND</t>
         </is>
       </c>
       <c r="C1329" t="inlineStr"/>
       <c r="D1329" t="inlineStr"/>
       <c r="E1329" t="n">
-        <v>7900</v>
+        <v>163300</v>
       </c>
       <c r="F1329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1329" t="n">
         <v>0</v>
@@ -71388,21 +71384,25 @@
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>DIPIRONA 500MG TABLETA X 10 DE ECAR</t>
-        </is>
-      </c>
-      <c r="C1330" t="inlineStr"/>
+          <t>DIOSMINA HESPERIDINA 450MG 50MG GENFAR</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>7705959013370</t>
+        </is>
+      </c>
       <c r="D1330" t="inlineStr"/>
       <c r="E1330" t="n">
-        <v>7900</v>
+        <v>42000</v>
       </c>
       <c r="F1330" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1330" t="n">
         <v>0</v>
@@ -71438,18 +71438,18 @@
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>DOMICILIO</t>
+          <t>DIPIORNA 500MG TABLETA X 10 DE ECAR</t>
         </is>
       </c>
       <c r="C1331" t="inlineStr"/>
       <c r="D1331" t="inlineStr"/>
       <c r="E1331" t="n">
-        <v>3000</v>
+        <v>7900</v>
       </c>
       <c r="F1331" t="n">
         <v>0</v>
@@ -71478,27 +71478,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1331" t="inlineStr"/>
+      <c r="M1331" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1331" t="inlineStr"/>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>DOXICICLINA 100MG X 10 TABL GENFAR</t>
+          <t>DIPIRONA 500MG TABLETA X 10 DE ECAR</t>
         </is>
       </c>
       <c r="C1332" t="inlineStr"/>
       <c r="D1332" t="inlineStr"/>
       <c r="E1332" t="n">
-        <v>12000</v>
+        <v>7900</v>
       </c>
       <c r="F1332" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1332" t="n">
         <v>0</v>
@@ -71534,21 +71538,21 @@
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>DUCHA INTIMA DESECHABLE VINAGRE</t>
+          <t>DOMICILIO</t>
         </is>
       </c>
       <c r="C1333" t="inlineStr"/>
       <c r="D1333" t="inlineStr"/>
       <c r="E1333" t="n">
-        <v>24800</v>
+        <v>3000</v>
       </c>
       <c r="F1333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1333" t="n">
         <v>0</v>
@@ -71574,35 +71578,27 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1333" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1333" t="inlineStr"/>
       <c r="N1333" t="inlineStr"/>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>E ala proel maléate 20mg medicbrand</t>
-        </is>
-      </c>
-      <c r="C1334" t="inlineStr">
-        <is>
-          <t>7703712035997</t>
-        </is>
-      </c>
+          <t>DOXICICLINA 100MG X 10 TABL GENFAR</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr"/>
       <c r="D1334" t="inlineStr"/>
       <c r="E1334" t="n">
-        <v>1250</v>
+        <v>12000</v>
       </c>
       <c r="F1334" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1334" t="n">
         <v>0</v>
@@ -71638,25 +71634,21 @@
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Enalapril 20 mg MK</t>
-        </is>
-      </c>
-      <c r="C1335" t="inlineStr">
-        <is>
-          <t>7702057716578</t>
-        </is>
-      </c>
+          <t>DUCHA INTIMA DESECHABLE VINAGRE</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr"/>
       <c r="D1335" t="inlineStr"/>
       <c r="E1335" t="n">
-        <v>4700</v>
+        <v>24800</v>
       </c>
       <c r="F1335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1335" t="n">
         <v>0</v>
@@ -71692,21 +71684,25 @@
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>ENALAPRIL 20MG TABLETA COAS</t>
-        </is>
-      </c>
-      <c r="C1336" t="inlineStr"/>
+          <t>E ala proel maléate 20mg medicbrand</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>7703712035997</t>
+        </is>
+      </c>
       <c r="D1336" t="inlineStr"/>
       <c r="E1336" t="n">
-        <v>3000</v>
+        <v>1250</v>
       </c>
       <c r="F1336" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1336" t="n">
         <v>0</v>
@@ -71742,21 +71738,25 @@
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>ENSURE ADVANCE VAINILLA 400GR</t>
-        </is>
-      </c>
-      <c r="C1337" t="inlineStr"/>
+          <t>Enalapril 20 mg MK</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>7702057716578</t>
+        </is>
+      </c>
       <c r="D1337" t="inlineStr"/>
       <c r="E1337" t="n">
-        <v>85900</v>
+        <v>4700</v>
       </c>
       <c r="F1337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1337" t="n">
         <v>0</v>
@@ -71792,21 +71792,21 @@
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>ENTRETENEDOR BEBE</t>
+          <t>ENALAPRIL 20MG TABLETA COAS</t>
         </is>
       </c>
       <c r="C1338" t="inlineStr"/>
       <c r="D1338" t="inlineStr"/>
       <c r="E1338" t="n">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="F1338" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1338" t="n">
         <v>0</v>
@@ -71842,18 +71842,18 @@
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>ESMALTE BRILLO ACRILICO BRESCIA</t>
+          <t>ENSURE ADVANCE VAINILLA 400GR</t>
         </is>
       </c>
       <c r="C1339" t="inlineStr"/>
       <c r="D1339" t="inlineStr"/>
       <c r="E1339" t="n">
-        <v>11500</v>
+        <v>85900</v>
       </c>
       <c r="F1339" t="n">
         <v>1</v>
@@ -71892,21 +71892,21 @@
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>ESOMEPRAZOL 20MG NOVAMED</t>
+          <t>ENTRETENEDOR BEBE</t>
         </is>
       </c>
       <c r="C1340" t="inlineStr"/>
       <c r="D1340" t="inlineStr"/>
       <c r="E1340" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="F1340" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="G1340" t="n">
         <v>0</v>
@@ -71942,18 +71942,18 @@
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>ESPASMOK HIOS +DIPIRO 5ML AMP BLASKOV</t>
+          <t>ESMALTE BRILLO ACRILICO BRESCIA</t>
         </is>
       </c>
       <c r="C1341" t="inlineStr"/>
       <c r="D1341" t="inlineStr"/>
       <c r="E1341" t="n">
-        <v>12000</v>
+        <v>11500</v>
       </c>
       <c r="F1341" t="n">
         <v>1</v>
@@ -71992,25 +71992,21 @@
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>ETORICOXIB 120MG GENFAR</t>
-        </is>
-      </c>
-      <c r="C1342" t="inlineStr">
-        <is>
-          <t>7702605109371</t>
-        </is>
-      </c>
+          <t>ESOMEPRAZOL 20MG NOVAMED</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr"/>
       <c r="D1342" t="inlineStr"/>
       <c r="E1342" t="n">
-        <v>48600</v>
+        <v>2000</v>
       </c>
       <c r="F1342" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G1342" t="n">
         <v>0</v>
@@ -72046,22 +72042,18 @@
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>EXTRACTOR DE LECHE MOBY</t>
-        </is>
-      </c>
-      <c r="C1343" t="inlineStr">
-        <is>
-          <t>7707233051436</t>
-        </is>
-      </c>
+          <t>ESPASMOK HIOS +DIPIRO 5ML AMP BLASKOV</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr"/>
       <c r="D1343" t="inlineStr"/>
       <c r="E1343" t="n">
-        <v>14285.714286</v>
+        <v>12000</v>
       </c>
       <c r="F1343" t="n">
         <v>1</v>
@@ -72092,7 +72084,7 @@
       </c>
       <c r="M1343" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1343" t="inlineStr"/>
@@ -72100,25 +72092,25 @@
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>FAMIIA MEGARROLLO PAPEL HIGUIEN</t>
+          <t>ETORICOXIB 120MG GENFAR</t>
         </is>
       </c>
       <c r="C1344" t="inlineStr">
         <is>
-          <t>7702026147471</t>
+          <t>7702605109371</t>
         </is>
       </c>
       <c r="D1344" t="inlineStr"/>
       <c r="E1344" t="n">
-        <v>3500</v>
+        <v>48600</v>
       </c>
       <c r="F1344" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G1344" t="n">
         <v>0</v>
@@ -72154,21 +72146,25 @@
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>Farma D 500 UI</t>
-        </is>
-      </c>
-      <c r="C1345" t="inlineStr"/>
+          <t>EXTRACTOR DE LECHE MOBY</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>7707233051436</t>
+        </is>
+      </c>
       <c r="D1345" t="inlineStr"/>
       <c r="E1345" t="n">
-        <v>74000</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1345" t="n">
         <v>0</v>
@@ -72196,7 +72192,7 @@
       </c>
       <c r="M1345" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1345" t="inlineStr"/>
@@ -72204,21 +72200,25 @@
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>FIBRA AMARILLA ARMONIZA X 450GR</t>
-        </is>
-      </c>
-      <c r="C1346" t="inlineStr"/>
+          <t>FAMIIA MEGARROLLO PAPEL HIGUIEN</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>7702026147471</t>
+        </is>
+      </c>
       <c r="D1346" t="inlineStr"/>
       <c r="E1346" t="n">
-        <v>28571.428571</v>
+        <v>3500</v>
       </c>
       <c r="F1346" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G1346" t="n">
         <v>0</v>
@@ -72246,7 +72246,7 @@
       </c>
       <c r="M1346" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1346" t="inlineStr"/>
@@ -72254,18 +72254,18 @@
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>FIBRA DE AVENA Y SALVADO DE TRIGO 450GR</t>
+          <t>Farma D 500 UI</t>
         </is>
       </c>
       <c r="C1347" t="inlineStr"/>
       <c r="D1347" t="inlineStr"/>
       <c r="E1347" t="n">
-        <v>30000</v>
+        <v>74000</v>
       </c>
       <c r="F1347" t="n">
         <v>0</v>
@@ -72304,21 +72304,21 @@
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>FITOSTIMONE 15% GEL</t>
+          <t>FIBRA AMARILLA ARMONIZA X 450GR</t>
         </is>
       </c>
       <c r="C1348" t="inlineStr"/>
       <c r="D1348" t="inlineStr"/>
       <c r="E1348" t="n">
-        <v>48900</v>
+        <v>28571.428571</v>
       </c>
       <c r="F1348" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1348" t="n">
         <v>0</v>
@@ -72346,7 +72346,7 @@
       </c>
       <c r="M1348" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1348" t="inlineStr"/>
@@ -72354,25 +72354,21 @@
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG CJA X 10 UND EXPORF</t>
-        </is>
-      </c>
-      <c r="C1349" t="inlineStr">
-        <is>
-          <t>7703432421681</t>
-        </is>
-      </c>
+          <t>FIBRA DE AVENA Y SALVADO DE TRIGO 450GR</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr"/>
       <c r="D1349" t="inlineStr"/>
       <c r="E1349" t="n">
-        <v>18300</v>
+        <v>30000</v>
       </c>
       <c r="F1349" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G1349" t="n">
         <v>0</v>
@@ -72408,18 +72404,18 @@
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS DE GENFAR</t>
+          <t>FITOSTIMONE 15% GEL</t>
         </is>
       </c>
       <c r="C1350" t="inlineStr"/>
       <c r="D1350" t="inlineStr"/>
       <c r="E1350" t="n">
-        <v>16900</v>
+        <v>48900</v>
       </c>
       <c r="F1350" t="n">
         <v>2</v>
@@ -72458,25 +72454,25 @@
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS. LA SANTE</t>
+          <t>FLUCONAZOL 200MG CJA X 10 UND EXPORF</t>
         </is>
       </c>
       <c r="C1351" t="inlineStr">
         <is>
-          <t>7703763480166</t>
+          <t>7703432421681</t>
         </is>
       </c>
       <c r="D1351" t="inlineStr"/>
       <c r="E1351" t="n">
-        <v>14700</v>
+        <v>18300</v>
       </c>
       <c r="F1351" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G1351" t="n">
         <v>0</v>
@@ -72512,22 +72508,18 @@
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>FLUCONAZOL 200MG X 4 CAPS.NOVAMED</t>
-        </is>
-      </c>
-      <c r="C1352" t="inlineStr">
-        <is>
-          <t>7703546927468</t>
-        </is>
-      </c>
+          <t>FLUCONAZOL 200MG X 4 CAPS DE GENFAR</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr"/>
       <c r="D1352" t="inlineStr"/>
       <c r="E1352" t="n">
-        <v>10900</v>
+        <v>16900</v>
       </c>
       <c r="F1352" t="n">
         <v>2</v>
@@ -72566,21 +72558,25 @@
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>Fluconazol Suspension</t>
-        </is>
-      </c>
-      <c r="C1353" t="inlineStr"/>
+          <t>FLUCONAZOL 200MG X 4 CAPS. LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>7703763480166</t>
+        </is>
+      </c>
       <c r="D1353" t="inlineStr"/>
       <c r="E1353" t="n">
-        <v>148000</v>
+        <v>14700</v>
       </c>
       <c r="F1353" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1353" t="n">
         <v>0</v>
@@ -72616,21 +72612,25 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>FUNGI-FIN LOCION GOTAS TOPICA 20ML</t>
-        </is>
-      </c>
-      <c r="C1354" t="inlineStr"/>
+          <t>FLUCONAZOL 200MG X 4 CAPS.NOVAMED</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>7703546927468</t>
+        </is>
+      </c>
       <c r="D1354" t="inlineStr"/>
       <c r="E1354" t="n">
-        <v>15966.386555</v>
+        <v>10900</v>
       </c>
       <c r="F1354" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1354" t="n">
         <v>0</v>
@@ -72658,7 +72658,7 @@
       </c>
       <c r="M1354" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1354" t="inlineStr"/>
@@ -72666,21 +72666,21 @@
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>GALLETA OREO PAQUETE X 6 UNDS</t>
+          <t>Fluconazol Suspension</t>
         </is>
       </c>
       <c r="C1355" t="inlineStr"/>
       <c r="D1355" t="inlineStr"/>
       <c r="E1355" t="n">
-        <v>1932.773109</v>
+        <v>148000</v>
       </c>
       <c r="F1355" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1355" t="n">
         <v>0</v>
@@ -72708,7 +72708,7 @@
       </c>
       <c r="M1355" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1355" t="inlineStr"/>
@@ -72716,21 +72716,21 @@
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="B1356" t="inlineStr">
         <is>
-          <t>GASEOSA PREMIO 400ML ROJO</t>
+          <t>FUNGI-FIN LOCION GOTAS TOPICA 20ML</t>
         </is>
       </c>
       <c r="C1356" t="inlineStr"/>
       <c r="D1356" t="inlineStr"/>
       <c r="E1356" t="n">
-        <v>2941.176471</v>
+        <v>15966.386555</v>
       </c>
       <c r="F1356" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G1356" t="n">
         <v>0</v>
@@ -72766,29 +72766,21 @@
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>GASTROFAST ADVANCE</t>
-        </is>
-      </c>
-      <c r="C1357" t="inlineStr">
-        <is>
-          <t>7702057803254</t>
-        </is>
-      </c>
-      <c r="D1357" t="inlineStr">
-        <is>
-          <t>se subio A 3800 ANTES 3.600, LEYDI</t>
-        </is>
-      </c>
+          <t>GALLETA OREO PAQUETE X 6 UNDS</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr"/>
+      <c r="D1357" t="inlineStr"/>
       <c r="E1357" t="n">
-        <v>3800</v>
+        <v>1932.773109</v>
       </c>
       <c r="F1357" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G1357" t="n">
         <v>0</v>
@@ -72816,7 +72808,7 @@
       </c>
       <c r="M1357" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1357" t="inlineStr"/>
@@ -72824,21 +72816,21 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>GASTROFAST ADVANCE X 240 ML</t>
+          <t>GASEOSA PREMIO 400ML ROJO</t>
         </is>
       </c>
       <c r="C1358" t="inlineStr"/>
       <c r="D1358" t="inlineStr"/>
       <c r="E1358" t="n">
-        <v>69500</v>
+        <v>2941.176471</v>
       </c>
       <c r="F1358" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G1358" t="n">
         <v>0</v>
@@ -72866,7 +72858,7 @@
       </c>
       <c r="M1358" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1358" t="inlineStr"/>
@@ -72874,25 +72866,29 @@
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>gatorade</t>
+          <t>GASTROFAST ADVANCE</t>
         </is>
       </c>
       <c r="C1359" t="inlineStr">
         <is>
-          <t>248656546</t>
-        </is>
-      </c>
-      <c r="D1359" t="inlineStr"/>
+          <t>7702057803254</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>se subio A 3800 ANTES 3.600, LEYDI</t>
+        </is>
+      </c>
       <c r="E1359" t="n">
-        <v>3782</v>
+        <v>3800</v>
       </c>
       <c r="F1359" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G1359" t="n">
         <v>0</v>
@@ -72920,7 +72916,7 @@
       </c>
       <c r="M1359" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1359" t="inlineStr"/>
@@ -72928,18 +72924,18 @@
     <row r="1360">
       <c r="A1360" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>GEL BACHUE 150GR</t>
+          <t>GASTROFAST ADVANCE X 240 ML</t>
         </is>
       </c>
       <c r="C1360" t="inlineStr"/>
       <c r="D1360" t="inlineStr"/>
       <c r="E1360" t="n">
-        <v>8800</v>
+        <v>69500</v>
       </c>
       <c r="F1360" t="n">
         <v>1</v>
@@ -72978,21 +72974,25 @@
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>GEMFIBROZILO 600 MG</t>
-        </is>
-      </c>
-      <c r="C1361" t="inlineStr"/>
+          <t>gatorade</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>248656546</t>
+        </is>
+      </c>
       <c r="D1361" t="inlineStr"/>
       <c r="E1361" t="n">
-        <v>8300</v>
+        <v>3782</v>
       </c>
       <c r="F1361" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1361" t="n">
         <v>0</v>
@@ -73020,7 +73020,7 @@
       </c>
       <c r="M1361" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1361" t="inlineStr"/>
@@ -73028,18 +73028,18 @@
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>GLICERINA CARBONATADA X 20ML FCO YOMA</t>
+          <t>GEL BACHUE 150GR</t>
         </is>
       </c>
       <c r="C1362" t="inlineStr"/>
       <c r="D1362" t="inlineStr"/>
       <c r="E1362" t="n">
-        <v>3900</v>
+        <v>8800</v>
       </c>
       <c r="F1362" t="n">
         <v>1</v>
@@ -73078,21 +73078,21 @@
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="B1363" t="inlineStr">
         <is>
-          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
+          <t>GEMFIBROZILO 600 MG</t>
         </is>
       </c>
       <c r="C1363" t="inlineStr"/>
       <c r="D1363" t="inlineStr"/>
       <c r="E1363" t="n">
-        <v>3361.344538</v>
+        <v>8300</v>
       </c>
       <c r="F1363" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1363" t="n">
         <v>0</v>
@@ -73120,7 +73120,7 @@
       </c>
       <c r="M1363" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1363" t="inlineStr"/>
@@ -73128,21 +73128,21 @@
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B1364" t="inlineStr">
         <is>
-          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
+          <t>GLICERINA CARBONATADA X 20ML FCO YOMA</t>
         </is>
       </c>
       <c r="C1364" t="inlineStr"/>
       <c r="D1364" t="inlineStr"/>
       <c r="E1364" t="n">
-        <v>23109.243697</v>
+        <v>3900</v>
       </c>
       <c r="F1364" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="G1364" t="n">
         <v>0</v>
@@ -73170,7 +73170,7 @@
       </c>
       <c r="M1364" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1364" t="inlineStr"/>
@@ -73178,25 +73178,21 @@
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1365" t="inlineStr">
-        <is>
-          <t>7709195419279</t>
-        </is>
-      </c>
+          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr"/>
       <c r="D1365" t="inlineStr"/>
       <c r="E1365" t="n">
-        <v>24370</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1365" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1365" t="n">
         <v>0</v>
@@ -73232,21 +73228,21 @@
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
+          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
         </is>
       </c>
       <c r="C1366" t="inlineStr"/>
       <c r="D1366" t="inlineStr"/>
       <c r="E1366" t="n">
-        <v>24369.747899</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1366" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G1366" t="n">
         <v>0</v>
@@ -73282,21 +73278,25 @@
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="B1367" t="inlineStr">
         <is>
-          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
-        </is>
-      </c>
-      <c r="C1367" t="inlineStr"/>
+          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>7709195419279</t>
+        </is>
+      </c>
       <c r="D1367" t="inlineStr"/>
       <c r="E1367" t="n">
-        <v>23109.243697</v>
+        <v>24370</v>
       </c>
       <c r="F1367" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G1367" t="n">
         <v>0</v>
@@ -73332,21 +73332,21 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>HALLS BARRA SURTIDOS SABORES</t>
+          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
         </is>
       </c>
       <c r="C1368" t="inlineStr"/>
       <c r="D1368" t="inlineStr"/>
       <c r="E1368" t="n">
-        <v>2100.840336</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1368" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="G1368" t="n">
         <v>0</v>
@@ -73382,21 +73382,21 @@
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>HALLS PEPA ROJO CEREZA X UND</t>
+          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
         </is>
       </c>
       <c r="C1369" t="inlineStr"/>
       <c r="D1369" t="inlineStr"/>
       <c r="E1369" t="n">
-        <v>336.134454</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1369" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G1369" t="n">
         <v>0</v>
@@ -73432,21 +73432,21 @@
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>HEPATODREN JARABE FCO X 240ML</t>
+          <t>HALLS BARRA SURTIDOS SABORES</t>
         </is>
       </c>
       <c r="C1370" t="inlineStr"/>
       <c r="D1370" t="inlineStr"/>
       <c r="E1370" t="n">
-        <v>34500</v>
+        <v>2100.840336</v>
       </c>
       <c r="F1370" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G1370" t="n">
         <v>0</v>
@@ -73474,7 +73474,7 @@
       </c>
       <c r="M1370" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1370" t="inlineStr"/>
@@ -73482,21 +73482,21 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>HEPATODREN X 60 CAPSULAS</t>
+          <t>HALLS PEPA ROJO CEREZA X UND</t>
         </is>
       </c>
       <c r="C1371" t="inlineStr"/>
       <c r="D1371" t="inlineStr"/>
       <c r="E1371" t="n">
-        <v>58300</v>
+        <v>336.134454</v>
       </c>
       <c r="F1371" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G1371" t="n">
         <v>0</v>
@@ -73524,7 +73524,7 @@
       </c>
       <c r="M1371" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1371" t="inlineStr"/>
@@ -73532,25 +73532,21 @@
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>Hidraplus 75 zinc uva 400ml</t>
-        </is>
-      </c>
-      <c r="C1372" t="inlineStr">
-        <is>
-          <t>7702057010928</t>
-        </is>
-      </c>
+          <t>HEPATODREN JARABE FCO X 240ML</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr"/>
       <c r="D1372" t="inlineStr"/>
       <c r="E1372" t="n">
-        <v>10600</v>
+        <v>34500</v>
       </c>
       <c r="F1372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1372" t="n">
         <v>0</v>
@@ -73586,21 +73582,21 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
+          <t>HEPATODREN X 60 CAPSULAS</t>
         </is>
       </c>
       <c r="C1373" t="inlineStr"/>
       <c r="D1373" t="inlineStr"/>
       <c r="E1373" t="n">
-        <v>15900</v>
+        <v>58300</v>
       </c>
       <c r="F1373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1373" t="n">
         <v>0</v>
@@ -73636,22 +73632,22 @@
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
+          <t>Hidraplus 75 zinc uva 400ml</t>
         </is>
       </c>
       <c r="C1374" t="inlineStr">
         <is>
-          <t>77099475597789</t>
+          <t>7702057010928</t>
         </is>
       </c>
       <c r="D1374" t="inlineStr"/>
       <c r="E1374" t="n">
-        <v>28000</v>
+        <v>10600</v>
       </c>
       <c r="F1374" t="n">
         <v>0</v>
@@ -73690,22 +73686,18 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>Hidroxicina 0.25 JBE x 120 ML</t>
-        </is>
-      </c>
-      <c r="C1375" t="inlineStr">
-        <is>
-          <t>7707035540596</t>
-        </is>
-      </c>
+          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr"/>
       <c r="D1375" t="inlineStr"/>
       <c r="E1375" t="n">
-        <v>11000</v>
+        <v>15900</v>
       </c>
       <c r="F1375" t="n">
         <v>2</v>
@@ -73744,21 +73736,25 @@
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
-        </is>
-      </c>
-      <c r="C1376" t="inlineStr"/>
+          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>77099475597789</t>
+        </is>
+      </c>
       <c r="D1376" t="inlineStr"/>
       <c r="E1376" t="n">
-        <v>4500</v>
+        <v>28000</v>
       </c>
       <c r="F1376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1376" t="n">
         <v>0</v>
@@ -73794,21 +73790,25 @@
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1377" t="inlineStr"/>
+          <t>Hidroxicina 0.25 JBE x 120 ML</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>7707035540596</t>
+        </is>
+      </c>
       <c r="D1377" t="inlineStr"/>
       <c r="E1377" t="n">
-        <v>6900</v>
+        <v>11000</v>
       </c>
       <c r="F1377" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1377" t="n">
         <v>0</v>
@@ -73844,21 +73844,21 @@
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
+          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
         </is>
       </c>
       <c r="C1378" t="inlineStr"/>
       <c r="D1378" t="inlineStr"/>
       <c r="E1378" t="n">
-        <v>12000</v>
+        <v>4500</v>
       </c>
       <c r="F1378" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1378" t="n">
         <v>0</v>
@@ -73894,21 +73894,21 @@
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>Hylo Gel</t>
+          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
         </is>
       </c>
       <c r="C1379" t="inlineStr"/>
       <c r="D1379" t="inlineStr"/>
       <c r="E1379" t="n">
-        <v>131600</v>
+        <v>6900</v>
       </c>
       <c r="F1379" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1379" t="n">
         <v>0</v>
@@ -73944,25 +73944,21 @@
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>IBUPROFENO 400MG/ GENFAR</t>
-        </is>
-      </c>
-      <c r="C1380" t="inlineStr">
-        <is>
-          <t>7702605101498</t>
-        </is>
-      </c>
+          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr"/>
       <c r="D1380" t="inlineStr"/>
       <c r="E1380" t="n">
-        <v>4400</v>
+        <v>12000</v>
       </c>
       <c r="F1380" t="n">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="G1380" t="n">
         <v>0</v>
@@ -73998,22 +73994,18 @@
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>Ibuprofeno 800mg AG</t>
-        </is>
-      </c>
-      <c r="C1381" t="inlineStr">
-        <is>
-          <t>7706569000385</t>
-        </is>
-      </c>
+          <t>Hylo Gel</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr"/>
       <c r="D1381" t="inlineStr"/>
       <c r="E1381" t="n">
-        <v>800</v>
+        <v>131600</v>
       </c>
       <c r="F1381" t="n">
         <v>0</v>
@@ -74052,25 +74044,25 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
+          <t>IBUPROFENO 400MG/ GENFAR</t>
         </is>
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>7705959885229</t>
+          <t>7702605101498</t>
         </is>
       </c>
       <c r="D1382" t="inlineStr"/>
       <c r="E1382" t="n">
-        <v>17900</v>
+        <v>4400</v>
       </c>
       <c r="F1382" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="G1382" t="n">
         <v>0</v>
@@ -74106,25 +74098,25 @@
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>ICE POWER 30 GR GEL COSMETICA</t>
+          <t>Ibuprofeno 800mg AG</t>
         </is>
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>737186238889</t>
+          <t>7706569000385</t>
         </is>
       </c>
       <c r="D1383" t="inlineStr"/>
       <c r="E1383" t="n">
-        <v>12521.008403</v>
+        <v>800</v>
       </c>
       <c r="F1383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1383" t="n">
         <v>0</v>
@@ -74152,7 +74144,7 @@
       </c>
       <c r="M1383" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1383" t="inlineStr"/>
@@ -74160,21 +74152,25 @@
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
-        </is>
-      </c>
-      <c r="C1384" t="inlineStr"/>
+          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>7705959885229</t>
+        </is>
+      </c>
       <c r="D1384" t="inlineStr"/>
       <c r="E1384" t="n">
-        <v>38900</v>
+        <v>17900</v>
       </c>
       <c r="F1384" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1384" t="n">
         <v>0</v>
@@ -74210,21 +74206,25 @@
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
-        </is>
-      </c>
-      <c r="C1385" t="inlineStr"/>
+          <t>ICE POWER 30 GR GEL COSMETICA</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>737186238889</t>
+        </is>
+      </c>
       <c r="D1385" t="inlineStr"/>
       <c r="E1385" t="n">
-        <v>38900</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1385" t="n">
         <v>0</v>
@@ -74252,7 +74252,7 @@
       </c>
       <c r="M1385" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1385" t="inlineStr"/>
@@ -74260,21 +74260,21 @@
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
+          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
         </is>
       </c>
       <c r="C1386" t="inlineStr"/>
       <c r="D1386" t="inlineStr"/>
       <c r="E1386" t="n">
-        <v>8235.294118</v>
+        <v>38900</v>
       </c>
       <c r="F1386" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1386" t="n">
         <v>0</v>
@@ -74302,7 +74302,7 @@
       </c>
       <c r="M1386" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1386" t="inlineStr"/>
@@ -74310,18 +74310,18 @@
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
+          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr"/>
       <c r="D1387" t="inlineStr"/>
       <c r="E1387" t="n">
-        <v>9831.932773</v>
+        <v>38900</v>
       </c>
       <c r="F1387" t="n">
         <v>1</v>
@@ -74352,7 +74352,7 @@
       </c>
       <c r="M1387" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1387" t="inlineStr"/>
@@ -74360,21 +74360,21 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>Jabon liquido manos mi dia</t>
+          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
         </is>
       </c>
       <c r="C1388" t="inlineStr"/>
       <c r="D1388" t="inlineStr"/>
       <c r="E1388" t="n">
-        <v>5882.352941</v>
+        <v>8235.294118</v>
       </c>
       <c r="F1388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1388" t="n">
         <v>0</v>
@@ -74410,21 +74410,21 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
+          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
         </is>
       </c>
       <c r="C1389" t="inlineStr"/>
       <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="n">
-        <v>4201.680672</v>
+        <v>9831.932773</v>
       </c>
       <c r="F1389" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1389" t="n">
         <v>0</v>
@@ -74460,18 +74460,18 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
+          <t>Jabon liquido manos mi dia</t>
         </is>
       </c>
       <c r="C1390" t="inlineStr"/>
       <c r="D1390" t="inlineStr"/>
       <c r="E1390" t="n">
-        <v>4201.680672</v>
+        <v>5882.352941</v>
       </c>
       <c r="F1390" t="n">
         <v>2</v>
@@ -74510,21 +74510,21 @@
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>JABON PROTEX HERBAL 110GR</t>
+          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
         </is>
       </c>
       <c r="C1391" t="inlineStr"/>
       <c r="D1391" t="inlineStr"/>
       <c r="E1391" t="n">
-        <v>4537.815126</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1391" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1391" t="n">
         <v>0</v>
@@ -74560,22 +74560,18 @@
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>JARABE ZETYGRIP FCO 60ML</t>
-        </is>
-      </c>
-      <c r="C1392" t="inlineStr">
-        <is>
-          <t>7709805542830</t>
-        </is>
-      </c>
+          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr"/>
       <c r="D1392" t="inlineStr"/>
       <c r="E1392" t="n">
-        <v>14000</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1392" t="n">
         <v>2</v>
@@ -74606,7 +74602,7 @@
       </c>
       <c r="M1392" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1392" t="inlineStr"/>
@@ -74614,21 +74610,21 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>JERINGA DE 50ML</t>
+          <t>JABON PROTEX HERBAL 110GR</t>
         </is>
       </c>
       <c r="C1393" t="inlineStr"/>
       <c r="D1393" t="inlineStr"/>
       <c r="E1393" t="n">
-        <v>2500</v>
+        <v>4537.815126</v>
       </c>
       <c r="F1393" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1393" t="n">
         <v>0</v>
@@ -74656,7 +74652,7 @@
       </c>
       <c r="M1393" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1393" t="inlineStr"/>
@@ -74664,21 +74660,25 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>Jeringa desechable estéril 20ml impormedicas</t>
-        </is>
-      </c>
-      <c r="C1394" t="inlineStr"/>
+          <t>JARABE ZETYGRIP FCO 60ML</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>7709805542830</t>
+        </is>
+      </c>
       <c r="D1394" t="inlineStr"/>
       <c r="E1394" t="n">
-        <v>920</v>
+        <v>14000</v>
       </c>
       <c r="F1394" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G1394" t="n">
         <v>0</v>
@@ -74706,7 +74706,7 @@
       </c>
       <c r="M1394" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1394" t="inlineStr"/>
@@ -74714,21 +74714,21 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
+          <t>JERINGA DE 50ML</t>
         </is>
       </c>
       <c r="C1395" t="inlineStr"/>
       <c r="D1395" t="inlineStr"/>
       <c r="E1395" t="n">
-        <v>1100</v>
+        <v>2500</v>
       </c>
       <c r="F1395" t="n">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="G1395" t="n">
         <v>0</v>
@@ -74764,21 +74764,21 @@
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>Kelocate</t>
+          <t>Jeringa desechable estéril 20ml impormedicas</t>
         </is>
       </c>
       <c r="C1396" t="inlineStr"/>
       <c r="D1396" t="inlineStr"/>
       <c r="E1396" t="n">
-        <v>180000</v>
+        <v>920</v>
       </c>
       <c r="F1396" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G1396" t="n">
         <v>0</v>
@@ -74806,7 +74806,7 @@
       </c>
       <c r="M1396" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1396" t="inlineStr"/>
@@ -74814,25 +74814,21 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
-        </is>
-      </c>
-      <c r="C1397" t="inlineStr">
-        <is>
-          <t>7702057073695</t>
-        </is>
-      </c>
+          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr"/>
       <c r="D1397" t="inlineStr"/>
       <c r="E1397" t="n">
-        <v>19500</v>
+        <v>1100</v>
       </c>
       <c r="F1397" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G1397" t="n">
         <v>0</v>
@@ -74868,22 +74864,18 @@
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
-        </is>
-      </c>
-      <c r="C1398" t="inlineStr">
-        <is>
-          <t>7709947559772</t>
-        </is>
-      </c>
+          <t>Kelocate</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr"/>
       <c r="D1398" t="inlineStr"/>
       <c r="E1398" t="n">
-        <v>15000</v>
+        <v>180000</v>
       </c>
       <c r="F1398" t="n">
         <v>0</v>
@@ -74922,18 +74914,22 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
-        </is>
-      </c>
-      <c r="C1399" t="inlineStr"/>
+          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>7702057073695</t>
+        </is>
+      </c>
       <c r="D1399" t="inlineStr"/>
       <c r="E1399" t="n">
-        <v>71000</v>
+        <v>19500</v>
       </c>
       <c r="F1399" t="n">
         <v>0</v>
@@ -74972,21 +74968,25 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
-        </is>
-      </c>
-      <c r="C1400" t="inlineStr"/>
+          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>7709947559772</t>
+        </is>
+      </c>
       <c r="D1400" t="inlineStr"/>
       <c r="E1400" t="n">
-        <v>37900</v>
+        <v>15000</v>
       </c>
       <c r="F1400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1400" t="n">
         <v>0</v>
@@ -75022,25 +75022,21 @@
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>Levotiroxina 100mcg MK</t>
-        </is>
-      </c>
-      <c r="C1401" t="inlineStr">
-        <is>
-          <t>7702057715908</t>
-        </is>
-      </c>
+          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr"/>
       <c r="D1401" t="inlineStr"/>
       <c r="E1401" t="n">
-        <v>27900</v>
+        <v>71000</v>
       </c>
       <c r="F1401" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1401" t="n">
         <v>0</v>
@@ -75076,18 +75072,18 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>LIMA MAYOMI 10/180</t>
+          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
         </is>
       </c>
       <c r="C1402" t="inlineStr"/>
       <c r="D1402" t="inlineStr"/>
       <c r="E1402" t="n">
-        <v>3900</v>
+        <v>37900</v>
       </c>
       <c r="F1402" t="n">
         <v>1</v>
@@ -75126,21 +75122,25 @@
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
-        </is>
-      </c>
-      <c r="C1403" t="inlineStr"/>
+          <t>Levotiroxina 100mcg MK</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>7702057715908</t>
+        </is>
+      </c>
       <c r="D1403" t="inlineStr"/>
       <c r="E1403" t="n">
-        <v>16807</v>
+        <v>27900</v>
       </c>
       <c r="F1403" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1403" t="n">
         <v>0</v>
@@ -75168,7 +75168,7 @@
       </c>
       <c r="M1403" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1403" t="inlineStr"/>
@@ -75176,18 +75176,18 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
+          <t>LIMA MAYOMI 10/180</t>
         </is>
       </c>
       <c r="C1404" t="inlineStr"/>
       <c r="D1404" t="inlineStr"/>
       <c r="E1404" t="n">
-        <v>15042.016807</v>
+        <v>3900</v>
       </c>
       <c r="F1404" t="n">
         <v>1</v>
@@ -75218,7 +75218,7 @@
       </c>
       <c r="M1404" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1404" t="inlineStr"/>
@@ -75226,21 +75226,21 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>LISTERINE CUIDADO TOTAL 180ML</t>
+          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
         </is>
       </c>
       <c r="C1405" t="inlineStr"/>
       <c r="D1405" t="inlineStr"/>
       <c r="E1405" t="n">
-        <v>16386.554622</v>
+        <v>16807</v>
       </c>
       <c r="F1405" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1405" t="n">
         <v>0</v>
@@ -75276,21 +75276,21 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
+          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
         </is>
       </c>
       <c r="C1406" t="inlineStr"/>
       <c r="D1406" t="inlineStr"/>
       <c r="E1406" t="n">
-        <v>3500</v>
+        <v>15042.016807</v>
       </c>
       <c r="F1406" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G1406" t="n">
         <v>0</v>
@@ -75318,7 +75318,7 @@
       </c>
       <c r="M1406" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1406" t="inlineStr"/>
@@ -75326,21 +75326,21 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+          <t>LISTERINE CUIDADO TOTAL 180ML</t>
         </is>
       </c>
       <c r="C1407" t="inlineStr"/>
       <c r="D1407" t="inlineStr"/>
       <c r="E1407" t="n">
-        <v>3500</v>
+        <v>16386.554622</v>
       </c>
       <c r="F1407" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1407" t="n">
         <v>0</v>
@@ -75368,7 +75368,7 @@
       </c>
       <c r="M1407" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1407" t="inlineStr"/>
@@ -75376,21 +75376,21 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
         </is>
       </c>
       <c r="C1408" t="inlineStr"/>
       <c r="D1408" t="inlineStr"/>
       <c r="E1408" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="F1408" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="G1408" t="n">
         <v>0</v>
@@ -75426,22 +75426,18 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>Losartan Tensofar 100 Mg</t>
-        </is>
-      </c>
-      <c r="C1409" t="inlineStr">
-        <is>
-          <t>7703546012119</t>
-        </is>
-      </c>
+          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr"/>
       <c r="D1409" t="inlineStr"/>
       <c r="E1409" t="n">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="F1409" t="n">
         <v>1</v>
@@ -75480,25 +75476,21 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
-        </is>
-      </c>
-      <c r="C1410" t="inlineStr">
-        <is>
-          <t>7501007528939</t>
-        </is>
-      </c>
+          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr"/>
       <c r="D1410" t="inlineStr"/>
       <c r="E1410" t="n">
-        <v>18907.563025</v>
+        <v>4500</v>
       </c>
       <c r="F1410" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1410" t="n">
         <v>0</v>
@@ -75526,7 +75518,7 @@
       </c>
       <c r="M1410" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1410" t="inlineStr"/>
@@ -75534,21 +75526,25 @@
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>MANTECA DE CACAO LABIAL LIMON</t>
-        </is>
-      </c>
-      <c r="C1411" t="inlineStr"/>
+          <t>Losartan Tensofar 100 Mg</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>7703546012119</t>
+        </is>
+      </c>
       <c r="D1411" t="inlineStr"/>
       <c r="E1411" t="n">
-        <v>3361.344538</v>
+        <v>5000</v>
       </c>
       <c r="F1411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1411" t="n">
         <v>0</v>
@@ -75576,7 +75572,7 @@
       </c>
       <c r="M1411" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1411" t="inlineStr"/>
@@ -75584,18 +75580,22 @@
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
-        </is>
-      </c>
-      <c r="C1412" t="inlineStr"/>
+          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>7501007528939</t>
+        </is>
+      </c>
       <c r="D1412" t="inlineStr"/>
       <c r="E1412" t="n">
-        <v>3361.344538</v>
+        <v>18907.563025</v>
       </c>
       <c r="F1412" t="n">
         <v>0</v>
@@ -75634,21 +75634,21 @@
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>Mega sex</t>
+          <t>MANTECA DE CACAO LABIAL LIMON</t>
         </is>
       </c>
       <c r="C1413" t="inlineStr"/>
       <c r="D1413" t="inlineStr"/>
       <c r="E1413" t="n">
-        <v>3200</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1413" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G1413" t="n">
         <v>0</v>
@@ -75676,7 +75676,7 @@
       </c>
       <c r="M1413" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1413" t="inlineStr"/>
@@ -75684,26 +75684,18 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>Melatonina 3mg</t>
-        </is>
-      </c>
-      <c r="C1414" t="inlineStr">
-        <is>
-          <t>7706849112906</t>
-        </is>
-      </c>
-      <c r="D1414" t="inlineStr">
-        <is>
-          <t>producto nuevo</t>
-        </is>
-      </c>
+          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr"/>
+      <c r="D1414" t="inlineStr"/>
       <c r="E1414" t="n">
-        <v>52000</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1414" t="n">
         <v>0</v>
@@ -75734,7 +75726,7 @@
       </c>
       <c r="M1414" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1414" t="inlineStr"/>
@@ -75742,25 +75734,21 @@
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
-        </is>
-      </c>
-      <c r="C1415" t="inlineStr">
-        <is>
-          <t>7707529435209</t>
-        </is>
-      </c>
+          <t>Mega sex</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr"/>
       <c r="D1415" t="inlineStr"/>
       <c r="E1415" t="n">
-        <v>36000</v>
+        <v>3200</v>
       </c>
       <c r="F1415" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G1415" t="n">
         <v>0</v>
@@ -75796,22 +75784,26 @@
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>Meloxicam 15mg AG</t>
+          <t>Melatonina 3mg</t>
         </is>
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>7706569020437</t>
-        </is>
-      </c>
-      <c r="D1416" t="inlineStr"/>
+          <t>7706849112906</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>producto nuevo</t>
+        </is>
+      </c>
       <c r="E1416" t="n">
-        <v>1500</v>
+        <v>52000</v>
       </c>
       <c r="F1416" t="n">
         <v>0</v>
@@ -75850,21 +75842,25 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
-        </is>
-      </c>
-      <c r="C1417" t="inlineStr"/>
+          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>7707529435209</t>
+        </is>
+      </c>
       <c r="D1417" t="inlineStr"/>
       <c r="E1417" t="n">
-        <v>9700</v>
+        <v>36000</v>
       </c>
       <c r="F1417" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1417" t="n">
         <v>0</v>
@@ -75900,22 +75896,22 @@
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>MELOXICAM COASPHARMA</t>
+          <t>Meloxicam 15mg AG</t>
         </is>
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>7703712036253</t>
+          <t>7706569020437</t>
         </is>
       </c>
       <c r="D1418" t="inlineStr"/>
       <c r="E1418" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F1418" t="n">
         <v>0</v>
@@ -75944,31 +75940,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1418" t="inlineStr"/>
+      <c r="M1418" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1418" t="inlineStr"/>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>metformina 850 mg pisa</t>
-        </is>
-      </c>
-      <c r="C1419" t="inlineStr">
-        <is>
-          <t>7501125188039</t>
-        </is>
-      </c>
+          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr"/>
       <c r="D1419" t="inlineStr"/>
       <c r="E1419" t="n">
-        <v>5500</v>
+        <v>9700</v>
       </c>
       <c r="F1419" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G1419" t="n">
         <v>0</v>
@@ -76004,25 +76000,25 @@
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10MG RECIPE</t>
+          <t>MELOXICAM COASPHARMA</t>
         </is>
       </c>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>7702195084355</t>
+          <t>7703712036253</t>
         </is>
       </c>
       <c r="D1420" t="inlineStr"/>
       <c r="E1420" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="F1420" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1420" t="n">
         <v>0</v>
@@ -76048,35 +76044,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1420" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1420" t="inlineStr"/>
       <c r="N1420" t="inlineStr"/>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>MICROPOR 1X3 Y</t>
+          <t>metformina 850 mg pisa</t>
         </is>
       </c>
       <c r="C1421" t="inlineStr">
         <is>
-          <t>7707282990205</t>
+          <t>7501125188039</t>
         </is>
       </c>
       <c r="D1421" t="inlineStr"/>
       <c r="E1421" t="n">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="F1421" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G1421" t="n">
         <v>0</v>
@@ -76112,25 +76104,21 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>MICROPOR CINTA 1/2X5Y</t>
-        </is>
-      </c>
-      <c r="C1422" t="inlineStr">
-        <is>
-          <t>7707282990182</t>
-        </is>
-      </c>
+          <t>METOCARBAMOL 750MG SOBRE X 1O TBL LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr"/>
       <c r="D1422" t="inlineStr"/>
       <c r="E1422" t="n">
-        <v>3900</v>
+        <v>13700</v>
       </c>
       <c r="F1422" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G1422" t="n">
         <v>0</v>
@@ -76166,21 +76154,25 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>MICROPORE COLOR PIEL 2YARDAS</t>
-        </is>
-      </c>
-      <c r="C1423" t="inlineStr"/>
+          <t>METOCLOPRAMIDA 10MG RECIPE</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>7702195084355</t>
+        </is>
+      </c>
       <c r="D1423" t="inlineStr"/>
       <c r="E1423" t="n">
-        <v>3700</v>
+        <v>1000</v>
       </c>
       <c r="F1423" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1423" t="n">
         <v>0</v>
@@ -76216,21 +76208,25 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
-        </is>
-      </c>
-      <c r="C1424" t="inlineStr"/>
+          <t>MICROPOR 1X3 Y</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>7707282990205</t>
+        </is>
+      </c>
       <c r="D1424" t="inlineStr"/>
       <c r="E1424" t="n">
-        <v>4000</v>
+        <v>5300</v>
       </c>
       <c r="F1424" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1424" t="n">
         <v>0</v>
@@ -76266,25 +76262,25 @@
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>MIELTERTOS JARABE X 240ML</t>
+          <t>MICROPOR CINTA 1/2X5Y</t>
         </is>
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>7707232095608</t>
+          <t>7707282990182</t>
         </is>
       </c>
       <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="n">
-        <v>34500</v>
+        <v>3900</v>
       </c>
       <c r="F1425" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G1425" t="n">
         <v>0</v>
@@ -76320,21 +76316,21 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>MOÑA CAUCHO TELEFONO</t>
+          <t>MICROPORE COLOR PIEL 2YARDAS</t>
         </is>
       </c>
       <c r="C1426" t="inlineStr"/>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="n">
-        <v>5000</v>
+        <v>3700</v>
       </c>
       <c r="F1426" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1426" t="n">
         <v>0</v>
@@ -76370,18 +76366,18 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>MOÑAS PARA EL PELO COLOR YIMEIJIA</t>
+          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
         </is>
       </c>
       <c r="C1427" t="inlineStr"/>
       <c r="D1427" t="inlineStr"/>
       <c r="E1427" t="n">
-        <v>4201.680672</v>
+        <v>4000</v>
       </c>
       <c r="F1427" t="n">
         <v>0</v>
@@ -76412,7 +76408,7 @@
       </c>
       <c r="M1427" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1427" t="inlineStr"/>
@@ -76420,25 +76416,25 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
-        </is>
-      </c>
-      <c r="C1428" t="inlineStr"/>
-      <c r="D1428" t="inlineStr">
-        <is>
-          <t>subio precio hector</t>
-        </is>
-      </c>
+          <t>MIELTERTOS JARABE X 240ML</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>7707232095608</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr"/>
       <c r="E1428" t="n">
-        <v>22700</v>
+        <v>34500</v>
       </c>
       <c r="F1428" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1428" t="n">
         <v>0</v>
@@ -76474,21 +76470,21 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
+          <t>MOÑA CAUCHO TELEFONO</t>
         </is>
       </c>
       <c r="C1429" t="inlineStr"/>
       <c r="D1429" t="inlineStr"/>
       <c r="E1429" t="n">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="F1429" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G1429" t="n">
         <v>0</v>
@@ -76524,21 +76520,21 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>NEOSALDINA TABLETA X UND</t>
+          <t>MOÑAS PARA EL PELO COLOR YIMEIJIA</t>
         </is>
       </c>
       <c r="C1430" t="inlineStr"/>
       <c r="D1430" t="inlineStr"/>
       <c r="E1430" t="n">
-        <v>2500</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1430" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G1430" t="n">
         <v>0</v>
@@ -76566,7 +76562,7 @@
       </c>
       <c r="M1430" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1430" t="inlineStr"/>
@@ -76574,21 +76570,25 @@
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>NIFEDIPINO 30MG NOVAMED</t>
+          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
         </is>
       </c>
       <c r="C1431" t="inlineStr"/>
-      <c r="D1431" t="inlineStr"/>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>subio precio hector</t>
+        </is>
+      </c>
       <c r="E1431" t="n">
-        <v>19000</v>
+        <v>22700</v>
       </c>
       <c r="F1431" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1431" t="n">
         <v>0</v>
@@ -76624,21 +76624,21 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
+          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
         </is>
       </c>
       <c r="C1432" t="inlineStr"/>
       <c r="D1432" t="inlineStr"/>
       <c r="E1432" t="n">
-        <v>23000</v>
+        <v>5500</v>
       </c>
       <c r="F1432" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G1432" t="n">
         <v>0</v>
@@ -76674,21 +76674,21 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>NITOXIPAR X 6 TABLETAS</t>
+          <t>NEOSALDINA TABLETA X UND</t>
         </is>
       </c>
       <c r="C1433" t="inlineStr"/>
       <c r="D1433" t="inlineStr"/>
       <c r="E1433" t="n">
-        <v>24500</v>
+        <v>2500</v>
       </c>
       <c r="F1433" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G1433" t="n">
         <v>0</v>
@@ -76724,21 +76724,21 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>NORAVER SPRAY CEREZA 120ML</t>
+          <t>NIFEDIPINO 30MG NOVAMED</t>
         </is>
       </c>
       <c r="C1434" t="inlineStr"/>
       <c r="D1434" t="inlineStr"/>
       <c r="E1434" t="n">
-        <v>52900</v>
+        <v>19000</v>
       </c>
       <c r="F1434" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1434" t="n">
         <v>0</v>
@@ -76774,25 +76774,21 @@
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
-        </is>
-      </c>
-      <c r="C1435" t="inlineStr">
-        <is>
-          <t>7702027041662</t>
-        </is>
-      </c>
+          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr"/>
       <c r="D1435" t="inlineStr"/>
       <c r="E1435" t="n">
-        <v>6300</v>
+        <v>23000</v>
       </c>
       <c r="F1435" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>
@@ -76828,21 +76824,21 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+          <t>NITOXIPAR X 6 TABLETAS</t>
         </is>
       </c>
       <c r="C1436" t="inlineStr"/>
       <c r="D1436" t="inlineStr"/>
       <c r="E1436" t="n">
-        <v>8823.529412</v>
+        <v>24500</v>
       </c>
       <c r="F1436" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1436" t="n">
         <v>0</v>
@@ -76870,7 +76866,7 @@
       </c>
       <c r="M1436" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1436" t="inlineStr"/>
@@ -76878,25 +76874,21 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
-        </is>
-      </c>
-      <c r="C1437" t="inlineStr">
-        <is>
-          <t>7702026158644</t>
-        </is>
-      </c>
+          <t>NORAVER SPRAY CEREZA 120ML</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr"/>
       <c r="D1437" t="inlineStr"/>
       <c r="E1437" t="n">
-        <v>8823.529412</v>
+        <v>52900</v>
       </c>
       <c r="F1437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1437" t="n">
         <v>0</v>
@@ -76924,7 +76916,7 @@
       </c>
       <c r="M1437" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1437" t="inlineStr"/>
@@ -76932,25 +76924,25 @@
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JBE 120ML</t>
+          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
         </is>
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>7707355053363</t>
+          <t>7702027041662</t>
         </is>
       </c>
       <c r="D1438" t="inlineStr"/>
       <c r="E1438" t="n">
-        <v>22700</v>
+        <v>6300</v>
       </c>
       <c r="F1438" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1438" t="n">
         <v>0</v>
@@ -76986,22 +76978,18 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
-        </is>
-      </c>
-      <c r="C1439" t="inlineStr">
-        <is>
-          <t>7707355053356</t>
-        </is>
-      </c>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr"/>
       <c r="D1439" t="inlineStr"/>
       <c r="E1439" t="n">
-        <v>17200</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1439" t="n">
         <v>0</v>
@@ -77032,7 +77020,7 @@
       </c>
       <c r="M1439" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1439" t="inlineStr"/>
@@ -77040,21 +77028,25 @@
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>NUTRIBELL ACEITE DE COCO</t>
-        </is>
-      </c>
-      <c r="C1440" t="inlineStr"/>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>7702026158644</t>
+        </is>
+      </c>
       <c r="D1440" t="inlineStr"/>
       <c r="E1440" t="n">
-        <v>2700</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1440" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1440" t="n">
         <v>0</v>
@@ -77082,7 +77074,7 @@
       </c>
       <c r="M1440" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1440" t="inlineStr"/>
@@ -77090,29 +77082,25 @@
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>Omega 3 6 9 suplemento totalmax</t>
+          <t>NOXPIRIN JUNIOR JBE 120ML</t>
         </is>
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>7707529434974</t>
-        </is>
-      </c>
-      <c r="D1441" t="inlineStr">
-        <is>
-          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
-        </is>
-      </c>
+          <t>7707355053363</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr"/>
       <c r="E1441" t="n">
-        <v>35000</v>
+        <v>22700</v>
       </c>
       <c r="F1441" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1441" t="n">
         <v>0</v>
@@ -77148,18 +77136,22 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1442" t="inlineStr"/>
+          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>7707355053356</t>
+        </is>
+      </c>
       <c r="D1442" t="inlineStr"/>
       <c r="E1442" t="n">
-        <v>5500</v>
+        <v>17200</v>
       </c>
       <c r="F1442" t="n">
         <v>0</v>
@@ -77198,25 +77190,21 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
-        </is>
-      </c>
-      <c r="C1443" t="inlineStr">
-        <is>
-          <t>7707529435940</t>
-        </is>
-      </c>
+          <t>NUTRIBELL ACEITE DE COCO</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr"/>
       <c r="D1443" t="inlineStr"/>
       <c r="E1443" t="n">
-        <v>35000</v>
+        <v>2700</v>
       </c>
       <c r="F1443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1443" t="n">
         <v>0</v>
@@ -77252,21 +77240,29 @@
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
-        </is>
-      </c>
-      <c r="C1444" t="inlineStr"/>
-      <c r="D1444" t="inlineStr"/>
+          <t>Omega 3 6 9 suplemento totalmax</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>7707529434974</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
+        </is>
+      </c>
       <c r="E1444" t="n">
-        <v>48000</v>
+        <v>35000</v>
       </c>
       <c r="F1444" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1444" t="n">
         <v>0</v>
@@ -77302,25 +77298,21 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>OROCAL CALCIO 600MG</t>
+          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
         </is>
       </c>
       <c r="C1445" t="inlineStr"/>
-      <c r="D1445" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="D1445" t="inlineStr"/>
       <c r="E1445" t="n">
-        <v>30500</v>
+        <v>5500</v>
       </c>
       <c r="F1445" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1445" t="n">
         <v>0</v>
@@ -77356,21 +77348,25 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>PALA DE MADERA RASPACALLO</t>
-        </is>
-      </c>
-      <c r="C1446" t="inlineStr"/>
+          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>7707529435940</t>
+        </is>
+      </c>
       <c r="D1446" t="inlineStr"/>
       <c r="E1446" t="n">
-        <v>4000</v>
+        <v>35000</v>
       </c>
       <c r="F1446" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1446" t="n">
         <v>0</v>
@@ -77406,21 +77402,21 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>PALO DE NARANJO X UNIDAD</t>
+          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
         </is>
       </c>
       <c r="C1447" t="inlineStr"/>
       <c r="D1447" t="inlineStr"/>
       <c r="E1447" t="n">
-        <v>400</v>
+        <v>48000</v>
       </c>
       <c r="F1447" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G1447" t="n">
         <v>0</v>
@@ -77456,22 +77452,22 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
-        </is>
-      </c>
-      <c r="C1448" t="inlineStr">
-        <is>
-          <t>7704412170896</t>
-        </is>
-      </c>
-      <c r="D1448" t="inlineStr"/>
+          <t>OROCAL CALCIO 600MG</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr"/>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E1448" t="n">
-        <v>6200</v>
+        <v>30500</v>
       </c>
       <c r="F1448" t="n">
         <v>1</v>
@@ -77510,18 +77506,18 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
+          <t>PALA DE MADERA RASPACALLO</t>
         </is>
       </c>
       <c r="C1449" t="inlineStr"/>
       <c r="D1449" t="inlineStr"/>
       <c r="E1449" t="n">
-        <v>14285.714286</v>
+        <v>4000</v>
       </c>
       <c r="F1449" t="n">
         <v>1</v>
@@ -77552,7 +77548,7 @@
       </c>
       <c r="M1449" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1449" t="inlineStr"/>
@@ -77560,21 +77556,21 @@
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
+          <t>PALO DE NARANJO X UNIDAD</t>
         </is>
       </c>
       <c r="C1450" t="inlineStr"/>
       <c r="D1450" t="inlineStr"/>
       <c r="E1450" t="n">
-        <v>28991.596639</v>
+        <v>400</v>
       </c>
       <c r="F1450" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G1450" t="n">
         <v>0</v>
@@ -77602,7 +77598,7 @@
       </c>
       <c r="M1450" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1450" t="inlineStr"/>
@@ -77610,18 +77606,22 @@
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
-        </is>
-      </c>
-      <c r="C1451" t="inlineStr"/>
+          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>7704412170896</t>
+        </is>
+      </c>
       <c r="D1451" t="inlineStr"/>
       <c r="E1451" t="n">
-        <v>41176.470588</v>
+        <v>6200</v>
       </c>
       <c r="F1451" t="n">
         <v>1</v>
@@ -77652,7 +77652,7 @@
       </c>
       <c r="M1451" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1451" t="inlineStr"/>
@@ -77660,22 +77660,18 @@
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Pañales Winny Etapa 5 X PAQUETE</t>
-        </is>
-      </c>
-      <c r="C1452" t="inlineStr">
-        <is>
-          <t>7701021114174</t>
-        </is>
-      </c>
+          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr"/>
       <c r="D1452" t="inlineStr"/>
       <c r="E1452" t="n">
-        <v>41849</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1452" t="n">
         <v>1</v>
@@ -77714,21 +77710,21 @@
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>PAÑALWINNY ETA 5 X 16 UND</t>
+          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr"/>
       <c r="D1453" t="inlineStr"/>
       <c r="E1453" t="n">
-        <v>24369.747899</v>
+        <v>28991.596639</v>
       </c>
       <c r="F1453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1453" t="n">
         <v>0</v>
@@ -77764,21 +77760,21 @@
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>pañitos humedos pequeñin 100unidades</t>
+          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
         </is>
       </c>
       <c r="C1454" t="inlineStr"/>
       <c r="D1454" t="inlineStr"/>
       <c r="E1454" t="n">
-        <v>10925</v>
+        <v>41176.470588</v>
       </c>
       <c r="F1454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1454" t="n">
         <v>0</v>
@@ -77814,21 +77810,25 @@
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1455" t="inlineStr"/>
+          <t>Pañales Winny Etapa 5 X PAQUETE</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>7701021114174</t>
+        </is>
+      </c>
       <c r="D1455" t="inlineStr"/>
       <c r="E1455" t="n">
-        <v>14900</v>
+        <v>41849</v>
       </c>
       <c r="F1455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1455" t="n">
         <v>0</v>
@@ -77856,7 +77856,7 @@
       </c>
       <c r="M1455" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1455" t="inlineStr"/>
@@ -77864,21 +77864,21 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Panotil B x 8ML</t>
+          <t>PAÑALWINNY ETA 5 X 16 UND</t>
         </is>
       </c>
       <c r="C1456" t="inlineStr"/>
       <c r="D1456" t="inlineStr"/>
       <c r="E1456" t="n">
-        <v>26400</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1456" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1456" t="n">
         <v>0</v>
@@ -77906,7 +77906,7 @@
       </c>
       <c r="M1456" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1456" t="inlineStr"/>
@@ -77914,25 +77914,21 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>PANTENE ACONDICIONADOR</t>
-        </is>
-      </c>
-      <c r="C1457" t="inlineStr">
-        <is>
-          <t>7500435153683</t>
-        </is>
-      </c>
+          <t>pañitos humedos pequeñin 100unidades</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr"/>
       <c r="D1457" t="inlineStr"/>
       <c r="E1457" t="n">
-        <v>1500</v>
+        <v>10925</v>
       </c>
       <c r="F1457" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G1457" t="n">
         <v>0</v>
@@ -77960,7 +77956,7 @@
       </c>
       <c r="M1457" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1457" t="inlineStr"/>
@@ -77968,25 +77964,21 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>PARCHE ACNE FIGURAS</t>
-        </is>
-      </c>
-      <c r="C1458" t="inlineStr">
-        <is>
-          <t>6971622250767</t>
-        </is>
-      </c>
+          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr"/>
       <c r="D1458" t="inlineStr"/>
       <c r="E1458" t="n">
-        <v>5882.352941</v>
+        <v>14900</v>
       </c>
       <c r="F1458" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1458" t="n">
         <v>0</v>
@@ -78014,7 +78006,7 @@
       </c>
       <c r="M1458" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1458" t="inlineStr"/>
@@ -78022,21 +78014,21 @@
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Parche Ocular Colostol</t>
+          <t>Panotil B x 8ML</t>
         </is>
       </c>
       <c r="C1459" t="inlineStr"/>
       <c r="D1459" t="inlineStr"/>
       <c r="E1459" t="n">
-        <v>1300</v>
+        <v>26400</v>
       </c>
       <c r="F1459" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G1459" t="n">
         <v>0</v>
@@ -78072,21 +78064,25 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>PARCHE PARA EL ACNE</t>
-        </is>
-      </c>
-      <c r="C1460" t="inlineStr"/>
+          <t>PANTENE ACONDICIONADOR</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>7500435153683</t>
+        </is>
+      </c>
       <c r="D1460" t="inlineStr"/>
       <c r="E1460" t="n">
-        <v>7000</v>
+        <v>1500</v>
       </c>
       <c r="F1460" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G1460" t="n">
         <v>0</v>
@@ -78122,22 +78118,22 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
+          <t>PARCHE ACNE FIGURAS</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>7501033957413</t>
+          <t>6971622250767</t>
         </is>
       </c>
       <c r="D1461" t="inlineStr"/>
       <c r="E1461" t="n">
-        <v>10600</v>
+        <v>5882.352941</v>
       </c>
       <c r="F1461" t="n">
         <v>0</v>
@@ -78168,7 +78164,7 @@
       </c>
       <c r="M1461" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1461" t="inlineStr"/>
@@ -78176,29 +78172,21 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
-        </is>
-      </c>
-      <c r="C1462" t="inlineStr">
-        <is>
-          <t>7501033961557</t>
-        </is>
-      </c>
-      <c r="D1462" t="inlineStr">
-        <is>
-          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
-        </is>
-      </c>
+          <t>Parche Ocular Colostol</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr"/>
+      <c r="D1462" t="inlineStr"/>
       <c r="E1462" t="n">
-        <v>10900</v>
+        <v>1300</v>
       </c>
       <c r="F1462" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G1462" t="n">
         <v>0</v>
@@ -78234,29 +78222,21 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
-        </is>
-      </c>
-      <c r="C1463" t="inlineStr">
-        <is>
-          <t>7501033957376</t>
-        </is>
-      </c>
-      <c r="D1463" t="inlineStr">
-        <is>
-          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
-        </is>
-      </c>
+          <t>PARCHE PARA EL ACNE</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr"/>
+      <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="n">
-        <v>10900</v>
+        <v>7000</v>
       </c>
       <c r="F1463" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1463" t="n">
         <v>0</v>
@@ -78292,21 +78272,25 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>PEGANTE GLUE X 10GR X UND</t>
-        </is>
-      </c>
-      <c r="C1464" t="inlineStr"/>
+          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>7501033957413</t>
+        </is>
+      </c>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="n">
-        <v>2000</v>
+        <v>10600</v>
       </c>
       <c r="F1464" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1464" t="n">
         <v>0</v>
@@ -78342,21 +78326,29 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>PEINETA COLA DE RATON METALICA</t>
-        </is>
-      </c>
-      <c r="C1465" t="inlineStr"/>
-      <c r="D1465" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>7501033961557</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
+        </is>
+      </c>
       <c r="E1465" t="n">
-        <v>4700</v>
+        <v>10900</v>
       </c>
       <c r="F1465" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1465" t="n">
         <v>0</v>
@@ -78392,21 +78384,29 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>PERFILADORES DE CEJAS</t>
-        </is>
-      </c>
-      <c r="C1466" t="inlineStr"/>
-      <c r="D1466" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>7501033957376</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+        </is>
+      </c>
       <c r="E1466" t="n">
-        <v>3900</v>
+        <v>10900</v>
       </c>
       <c r="F1466" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1466" t="n">
         <v>0</v>
@@ -78442,21 +78442,21 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
+          <t>PEGANTE GLUE X 10GR X UND</t>
         </is>
       </c>
       <c r="C1467" t="inlineStr"/>
       <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="n">
-        <v>27983.193277</v>
+        <v>2000</v>
       </c>
       <c r="F1467" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1467" t="n">
         <v>0</v>
@@ -78484,7 +78484,7 @@
       </c>
       <c r="M1467" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1467" t="inlineStr"/>
@@ -78492,21 +78492,21 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>POPETAS SURTIDAS X UND</t>
+          <t>PEINETA COLA DE RATON METALICA</t>
         </is>
       </c>
       <c r="C1468" t="inlineStr"/>
       <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="n">
-        <v>2521.008403</v>
+        <v>4700</v>
       </c>
       <c r="F1468" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1468" t="n">
         <v>0</v>
@@ -78534,7 +78534,7 @@
       </c>
       <c r="M1468" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1468" t="inlineStr"/>
@@ -78542,21 +78542,21 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+          <t>PERFILADORES DE CEJAS</t>
         </is>
       </c>
       <c r="C1469" t="inlineStr"/>
       <c r="D1469" t="inlineStr"/>
       <c r="E1469" t="n">
-        <v>20500</v>
+        <v>3900</v>
       </c>
       <c r="F1469" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1469" t="n">
         <v>0</v>
@@ -78592,26 +78592,18 @@
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>privatos miel limon la francol 120ml</t>
-        </is>
-      </c>
-      <c r="C1470" t="inlineStr">
-        <is>
-          <t>7702207163948</t>
-        </is>
-      </c>
-      <c r="D1470" t="inlineStr">
-        <is>
-          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
-        </is>
-      </c>
+          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr"/>
+      <c r="D1470" t="inlineStr"/>
       <c r="E1470" t="n">
-        <v>35900</v>
+        <v>27983.193277</v>
       </c>
       <c r="F1470" t="n">
         <v>1</v>
@@ -78642,7 +78634,7 @@
       </c>
       <c r="M1470" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1470" t="inlineStr"/>
@@ -78650,21 +78642,21 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
+          <t>POPETAS SURTIDAS X UND</t>
         </is>
       </c>
       <c r="C1471" t="inlineStr"/>
       <c r="D1471" t="inlineStr"/>
       <c r="E1471" t="n">
-        <v>0</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1471" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1471" t="n">
         <v>0</v>
@@ -78700,21 +78692,21 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>PROTECTOR NOSOTRAS LARGOS</t>
+          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
         </is>
       </c>
       <c r="C1472" t="inlineStr"/>
       <c r="D1472" t="inlineStr"/>
       <c r="E1472" t="n">
-        <v>3700</v>
+        <v>20500</v>
       </c>
       <c r="F1472" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1472" t="n">
         <v>0</v>
@@ -78750,18 +78742,26 @@
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
-        </is>
-      </c>
-      <c r="C1473" t="inlineStr"/>
-      <c r="D1473" t="inlineStr"/>
+          <t>privatos miel limon la francol 120ml</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>7702207163948</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
+        </is>
+      </c>
       <c r="E1473" t="n">
-        <v>8900</v>
+        <v>35900</v>
       </c>
       <c r="F1473" t="n">
         <v>1</v>
@@ -78800,18 +78800,18 @@
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>778</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>Protector Solar Sunaid</t>
+          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
         </is>
       </c>
       <c r="C1474" t="inlineStr"/>
       <c r="D1474" t="inlineStr"/>
       <c r="E1474" t="n">
-        <v>158000</v>
+        <v>0</v>
       </c>
       <c r="F1474" t="n">
         <v>0</v>
@@ -78842,7 +78842,7 @@
       </c>
       <c r="M1474" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1474" t="inlineStr"/>
@@ -78850,25 +78850,21 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>Prueba de embarazo esfero</t>
-        </is>
-      </c>
-      <c r="C1475" t="inlineStr">
-        <is>
-          <t>7709299854228</t>
-        </is>
-      </c>
+          <t>PROTECTOR NOSOTRAS LARGOS</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr"/>
       <c r="D1475" t="inlineStr"/>
       <c r="E1475" t="n">
-        <v>16500</v>
+        <v>3700</v>
       </c>
       <c r="F1475" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1475" t="n">
         <v>0</v>
@@ -78904,25 +78900,21 @@
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Prueba de embarazo HCG cassette begut</t>
-        </is>
-      </c>
-      <c r="C1476" t="inlineStr">
-        <is>
-          <t>7707282990953</t>
-        </is>
-      </c>
+          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr"/>
       <c r="D1476" t="inlineStr"/>
       <c r="E1476" t="n">
         <v>8900</v>
       </c>
       <c r="F1476" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G1476" t="n">
         <v>0</v>
@@ -78958,21 +78950,21 @@
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>PUSHER METALICO</t>
+          <t>Protector Solar Sunaid</t>
         </is>
       </c>
       <c r="C1477" t="inlineStr"/>
       <c r="D1477" t="inlineStr"/>
       <c r="E1477" t="n">
-        <v>4300</v>
+        <v>158000</v>
       </c>
       <c r="F1477" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1477" t="n">
         <v>0</v>
@@ -79008,21 +79000,25 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
-        </is>
-      </c>
-      <c r="C1478" t="inlineStr"/>
+          <t>Prueba de embarazo esfero</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>7709299854228</t>
+        </is>
+      </c>
       <c r="D1478" t="inlineStr"/>
       <c r="E1478" t="n">
-        <v>17900</v>
+        <v>16500</v>
       </c>
       <c r="F1478" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1478" t="n">
         <v>0</v>
@@ -79058,25 +79054,25 @@
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>Recolector de orina granandina</t>
+          <t>Prueba de embarazo HCG cassette begut</t>
         </is>
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>7707233050590</t>
+          <t>7707282990953</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr"/>
       <c r="E1479" t="n">
-        <v>673</v>
+        <v>8900</v>
       </c>
       <c r="F1479" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G1479" t="n">
         <v>0</v>
@@ -79104,7 +79100,7 @@
       </c>
       <c r="M1479" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1479" t="inlineStr"/>
@@ -79112,21 +79108,21 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
+          <t>PUSHER METALICO</t>
         </is>
       </c>
       <c r="C1480" t="inlineStr"/>
       <c r="D1480" t="inlineStr"/>
       <c r="E1480" t="n">
-        <v>3820</v>
+        <v>4300</v>
       </c>
       <c r="F1480" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1480" t="n">
         <v>0</v>
@@ -79162,21 +79158,21 @@
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>RegistroManual - Registro manual</t>
+          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
         </is>
       </c>
       <c r="C1481" t="inlineStr"/>
       <c r="D1481" t="inlineStr"/>
       <c r="E1481" t="n">
-        <v>0</v>
+        <v>17900</v>
       </c>
       <c r="F1481" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1481" t="n">
         <v>0</v>
@@ -79204,7 +79200,7 @@
       </c>
       <c r="M1481" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1481" t="inlineStr"/>
@@ -79212,21 +79208,25 @@
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>REMOVEDOR DE ESMALTE 60CC</t>
-        </is>
-      </c>
-      <c r="C1482" t="inlineStr"/>
+          <t>Recolector de orina granandina</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>7707233050590</t>
+        </is>
+      </c>
       <c r="D1482" t="inlineStr"/>
       <c r="E1482" t="n">
-        <v>3500</v>
+        <v>673</v>
       </c>
       <c r="F1482" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G1482" t="n">
         <v>0</v>
@@ -79254,7 +79254,7 @@
       </c>
       <c r="M1482" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1482" t="inlineStr"/>
@@ -79262,25 +79262,21 @@
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
-        </is>
-      </c>
-      <c r="C1483" t="inlineStr">
-        <is>
-          <t>7591005981270</t>
-        </is>
-      </c>
+          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr"/>
       <c r="D1483" t="inlineStr"/>
       <c r="E1483" t="n">
-        <v>9500</v>
+        <v>3820</v>
       </c>
       <c r="F1483" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1483" t="n">
         <v>0</v>
@@ -79316,25 +79312,21 @@
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
-        </is>
-      </c>
-      <c r="C1484" t="inlineStr">
-        <is>
-          <t>7503051868245</t>
-        </is>
-      </c>
+          <t>RegistroManual - Registro manual</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr"/>
       <c r="D1484" t="inlineStr"/>
       <c r="E1484" t="n">
-        <v>20900</v>
+        <v>0</v>
       </c>
       <c r="F1484" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1484" t="n">
         <v>0</v>
@@ -79362,7 +79354,7 @@
       </c>
       <c r="M1484" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1484" t="inlineStr"/>
@@ -79370,25 +79362,21 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1MG X 20 TABL MK</t>
-        </is>
-      </c>
-      <c r="C1485" t="inlineStr">
-        <is>
-          <t>7702057079642</t>
-        </is>
-      </c>
+          <t>REMOVEDOR DE ESMALTE 60CC</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr"/>
       <c r="D1485" t="inlineStr"/>
       <c r="E1485" t="n">
-        <v>13000</v>
+        <v>3500</v>
       </c>
       <c r="F1485" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1485" t="n">
         <v>0</v>
@@ -79424,21 +79412,25 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>Ryaltris Spray Nasal 240 dosis</t>
-        </is>
-      </c>
-      <c r="C1486" t="inlineStr"/>
+          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>7591005981270</t>
+        </is>
+      </c>
       <c r="D1486" t="inlineStr"/>
       <c r="E1486" t="n">
-        <v>216400</v>
+        <v>9500</v>
       </c>
       <c r="F1486" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1486" t="n">
         <v>0</v>
@@ -79474,22 +79466,22 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
         </is>
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>7706849116676</t>
+          <t>7503051868245</t>
         </is>
       </c>
       <c r="D1487" t="inlineStr"/>
       <c r="E1487" t="n">
-        <v>31500</v>
+        <v>20900</v>
       </c>
       <c r="F1487" t="n">
         <v>1</v>
@@ -79528,21 +79520,25 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>SCOBIT PURGANTE 60GR</t>
-        </is>
-      </c>
-      <c r="C1488" t="inlineStr"/>
+          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>7702057079642</t>
+        </is>
+      </c>
       <c r="D1488" t="inlineStr"/>
       <c r="E1488" t="n">
-        <v>15238.095238</v>
+        <v>13000</v>
       </c>
       <c r="F1488" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1488" t="n">
         <v>0</v>
@@ -79570,7 +79566,7 @@
       </c>
       <c r="M1488" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1488" t="inlineStr"/>
@@ -79578,21 +79574,21 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
+          <t>Ryaltris Spray Nasal 240 dosis</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr"/>
       <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="n">
-        <v>6554.621849</v>
+        <v>216400</v>
       </c>
       <c r="F1489" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1489" t="n">
         <v>0</v>
@@ -79620,7 +79616,7 @@
       </c>
       <c r="M1489" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1489" t="inlineStr"/>
@@ -79628,25 +79624,25 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>SHAMPOO PANTENE COLAGENO</t>
+          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
         </is>
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>7500435191500</t>
+          <t>7706849116676</t>
         </is>
       </c>
       <c r="D1490" t="inlineStr"/>
       <c r="E1490" t="n">
-        <v>1429</v>
+        <v>31500</v>
       </c>
       <c r="F1490" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1490" t="n">
         <v>0</v>
@@ -79674,7 +79670,7 @@
       </c>
       <c r="M1490" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1490" t="inlineStr"/>
@@ -79682,21 +79678,21 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>SILDENAFIL 50MG TQ</t>
+          <t>SCOBIT PURGANTE 60GR</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr"/>
       <c r="D1491" t="inlineStr"/>
       <c r="E1491" t="n">
-        <v>5000</v>
+        <v>15238.095238</v>
       </c>
       <c r="F1491" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1491" t="n">
         <v>0</v>
@@ -79724,7 +79720,7 @@
       </c>
       <c r="M1491" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1491" t="inlineStr"/>
@@ -79732,25 +79728,21 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>SILIMARINA 167MG EPANAT</t>
-        </is>
-      </c>
-      <c r="C1492" t="inlineStr">
-        <is>
-          <t>7706849115921</t>
-        </is>
-      </c>
+          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr"/>
       <c r="D1492" t="inlineStr"/>
       <c r="E1492" t="n">
-        <v>2000</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1492" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G1492" t="n">
         <v>0</v>
@@ -79778,7 +79770,7 @@
       </c>
       <c r="M1492" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1492" t="inlineStr"/>
@@ -79786,21 +79778,25 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>SMECTA 3GR NARANJA S/B</t>
-        </is>
-      </c>
-      <c r="C1493" t="inlineStr"/>
+          <t>SHAMPOO PANTENE COLAGENO</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>7500435191500</t>
+        </is>
+      </c>
       <c r="D1493" t="inlineStr"/>
       <c r="E1493" t="n">
-        <v>8900</v>
+        <v>1429</v>
       </c>
       <c r="F1493" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1493" t="n">
         <v>0</v>
@@ -79828,7 +79824,7 @@
       </c>
       <c r="M1493" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1493" t="inlineStr"/>
@@ -79836,21 +79832,21 @@
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>SONDA FOLEY 2 VIAS BAL #18</t>
+          <t>SILDENAFIL 50MG TQ</t>
         </is>
       </c>
       <c r="C1494" t="inlineStr"/>
       <c r="D1494" t="inlineStr"/>
       <c r="E1494" t="n">
-        <v>7500</v>
+        <v>5000</v>
       </c>
       <c r="F1494" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1494" t="n">
         <v>0</v>
@@ -79886,21 +79882,25 @@
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>SONDA NELATON #6</t>
-        </is>
-      </c>
-      <c r="C1495" t="inlineStr"/>
+          <t>SILIMARINA 167MG EPANAT</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>7706849115921</t>
+        </is>
+      </c>
       <c r="D1495" t="inlineStr"/>
       <c r="E1495" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="F1495" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G1495" t="n">
         <v>0</v>
@@ -79936,21 +79936,21 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>SPRAY NASAL MOMETASONA 18ML</t>
+          <t>SMECTA 3GR NARANJA S/B</t>
         </is>
       </c>
       <c r="C1496" t="inlineStr"/>
       <c r="D1496" t="inlineStr"/>
       <c r="E1496" t="n">
-        <v>36900</v>
+        <v>8900</v>
       </c>
       <c r="F1496" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1496" t="n">
         <v>0</v>
@@ -79986,21 +79986,21 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>suerox mora azul x630ml</t>
+          <t>SONDA FOLEY 2 VIAS BAL #18</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr"/>
       <c r="D1497" t="inlineStr"/>
       <c r="E1497" t="n">
-        <v>5882.352941</v>
+        <v>7500</v>
       </c>
       <c r="F1497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1497" t="n">
         <v>0</v>
@@ -80028,7 +80028,7 @@
       </c>
       <c r="M1497" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1497" t="inlineStr"/>
@@ -80036,25 +80036,21 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1498" t="inlineStr">
-        <is>
-          <t>7703712035034</t>
-        </is>
-      </c>
+          <t>SONDA NELATON #6</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr"/>
       <c r="D1498" t="inlineStr"/>
       <c r="E1498" t="n">
-        <v>14800</v>
+        <v>2500</v>
       </c>
       <c r="F1498" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1498" t="n">
         <v>0</v>
@@ -80090,18 +80086,18 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
+          <t>SPRAY NASAL MOMETASONA 18ML</t>
         </is>
       </c>
       <c r="C1499" t="inlineStr"/>
       <c r="D1499" t="inlineStr"/>
       <c r="E1499" t="n">
-        <v>3781.512605</v>
+        <v>36900</v>
       </c>
       <c r="F1499" t="n">
         <v>1</v>
@@ -80132,7 +80128,7 @@
       </c>
       <c r="M1499" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1499" t="inlineStr"/>
@@ -80140,21 +80136,21 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
+          <t>suerox mora azul x630ml</t>
         </is>
       </c>
       <c r="C1500" t="inlineStr"/>
       <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="n">
-        <v>5210.084034</v>
+        <v>5882.352941</v>
       </c>
       <c r="F1500" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1500" t="n">
         <v>0</v>
@@ -80190,21 +80186,25 @@
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
-        </is>
-      </c>
-      <c r="C1501" t="inlineStr"/>
+          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>7703712035034</t>
+        </is>
+      </c>
       <c r="D1501" t="inlineStr"/>
       <c r="E1501" t="n">
-        <v>8319.327730999999</v>
+        <v>14800</v>
       </c>
       <c r="F1501" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1501" t="n">
         <v>0</v>
@@ -80232,7 +80232,7 @@
       </c>
       <c r="M1501" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1501" t="inlineStr"/>
@@ -80240,18 +80240,18 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>SULZINC SUSP X 80ML HUMAX</t>
+          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
         </is>
       </c>
       <c r="C1502" t="inlineStr"/>
       <c r="D1502" t="inlineStr"/>
       <c r="E1502" t="n">
-        <v>22400</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1502" t="n">
         <v>1</v>
@@ -80282,7 +80282,7 @@
       </c>
       <c r="M1502" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1502" t="inlineStr"/>
@@ -80290,21 +80290,21 @@
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>SUNDARK FPS 60 CON TAPA</t>
+          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
         </is>
       </c>
       <c r="C1503" t="inlineStr"/>
       <c r="D1503" t="inlineStr"/>
       <c r="E1503" t="n">
-        <v>3781.512605</v>
+        <v>5210.084034</v>
       </c>
       <c r="F1503" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G1503" t="n">
         <v>0</v>
@@ -80340,21 +80340,21 @@
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>Synthroid 125 mcg</t>
+          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
         </is>
       </c>
       <c r="C1504" t="inlineStr"/>
       <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="n">
-        <v>178000</v>
+        <v>8319.327730999999</v>
       </c>
       <c r="F1504" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1504" t="n">
         <v>0</v>
@@ -80382,7 +80382,7 @@
       </c>
       <c r="M1504" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1504" t="inlineStr"/>
@@ -80390,25 +80390,21 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>Talco medicado Neofungina 40gm</t>
-        </is>
-      </c>
-      <c r="C1505" t="inlineStr">
-        <is>
-          <t>7706142707106</t>
-        </is>
-      </c>
+          <t>SULTAMICILINA 375MG X10 TBL - COASPH</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr"/>
       <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="n">
-        <v>14900</v>
+        <v>48000</v>
       </c>
       <c r="F1505" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1505" t="n">
         <v>0</v>
@@ -80444,21 +80440,21 @@
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
+          <t>SULZINC SUSP X 80ML HUMAX</t>
         </is>
       </c>
       <c r="C1506" t="inlineStr"/>
       <c r="D1506" t="inlineStr"/>
       <c r="E1506" t="n">
-        <v>13300</v>
+        <v>22400</v>
       </c>
       <c r="F1506" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1506" t="n">
         <v>0</v>
@@ -80494,21 +80490,21 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
+          <t>SUNDARK FPS 60 CON TAPA</t>
         </is>
       </c>
       <c r="C1507" t="inlineStr"/>
       <c r="D1507" t="inlineStr"/>
       <c r="E1507" t="n">
-        <v>4874</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1507" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G1507" t="n">
         <v>0</v>
@@ -80544,21 +80540,21 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
+          <t>Synthroid 125 mcg</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr"/>
       <c r="D1508" t="inlineStr"/>
       <c r="E1508" t="n">
-        <v>28800</v>
+        <v>178000</v>
       </c>
       <c r="F1508" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1508" t="n">
         <v>0</v>
@@ -80594,21 +80590,25 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
-        </is>
-      </c>
-      <c r="C1509" t="inlineStr"/>
+          <t>Talco medicado Neofungina 40gm</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>7706142707106</t>
+        </is>
+      </c>
       <c r="D1509" t="inlineStr"/>
       <c r="E1509" t="n">
-        <v>11596.638655</v>
+        <v>14900</v>
       </c>
       <c r="F1509" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1509" t="n">
         <v>0</v>
@@ -80636,7 +80636,7 @@
       </c>
       <c r="M1509" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1509" t="inlineStr"/>
@@ -80644,21 +80644,21 @@
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>TIJERA DE DOBLAR METALICA</t>
+          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr"/>
       <c r="D1510" t="inlineStr"/>
       <c r="E1510" t="n">
-        <v>3500</v>
+        <v>13300</v>
       </c>
       <c r="F1510" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1510" t="n">
         <v>0</v>
@@ -80694,21 +80694,21 @@
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
         </is>
       </c>
       <c r="C1511" t="inlineStr"/>
       <c r="D1511" t="inlineStr"/>
       <c r="E1511" t="n">
-        <v>3781.512605</v>
+        <v>4874</v>
       </c>
       <c r="F1511" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G1511" t="n">
         <v>0</v>
@@ -80744,21 +80744,21 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
         </is>
       </c>
       <c r="C1512" t="inlineStr"/>
       <c r="D1512" t="inlineStr"/>
       <c r="E1512" t="n">
-        <v>29800</v>
+        <v>28800</v>
       </c>
       <c r="F1512" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1512" t="n">
         <v>0</v>
@@ -80794,22 +80794,18 @@
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
-        </is>
-      </c>
-      <c r="C1513" t="inlineStr">
-        <is>
-          <t>7702026149567</t>
-        </is>
-      </c>
+          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr"/>
       <c r="D1513" t="inlineStr"/>
       <c r="E1513" t="n">
-        <v>13500</v>
+        <v>11596.638655</v>
       </c>
       <c r="F1513" t="n">
         <v>2</v>
@@ -80840,7 +80836,7 @@
       </c>
       <c r="M1513" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1513" t="inlineStr"/>
@@ -80848,25 +80844,21 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>Toallas húmedas winny 24unidades</t>
-        </is>
-      </c>
-      <c r="C1514" t="inlineStr">
-        <is>
-          <t>7701021143655</t>
-        </is>
-      </c>
+          <t>TIJERA DE DOBLAR METALICA</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr"/>
       <c r="D1514" t="inlineStr"/>
       <c r="E1514" t="n">
-        <v>4033.613445</v>
+        <v>3500</v>
       </c>
       <c r="F1514" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G1514" t="n">
         <v>0</v>
@@ -80894,7 +80886,7 @@
       </c>
       <c r="M1514" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1514" t="inlineStr"/>
@@ -80902,25 +80894,21 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>Toallas maternas maternity</t>
-        </is>
-      </c>
-      <c r="C1515" t="inlineStr">
-        <is>
-          <t>7703252489526</t>
-        </is>
-      </c>
+          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr"/>
       <c r="D1515" t="inlineStr"/>
       <c r="E1515" t="n">
-        <v>16900</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1515" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1515" t="n">
         <v>0</v>
@@ -80948,7 +80936,7 @@
       </c>
       <c r="M1515" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1515" t="inlineStr"/>
@@ -80956,25 +80944,21 @@
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>Toallas Nosotras Rapigel x Und</t>
-        </is>
-      </c>
-      <c r="C1516" t="inlineStr">
-        <is>
-          <t>7702027416859</t>
-        </is>
-      </c>
+          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr"/>
       <c r="D1516" t="inlineStr"/>
       <c r="E1516" t="n">
-        <v>756.302521</v>
+        <v>29800</v>
       </c>
       <c r="F1516" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G1516" t="n">
         <v>0</v>
@@ -81002,7 +80986,7 @@
       </c>
       <c r="M1516" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1516" t="inlineStr"/>
@@ -81010,21 +80994,25 @@
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>TRAMADOL 50MG CAPSULA MP</t>
-        </is>
-      </c>
-      <c r="C1517" t="inlineStr"/>
+          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>7702026149567</t>
+        </is>
+      </c>
       <c r="D1517" t="inlineStr"/>
       <c r="E1517" t="n">
-        <v>1500</v>
+        <v>13500</v>
       </c>
       <c r="F1517" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G1517" t="n">
         <v>0</v>
@@ -81060,25 +81048,25 @@
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>Tramadol clorhidrato 100mg laquifar</t>
+          <t>Toallas húmedas winny 24unidades</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>7707019426977</t>
+          <t>7701021143655</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr"/>
       <c r="E1518" t="n">
-        <v>1600</v>
+        <v>4033.613445</v>
       </c>
       <c r="F1518" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G1518" t="n">
         <v>0</v>
@@ -81106,7 +81094,7 @@
       </c>
       <c r="M1518" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1518" t="inlineStr"/>
@@ -81114,21 +81102,25 @@
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>TRIGENTAX CREMA TBO X 20GR</t>
-        </is>
-      </c>
-      <c r="C1519" t="inlineStr"/>
+          <t>Toallas maternas maternity</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>7703252489526</t>
+        </is>
+      </c>
       <c r="D1519" t="inlineStr"/>
       <c r="E1519" t="n">
-        <v>33500</v>
+        <v>16900</v>
       </c>
       <c r="F1519" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1519" t="n">
         <v>0</v>
@@ -81164,21 +81156,25 @@
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
-        </is>
-      </c>
-      <c r="C1520" t="inlineStr"/>
+          <t>Toallas Nosotras Rapigel x Und</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>7702027416859</t>
+        </is>
+      </c>
       <c r="D1520" t="inlineStr"/>
       <c r="E1520" t="n">
-        <v>9000</v>
+        <v>756.302521</v>
       </c>
       <c r="F1520" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="G1520" t="n">
         <v>0</v>
@@ -81206,7 +81202,7 @@
       </c>
       <c r="M1520" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1520" t="inlineStr"/>
@@ -81214,21 +81210,21 @@
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
+          <t>TRAMADOL 50MG CAPSULA MP</t>
         </is>
       </c>
       <c r="C1521" t="inlineStr"/>
       <c r="D1521" t="inlineStr"/>
       <c r="E1521" t="n">
-        <v>10500</v>
+        <v>1500</v>
       </c>
       <c r="F1521" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G1521" t="n">
         <v>0</v>
@@ -81264,21 +81260,25 @@
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
-        </is>
-      </c>
-      <c r="C1522" t="inlineStr"/>
+          <t>Tramadol clorhidrato 100mg laquifar</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>7707019426977</t>
+        </is>
+      </c>
       <c r="D1522" t="inlineStr"/>
       <c r="E1522" t="n">
-        <v>10500</v>
+        <v>1600</v>
       </c>
       <c r="F1522" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G1522" t="n">
         <v>0</v>
@@ -81314,21 +81314,21 @@
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
+          <t>TRIGENTAX CREMA TBO X 20GR</t>
         </is>
       </c>
       <c r="C1523" t="inlineStr"/>
       <c r="D1523" t="inlineStr"/>
       <c r="E1523" t="n">
-        <v>18800</v>
+        <v>33500</v>
       </c>
       <c r="F1523" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1523" t="n">
         <v>0</v>
@@ -81364,21 +81364,21 @@
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
+          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
         </is>
       </c>
       <c r="C1524" t="inlineStr"/>
       <c r="D1524" t="inlineStr"/>
       <c r="E1524" t="n">
-        <v>13800</v>
+        <v>9000</v>
       </c>
       <c r="F1524" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1524" t="n">
         <v>0</v>
@@ -81414,21 +81414,21 @@
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
+          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
         </is>
       </c>
       <c r="C1525" t="inlineStr"/>
       <c r="D1525" t="inlineStr"/>
       <c r="E1525" t="n">
-        <v>7900</v>
+        <v>10500</v>
       </c>
       <c r="F1525" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1525" t="n">
         <v>0</v>
@@ -81464,21 +81464,21 @@
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>VASELINA FC X 200GR YOMA</t>
+          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
         </is>
       </c>
       <c r="C1526" t="inlineStr"/>
       <c r="D1526" t="inlineStr"/>
       <c r="E1526" t="n">
-        <v>12521.008403</v>
+        <v>10500</v>
       </c>
       <c r="F1526" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G1526" t="n">
         <v>0</v>
@@ -81506,7 +81506,7 @@
       </c>
       <c r="M1526" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1526" t="inlineStr"/>
@@ -81514,18 +81514,18 @@
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
+          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
         </is>
       </c>
       <c r="C1527" t="inlineStr"/>
       <c r="D1527" t="inlineStr"/>
       <c r="E1527" t="n">
-        <v>420.168067</v>
+        <v>18800</v>
       </c>
       <c r="F1527" t="n">
         <v>1</v>
@@ -81556,7 +81556,7 @@
       </c>
       <c r="M1527" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1527" t="inlineStr"/>
@@ -81564,25 +81564,21 @@
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
-        </is>
-      </c>
-      <c r="C1528" t="inlineStr">
-        <is>
-          <t>7708480649803</t>
-        </is>
-      </c>
+          <t>ULCEPAR (OMEPRAZOL 20MG) CAPS- COASPH</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr"/>
       <c r="D1528" t="inlineStr"/>
       <c r="E1528" t="n">
-        <v>28000</v>
+        <v>4200</v>
       </c>
       <c r="F1528" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G1528" t="n">
         <v>0</v>
@@ -81618,25 +81614,21 @@
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>Venda Elastica 6x5 y piel</t>
+          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
         </is>
       </c>
       <c r="C1529" t="inlineStr"/>
-      <c r="D1529" t="inlineStr">
-        <is>
-          <t>SUBIO A 6200 ANTES 5700</t>
-        </is>
-      </c>
+      <c r="D1529" t="inlineStr"/>
       <c r="E1529" t="n">
-        <v>6200</v>
+        <v>13800</v>
       </c>
       <c r="F1529" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1529" t="n">
         <v>0</v>
@@ -81672,18 +81664,18 @@
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
+          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
         </is>
       </c>
       <c r="C1530" t="inlineStr"/>
       <c r="D1530" t="inlineStr"/>
       <c r="E1530" t="n">
-        <v>5500</v>
+        <v>7900</v>
       </c>
       <c r="F1530" t="n">
         <v>2</v>
@@ -81722,18 +81714,18 @@
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>Venta simple</t>
+          <t>VASELINA FC X 200GR YOMA</t>
         </is>
       </c>
       <c r="C1531" t="inlineStr"/>
       <c r="D1531" t="inlineStr"/>
       <c r="E1531" t="n">
-        <v>0</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1531" t="n">
         <v>0</v>
@@ -81754,7 +81746,7 @@
       </c>
       <c r="K1531" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="L1531" t="inlineStr">
@@ -81762,27 +81754,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1531" t="inlineStr"/>
+      <c r="M1531" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
       <c r="N1531" t="inlineStr"/>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
+          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
         </is>
       </c>
       <c r="C1532" t="inlineStr"/>
       <c r="D1532" t="inlineStr"/>
       <c r="E1532" t="n">
-        <v>1000</v>
+        <v>420.168067</v>
       </c>
       <c r="F1532" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1532" t="n">
         <v>0</v>
@@ -81810,7 +81806,7 @@
       </c>
       <c r="M1532" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1532" t="inlineStr"/>
@@ -81818,25 +81814,25 @@
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
+          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
         </is>
       </c>
       <c r="C1533" t="inlineStr">
         <is>
-          <t>793969226467</t>
+          <t>7708480649803</t>
         </is>
       </c>
       <c r="D1533" t="inlineStr"/>
       <c r="E1533" t="n">
-        <v>17000</v>
+        <v>28000</v>
       </c>
       <c r="F1533" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1533" t="n">
         <v>0</v>
@@ -81859,7 +81855,7 @@
       </c>
       <c r="L1533" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="M1533" t="inlineStr">
@@ -81872,21 +81868,25 @@
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>VINO CEREBRAL JARABE X 1100ML</t>
+          <t>Venda Elastica 6x5 y piel</t>
         </is>
       </c>
       <c r="C1534" t="inlineStr"/>
-      <c r="D1534" t="inlineStr"/>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>SUBIO A 6200 ANTES 5700</t>
+        </is>
+      </c>
       <c r="E1534" t="n">
-        <v>48900</v>
+        <v>6200</v>
       </c>
       <c r="F1534" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1534" t="n">
         <v>0</v>
@@ -81922,21 +81922,21 @@
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>VIOXIN ENJUAGUE BUCAL 0.12% CLORH 120ML</t>
+          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
         </is>
       </c>
       <c r="C1535" t="inlineStr"/>
       <c r="D1535" t="inlineStr"/>
       <c r="E1535" t="n">
-        <v>22900</v>
+        <v>5500</v>
       </c>
       <c r="F1535" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1535" t="n">
         <v>0</v>
@@ -81972,21 +81972,21 @@
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
+          <t>Venta simple</t>
         </is>
       </c>
       <c r="C1536" t="inlineStr"/>
       <c r="D1536" t="inlineStr"/>
       <c r="E1536" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="F1536" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G1536" t="n">
         <v>0</v>
@@ -82004,7 +82004,7 @@
       </c>
       <c r="K1536" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="L1536" t="inlineStr">
@@ -82012,31 +82012,27 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1536" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1536" t="inlineStr"/>
       <c r="N1536" t="inlineStr"/>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
+          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
         </is>
       </c>
       <c r="C1537" t="inlineStr"/>
       <c r="D1537" t="inlineStr"/>
       <c r="E1537" t="n">
-        <v>5500</v>
+        <v>1000</v>
       </c>
       <c r="F1537" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G1537" t="n">
         <v>0</v>
@@ -82072,21 +82068,25 @@
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>WINNY PAÑAL ETP 6 X 30</t>
-        </is>
-      </c>
-      <c r="C1538" t="inlineStr"/>
+          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>793969226467</t>
+        </is>
+      </c>
       <c r="D1538" t="inlineStr"/>
       <c r="E1538" t="n">
-        <v>57000</v>
+        <v>17000</v>
       </c>
       <c r="F1538" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1538" t="n">
         <v>0</v>
@@ -82109,7 +82109,7 @@
       </c>
       <c r="L1538" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="M1538" t="inlineStr">
@@ -82122,52 +82122,302 @@
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>YODO BLANCO FC X30ML</t>
+          <t>VINO CEREBRAL JARABE X 1100ML</t>
         </is>
       </c>
       <c r="C1539" t="inlineStr"/>
       <c r="D1539" t="inlineStr"/>
       <c r="E1539" t="n">
+        <v>48900</v>
+      </c>
+      <c r="F1539" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1539" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1539" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1539" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1539" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1539" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1539" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1539" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1539" t="inlineStr"/>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>VIOXIN ENJUAGUE BUCAL 0.12% CLORH 120ML</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr"/>
+      <c r="D1540" t="inlineStr"/>
+      <c r="E1540" t="n">
+        <v>22900</v>
+      </c>
+      <c r="F1540" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1540" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1540" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1540" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1540" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1540" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1540" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1540" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1540" t="inlineStr"/>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr"/>
+      <c r="D1541" t="inlineStr"/>
+      <c r="E1541" t="n">
+        <v>5400</v>
+      </c>
+      <c r="F1541" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1541" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1541" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1541" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1541" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1541" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1541" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1541" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1541" t="inlineStr"/>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr"/>
+      <c r="D1542" t="inlineStr"/>
+      <c r="E1542" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F1542" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1542" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1542" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1542" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1542" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1542" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1542" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1542" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1542" t="inlineStr"/>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>WINNY PAÑAL ETP 6 X 30</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr"/>
+      <c r="D1543" t="inlineStr"/>
+      <c r="E1543" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F1543" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1543" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1543" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1543" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1543" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1543" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1543" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1543" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1543" t="inlineStr"/>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>YODO BLANCO FC X30ML</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr"/>
+      <c r="D1544" t="inlineStr"/>
+      <c r="E1544" t="n">
         <v>6000</v>
       </c>
-      <c r="F1539" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1539" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1539" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1539" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1539" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="K1539" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="L1539" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="M1539" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="N1539" t="inlineStr"/>
+      <c r="F1544" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1544" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1544" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1544" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1544" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1544" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1544" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1544" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1544" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -4853,7 +4853,7 @@
         <v>4500</v>
       </c>
       <c r="F84" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -31895,7 +31895,7 @@
         <v>3000</v>
       </c>
       <c r="F589" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G589" t="n">
         <v>0</v>
@@ -32659,7 +32659,7 @@
         <v>2200</v>
       </c>
       <c r="F603" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G603" t="n">
         <v>0</v>
@@ -42091,7 +42091,7 @@
         <v>3700</v>
       </c>
       <c r="F781" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G781" t="n">
         <v>0</v>
@@ -51357,7 +51357,7 @@
         <v>2200</v>
       </c>
       <c r="F954" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G954" t="n">
         <v>0</v>
@@ -58786,7 +58786,7 @@
         <v>2900</v>
       </c>
       <c r="F1092" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G1092" t="n">
         <v>0</v>
@@ -66334,7 +66334,7 @@
         <v>22000</v>
       </c>
       <c r="F1232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1232" t="n">
         <v>0</v>
@@ -66754,7 +66754,7 @@
         <v>14800</v>
       </c>
       <c r="F1240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1240" t="n">
         <v>0</v>
@@ -76480,7 +76480,7 @@
         <v>3700</v>
       </c>
       <c r="F1429" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1429" t="n">
         <v>0</v>
@@ -76788,7 +76788,7 @@
         <v>5500</v>
       </c>
       <c r="F1435" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -26477,7 +26477,7 @@
         <v>2100.84</v>
       </c>
       <c r="F488" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G488" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -3901,7 +3901,7 @@
         <v>5800</v>
       </c>
       <c r="F66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -5451,7 +5451,7 @@
         <v>5500</v>
       </c>
       <c r="F95" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -10329,7 +10329,7 @@
         <v>4000</v>
       </c>
       <c r="F186" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -14073,7 +14073,7 @@
         <v>672</v>
       </c>
       <c r="F256" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -14127,7 +14127,7 @@
         <v>840.336134</v>
       </c>
       <c r="F257" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -14879,7 +14879,7 @@
         <v>22200</v>
       </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G271" t="n">
         <v>0</v>
@@ -18593,7 +18593,7 @@
         <v>2600</v>
       </c>
       <c r="F340" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G340" t="n">
         <v>0</v>
@@ -20781,7 +20781,7 @@
         <v>9000</v>
       </c>
       <c r="F382" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G382" t="n">
         <v>0</v>
@@ -22791,7 +22791,7 @@
         <v>5000</v>
       </c>
       <c r="F419" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G419" t="n">
         <v>0</v>
@@ -23311,7 +23311,7 @@
         <v>1900</v>
       </c>
       <c r="F429" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G429" t="n">
         <v>0</v>
@@ -23415,7 +23415,7 @@
         <v>2000</v>
       </c>
       <c r="F431" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G431" t="n">
         <v>0</v>
@@ -23735,7 +23735,7 @@
         <v>2900</v>
       </c>
       <c r="F437" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G437" t="n">
         <v>0</v>
@@ -23847,7 +23847,7 @@
         <v>3300</v>
       </c>
       <c r="F439" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G439" t="n">
         <v>0</v>
@@ -24695,7 +24695,7 @@
         <v>4000</v>
       </c>
       <c r="F455" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G455" t="n">
         <v>0</v>
@@ -25031,7 +25031,7 @@
         <v>9200</v>
       </c>
       <c r="F461" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G461" t="n">
         <v>0</v>
@@ -29253,7 +29253,7 @@
         <v>18403.361345</v>
       </c>
       <c r="F540" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G540" t="n">
         <v>0</v>
@@ -34903,7 +34903,7 @@
         <v>1344.537815</v>
       </c>
       <c r="F645" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G645" t="n">
         <v>0</v>
@@ -48629,7 +48629,7 @@
         <v>3500</v>
       </c>
       <c r="F902" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G902" t="n">
         <v>0</v>
@@ -50321,7 +50321,7 @@
         <v>2300</v>
       </c>
       <c r="F934" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G934" t="n">
         <v>0</v>
@@ -55118,7 +55118,7 @@
         <v>3200</v>
       </c>
       <c r="F1024" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1024" t="n">
         <v>0</v>
@@ -59430,7 +59430,7 @@
         <v>9000</v>
       </c>
       <c r="F1104" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G1104" t="n">
         <v>0</v>
@@ -60672,7 +60672,7 @@
         <v>1900</v>
       </c>
       <c r="F1127" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G1127" t="n">
         <v>0</v>
@@ -71090,7 +71090,7 @@
         <v>33900</v>
       </c>
       <c r="F1324" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1324" t="n">
         <v>0</v>
@@ -71194,7 +71194,7 @@
         <v>20500</v>
       </c>
       <c r="F1326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1326" t="n">
         <v>0</v>
@@ -71856,7 +71856,7 @@
         <v>3000</v>
       </c>
       <c r="F1339" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1339" t="n">
         <v>0</v>
@@ -76788,7 +76788,7 @@
         <v>5500</v>
       </c>
       <c r="F1435" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -2687,7 +2687,7 @@
         <v>3277.310924</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -9419,7 +9419,7 @@
         <v>23200</v>
       </c>
       <c r="F169" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -17885,7 +17885,7 @@
         <v>1500</v>
       </c>
       <c r="F326" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G326" t="n">
         <v>0</v>
@@ -31567,7 +31567,7 @@
         <v>2600</v>
       </c>
       <c r="F583" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G583" t="n">
         <v>0</v>
@@ -31621,7 +31621,7 @@
         <v>2800</v>
       </c>
       <c r="F584" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G584" t="n">
         <v>0</v>
@@ -32659,7 +32659,7 @@
         <v>2200</v>
       </c>
       <c r="F603" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G603" t="n">
         <v>0</v>
@@ -33465,7 +33465,7 @@
         <v>1900</v>
       </c>
       <c r="F618" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G618" t="n">
         <v>0</v>
@@ -34417,7 +34417,7 @@
         <v>2800</v>
       </c>
       <c r="F636" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G636" t="n">
         <v>0</v>
@@ -79892,7 +79892,7 @@
         <v>6554.621849</v>
       </c>
       <c r="F1495" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1495" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -14717,7 +14717,7 @@
         <v>8900</v>
       </c>
       <c r="F268" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G268" t="n">
         <v>0</v>
@@ -22093,7 +22093,7 @@
         <v>14900</v>
       </c>
       <c r="F406" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G406" t="n">
         <v>0</v>
@@ -31351,7 +31351,7 @@
         <v>3400</v>
       </c>
       <c r="F579" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G579" t="n">
         <v>0</v>
@@ -31621,7 +31621,7 @@
         <v>2800</v>
       </c>
       <c r="F584" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G584" t="n">
         <v>0</v>
@@ -31895,7 +31895,7 @@
         <v>3000</v>
       </c>
       <c r="F589" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G589" t="n">
         <v>0</v>
@@ -32987,7 +32987,7 @@
         <v>3700</v>
       </c>
       <c r="F609" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G609" t="n">
         <v>0</v>
@@ -43623,7 +43623,7 @@
         <v>9500</v>
       </c>
       <c r="F809" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G809" t="n">
         <v>0</v>
@@ -45255,7 +45255,7 @@
         <v>6800</v>
       </c>
       <c r="F839" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G839" t="n">
         <v>0</v>
@@ -50321,7 +50321,7 @@
         <v>2300</v>
       </c>
       <c r="F934" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G934" t="n">
         <v>0</v>
@@ -50641,7 +50641,7 @@
         <v>4400</v>
       </c>
       <c r="F940" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G940" t="n">
         <v>0</v>
@@ -57078,7 +57078,7 @@
         <v>52000</v>
       </c>
       <c r="F1060" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1060" t="n">
         <v>0</v>
@@ -64888,7 +64888,7 @@
         <v>9300</v>
       </c>
       <c r="F1205" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1205" t="n">
         <v>0</v>
@@ -71806,7 +71806,7 @@
         <v>4700</v>
       </c>
       <c r="F1338" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1338" t="n">
         <v>0</v>
@@ -71856,7 +71856,7 @@
         <v>3000</v>
       </c>
       <c r="F1339" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G1339" t="n">
         <v>0</v>
@@ -76218,7 +76218,7 @@
         <v>5500</v>
       </c>
       <c r="F1424" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G1424" t="n">
         <v>0</v>
@@ -81099,16 +81099,16 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>TIZANIDINA 2MG ALERTADINA CJA X 20 TBL</t>
+          <t>TIZANIDINA 2MG ALERTADINA SOB X10 TBL</t>
         </is>
       </c>
       <c r="C1519" t="inlineStr"/>
       <c r="D1519" t="inlineStr"/>
       <c r="E1519" t="n">
-        <v>29800</v>
+        <v>18000</v>
       </c>
       <c r="F1519" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1519" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -82333,7 +82333,7 @@
       <c r="C1543" t="inlineStr"/>
       <c r="D1543" t="inlineStr"/>
       <c r="E1543" t="n">
-        <v>22900</v>
+        <v>24800</v>
       </c>
       <c r="F1543" t="n">
         <v>1</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -15431,7 +15431,7 @@
         <v>7800</v>
       </c>
       <c r="F281" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
@@ -16299,7 +16299,7 @@
         <v>13700</v>
       </c>
       <c r="F297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G297" t="n">
         <v>0</v>
@@ -17885,7 +17885,7 @@
         <v>1500</v>
       </c>
       <c r="F326" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G326" t="n">
         <v>0</v>
@@ -23415,7 +23415,7 @@
         <v>2000</v>
       </c>
       <c r="F431" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G431" t="n">
         <v>0</v>
@@ -23681,7 +23681,7 @@
         <v>2900</v>
       </c>
       <c r="F436" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G436" t="n">
         <v>0</v>
@@ -23735,7 +23735,7 @@
         <v>2900</v>
       </c>
       <c r="F437" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G437" t="n">
         <v>0</v>
@@ -24009,7 +24009,7 @@
         <v>17500</v>
       </c>
       <c r="F442" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G442" t="n">
         <v>0</v>
@@ -31953,7 +31953,7 @@
         <v>2500</v>
       </c>
       <c r="F590" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G590" t="n">
         <v>0</v>
@@ -32659,7 +32659,7 @@
         <v>2200</v>
       </c>
       <c r="F603" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G603" t="n">
         <v>0</v>
@@ -40211,7 +40211,7 @@
         <v>1260.504202</v>
       </c>
       <c r="F745" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G745" t="n">
         <v>0</v>
@@ -42311,7 +42311,7 @@
         <v>2000</v>
       </c>
       <c r="F785" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G785" t="n">
         <v>0</v>
@@ -43237,7 +43237,7 @@
         <v>17000</v>
       </c>
       <c r="F802" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G802" t="n">
         <v>0</v>
@@ -47021,7 +47021,7 @@
         <v>2700</v>
       </c>
       <c r="F872" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G872" t="n">
         <v>0</v>
@@ -47615,7 +47615,7 @@
         <v>1800</v>
       </c>
       <c r="F883" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G883" t="n">
         <v>0</v>
@@ -51357,7 +51357,7 @@
         <v>2200</v>
       </c>
       <c r="F954" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G954" t="n">
         <v>0</v>
@@ -52300,7 +52300,7 @@
         <v>13500</v>
       </c>
       <c r="F971" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G971" t="n">
         <v>0</v>
@@ -54856,7 +54856,7 @@
         <v>6900</v>
       </c>
       <c r="F1019" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1019" t="n">
         <v>0</v>
@@ -55770,7 +55770,7 @@
         <v>11000</v>
       </c>
       <c r="F1036" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1036" t="n">
         <v>0</v>
@@ -63738,7 +63738,7 @@
         <v>4000</v>
       </c>
       <c r="F1184" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G1184" t="n">
         <v>0</v>
@@ -63958,7 +63958,7 @@
         <v>15200</v>
       </c>
       <c r="F1188" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1188" t="n">
         <v>0</v>
@@ -64232,7 +64232,7 @@
         <v>4800</v>
       </c>
       <c r="F1193" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G1193" t="n">
         <v>0</v>
@@ -66908,7 +66908,7 @@
         <v>2200</v>
       </c>
       <c r="F1243" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G1243" t="n">
         <v>0</v>
@@ -74212,7 +74212,7 @@
         <v>4400</v>
       </c>
       <c r="F1385" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G1385" t="n">
         <v>0</v>
@@ -76788,7 +76788,7 @@
         <v>5500</v>
       </c>
       <c r="F1435" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>
@@ -78556,7 +78556,7 @@
         <v>10900</v>
       </c>
       <c r="F1469" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1469" t="n">
         <v>0</v>
@@ -82336,7 +82336,7 @@
         <v>24800</v>
       </c>
       <c r="F1543" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1543" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -4579,7 +4579,7 @@
         <v>3361.344538</v>
       </c>
       <c r="F79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -11797,7 +11797,7 @@
         <v>4800</v>
       </c>
       <c r="F214" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -23415,7 +23415,7 @@
         <v>2000</v>
       </c>
       <c r="F431" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G431" t="n">
         <v>0</v>
@@ -31953,7 +31953,7 @@
         <v>2500</v>
       </c>
       <c r="F590" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G590" t="n">
         <v>0</v>
@@ -32659,7 +32659,7 @@
         <v>2200</v>
       </c>
       <c r="F603" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G603" t="n">
         <v>0</v>
@@ -36957,7 +36957,7 @@
         <v>3277.310924</v>
       </c>
       <c r="F684" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G684" t="n">
         <v>0</v>
@@ -39509,7 +39509,7 @@
         <v>2800</v>
       </c>
       <c r="F732" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G732" t="n">
         <v>0</v>
@@ -42311,7 +42311,7 @@
         <v>2000</v>
       </c>
       <c r="F785" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G785" t="n">
         <v>0</v>
@@ -47021,7 +47021,7 @@
         <v>2700</v>
       </c>
       <c r="F872" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G872" t="n">
         <v>0</v>
@@ -59110,7 +59110,7 @@
         <v>28067.226891</v>
       </c>
       <c r="F1098" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1098" t="n">
         <v>0</v>
@@ -72318,7 +72318,7 @@
         <v>3500</v>
       </c>
       <c r="F1348" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1348" t="n">
         <v>0</v>
@@ -76788,7 +76788,7 @@
         <v>5500</v>
       </c>
       <c r="F1435" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>
@@ -82386,7 +82386,7 @@
         <v>5400</v>
       </c>
       <c r="F1544" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G1544" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -15534,9 +15534,13 @@
           <t>´7703038067566</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>SUBIO A 11500 ANTES 9800</t>
+        </is>
+      </c>
       <c r="E283" t="n">
-        <v>9800</v>
+        <v>11500</v>
       </c>
       <c r="F283" t="n">
         <v>7</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1547"/>
+  <dimension ref="A1:N1548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5451,7 +5451,7 @@
         <v>5500</v>
       </c>
       <c r="F95" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -9835,7 +9835,7 @@
         <v>8900</v>
       </c>
       <c r="F177" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -11519,7 +11519,7 @@
         <v>1500</v>
       </c>
       <c r="F209" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>16900</v>
       </c>
       <c r="F219" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -12291,7 +12291,7 @@
         <v>22500</v>
       </c>
       <c r="F223" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -13093,7 +13093,7 @@
         <v>2900</v>
       </c>
       <c r="F238" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -15543,7 +15543,7 @@
         <v>11500</v>
       </c>
       <c r="F283" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G283" t="n">
         <v>0</v>
@@ -17241,7 +17241,7 @@
         <v>6300</v>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G314" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>1500</v>
       </c>
       <c r="F326" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G326" t="n">
         <v>0</v>
@@ -20249,7 +20249,7 @@
         <v>16800</v>
       </c>
       <c r="F372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G372" t="n">
         <v>0</v>
@@ -20785,7 +20785,7 @@
         <v>9000</v>
       </c>
       <c r="F382" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G382" t="n">
         <v>0</v>
@@ -22247,7 +22247,7 @@
         <v>1500</v>
       </c>
       <c r="F409" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G409" t="n">
         <v>0</v>
@@ -24013,7 +24013,7 @@
         <v>17500</v>
       </c>
       <c r="F442" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G442" t="n">
         <v>0</v>
@@ -31409,7 +31409,7 @@
         <v>1200</v>
       </c>
       <c r="F580" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G580" t="n">
         <v>0</v>
@@ -31625,7 +31625,7 @@
         <v>2800</v>
       </c>
       <c r="F584" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G584" t="n">
         <v>0</v>
@@ -31957,7 +31957,7 @@
         <v>2500</v>
       </c>
       <c r="F590" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G590" t="n">
         <v>0</v>
@@ -32011,7 +32011,7 @@
         <v>25800</v>
       </c>
       <c r="F591" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G591" t="n">
         <v>0</v>
@@ -33099,7 +33099,7 @@
         <v>1600</v>
       </c>
       <c r="F611" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G611" t="n">
         <v>0</v>
@@ -35173,7 +35173,7 @@
         <v>3500</v>
       </c>
       <c r="F650" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G650" t="n">
         <v>0</v>
@@ -42315,7 +42315,7 @@
         <v>2000</v>
       </c>
       <c r="F785" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="G785" t="n">
         <v>0</v>
@@ -42427,7 +42427,7 @@
         <v>2300</v>
       </c>
       <c r="F787" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G787" t="n">
         <v>0</v>
@@ -43295,7 +43295,7 @@
         <v>6500</v>
       </c>
       <c r="F803" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G803" t="n">
         <v>0</v>
@@ -43407,7 +43407,7 @@
         <v>16500</v>
       </c>
       <c r="F805" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G805" t="n">
         <v>0</v>
@@ -46863,7 +46863,7 @@
         <v>4033.613445</v>
       </c>
       <c r="F869" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G869" t="n">
         <v>0</v>
@@ -47025,7 +47025,7 @@
         <v>2700</v>
       </c>
       <c r="F872" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="G872" t="n">
         <v>0</v>
@@ -50221,7 +50221,7 @@
         <v>2800</v>
       </c>
       <c r="F932" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G932" t="n">
         <v>0</v>
@@ -51361,7 +51361,7 @@
         <v>2200</v>
       </c>
       <c r="F954" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G954" t="n">
         <v>0</v>
@@ -55720,7 +55720,7 @@
         <v>3500</v>
       </c>
       <c r="F1035" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G1035" t="n">
         <v>0</v>
@@ -55774,7 +55774,7 @@
         <v>11000</v>
       </c>
       <c r="F1036" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1036" t="n">
         <v>0</v>
@@ -57884,7 +57884,7 @@
         <v>25900</v>
       </c>
       <c r="F1075" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1075" t="n">
         <v>0</v>
@@ -60074,7 +60074,7 @@
         <v>17300</v>
       </c>
       <c r="F1116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1116" t="n">
         <v>0</v>
@@ -65756,7 +65756,7 @@
         <v>7000</v>
       </c>
       <c r="F1221" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1221" t="n">
         <v>0</v>
@@ -66912,7 +66912,7 @@
         <v>2200</v>
       </c>
       <c r="F1243" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1243" t="n">
         <v>0</v>
@@ -67016,7 +67016,7 @@
         <v>4900</v>
       </c>
       <c r="F1245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1245" t="n">
         <v>0</v>
@@ -67066,7 +67066,7 @@
         <v>3800</v>
       </c>
       <c r="F1246" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G1246" t="n">
         <v>0</v>
@@ -71040,7 +71040,7 @@
         <v>28900</v>
       </c>
       <c r="F1323" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1323" t="n">
         <v>0</v>
@@ -72992,7 +72992,7 @@
         <v>3800</v>
       </c>
       <c r="F1361" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G1361" t="n">
         <v>0</v>
@@ -75544,7 +75544,7 @@
         <v>3500</v>
       </c>
       <c r="F1411" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1411" t="n">
         <v>0</v>
@@ -76792,7 +76792,7 @@
         <v>5500</v>
       </c>
       <c r="F1435" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>
@@ -80544,18 +80544,18 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>SULTAMICILINA 375MG X10 TBL - COASPH</t>
+          <t>SULFATO FERROSO JARABE 120ML LAPROFF</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr"/>
       <c r="D1508" t="inlineStr"/>
       <c r="E1508" t="n">
-        <v>48000</v>
+        <v>9500</v>
       </c>
       <c r="F1508" t="n">
         <v>1</v>
@@ -80594,18 +80594,18 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>SULZINC SUSP X 80ML HUMAX</t>
+          <t>SULTAMICILINA 375MG X10 TBL - COASPH</t>
         </is>
       </c>
       <c r="C1509" t="inlineStr"/>
       <c r="D1509" t="inlineStr"/>
       <c r="E1509" t="n">
-        <v>22400</v>
+        <v>48000</v>
       </c>
       <c r="F1509" t="n">
         <v>1</v>
@@ -80644,21 +80644,21 @@
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>SUNDARK FPS 60 CON TAPA</t>
+          <t>SULZINC SUSP X 80ML HUMAX</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr"/>
       <c r="D1510" t="inlineStr"/>
       <c r="E1510" t="n">
-        <v>3781.512605</v>
+        <v>22400</v>
       </c>
       <c r="F1510" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1510" t="n">
         <v>0</v>
@@ -80686,7 +80686,7 @@
       </c>
       <c r="M1510" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1510" t="inlineStr"/>
@@ -80694,21 +80694,21 @@
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>Synthroid 125 mcg</t>
+          <t>SUNDARK FPS 60 CON TAPA</t>
         </is>
       </c>
       <c r="C1511" t="inlineStr"/>
       <c r="D1511" t="inlineStr"/>
       <c r="E1511" t="n">
-        <v>178000</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1511" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1511" t="n">
         <v>0</v>
@@ -80736,7 +80736,7 @@
       </c>
       <c r="M1511" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1511" t="inlineStr"/>
@@ -80744,25 +80744,21 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>Talco medicado Neofungina 40gm</t>
-        </is>
-      </c>
-      <c r="C1512" t="inlineStr">
-        <is>
-          <t>7706142707106</t>
-        </is>
-      </c>
+          <t>Synthroid 125 mcg</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr"/>
       <c r="D1512" t="inlineStr"/>
       <c r="E1512" t="n">
-        <v>14900</v>
+        <v>178000</v>
       </c>
       <c r="F1512" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1512" t="n">
         <v>0</v>
@@ -80798,21 +80794,25 @@
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
-        </is>
-      </c>
-      <c r="C1513" t="inlineStr"/>
+          <t>Talco medicado Neofungina 40gm</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>7706142707106</t>
+        </is>
+      </c>
       <c r="D1513" t="inlineStr"/>
       <c r="E1513" t="n">
-        <v>13300</v>
+        <v>14900</v>
       </c>
       <c r="F1513" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1513" t="n">
         <v>0</v>
@@ -80848,21 +80848,21 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
+          <t>TENA MUJER MEDIUM TOALLA X10UND</t>
         </is>
       </c>
       <c r="C1514" t="inlineStr"/>
       <c r="D1514" t="inlineStr"/>
       <c r="E1514" t="n">
-        <v>4874</v>
+        <v>13300</v>
       </c>
       <c r="F1514" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G1514" t="n">
         <v>0</v>
@@ -80890,7 +80890,7 @@
       </c>
       <c r="M1514" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1514" t="inlineStr"/>
@@ -80898,21 +80898,21 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
+          <t>TENA PANTS CLASICO TALLA M X 8UND</t>
         </is>
       </c>
       <c r="C1515" t="inlineStr"/>
       <c r="D1515" t="inlineStr"/>
       <c r="E1515" t="n">
-        <v>28800</v>
+        <v>4874</v>
       </c>
       <c r="F1515" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G1515" t="n">
         <v>0</v>
@@ -80940,7 +80940,7 @@
       </c>
       <c r="M1515" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1515" t="inlineStr"/>
@@ -80948,21 +80948,21 @@
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
+          <t>TERBINAFINA TERBIFEET TUBO X 20 GR</t>
         </is>
       </c>
       <c r="C1516" t="inlineStr"/>
       <c r="D1516" t="inlineStr"/>
       <c r="E1516" t="n">
-        <v>11596.638655</v>
+        <v>28800</v>
       </c>
       <c r="F1516" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1516" t="n">
         <v>0</v>
@@ -80990,7 +80990,7 @@
       </c>
       <c r="M1516" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1516" t="inlineStr"/>
@@ -80998,21 +80998,21 @@
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>TIJERA DE DOBLAR METALICA</t>
+          <t>TETERO DOBLE MANIJA GRANDE 8 OZ AZUL</t>
         </is>
       </c>
       <c r="C1517" t="inlineStr"/>
       <c r="D1517" t="inlineStr"/>
       <c r="E1517" t="n">
-        <v>3500</v>
+        <v>11596.638655</v>
       </c>
       <c r="F1517" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1517" t="n">
         <v>0</v>
@@ -81040,7 +81040,7 @@
       </c>
       <c r="M1517" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1517" t="inlineStr"/>
@@ -81048,21 +81048,21 @@
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>TINTURA DE RUIBARDO FCO 30ML</t>
+          <t>TIJERA DE DOBLAR METALICA</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr"/>
       <c r="D1518" t="inlineStr"/>
       <c r="E1518" t="n">
-        <v>3781.512605</v>
+        <v>3500</v>
       </c>
       <c r="F1518" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1518" t="n">
         <v>0</v>
@@ -81090,7 +81090,7 @@
       </c>
       <c r="M1518" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1518" t="inlineStr"/>
@@ -81098,18 +81098,18 @@
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>TIZANIDINA 2MG ALERTADINA SOB X10 TBL</t>
+          <t>TINTURA DE RUIBARDO FCO 30ML</t>
         </is>
       </c>
       <c r="C1519" t="inlineStr"/>
       <c r="D1519" t="inlineStr"/>
       <c r="E1519" t="n">
-        <v>18000</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1519" t="n">
         <v>2</v>
@@ -81140,7 +81140,7 @@
       </c>
       <c r="M1519" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1519" t="inlineStr"/>
@@ -81148,22 +81148,18 @@
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
-        </is>
-      </c>
-      <c r="C1520" t="inlineStr">
-        <is>
-          <t>7702026149567</t>
-        </is>
-      </c>
+          <t>TIZANIDINA 2MG ALERTADINA SOB X10 TBL</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr"/>
       <c r="D1520" t="inlineStr"/>
       <c r="E1520" t="n">
-        <v>13500</v>
+        <v>18000</v>
       </c>
       <c r="F1520" t="n">
         <v>2</v>
@@ -81202,25 +81198,25 @@
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>Toallas húmedas winny 24unidades</t>
+          <t>TOA.NOSOTRAS BUENAS NOCHES X 10 UNDS</t>
         </is>
       </c>
       <c r="C1521" t="inlineStr">
         <is>
-          <t>7701021143655</t>
+          <t>7702026149567</t>
         </is>
       </c>
       <c r="D1521" t="inlineStr"/>
       <c r="E1521" t="n">
-        <v>4033.613445</v>
+        <v>13500</v>
       </c>
       <c r="F1521" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G1521" t="n">
         <v>0</v>
@@ -81248,7 +81244,7 @@
       </c>
       <c r="M1521" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1521" t="inlineStr"/>
@@ -81256,25 +81252,25 @@
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>Toallas maternas maternity</t>
+          <t>Toallas húmedas winny 24unidades</t>
         </is>
       </c>
       <c r="C1522" t="inlineStr">
         <is>
-          <t>7703252489526</t>
+          <t>7701021143655</t>
         </is>
       </c>
       <c r="D1522" t="inlineStr"/>
       <c r="E1522" t="n">
-        <v>16900</v>
+        <v>4033.613445</v>
       </c>
       <c r="F1522" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G1522" t="n">
         <v>0</v>
@@ -81302,7 +81298,7 @@
       </c>
       <c r="M1522" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1522" t="inlineStr"/>
@@ -81310,25 +81306,25 @@
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>Toallas Nosotras Rapigel x Und</t>
+          <t>Toallas maternas maternity</t>
         </is>
       </c>
       <c r="C1523" t="inlineStr">
         <is>
-          <t>7702027416859</t>
+          <t>7703252489526</t>
         </is>
       </c>
       <c r="D1523" t="inlineStr"/>
       <c r="E1523" t="n">
-        <v>756.302521</v>
+        <v>16900</v>
       </c>
       <c r="F1523" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="G1523" t="n">
         <v>0</v>
@@ -81356,7 +81352,7 @@
       </c>
       <c r="M1523" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1523" t="inlineStr"/>
@@ -81364,21 +81360,25 @@
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>TRAMADOL 50MG CAPSULA MP</t>
-        </is>
-      </c>
-      <c r="C1524" t="inlineStr"/>
+          <t>Toallas Nosotras Rapigel x Und</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>7702027416859</t>
+        </is>
+      </c>
       <c r="D1524" t="inlineStr"/>
       <c r="E1524" t="n">
-        <v>1500</v>
+        <v>756.302521</v>
       </c>
       <c r="F1524" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="G1524" t="n">
         <v>0</v>
@@ -81406,7 +81406,7 @@
       </c>
       <c r="M1524" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1524" t="inlineStr"/>
@@ -81414,25 +81414,21 @@
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Tramadol clorhidrato 100mg laquifar</t>
-        </is>
-      </c>
-      <c r="C1525" t="inlineStr">
-        <is>
-          <t>7707019426977</t>
-        </is>
-      </c>
+          <t>TRAMADOL 50MG CAPSULA MP</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr"/>
       <c r="D1525" t="inlineStr"/>
       <c r="E1525" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="F1525" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G1525" t="n">
         <v>0</v>
@@ -81468,18 +81464,22 @@
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>TRIGENTAX CREMA TBO X 20GR</t>
-        </is>
-      </c>
-      <c r="C1526" t="inlineStr"/>
+          <t>Tramadol clorhidrato 100mg laquifar</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>7707019426977</t>
+        </is>
+      </c>
       <c r="D1526" t="inlineStr"/>
       <c r="E1526" t="n">
-        <v>33500</v>
+        <v>1600</v>
       </c>
       <c r="F1526" t="n">
         <v>0</v>
@@ -81518,21 +81518,21 @@
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
+          <t>TRIGENTAX CREMA TBO X 20GR</t>
         </is>
       </c>
       <c r="C1527" t="inlineStr"/>
       <c r="D1527" t="inlineStr"/>
       <c r="E1527" t="n">
-        <v>9000</v>
+        <v>33500</v>
       </c>
       <c r="F1527" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1527" t="n">
         <v>0</v>
@@ -81568,21 +81568,21 @@
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
+          <t>TRIMEBUTINA 200MG TABLETA LAPROFF</t>
         </is>
       </c>
       <c r="C1528" t="inlineStr"/>
       <c r="D1528" t="inlineStr"/>
       <c r="E1528" t="n">
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="F1528" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1528" t="n">
         <v>0</v>
@@ -81618,12 +81618,12 @@
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
+          <t>TRIMEBUTINA 200MG X SOBRE DE 10 DE LA SANTE</t>
         </is>
       </c>
       <c r="C1529" t="inlineStr"/>
@@ -81632,7 +81632,7 @@
         <v>10500</v>
       </c>
       <c r="F1529" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G1529" t="n">
         <v>0</v>
@@ -81668,21 +81668,21 @@
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
+          <t>TRIMETOPRIM SULFA 160/800 MG GENFAR</t>
         </is>
       </c>
       <c r="C1530" t="inlineStr"/>
       <c r="D1530" t="inlineStr"/>
       <c r="E1530" t="n">
-        <v>18800</v>
+        <v>10500</v>
       </c>
       <c r="F1530" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G1530" t="n">
         <v>0</v>
@@ -81718,21 +81718,21 @@
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>ULCEPAR (OMEPRAZOL 20MG) CAPS- COASPH</t>
+          <t>TRIMETOPRIM SULFA 80/400MG X 120ML ECAR</t>
         </is>
       </c>
       <c r="C1531" t="inlineStr"/>
       <c r="D1531" t="inlineStr"/>
       <c r="E1531" t="n">
-        <v>4200</v>
+        <v>18800</v>
       </c>
       <c r="F1531" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G1531" t="n">
         <v>0</v>
@@ -81768,21 +81768,21 @@
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
+          <t>ULCEPAR (OMEPRAZOL 20MG) CAPS- COASPH</t>
         </is>
       </c>
       <c r="C1532" t="inlineStr"/>
       <c r="D1532" t="inlineStr"/>
       <c r="E1532" t="n">
-        <v>13800</v>
+        <v>4200</v>
       </c>
       <c r="F1532" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="G1532" t="n">
         <v>0</v>
@@ -81818,21 +81818,21 @@
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
+          <t>UROVITAL SOBRE X 10 CAPSULAS</t>
         </is>
       </c>
       <c r="C1533" t="inlineStr"/>
       <c r="D1533" t="inlineStr"/>
       <c r="E1533" t="n">
-        <v>7900</v>
+        <v>13800</v>
       </c>
       <c r="F1533" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1533" t="n">
         <v>0</v>
@@ -81868,21 +81868,21 @@
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>VASELINA FC X 200GR YOMA</t>
+          <t>VALSARTAN 80MG X 14TBL DE LA SANTE</t>
         </is>
       </c>
       <c r="C1534" t="inlineStr"/>
       <c r="D1534" t="inlineStr"/>
       <c r="E1534" t="n">
-        <v>12521.008403</v>
+        <v>7900</v>
       </c>
       <c r="F1534" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1534" t="n">
         <v>0</v>
@@ -81910,7 +81910,7 @@
       </c>
       <c r="M1534" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1534" t="inlineStr"/>
@@ -81918,21 +81918,21 @@
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
+          <t>VASELINA FC X 200GR YOMA</t>
         </is>
       </c>
       <c r="C1535" t="inlineStr"/>
       <c r="D1535" t="inlineStr"/>
       <c r="E1535" t="n">
-        <v>420.168067</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1535" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1535" t="n">
         <v>0</v>
@@ -81968,25 +81968,21 @@
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
-        </is>
-      </c>
-      <c r="C1536" t="inlineStr">
-        <is>
-          <t>7708480649803</t>
-        </is>
-      </c>
+          <t>VASO 7 OZ PAQUETE X 50 UNDS</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr"/>
       <c r="D1536" t="inlineStr"/>
       <c r="E1536" t="n">
-        <v>28000</v>
+        <v>420.168067</v>
       </c>
       <c r="F1536" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1536" t="n">
         <v>0</v>
@@ -82014,7 +82010,7 @@
       </c>
       <c r="M1536" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1536" t="inlineStr"/>
@@ -82022,25 +82018,25 @@
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>Venda Elastica 6x5 y piel</t>
-        </is>
-      </c>
-      <c r="C1537" t="inlineStr"/>
-      <c r="D1537" t="inlineStr">
-        <is>
-          <t>SUBIO A 6200 ANTES 5700</t>
-        </is>
-      </c>
+          <t>VAXOMIZOL TERBINAFINA 1% CREMA TBO20GR</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>7708480649803</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr"/>
       <c r="E1537" t="n">
-        <v>6200</v>
+        <v>28000</v>
       </c>
       <c r="F1537" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1537" t="n">
         <v>0</v>
@@ -82076,21 +82072,25 @@
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
+          <t>Venda Elastica 6x5 y piel</t>
         </is>
       </c>
       <c r="C1538" t="inlineStr"/>
-      <c r="D1538" t="inlineStr"/>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>SUBIO A 6200 ANTES 5700</t>
+        </is>
+      </c>
       <c r="E1538" t="n">
-        <v>5500</v>
+        <v>6200</v>
       </c>
       <c r="F1538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1538" t="n">
         <v>0</v>
@@ -82126,21 +82126,21 @@
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>Venta simple</t>
+          <t>VENDA FIJA BLANCA ALFA 3X2.2MTS</t>
         </is>
       </c>
       <c r="C1539" t="inlineStr"/>
       <c r="D1539" t="inlineStr"/>
       <c r="E1539" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="F1539" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1539" t="n">
         <v>0</v>
@@ -82158,7 +82158,7 @@
       </c>
       <c r="K1539" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="L1539" t="inlineStr">
@@ -82166,27 +82166,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1539" t="inlineStr"/>
+      <c r="M1539" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1539" t="inlineStr"/>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
+          <t>Venta simple</t>
         </is>
       </c>
       <c r="C1540" t="inlineStr"/>
       <c r="D1540" t="inlineStr"/>
       <c r="E1540" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F1540" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1540" t="n">
         <v>0</v>
@@ -82204,7 +82208,7 @@
       </c>
       <c r="K1540" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="L1540" t="inlineStr">
@@ -82212,35 +82216,27 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1540" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1540" t="inlineStr"/>
       <c r="N1540" t="inlineStr"/>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
-        </is>
-      </c>
-      <c r="C1541" t="inlineStr">
-        <is>
-          <t>793969226467</t>
-        </is>
-      </c>
+          <t>VICK PASTILLAS X UNIDAD CADA 1</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr"/>
       <c r="D1541" t="inlineStr"/>
       <c r="E1541" t="n">
-        <v>17000</v>
+        <v>1000</v>
       </c>
       <c r="F1541" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1541" t="n">
         <v>0</v>
@@ -82263,7 +82259,7 @@
       </c>
       <c r="L1541" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="M1541" t="inlineStr">
@@ -82276,21 +82272,25 @@
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>VINO CEREBRAL JARABE X 1100ML</t>
-        </is>
-      </c>
-      <c r="C1542" t="inlineStr"/>
+          <t>VINAGRE SIDRA DE MANZANA CON MAD,375ML</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>793969226467</t>
+        </is>
+      </c>
       <c r="D1542" t="inlineStr"/>
       <c r="E1542" t="n">
-        <v>48900</v>
+        <v>17000</v>
       </c>
       <c r="F1542" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1542" t="n">
         <v>0</v>
@@ -82313,7 +82313,7 @@
       </c>
       <c r="L1542" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="M1542" t="inlineStr">
@@ -82326,21 +82326,21 @@
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>VIOXIN ENJUAGUE BUCAL 0.12% CLORH 120ML</t>
+          <t>VINO CEREBRAL JARABE X 1100ML</t>
         </is>
       </c>
       <c r="C1543" t="inlineStr"/>
       <c r="D1543" t="inlineStr"/>
       <c r="E1543" t="n">
-        <v>24800</v>
+        <v>48900</v>
       </c>
       <c r="F1543" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1543" t="n">
         <v>0</v>
@@ -82376,21 +82376,21 @@
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
+          <t>VIOXIN ENJUAGUE BUCAL 0.12% CLORH 120ML</t>
         </is>
       </c>
       <c r="C1544" t="inlineStr"/>
       <c r="D1544" t="inlineStr"/>
       <c r="E1544" t="n">
-        <v>5400</v>
+        <v>24800</v>
       </c>
       <c r="F1544" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G1544" t="n">
         <v>0</v>
@@ -82426,21 +82426,21 @@
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
+          <t>VITAMINA C DE NARANJA 500MG LS.SBS</t>
         </is>
       </c>
       <c r="C1545" t="inlineStr"/>
       <c r="D1545" t="inlineStr"/>
       <c r="E1545" t="n">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="F1545" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G1545" t="n">
         <v>0</v>
@@ -82476,21 +82476,21 @@
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>WINNY PAÑAL ETP 6 X 30</t>
+          <t>VITAMINA E 400UI SOBRE X 10 CAPS COLMD</t>
         </is>
       </c>
       <c r="C1546" t="inlineStr"/>
       <c r="D1546" t="inlineStr"/>
       <c r="E1546" t="n">
-        <v>57000</v>
+        <v>5500</v>
       </c>
       <c r="F1546" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G1546" t="n">
         <v>0</v>
@@ -82526,52 +82526,102 @@
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>YODO BLANCO FC X30ML</t>
+          <t>WINNY PAÑAL ETP 6 X 30</t>
         </is>
       </c>
       <c r="C1547" t="inlineStr"/>
       <c r="D1547" t="inlineStr"/>
       <c r="E1547" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F1547" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1547" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1547" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1547" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1547" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1547" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1547" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1547" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1547" t="inlineStr"/>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>YODO BLANCO FC X30ML</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr"/>
+      <c r="D1548" t="inlineStr"/>
+      <c r="E1548" t="n">
         <v>6000</v>
       </c>
-      <c r="F1547" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1547" t="n">
-        <v>0</v>
-      </c>
-      <c r="H1547" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1547" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1547" t="inlineStr">
-        <is>
-          <t>Ventas</t>
-        </is>
-      </c>
-      <c r="K1547" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="L1547" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="M1547" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="N1547" t="inlineStr"/>
+      <c r="F1548" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1548" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1548" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1548" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1548" t="inlineStr">
+        <is>
+          <t>Ventas</t>
+        </is>
+      </c>
+      <c r="K1548" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="L1548" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="M1548" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="N1548" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -15543,7 +15543,7 @@
         <v>11500</v>
       </c>
       <c r="F283" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G283" t="n">
         <v>0</v>
@@ -56970,7 +56970,7 @@
         <v>9500</v>
       </c>
       <c r="F1058" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1058" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -10329,7 +10329,7 @@
         <v>4000</v>
       </c>
       <c r="F186" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -11519,7 +11519,7 @@
         <v>1500</v>
       </c>
       <c r="F209" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -14127,7 +14127,7 @@
         <v>840.336134</v>
       </c>
       <c r="F257" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -15157,7 +15157,7 @@
         <v>1900</v>
       </c>
       <c r="F276" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G276" t="n">
         <v>0</v>
@@ -16681,7 +16681,7 @@
         <v>3800</v>
       </c>
       <c r="F304" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G304" t="n">
         <v>0</v>
@@ -23215,7 +23215,7 @@
         <v>2200</v>
       </c>
       <c r="F427" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G427" t="n">
         <v>0</v>
@@ -23473,7 +23473,7 @@
         <v>3000</v>
       </c>
       <c r="F432" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G432" t="n">
         <v>0</v>
@@ -31679,7 +31679,7 @@
         <v>2800</v>
       </c>
       <c r="F585" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G585" t="n">
         <v>0</v>
@@ -36961,7 +36961,7 @@
         <v>3277.310924</v>
       </c>
       <c r="F684" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G684" t="n">
         <v>0</v>
@@ -50325,7 +50325,7 @@
         <v>2300</v>
       </c>
       <c r="F934" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G934" t="n">
         <v>0</v>
@@ -51361,7 +51361,7 @@
         <v>2200</v>
       </c>
       <c r="F954" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G954" t="n">
         <v>0</v>
@@ -55450,7 +55450,7 @@
         <v>10504.201681</v>
       </c>
       <c r="F1030" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1030" t="n">
         <v>0</v>
@@ -56970,7 +56970,7 @@
         <v>9500</v>
       </c>
       <c r="F1058" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1058" t="n">
         <v>0</v>
@@ -66912,7 +66912,7 @@
         <v>2200</v>
       </c>
       <c r="F1243" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G1243" t="n">
         <v>0</v>
@@ -80912,7 +80912,7 @@
         <v>4874</v>
       </c>
       <c r="F1515" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G1515" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -7325,7 +7325,7 @@
         <v>26000</v>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -9419,7 +9419,7 @@
         <v>23200</v>
       </c>
       <c r="F169" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -38777,7 +38777,7 @@
         <v>3781.512605</v>
       </c>
       <c r="F718" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G718" t="n">
         <v>0</v>
@@ -42373,7 +42373,7 @@
         <v>5500</v>
       </c>
       <c r="F786" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G786" t="n">
         <v>0</v>
@@ -52192,7 +52192,7 @@
         <v>4537.815126</v>
       </c>
       <c r="F969" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G969" t="n">
         <v>0</v>
@@ -71144,7 +71144,7 @@
         <v>33900</v>
       </c>
       <c r="F1325" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G1325" t="n">
         <v>0</v>
@@ -75494,7 +75494,7 @@
         <v>15042.016807</v>
       </c>
       <c r="F1410" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1410" t="n">
         <v>0</v>
@@ -75852,7 +75852,7 @@
         <v>3361.344538</v>
       </c>
       <c r="F1417" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1417" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -3901,7 +3901,7 @@
         <v>5800</v>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -6743,7 +6743,7 @@
         <v>40000</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -14073,7 +14073,7 @@
         <v>672</v>
       </c>
       <c r="F256" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -14127,7 +14127,7 @@
         <v>840.336134</v>
       </c>
       <c r="F257" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -16303,7 +16303,7 @@
         <v>13700</v>
       </c>
       <c r="F297" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G297" t="n">
         <v>0</v>
@@ -23315,7 +23315,7 @@
         <v>1900</v>
       </c>
       <c r="F429" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G429" t="n">
         <v>0</v>
@@ -23631,7 +23631,7 @@
         <v>3300</v>
       </c>
       <c r="F435" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G435" t="n">
         <v>0</v>
@@ -27337,7 +27337,7 @@
         <v>2500</v>
       </c>
       <c r="F504" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G504" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>41000</v>
       </c>
       <c r="F516" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G516" t="n">
         <v>0</v>
@@ -31297,7 +31297,7 @@
         <v>2700</v>
       </c>
       <c r="F578" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G578" t="n">
         <v>0</v>
@@ -31355,7 +31355,7 @@
         <v>3400</v>
       </c>
       <c r="F579" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G579" t="n">
         <v>0</v>
@@ -31625,7 +31625,7 @@
         <v>2800</v>
       </c>
       <c r="F584" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G584" t="n">
         <v>0</v>
@@ -31791,7 +31791,7 @@
         <v>2500</v>
       </c>
       <c r="F587" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G587" t="n">
         <v>0</v>
@@ -32825,7 +32825,7 @@
         <v>2800</v>
       </c>
       <c r="F606" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G606" t="n">
         <v>0</v>
@@ -42373,7 +42373,7 @@
         <v>5500</v>
       </c>
       <c r="F786" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G786" t="n">
         <v>0</v>
@@ -47025,7 +47025,7 @@
         <v>2700</v>
       </c>
       <c r="F872" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G872" t="n">
         <v>0</v>
@@ -50325,7 +50325,7 @@
         <v>2300</v>
       </c>
       <c r="F934" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G934" t="n">
         <v>0</v>
@@ -50645,7 +50645,7 @@
         <v>4400</v>
       </c>
       <c r="F940" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G940" t="n">
         <v>0</v>
@@ -52944,7 +52944,7 @@
         <v>1500</v>
       </c>
       <c r="F983" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G983" t="n">
         <v>0</v>
@@ -58790,7 +58790,7 @@
         <v>2900</v>
       </c>
       <c r="F1092" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G1092" t="n">
         <v>0</v>
@@ -61586,7 +61586,7 @@
         <v>11800</v>
       </c>
       <c r="F1144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1144" t="n">
         <v>0</v>
@@ -65004,7 +65004,7 @@
         <v>3100</v>
       </c>
       <c r="F1207" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1207" t="n">
         <v>0</v>
@@ -66808,7 +66808,7 @@
         <v>49800</v>
       </c>
       <c r="F1241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1241" t="n">
         <v>0</v>
@@ -67166,7 +67166,7 @@
         <v>8700</v>
       </c>
       <c r="F1248" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1248" t="n">
         <v>0</v>
@@ -67424,7 +67424,7 @@
         <v>6300</v>
       </c>
       <c r="F1253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1253" t="n">
         <v>0</v>
@@ -70832,7 +70832,7 @@
         <v>28900</v>
       </c>
       <c r="F1319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1319" t="n">
         <v>0</v>
@@ -74212,7 +74212,7 @@
         <v>4800</v>
       </c>
       <c r="F1385" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1385" t="n">
         <v>0</v>
@@ -76272,7 +76272,7 @@
         <v>5500</v>
       </c>
       <c r="F1425" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G1425" t="n">
         <v>0</v>
@@ -77042,7 +77042,7 @@
         <v>24500</v>
       </c>
       <c r="F1440" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1440" t="n">
         <v>0</v>
@@ -81266,7 +81266,7 @@
         <v>13500</v>
       </c>
       <c r="F1522" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1522" t="n">
         <v>0</v>
@@ -82190,7 +82190,7 @@
         <v>5500</v>
       </c>
       <c r="F1540" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1540" t="n">
         <v>0</v>
@@ -82490,7 +82490,7 @@
         <v>5400</v>
       </c>
       <c r="F1546" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G1546" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -4113,7 +4113,7 @@
         <v>5882.352941</v>
       </c>
       <c r="F70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -18047,7 +18047,7 @@
         <v>3109.243697</v>
       </c>
       <c r="F329" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G329" t="n">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v>6723</v>
       </c>
       <c r="F331" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G331" t="n">
         <v>0</v>
@@ -21441,7 +21441,7 @@
         <v>24000</v>
       </c>
       <c r="F394" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G394" t="n">
         <v>0</v>
@@ -22305,7 +22305,7 @@
         <v>7900</v>
       </c>
       <c r="F410" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G410" t="n">
         <v>0</v>
@@ -31297,7 +31297,7 @@
         <v>2700</v>
       </c>
       <c r="F578" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G578" t="n">
         <v>0</v>
@@ -31957,7 +31957,7 @@
         <v>2500</v>
       </c>
       <c r="F590" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G590" t="n">
         <v>0</v>
@@ -42095,7 +42095,7 @@
         <v>3700</v>
       </c>
       <c r="F781" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G781" t="n">
         <v>0</v>
@@ -60402,7 +60402,7 @@
         <v>6300</v>
       </c>
       <c r="F1122" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G1122" t="n">
         <v>0</v>
@@ -66962,7 +66962,7 @@
         <v>2200</v>
       </c>
       <c r="F1244" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G1244" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -3901,7 +3901,7 @@
         <v>5800</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -14127,7 +14127,7 @@
         <v>840.336134</v>
       </c>
       <c r="F257" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>840.336134</v>
       </c>
       <c r="F260" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -23419,7 +23419,7 @@
         <v>2000</v>
       </c>
       <c r="F431" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G431" t="n">
         <v>0</v>
@@ -23851,7 +23851,7 @@
         <v>3300</v>
       </c>
       <c r="F439" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G439" t="n">
         <v>0</v>
@@ -31297,7 +31297,7 @@
         <v>2700</v>
       </c>
       <c r="F578" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G578" t="n">
         <v>0</v>
@@ -31571,7 +31571,7 @@
         <v>2600</v>
       </c>
       <c r="F583" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G583" t="n">
         <v>0</v>
@@ -32389,7 +32389,7 @@
         <v>900</v>
       </c>
       <c r="F598" t="n">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="G598" t="n">
         <v>0</v>
@@ -32663,7 +32663,7 @@
         <v>2200</v>
       </c>
       <c r="F603" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G603" t="n">
         <v>0</v>
@@ -40685,7 +40685,7 @@
         <v>12000</v>
       </c>
       <c r="F754" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G754" t="n">
         <v>0</v>
@@ -46439,7 +46439,7 @@
         <v>3000</v>
       </c>
       <c r="F861" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G861" t="n">
         <v>0</v>
@@ -47025,7 +47025,7 @@
         <v>2700</v>
       </c>
       <c r="F872" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G872" t="n">
         <v>0</v>
@@ -47619,7 +47619,7 @@
         <v>1800</v>
       </c>
       <c r="F883" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G883" t="n">
         <v>0</v>
@@ -50013,7 +50013,7 @@
         <v>1200</v>
       </c>
       <c r="F928" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G928" t="n">
         <v>0</v>
@@ -51361,7 +51361,7 @@
         <v>2200</v>
       </c>
       <c r="F954" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G954" t="n">
         <v>0</v>
@@ -52192,7 +52192,7 @@
         <v>4537.815126</v>
       </c>
       <c r="F969" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G969" t="n">
         <v>0</v>
@@ -54860,7 +54860,7 @@
         <v>6900</v>
       </c>
       <c r="F1019" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1019" t="n">
         <v>0</v>
@@ -55122,7 +55122,7 @@
         <v>3200</v>
       </c>
       <c r="F1024" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1024" t="n">
         <v>0</v>
@@ -55338,7 +55338,7 @@
         <v>12352.941176</v>
       </c>
       <c r="F1028" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1028" t="n">
         <v>0</v>
@@ -60402,7 +60402,7 @@
         <v>6300</v>
       </c>
       <c r="F1122" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G1122" t="n">
         <v>0</v>
@@ -64236,7 +64236,7 @@
         <v>4800</v>
       </c>
       <c r="F1193" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1193" t="n">
         <v>0</v>
@@ -67012,7 +67012,7 @@
         <v>2500</v>
       </c>
       <c r="F1245" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1245" t="n">
         <v>0</v>
@@ -67582,7 +67582,7 @@
         <v>20000</v>
       </c>
       <c r="F1256" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1256" t="n">
         <v>0</v>
@@ -68988,7 +68988,7 @@
         <v>10800</v>
       </c>
       <c r="F1283" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G1283" t="n">
         <v>0</v>
@@ -71090,7 +71090,7 @@
         <v>28900</v>
       </c>
       <c r="F1324" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1324" t="n">
         <v>0</v>
@@ -73042,7 +73042,7 @@
         <v>3800</v>
       </c>
       <c r="F1362" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1362" t="n">
         <v>0</v>
@@ -76842,7 +76842,7 @@
         <v>5500</v>
       </c>
       <c r="F1436" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G1436" t="n">
         <v>0</v>
@@ -78968,7 +78968,7 @@
         <v>35900</v>
       </c>
       <c r="F1477" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1477" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -4113,7 +4113,7 @@
         <v>5882.352941</v>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>672</v>
       </c>
       <c r="F255" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -23631,7 +23631,7 @@
         <v>3300</v>
       </c>
       <c r="F435" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G435" t="n">
         <v>0</v>
@@ -32663,7 +32663,7 @@
         <v>2200</v>
       </c>
       <c r="F603" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G603" t="n">
         <v>0</v>
@@ -44017,7 +44017,7 @@
         <v>16000</v>
       </c>
       <c r="F816" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G816" t="n">
         <v>0</v>
@@ -45421,7 +45421,7 @@
         <v>1800</v>
       </c>
       <c r="F842" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G842" t="n">
         <v>0</v>
@@ -46439,7 +46439,7 @@
         <v>3000</v>
       </c>
       <c r="F861" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G861" t="n">
         <v>0</v>
@@ -55720,7 +55720,7 @@
         <v>3500</v>
       </c>
       <c r="F1035" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1035" t="n">
         <v>0</v>
@@ -66962,7 +66962,7 @@
         <v>2200</v>
       </c>
       <c r="F1244" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G1244" t="n">
         <v>0</v>
@@ -75952,7 +75952,7 @@
         <v>3200</v>
       </c>
       <c r="F1419" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1419" t="n">
         <v>0</v>
@@ -81732,7 +81732,7 @@
         <v>10500</v>
       </c>
       <c r="F1531" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1531" t="n">
         <v>0</v>

--- a/inventario_alegra.xlsx
+++ b/inventario_alegra.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1550"/>
+  <dimension ref="A1:N1551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3901,7 +3901,7 @@
         <v>5800</v>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -6261,7 +6261,7 @@
         <v>3700</v>
       </c>
       <c r="F110" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -13309,7 +13309,7 @@
         <v>8900</v>
       </c>
       <c r="F242" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -13691,7 +13691,7 @@
         <v>5800</v>
       </c>
       <c r="F249" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -13745,7 +13745,7 @@
         <v>4900</v>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -14073,7 +14073,7 @@
         <v>672</v>
       </c>
       <c r="F256" t="n">
-        <v>154</v>
+        <v>254</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -14767,7 +14767,7 @@
         <v>3361</v>
       </c>
       <c r="F269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -15431,7 +15431,7 @@
         <v>7800</v>
       </c>
       <c r="F281" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
@@ -15485,7 +15485,7 @@
         <v>13000</v>
       </c>
       <c r="F282" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G282" t="n">
         <v>0</v>
@@ -23797,7 +23797,7 @@
         <v>14000</v>
       </c>
       <c r="F438" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G438" t="n">
         <v>0</v>
@@ -28243,7 +28243,7 @@
         <v>5500</v>
       </c>
       <c r="F521" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G521" t="n">
         <v>0</v>
@@ -42867,7 +42867,7 @@
         <v>9800</v>
       </c>
       <c r="F795" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G795" t="n">
         <v>0</v>
@@ -49327,7 +49327,7 @@
         <v>3700</v>
       </c>
       <c r="F915" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G915" t="n">
         <v>0</v>
@@ -49385,7 +49385,7 @@
         <v>3700</v>
       </c>
       <c r="F916" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G916" t="n">
         <v>0</v>
@@ -51361,7 +51361,7 @@
         <v>2200</v>
       </c>
       <c r="F954" t="n">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="G954" t="n">
         <v>0</v>
@@ -56534,7 +56534,7 @@
         <v>3700</v>
       </c>
       <c r="F1050" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G1050" t="n">
         <v>0</v>
@@ -58308,7 +58308,7 @@
         <v>16400</v>
       </c>
       <c r="F1083" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1083" t="n">
         <v>0</v>
@@ -58898,7 +58898,7 @@
         <v>3900</v>
       </c>
       <c r="F1094" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1094" t="n">
         <v>0</v>
@@ -58952,7 +58952,7 @@
         <v>3400</v>
       </c>
       <c r="F1095" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1095" t="n">
         <v>0</v>
@@ -61586,7 +61586,7 @@
         <v>11800</v>
       </c>
       <c r="F1144" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G1144" t="n">
         <v>0</v>
@@ -62234,7 +62234,7 @@
         <v>2900</v>
       </c>
       <c r="F1156" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1156" t="n">
         <v>0</v>
@@ -64344,7 +64344,7 @@
         <v>6900</v>
       </c>
       <c r="F1195" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1195" t="n">
         <v>0</v>
@@ -71506,7 +71506,7 @@
         <v>42000</v>
       </c>
       <c r="F1332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1332" t="n">
         <v>0</v>
@@ -72264,7 +72264,7 @@
         <v>48600</v>
       </c>
       <c r="F1347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1347" t="n">
         <v>0</v>
@@ -73332,21 +73332,21 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
+          <t>GOTERO DE VIDRIO X UND ALFASAFE</t>
         </is>
       </c>
       <c r="C1368" t="inlineStr"/>
       <c r="D1368" t="inlineStr"/>
       <c r="E1368" t="n">
-        <v>3361.344538</v>
+        <v>1260.504202</v>
       </c>
       <c r="F1368" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G1368" t="n">
         <v>0</v>
@@ -73382,21 +73382,21 @@
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
+          <t>GUANTE LATEX ESTERIL CIRUGIA 7.5X1 ALF TRADING</t>
         </is>
       </c>
       <c r="C1369" t="inlineStr"/>
       <c r="D1369" t="inlineStr"/>
       <c r="E1369" t="n">
-        <v>23109.243697</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1369" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G1369" t="n">
         <v>0</v>
@@ -73432,25 +73432,21 @@
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1370" t="inlineStr">
-        <is>
-          <t>7709195419279</t>
-        </is>
-      </c>
+          <t>GUANTE LATEX EXAMEN (S) X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr"/>
       <c r="D1370" t="inlineStr"/>
       <c r="E1370" t="n">
-        <v>24370</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1370" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1370" t="n">
         <v>0</v>
@@ -73486,21 +73482,25 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="B1371" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
-        </is>
-      </c>
-      <c r="C1371" t="inlineStr"/>
+          <t>GUANTE NITRILO NEGRO (M) X 100 UND</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>7709195419279</t>
+        </is>
+      </c>
       <c r="D1371" t="inlineStr"/>
       <c r="E1371" t="n">
-        <v>24369.747899</v>
+        <v>24370</v>
       </c>
       <c r="F1371" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1371" t="n">
         <v>0</v>
@@ -73536,21 +73536,21 @@
     <row r="1372">
       <c r="A1372" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="B1372" t="inlineStr">
         <is>
-          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
+          <t>GUANTE NITRILO NEGRO TALLA L X 100 UND</t>
         </is>
       </c>
       <c r="C1372" t="inlineStr"/>
       <c r="D1372" t="inlineStr"/>
       <c r="E1372" t="n">
-        <v>23109.243697</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1372" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G1372" t="n">
         <v>0</v>
@@ -73586,21 +73586,21 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>HALLS BARRA SURTIDOS SABORES</t>
+          <t>GUANTES EXAMEN LATEX TALLA L CJA X 100UND</t>
         </is>
       </c>
       <c r="C1373" t="inlineStr"/>
       <c r="D1373" t="inlineStr"/>
       <c r="E1373" t="n">
-        <v>2100.840336</v>
+        <v>23109.243697</v>
       </c>
       <c r="F1373" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G1373" t="n">
         <v>0</v>
@@ -73636,21 +73636,21 @@
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="B1374" t="inlineStr">
         <is>
-          <t>HALLS PEPA ROJO CEREZA X UND</t>
+          <t>HALLS BARRA SURTIDOS SABORES</t>
         </is>
       </c>
       <c r="C1374" t="inlineStr"/>
       <c r="D1374" t="inlineStr"/>
       <c r="E1374" t="n">
-        <v>336.134454</v>
+        <v>2100.840336</v>
       </c>
       <c r="F1374" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="G1374" t="n">
         <v>0</v>
@@ -73686,21 +73686,21 @@
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="B1375" t="inlineStr">
         <is>
-          <t>HEPATODREN JARABE FCO X 240ML</t>
+          <t>HALLS PEPA ROJO CEREZA X UND</t>
         </is>
       </c>
       <c r="C1375" t="inlineStr"/>
       <c r="D1375" t="inlineStr"/>
       <c r="E1375" t="n">
-        <v>34500</v>
+        <v>336.134454</v>
       </c>
       <c r="F1375" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G1375" t="n">
         <v>0</v>
@@ -73728,7 +73728,7 @@
       </c>
       <c r="M1375" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1375" t="inlineStr"/>
@@ -73736,18 +73736,18 @@
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="B1376" t="inlineStr">
         <is>
-          <t>HEPATODREN X 60 CAPSULAS</t>
+          <t>HEPATODREN JARABE FCO X 240ML</t>
         </is>
       </c>
       <c r="C1376" t="inlineStr"/>
       <c r="D1376" t="inlineStr"/>
       <c r="E1376" t="n">
-        <v>58300</v>
+        <v>34500</v>
       </c>
       <c r="F1376" t="n">
         <v>1</v>
@@ -73786,25 +73786,21 @@
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>Hidraplus 75 zinc uva 400ml</t>
-        </is>
-      </c>
-      <c r="C1377" t="inlineStr">
-        <is>
-          <t>7702057010928</t>
-        </is>
-      </c>
+          <t>HEPATODREN X 60 CAPSULAS</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr"/>
       <c r="D1377" t="inlineStr"/>
       <c r="E1377" t="n">
-        <v>10600</v>
+        <v>58300</v>
       </c>
       <c r="F1377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1377" t="n">
         <v>0</v>
@@ -73840,21 +73836,25 @@
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="B1378" t="inlineStr">
         <is>
-          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
-        </is>
-      </c>
-      <c r="C1378" t="inlineStr"/>
+          <t>Hidraplus 75 zinc uva 400ml</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>7702057010928</t>
+        </is>
+      </c>
       <c r="D1378" t="inlineStr"/>
       <c r="E1378" t="n">
-        <v>15900</v>
+        <v>10600</v>
       </c>
       <c r="F1378" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1378" t="n">
         <v>0</v>
@@ -73890,25 +73890,21 @@
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
-        </is>
-      </c>
-      <c r="C1379" t="inlineStr">
-        <is>
-          <t>77099475597789</t>
-        </is>
-      </c>
+          <t>HIDROCORTISONA 1% 15GR DE A.G CREMA</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr"/>
       <c r="D1379" t="inlineStr"/>
       <c r="E1379" t="n">
-        <v>28000</v>
+        <v>15900</v>
       </c>
       <c r="F1379" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1379" t="n">
         <v>0</v>
@@ -73944,25 +73940,25 @@
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>Hidroxicina 0.25 JBE x 120 ML</t>
+          <t>HIDROPIEL 2% CREMA X 30GR (KETOCONAZOL)</t>
         </is>
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>7707035540596</t>
+          <t>77099475597789</t>
         </is>
       </c>
       <c r="D1380" t="inlineStr"/>
       <c r="E1380" t="n">
-        <v>11000</v>
+        <v>28000</v>
       </c>
       <c r="F1380" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1380" t="n">
         <v>0</v>
@@ -73998,18 +73994,22 @@
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="B1381" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
-        </is>
-      </c>
-      <c r="C1381" t="inlineStr"/>
+          <t>Hidroxicina 0.25 JBE x 120 ML</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>7707035540596</t>
+        </is>
+      </c>
       <c r="D1381" t="inlineStr"/>
       <c r="E1381" t="n">
-        <v>4500</v>
+        <v>11000</v>
       </c>
       <c r="F1381" t="n">
         <v>2</v>
@@ -74048,21 +74048,21 @@
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
+          <t>HIDROXICINA 25MG SB X 10 DE COAS</t>
         </is>
       </c>
       <c r="C1382" t="inlineStr"/>
       <c r="D1382" t="inlineStr"/>
       <c r="E1382" t="n">
-        <v>6900</v>
+        <v>4500</v>
       </c>
       <c r="F1382" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1382" t="n">
         <v>0</v>
@@ -74098,18 +74098,18 @@
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
+          <t>HIDROXICINA 25MG SOBRE X 10 TABL DE GENFAR</t>
         </is>
       </c>
       <c r="C1383" t="inlineStr"/>
       <c r="D1383" t="inlineStr"/>
       <c r="E1383" t="n">
-        <v>12000</v>
+        <v>6900</v>
       </c>
       <c r="F1383" t="n">
         <v>4</v>
@@ -74148,21 +74148,21 @@
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>Hylo Gel</t>
+          <t>HIOSCINA+DIPIRONA20MG+2.5G/5ML 1AMP VT</t>
         </is>
       </c>
       <c r="C1384" t="inlineStr"/>
       <c r="D1384" t="inlineStr"/>
       <c r="E1384" t="n">
-        <v>131600</v>
+        <v>12000</v>
       </c>
       <c r="F1384" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1384" t="n">
         <v>0</v>
@@ -74198,21 +74198,21 @@
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>IBUFLASH 400MG CAPSULA ROJA IBUPROF.</t>
+          <t>Hylo Gel</t>
         </is>
       </c>
       <c r="C1385" t="inlineStr"/>
       <c r="D1385" t="inlineStr"/>
       <c r="E1385" t="n">
-        <v>4800</v>
+        <v>131600</v>
       </c>
       <c r="F1385" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G1385" t="n">
         <v>0</v>
@@ -74248,25 +74248,21 @@
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>IBUPROFENO 400MG/ GENFAR</t>
-        </is>
-      </c>
-      <c r="C1386" t="inlineStr">
-        <is>
-          <t>7702605101498</t>
-        </is>
-      </c>
+          <t>IBUFLASH 400MG CAPSULA ROJA IBUPROF.</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr"/>
       <c r="D1386" t="inlineStr"/>
       <c r="E1386" t="n">
-        <v>4400</v>
+        <v>4800</v>
       </c>
       <c r="F1386" t="n">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="G1386" t="n">
         <v>0</v>
@@ -74302,25 +74298,25 @@
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>Ibuprofeno 800mg AG</t>
+          <t>IBUPROFENO 400MG/ GENFAR</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr">
         <is>
-          <t>7706569000385</t>
+          <t>7702605101498</t>
         </is>
       </c>
       <c r="D1387" t="inlineStr"/>
       <c r="E1387" t="n">
-        <v>800</v>
+        <v>4400</v>
       </c>
       <c r="F1387" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G1387" t="n">
         <v>0</v>
@@ -74356,25 +74352,25 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
+          <t>Ibuprofeno 800mg AG</t>
         </is>
       </c>
       <c r="C1388" t="inlineStr">
         <is>
-          <t>7705959885229</t>
+          <t>7706569000385</t>
         </is>
       </c>
       <c r="D1388" t="inlineStr"/>
       <c r="E1388" t="n">
-        <v>17900</v>
+        <v>800</v>
       </c>
       <c r="F1388" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1388" t="n">
         <v>0</v>
@@ -74410,22 +74406,22 @@
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>ICE POWER 30 GR GEL COSMETICA</t>
+          <t>IBUPROFENO KIDS 100MGX120ML SUSP GENFAR</t>
         </is>
       </c>
       <c r="C1389" t="inlineStr">
         <is>
-          <t>737186238889</t>
+          <t>7705959885229</t>
         </is>
       </c>
       <c r="D1389" t="inlineStr"/>
       <c r="E1389" t="n">
-        <v>12521.008403</v>
+        <v>17900</v>
       </c>
       <c r="F1389" t="n">
         <v>2</v>
@@ -74456,7 +74452,7 @@
       </c>
       <c r="M1389" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1389" t="inlineStr"/>
@@ -74464,21 +74460,25 @@
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
-        </is>
-      </c>
-      <c r="C1390" t="inlineStr"/>
+          <t>ICE POWER 30 GR GEL COSMETICA</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>737186238889</t>
+        </is>
+      </c>
       <c r="D1390" t="inlineStr"/>
       <c r="E1390" t="n">
-        <v>38900</v>
+        <v>12521.008403</v>
       </c>
       <c r="F1390" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1390" t="n">
         <v>0</v>
@@ -74506,7 +74506,7 @@
       </c>
       <c r="M1390" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1390" t="inlineStr"/>
@@ -74514,12 +74514,12 @@
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
+          <t>IPRASYNT(BROMURODE IPRATROPIO)X 200 DOSIS INHA</t>
         </is>
       </c>
       <c r="C1391" t="inlineStr"/>
@@ -74564,21 +74564,21 @@
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
+          <t>ISOFLOVONA DE SOYA CJ X 30 CAPS NF</t>
         </is>
       </c>
       <c r="C1392" t="inlineStr"/>
       <c r="D1392" t="inlineStr"/>
       <c r="E1392" t="n">
-        <v>8235.294118</v>
+        <v>38900</v>
       </c>
       <c r="F1392" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1392" t="n">
         <v>0</v>
@@ -74606,7 +74606,7 @@
       </c>
       <c r="M1392" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1392" t="inlineStr"/>
@@ -74614,21 +74614,21 @@
     <row r="1393">
       <c r="A1393" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="B1393" t="inlineStr">
         <is>
-          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
+          <t>JABON ALMIPRO DERMOLIMPIADOR 100 GR</t>
         </is>
       </c>
       <c r="C1393" t="inlineStr"/>
       <c r="D1393" t="inlineStr"/>
       <c r="E1393" t="n">
-        <v>9831.932773</v>
+        <v>8235.294118</v>
       </c>
       <c r="F1393" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1393" t="n">
         <v>0</v>
@@ -74664,21 +74664,21 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
         <is>
-          <t>Jabon liquido manos mi dia</t>
+          <t>JABON INTIMO MANZANILLA Y CALENDULA X 85ML</t>
         </is>
       </c>
       <c r="C1394" t="inlineStr"/>
       <c r="D1394" t="inlineStr"/>
       <c r="E1394" t="n">
-        <v>5882.352941</v>
+        <v>9831.932773</v>
       </c>
       <c r="F1394" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1394" t="n">
         <v>0</v>
@@ -74714,21 +74714,21 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
+          <t>Jabon liquido manos mi dia</t>
         </is>
       </c>
       <c r="C1395" t="inlineStr"/>
       <c r="D1395" t="inlineStr"/>
       <c r="E1395" t="n">
-        <v>4201.680672</v>
+        <v>5882.352941</v>
       </c>
       <c r="F1395" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1395" t="n">
         <v>0</v>
@@ -74764,12 +74764,12 @@
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
         <is>
-          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
+          <t>JABON PALMOLIVE ALOE OLIVA 110GR</t>
         </is>
       </c>
       <c r="C1396" t="inlineStr"/>
@@ -74778,7 +74778,7 @@
         <v>4201.680672</v>
       </c>
       <c r="F1396" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1396" t="n">
         <v>0</v>
@@ -74814,18 +74814,18 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>JABON PROTEX HERBAL 110GR</t>
+          <t>JABON PALMOLIVE POMEGRANATE X 110 GR</t>
         </is>
       </c>
       <c r="C1397" t="inlineStr"/>
       <c r="D1397" t="inlineStr"/>
       <c r="E1397" t="n">
-        <v>4537.815126</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1397" t="n">
         <v>2</v>
@@ -74864,25 +74864,21 @@
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>JARABE ZETYGRIP FCO 60ML</t>
-        </is>
-      </c>
-      <c r="C1398" t="inlineStr">
-        <is>
-          <t>7709805542830</t>
-        </is>
-      </c>
+          <t>JABON PROTEX HERBAL 110GR</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr"/>
       <c r="D1398" t="inlineStr"/>
       <c r="E1398" t="n">
-        <v>14000</v>
+        <v>4537.815126</v>
       </c>
       <c r="F1398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1398" t="n">
         <v>0</v>
@@ -74910,7 +74906,7 @@
       </c>
       <c r="M1398" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1398" t="inlineStr"/>
@@ -74918,21 +74914,25 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>JERINGA DE 50ML</t>
-        </is>
-      </c>
-      <c r="C1399" t="inlineStr"/>
+          <t>JARABE ZETYGRIP FCO 60ML</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>7709805542830</t>
+        </is>
+      </c>
       <c r="D1399" t="inlineStr"/>
       <c r="E1399" t="n">
-        <v>2500</v>
+        <v>14000</v>
       </c>
       <c r="F1399" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1399" t="n">
         <v>0</v>
@@ -74968,21 +74968,21 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>Jeringa desechable estéril 20ml impormedicas</t>
+          <t>JERINGA DE 50ML</t>
         </is>
       </c>
       <c r="C1400" t="inlineStr"/>
       <c r="D1400" t="inlineStr"/>
       <c r="E1400" t="n">
-        <v>920</v>
+        <v>2500</v>
       </c>
       <c r="F1400" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G1400" t="n">
         <v>0</v>
@@ -75010,7 +75010,7 @@
       </c>
       <c r="M1400" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1400" t="inlineStr"/>
@@ -75018,21 +75018,21 @@
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
+          <t>Jeringa desechable estéril 20ml impormedicas</t>
         </is>
       </c>
       <c r="C1401" t="inlineStr"/>
       <c r="D1401" t="inlineStr"/>
       <c r="E1401" t="n">
-        <v>1100</v>
+        <v>920</v>
       </c>
       <c r="F1401" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="G1401" t="n">
         <v>0</v>
@@ -75060,7 +75060,7 @@
       </c>
       <c r="M1401" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1401" t="inlineStr"/>
@@ -75068,21 +75068,21 @@
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>Kelocate</t>
+          <t>JERINGA INSULINA DE 1ML DE TAPA NARANJA</t>
         </is>
       </c>
       <c r="C1402" t="inlineStr"/>
       <c r="D1402" t="inlineStr"/>
       <c r="E1402" t="n">
-        <v>180000</v>
+        <v>1100</v>
       </c>
       <c r="F1402" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G1402" t="n">
         <v>0</v>
@@ -75118,22 +75118,18 @@
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
-        </is>
-      </c>
-      <c r="C1403" t="inlineStr">
-        <is>
-          <t>7702057073695</t>
-        </is>
-      </c>
+          <t>Kelocate</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr"/>
       <c r="D1403" t="inlineStr"/>
       <c r="E1403" t="n">
-        <v>19500</v>
+        <v>180000</v>
       </c>
       <c r="F1403" t="n">
         <v>0</v>
@@ -75172,22 +75168,22 @@
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
+          <t>KETOCONAZOL 200MG X 10 TBL DE MK</t>
         </is>
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>7709947559772</t>
+          <t>7702057073695</t>
         </is>
       </c>
       <c r="D1404" t="inlineStr"/>
       <c r="E1404" t="n">
-        <v>15000</v>
+        <v>19500</v>
       </c>
       <c r="F1404" t="n">
         <v>0</v>
@@ -75226,18 +75222,22 @@
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
-        </is>
-      </c>
-      <c r="C1405" t="inlineStr"/>
+          <t>LAGRIMART CARBOXIMETILCELULOSA SODICA 0.5%FRSC 5 ML</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>7709947559772</t>
+        </is>
+      </c>
       <c r="D1405" t="inlineStr"/>
       <c r="E1405" t="n">
-        <v>71000</v>
+        <v>15000</v>
       </c>
       <c r="F1405" t="n">
         <v>0</v>
@@ -75276,21 +75276,21 @@
     <row r="1406">
       <c r="A1406" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
+          <t>Levofloxacino Gotas Oftalmicas 0.5x5ml</t>
         </is>
       </c>
       <c r="C1406" t="inlineStr"/>
       <c r="D1406" t="inlineStr"/>
       <c r="E1406" t="n">
-        <v>37900</v>
+        <v>71000</v>
       </c>
       <c r="F1406" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1406" t="n">
         <v>0</v>
@@ -75326,25 +75326,21 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>Levotiroxina 100mcg MK</t>
-        </is>
-      </c>
-      <c r="C1407" t="inlineStr">
-        <is>
-          <t>7702057715908</t>
-        </is>
-      </c>
+          <t>LEVOMEPROMAZINA 25MG X 20 TABL HUMAX</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr"/>
       <c r="D1407" t="inlineStr"/>
       <c r="E1407" t="n">
-        <v>27900</v>
+        <v>37900</v>
       </c>
       <c r="F1407" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1407" t="n">
         <v>0</v>
@@ -75380,21 +75376,25 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>LIMA MAYOMI 10/180</t>
-        </is>
-      </c>
-      <c r="C1408" t="inlineStr"/>
+          <t>Levotiroxina 100mcg MK</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>7702057715908</t>
+        </is>
+      </c>
       <c r="D1408" t="inlineStr"/>
       <c r="E1408" t="n">
-        <v>3900</v>
+        <v>27900</v>
       </c>
       <c r="F1408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1408" t="n">
         <v>0</v>
@@ -75430,21 +75430,21 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
+          <t>LIMA MAYOMI 10/180</t>
         </is>
       </c>
       <c r="C1409" t="inlineStr"/>
       <c r="D1409" t="inlineStr"/>
       <c r="E1409" t="n">
-        <v>16807</v>
+        <v>3900</v>
       </c>
       <c r="F1409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1409" t="n">
         <v>0</v>
@@ -75472,7 +75472,7 @@
       </c>
       <c r="M1409" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1409" t="inlineStr"/>
@@ -75480,21 +75480,21 @@
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
+          <t>LIMPIADOR FACIAL DIARIO PONDS 50 GR</t>
         </is>
       </c>
       <c r="C1410" t="inlineStr"/>
       <c r="D1410" t="inlineStr"/>
       <c r="E1410" t="n">
-        <v>15042.016807</v>
+        <v>16807</v>
       </c>
       <c r="F1410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1410" t="n">
         <v>0</v>
@@ -75530,21 +75530,21 @@
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>LISTERINE CUIDADO TOTAL 180ML</t>
+          <t>LISTERINE ANTICARIES ZERO X 180ML</t>
         </is>
       </c>
       <c r="C1411" t="inlineStr"/>
       <c r="D1411" t="inlineStr"/>
       <c r="E1411" t="n">
-        <v>16386.554622</v>
+        <v>15042.016807</v>
       </c>
       <c r="F1411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1411" t="n">
         <v>0</v>
@@ -75580,21 +75580,21 @@
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
+          <t>LISTERINE CUIDADO TOTAL 180ML</t>
         </is>
       </c>
       <c r="C1412" t="inlineStr"/>
       <c r="D1412" t="inlineStr"/>
       <c r="E1412" t="n">
-        <v>3500</v>
+        <v>16386.554622</v>
       </c>
       <c r="F1412" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G1412" t="n">
         <v>0</v>
@@ -75622,7 +75622,7 @@
       </c>
       <c r="M1412" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1412" t="inlineStr"/>
@@ -75630,12 +75630,12 @@
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
+          <t>LOPERAMIDA 2MG X 6 TABL,DE ECAR</t>
         </is>
       </c>
       <c r="C1413" t="inlineStr"/>
@@ -75644,7 +75644,7 @@
         <v>3500</v>
       </c>
       <c r="F1413" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="G1413" t="n">
         <v>0</v>
@@ -75680,21 +75680,21 @@
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+          <t>LORATADINA 10MG SOBRE X 10 DE A.G</t>
         </is>
       </c>
       <c r="C1414" t="inlineStr"/>
       <c r="D1414" t="inlineStr"/>
       <c r="E1414" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="F1414" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1414" t="n">
         <v>0</v>
@@ -75730,25 +75730,21 @@
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>Losartan Tensofar 100 Mg</t>
-        </is>
-      </c>
-      <c r="C1415" t="inlineStr">
-        <is>
-          <t>7703546012119</t>
-        </is>
-      </c>
+          <t>LORATADINA TABLETA X 10MG DE LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr"/>
       <c r="D1415" t="inlineStr"/>
       <c r="E1415" t="n">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="F1415" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1415" t="n">
         <v>0</v>
@@ -75784,25 +75780,25 @@
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+          <t>Losartan Tensofar 100 Mg</t>
         </is>
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>7501007528939</t>
+          <t>7703546012119</t>
         </is>
       </c>
       <c r="D1416" t="inlineStr"/>
       <c r="E1416" t="n">
-        <v>18907.563025</v>
+        <v>5000</v>
       </c>
       <c r="F1416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1416" t="n">
         <v>0</v>
@@ -75830,7 +75826,7 @@
       </c>
       <c r="M1416" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1416" t="inlineStr"/>
@@ -75838,21 +75834,25 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>MANTECA DE CACAO LABIAL LIMON</t>
-        </is>
-      </c>
-      <c r="C1417" t="inlineStr"/>
+          <t>LUBRIDER/REPARACION INTENSIVA 120ML</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>7501007528939</t>
+        </is>
+      </c>
       <c r="D1417" t="inlineStr"/>
       <c r="E1417" t="n">
-        <v>3361.344538</v>
+        <v>18907.563025</v>
       </c>
       <c r="F1417" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1417" t="n">
         <v>0</v>
@@ -75888,12 +75888,12 @@
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
+          <t>MANTECA DE CACAO LABIAL LIMON</t>
         </is>
       </c>
       <c r="C1418" t="inlineStr"/>
@@ -75902,7 +75902,7 @@
         <v>3361.344538</v>
       </c>
       <c r="F1418" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1418" t="n">
         <v>0</v>
@@ -75938,21 +75938,21 @@
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>Mega sex</t>
+          <t>MASCARILLA NEGRA VITAL 10GR X UND</t>
         </is>
       </c>
       <c r="C1419" t="inlineStr"/>
       <c r="D1419" t="inlineStr"/>
       <c r="E1419" t="n">
-        <v>3200</v>
+        <v>3361.344538</v>
       </c>
       <c r="F1419" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G1419" t="n">
         <v>0</v>
@@ -75980,7 +75980,7 @@
       </c>
       <c r="M1419" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1419" t="inlineStr"/>
@@ -75988,29 +75988,21 @@
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>Melatonina 3mg</t>
-        </is>
-      </c>
-      <c r="C1420" t="inlineStr">
-        <is>
-          <t>7706849112906</t>
-        </is>
-      </c>
-      <c r="D1420" t="inlineStr">
-        <is>
-          <t>producto nuevo</t>
-        </is>
-      </c>
+          <t>Mega sex</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr"/>
+      <c r="D1420" t="inlineStr"/>
       <c r="E1420" t="n">
-        <v>52000</v>
+        <v>3200</v>
       </c>
       <c r="F1420" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G1420" t="n">
         <v>0</v>
@@ -76046,22 +76038,26 @@
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
+          <t>Melatonina 3mg</t>
         </is>
       </c>
       <c r="C1421" t="inlineStr">
         <is>
-          <t>7707529435209</t>
-        </is>
-      </c>
-      <c r="D1421" t="inlineStr"/>
+          <t>7706849112906</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>producto nuevo</t>
+        </is>
+      </c>
       <c r="E1421" t="n">
-        <v>36000</v>
+        <v>52000</v>
       </c>
       <c r="F1421" t="n">
         <v>0</v>
@@ -76100,22 +76096,22 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>Meloxicam 15mg AG</t>
+          <t>MELATONINA X 30 SOFTGEL TOTALMAX</t>
         </is>
       </c>
       <c r="C1422" t="inlineStr">
         <is>
-          <t>7706569020437</t>
+          <t>7707529435209</t>
         </is>
       </c>
       <c r="D1422" t="inlineStr"/>
       <c r="E1422" t="n">
-        <v>1500</v>
+        <v>36000</v>
       </c>
       <c r="F1422" t="n">
         <v>0</v>
@@ -76154,21 +76150,25 @@
     <row r="1423">
       <c r="A1423" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
-        </is>
-      </c>
-      <c r="C1423" t="inlineStr"/>
+          <t>Meloxicam 15mg AG</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>7706569020437</t>
+        </is>
+      </c>
       <c r="D1423" t="inlineStr"/>
       <c r="E1423" t="n">
-        <v>9700</v>
+        <v>1500</v>
       </c>
       <c r="F1423" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1423" t="n">
         <v>0</v>
@@ -76204,25 +76204,21 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>MELOXICAM COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1424" t="inlineStr">
-        <is>
-          <t>7703712036253</t>
-        </is>
-      </c>
+          <t>MELOXICAM 15MG/1.5MLX 1 AMP VITALIS</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr"/>
       <c r="D1424" t="inlineStr"/>
       <c r="E1424" t="n">
-        <v>1300</v>
+        <v>9700</v>
       </c>
       <c r="F1424" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1424" t="n">
         <v>0</v>
@@ -76248,31 +76244,35 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1424" t="inlineStr"/>
+      <c r="M1424" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="N1424" t="inlineStr"/>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>metformina 850 mg pisa</t>
+          <t>MELOXICAM COASPHARMA</t>
         </is>
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>7501125188039</t>
+          <t>7703712036253</t>
         </is>
       </c>
       <c r="D1425" t="inlineStr"/>
       <c r="E1425" t="n">
-        <v>5500</v>
+        <v>1300</v>
       </c>
       <c r="F1425" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G1425" t="n">
         <v>0</v>
@@ -76298,31 +76298,31 @@
           <t>active</t>
         </is>
       </c>
-      <c r="M1425" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="M1425" t="inlineStr"/>
       <c r="N1425" t="inlineStr"/>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>METOCARBAMOL 750MG SOBRE X 1O TBL LA SANTE</t>
-        </is>
-      </c>
-      <c r="C1426" t="inlineStr"/>
+          <t>metformina 850 mg pisa</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>7501125188039</t>
+        </is>
+      </c>
       <c r="D1426" t="inlineStr"/>
       <c r="E1426" t="n">
-        <v>13700</v>
+        <v>5500</v>
       </c>
       <c r="F1426" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G1426" t="n">
         <v>0</v>
@@ -76358,25 +76358,21 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>METOCLOPRAMIDA 10MG RECIPE</t>
-        </is>
-      </c>
-      <c r="C1427" t="inlineStr">
-        <is>
-          <t>7702195084355</t>
-        </is>
-      </c>
+          <t>METOCARBAMOL 750MG SOBRE X 1O TBL LA SANTE</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr"/>
       <c r="D1427" t="inlineStr"/>
       <c r="E1427" t="n">
-        <v>1000</v>
+        <v>13700</v>
       </c>
       <c r="F1427" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1427" t="n">
         <v>0</v>
@@ -76412,25 +76408,25 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>MICROPOR 1X3 Y</t>
+          <t>METOCLOPRAMIDA 10MG RECIPE</t>
         </is>
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>7707282990205</t>
+          <t>7702195084355</t>
         </is>
       </c>
       <c r="D1428" t="inlineStr"/>
       <c r="E1428" t="n">
-        <v>5300</v>
+        <v>1000</v>
       </c>
       <c r="F1428" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1428" t="n">
         <v>0</v>
@@ -76466,25 +76462,25 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>MICROPOR CINTA 1/2X5Y</t>
+          <t>MICROPOR 1X3 Y</t>
         </is>
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>7707282990182</t>
+          <t>7707282990205</t>
         </is>
       </c>
       <c r="D1429" t="inlineStr"/>
       <c r="E1429" t="n">
-        <v>3900</v>
+        <v>5300</v>
       </c>
       <c r="F1429" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G1429" t="n">
         <v>0</v>
@@ -76520,21 +76516,25 @@
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>MICROPORE COLOR PIEL 2YARDAS</t>
-        </is>
-      </c>
-      <c r="C1430" t="inlineStr"/>
+          <t>MICROPOR CINTA 1/2X5Y</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>7707282990182</t>
+        </is>
+      </c>
       <c r="D1430" t="inlineStr"/>
       <c r="E1430" t="n">
-        <v>3700</v>
+        <v>3900</v>
       </c>
       <c r="F1430" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G1430" t="n">
         <v>0</v>
@@ -76570,21 +76570,21 @@
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
+          <t>MICROPORE COLOR PIEL 2YARDAS</t>
         </is>
       </c>
       <c r="C1431" t="inlineStr"/>
       <c r="D1431" t="inlineStr"/>
       <c r="E1431" t="n">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="F1431" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1431" t="n">
         <v>0</v>
@@ -76620,25 +76620,21 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>MIELTERTOS JARABE X 240ML</t>
-        </is>
-      </c>
-      <c r="C1432" t="inlineStr">
-        <is>
-          <t>7707232095608</t>
-        </is>
-      </c>
+          <t>MIEL DE ROSAS FCO X 30ML -DROGAM</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr"/>
       <c r="D1432" t="inlineStr"/>
       <c r="E1432" t="n">
-        <v>34500</v>
+        <v>4000</v>
       </c>
       <c r="F1432" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1432" t="n">
         <v>0</v>
@@ -76674,21 +76670,25 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>MOÑA CAUCHO TELEFONO</t>
-        </is>
-      </c>
-      <c r="C1433" t="inlineStr"/>
+          <t>MIELTERTOS JARABE X 240ML</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>7707232095608</t>
+        </is>
+      </c>
       <c r="D1433" t="inlineStr"/>
       <c r="E1433" t="n">
-        <v>5000</v>
+        <v>34500</v>
       </c>
       <c r="F1433" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1433" t="n">
         <v>0</v>
@@ -76724,21 +76724,21 @@
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>MOÑAS PARA EL PELO COLOR YIMEIJIA</t>
+          <t>MOÑA CAUCHO TELEFONO</t>
         </is>
       </c>
       <c r="C1434" t="inlineStr"/>
       <c r="D1434" t="inlineStr"/>
       <c r="E1434" t="n">
-        <v>4201.680672</v>
+        <v>5000</v>
       </c>
       <c r="F1434" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1434" t="n">
         <v>0</v>
@@ -76766,7 +76766,7 @@
       </c>
       <c r="M1434" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1434" t="inlineStr"/>
@@ -76774,25 +76774,21 @@
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
+          <t>MOÑAS PARA EL PELO COLOR YIMEIJIA</t>
         </is>
       </c>
       <c r="C1435" t="inlineStr"/>
-      <c r="D1435" t="inlineStr">
-        <is>
-          <t>subio precio hector</t>
-        </is>
-      </c>
+      <c r="D1435" t="inlineStr"/>
       <c r="E1435" t="n">
-        <v>22700</v>
+        <v>4201.680672</v>
       </c>
       <c r="F1435" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1435" t="n">
         <v>0</v>
@@ -76820,7 +76816,7 @@
       </c>
       <c r="M1435" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1435" t="inlineStr"/>
@@ -76828,21 +76824,25 @@
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
+          <t>MONURIL SOBRE 3 GR FOSFOMICINA</t>
         </is>
       </c>
       <c r="C1436" t="inlineStr"/>
-      <c r="D1436" t="inlineStr"/>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>subio precio hector</t>
+        </is>
+      </c>
       <c r="E1436" t="n">
-        <v>5500</v>
+        <v>22700</v>
       </c>
       <c r="F1436" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G1436" t="n">
         <v>0</v>
@@ -76878,21 +76878,21 @@
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>NEOSALDINA TABLETA X UND</t>
+          <t>NAPROXENO 500MG SOBRE X 10 DE LAPROFF</t>
         </is>
       </c>
       <c r="C1437" t="inlineStr"/>
       <c r="D1437" t="inlineStr"/>
       <c r="E1437" t="n">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="F1437" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G1437" t="n">
         <v>0</v>
@@ -76928,21 +76928,21 @@
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>NIFEDIPINO 30MG NOVAMED</t>
+          <t>NEOSALDINA TABLETA X UND</t>
         </is>
       </c>
       <c r="C1438" t="inlineStr"/>
       <c r="D1438" t="inlineStr"/>
       <c r="E1438" t="n">
-        <v>19000</v>
+        <v>2500</v>
       </c>
       <c r="F1438" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G1438" t="n">
         <v>0</v>
@@ -76978,21 +76978,21 @@
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
+          <t>NIFEDIPINO 30MG NOVAMED</t>
         </is>
       </c>
       <c r="C1439" t="inlineStr"/>
       <c r="D1439" t="inlineStr"/>
       <c r="E1439" t="n">
-        <v>23000</v>
+        <v>19000</v>
       </c>
       <c r="F1439" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1439" t="n">
         <v>0</v>
@@ -77028,21 +77028,21 @@
     <row r="1440">
       <c r="A1440" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>NITOXIPAR X 6 TABLETAS</t>
+          <t>NITOXIPAR 100MG/5ML SUSP X 30ML</t>
         </is>
       </c>
       <c r="C1440" t="inlineStr"/>
       <c r="D1440" t="inlineStr"/>
       <c r="E1440" t="n">
-        <v>24500</v>
+        <v>23000</v>
       </c>
       <c r="F1440" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1440" t="n">
         <v>0</v>
@@ -77078,18 +77078,18 @@
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>NORAVER SPRAY CEREZA 120ML</t>
+          <t>NITOXIPAR X 6 TABLETAS</t>
         </is>
       </c>
       <c r="C1441" t="inlineStr"/>
       <c r="D1441" t="inlineStr"/>
       <c r="E1441" t="n">
-        <v>52900</v>
+        <v>24500</v>
       </c>
       <c r="F1441" t="n">
         <v>1</v>
@@ -77128,25 +77128,21 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
-        </is>
-      </c>
-      <c r="C1442" t="inlineStr">
-        <is>
-          <t>7702027041662</t>
-        </is>
-      </c>
+          <t>NORAVER SPRAY CEREZA 120ML</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr"/>
       <c r="D1442" t="inlineStr"/>
       <c r="E1442" t="n">
-        <v>6300</v>
+        <v>52900</v>
       </c>
       <c r="F1442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1442" t="n">
         <v>0</v>
@@ -77182,18 +77178,22 @@
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>NOSOTRAS JABON INTIMO X 200ML</t>
-        </is>
-      </c>
-      <c r="C1443" t="inlineStr"/>
+          <t>NOSOTRAS CLASICAS X 10 TOALLAS</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>7702027041662</t>
+        </is>
+      </c>
       <c r="D1443" t="inlineStr"/>
       <c r="E1443" t="n">
-        <v>8823.529412</v>
+        <v>6300</v>
       </c>
       <c r="F1443" t="n">
         <v>0</v>
@@ -77224,7 +77224,7 @@
       </c>
       <c r="M1443" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1443" t="inlineStr"/>
@@ -77232,7 +77232,7 @@
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
@@ -77240,11 +77240,7 @@
           <t>NOSOTRAS JABON INTIMO X 200ML</t>
         </is>
       </c>
-      <c r="C1444" t="inlineStr">
-        <is>
-          <t>7702026158644</t>
-        </is>
-      </c>
+      <c r="C1444" t="inlineStr"/>
       <c r="D1444" t="inlineStr"/>
       <c r="E1444" t="n">
         <v>8823.529412</v>
@@ -77286,25 +77282,25 @@
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JBE 120ML</t>
+          <t>NOSOTRAS JABON INTIMO X 200ML</t>
         </is>
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>7707355053363</t>
+          <t>7702026158644</t>
         </is>
       </c>
       <c r="D1445" t="inlineStr"/>
       <c r="E1445" t="n">
-        <v>22700</v>
+        <v>8823.529412</v>
       </c>
       <c r="F1445" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1445" t="n">
         <v>0</v>
@@ -77332,7 +77328,7 @@
       </c>
       <c r="M1445" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1445" t="inlineStr"/>
@@ -77340,25 +77336,25 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+          <t>NOXPIRIN JUNIOR JBE 120ML</t>
         </is>
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>7707355053356</t>
+          <t>7707355053363</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr"/>
       <c r="E1446" t="n">
-        <v>17200</v>
+        <v>22700</v>
       </c>
       <c r="F1446" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1446" t="n">
         <v>0</v>
@@ -77394,21 +77390,25 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>NUTRIBELL ACEITE DE COCO</t>
-        </is>
-      </c>
-      <c r="C1447" t="inlineStr"/>
+          <t>NOXPIRIN JUNIOR JRB X 60ML</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>7707355053356</t>
+        </is>
+      </c>
       <c r="D1447" t="inlineStr"/>
       <c r="E1447" t="n">
-        <v>2700</v>
+        <v>17200</v>
       </c>
       <c r="F1447" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1447" t="n">
         <v>0</v>
@@ -77444,29 +77444,21 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>Omega 3 6 9 suplemento totalmax</t>
-        </is>
-      </c>
-      <c r="C1448" t="inlineStr">
-        <is>
-          <t>7707529434974</t>
-        </is>
-      </c>
-      <c r="D1448" t="inlineStr">
-        <is>
-          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
-        </is>
-      </c>
+          <t>NUTRIBELL ACEITE DE COCO</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr"/>
+      <c r="D1448" t="inlineStr"/>
       <c r="E1448" t="n">
-        <v>35000</v>
+        <v>2700</v>
       </c>
       <c r="F1448" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1448" t="n">
         <v>0</v>
@@ -77502,21 +77494,29 @@
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
-        </is>
-      </c>
-      <c r="C1449" t="inlineStr"/>
-      <c r="D1449" t="inlineStr"/>
+          <t>Omega 3 6 9 suplemento totalmax</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>7707529434974</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>SE AUNMENTA PRECIO A 35000 ANTES ESTABA EN 26000/LEYDI</t>
+        </is>
+      </c>
       <c r="E1449" t="n">
-        <v>5500</v>
+        <v>35000</v>
       </c>
       <c r="F1449" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1449" t="n">
         <v>0</v>
@@ -77552,22 +77552,18 @@
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
-        </is>
-      </c>
-      <c r="C1450" t="inlineStr">
-        <is>
-          <t>7707529435940</t>
-        </is>
-      </c>
+          <t>OMEPRAZOL 20MG X 10 CAPS DE GENFAR</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr"/>
       <c r="D1450" t="inlineStr"/>
       <c r="E1450" t="n">
-        <v>35000</v>
+        <v>5500</v>
       </c>
       <c r="F1450" t="n">
         <v>0</v>
@@ -77606,21 +77602,25 @@
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
-        </is>
-      </c>
-      <c r="C1451" t="inlineStr"/>
+          <t>OREGANO X 3O CAPS DE TOTAL MAX</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>7707529435940</t>
+        </is>
+      </c>
       <c r="D1451" t="inlineStr"/>
       <c r="E1451" t="n">
-        <v>48000</v>
+        <v>35000</v>
       </c>
       <c r="F1451" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1451" t="n">
         <v>0</v>
@@ -77656,25 +77656,21 @@
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>OROCAL CALCIO 600MG</t>
+          <t>OREGANO X 60 CAPSULAS DE ARMONIZA</t>
         </is>
       </c>
       <c r="C1452" t="inlineStr"/>
-      <c r="D1452" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="D1452" t="inlineStr"/>
       <c r="E1452" t="n">
-        <v>30500</v>
+        <v>48000</v>
       </c>
       <c r="F1452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1452" t="n">
         <v>0</v>
@@ -77710,18 +77706,22 @@
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>PALA DE MADERA RASPACALLO</t>
+          <t>OROCAL CALCIO 600MG</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr"/>
-      <c r="D1453" t="inlineStr"/>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E1453" t="n">
-        <v>4000</v>
+        <v>30500</v>
       </c>
       <c r="F1453" t="n">
         <v>1</v>
@@ -77760,21 +77760,21 @@
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>PALO DE NARANJO X UNIDAD</t>
+          <t>PALA DE MADERA RASPACALLO</t>
         </is>
       </c>
       <c r="C1454" t="inlineStr"/>
       <c r="D1454" t="inlineStr"/>
       <c r="E1454" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="F1454" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G1454" t="n">
         <v>0</v>
@@ -77810,25 +77810,21 @@
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
-        </is>
-      </c>
-      <c r="C1455" t="inlineStr">
-        <is>
-          <t>7704412170896</t>
-        </is>
-      </c>
+          <t>PALO DE NARANJO X UNIDAD</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr"/>
       <c r="D1455" t="inlineStr"/>
       <c r="E1455" t="n">
-        <v>6200</v>
+        <v>400</v>
       </c>
       <c r="F1455" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G1455" t="n">
         <v>0</v>
@@ -77864,18 +77860,22 @@
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
-        </is>
-      </c>
-      <c r="C1456" t="inlineStr"/>
+          <t>pamoato de pirantel 5% 15ml suspensión oral memphis</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>7704412170896</t>
+        </is>
+      </c>
       <c r="D1456" t="inlineStr"/>
       <c r="E1456" t="n">
-        <v>14285.714286</v>
+        <v>6200</v>
       </c>
       <c r="F1456" t="n">
         <v>1</v>
@@ -77906,7 +77906,7 @@
       </c>
       <c r="M1456" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1456" t="inlineStr"/>
@@ -77914,18 +77914,18 @@
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
+          <t>PAÑAL WINNY ETAPA 1 X 16 UNDS</t>
         </is>
       </c>
       <c r="C1457" t="inlineStr"/>
       <c r="D1457" t="inlineStr"/>
       <c r="E1457" t="n">
-        <v>28991.596639</v>
+        <v>14285.714286</v>
       </c>
       <c r="F1457" t="n">
         <v>1</v>
@@ -77964,18 +77964,18 @@
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+          <t>PAÑAL WINNY ETAPA 2X 30 UND</t>
         </is>
       </c>
       <c r="C1458" t="inlineStr"/>
       <c r="D1458" t="inlineStr"/>
       <c r="E1458" t="n">
-        <v>41176.470588</v>
+        <v>28991.596639</v>
       </c>
       <c r="F1458" t="n">
         <v>1</v>
@@ -78014,22 +78014,18 @@
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Pañales Winny Etapa 5 X PAQUETE</t>
-        </is>
-      </c>
-      <c r="C1459" t="inlineStr">
-        <is>
-          <t>7701021114174</t>
-        </is>
-      </c>
+          <t>PAÑAL WINNY ETP 4 X 30 UND</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr"/>
       <c r="D1459" t="inlineStr"/>
       <c r="E1459" t="n">
-        <v>41849</v>
+        <v>41176.470588</v>
       </c>
       <c r="F1459" t="n">
         <v>1</v>
@@ -78068,21 +78064,25 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>PAÑALWINNY ETA 5 X 16 UND</t>
-        </is>
-      </c>
-      <c r="C1460" t="inlineStr"/>
+          <t>Pañales Winny Etapa 5 X PAQUETE</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>7701021114174</t>
+        </is>
+      </c>
       <c r="D1460" t="inlineStr"/>
       <c r="E1460" t="n">
-        <v>24369.747899</v>
+        <v>41849</v>
       </c>
       <c r="F1460" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1460" t="n">
         <v>0</v>
@@ -78118,21 +78118,21 @@
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>pañitos humedos pequeñin 100unidades</t>
+          <t>PAÑALWINNY ETA 5 X 16 UND</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr"/>
       <c r="D1461" t="inlineStr"/>
       <c r="E1461" t="n">
-        <v>10925</v>
+        <v>24369.747899</v>
       </c>
       <c r="F1461" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1461" t="n">
         <v>0</v>
@@ -78168,21 +78168,21 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
+          <t>pañitos humedos pequeñin 100unidades</t>
         </is>
       </c>
       <c r="C1462" t="inlineStr"/>
       <c r="D1462" t="inlineStr"/>
       <c r="E1462" t="n">
-        <v>14900</v>
+        <v>10925</v>
       </c>
       <c r="F1462" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1462" t="n">
         <v>0</v>
@@ -78210,7 +78210,7 @@
       </c>
       <c r="M1462" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1462" t="inlineStr"/>
@@ -78218,21 +78218,21 @@
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Panotil B x 8ML</t>
+          <t>PAÑITOS HUMEDOS PEQUEÑIN PAQ X 100 UND</t>
         </is>
       </c>
       <c r="C1463" t="inlineStr"/>
       <c r="D1463" t="inlineStr"/>
       <c r="E1463" t="n">
-        <v>26400</v>
+        <v>14900</v>
       </c>
       <c r="F1463" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1463" t="n">
         <v>0</v>
@@ -78268,25 +78268,21 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>PANTENE ACONDICIONADOR</t>
-        </is>
-      </c>
-      <c r="C1464" t="inlineStr">
-        <is>
-          <t>7500435153683</t>
-        </is>
-      </c>
+          <t>Panotil B x 8ML</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr"/>
       <c r="D1464" t="inlineStr"/>
       <c r="E1464" t="n">
-        <v>1500</v>
+        <v>26400</v>
       </c>
       <c r="F1464" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1464" t="n">
         <v>0</v>
@@ -78322,25 +78318,25 @@
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>PARCHE ACNE FIGURAS</t>
+          <t>PANTENE ACONDICIONADOR</t>
         </is>
       </c>
       <c r="C1465" t="inlineStr">
         <is>
-          <t>6971622250767</t>
+          <t>7500435153683</t>
         </is>
       </c>
       <c r="D1465" t="inlineStr"/>
       <c r="E1465" t="n">
-        <v>5882.352941</v>
+        <v>1500</v>
       </c>
       <c r="F1465" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G1465" t="n">
         <v>0</v>
@@ -78368,7 +78364,7 @@
       </c>
       <c r="M1465" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1465" t="inlineStr"/>
@@ -78376,21 +78372,25 @@
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Parche Ocular Colostol</t>
-        </is>
-      </c>
-      <c r="C1466" t="inlineStr"/>
+          <t>PARCHE ACNE FIGURAS</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>6971622250767</t>
+        </is>
+      </c>
       <c r="D1466" t="inlineStr"/>
       <c r="E1466" t="n">
-        <v>1300</v>
+        <v>5882.352941</v>
       </c>
       <c r="F1466" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G1466" t="n">
         <v>0</v>
@@ -78418,7 +78418,7 @@
       </c>
       <c r="M1466" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1466" t="inlineStr"/>
@@ -78426,21 +78426,21 @@
     <row r="1467">
       <c r="A1467" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>PARCHE PARA EL ACNE</t>
+          <t>Parche Ocular Colostol</t>
         </is>
       </c>
       <c r="C1467" t="inlineStr"/>
       <c r="D1467" t="inlineStr"/>
       <c r="E1467" t="n">
-        <v>7000</v>
+        <v>1300</v>
       </c>
       <c r="F1467" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G1467" t="n">
         <v>0</v>
@@ -78476,25 +78476,21 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
-        </is>
-      </c>
-      <c r="C1468" t="inlineStr">
-        <is>
-          <t>7501033957413</t>
-        </is>
-      </c>
+          <t>PARCHE PARA EL ACNE</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr"/>
       <c r="D1468" t="inlineStr"/>
       <c r="E1468" t="n">
-        <v>10600</v>
+        <v>7000</v>
       </c>
       <c r="F1468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1468" t="n">
         <v>0</v>
@@ -78530,26 +78526,22 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
+          <t>PEDIALYTE ACTIVE 45MEQ FRESA</t>
         </is>
       </c>
       <c r="C1469" t="inlineStr">
         <is>
-          <t>7501033961557</t>
-        </is>
-      </c>
-      <c r="D1469" t="inlineStr">
-        <is>
-          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
-        </is>
-      </c>
+          <t>7501033957413</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr"/>
       <c r="E1469" t="n">
-        <v>10900</v>
+        <v>10600</v>
       </c>
       <c r="F1469" t="n">
         <v>0</v>
@@ -78588,29 +78580,29 @@
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+          <t>PEDIALYTE MAX 60MEP CON ZIN FRESA</t>
         </is>
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>7501033957376</t>
+          <t>7501033961557</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">
         <is>
-          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+          <t>SE CAMBIO EL PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI.</t>
         </is>
       </c>
       <c r="E1470" t="n">
         <v>10900</v>
       </c>
       <c r="F1470" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1470" t="n">
         <v>0</v>
@@ -78646,21 +78638,29 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>PEGANTE GLUE X 10GR X UND</t>
-        </is>
-      </c>
-      <c r="C1471" t="inlineStr"/>
-      <c r="D1471" t="inlineStr"/>
+          <t>PEDIALYTE MAX 60MEQ CON ZINC UVA</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>7501033957376</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>SE SUBIO DE PRECIO PORQUE ESTABA EN 10.600 Y SUBIO A 10.900 LEYDI...</t>
+        </is>
+      </c>
       <c r="E1471" t="n">
-        <v>2000</v>
+        <v>10900</v>
       </c>
       <c r="F1471" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1471" t="n">
         <v>0</v>
@@ -78696,21 +78696,21 @@
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>PEINETA COLA DE RATON METALICA</t>
+          <t>PEGANTE GLUE X 10GR X UND</t>
         </is>
       </c>
       <c r="C1472" t="inlineStr"/>
       <c r="D1472" t="inlineStr"/>
       <c r="E1472" t="n">
-        <v>4700</v>
+        <v>2000</v>
       </c>
       <c r="F1472" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1472" t="n">
         <v>0</v>
@@ -78746,18 +78746,18 @@
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>PERFILADORES DE CEJAS</t>
+          <t>PEINETA COLA DE RATON METALICA</t>
         </is>
       </c>
       <c r="C1473" t="inlineStr"/>
       <c r="D1473" t="inlineStr"/>
       <c r="E1473" t="n">
-        <v>3900</v>
+        <v>4700</v>
       </c>
       <c r="F1473" t="n">
         <v>1</v>
@@ -78796,18 +78796,18 @@
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
+          <t>PERFILADORES DE CEJAS</t>
         </is>
       </c>
       <c r="C1474" t="inlineStr"/>
       <c r="D1474" t="inlineStr"/>
       <c r="E1474" t="n">
-        <v>27983.193277</v>
+        <v>3900</v>
       </c>
       <c r="F1474" t="n">
         <v>1</v>
@@ -78838,7 +78838,7 @@
       </c>
       <c r="M1474" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1474" t="inlineStr"/>
@@ -78846,21 +78846,21 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>POPETAS SURTIDAS X UND</t>
+          <t>POLVOS COMPACTO ANA MARIA SURTIDOS</t>
         </is>
       </c>
       <c r="C1475" t="inlineStr"/>
       <c r="D1475" t="inlineStr"/>
       <c r="E1475" t="n">
-        <v>2521.008403</v>
+        <v>27983.193277</v>
       </c>
       <c r="F1475" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1475" t="n">
         <v>0</v>
@@ -78896,21 +78896,21 @@
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+          <t>POPETAS SURTIDAS X UND</t>
         </is>
       </c>
       <c r="C1476" t="inlineStr"/>
       <c r="D1476" t="inlineStr"/>
       <c r="E1476" t="n">
-        <v>20500</v>
+        <v>2521.008403</v>
       </c>
       <c r="F1476" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1476" t="n">
         <v>0</v>
@@ -78938,7 +78938,7 @@
       </c>
       <c r="M1476" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1476" t="inlineStr"/>
@@ -78946,26 +78946,18 @@
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>privatos miel limon la francol 120ml</t>
-        </is>
-      </c>
-      <c r="C1477" t="inlineStr">
-        <is>
-          <t>7702207163948</t>
-        </is>
-      </c>
-      <c r="D1477" t="inlineStr">
-        <is>
-          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
-        </is>
-      </c>
+          <t>POSTDAY 0.75MG CJA X 2 TABLE</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr"/>
+      <c r="D1477" t="inlineStr"/>
       <c r="E1477" t="n">
-        <v>35900</v>
+        <v>20500</v>
       </c>
       <c r="F1477" t="n">
         <v>0</v>
@@ -79004,18 +78996,26 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
-        </is>
-      </c>
-      <c r="C1478" t="inlineStr"/>
-      <c r="D1478" t="inlineStr"/>
+          <t>privatos miel limon la francol 120ml</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>7702207163948</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>SUBIO A 35900 ANTES 24500/LEYDI</t>
+        </is>
+      </c>
       <c r="E1478" t="n">
-        <v>0</v>
+        <v>35900</v>
       </c>
       <c r="F1478" t="n">
         <v>0</v>
@@ -79046,7 +79046,7 @@
       </c>
       <c r="M1478" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1478" t="inlineStr"/>
@@ -79054,21 +79054,21 @@
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>778</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>PROTECTOR NOSOTRAS LARGOS</t>
+          <t>productogenericonube - Producto genérico del sistema Siigo Nube (POS - WhatsApp)</t>
         </is>
       </c>
       <c r="C1479" t="inlineStr"/>
       <c r="D1479" t="inlineStr"/>
       <c r="E1479" t="n">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="F1479" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1479" t="n">
         <v>0</v>
@@ -79096,7 +79096,7 @@
       </c>
       <c r="M1479" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1479" t="inlineStr"/>
@@ -79104,18 +79104,18 @@
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
+          <t>PROTECTOR NOSOTRAS LARGOS</t>
         </is>
       </c>
       <c r="C1480" t="inlineStr"/>
       <c r="D1480" t="inlineStr"/>
       <c r="E1480" t="n">
-        <v>8900</v>
+        <v>3700</v>
       </c>
       <c r="F1480" t="n">
         <v>1</v>
@@ -79154,21 +79154,21 @@
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>Protector Solar Sunaid</t>
+          <t>PROTECTOR SOLAR SUN NOW X 10GR SACHET</t>
         </is>
       </c>
       <c r="C1481" t="inlineStr"/>
       <c r="D1481" t="inlineStr"/>
       <c r="E1481" t="n">
-        <v>158000</v>
+        <v>8900</v>
       </c>
       <c r="F1481" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1481" t="n">
         <v>0</v>
@@ -79204,25 +79204,21 @@
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>Prueba de embarazo esfero</t>
-        </is>
-      </c>
-      <c r="C1482" t="inlineStr">
-        <is>
-          <t>7709299854228</t>
-        </is>
-      </c>
+          <t>Protector Solar Sunaid</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr"/>
       <c r="D1482" t="inlineStr"/>
       <c r="E1482" t="n">
-        <v>16500</v>
+        <v>158000</v>
       </c>
       <c r="F1482" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1482" t="n">
         <v>0</v>
@@ -79258,25 +79254,25 @@
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>Prueba de embarazo HCG cassette begut</t>
+          <t>Prueba de embarazo esfero</t>
         </is>
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>7707282990953</t>
+          <t>7709299854228</t>
         </is>
       </c>
       <c r="D1483" t="inlineStr"/>
       <c r="E1483" t="n">
-        <v>8900</v>
+        <v>16500</v>
       </c>
       <c r="F1483" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G1483" t="n">
         <v>0</v>
@@ -79312,21 +79308,25 @@
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>PUSHER METALICO</t>
-        </is>
-      </c>
-      <c r="C1484" t="inlineStr"/>
+          <t>Prueba de embarazo HCG cassette begut</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>7707282990953</t>
+        </is>
+      </c>
       <c r="D1484" t="inlineStr"/>
       <c r="E1484" t="n">
-        <v>4300</v>
+        <v>8900</v>
       </c>
       <c r="F1484" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1484" t="n">
         <v>0</v>
@@ -79362,21 +79362,21 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
+          <t>PUSHER METALICO</t>
         </is>
       </c>
       <c r="C1485" t="inlineStr"/>
       <c r="D1485" t="inlineStr"/>
       <c r="E1485" t="n">
-        <v>17900</v>
+        <v>4300</v>
       </c>
       <c r="F1485" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1485" t="n">
         <v>0</v>
@@ -79412,25 +79412,21 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>Recolector de orina granandina</t>
-        </is>
-      </c>
-      <c r="C1486" t="inlineStr">
-        <is>
-          <t>7707233050590</t>
-        </is>
-      </c>
+          <t>QUETIAPINA 100MG SOBRE X 10 HUMAX</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr"/>
       <c r="D1486" t="inlineStr"/>
       <c r="E1486" t="n">
-        <v>673</v>
+        <v>17900</v>
       </c>
       <c r="F1486" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="G1486" t="n">
         <v>0</v>
@@ -79458,7 +79454,7 @@
       </c>
       <c r="M1486" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1486" t="inlineStr"/>
@@ -79466,21 +79462,25 @@
     <row r="1487">
       <c r="A1487" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
-        </is>
-      </c>
-      <c r="C1487" t="inlineStr"/>
+          <t>Recolector de orina granandina</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>7707233050590</t>
+        </is>
+      </c>
       <c r="D1487" t="inlineStr"/>
       <c r="E1487" t="n">
-        <v>3820</v>
+        <v>673</v>
       </c>
       <c r="F1487" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="G1487" t="n">
         <v>0</v>
@@ -79508,7 +79508,7 @@
       </c>
       <c r="M1487" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1487" t="inlineStr"/>
@@ -79516,21 +79516,21 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>RegistroManual - Registro manual</t>
+          <t>RECOLECTOR GUARDIAN 1.5 LITROS</t>
         </is>
       </c>
       <c r="C1488" t="inlineStr"/>
       <c r="D1488" t="inlineStr"/>
       <c r="E1488" t="n">
-        <v>0</v>
+        <v>3820</v>
       </c>
       <c r="F1488" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1488" t="n">
         <v>0</v>
@@ -79558,7 +79558,7 @@
       </c>
       <c r="M1488" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1488" t="inlineStr"/>
@@ -79566,21 +79566,21 @@
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>780</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>REMOVEDOR DE ESMALTE 60CC</t>
+          <t>RegistroManual - Registro manual</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr"/>
       <c r="D1489" t="inlineStr"/>
       <c r="E1489" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="F1489" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1489" t="n">
         <v>0</v>
@@ -79608,7 +79608,7 @@
       </c>
       <c r="M1489" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1489" t="inlineStr"/>
@@ -79616,25 +79616,21 @@
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
-        </is>
-      </c>
-      <c r="C1490" t="inlineStr">
-        <is>
-          <t>7591005981270</t>
-        </is>
-      </c>
+          <t>REMOVEDOR DE ESMALTE 60CC</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr"/>
       <c r="D1490" t="inlineStr"/>
       <c r="E1490" t="n">
-        <v>9500</v>
+        <v>3500</v>
       </c>
       <c r="F1490" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1490" t="n">
         <v>0</v>
@@ -79670,22 +79666,22 @@
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
+          <t>REPELENTE AUTAN FAMYLY CREMA 60 GR</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>7503051868245</t>
+          <t>7591005981270</t>
         </is>
       </c>
       <c r="D1491" t="inlineStr"/>
       <c r="E1491" t="n">
-        <v>20900</v>
+        <v>9500</v>
       </c>
       <c r="F1491" t="n">
         <v>1</v>
@@ -79724,25 +79720,25 @@
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+          <t>REPELENTE AUTAN SPRAY ADULTO 100ML8</t>
         </is>
       </c>
       <c r="C1492" t="inlineStr">
         <is>
-          <t>7702057079642</t>
+          <t>7503051868245</t>
         </is>
       </c>
       <c r="D1492" t="inlineStr"/>
       <c r="E1492" t="n">
-        <v>13000</v>
+        <v>20900</v>
       </c>
       <c r="F1492" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1492" t="n">
         <v>0</v>
@@ -79778,18 +79774,22 @@
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>Ryaltris Spray Nasal 240 dosis</t>
-        </is>
-      </c>
-      <c r="C1493" t="inlineStr"/>
+          <t>RISPERIDONA 1MG X 20 TABL MK</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>7702057079642</t>
+        </is>
+      </c>
       <c r="D1493" t="inlineStr"/>
       <c r="E1493" t="n">
-        <v>216400</v>
+        <v>13000</v>
       </c>
       <c r="F1493" t="n">
         <v>0</v>
@@ -79828,25 +79828,21 @@
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
-        </is>
-      </c>
-      <c r="C1494" t="inlineStr">
-        <is>
-          <t>7706849116676</t>
-        </is>
-      </c>
+          <t>Ryaltris Spray Nasal 240 dosis</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr"/>
       <c r="D1494" t="inlineStr"/>
       <c r="E1494" t="n">
-        <v>31500</v>
+        <v>216400</v>
       </c>
       <c r="F1494" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1494" t="n">
         <v>0</v>
@@ -79882,21 +79878,25 @@
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>SCOBIT PURGANTE 60GR</t>
-        </is>
-      </c>
-      <c r="C1495" t="inlineStr"/>
+          <t>SANGRE DE DRAGO GTS FCO X 60ML FUNAT</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>7706849116676</t>
+        </is>
+      </c>
       <c r="D1495" t="inlineStr"/>
       <c r="E1495" t="n">
-        <v>15238.095238</v>
+        <v>31500</v>
       </c>
       <c r="F1495" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1495" t="n">
         <v>0</v>
@@ -79924,7 +79924,7 @@
       </c>
       <c r="M1495" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1495" t="inlineStr"/>
@@ -79932,21 +79932,21 @@
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
+          <t>SCOBIT PURGANTE 60GR</t>
         </is>
       </c>
       <c r="C1496" t="inlineStr"/>
       <c r="D1496" t="inlineStr"/>
       <c r="E1496" t="n">
-        <v>6554.621849</v>
+        <v>15238.095238</v>
       </c>
       <c r="F1496" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1496" t="n">
         <v>0</v>
@@ -79974,7 +79974,7 @@
       </c>
       <c r="M1496" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N1496" t="inlineStr"/>
@@ -79982,25 +79982,21 @@
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>SHAMPOO PANTENE COLAGENO</t>
-        </is>
-      </c>
-      <c r="C1497" t="inlineStr">
-        <is>
-          <t>7500435191500</t>
-        </is>
-      </c>
+          <t>SEDA DENTAL SONRIDENT X 50 MTR</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr"/>
       <c r="D1497" t="inlineStr"/>
       <c r="E1497" t="n">
-        <v>1429</v>
+        <v>6554.621849</v>
       </c>
       <c r="F1497" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1497" t="n">
         <v>0</v>
@@ -80036,21 +80032,25 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>SILDENAFIL 50MG TQ</t>
-        </is>
-      </c>
-      <c r="C1498" t="inlineStr"/>
+          <t>SHAMPOO PANTENE COLAGENO</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>7500435191500</t>
+        </is>
+      </c>
       <c r="D1498" t="inlineStr"/>
       <c r="E1498" t="n">
-        <v>5000</v>
+        <v>1429</v>
       </c>
       <c r="F1498" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1498" t="n">
         <v>0</v>
@@ -80078,7 +80078,7 @@
       </c>
       <c r="M1498" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1498" t="inlineStr"/>
@@ -80086,25 +80086,21 @@
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>SILIMARINA 167MG EPANAT</t>
-        </is>
-      </c>
-      <c r="C1499" t="inlineStr">
-        <is>
-          <t>7706849115921</t>
-        </is>
-      </c>
+          <t>SILDENAFIL 50MG TQ</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr"/>
       <c r="D1499" t="inlineStr"/>
       <c r="E1499" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F1499" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G1499" t="n">
         <v>0</v>
@@ -80140,21 +80136,25 @@
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>SMECTA 3GR NARANJA S/B</t>
-        </is>
-      </c>
-      <c r="C1500" t="inlineStr"/>
+          <t>SILIMARINA 167MG EPANAT</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>7706849115921</t>
+        </is>
+      </c>
       <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="n">
-        <v>8900</v>
+        <v>2000</v>
       </c>
       <c r="F1500" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G1500" t="n">
         <v>0</v>
@@ -80190,21 +80190,21 @@
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>SONDA FOLEY 2 VIAS BAL #18</t>
+          <t>SMECTA 3GR NARANJA S/B</t>
         </is>
       </c>
       <c r="C1501" t="inlineStr"/>
       <c r="D1501" t="inlineStr"/>
       <c r="E1501" t="n">
-        <v>7500</v>
+        <v>8900</v>
       </c>
       <c r="F1501" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1501" t="n">
         <v>0</v>
@@ -80240,21 +80240,21 @@
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>SONDA NELATON #6</t>
+          <t>SONDA FOLEY 2 VIAS BAL #18</t>
         </is>
       </c>
       <c r="C1502" t="inlineStr"/>
       <c r="D1502" t="inlineStr"/>
       <c r="E1502" t="n">
-        <v>2500</v>
+        <v>7500</v>
       </c>
       <c r="F1502" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1502" t="n">
         <v>0</v>
@@ -80290,21 +80290,21 @@
     <row r="1503">
       <c r="A1503" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>SPRAY NASAL MOMETASONA 18ML</t>
+          <t>SONDA NELATON #6</t>
         </is>
       </c>
       <c r="C1503" t="inlineStr"/>
       <c r="D1503" t="inlineStr"/>
       <c r="E1503" t="n">
-        <v>36900</v>
+        <v>2500</v>
       </c>
       <c r="F1503" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1503" t="n">
         <v>0</v>
@@ -80340,21 +80340,21 @@
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>suerox mora azul x630ml</t>
+          <t>SPRAY NASAL MOMETASONA 18ML</t>
         </is>
       </c>
       <c r="C1504" t="inlineStr"/>
       <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="n">
-        <v>5882.352941</v>
+        <v>36900</v>
       </c>
       <c r="F1504" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1504" t="n">
         <v>0</v>
@@ -80382,7 +80382,7 @@
       </c>
       <c r="M1504" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1504" t="inlineStr"/>
@@ -80390,25 +80390,21 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
-        </is>
-      </c>
-      <c r="C1505" t="inlineStr">
-        <is>
-          <t>7703712035034</t>
-        </is>
-      </c>
+          <t>suerox mora azul x630ml</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr"/>
       <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="n">
-        <v>14800</v>
+        <v>5882.352941</v>
       </c>
       <c r="F1505" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1505" t="n">
         <v>0</v>
@@ -80436,7 +80432,7 @@
       </c>
       <c r="M1505" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1505" t="inlineStr"/>
@@ -80444,21 +80440,25 @@
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
-        </is>
-      </c>
-      <c r="C1506" t="inlineStr"/>
+          <t>SULFADIAZINA DE PLATA 1% 30GR COASPHARMA</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>7703712035034</t>
+        </is>
+      </c>
       <c r="D1506" t="inlineStr"/>
       <c r="E1506" t="n">
-        <v>3781.512605</v>
+        <v>14800</v>
       </c>
       <c r="F1506" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1506" t="n">
         <v>0</v>
@@ -80486,7 +80486,7 @@
       </c>
       <c r="M1506" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="N1506" t="inlineStr"/>
@@ -80494,21 +80494,21 @@
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
+          <t>SULFATO DE MAGNESIO 200GR YOMA</t>
         </is>
       </c>
       <c r="C1507" t="inlineStr"/>
       <c r="D1507" t="inlineStr"/>
       <c r="E1507" t="n">
-        <v>5210.084034</v>
+        <v>3781.512605</v>
       </c>
       <c r="F1507" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1507" t="n">
         <v>0</v>
@@ -80544,21 +80544,21 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
+          <t>SULFATO DE MAGNESIO 400GR YOMA</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr"/>
       <c r="D1508" t="inlineStr"/>
       <c r="E1508" t="n">
-        <v>8319.327730999999</v>
+        <v>5210.084034</v>
       </c>
       <c r="F1508" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1508" t="n">
         <v>0</v>
@@ -80594,18 +80594,18 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>SULFATO FERROSO JARABE 120ML LAPROFF</t>
+          <t>SULFATO DE MAGNESIO 500 DROQUIMICOS</t>
         </is>
       </c>
       <c r="C1509" t="inlineStr"/>
       <c r="D1509" t="inlineStr"/>
       <c r="E1509" t="n">
-        <v>9500</v>
+        <v>8319.327730999999</v>
       </c>
       <c r="F1509" t="n">
         <v>1</v>
@@ -80636,7 +80636,7 @@
       </c>
       <c r="M1509" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="N1509" t="inlineStr"/>
@@ -80644,18 +80644,18 @@
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>SULTAMICILINA 375MG X10 TBL - COASPH</t>
+          <t>SULFATO FERROSO JARABE 1